--- a/nba/public/data/nba_matchup_probs.xlsx
+++ b/nba/public/data/nba_matchup_probs.xlsx
@@ -678,22 +678,22 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.7469</v>
+        <v>0.7643</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6162</v>
+        <v>0.6377</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6816</v>
+        <v>0.701</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2531</v>
+        <v>0.2357</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3838</v>
+        <v>0.3623</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3184</v>
+        <v>0.299</v>
       </c>
       <c r="M5" t="n">
         <v>155</v>
@@ -732,22 +732,22 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.8051</v>
+        <v>0.8074</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6928</v>
+        <v>0.6974</v>
       </c>
       <c r="I6" t="n">
-        <v>0.749</v>
+        <v>0.7524</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1949</v>
+        <v>0.1926</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3072</v>
+        <v>0.3026</v>
       </c>
       <c r="L6" t="n">
-        <v>0.251</v>
+        <v>0.2476</v>
       </c>
       <c r="M6" t="n">
         <v>155</v>
@@ -786,22 +786,22 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.4636</v>
+        <v>0.4976</v>
       </c>
       <c r="H7" t="n">
-        <v>0.311</v>
+        <v>0.3418</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3873</v>
+        <v>0.4197</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5364</v>
+        <v>0.5024</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6582</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6127</v>
+        <v>0.5803</v>
       </c>
       <c r="M7" t="n">
         <v>155</v>
@@ -840,22 +840,22 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.706</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5534</v>
+        <v>0.5535</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6297</v>
+        <v>0.6298</v>
       </c>
       <c r="J8" t="n">
-        <v>0.294</v>
+        <v>0.2939</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4466</v>
+        <v>0.4465</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3703</v>
+        <v>0.3702</v>
       </c>
       <c r="M8" t="n">
         <v>155</v>
@@ -894,22 +894,22 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.5958</v>
+        <v>0.5978</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4364</v>
+        <v>0.439</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5161</v>
+        <v>0.5184</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4042</v>
+        <v>0.4022</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5636</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4839</v>
+        <v>0.4816</v>
       </c>
       <c r="M9" t="n">
         <v>155</v>
@@ -1002,22 +1002,22 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.5192</v>
+        <v>0.5369</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3538</v>
+        <v>0.3671</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4365</v>
+        <v>0.452</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4808</v>
+        <v>0.4631</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6462</v>
+        <v>0.6329</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5635</v>
+        <v>0.548</v>
       </c>
       <c r="M11" t="n">
         <v>155</v>
@@ -1110,22 +1110,22 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.7806999999999999</v>
+        <v>0.7975</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6546</v>
+        <v>0.6834</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7176</v>
+        <v>0.7405</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2193</v>
+        <v>0.2025</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3454</v>
+        <v>0.3166</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2824</v>
+        <v>0.2595</v>
       </c>
       <c r="M13" t="n">
         <v>155</v>
@@ -1164,22 +1164,22 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.5962</v>
+        <v>0.6148</v>
       </c>
       <c r="H14" t="n">
-        <v>0.432</v>
+        <v>0.4484</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5141</v>
+        <v>0.5316</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4038</v>
+        <v>0.3852</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5516</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4859</v>
+        <v>0.4684</v>
       </c>
       <c r="M14" t="n">
         <v>155</v>
@@ -1434,22 +1434,22 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.7486</v>
+        <v>0.729</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6024</v>
+        <v>0.5786</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6755</v>
+        <v>0.6538</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2514</v>
+        <v>0.271</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3976</v>
+        <v>0.4214</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3245</v>
+        <v>0.3462</v>
       </c>
       <c r="M19" t="n">
         <v>155</v>
@@ -1596,22 +1596,22 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.8265</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7216</v>
+        <v>0.7239</v>
       </c>
       <c r="I22" t="n">
-        <v>0.774</v>
+        <v>0.776</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1735</v>
+        <v>0.1719</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2784</v>
+        <v>0.2761</v>
       </c>
       <c r="L22" t="n">
-        <v>0.226</v>
+        <v>0.224</v>
       </c>
       <c r="M22" t="n">
         <v>155</v>
@@ -1758,22 +1758,22 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.6309</v>
+        <v>0.6344</v>
       </c>
       <c r="H25" t="n">
-        <v>0.471</v>
+        <v>0.4767</v>
       </c>
       <c r="I25" t="n">
-        <v>0.551</v>
+        <v>0.5556</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3691</v>
+        <v>0.3656</v>
       </c>
       <c r="K25" t="n">
-        <v>0.529</v>
+        <v>0.5233</v>
       </c>
       <c r="L25" t="n">
-        <v>0.449</v>
+        <v>0.4444</v>
       </c>
       <c r="M25" t="n">
         <v>155</v>
@@ -1812,22 +1812,22 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.8287</v>
+        <v>0.8323</v>
       </c>
       <c r="H26" t="n">
-        <v>0.723</v>
+        <v>0.731</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7758</v>
+        <v>0.7816</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1713</v>
+        <v>0.1677</v>
       </c>
       <c r="K26" t="n">
-        <v>0.277</v>
+        <v>0.269</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2242</v>
+        <v>0.2184</v>
       </c>
       <c r="M26" t="n">
         <v>155</v>
@@ -1974,22 +1974,22 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.5676</v>
+        <v>0.5755</v>
       </c>
       <c r="H29" t="n">
-        <v>0.4061</v>
+        <v>0.4139</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4868</v>
+        <v>0.4947</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4324</v>
+        <v>0.4245</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5939</v>
+        <v>0.5861</v>
       </c>
       <c r="L29" t="n">
-        <v>0.5132</v>
+        <v>0.5053</v>
       </c>
       <c r="M29" t="n">
         <v>155</v>
@@ -2028,22 +2028,22 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.541</v>
+        <v>0.5429</v>
       </c>
       <c r="H30" t="n">
-        <v>0.4093</v>
+        <v>0.4112</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4752</v>
+        <v>0.477</v>
       </c>
       <c r="J30" t="n">
-        <v>0.459</v>
+        <v>0.4571</v>
       </c>
       <c r="K30" t="n">
-        <v>0.5907</v>
+        <v>0.5888</v>
       </c>
       <c r="L30" t="n">
-        <v>0.5248</v>
+        <v>0.523</v>
       </c>
       <c r="M30" t="n">
         <v>155</v>
@@ -2190,22 +2190,22 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.7997</v>
+        <v>0.8158</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6886</v>
+        <v>0.7089</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7442</v>
+        <v>0.7624</v>
       </c>
       <c r="J33" t="n">
-        <v>0.2003</v>
+        <v>0.1842</v>
       </c>
       <c r="K33" t="n">
-        <v>0.3114</v>
+        <v>0.2911</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2558</v>
+        <v>0.2376</v>
       </c>
       <c r="M33" t="n">
         <v>155</v>
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.8471</v>
+        <v>0.8506</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7523</v>
+        <v>0.7615</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7997</v>
+        <v>0.806</v>
       </c>
       <c r="J34" t="n">
-        <v>0.1529</v>
+        <v>0.1494</v>
       </c>
       <c r="K34" t="n">
-        <v>0.2477</v>
+        <v>0.2385</v>
       </c>
       <c r="L34" t="n">
-        <v>0.2003</v>
+        <v>0.194</v>
       </c>
       <c r="M34" t="n">
         <v>155</v>
@@ -2298,22 +2298,22 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.6126</v>
+        <v>0.622</v>
       </c>
       <c r="H35" t="n">
-        <v>0.4454</v>
+        <v>0.4594</v>
       </c>
       <c r="I35" t="n">
-        <v>0.529</v>
+        <v>0.5407</v>
       </c>
       <c r="J35" t="n">
-        <v>0.3874</v>
+        <v>0.378</v>
       </c>
       <c r="K35" t="n">
-        <v>0.5546</v>
+        <v>0.5406</v>
       </c>
       <c r="L35" t="n">
-        <v>0.471</v>
+        <v>0.4593</v>
       </c>
       <c r="M35" t="n">
         <v>155</v>
@@ -2514,22 +2514,22 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.6374</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4861</v>
+        <v>0.4932</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5618</v>
+        <v>0.5679</v>
       </c>
       <c r="J39" t="n">
-        <v>0.3626</v>
+        <v>0.3574</v>
       </c>
       <c r="K39" t="n">
-        <v>0.5139</v>
+        <v>0.5068</v>
       </c>
       <c r="L39" t="n">
-        <v>0.4382</v>
+        <v>0.4321</v>
       </c>
       <c r="M39" t="n">
         <v>155</v>
@@ -2622,22 +2622,22 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.8481</v>
+        <v>0.8574000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>0.7551</v>
+        <v>0.7677</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8016</v>
+        <v>0.8126</v>
       </c>
       <c r="J41" t="n">
-        <v>0.1519</v>
+        <v>0.1426</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2449</v>
+        <v>0.2323</v>
       </c>
       <c r="L41" t="n">
-        <v>0.1984</v>
+        <v>0.1874</v>
       </c>
       <c r="M41" t="n">
         <v>155</v>
@@ -2676,22 +2676,22 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.6788</v>
+        <v>0.697</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5362</v>
+        <v>0.5583</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6075</v>
+        <v>0.6276</v>
       </c>
       <c r="J42" t="n">
-        <v>0.3212</v>
+        <v>0.303</v>
       </c>
       <c r="K42" t="n">
-        <v>0.4638</v>
+        <v>0.4417</v>
       </c>
       <c r="L42" t="n">
-        <v>0.3925</v>
+        <v>0.3724</v>
       </c>
       <c r="M42" t="n">
         <v>155</v>
@@ -2838,22 +2838,22 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.7867</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>0.6592</v>
+        <v>0.6607</v>
       </c>
       <c r="I45" t="n">
-        <v>0.723</v>
+        <v>0.7242</v>
       </c>
       <c r="J45" t="n">
-        <v>0.2133</v>
+        <v>0.2122</v>
       </c>
       <c r="K45" t="n">
-        <v>0.3408</v>
+        <v>0.3393</v>
       </c>
       <c r="L45" t="n">
-        <v>0.277</v>
+        <v>0.2758</v>
       </c>
       <c r="M45" t="n">
         <v>155</v>
@@ -2892,22 +2892,22 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.8658</v>
       </c>
       <c r="H46" t="n">
         <v>0.7788</v>
       </c>
       <c r="I46" t="n">
-        <v>0.8216</v>
+        <v>0.8223</v>
       </c>
       <c r="J46" t="n">
-        <v>0.1356</v>
+        <v>0.1342</v>
       </c>
       <c r="K46" t="n">
         <v>0.2212</v>
       </c>
       <c r="L46" t="n">
-        <v>0.1784</v>
+        <v>0.1777</v>
       </c>
       <c r="M46" t="n">
         <v>155</v>
@@ -2946,22 +2946,22 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.8048</v>
+        <v>0.7862</v>
       </c>
       <c r="H47" t="n">
-        <v>0.7063</v>
+        <v>0.6846</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>0.1952</v>
+        <v>0.2138</v>
       </c>
       <c r="K47" t="n">
-        <v>0.2937</v>
+        <v>0.3154</v>
       </c>
       <c r="L47" t="n">
-        <v>0.2445</v>
+        <v>0.2646</v>
       </c>
       <c r="M47" t="n">
         <v>155</v>
@@ -3108,22 +3108,22 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.8598</v>
+        <v>0.8608</v>
       </c>
       <c r="H50" t="n">
         <v>0.7683</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8146</v>
       </c>
       <c r="J50" t="n">
-        <v>0.1402</v>
+        <v>0.1392</v>
       </c>
       <c r="K50" t="n">
         <v>0.2317</v>
       </c>
       <c r="L50" t="n">
-        <v>0.186</v>
+        <v>0.1854</v>
       </c>
       <c r="M50" t="n">
         <v>155</v>
@@ -3162,22 +3162,22 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.5431</v>
       </c>
       <c r="H51" t="n">
-        <v>0.3986</v>
+        <v>0.3988</v>
       </c>
       <c r="I51" t="n">
-        <v>0.4707</v>
+        <v>0.471</v>
       </c>
       <c r="J51" t="n">
-        <v>0.4572</v>
+        <v>0.4569</v>
       </c>
       <c r="K51" t="n">
-        <v>0.6014</v>
+        <v>0.6012</v>
       </c>
       <c r="L51" t="n">
-        <v>0.5293</v>
+        <v>0.529</v>
       </c>
       <c r="M51" t="n">
         <v>155</v>
@@ -3270,22 +3270,22 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.7265</v>
+        <v>0.7356</v>
       </c>
       <c r="H53" t="n">
-        <v>0.5919</v>
+        <v>0.6045</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6592</v>
+        <v>0.67</v>
       </c>
       <c r="J53" t="n">
-        <v>0.2735</v>
+        <v>0.2644</v>
       </c>
       <c r="K53" t="n">
-        <v>0.4081</v>
+        <v>0.3955</v>
       </c>
       <c r="L53" t="n">
-        <v>0.3408</v>
+        <v>0.33</v>
       </c>
       <c r="M53" t="n">
         <v>155</v>
@@ -3594,22 +3594,22 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.7779</v>
+        <v>0.7786</v>
       </c>
       <c r="H59" t="n">
-        <v>0.6666</v>
+        <v>0.6674</v>
       </c>
       <c r="I59" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.723</v>
       </c>
       <c r="J59" t="n">
-        <v>0.2221</v>
+        <v>0.2214</v>
       </c>
       <c r="K59" t="n">
-        <v>0.3334</v>
+        <v>0.3326</v>
       </c>
       <c r="L59" t="n">
-        <v>0.2777</v>
+        <v>0.277</v>
       </c>
       <c r="M59" t="n">
         <v>155</v>
@@ -3648,22 +3648,22 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.7823</v>
+        <v>0.7985</v>
       </c>
       <c r="H60" t="n">
-        <v>0.6811</v>
+        <v>0.7012</v>
       </c>
       <c r="I60" t="n">
-        <v>0.7317</v>
+        <v>0.7498</v>
       </c>
       <c r="J60" t="n">
-        <v>0.2177</v>
+        <v>0.2015</v>
       </c>
       <c r="K60" t="n">
-        <v>0.3189</v>
+        <v>0.2988</v>
       </c>
       <c r="L60" t="n">
-        <v>0.2683</v>
+        <v>0.2502</v>
       </c>
       <c r="M60" t="n">
         <v>155</v>
@@ -3702,22 +3702,22 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.838</v>
+        <v>0.8399</v>
       </c>
       <c r="H61" t="n">
-        <v>0.7504</v>
+        <v>0.7514</v>
       </c>
       <c r="I61" t="n">
-        <v>0.7942</v>
+        <v>0.7956</v>
       </c>
       <c r="J61" t="n">
-        <v>0.162</v>
+        <v>0.1601</v>
       </c>
       <c r="K61" t="n">
-        <v>0.2496</v>
+        <v>0.2486</v>
       </c>
       <c r="L61" t="n">
-        <v>0.2058</v>
+        <v>0.2044</v>
       </c>
       <c r="M61" t="n">
         <v>155</v>
@@ -3756,22 +3756,22 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.5919</v>
+        <v>0.5991</v>
       </c>
       <c r="H62" t="n">
-        <v>0.4315</v>
+        <v>0.448</v>
       </c>
       <c r="I62" t="n">
-        <v>0.5117</v>
+        <v>0.5236</v>
       </c>
       <c r="J62" t="n">
-        <v>0.4081</v>
+        <v>0.4009</v>
       </c>
       <c r="K62" t="n">
-        <v>0.5685</v>
+        <v>0.552</v>
       </c>
       <c r="L62" t="n">
-        <v>0.4883</v>
+        <v>0.4764</v>
       </c>
       <c r="M62" t="n">
         <v>155</v>
@@ -3813,19 +3813,19 @@
         <v>0.7574</v>
       </c>
       <c r="H63" t="n">
-        <v>0.6427</v>
+        <v>0.6448</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7000999999999999</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="J63" t="n">
         <v>0.2426</v>
       </c>
       <c r="K63" t="n">
-        <v>0.3573</v>
+        <v>0.3552</v>
       </c>
       <c r="L63" t="n">
-        <v>0.2999</v>
+        <v>0.2989</v>
       </c>
       <c r="M63" t="n">
         <v>155</v>
@@ -3864,22 +3864,22 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.6748</v>
+        <v>0.6765</v>
       </c>
       <c r="H64" t="n">
-        <v>0.52</v>
+        <v>0.5228</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5974</v>
+        <v>0.5996</v>
       </c>
       <c r="J64" t="n">
-        <v>0.3252</v>
+        <v>0.3235</v>
       </c>
       <c r="K64" t="n">
-        <v>0.48</v>
+        <v>0.4772</v>
       </c>
       <c r="L64" t="n">
-        <v>0.4026</v>
+        <v>0.4004</v>
       </c>
       <c r="M64" t="n">
         <v>155</v>
@@ -3972,22 +3972,22 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.6063</v>
+        <v>0.6075</v>
       </c>
       <c r="H66" t="n">
-        <v>0.4542</v>
+        <v>0.4575</v>
       </c>
       <c r="I66" t="n">
-        <v>0.5302</v>
+        <v>0.5325</v>
       </c>
       <c r="J66" t="n">
-        <v>0.3937</v>
+        <v>0.3925</v>
       </c>
       <c r="K66" t="n">
-        <v>0.5458</v>
+        <v>0.5425</v>
       </c>
       <c r="L66" t="n">
-        <v>0.4698</v>
+        <v>0.4675</v>
       </c>
       <c r="M66" t="n">
         <v>155</v>
@@ -4026,22 +4026,22 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.7083</v>
+        <v>0.71</v>
       </c>
       <c r="H67" t="n">
-        <v>0.5714</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6398</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="J67" t="n">
-        <v>0.2917</v>
+        <v>0.29</v>
       </c>
       <c r="K67" t="n">
-        <v>0.4286</v>
+        <v>0.4269</v>
       </c>
       <c r="L67" t="n">
-        <v>0.3602</v>
+        <v>0.3584</v>
       </c>
       <c r="M67" t="n">
         <v>155</v>
@@ -4080,22 +4080,22 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0.8396</v>
+        <v>0.8494</v>
       </c>
       <c r="H68" t="n">
-        <v>0.7542</v>
+        <v>0.7669</v>
       </c>
       <c r="I68" t="n">
-        <v>0.7969000000000001</v>
+        <v>0.8082</v>
       </c>
       <c r="J68" t="n">
-        <v>0.1604</v>
+        <v>0.1506</v>
       </c>
       <c r="K68" t="n">
-        <v>0.2458</v>
+        <v>0.2331</v>
       </c>
       <c r="L68" t="n">
-        <v>0.2031</v>
+        <v>0.1918</v>
       </c>
       <c r="M68" t="n">
         <v>155</v>
@@ -4134,22 +4134,22 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.6661</v>
+        <v>0.6765</v>
       </c>
       <c r="H69" t="n">
-        <v>0.5225</v>
+        <v>0.5351</v>
       </c>
       <c r="I69" t="n">
-        <v>0.5943000000000001</v>
+        <v>0.6058</v>
       </c>
       <c r="J69" t="n">
-        <v>0.3339</v>
+        <v>0.3235</v>
       </c>
       <c r="K69" t="n">
-        <v>0.4775</v>
+        <v>0.4649</v>
       </c>
       <c r="L69" t="n">
-        <v>0.4057</v>
+        <v>0.3942</v>
       </c>
       <c r="M69" t="n">
         <v>155</v>
@@ -4245,19 +4245,19 @@
         <v>0.5676</v>
       </c>
       <c r="H71" t="n">
-        <v>0.4262</v>
+        <v>0.4269</v>
       </c>
       <c r="I71" t="n">
-        <v>0.4969</v>
+        <v>0.4972</v>
       </c>
       <c r="J71" t="n">
         <v>0.4324</v>
       </c>
       <c r="K71" t="n">
-        <v>0.5738</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="L71" t="n">
-        <v>0.5031</v>
+        <v>0.5028</v>
       </c>
       <c r="M71" t="n">
         <v>155</v>
@@ -4296,22 +4296,22 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.7471</v>
+        <v>0.7494</v>
       </c>
       <c r="H72" t="n">
-        <v>0.624</v>
+        <v>0.6269</v>
       </c>
       <c r="I72" t="n">
-        <v>0.6856</v>
+        <v>0.6882</v>
       </c>
       <c r="J72" t="n">
-        <v>0.2529</v>
+        <v>0.2506</v>
       </c>
       <c r="K72" t="n">
-        <v>0.376</v>
+        <v>0.3731</v>
       </c>
       <c r="L72" t="n">
-        <v>0.3144</v>
+        <v>0.3118</v>
       </c>
       <c r="M72" t="n">
         <v>155</v>
@@ -4404,22 +4404,22 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.7723</v>
       </c>
       <c r="H74" t="n">
-        <v>0.6724</v>
+        <v>0.6586</v>
       </c>
       <c r="I74" t="n">
-        <v>0.7281</v>
+        <v>0.7154</v>
       </c>
       <c r="J74" t="n">
-        <v>0.2162</v>
+        <v>0.2277</v>
       </c>
       <c r="K74" t="n">
-        <v>0.3276</v>
+        <v>0.3414</v>
       </c>
       <c r="L74" t="n">
-        <v>0.2719</v>
+        <v>0.2846</v>
       </c>
       <c r="M74" t="n">
         <v>155</v>
@@ -4512,22 +4512,22 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.7477</v>
+        <v>0.7487</v>
       </c>
       <c r="H76" t="n">
-        <v>0.6197</v>
+        <v>0.621</v>
       </c>
       <c r="I76" t="n">
-        <v>0.6837</v>
+        <v>0.6848</v>
       </c>
       <c r="J76" t="n">
-        <v>0.2523</v>
+        <v>0.2513</v>
       </c>
       <c r="K76" t="n">
-        <v>0.3803</v>
+        <v>0.379</v>
       </c>
       <c r="L76" t="n">
-        <v>0.3163</v>
+        <v>0.3152</v>
       </c>
       <c r="M76" t="n">
         <v>155</v>
@@ -4620,22 +4620,22 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.54</v>
+        <v>0.5434</v>
       </c>
       <c r="H78" t="n">
-        <v>0.3979</v>
+        <v>0.4044</v>
       </c>
       <c r="I78" t="n">
-        <v>0.469</v>
+        <v>0.4739</v>
       </c>
       <c r="J78" t="n">
-        <v>0.46</v>
+        <v>0.4566</v>
       </c>
       <c r="K78" t="n">
-        <v>0.6021</v>
+        <v>0.5956</v>
       </c>
       <c r="L78" t="n">
-        <v>0.531</v>
+        <v>0.5261</v>
       </c>
       <c r="M78" t="n">
         <v>155</v>
@@ -4728,22 +4728,22 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.7024</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="H80" t="n">
-        <v>0.5799</v>
+        <v>0.5887</v>
       </c>
       <c r="I80" t="n">
-        <v>0.6412</v>
+        <v>0.65</v>
       </c>
       <c r="J80" t="n">
-        <v>0.2976</v>
+        <v>0.2888</v>
       </c>
       <c r="K80" t="n">
-        <v>0.4201</v>
+        <v>0.4113</v>
       </c>
       <c r="L80" t="n">
-        <v>0.3588</v>
+        <v>0.35</v>
       </c>
       <c r="M80" t="n">
         <v>155</v>
@@ -4836,22 +4836,22 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0.836</v>
+        <v>0.8379</v>
       </c>
       <c r="H82" t="n">
-        <v>0.742</v>
+        <v>0.7446</v>
       </c>
       <c r="I82" t="n">
-        <v>0.789</v>
+        <v>0.7912</v>
       </c>
       <c r="J82" t="n">
-        <v>0.164</v>
+        <v>0.1621</v>
       </c>
       <c r="K82" t="n">
-        <v>0.258</v>
+        <v>0.2554</v>
       </c>
       <c r="L82" t="n">
-        <v>0.211</v>
+        <v>0.2088</v>
       </c>
       <c r="M82" t="n">
         <v>155</v>
@@ -4944,22 +4944,22 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.5976</v>
+        <v>0.6026</v>
       </c>
       <c r="H84" t="n">
-        <v>0.4735</v>
+        <v>0.4787</v>
       </c>
       <c r="I84" t="n">
-        <v>0.5356</v>
+        <v>0.5407</v>
       </c>
       <c r="J84" t="n">
-        <v>0.4024</v>
+        <v>0.3974</v>
       </c>
       <c r="K84" t="n">
-        <v>0.5265</v>
+        <v>0.5213</v>
       </c>
       <c r="L84" t="n">
-        <v>0.4644</v>
+        <v>0.4593</v>
       </c>
       <c r="M84" t="n">
         <v>155</v>
@@ -4998,22 +4998,22 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.6389</v>
       </c>
       <c r="H85" t="n">
-        <v>0.498</v>
+        <v>0.4993</v>
       </c>
       <c r="I85" t="n">
-        <v>0.5678</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="J85" t="n">
-        <v>0.3624</v>
+        <v>0.3611</v>
       </c>
       <c r="K85" t="n">
-        <v>0.502</v>
+        <v>0.5007</v>
       </c>
       <c r="L85" t="n">
-        <v>0.4322</v>
+        <v>0.4309</v>
       </c>
       <c r="M85" t="n">
         <v>155</v>
@@ -5052,22 +5052,22 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>0.5809</v>
+        <v>0.6015</v>
       </c>
       <c r="H86" t="n">
-        <v>0.4271</v>
+        <v>0.4468</v>
       </c>
       <c r="I86" t="n">
-        <v>0.504</v>
+        <v>0.5242</v>
       </c>
       <c r="J86" t="n">
-        <v>0.4191</v>
+        <v>0.3985</v>
       </c>
       <c r="K86" t="n">
-        <v>0.5729</v>
+        <v>0.5532</v>
       </c>
       <c r="L86" t="n">
-        <v>0.496</v>
+        <v>0.4758</v>
       </c>
       <c r="M86" t="n">
         <v>155</v>
@@ -5106,22 +5106,22 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>0.6711</v>
+        <v>0.6737</v>
       </c>
       <c r="H87" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.5264</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5979</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
-        <v>0.3289</v>
+        <v>0.3263</v>
       </c>
       <c r="K87" t="n">
-        <v>0.4753</v>
+        <v>0.4736</v>
       </c>
       <c r="L87" t="n">
-        <v>0.4021</v>
+        <v>0.4</v>
       </c>
       <c r="M87" t="n">
         <v>155</v>
@@ -5160,22 +5160,22 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0.297</v>
+        <v>0.3119</v>
       </c>
       <c r="H88" t="n">
-        <v>0.1961</v>
+        <v>0.2037</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2466</v>
+        <v>0.2578</v>
       </c>
       <c r="J88" t="n">
-        <v>0.703</v>
+        <v>0.6881</v>
       </c>
       <c r="K88" t="n">
-        <v>0.8038999999999999</v>
+        <v>0.7963</v>
       </c>
       <c r="L88" t="n">
-        <v>0.7534</v>
+        <v>0.7422</v>
       </c>
       <c r="M88" t="n">
         <v>155</v>
@@ -5376,22 +5376,22 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>0.3139</v>
+        <v>0.3212</v>
       </c>
       <c r="H92" t="n">
-        <v>0.2116</v>
+        <v>0.2148</v>
       </c>
       <c r="I92" t="n">
-        <v>0.2628</v>
+        <v>0.268</v>
       </c>
       <c r="J92" t="n">
-        <v>0.6861</v>
+        <v>0.6788</v>
       </c>
       <c r="K92" t="n">
-        <v>0.7884</v>
+        <v>0.7852</v>
       </c>
       <c r="L92" t="n">
-        <v>0.7372</v>
+        <v>0.732</v>
       </c>
       <c r="M92" t="n">
         <v>155</v>
@@ -5430,22 +5430,22 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>0.4843</v>
+        <v>0.4831</v>
       </c>
       <c r="H93" t="n">
-        <v>0.3373</v>
+        <v>0.3363</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4108</v>
+        <v>0.4097</v>
       </c>
       <c r="J93" t="n">
-        <v>0.5157</v>
+        <v>0.5169</v>
       </c>
       <c r="K93" t="n">
-        <v>0.6627</v>
+        <v>0.6637</v>
       </c>
       <c r="L93" t="n">
-        <v>0.5891999999999999</v>
+        <v>0.5903</v>
       </c>
       <c r="M93" t="n">
         <v>155</v>
@@ -5484,22 +5484,22 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>0.6682</v>
+        <v>0.6824</v>
       </c>
       <c r="H94" t="n">
-        <v>0.5164</v>
+        <v>0.5355</v>
       </c>
       <c r="I94" t="n">
-        <v>0.5923</v>
+        <v>0.609</v>
       </c>
       <c r="J94" t="n">
-        <v>0.3318</v>
+        <v>0.3176</v>
       </c>
       <c r="K94" t="n">
-        <v>0.4836</v>
+        <v>0.4645</v>
       </c>
       <c r="L94" t="n">
-        <v>0.4077</v>
+        <v>0.391</v>
       </c>
       <c r="M94" t="n">
         <v>155</v>
@@ -5538,22 +5538,22 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>0.4206</v>
+        <v>0.4312</v>
       </c>
       <c r="H95" t="n">
-        <v>0.2742</v>
+        <v>0.2882</v>
       </c>
       <c r="I95" t="n">
-        <v>0.3474</v>
+        <v>0.3597</v>
       </c>
       <c r="J95" t="n">
-        <v>0.5794</v>
+        <v>0.5688</v>
       </c>
       <c r="K95" t="n">
-        <v>0.7258</v>
+        <v>0.7118</v>
       </c>
       <c r="L95" t="n">
-        <v>0.6526</v>
+        <v>0.6403</v>
       </c>
       <c r="M95" t="n">
         <v>155</v>
@@ -5808,22 +5808,22 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0.5737</v>
+        <v>0.5448</v>
       </c>
       <c r="H100" t="n">
-        <v>0.4209</v>
+        <v>0.3894</v>
       </c>
       <c r="I100" t="n">
-        <v>0.4973</v>
+        <v>0.4671</v>
       </c>
       <c r="J100" t="n">
-        <v>0.4263</v>
+        <v>0.4552</v>
       </c>
       <c r="K100" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.6106</v>
       </c>
       <c r="L100" t="n">
-        <v>0.5027</v>
+        <v>0.5329</v>
       </c>
       <c r="M100" t="n">
         <v>155</v>
@@ -6078,22 +6078,22 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>0.2557</v>
+        <v>0.2552</v>
       </c>
       <c r="H105" t="n">
-        <v>0.155</v>
+        <v>0.1547</v>
       </c>
       <c r="I105" t="n">
-        <v>0.2053</v>
+        <v>0.205</v>
       </c>
       <c r="J105" t="n">
-        <v>0.7443</v>
+        <v>0.7448</v>
       </c>
       <c r="K105" t="n">
-        <v>0.845</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="L105" t="n">
-        <v>0.7947</v>
+        <v>0.795</v>
       </c>
       <c r="M105" t="n">
         <v>155</v>
@@ -6132,22 +6132,22 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>0.4856</v>
+        <v>0.4907</v>
       </c>
       <c r="H106" t="n">
-        <v>0.3409</v>
+        <v>0.3434</v>
       </c>
       <c r="I106" t="n">
-        <v>0.4132</v>
+        <v>0.417</v>
       </c>
       <c r="J106" t="n">
-        <v>0.5144</v>
+        <v>0.5093</v>
       </c>
       <c r="K106" t="n">
-        <v>0.6591</v>
+        <v>0.6566</v>
       </c>
       <c r="L106" t="n">
-        <v>0.5868</v>
+        <v>0.583</v>
       </c>
       <c r="M106" t="n">
         <v>155</v>
@@ -6294,22 +6294,22 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>0.7952</v>
+        <v>0.7984</v>
       </c>
       <c r="H109" t="n">
-        <v>0.6825</v>
+        <v>0.6867</v>
       </c>
       <c r="I109" t="n">
-        <v>0.7388</v>
+        <v>0.7426</v>
       </c>
       <c r="J109" t="n">
-        <v>0.2048</v>
+        <v>0.2016</v>
       </c>
       <c r="K109" t="n">
-        <v>0.3175</v>
+        <v>0.3133</v>
       </c>
       <c r="L109" t="n">
-        <v>0.2612</v>
+        <v>0.2574</v>
       </c>
       <c r="M109" t="n">
         <v>155</v>
@@ -6402,22 +6402,22 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>0.3919</v>
+        <v>0.3875</v>
       </c>
       <c r="H111" t="n">
-        <v>0.2637</v>
+        <v>0.2602</v>
       </c>
       <c r="I111" t="n">
-        <v>0.3278</v>
+        <v>0.3238</v>
       </c>
       <c r="J111" t="n">
-        <v>0.6081</v>
+        <v>0.6125</v>
       </c>
       <c r="K111" t="n">
-        <v>0.7363</v>
+        <v>0.7398</v>
       </c>
       <c r="L111" t="n">
-        <v>0.6722</v>
+        <v>0.6762</v>
       </c>
       <c r="M111" t="n">
         <v>155</v>
@@ -6456,22 +6456,22 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>0.669</v>
+        <v>0.6482</v>
       </c>
       <c r="H112" t="n">
-        <v>0.51</v>
+        <v>0.4862</v>
       </c>
       <c r="I112" t="n">
-        <v>0.5895</v>
+        <v>0.5672</v>
       </c>
       <c r="J112" t="n">
-        <v>0.331</v>
+        <v>0.3518</v>
       </c>
       <c r="K112" t="n">
-        <v>0.49</v>
+        <v>0.5138</v>
       </c>
       <c r="L112" t="n">
-        <v>0.4105</v>
+        <v>0.4328</v>
       </c>
       <c r="M112" t="n">
         <v>155</v>
@@ -6510,22 +6510,22 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>0.3044</v>
+        <v>0.2989</v>
       </c>
       <c r="H113" t="n">
-        <v>0.2076</v>
+        <v>0.2048</v>
       </c>
       <c r="I113" t="n">
-        <v>0.256</v>
+        <v>0.2518</v>
       </c>
       <c r="J113" t="n">
-        <v>0.6956</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="K113" t="n">
-        <v>0.7924</v>
+        <v>0.7952</v>
       </c>
       <c r="L113" t="n">
-        <v>0.744</v>
+        <v>0.7482</v>
       </c>
       <c r="M113" t="n">
         <v>155</v>
@@ -6564,22 +6564,22 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>0.5336</v>
+        <v>0.5155</v>
       </c>
       <c r="H114" t="n">
-        <v>0.3822</v>
+        <v>0.3665</v>
       </c>
       <c r="I114" t="n">
-        <v>0.4579</v>
+        <v>0.441</v>
       </c>
       <c r="J114" t="n">
-        <v>0.4664</v>
+        <v>0.4845</v>
       </c>
       <c r="K114" t="n">
-        <v>0.6178</v>
+        <v>0.6335</v>
       </c>
       <c r="L114" t="n">
-        <v>0.5421</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="M114" t="n">
         <v>155</v>
@@ -6618,22 +6618,22 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>0.4497</v>
+        <v>0.4294</v>
       </c>
       <c r="H115" t="n">
-        <v>0.3029</v>
+        <v>0.2824</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3763</v>
+        <v>0.3559</v>
       </c>
       <c r="J115" t="n">
-        <v>0.5503</v>
+        <v>0.5706</v>
       </c>
       <c r="K115" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.7176</v>
       </c>
       <c r="L115" t="n">
-        <v>0.6237</v>
+        <v>0.6441</v>
       </c>
       <c r="M115" t="n">
         <v>155</v>
@@ -6672,22 +6672,22 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>0.3851</v>
+        <v>0.3469</v>
       </c>
       <c r="H116" t="n">
-        <v>0.2551</v>
+        <v>0.2344</v>
       </c>
       <c r="I116" t="n">
-        <v>0.3201</v>
+        <v>0.2906</v>
       </c>
       <c r="J116" t="n">
-        <v>0.6149</v>
+        <v>0.6531</v>
       </c>
       <c r="K116" t="n">
-        <v>0.7449</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="L116" t="n">
-        <v>0.6798999999999999</v>
+        <v>0.7094</v>
       </c>
       <c r="M116" t="n">
         <v>155</v>
@@ -6726,22 +6726,22 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>0.307</v>
+        <v>0.2894</v>
       </c>
       <c r="H117" t="n">
-        <v>0.2044</v>
+        <v>0.1946</v>
       </c>
       <c r="I117" t="n">
-        <v>0.2557</v>
+        <v>0.242</v>
       </c>
       <c r="J117" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.7106</v>
       </c>
       <c r="K117" t="n">
-        <v>0.7956</v>
+        <v>0.8054</v>
       </c>
       <c r="L117" t="n">
-        <v>0.7443</v>
+        <v>0.758</v>
       </c>
       <c r="M117" t="n">
         <v>155</v>
@@ -6780,22 +6780,22 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>0.4719</v>
+        <v>0.4412</v>
       </c>
       <c r="H118" t="n">
-        <v>0.3265</v>
+        <v>0.3012</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3992</v>
+        <v>0.3712</v>
       </c>
       <c r="J118" t="n">
-        <v>0.5281</v>
+        <v>0.5588</v>
       </c>
       <c r="K118" t="n">
-        <v>0.6735</v>
+        <v>0.6988</v>
       </c>
       <c r="L118" t="n">
-        <v>0.6008</v>
+        <v>0.6288</v>
       </c>
       <c r="M118" t="n">
         <v>155</v>
@@ -6834,22 +6834,22 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0.6498</v>
+        <v>0.6541</v>
       </c>
       <c r="H119" t="n">
-        <v>0.5218</v>
+        <v>0.5266</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5858</v>
+        <v>0.5903</v>
       </c>
       <c r="J119" t="n">
-        <v>0.3502</v>
+        <v>0.3459</v>
       </c>
       <c r="K119" t="n">
-        <v>0.4782</v>
+        <v>0.4734</v>
       </c>
       <c r="L119" t="n">
-        <v>0.4142</v>
+        <v>0.4097</v>
       </c>
       <c r="M119" t="n">
         <v>155</v>
@@ -6888,22 +6888,22 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>0.4282</v>
+        <v>0.4185</v>
       </c>
       <c r="H120" t="n">
-        <v>0.2987</v>
+        <v>0.2857</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3635</v>
+        <v>0.3521</v>
       </c>
       <c r="J120" t="n">
-        <v>0.5718</v>
+        <v>0.5815</v>
       </c>
       <c r="K120" t="n">
-        <v>0.7013</v>
+        <v>0.7143</v>
       </c>
       <c r="L120" t="n">
-        <v>0.6365</v>
+        <v>0.6479</v>
       </c>
       <c r="M120" t="n">
         <v>155</v>
@@ -6942,22 +6942,22 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>0.7687</v>
+        <v>0.76</v>
       </c>
       <c r="H121" t="n">
-        <v>0.645</v>
+        <v>0.6324</v>
       </c>
       <c r="I121" t="n">
-        <v>0.7068</v>
+        <v>0.6962</v>
       </c>
       <c r="J121" t="n">
-        <v>0.2313</v>
+        <v>0.24</v>
       </c>
       <c r="K121" t="n">
-        <v>0.355</v>
+        <v>0.3676</v>
       </c>
       <c r="L121" t="n">
-        <v>0.2932</v>
+        <v>0.3038</v>
       </c>
       <c r="M121" t="n">
         <v>155</v>
@@ -6996,22 +6996,22 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0.3555</v>
+        <v>0.3011</v>
       </c>
       <c r="H122" t="n">
-        <v>0.2293</v>
+        <v>0.1947</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2924</v>
+        <v>0.2479</v>
       </c>
       <c r="J122" t="n">
-        <v>0.6445</v>
+        <v>0.6989</v>
       </c>
       <c r="K122" t="n">
-        <v>0.7707000000000001</v>
+        <v>0.8053</v>
       </c>
       <c r="L122" t="n">
-        <v>0.7076</v>
+        <v>0.7521</v>
       </c>
       <c r="M122" t="n">
         <v>155</v>
@@ -7050,22 +7050,22 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>0.5371</v>
+        <v>0.5175</v>
       </c>
       <c r="H123" t="n">
-        <v>0.3882</v>
+        <v>0.3666</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4626</v>
+        <v>0.442</v>
       </c>
       <c r="J123" t="n">
-        <v>0.4629</v>
+        <v>0.4825</v>
       </c>
       <c r="K123" t="n">
-        <v>0.6118</v>
+        <v>0.6334</v>
       </c>
       <c r="L123" t="n">
-        <v>0.5374</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="M123" t="n">
         <v>155</v>
@@ -7104,22 +7104,22 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.714</v>
+        <v>0.7036</v>
       </c>
       <c r="H124" t="n">
-        <v>0.5931</v>
+        <v>0.5782</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6536</v>
+        <v>0.6409</v>
       </c>
       <c r="J124" t="n">
-        <v>0.286</v>
+        <v>0.2964</v>
       </c>
       <c r="K124" t="n">
-        <v>0.4069</v>
+        <v>0.4218</v>
       </c>
       <c r="L124" t="n">
-        <v>0.3464</v>
+        <v>0.3591</v>
       </c>
       <c r="M124" t="n">
         <v>155</v>
@@ -7158,22 +7158,22 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>0.5967</v>
+        <v>0.5261</v>
       </c>
       <c r="H125" t="n">
-        <v>0.4417</v>
+        <v>0.379</v>
       </c>
       <c r="I125" t="n">
-        <v>0.5192</v>
+        <v>0.4526</v>
       </c>
       <c r="J125" t="n">
-        <v>0.4033</v>
+        <v>0.4739</v>
       </c>
       <c r="K125" t="n">
-        <v>0.5583</v>
+        <v>0.621</v>
       </c>
       <c r="L125" t="n">
-        <v>0.4808</v>
+        <v>0.5474</v>
       </c>
       <c r="M125" t="n">
         <v>155</v>
@@ -7212,22 +7212,22 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>0.5007</v>
+        <v>0.4755</v>
       </c>
       <c r="H126" t="n">
-        <v>0.3531</v>
+        <v>0.3293</v>
       </c>
       <c r="I126" t="n">
-        <v>0.4269</v>
+        <v>0.4024</v>
       </c>
       <c r="J126" t="n">
-        <v>0.4993</v>
+        <v>0.5245</v>
       </c>
       <c r="K126" t="n">
-        <v>0.6469</v>
+        <v>0.6707</v>
       </c>
       <c r="L126" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.5976</v>
       </c>
       <c r="M126" t="n">
         <v>155</v>
@@ -7266,22 +7266,22 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>0.5211</v>
+        <v>0.4976</v>
       </c>
       <c r="H127" t="n">
-        <v>0.3639</v>
+        <v>0.3422</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4425</v>
+        <v>0.4199</v>
       </c>
       <c r="J127" t="n">
-        <v>0.4789</v>
+        <v>0.5024</v>
       </c>
       <c r="K127" t="n">
-        <v>0.6361</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="L127" t="n">
-        <v>0.5575</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="M127" t="n">
         <v>155</v>
@@ -7320,22 +7320,22 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>0.7199</v>
+        <v>0.6938</v>
       </c>
       <c r="H128" t="n">
-        <v>0.5787</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="I128" t="n">
-        <v>0.6493</v>
+        <v>0.6214</v>
       </c>
       <c r="J128" t="n">
-        <v>0.2801</v>
+        <v>0.3062</v>
       </c>
       <c r="K128" t="n">
-        <v>0.4213</v>
+        <v>0.4511</v>
       </c>
       <c r="L128" t="n">
-        <v>0.3507</v>
+        <v>0.3786</v>
       </c>
       <c r="M128" t="n">
         <v>155</v>
@@ -7374,22 +7374,22 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>0.3345</v>
+        <v>0.2882</v>
       </c>
       <c r="H129" t="n">
-        <v>0.2149</v>
+        <v>0.1837</v>
       </c>
       <c r="I129" t="n">
-        <v>0.2747</v>
+        <v>0.236</v>
       </c>
       <c r="J129" t="n">
-        <v>0.6655</v>
+        <v>0.7118</v>
       </c>
       <c r="K129" t="n">
-        <v>0.7851</v>
+        <v>0.8163</v>
       </c>
       <c r="L129" t="n">
-        <v>0.7252999999999999</v>
+        <v>0.764</v>
       </c>
       <c r="M129" t="n">
         <v>155</v>
@@ -7428,22 +7428,22 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>0.2589</v>
+        <v>0.2301</v>
       </c>
       <c r="H130" t="n">
-        <v>0.1663</v>
+        <v>0.1478</v>
       </c>
       <c r="I130" t="n">
-        <v>0.2126</v>
+        <v>0.189</v>
       </c>
       <c r="J130" t="n">
-        <v>0.7411</v>
+        <v>0.7699</v>
       </c>
       <c r="K130" t="n">
-        <v>0.8337</v>
+        <v>0.8522</v>
       </c>
       <c r="L130" t="n">
-        <v>0.7874</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="M130" t="n">
         <v>155</v>
@@ -7482,22 +7482,22 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>0.4622</v>
+        <v>0.4394</v>
       </c>
       <c r="H131" t="n">
-        <v>0.326</v>
+        <v>0.3088</v>
       </c>
       <c r="I131" t="n">
-        <v>0.3941</v>
+        <v>0.3741</v>
       </c>
       <c r="J131" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.5606</v>
       </c>
       <c r="K131" t="n">
-        <v>0.674</v>
+        <v>0.6912</v>
       </c>
       <c r="L131" t="n">
-        <v>0.6059</v>
+        <v>0.6259</v>
       </c>
       <c r="M131" t="n">
         <v>155</v>
@@ -7536,22 +7536,22 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>0.7403</v>
+        <v>0.7189</v>
       </c>
       <c r="H132" t="n">
-        <v>0.6007</v>
+        <v>0.576</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6705</v>
+        <v>0.6474</v>
       </c>
       <c r="J132" t="n">
-        <v>0.2597</v>
+        <v>0.2811</v>
       </c>
       <c r="K132" t="n">
-        <v>0.3993</v>
+        <v>0.424</v>
       </c>
       <c r="L132" t="n">
-        <v>0.3295</v>
+        <v>0.3526</v>
       </c>
       <c r="M132" t="n">
         <v>155</v>
@@ -7590,22 +7590,22 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>0.6876</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="H133" t="n">
-        <v>0.5364</v>
+        <v>0.5095</v>
       </c>
       <c r="I133" t="n">
-        <v>0.612</v>
+        <v>0.5871</v>
       </c>
       <c r="J133" t="n">
-        <v>0.3124</v>
+        <v>0.3352</v>
       </c>
       <c r="K133" t="n">
-        <v>0.4636</v>
+        <v>0.4905</v>
       </c>
       <c r="L133" t="n">
-        <v>0.388</v>
+        <v>0.4129</v>
       </c>
       <c r="M133" t="n">
         <v>155</v>
@@ -7644,22 +7644,22 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>0.794</v>
+        <v>0.7762</v>
       </c>
       <c r="H134" t="n">
-        <v>0.6733</v>
+        <v>0.6504</v>
       </c>
       <c r="I134" t="n">
-        <v>0.7336</v>
+        <v>0.7133</v>
       </c>
       <c r="J134" t="n">
-        <v>0.206</v>
+        <v>0.2238</v>
       </c>
       <c r="K134" t="n">
-        <v>0.3267</v>
+        <v>0.3496</v>
       </c>
       <c r="L134" t="n">
-        <v>0.2664</v>
+        <v>0.2867</v>
       </c>
       <c r="M134" t="n">
         <v>155</v>
@@ -7698,22 +7698,22 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>0.4121</v>
+        <v>0.3747</v>
       </c>
       <c r="H135" t="n">
-        <v>0.2889</v>
+        <v>0.2576</v>
       </c>
       <c r="I135" t="n">
-        <v>0.3505</v>
+        <v>0.3162</v>
       </c>
       <c r="J135" t="n">
-        <v>0.5879</v>
+        <v>0.6253</v>
       </c>
       <c r="K135" t="n">
-        <v>0.7111</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="L135" t="n">
-        <v>0.6495</v>
+        <v>0.6838</v>
       </c>
       <c r="M135" t="n">
         <v>155</v>
@@ -7752,22 +7752,22 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>0.3826</v>
+        <v>0.3569</v>
       </c>
       <c r="H136" t="n">
-        <v>0.269</v>
+        <v>0.2448</v>
       </c>
       <c r="I136" t="n">
-        <v>0.3258</v>
+        <v>0.3008</v>
       </c>
       <c r="J136" t="n">
-        <v>0.6173999999999999</v>
+        <v>0.6431</v>
       </c>
       <c r="K136" t="n">
-        <v>0.731</v>
+        <v>0.7552</v>
       </c>
       <c r="L136" t="n">
-        <v>0.6742</v>
+        <v>0.6992</v>
       </c>
       <c r="M136" t="n">
         <v>155</v>
@@ -7806,22 +7806,22 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>0.2266</v>
+        <v>0.2331</v>
       </c>
       <c r="H137" t="n">
-        <v>0.1539</v>
+        <v>0.1579</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1902</v>
+        <v>0.1955</v>
       </c>
       <c r="J137" t="n">
-        <v>0.7734</v>
+        <v>0.7669</v>
       </c>
       <c r="K137" t="n">
-        <v>0.8461</v>
+        <v>0.8421</v>
       </c>
       <c r="L137" t="n">
-        <v>0.8098</v>
+        <v>0.8045</v>
       </c>
       <c r="M137" t="n">
         <v>155</v>
@@ -7860,22 +7860,22 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>0.4124</v>
+        <v>0.4068</v>
       </c>
       <c r="H138" t="n">
-        <v>0.2727</v>
+        <v>0.2642</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3426</v>
+        <v>0.3355</v>
       </c>
       <c r="J138" t="n">
-        <v>0.5876</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="K138" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.7358</v>
       </c>
       <c r="L138" t="n">
-        <v>0.6574</v>
+        <v>0.6645</v>
       </c>
       <c r="M138" t="n">
         <v>155</v>
@@ -7914,22 +7914,22 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>0.3328</v>
+        <v>0.317</v>
       </c>
       <c r="H139" t="n">
-        <v>0.2277</v>
+        <v>0.2179</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2802</v>
+        <v>0.2674</v>
       </c>
       <c r="J139" t="n">
-        <v>0.6672</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="K139" t="n">
-        <v>0.7723</v>
+        <v>0.7821</v>
       </c>
       <c r="L139" t="n">
-        <v>0.7198</v>
+        <v>0.7326</v>
       </c>
       <c r="M139" t="n">
         <v>155</v>
@@ -7968,22 +7968,22 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0.254</v>
+        <v>0.2534</v>
       </c>
       <c r="H140" t="n">
-        <v>0.1722</v>
+        <v>0.1717</v>
       </c>
       <c r="I140" t="n">
-        <v>0.2131</v>
+        <v>0.2126</v>
       </c>
       <c r="J140" t="n">
-        <v>0.746</v>
+        <v>0.7466</v>
       </c>
       <c r="K140" t="n">
-        <v>0.8278</v>
+        <v>0.8283</v>
       </c>
       <c r="L140" t="n">
-        <v>0.7869</v>
+        <v>0.7874</v>
       </c>
       <c r="M140" t="n">
         <v>155</v>
@@ -8076,22 +8076,22 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>0.3074</v>
+        <v>0.3048</v>
       </c>
       <c r="H142" t="n">
-        <v>0.2066</v>
+        <v>0.2035</v>
       </c>
       <c r="I142" t="n">
-        <v>0.257</v>
+        <v>0.2542</v>
       </c>
       <c r="J142" t="n">
-        <v>0.6926</v>
+        <v>0.6952</v>
       </c>
       <c r="K142" t="n">
-        <v>0.7934</v>
+        <v>0.7965</v>
       </c>
       <c r="L142" t="n">
-        <v>0.743</v>
+        <v>0.7458</v>
       </c>
       <c r="M142" t="n">
         <v>155</v>
@@ -8130,22 +8130,22 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>0.5525</v>
+        <v>0.576</v>
       </c>
       <c r="H143" t="n">
-        <v>0.4023</v>
+        <v>0.4281</v>
       </c>
       <c r="I143" t="n">
-        <v>0.4774</v>
+        <v>0.502</v>
       </c>
       <c r="J143" t="n">
-        <v>0.4475</v>
+        <v>0.424</v>
       </c>
       <c r="K143" t="n">
-        <v>0.5977</v>
+        <v>0.5719</v>
       </c>
       <c r="L143" t="n">
-        <v>0.5226</v>
+        <v>0.498</v>
       </c>
       <c r="M143" t="n">
         <v>155</v>
@@ -8184,22 +8184,22 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>0.289</v>
+        <v>0.308</v>
       </c>
       <c r="H144" t="n">
-        <v>0.1878</v>
+        <v>0.1995</v>
       </c>
       <c r="I144" t="n">
-        <v>0.2384</v>
+        <v>0.2538</v>
       </c>
       <c r="J144" t="n">
-        <v>0.711</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="K144" t="n">
-        <v>0.8122</v>
+        <v>0.8005</v>
       </c>
       <c r="L144" t="n">
-        <v>0.7616000000000001</v>
+        <v>0.7462</v>
       </c>
       <c r="M144" t="n">
         <v>155</v>
@@ -8238,22 +8238,22 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>0.6832</v>
+        <v>0.6803</v>
       </c>
       <c r="H145" t="n">
-        <v>0.5442</v>
+        <v>0.54</v>
       </c>
       <c r="I145" t="n">
-        <v>0.6137</v>
+        <v>0.6102</v>
       </c>
       <c r="J145" t="n">
-        <v>0.3168</v>
+        <v>0.3197</v>
       </c>
       <c r="K145" t="n">
-        <v>0.4558</v>
+        <v>0.46</v>
       </c>
       <c r="L145" t="n">
-        <v>0.3863</v>
+        <v>0.3898</v>
       </c>
       <c r="M145" t="n">
         <v>155</v>
@@ -8292,22 +8292,22 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>0.2131</v>
+        <v>0.21</v>
       </c>
       <c r="H146" t="n">
-        <v>0.1338</v>
+        <v>0.1327</v>
       </c>
       <c r="I146" t="n">
-        <v>0.1734</v>
+        <v>0.1714</v>
       </c>
       <c r="J146" t="n">
-        <v>0.7869</v>
+        <v>0.79</v>
       </c>
       <c r="K146" t="n">
-        <v>0.8662</v>
+        <v>0.8673</v>
       </c>
       <c r="L146" t="n">
-        <v>0.8266</v>
+        <v>0.8286</v>
       </c>
       <c r="M146" t="n">
         <v>155</v>
@@ -8346,22 +8346,22 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>0.4164</v>
+        <v>0.4124</v>
       </c>
       <c r="H147" t="n">
-        <v>0.2823</v>
+        <v>0.2808</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3494</v>
+        <v>0.3466</v>
       </c>
       <c r="J147" t="n">
-        <v>0.5836</v>
+        <v>0.5876</v>
       </c>
       <c r="K147" t="n">
-        <v>0.7177</v>
+        <v>0.7192</v>
       </c>
       <c r="L147" t="n">
-        <v>0.6506</v>
+        <v>0.6534</v>
       </c>
       <c r="M147" t="n">
         <v>155</v>
@@ -8400,22 +8400,22 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>0.6467000000000001</v>
+        <v>0.6455</v>
       </c>
       <c r="H148" t="n">
-        <v>0.5057</v>
+        <v>0.5036</v>
       </c>
       <c r="I148" t="n">
-        <v>0.5762</v>
+        <v>0.5746</v>
       </c>
       <c r="J148" t="n">
-        <v>0.3533</v>
+        <v>0.3545</v>
       </c>
       <c r="K148" t="n">
-        <v>0.4943</v>
+        <v>0.4964</v>
       </c>
       <c r="L148" t="n">
-        <v>0.4238</v>
+        <v>0.4254</v>
       </c>
       <c r="M148" t="n">
         <v>155</v>
@@ -8454,22 +8454,22 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>0.4644</v>
+        <v>0.4273</v>
       </c>
       <c r="H149" t="n">
-        <v>0.3254</v>
+        <v>0.2927</v>
       </c>
       <c r="I149" t="n">
-        <v>0.3949</v>
+        <v>0.36</v>
       </c>
       <c r="J149" t="n">
-        <v>0.5356</v>
+        <v>0.5727</v>
       </c>
       <c r="K149" t="n">
-        <v>0.6746</v>
+        <v>0.7073</v>
       </c>
       <c r="L149" t="n">
-        <v>0.6051</v>
+        <v>0.64</v>
       </c>
       <c r="M149" t="n">
         <v>155</v>
@@ -8508,22 +8508,22 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0.3491</v>
+        <v>0.3481</v>
       </c>
       <c r="H150" t="n">
-        <v>0.2327</v>
+        <v>0.2308</v>
       </c>
       <c r="I150" t="n">
-        <v>0.2909</v>
+        <v>0.2894</v>
       </c>
       <c r="J150" t="n">
-        <v>0.6509</v>
+        <v>0.6519</v>
       </c>
       <c r="K150" t="n">
-        <v>0.7673</v>
+        <v>0.7692</v>
       </c>
       <c r="L150" t="n">
-        <v>0.7091</v>
+        <v>0.7106</v>
       </c>
       <c r="M150" t="n">
         <v>155</v>
@@ -8562,22 +8562,22 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>0.4068</v>
+        <v>0.4033</v>
       </c>
       <c r="H151" t="n">
-        <v>0.2705</v>
+        <v>0.2677</v>
       </c>
       <c r="I151" t="n">
-        <v>0.3386</v>
+        <v>0.3355</v>
       </c>
       <c r="J151" t="n">
-        <v>0.5931999999999999</v>
+        <v>0.5967</v>
       </c>
       <c r="K151" t="n">
-        <v>0.7295</v>
+        <v>0.7323</v>
       </c>
       <c r="L151" t="n">
-        <v>0.6614</v>
+        <v>0.6645</v>
       </c>
       <c r="M151" t="n">
         <v>155</v>
@@ -8616,22 +8616,22 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>0.6448</v>
+        <v>0.6453</v>
       </c>
       <c r="H152" t="n">
-        <v>0.4964</v>
+        <v>0.4969</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5706</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="J152" t="n">
-        <v>0.3552</v>
+        <v>0.3547</v>
       </c>
       <c r="K152" t="n">
-        <v>0.5036</v>
+        <v>0.5031</v>
       </c>
       <c r="L152" t="n">
-        <v>0.4294</v>
+        <v>0.4289</v>
       </c>
       <c r="M152" t="n">
         <v>155</v>
@@ -8670,22 +8670,22 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>0.2087</v>
+        <v>0.2035</v>
       </c>
       <c r="H153" t="n">
-        <v>0.1374</v>
+        <v>0.1353</v>
       </c>
       <c r="I153" t="n">
-        <v>0.173</v>
+        <v>0.1694</v>
       </c>
       <c r="J153" t="n">
-        <v>0.7913</v>
+        <v>0.7965</v>
       </c>
       <c r="K153" t="n">
-        <v>0.8626</v>
+        <v>0.8647</v>
       </c>
       <c r="L153" t="n">
-        <v>0.827</v>
+        <v>0.8306</v>
       </c>
       <c r="M153" t="n">
         <v>155</v>
@@ -8724,22 +8724,22 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>0.1921</v>
+        <v>0.1895</v>
       </c>
       <c r="H154" t="n">
-        <v>0.1256</v>
+        <v>0.1237</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1588</v>
+        <v>0.1566</v>
       </c>
       <c r="J154" t="n">
-        <v>0.8079</v>
+        <v>0.8105</v>
       </c>
       <c r="K154" t="n">
-        <v>0.8744</v>
+        <v>0.8763</v>
       </c>
       <c r="L154" t="n">
-        <v>0.8411999999999999</v>
+        <v>0.8434</v>
       </c>
       <c r="M154" t="n">
         <v>155</v>
@@ -8835,19 +8835,19 @@
         <v>0.647</v>
       </c>
       <c r="H156" t="n">
-        <v>0.4991</v>
+        <v>0.4979</v>
       </c>
       <c r="I156" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.5724</v>
       </c>
       <c r="J156" t="n">
         <v>0.353</v>
       </c>
       <c r="K156" t="n">
-        <v>0.5009</v>
+        <v>0.5021</v>
       </c>
       <c r="L156" t="n">
-        <v>0.4269</v>
+        <v>0.4276</v>
       </c>
       <c r="M156" t="n">
         <v>155</v>
@@ -8886,22 +8886,22 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>0.5718</v>
+        <v>0.5709</v>
       </c>
       <c r="H157" t="n">
-        <v>0.4237</v>
+        <v>0.42</v>
       </c>
       <c r="I157" t="n">
-        <v>0.4978</v>
+        <v>0.4954</v>
       </c>
       <c r="J157" t="n">
-        <v>0.4282</v>
+        <v>0.4291</v>
       </c>
       <c r="K157" t="n">
-        <v>0.5763</v>
+        <v>0.58</v>
       </c>
       <c r="L157" t="n">
-        <v>0.5022</v>
+        <v>0.5046</v>
       </c>
       <c r="M157" t="n">
         <v>155</v>
@@ -8940,22 +8940,22 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>0.7338</v>
+        <v>0.733</v>
       </c>
       <c r="H158" t="n">
-        <v>0.5915</v>
+        <v>0.5887</v>
       </c>
       <c r="I158" t="n">
-        <v>0.6626</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="J158" t="n">
-        <v>0.2662</v>
+        <v>0.267</v>
       </c>
       <c r="K158" t="n">
-        <v>0.4085</v>
+        <v>0.4113</v>
       </c>
       <c r="L158" t="n">
-        <v>0.3374</v>
+        <v>0.3392</v>
       </c>
       <c r="M158" t="n">
         <v>155</v>
@@ -8994,22 +8994,22 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>0.2991</v>
+        <v>0.2905</v>
       </c>
       <c r="H159" t="n">
-        <v>0.1899</v>
+        <v>0.1836</v>
       </c>
       <c r="I159" t="n">
-        <v>0.2445</v>
+        <v>0.237</v>
       </c>
       <c r="J159" t="n">
-        <v>0.7009</v>
+        <v>0.7095</v>
       </c>
       <c r="K159" t="n">
-        <v>0.8101</v>
+        <v>0.8164</v>
       </c>
       <c r="L159" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.763</v>
       </c>
       <c r="M159" t="n">
         <v>155</v>
@@ -9048,22 +9048,22 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>0.2738</v>
+        <v>0.2611</v>
       </c>
       <c r="H160" t="n">
-        <v>0.1773</v>
+        <v>0.1701</v>
       </c>
       <c r="I160" t="n">
-        <v>0.2256</v>
+        <v>0.2156</v>
       </c>
       <c r="J160" t="n">
-        <v>0.7262</v>
+        <v>0.7389</v>
       </c>
       <c r="K160" t="n">
-        <v>0.8227</v>
+        <v>0.8299</v>
       </c>
       <c r="L160" t="n">
-        <v>0.7744</v>
+        <v>0.7844</v>
       </c>
       <c r="M160" t="n">
         <v>155</v>
@@ -9102,22 +9102,22 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>0.7571</v>
+        <v>0.743</v>
       </c>
       <c r="H161" t="n">
-        <v>0.63</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="I161" t="n">
-        <v>0.6936</v>
+        <v>0.6777</v>
       </c>
       <c r="J161" t="n">
-        <v>0.2429</v>
+        <v>0.257</v>
       </c>
       <c r="K161" t="n">
-        <v>0.37</v>
+        <v>0.3876</v>
       </c>
       <c r="L161" t="n">
-        <v>0.3064</v>
+        <v>0.3223</v>
       </c>
       <c r="M161" t="n">
         <v>155</v>
@@ -9156,22 +9156,22 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>0.6893</v>
+        <v>0.6786</v>
       </c>
       <c r="H162" t="n">
-        <v>0.5402</v>
+        <v>0.5256</v>
       </c>
       <c r="I162" t="n">
-        <v>0.6148</v>
+        <v>0.6021</v>
       </c>
       <c r="J162" t="n">
-        <v>0.3107</v>
+        <v>0.3214</v>
       </c>
       <c r="K162" t="n">
-        <v>0.4598</v>
+        <v>0.4744</v>
       </c>
       <c r="L162" t="n">
-        <v>0.3852</v>
+        <v>0.3979</v>
       </c>
       <c r="M162" t="n">
         <v>155</v>
@@ -9210,22 +9210,22 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>0.6465</v>
+        <v>0.6224</v>
       </c>
       <c r="H163" t="n">
-        <v>0.5074</v>
+        <v>0.4791</v>
       </c>
       <c r="I163" t="n">
-        <v>0.577</v>
+        <v>0.5508</v>
       </c>
       <c r="J163" t="n">
-        <v>0.3535</v>
+        <v>0.3776</v>
       </c>
       <c r="K163" t="n">
-        <v>0.4926</v>
+        <v>0.5209</v>
       </c>
       <c r="L163" t="n">
-        <v>0.423</v>
+        <v>0.4492</v>
       </c>
       <c r="M163" t="n">
         <v>155</v>
@@ -9264,22 +9264,22 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>0.6041</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="H164" t="n">
-        <v>0.4529</v>
+        <v>0.4374</v>
       </c>
       <c r="I164" t="n">
-        <v>0.5285</v>
+        <v>0.5098</v>
       </c>
       <c r="J164" t="n">
-        <v>0.3959</v>
+        <v>0.4178</v>
       </c>
       <c r="K164" t="n">
-        <v>0.5471</v>
+        <v>0.5626</v>
       </c>
       <c r="L164" t="n">
-        <v>0.4715</v>
+        <v>0.4902</v>
       </c>
       <c r="M164" t="n">
         <v>155</v>
@@ -9318,22 +9318,22 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>0.703</v>
+        <v>0.6885</v>
       </c>
       <c r="H165" t="n">
-        <v>0.5627</v>
+        <v>0.5462</v>
       </c>
       <c r="I165" t="n">
-        <v>0.6328</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="J165" t="n">
-        <v>0.297</v>
+        <v>0.3115</v>
       </c>
       <c r="K165" t="n">
-        <v>0.4373</v>
+        <v>0.4538</v>
       </c>
       <c r="L165" t="n">
-        <v>0.3672</v>
+        <v>0.3826</v>
       </c>
       <c r="M165" t="n">
         <v>155</v>
@@ -9372,22 +9372,22 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>0.8357</v>
+        <v>0.8379</v>
       </c>
       <c r="H166" t="n">
-        <v>0.7409</v>
+        <v>0.744</v>
       </c>
       <c r="I166" t="n">
-        <v>0.7883</v>
+        <v>0.791</v>
       </c>
       <c r="J166" t="n">
-        <v>0.1643</v>
+        <v>0.1621</v>
       </c>
       <c r="K166" t="n">
-        <v>0.2591</v>
+        <v>0.256</v>
       </c>
       <c r="L166" t="n">
-        <v>0.2117</v>
+        <v>0.209</v>
       </c>
       <c r="M166" t="n">
         <v>155</v>
@@ -9426,22 +9426,22 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>0.6589</v>
+        <v>0.6577</v>
       </c>
       <c r="H167" t="n">
-        <v>0.5123</v>
+        <v>0.511</v>
       </c>
       <c r="I167" t="n">
-        <v>0.5856</v>
+        <v>0.5843</v>
       </c>
       <c r="J167" t="n">
-        <v>0.3411</v>
+        <v>0.3423</v>
       </c>
       <c r="K167" t="n">
-        <v>0.4877</v>
+        <v>0.489</v>
       </c>
       <c r="L167" t="n">
-        <v>0.4144</v>
+        <v>0.4157</v>
       </c>
       <c r="M167" t="n">
         <v>155</v>
@@ -9534,22 +9534,22 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>0.5593</v>
+        <v>0.5363</v>
       </c>
       <c r="H169" t="n">
-        <v>0.4139</v>
+        <v>0.3917</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4866</v>
+        <v>0.464</v>
       </c>
       <c r="J169" t="n">
-        <v>0.4407</v>
+        <v>0.4637</v>
       </c>
       <c r="K169" t="n">
-        <v>0.5861</v>
+        <v>0.6083</v>
       </c>
       <c r="L169" t="n">
-        <v>0.5134</v>
+        <v>0.536</v>
       </c>
       <c r="M169" t="n">
         <v>155</v>
@@ -9588,22 +9588,22 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>0.7319</v>
+        <v>0.7231</v>
       </c>
       <c r="H170" t="n">
-        <v>0.6032</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="I170" t="n">
-        <v>0.6676</v>
+        <v>0.6552</v>
       </c>
       <c r="J170" t="n">
-        <v>0.2681</v>
+        <v>0.2769</v>
       </c>
       <c r="K170" t="n">
-        <v>0.3968</v>
+        <v>0.4128</v>
       </c>
       <c r="L170" t="n">
-        <v>0.3324</v>
+        <v>0.3448</v>
       </c>
       <c r="M170" t="n">
         <v>155</v>
@@ -9642,22 +9642,22 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>0.8552999999999999</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="H171" t="n">
-        <v>0.7671</v>
+        <v>0.7641</v>
       </c>
       <c r="I171" t="n">
-        <v>0.8112</v>
+        <v>0.8087</v>
       </c>
       <c r="J171" t="n">
-        <v>0.1447</v>
+        <v>0.1467</v>
       </c>
       <c r="K171" t="n">
-        <v>0.2329</v>
+        <v>0.2359</v>
       </c>
       <c r="L171" t="n">
-        <v>0.1888</v>
+        <v>0.1913</v>
       </c>
       <c r="M171" t="n">
         <v>155</v>
@@ -9696,22 +9696,22 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>0.7891</v>
+        <v>0.7679</v>
       </c>
       <c r="H172" t="n">
-        <v>0.6753</v>
+        <v>0.6432</v>
       </c>
       <c r="I172" t="n">
-        <v>0.7322</v>
+        <v>0.7056</v>
       </c>
       <c r="J172" t="n">
-        <v>0.2109</v>
+        <v>0.2321</v>
       </c>
       <c r="K172" t="n">
-        <v>0.3247</v>
+        <v>0.3568</v>
       </c>
       <c r="L172" t="n">
-        <v>0.2678</v>
+        <v>0.2944</v>
       </c>
       <c r="M172" t="n">
         <v>155</v>
@@ -9750,22 +9750,22 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>0.7075</v>
+        <v>0.6844</v>
       </c>
       <c r="H173" t="n">
-        <v>0.5696</v>
+        <v>0.5427</v>
       </c>
       <c r="I173" t="n">
-        <v>0.6385</v>
+        <v>0.6136</v>
       </c>
       <c r="J173" t="n">
-        <v>0.2925</v>
+        <v>0.3156</v>
       </c>
       <c r="K173" t="n">
-        <v>0.4304</v>
+        <v>0.4573</v>
       </c>
       <c r="L173" t="n">
-        <v>0.3615</v>
+        <v>0.3864</v>
       </c>
       <c r="M173" t="n">
         <v>155</v>
@@ -9804,22 +9804,22 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>0.7622</v>
+        <v>0.7406</v>
       </c>
       <c r="H174" t="n">
-        <v>0.6389</v>
+        <v>0.6119</v>
       </c>
       <c r="I174" t="n">
-        <v>0.7006</v>
+        <v>0.6762</v>
       </c>
       <c r="J174" t="n">
-        <v>0.2378</v>
+        <v>0.2594</v>
       </c>
       <c r="K174" t="n">
-        <v>0.3611</v>
+        <v>0.3881</v>
       </c>
       <c r="L174" t="n">
-        <v>0.2994</v>
+        <v>0.3238</v>
       </c>
       <c r="M174" t="n">
         <v>155</v>
@@ -9858,22 +9858,22 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>0.8467</v>
+        <v>0.8431</v>
       </c>
       <c r="H175" t="n">
-        <v>0.756</v>
+        <v>0.753</v>
       </c>
       <c r="I175" t="n">
-        <v>0.8014</v>
+        <v>0.798</v>
       </c>
       <c r="J175" t="n">
-        <v>0.1533</v>
+        <v>0.1569</v>
       </c>
       <c r="K175" t="n">
-        <v>0.244</v>
+        <v>0.247</v>
       </c>
       <c r="L175" t="n">
-        <v>0.1986</v>
+        <v>0.202</v>
       </c>
       <c r="M175" t="n">
         <v>155</v>
@@ -9912,22 +9912,22 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>0.5324</v>
+        <v>0.5147</v>
       </c>
       <c r="H176" t="n">
-        <v>0.3963</v>
+        <v>0.3772</v>
       </c>
       <c r="I176" t="n">
-        <v>0.4644</v>
+        <v>0.446</v>
       </c>
       <c r="J176" t="n">
-        <v>0.4676</v>
+        <v>0.4853</v>
       </c>
       <c r="K176" t="n">
-        <v>0.6037</v>
+        <v>0.6228</v>
       </c>
       <c r="L176" t="n">
-        <v>0.5356</v>
+        <v>0.554</v>
       </c>
       <c r="M176" t="n">
         <v>155</v>
@@ -9966,22 +9966,22 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>0.491</v>
+        <v>0.4659</v>
       </c>
       <c r="H177" t="n">
-        <v>0.3491</v>
+        <v>0.3264</v>
       </c>
       <c r="I177" t="n">
-        <v>0.42</v>
+        <v>0.3962</v>
       </c>
       <c r="J177" t="n">
-        <v>0.509</v>
+        <v>0.5341</v>
       </c>
       <c r="K177" t="n">
-        <v>0.6509</v>
+        <v>0.6736</v>
       </c>
       <c r="L177" t="n">
-        <v>0.58</v>
+        <v>0.6038</v>
       </c>
       <c r="M177" t="n">
         <v>155</v>
@@ -10020,22 +10020,22 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>0.6875</v>
+        <v>0.6741</v>
       </c>
       <c r="H178" t="n">
-        <v>0.5429</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="I178" t="n">
-        <v>0.6152</v>
+        <v>0.6004</v>
       </c>
       <c r="J178" t="n">
-        <v>0.3125</v>
+        <v>0.3259</v>
       </c>
       <c r="K178" t="n">
-        <v>0.4571</v>
+        <v>0.4733</v>
       </c>
       <c r="L178" t="n">
-        <v>0.3848</v>
+        <v>0.3996</v>
       </c>
       <c r="M178" t="n">
         <v>155</v>
@@ -10128,22 +10128,22 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>0.8431</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="H180" t="n">
-        <v>0.7522</v>
+        <v>0.7421</v>
       </c>
       <c r="I180" t="n">
-        <v>0.7976</v>
+        <v>0.7887</v>
       </c>
       <c r="J180" t="n">
-        <v>0.1569</v>
+        <v>0.1648</v>
       </c>
       <c r="K180" t="n">
-        <v>0.2478</v>
+        <v>0.2579</v>
       </c>
       <c r="L180" t="n">
-        <v>0.2024</v>
+        <v>0.2113</v>
       </c>
       <c r="M180" t="n">
         <v>155</v>
@@ -10236,22 +10236,22 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0.6061</v>
+        <v>0.5979</v>
       </c>
       <c r="H182" t="n">
-        <v>0.4661</v>
+        <v>0.457</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5361</v>
+        <v>0.5274</v>
       </c>
       <c r="J182" t="n">
-        <v>0.3939</v>
+        <v>0.4021</v>
       </c>
       <c r="K182" t="n">
-        <v>0.5339</v>
+        <v>0.543</v>
       </c>
       <c r="L182" t="n">
-        <v>0.4639</v>
+        <v>0.4726</v>
       </c>
       <c r="M182" t="n">
         <v>155</v>
@@ -10290,22 +10290,22 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>0.6319</v>
+        <v>0.6158</v>
       </c>
       <c r="H183" t="n">
-        <v>0.4837</v>
+        <v>0.467</v>
       </c>
       <c r="I183" t="n">
-        <v>0.5578</v>
+        <v>0.5414</v>
       </c>
       <c r="J183" t="n">
-        <v>0.3681</v>
+        <v>0.3842</v>
       </c>
       <c r="K183" t="n">
-        <v>0.5163</v>
+        <v>0.533</v>
       </c>
       <c r="L183" t="n">
-        <v>0.4422</v>
+        <v>0.4586</v>
       </c>
       <c r="M183" t="n">
         <v>155</v>
@@ -10401,19 +10401,19 @@
         <v>0.4031</v>
       </c>
       <c r="H185" t="n">
-        <v>0.2805</v>
+        <v>0.2811</v>
       </c>
       <c r="I185" t="n">
-        <v>0.3418</v>
+        <v>0.3421</v>
       </c>
       <c r="J185" t="n">
         <v>0.5969</v>
       </c>
       <c r="K185" t="n">
-        <v>0.7195</v>
+        <v>0.7189</v>
       </c>
       <c r="L185" t="n">
-        <v>0.6582</v>
+        <v>0.6579</v>
       </c>
       <c r="M185" t="n">
         <v>155</v>
@@ -10452,22 +10452,22 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>0.3244</v>
+        <v>0.3303</v>
       </c>
       <c r="H186" t="n">
-        <v>0.2347</v>
+        <v>0.2396</v>
       </c>
       <c r="I186" t="n">
-        <v>0.2796</v>
+        <v>0.285</v>
       </c>
       <c r="J186" t="n">
-        <v>0.6756</v>
+        <v>0.6697</v>
       </c>
       <c r="K186" t="n">
-        <v>0.7653</v>
+        <v>0.7604</v>
       </c>
       <c r="L186" t="n">
-        <v>0.7204</v>
+        <v>0.715</v>
       </c>
       <c r="M186" t="n">
         <v>155</v>
@@ -10560,22 +10560,22 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>0.7247</v>
+        <v>0.7345</v>
       </c>
       <c r="H188" t="n">
-        <v>0.5765</v>
+        <v>0.5903</v>
       </c>
       <c r="I188" t="n">
-        <v>0.6506</v>
+        <v>0.6624</v>
       </c>
       <c r="J188" t="n">
-        <v>0.2753</v>
+        <v>0.2655</v>
       </c>
       <c r="K188" t="n">
-        <v>0.4235</v>
+        <v>0.4097</v>
       </c>
       <c r="L188" t="n">
-        <v>0.3494</v>
+        <v>0.3376</v>
       </c>
       <c r="M188" t="n">
         <v>155</v>
@@ -10614,22 +10614,22 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>0.4654</v>
+        <v>0.4768</v>
       </c>
       <c r="H189" t="n">
-        <v>0.3276</v>
+        <v>0.3417</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3965</v>
+        <v>0.4092</v>
       </c>
       <c r="J189" t="n">
-        <v>0.5346</v>
+        <v>0.5232</v>
       </c>
       <c r="K189" t="n">
-        <v>0.6724</v>
+        <v>0.6583</v>
       </c>
       <c r="L189" t="n">
-        <v>0.6035</v>
+        <v>0.5908</v>
       </c>
       <c r="M189" t="n">
         <v>155</v>
@@ -10776,22 +10776,22 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>0.5635</v>
+        <v>0.5718</v>
       </c>
       <c r="H192" t="n">
-        <v>0.4114</v>
+        <v>0.4196</v>
       </c>
       <c r="I192" t="n">
-        <v>0.4874</v>
+        <v>0.4957</v>
       </c>
       <c r="J192" t="n">
-        <v>0.4365</v>
+        <v>0.4282</v>
       </c>
       <c r="K192" t="n">
-        <v>0.5886</v>
+        <v>0.5804</v>
       </c>
       <c r="L192" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.5043</v>
       </c>
       <c r="M192" t="n">
         <v>155</v>
@@ -10830,22 +10830,22 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>0.774</v>
+        <v>0.7746</v>
       </c>
       <c r="H193" t="n">
-        <v>0.6461</v>
+        <v>0.6468</v>
       </c>
       <c r="I193" t="n">
-        <v>0.7101</v>
+        <v>0.7107</v>
       </c>
       <c r="J193" t="n">
-        <v>0.226</v>
+        <v>0.2254</v>
       </c>
       <c r="K193" t="n">
-        <v>0.3539</v>
+        <v>0.3532</v>
       </c>
       <c r="L193" t="n">
-        <v>0.2899</v>
+        <v>0.2893</v>
       </c>
       <c r="M193" t="n">
         <v>155</v>
@@ -10884,22 +10884,22 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>0.6179</v>
+        <v>0.5907</v>
       </c>
       <c r="H194" t="n">
-        <v>0.4672</v>
+        <v>0.4384</v>
       </c>
       <c r="I194" t="n">
-        <v>0.5426</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="J194" t="n">
-        <v>0.3821</v>
+        <v>0.4093</v>
       </c>
       <c r="K194" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.5616</v>
       </c>
       <c r="L194" t="n">
-        <v>0.4574</v>
+        <v>0.4854</v>
       </c>
       <c r="M194" t="n">
         <v>155</v>
@@ -11208,22 +11208,22 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>0.5316</v>
+        <v>0.5372</v>
       </c>
       <c r="H200" t="n">
-        <v>0.3801</v>
+        <v>0.3832</v>
       </c>
       <c r="I200" t="n">
-        <v>0.4558</v>
+        <v>0.4602</v>
       </c>
       <c r="J200" t="n">
-        <v>0.4684</v>
+        <v>0.4628</v>
       </c>
       <c r="K200" t="n">
-        <v>0.6199</v>
+        <v>0.6168</v>
       </c>
       <c r="L200" t="n">
-        <v>0.5442</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="M200" t="n">
         <v>155</v>
@@ -11316,22 +11316,22 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>0.711</v>
+        <v>0.7134</v>
       </c>
       <c r="H202" t="n">
-        <v>0.5687</v>
+        <v>0.5702</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6398</v>
+        <v>0.6418</v>
       </c>
       <c r="J202" t="n">
-        <v>0.289</v>
+        <v>0.2866</v>
       </c>
       <c r="K202" t="n">
-        <v>0.4313</v>
+        <v>0.4298</v>
       </c>
       <c r="L202" t="n">
-        <v>0.3602</v>
+        <v>0.3582</v>
       </c>
       <c r="M202" t="n">
         <v>155</v>
@@ -11370,22 +11370,22 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>0.8133</v>
+        <v>0.8166</v>
       </c>
       <c r="H203" t="n">
-        <v>0.697</v>
+        <v>0.7</v>
       </c>
       <c r="I203" t="n">
-        <v>0.7552</v>
+        <v>0.7583</v>
       </c>
       <c r="J203" t="n">
-        <v>0.1867</v>
+        <v>0.1834</v>
       </c>
       <c r="K203" t="n">
-        <v>0.303</v>
+        <v>0.3</v>
       </c>
       <c r="L203" t="n">
-        <v>0.2448</v>
+        <v>0.2417</v>
       </c>
       <c r="M203" t="n">
         <v>155</v>
@@ -11532,22 +11532,22 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>0.5458</v>
+        <v>0.5414</v>
       </c>
       <c r="H206" t="n">
-        <v>0.4001</v>
+        <v>0.3958</v>
       </c>
       <c r="I206" t="n">
-        <v>0.473</v>
+        <v>0.4686</v>
       </c>
       <c r="J206" t="n">
-        <v>0.4542</v>
+        <v>0.4586</v>
       </c>
       <c r="K206" t="n">
-        <v>0.5999</v>
+        <v>0.6042</v>
       </c>
       <c r="L206" t="n">
-        <v>0.527</v>
+        <v>0.5314</v>
       </c>
       <c r="M206" t="n">
         <v>155</v>
@@ -11586,22 +11586,22 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>0.4505</v>
+        <v>0.4659</v>
       </c>
       <c r="H207" t="n">
-        <v>0.3344</v>
+        <v>0.346</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3924</v>
+        <v>0.406</v>
       </c>
       <c r="J207" t="n">
-        <v>0.5495</v>
+        <v>0.5341</v>
       </c>
       <c r="K207" t="n">
-        <v>0.6656</v>
+        <v>0.654</v>
       </c>
       <c r="L207" t="n">
-        <v>0.6076</v>
+        <v>0.594</v>
       </c>
       <c r="M207" t="n">
         <v>155</v>
@@ -11694,22 +11694,22 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>0.784</v>
+        <v>0.8062</v>
       </c>
       <c r="H209" t="n">
-        <v>0.6601</v>
+        <v>0.6908</v>
       </c>
       <c r="I209" t="n">
-        <v>0.7221</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="J209" t="n">
-        <v>0.216</v>
+        <v>0.1938</v>
       </c>
       <c r="K209" t="n">
-        <v>0.3399</v>
+        <v>0.3092</v>
       </c>
       <c r="L209" t="n">
-        <v>0.2779</v>
+        <v>0.2515</v>
       </c>
       <c r="M209" t="n">
         <v>155</v>
@@ -11748,22 +11748,22 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>0.5534</v>
+        <v>0.5717</v>
       </c>
       <c r="H210" t="n">
-        <v>0.4089</v>
+        <v>0.4269</v>
       </c>
       <c r="I210" t="n">
-        <v>0.4812</v>
+        <v>0.4993</v>
       </c>
       <c r="J210" t="n">
-        <v>0.4466</v>
+        <v>0.4283</v>
       </c>
       <c r="K210" t="n">
-        <v>0.5911</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="L210" t="n">
-        <v>0.5188</v>
+        <v>0.5007</v>
       </c>
       <c r="M210" t="n">
         <v>155</v>
@@ -11802,22 +11802,22 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>0.8375</v>
+        <v>0.8387</v>
       </c>
       <c r="H211" t="n">
         <v>0.7467</v>
       </c>
       <c r="I211" t="n">
-        <v>0.7921</v>
+        <v>0.7927</v>
       </c>
       <c r="J211" t="n">
-        <v>0.1625</v>
+        <v>0.1613</v>
       </c>
       <c r="K211" t="n">
         <v>0.2533</v>
       </c>
       <c r="L211" t="n">
-        <v>0.2079</v>
+        <v>0.2073</v>
       </c>
       <c r="M211" t="n">
         <v>155</v>
@@ -12018,22 +12018,22 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>0.7034</v>
+        <v>0.6825</v>
       </c>
       <c r="H215" t="n">
-        <v>0.5666</v>
+        <v>0.5413</v>
       </c>
       <c r="I215" t="n">
-        <v>0.635</v>
+        <v>0.6119</v>
       </c>
       <c r="J215" t="n">
-        <v>0.2966</v>
+        <v>0.3175</v>
       </c>
       <c r="K215" t="n">
-        <v>0.4334</v>
+        <v>0.4587</v>
       </c>
       <c r="L215" t="n">
-        <v>0.365</v>
+        <v>0.3881</v>
       </c>
       <c r="M215" t="n">
         <v>155</v>
@@ -12180,22 +12180,22 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>0.8056</v>
+        <v>0.8064</v>
       </c>
       <c r="H218" t="n">
         <v>0.6953</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7504999999999999</v>
+        <v>0.7508</v>
       </c>
       <c r="J218" t="n">
-        <v>0.1944</v>
+        <v>0.1936</v>
       </c>
       <c r="K218" t="n">
         <v>0.3047</v>
       </c>
       <c r="L218" t="n">
-        <v>0.2495</v>
+        <v>0.2492</v>
       </c>
       <c r="M218" t="n">
         <v>155</v>
@@ -12234,22 +12234,22 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>0.4041</v>
+        <v>0.4034</v>
       </c>
       <c r="H219" t="n">
-        <v>0.2964</v>
+        <v>0.2958</v>
       </c>
       <c r="I219" t="n">
-        <v>0.3502</v>
+        <v>0.3496</v>
       </c>
       <c r="J219" t="n">
-        <v>0.5959</v>
+        <v>0.5966</v>
       </c>
       <c r="K219" t="n">
-        <v>0.7036</v>
+        <v>0.7042</v>
       </c>
       <c r="L219" t="n">
-        <v>0.6498</v>
+        <v>0.6504</v>
       </c>
       <c r="M219" t="n">
         <v>155</v>
@@ -12288,22 +12288,22 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>0.3289</v>
+        <v>0.3276</v>
       </c>
       <c r="H220" t="n">
-        <v>0.2202</v>
+        <v>0.2191</v>
       </c>
       <c r="I220" t="n">
-        <v>0.2746</v>
+        <v>0.2734</v>
       </c>
       <c r="J220" t="n">
-        <v>0.6711</v>
+        <v>0.6724</v>
       </c>
       <c r="K220" t="n">
-        <v>0.7798</v>
+        <v>0.7809</v>
       </c>
       <c r="L220" t="n">
-        <v>0.7254</v>
+        <v>0.7266</v>
       </c>
       <c r="M220" t="n">
         <v>155</v>
@@ -12342,22 +12342,22 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>0.5969</v>
+        <v>0.6002999999999999</v>
       </c>
       <c r="H221" t="n">
-        <v>0.4544</v>
+        <v>0.4599</v>
       </c>
       <c r="I221" t="n">
-        <v>0.5256</v>
+        <v>0.5301</v>
       </c>
       <c r="J221" t="n">
-        <v>0.4031</v>
+        <v>0.3997</v>
       </c>
       <c r="K221" t="n">
-        <v>0.5456</v>
+        <v>0.5401</v>
       </c>
       <c r="L221" t="n">
-        <v>0.4744</v>
+        <v>0.4699</v>
       </c>
       <c r="M221" t="n">
         <v>155</v>
@@ -12396,22 +12396,22 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>0.8073</v>
+        <v>0.8092</v>
       </c>
       <c r="H222" t="n">
-        <v>0.6988</v>
+        <v>0.7014</v>
       </c>
       <c r="I222" t="n">
-        <v>0.753</v>
+        <v>0.7553</v>
       </c>
       <c r="J222" t="n">
-        <v>0.1927</v>
+        <v>0.1908</v>
       </c>
       <c r="K222" t="n">
-        <v>0.3012</v>
+        <v>0.2986</v>
       </c>
       <c r="L222" t="n">
-        <v>0.247</v>
+        <v>0.2447</v>
       </c>
       <c r="M222" t="n">
         <v>155</v>
@@ -12561,19 +12561,19 @@
         <v>0.498</v>
       </c>
       <c r="H225" t="n">
-        <v>0.3637</v>
+        <v>0.3655</v>
       </c>
       <c r="I225" t="n">
-        <v>0.4308</v>
+        <v>0.4318</v>
       </c>
       <c r="J225" t="n">
         <v>0.502</v>
       </c>
       <c r="K225" t="n">
-        <v>0.6363</v>
+        <v>0.6345</v>
       </c>
       <c r="L225" t="n">
-        <v>0.5692</v>
+        <v>0.5682</v>
       </c>
       <c r="M225" t="n">
         <v>155</v>
@@ -12666,22 +12666,22 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>0.5354</v>
+        <v>0.5401</v>
       </c>
       <c r="H227" t="n">
-        <v>0.4148</v>
+        <v>0.4171</v>
       </c>
       <c r="I227" t="n">
-        <v>0.4751</v>
+        <v>0.4786</v>
       </c>
       <c r="J227" t="n">
-        <v>0.4646</v>
+        <v>0.4599</v>
       </c>
       <c r="K227" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.5829</v>
       </c>
       <c r="L227" t="n">
-        <v>0.5249</v>
+        <v>0.5214</v>
       </c>
       <c r="M227" t="n">
         <v>155</v>
@@ -12774,22 +12774,22 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="H229" t="n">
-        <v>0.7059</v>
+        <v>0.7311</v>
       </c>
       <c r="I229" t="n">
-        <v>0.759</v>
+        <v>0.7786</v>
       </c>
       <c r="J229" t="n">
-        <v>0.188</v>
+        <v>0.1739</v>
       </c>
       <c r="K229" t="n">
-        <v>0.2941</v>
+        <v>0.2689</v>
       </c>
       <c r="L229" t="n">
-        <v>0.241</v>
+        <v>0.2214</v>
       </c>
       <c r="M229" t="n">
         <v>155</v>
@@ -12828,22 +12828,22 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>0.5967</v>
+        <v>0.6233</v>
       </c>
       <c r="H230" t="n">
-        <v>0.4466</v>
+        <v>0.4715</v>
       </c>
       <c r="I230" t="n">
-        <v>0.5216</v>
+        <v>0.5474</v>
       </c>
       <c r="J230" t="n">
-        <v>0.4033</v>
+        <v>0.3767</v>
       </c>
       <c r="K230" t="n">
-        <v>0.5534</v>
+        <v>0.5285</v>
       </c>
       <c r="L230" t="n">
-        <v>0.4784</v>
+        <v>0.4526</v>
       </c>
       <c r="M230" t="n">
         <v>155</v>
@@ -13044,22 +13044,22 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>0.8381</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="H234" t="n">
         <v>0.7504999999999999</v>
       </c>
       <c r="I234" t="n">
-        <v>0.7943</v>
+        <v>0.7948</v>
       </c>
       <c r="J234" t="n">
-        <v>0.1619</v>
+        <v>0.1608</v>
       </c>
       <c r="K234" t="n">
         <v>0.2495</v>
       </c>
       <c r="L234" t="n">
-        <v>0.2057</v>
+        <v>0.2052</v>
       </c>
       <c r="M234" t="n">
         <v>155</v>
@@ -13098,22 +13098,22 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>0.7389</v>
+        <v>0.7179</v>
       </c>
       <c r="H235" t="n">
-        <v>0.5962</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="I235" t="n">
-        <v>0.6676</v>
+        <v>0.6445</v>
       </c>
       <c r="J235" t="n">
-        <v>0.2611</v>
+        <v>0.2821</v>
       </c>
       <c r="K235" t="n">
-        <v>0.4038</v>
+        <v>0.4289</v>
       </c>
       <c r="L235" t="n">
-        <v>0.3324</v>
+        <v>0.3555</v>
       </c>
       <c r="M235" t="n">
         <v>155</v>
@@ -13152,22 +13152,22 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>0.6449</v>
+        <v>0.6466</v>
       </c>
       <c r="H236" t="n">
-        <v>0.5022</v>
+        <v>0.5041</v>
       </c>
       <c r="I236" t="n">
-        <v>0.5736</v>
+        <v>0.5754</v>
       </c>
       <c r="J236" t="n">
-        <v>0.3551</v>
+        <v>0.3534</v>
       </c>
       <c r="K236" t="n">
-        <v>0.4978</v>
+        <v>0.4959</v>
       </c>
       <c r="L236" t="n">
-        <v>0.4264</v>
+        <v>0.4246</v>
       </c>
       <c r="M236" t="n">
         <v>155</v>
@@ -13206,22 +13206,22 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6891</v>
       </c>
       <c r="H237" t="n">
-        <v>0.5471</v>
+        <v>0.5481</v>
       </c>
       <c r="I237" t="n">
-        <v>0.618</v>
+        <v>0.6186</v>
       </c>
       <c r="J237" t="n">
-        <v>0.311</v>
+        <v>0.3109</v>
       </c>
       <c r="K237" t="n">
-        <v>0.4529</v>
+        <v>0.4519</v>
       </c>
       <c r="L237" t="n">
-        <v>0.382</v>
+        <v>0.3814</v>
       </c>
       <c r="M237" t="n">
         <v>155</v>
@@ -13422,22 +13422,22 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>0.6332</v>
+        <v>0.6344</v>
       </c>
       <c r="H241" t="n">
-        <v>0.4766</v>
+        <v>0.4787</v>
       </c>
       <c r="I241" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.5566</v>
       </c>
       <c r="J241" t="n">
-        <v>0.3668</v>
+        <v>0.3656</v>
       </c>
       <c r="K241" t="n">
-        <v>0.5234</v>
+        <v>0.5213</v>
       </c>
       <c r="L241" t="n">
-        <v>0.4451</v>
+        <v>0.4434</v>
       </c>
       <c r="M241" t="n">
         <v>155</v>
@@ -13530,22 +13530,22 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>0.8164</v>
+        <v>0.8186</v>
       </c>
       <c r="H243" t="n">
-        <v>0.7078</v>
+        <v>0.7114</v>
       </c>
       <c r="I243" t="n">
-        <v>0.7621</v>
+        <v>0.765</v>
       </c>
       <c r="J243" t="n">
-        <v>0.1836</v>
+        <v>0.1814</v>
       </c>
       <c r="K243" t="n">
-        <v>0.2922</v>
+        <v>0.2886</v>
       </c>
       <c r="L243" t="n">
-        <v>0.2379</v>
+        <v>0.235</v>
       </c>
       <c r="M243" t="n">
         <v>155</v>
@@ -13692,22 +13692,22 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>0.5796</v>
+        <v>0.5818</v>
       </c>
       <c r="H246" t="n">
-        <v>0.4323</v>
+        <v>0.432</v>
       </c>
       <c r="I246" t="n">
-        <v>0.506</v>
+        <v>0.5069</v>
       </c>
       <c r="J246" t="n">
-        <v>0.4204</v>
+        <v>0.4182</v>
       </c>
       <c r="K246" t="n">
-        <v>0.5677</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="L246" t="n">
-        <v>0.494</v>
+        <v>0.4931</v>
       </c>
       <c r="M246" t="n">
         <v>155</v>
@@ -13746,22 +13746,22 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>0.6744</v>
+        <v>0.6641</v>
       </c>
       <c r="H247" t="n">
-        <v>0.5252</v>
+        <v>0.5135</v>
       </c>
       <c r="I247" t="n">
-        <v>0.5998</v>
+        <v>0.5888</v>
       </c>
       <c r="J247" t="n">
-        <v>0.3256</v>
+        <v>0.3359</v>
       </c>
       <c r="K247" t="n">
-        <v>0.4748</v>
+        <v>0.4865</v>
       </c>
       <c r="L247" t="n">
-        <v>0.4002</v>
+        <v>0.4112</v>
       </c>
       <c r="M247" t="n">
         <v>155</v>
@@ -13800,22 +13800,22 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>0.828</v>
+        <v>0.8303</v>
       </c>
       <c r="H248" t="n">
-        <v>0.7339</v>
+        <v>0.737</v>
       </c>
       <c r="I248" t="n">
-        <v>0.781</v>
+        <v>0.7836</v>
       </c>
       <c r="J248" t="n">
-        <v>0.172</v>
+        <v>0.1697</v>
       </c>
       <c r="K248" t="n">
-        <v>0.2661</v>
+        <v>0.263</v>
       </c>
       <c r="L248" t="n">
-        <v>0.219</v>
+        <v>0.2164</v>
       </c>
       <c r="M248" t="n">
         <v>155</v>
@@ -13854,22 +13854,22 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>0.6551</v>
+        <v>0.656</v>
       </c>
       <c r="H249" t="n">
-        <v>0.4996</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="I249" t="n">
-        <v>0.5774</v>
+        <v>0.5782</v>
       </c>
       <c r="J249" t="n">
-        <v>0.3449</v>
+        <v>0.344</v>
       </c>
       <c r="K249" t="n">
-        <v>0.5004</v>
+        <v>0.4995</v>
       </c>
       <c r="L249" t="n">
-        <v>0.4226</v>
+        <v>0.4218</v>
       </c>
       <c r="M249" t="n">
         <v>155</v>
@@ -13962,22 +13962,22 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>0.5555</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="H251" t="n">
-        <v>0.4029</v>
+        <v>0.3904</v>
       </c>
       <c r="I251" t="n">
-        <v>0.4792</v>
+        <v>0.4651</v>
       </c>
       <c r="J251" t="n">
-        <v>0.4445</v>
+        <v>0.4602</v>
       </c>
       <c r="K251" t="n">
-        <v>0.5971</v>
+        <v>0.6096</v>
       </c>
       <c r="L251" t="n">
-        <v>0.5208</v>
+        <v>0.5349</v>
       </c>
       <c r="M251" t="n">
         <v>155</v>
@@ -14016,22 +14016,22 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>0.7138</v>
+        <v>0.7078</v>
       </c>
       <c r="H252" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.5638</v>
       </c>
       <c r="I252" t="n">
-        <v>0.6424</v>
+        <v>0.6358</v>
       </c>
       <c r="J252" t="n">
-        <v>0.2862</v>
+        <v>0.2922</v>
       </c>
       <c r="K252" t="n">
-        <v>0.4289</v>
+        <v>0.4362</v>
       </c>
       <c r="L252" t="n">
-        <v>0.3576</v>
+        <v>0.3642</v>
       </c>
       <c r="M252" t="n">
         <v>155</v>
@@ -14124,22 +14124,22 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>0.7595</v>
+        <v>0.7415</v>
       </c>
       <c r="H254" t="n">
-        <v>0.6319</v>
+        <v>0.6019</v>
       </c>
       <c r="I254" t="n">
-        <v>0.6957</v>
+        <v>0.6717</v>
       </c>
       <c r="J254" t="n">
-        <v>0.2405</v>
+        <v>0.2585</v>
       </c>
       <c r="K254" t="n">
-        <v>0.3681</v>
+        <v>0.3981</v>
       </c>
       <c r="L254" t="n">
-        <v>0.3043</v>
+        <v>0.3283</v>
       </c>
       <c r="M254" t="n">
         <v>155</v>
@@ -14178,22 +14178,22 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>0.6807</v>
+        <v>0.6784</v>
       </c>
       <c r="H255" t="n">
-        <v>0.5423</v>
+        <v>0.5396</v>
       </c>
       <c r="I255" t="n">
-        <v>0.6115</v>
+        <v>0.609</v>
       </c>
       <c r="J255" t="n">
-        <v>0.3193</v>
+        <v>0.3216</v>
       </c>
       <c r="K255" t="n">
-        <v>0.4577</v>
+        <v>0.4604</v>
       </c>
       <c r="L255" t="n">
-        <v>0.3885</v>
+        <v>0.391</v>
       </c>
       <c r="M255" t="n">
         <v>155</v>
@@ -14232,22 +14232,22 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>0.7383</v>
+        <v>0.732</v>
       </c>
       <c r="H256" t="n">
-        <v>0.5985</v>
+        <v>0.5907</v>
       </c>
       <c r="I256" t="n">
-        <v>0.6684</v>
+        <v>0.6614</v>
       </c>
       <c r="J256" t="n">
-        <v>0.2617</v>
+        <v>0.268</v>
       </c>
       <c r="K256" t="n">
-        <v>0.4015</v>
+        <v>0.4093</v>
       </c>
       <c r="L256" t="n">
-        <v>0.3316</v>
+        <v>0.3386</v>
       </c>
       <c r="M256" t="n">
         <v>155</v>
@@ -14286,22 +14286,22 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>0.8512</v>
+        <v>0.8498</v>
       </c>
       <c r="H257" t="n">
         <v>0.7704</v>
       </c>
       <c r="I257" t="n">
-        <v>0.8108</v>
+        <v>0.8101</v>
       </c>
       <c r="J257" t="n">
-        <v>0.1488</v>
+        <v>0.1502</v>
       </c>
       <c r="K257" t="n">
         <v>0.2296</v>
       </c>
       <c r="L257" t="n">
-        <v>0.1892</v>
+        <v>0.1899</v>
       </c>
       <c r="M257" t="n">
         <v>155</v>
@@ -14394,22 +14394,22 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>0.455</v>
+        <v>0.4508</v>
       </c>
       <c r="H259" t="n">
-        <v>0.3119</v>
+        <v>0.3083</v>
       </c>
       <c r="I259" t="n">
-        <v>0.3834</v>
+        <v>0.3796</v>
       </c>
       <c r="J259" t="n">
-        <v>0.545</v>
+        <v>0.5492</v>
       </c>
       <c r="K259" t="n">
-        <v>0.6881</v>
+        <v>0.6917</v>
       </c>
       <c r="L259" t="n">
-        <v>0.6166</v>
+        <v>0.6204</v>
       </c>
       <c r="M259" t="n">
         <v>155</v>
@@ -14448,22 +14448,22 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>0.6743</v>
+        <v>0.6786</v>
       </c>
       <c r="H260" t="n">
-        <v>0.5248</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="I260" t="n">
-        <v>0.5996</v>
+        <v>0.6042</v>
       </c>
       <c r="J260" t="n">
-        <v>0.3257</v>
+        <v>0.3214</v>
       </c>
       <c r="K260" t="n">
-        <v>0.4752</v>
+        <v>0.4703</v>
       </c>
       <c r="L260" t="n">
-        <v>0.4004</v>
+        <v>0.3958</v>
       </c>
       <c r="M260" t="n">
         <v>155</v>
@@ -14556,22 +14556,22 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>0.838</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="H262" t="n">
-        <v>0.7471</v>
+        <v>0.7446</v>
       </c>
       <c r="I262" t="n">
-        <v>0.7926</v>
+        <v>0.7904</v>
       </c>
       <c r="J262" t="n">
-        <v>0.162</v>
+        <v>0.1638</v>
       </c>
       <c r="K262" t="n">
-        <v>0.2529</v>
+        <v>0.2554</v>
       </c>
       <c r="L262" t="n">
-        <v>0.2074</v>
+        <v>0.2096</v>
       </c>
       <c r="M262" t="n">
         <v>155</v>
@@ -14664,22 +14664,22 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>0.6046</v>
+        <v>0.6017</v>
       </c>
       <c r="H264" t="n">
-        <v>0.4547</v>
+        <v>0.4517</v>
       </c>
       <c r="I264" t="n">
-        <v>0.5296</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="J264" t="n">
-        <v>0.3954</v>
+        <v>0.3983</v>
       </c>
       <c r="K264" t="n">
-        <v>0.5453</v>
+        <v>0.5483</v>
       </c>
       <c r="L264" t="n">
-        <v>0.4704</v>
+        <v>0.4733</v>
       </c>
       <c r="M264" t="n">
         <v>155</v>
@@ -14772,22 +14772,22 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>0.7738</v>
+        <v>0.7995</v>
       </c>
       <c r="H266" t="n">
-        <v>0.6411</v>
+        <v>0.6746</v>
       </c>
       <c r="I266" t="n">
-        <v>0.7074</v>
+        <v>0.737</v>
       </c>
       <c r="J266" t="n">
-        <v>0.2262</v>
+        <v>0.2005</v>
       </c>
       <c r="K266" t="n">
-        <v>0.3589</v>
+        <v>0.3254</v>
       </c>
       <c r="L266" t="n">
-        <v>0.2926</v>
+        <v>0.263</v>
       </c>
       <c r="M266" t="n">
         <v>155</v>
@@ -14826,22 +14826,22 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>0.5308</v>
+        <v>0.5423</v>
       </c>
       <c r="H267" t="n">
-        <v>0.3806</v>
+        <v>0.3916</v>
       </c>
       <c r="I267" t="n">
-        <v>0.4557</v>
+        <v>0.467</v>
       </c>
       <c r="J267" t="n">
-        <v>0.4692</v>
+        <v>0.4577</v>
       </c>
       <c r="K267" t="n">
-        <v>0.6194</v>
+        <v>0.6084000000000001</v>
       </c>
       <c r="L267" t="n">
-        <v>0.5443</v>
+        <v>0.533</v>
       </c>
       <c r="M267" t="n">
         <v>155</v>
@@ -15096,22 +15096,22 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>0.6987</v>
+        <v>0.663</v>
       </c>
       <c r="H272" t="n">
-        <v>0.5513</v>
+        <v>0.5161</v>
       </c>
       <c r="I272" t="n">
-        <v>0.625</v>
+        <v>0.5896</v>
       </c>
       <c r="J272" t="n">
-        <v>0.3013</v>
+        <v>0.337</v>
       </c>
       <c r="K272" t="n">
-        <v>0.4487</v>
+        <v>0.4839</v>
       </c>
       <c r="L272" t="n">
-        <v>0.375</v>
+        <v>0.4104</v>
       </c>
       <c r="M272" t="n">
         <v>155</v>
@@ -15258,22 +15258,22 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>0.8014</v>
+        <v>0.8047</v>
       </c>
       <c r="H275" t="n">
-        <v>0.6876</v>
+        <v>0.6921</v>
       </c>
       <c r="I275" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.7484</v>
       </c>
       <c r="J275" t="n">
-        <v>0.1986</v>
+        <v>0.1953</v>
       </c>
       <c r="K275" t="n">
-        <v>0.3124</v>
+        <v>0.3079</v>
       </c>
       <c r="L275" t="n">
-        <v>0.2555</v>
+        <v>0.2516</v>
       </c>
       <c r="M275" t="n">
         <v>155</v>
@@ -15420,22 +15420,22 @@
         </is>
       </c>
       <c r="G278" t="n">
-        <v>0.5936</v>
+        <v>0.6106</v>
       </c>
       <c r="H278" t="n">
-        <v>0.4453</v>
+        <v>0.4584</v>
       </c>
       <c r="I278" t="n">
-        <v>0.5194</v>
+        <v>0.5345</v>
       </c>
       <c r="J278" t="n">
-        <v>0.4064</v>
+        <v>0.3894</v>
       </c>
       <c r="K278" t="n">
-        <v>0.5547</v>
+        <v>0.5416</v>
       </c>
       <c r="L278" t="n">
-        <v>0.4806</v>
+        <v>0.4655</v>
       </c>
       <c r="M278" t="n">
         <v>155</v>
@@ -15528,22 +15528,22 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>0.7859</v>
+        <v>0.7867</v>
       </c>
       <c r="H280" t="n">
         <v>0.6646</v>
       </c>
       <c r="I280" t="n">
-        <v>0.7252</v>
+        <v>0.7256</v>
       </c>
       <c r="J280" t="n">
-        <v>0.2141</v>
+        <v>0.2133</v>
       </c>
       <c r="K280" t="n">
         <v>0.3354</v>
       </c>
       <c r="L280" t="n">
-        <v>0.2748</v>
+        <v>0.2744</v>
       </c>
       <c r="M280" t="n">
         <v>155</v>
@@ -15744,22 +15744,22 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>0.2933</v>
+        <v>0.2819</v>
       </c>
       <c r="H284" t="n">
-        <v>0.1989</v>
+        <v>0.1924</v>
       </c>
       <c r="I284" t="n">
-        <v>0.2461</v>
+        <v>0.2371</v>
       </c>
       <c r="J284" t="n">
-        <v>0.7067</v>
+        <v>0.7181</v>
       </c>
       <c r="K284" t="n">
-        <v>0.8011</v>
+        <v>0.8076</v>
       </c>
       <c r="L284" t="n">
-        <v>0.7539</v>
+        <v>0.7629</v>
       </c>
       <c r="M284" t="n">
         <v>155</v>
@@ -15798,22 +15798,22 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>0.706</v>
+        <v>0.6821</v>
       </c>
       <c r="H285" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5327</v>
       </c>
       <c r="I285" t="n">
-        <v>0.6335</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="J285" t="n">
-        <v>0.294</v>
+        <v>0.3179</v>
       </c>
       <c r="K285" t="n">
-        <v>0.439</v>
+        <v>0.4673</v>
       </c>
       <c r="L285" t="n">
-        <v>0.3665</v>
+        <v>0.3926</v>
       </c>
       <c r="M285" t="n">
         <v>155</v>
@@ -15852,22 +15852,22 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>0.2324</v>
+        <v>0.2204</v>
       </c>
       <c r="H286" t="n">
-        <v>0.1535</v>
+        <v>0.1458</v>
       </c>
       <c r="I286" t="n">
-        <v>0.193</v>
+        <v>0.1831</v>
       </c>
       <c r="J286" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.7796</v>
       </c>
       <c r="K286" t="n">
-        <v>0.8465</v>
+        <v>0.8542</v>
       </c>
       <c r="L286" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8169</v>
       </c>
       <c r="M286" t="n">
         <v>155</v>
@@ -15906,22 +15906,22 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>0.4116</v>
+        <v>0.3623</v>
       </c>
       <c r="H287" t="n">
-        <v>0.2808</v>
+        <v>0.2474</v>
       </c>
       <c r="I287" t="n">
-        <v>0.3462</v>
+        <v>0.3048</v>
       </c>
       <c r="J287" t="n">
-        <v>0.5884</v>
+        <v>0.6377</v>
       </c>
       <c r="K287" t="n">
-        <v>0.7192</v>
+        <v>0.7526</v>
       </c>
       <c r="L287" t="n">
-        <v>0.6538</v>
+        <v>0.6952</v>
       </c>
       <c r="M287" t="n">
         <v>155</v>
@@ -15960,22 +15960,22 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>0.6424</v>
+        <v>0.6047</v>
       </c>
       <c r="H288" t="n">
-        <v>0.5067</v>
+        <v>0.4711</v>
       </c>
       <c r="I288" t="n">
-        <v>0.5746</v>
+        <v>0.5379</v>
       </c>
       <c r="J288" t="n">
-        <v>0.3576</v>
+        <v>0.3953</v>
       </c>
       <c r="K288" t="n">
-        <v>0.4933</v>
+        <v>0.5289</v>
       </c>
       <c r="L288" t="n">
-        <v>0.4254</v>
+        <v>0.4621</v>
       </c>
       <c r="M288" t="n">
         <v>155</v>
@@ -16014,22 +16014,22 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>0.5057</v>
+        <v>0.4149</v>
       </c>
       <c r="H289" t="n">
-        <v>0.3616</v>
+        <v>0.2907</v>
       </c>
       <c r="I289" t="n">
-        <v>0.4336</v>
+        <v>0.3528</v>
       </c>
       <c r="J289" t="n">
-        <v>0.4943</v>
+        <v>0.5851</v>
       </c>
       <c r="K289" t="n">
-        <v>0.6384</v>
+        <v>0.7093</v>
       </c>
       <c r="L289" t="n">
-        <v>0.5664</v>
+        <v>0.6472</v>
       </c>
       <c r="M289" t="n">
         <v>155</v>
@@ -16068,22 +16068,22 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>0.3751</v>
+        <v>0.3246</v>
       </c>
       <c r="H290" t="n">
-        <v>0.2509</v>
+        <v>0.2178</v>
       </c>
       <c r="I290" t="n">
-        <v>0.313</v>
+        <v>0.2712</v>
       </c>
       <c r="J290" t="n">
-        <v>0.6249</v>
+        <v>0.6754</v>
       </c>
       <c r="K290" t="n">
-        <v>0.7491</v>
+        <v>0.7822</v>
       </c>
       <c r="L290" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.7288</v>
       </c>
       <c r="M290" t="n">
         <v>155</v>
@@ -16122,22 +16122,22 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>0.4402</v>
+        <v>0.3907</v>
       </c>
       <c r="H291" t="n">
-        <v>0.3018</v>
+        <v>0.268</v>
       </c>
       <c r="I291" t="n">
-        <v>0.371</v>
+        <v>0.3294</v>
       </c>
       <c r="J291" t="n">
-        <v>0.5598</v>
+        <v>0.6093</v>
       </c>
       <c r="K291" t="n">
-        <v>0.6982</v>
+        <v>0.732</v>
       </c>
       <c r="L291" t="n">
-        <v>0.629</v>
+        <v>0.6706</v>
       </c>
       <c r="M291" t="n">
         <v>155</v>
@@ -16176,22 +16176,22 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>0.6387</v>
+        <v>0.6057</v>
       </c>
       <c r="H292" t="n">
-        <v>0.499</v>
+        <v>0.4621</v>
       </c>
       <c r="I292" t="n">
-        <v>0.5689</v>
+        <v>0.5339</v>
       </c>
       <c r="J292" t="n">
-        <v>0.3613</v>
+        <v>0.3943</v>
       </c>
       <c r="K292" t="n">
-        <v>0.501</v>
+        <v>0.5379</v>
       </c>
       <c r="L292" t="n">
-        <v>0.4311</v>
+        <v>0.4661</v>
       </c>
       <c r="M292" t="n">
         <v>155</v>
@@ -16230,22 +16230,22 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>0.2326</v>
+        <v>0.2185</v>
       </c>
       <c r="H293" t="n">
-        <v>0.1481</v>
+        <v>0.1413</v>
       </c>
       <c r="I293" t="n">
-        <v>0.1904</v>
+        <v>0.1799</v>
       </c>
       <c r="J293" t="n">
-        <v>0.7674</v>
+        <v>0.7815</v>
       </c>
       <c r="K293" t="n">
-        <v>0.8519</v>
+        <v>0.8587</v>
       </c>
       <c r="L293" t="n">
-        <v>0.8096</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="M293" t="n">
         <v>155</v>
@@ -16284,22 +16284,22 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>0.2173</v>
+        <v>0.2111</v>
       </c>
       <c r="H294" t="n">
-        <v>0.1399</v>
+        <v>0.1377</v>
       </c>
       <c r="I294" t="n">
-        <v>0.1786</v>
+        <v>0.1744</v>
       </c>
       <c r="J294" t="n">
-        <v>0.7827</v>
+        <v>0.7889</v>
       </c>
       <c r="K294" t="n">
-        <v>0.8601</v>
+        <v>0.8623</v>
       </c>
       <c r="L294" t="n">
-        <v>0.8214</v>
+        <v>0.8256</v>
       </c>
       <c r="M294" t="n">
         <v>155</v>
@@ -16338,22 +16338,22 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>0.318</v>
+        <v>0.3037</v>
       </c>
       <c r="H295" t="n">
-        <v>0.2236</v>
+        <v>0.216</v>
       </c>
       <c r="I295" t="n">
-        <v>0.2708</v>
+        <v>0.2599</v>
       </c>
       <c r="J295" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.6963</v>
       </c>
       <c r="K295" t="n">
-        <v>0.7764</v>
+        <v>0.784</v>
       </c>
       <c r="L295" t="n">
-        <v>0.7292</v>
+        <v>0.7401</v>
       </c>
       <c r="M295" t="n">
         <v>155</v>
@@ -16392,22 +16392,22 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>0.6463</v>
+        <v>0.6089</v>
       </c>
       <c r="H296" t="n">
-        <v>0.5056</v>
+        <v>0.4656</v>
       </c>
       <c r="I296" t="n">
-        <v>0.576</v>
+        <v>0.5372</v>
       </c>
       <c r="J296" t="n">
-        <v>0.3537</v>
+        <v>0.3911</v>
       </c>
       <c r="K296" t="n">
-        <v>0.4944</v>
+        <v>0.5344</v>
       </c>
       <c r="L296" t="n">
-        <v>0.424</v>
+        <v>0.4628</v>
       </c>
       <c r="M296" t="n">
         <v>155</v>
@@ -16446,22 +16446,22 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>0.602</v>
+        <v>0.5677</v>
       </c>
       <c r="H297" t="n">
-        <v>0.4392</v>
+        <v>0.4064</v>
       </c>
       <c r="I297" t="n">
-        <v>0.5206</v>
+        <v>0.487</v>
       </c>
       <c r="J297" t="n">
-        <v>0.398</v>
+        <v>0.4323</v>
       </c>
       <c r="K297" t="n">
-        <v>0.5608</v>
+        <v>0.5936</v>
       </c>
       <c r="L297" t="n">
-        <v>0.4794</v>
+        <v>0.513</v>
       </c>
       <c r="M297" t="n">
         <v>155</v>
@@ -16500,22 +16500,22 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>0.7337</v>
+        <v>0.6998</v>
       </c>
       <c r="H298" t="n">
-        <v>0.6065</v>
+        <v>0.5654</v>
       </c>
       <c r="I298" t="n">
-        <v>0.6701</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="J298" t="n">
-        <v>0.2663</v>
+        <v>0.3002</v>
       </c>
       <c r="K298" t="n">
-        <v>0.3935</v>
+        <v>0.4346</v>
       </c>
       <c r="L298" t="n">
-        <v>0.3299</v>
+        <v>0.3674</v>
       </c>
       <c r="M298" t="n">
         <v>155</v>
@@ -16554,22 +16554,22 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>0.3034</v>
+        <v>0.25</v>
       </c>
       <c r="H299" t="n">
-        <v>0.2041</v>
+        <v>0.1687</v>
       </c>
       <c r="I299" t="n">
-        <v>0.2538</v>
+        <v>0.2094</v>
       </c>
       <c r="J299" t="n">
-        <v>0.6966</v>
+        <v>0.75</v>
       </c>
       <c r="K299" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.8313</v>
       </c>
       <c r="L299" t="n">
-        <v>0.7462</v>
+        <v>0.7906</v>
       </c>
       <c r="M299" t="n">
         <v>155</v>
@@ -16608,22 +16608,22 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>0.2927</v>
+        <v>0.2559</v>
       </c>
       <c r="H300" t="n">
-        <v>0.1924</v>
+        <v>0.1719</v>
       </c>
       <c r="I300" t="n">
-        <v>0.2426</v>
+        <v>0.2139</v>
       </c>
       <c r="J300" t="n">
-        <v>0.7073</v>
+        <v>0.7441</v>
       </c>
       <c r="K300" t="n">
-        <v>0.8076</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="L300" t="n">
-        <v>0.7574</v>
+        <v>0.7861</v>
       </c>
       <c r="M300" t="n">
         <v>155</v>
@@ -16662,22 +16662,22 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>0.8494</v>
+        <v>0.843</v>
       </c>
       <c r="H301" t="n">
-        <v>0.7652</v>
+        <v>0.7509</v>
       </c>
       <c r="I301" t="n">
-        <v>0.8073</v>
+        <v>0.797</v>
       </c>
       <c r="J301" t="n">
-        <v>0.1506</v>
+        <v>0.157</v>
       </c>
       <c r="K301" t="n">
-        <v>0.2348</v>
+        <v>0.2491</v>
       </c>
       <c r="L301" t="n">
-        <v>0.1927</v>
+        <v>0.203</v>
       </c>
       <c r="M301" t="n">
         <v>155</v>
@@ -16716,22 +16716,22 @@
         </is>
       </c>
       <c r="G302" t="n">
-        <v>0.4544</v>
+        <v>0.4412</v>
       </c>
       <c r="H302" t="n">
-        <v>0.3158</v>
+        <v>0.3054</v>
       </c>
       <c r="I302" t="n">
-        <v>0.3851</v>
+        <v>0.3733</v>
       </c>
       <c r="J302" t="n">
-        <v>0.5456</v>
+        <v>0.5588</v>
       </c>
       <c r="K302" t="n">
-        <v>0.6842</v>
+        <v>0.6946</v>
       </c>
       <c r="L302" t="n">
-        <v>0.6149</v>
+        <v>0.6267</v>
       </c>
       <c r="M302" t="n">
         <v>155</v>
@@ -16770,22 +16770,22 @@
         </is>
       </c>
       <c r="G303" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6682</v>
       </c>
       <c r="H303" t="n">
-        <v>0.5483</v>
+        <v>0.5242</v>
       </c>
       <c r="I303" t="n">
-        <v>0.6182</v>
+        <v>0.5962</v>
       </c>
       <c r="J303" t="n">
-        <v>0.312</v>
+        <v>0.3318</v>
       </c>
       <c r="K303" t="n">
-        <v>0.4517</v>
+        <v>0.4758</v>
       </c>
       <c r="L303" t="n">
-        <v>0.3818</v>
+        <v>0.4038</v>
       </c>
       <c r="M303" t="n">
         <v>155</v>
@@ -16824,22 +16824,22 @@
         </is>
       </c>
       <c r="G304" t="n">
-        <v>0.8336</v>
+        <v>0.8203</v>
       </c>
       <c r="H304" t="n">
-        <v>0.7336</v>
+        <v>0.7164</v>
       </c>
       <c r="I304" t="n">
-        <v>0.7836</v>
+        <v>0.7684</v>
       </c>
       <c r="J304" t="n">
-        <v>0.1664</v>
+        <v>0.1797</v>
       </c>
       <c r="K304" t="n">
-        <v>0.2664</v>
+        <v>0.2836</v>
       </c>
       <c r="L304" t="n">
-        <v>0.2164</v>
+        <v>0.2316</v>
       </c>
       <c r="M304" t="n">
         <v>155</v>
@@ -16878,22 +16878,22 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>0.7246</v>
+        <v>0.6877</v>
       </c>
       <c r="H305" t="n">
-        <v>0.5843</v>
+        <v>0.5369</v>
       </c>
       <c r="I305" t="n">
-        <v>0.6544</v>
+        <v>0.6123</v>
       </c>
       <c r="J305" t="n">
-        <v>0.2754</v>
+        <v>0.3123</v>
       </c>
       <c r="K305" t="n">
-        <v>0.4157</v>
+        <v>0.4631</v>
       </c>
       <c r="L305" t="n">
-        <v>0.3456</v>
+        <v>0.3877</v>
       </c>
       <c r="M305" t="n">
         <v>155</v>
@@ -16932,22 +16932,22 @@
         </is>
       </c>
       <c r="G306" t="n">
-        <v>0.6482</v>
+        <v>0.6313</v>
       </c>
       <c r="H306" t="n">
-        <v>0.4983</v>
+        <v>0.4791</v>
       </c>
       <c r="I306" t="n">
-        <v>0.5732</v>
+        <v>0.5552</v>
       </c>
       <c r="J306" t="n">
-        <v>0.3518</v>
+        <v>0.3687</v>
       </c>
       <c r="K306" t="n">
-        <v>0.5017</v>
+        <v>0.5209</v>
       </c>
       <c r="L306" t="n">
-        <v>0.4268</v>
+        <v>0.4448</v>
       </c>
       <c r="M306" t="n">
         <v>155</v>
@@ -16986,22 +16986,22 @@
         </is>
       </c>
       <c r="G307" t="n">
-        <v>0.696</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="H307" t="n">
-        <v>0.5618</v>
+        <v>0.5345</v>
       </c>
       <c r="I307" t="n">
-        <v>0.6289</v>
+        <v>0.6037</v>
       </c>
       <c r="J307" t="n">
-        <v>0.304</v>
+        <v>0.3271</v>
       </c>
       <c r="K307" t="n">
-        <v>0.4382</v>
+        <v>0.4655</v>
       </c>
       <c r="L307" t="n">
-        <v>0.3711</v>
+        <v>0.3963</v>
       </c>
       <c r="M307" t="n">
         <v>155</v>
@@ -17040,22 +17040,22 @@
         </is>
       </c>
       <c r="G308" t="n">
-        <v>0.8152</v>
+        <v>0.8133</v>
       </c>
       <c r="H308" t="n">
-        <v>0.704</v>
+        <v>0.7007</v>
       </c>
       <c r="I308" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.757</v>
       </c>
       <c r="J308" t="n">
-        <v>0.1848</v>
+        <v>0.1867</v>
       </c>
       <c r="K308" t="n">
-        <v>0.296</v>
+        <v>0.2993</v>
       </c>
       <c r="L308" t="n">
-        <v>0.2404</v>
+        <v>0.243</v>
       </c>
       <c r="M308" t="n">
         <v>155</v>
@@ -17094,22 +17094,22 @@
         </is>
       </c>
       <c r="G309" t="n">
-        <v>0.4347</v>
+        <v>0.4235</v>
       </c>
       <c r="H309" t="n">
-        <v>0.3073</v>
+        <v>0.2923</v>
       </c>
       <c r="I309" t="n">
-        <v>0.371</v>
+        <v>0.3579</v>
       </c>
       <c r="J309" t="n">
-        <v>0.5653</v>
+        <v>0.5765</v>
       </c>
       <c r="K309" t="n">
-        <v>0.6927</v>
+        <v>0.7077</v>
       </c>
       <c r="L309" t="n">
-        <v>0.629</v>
+        <v>0.6421</v>
       </c>
       <c r="M309" t="n">
         <v>155</v>
@@ -17148,22 +17148,22 @@
         </is>
       </c>
       <c r="G310" t="n">
-        <v>0.3594</v>
+        <v>0.3283</v>
       </c>
       <c r="H310" t="n">
-        <v>0.2337</v>
+        <v>0.2184</v>
       </c>
       <c r="I310" t="n">
-        <v>0.2966</v>
+        <v>0.2734</v>
       </c>
       <c r="J310" t="n">
-        <v>0.6405999999999999</v>
+        <v>0.6717</v>
       </c>
       <c r="K310" t="n">
-        <v>0.7663</v>
+        <v>0.7816</v>
       </c>
       <c r="L310" t="n">
-        <v>0.7034</v>
+        <v>0.7266</v>
       </c>
       <c r="M310" t="n">
         <v>155</v>
@@ -17202,22 +17202,22 @@
         </is>
       </c>
       <c r="G311" t="n">
-        <v>0.6131</v>
+        <v>0.6094000000000001</v>
       </c>
       <c r="H311" t="n">
-        <v>0.4702</v>
+        <v>0.4643</v>
       </c>
       <c r="I311" t="n">
-        <v>0.5416</v>
+        <v>0.5369</v>
       </c>
       <c r="J311" t="n">
-        <v>0.3869</v>
+        <v>0.3906</v>
       </c>
       <c r="K311" t="n">
-        <v>0.5298</v>
+        <v>0.5357</v>
       </c>
       <c r="L311" t="n">
-        <v>0.4584</v>
+        <v>0.4631</v>
       </c>
       <c r="M311" t="n">
         <v>155</v>
@@ -17256,22 +17256,22 @@
         </is>
       </c>
       <c r="G312" t="n">
-        <v>0.8209</v>
+        <v>0.8139</v>
       </c>
       <c r="H312" t="n">
-        <v>0.7083</v>
+        <v>0.6994</v>
       </c>
       <c r="I312" t="n">
-        <v>0.7645999999999999</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="J312" t="n">
-        <v>0.1791</v>
+        <v>0.1861</v>
       </c>
       <c r="K312" t="n">
-        <v>0.2917</v>
+        <v>0.3006</v>
       </c>
       <c r="L312" t="n">
-        <v>0.2354</v>
+        <v>0.2434</v>
       </c>
       <c r="M312" t="n">
         <v>155</v>
@@ -17310,22 +17310,22 @@
         </is>
       </c>
       <c r="G313" t="n">
-        <v>0.8012</v>
+        <v>0.7942</v>
       </c>
       <c r="H313" t="n">
-        <v>0.6892</v>
+        <v>0.6791</v>
       </c>
       <c r="I313" t="n">
-        <v>0.7452</v>
+        <v>0.7366</v>
       </c>
       <c r="J313" t="n">
-        <v>0.1988</v>
+        <v>0.2058</v>
       </c>
       <c r="K313" t="n">
-        <v>0.3108</v>
+        <v>0.3209</v>
       </c>
       <c r="L313" t="n">
-        <v>0.2548</v>
+        <v>0.2634</v>
       </c>
       <c r="M313" t="n">
         <v>155</v>
@@ -17364,22 +17364,22 @@
         </is>
       </c>
       <c r="G314" t="n">
-        <v>0.8449</v>
+        <v>0.8383</v>
       </c>
       <c r="H314" t="n">
-        <v>0.7473</v>
+        <v>0.7387</v>
       </c>
       <c r="I314" t="n">
-        <v>0.7961</v>
+        <v>0.7885</v>
       </c>
       <c r="J314" t="n">
-        <v>0.1551</v>
+        <v>0.1617</v>
       </c>
       <c r="K314" t="n">
-        <v>0.2527</v>
+        <v>0.2613</v>
       </c>
       <c r="L314" t="n">
-        <v>0.2039</v>
+        <v>0.2115</v>
       </c>
       <c r="M314" t="n">
         <v>155</v>
@@ -17418,22 +17418,22 @@
         </is>
       </c>
       <c r="G315" t="n">
-        <v>0.5184</v>
+        <v>0.513</v>
       </c>
       <c r="H315" t="n">
-        <v>0.3815</v>
+        <v>0.3732</v>
       </c>
       <c r="I315" t="n">
-        <v>0.45</v>
+        <v>0.4431</v>
       </c>
       <c r="J315" t="n">
-        <v>0.4816</v>
+        <v>0.487</v>
       </c>
       <c r="K315" t="n">
-        <v>0.6185</v>
+        <v>0.6268</v>
       </c>
       <c r="L315" t="n">
-        <v>0.55</v>
+        <v>0.5569</v>
       </c>
       <c r="M315" t="n">
         <v>155</v>
@@ -17472,22 +17472,22 @@
         </is>
       </c>
       <c r="G316" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.5238</v>
       </c>
       <c r="H316" t="n">
-        <v>0.3958</v>
+        <v>0.3826</v>
       </c>
       <c r="I316" t="n">
-        <v>0.4683</v>
+        <v>0.4532</v>
       </c>
       <c r="J316" t="n">
-        <v>0.4592</v>
+        <v>0.4762</v>
       </c>
       <c r="K316" t="n">
-        <v>0.6042</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="L316" t="n">
-        <v>0.5317</v>
+        <v>0.5468</v>
       </c>
       <c r="M316" t="n">
         <v>155</v>
@@ -17580,22 +17580,22 @@
         </is>
       </c>
       <c r="G318" t="n">
-        <v>0.2731</v>
+        <v>0.2703</v>
       </c>
       <c r="H318" t="n">
         <v>0.1852</v>
       </c>
       <c r="I318" t="n">
-        <v>0.2292</v>
+        <v>0.2278</v>
       </c>
       <c r="J318" t="n">
-        <v>0.7269</v>
+        <v>0.7297</v>
       </c>
       <c r="K318" t="n">
         <v>0.8148</v>
       </c>
       <c r="L318" t="n">
-        <v>0.7708</v>
+        <v>0.7722</v>
       </c>
       <c r="M318" t="n">
         <v>155</v>
@@ -17688,22 +17688,22 @@
         </is>
       </c>
       <c r="G320" t="n">
-        <v>0.3265</v>
+        <v>0.2848</v>
       </c>
       <c r="H320" t="n">
-        <v>0.2297</v>
+        <v>0.2042</v>
       </c>
       <c r="I320" t="n">
-        <v>0.2781</v>
+        <v>0.2445</v>
       </c>
       <c r="J320" t="n">
-        <v>0.6735</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="K320" t="n">
-        <v>0.7703</v>
+        <v>0.7958</v>
       </c>
       <c r="L320" t="n">
-        <v>0.7219</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="M320" t="n">
         <v>155</v>
@@ -17742,22 +17742,22 @@
         </is>
       </c>
       <c r="G321" t="n">
-        <v>0.2422</v>
+        <v>0.2415</v>
       </c>
       <c r="H321" t="n">
-        <v>0.1589</v>
+        <v>0.1585</v>
       </c>
       <c r="I321" t="n">
-        <v>0.2006</v>
+        <v>0.2</v>
       </c>
       <c r="J321" t="n">
-        <v>0.7578</v>
+        <v>0.7585</v>
       </c>
       <c r="K321" t="n">
-        <v>0.8411</v>
+        <v>0.8415</v>
       </c>
       <c r="L321" t="n">
-        <v>0.7994</v>
+        <v>0.8</v>
       </c>
       <c r="M321" t="n">
         <v>155</v>
@@ -17850,22 +17850,22 @@
         </is>
       </c>
       <c r="G323" t="n">
-        <v>0.5016</v>
+        <v>0.5031</v>
       </c>
       <c r="H323" t="n">
         <v>0.3562</v>
       </c>
       <c r="I323" t="n">
-        <v>0.4289</v>
+        <v>0.4296</v>
       </c>
       <c r="J323" t="n">
-        <v>0.4984</v>
+        <v>0.4969</v>
       </c>
       <c r="K323" t="n">
         <v>0.6438</v>
       </c>
       <c r="L323" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.5704</v>
       </c>
       <c r="M323" t="n">
         <v>155</v>
@@ -17904,22 +17904,22 @@
         </is>
       </c>
       <c r="G324" t="n">
-        <v>0.1942</v>
+        <v>0.1911</v>
       </c>
       <c r="H324" t="n">
         <v>0.1243</v>
       </c>
       <c r="I324" t="n">
-        <v>0.1592</v>
+        <v>0.1577</v>
       </c>
       <c r="J324" t="n">
-        <v>0.8058</v>
+        <v>0.8089</v>
       </c>
       <c r="K324" t="n">
         <v>0.8757</v>
       </c>
       <c r="L324" t="n">
-        <v>0.8408</v>
+        <v>0.8423</v>
       </c>
       <c r="M324" t="n">
         <v>155</v>
@@ -18120,22 +18120,22 @@
         </is>
       </c>
       <c r="G328" t="n">
-        <v>0.4376</v>
+        <v>0.4361</v>
       </c>
       <c r="H328" t="n">
-        <v>0.2978</v>
+        <v>0.2966</v>
       </c>
       <c r="I328" t="n">
-        <v>0.3677</v>
+        <v>0.3663</v>
       </c>
       <c r="J328" t="n">
-        <v>0.5624</v>
+        <v>0.5639</v>
       </c>
       <c r="K328" t="n">
-        <v>0.7022</v>
+        <v>0.7034</v>
       </c>
       <c r="L328" t="n">
-        <v>0.6323</v>
+        <v>0.6337</v>
       </c>
       <c r="M328" t="n">
         <v>155</v>
@@ -18282,22 +18282,22 @@
         </is>
       </c>
       <c r="G331" t="n">
-        <v>0.1918</v>
+        <v>0.1899</v>
       </c>
       <c r="H331" t="n">
-        <v>0.1273</v>
+        <v>0.126</v>
       </c>
       <c r="I331" t="n">
-        <v>0.1596</v>
+        <v>0.158</v>
       </c>
       <c r="J331" t="n">
-        <v>0.8082</v>
+        <v>0.8101</v>
       </c>
       <c r="K331" t="n">
-        <v>0.8727</v>
+        <v>0.874</v>
       </c>
       <c r="L331" t="n">
-        <v>0.8404</v>
+        <v>0.842</v>
       </c>
       <c r="M331" t="n">
         <v>155</v>
@@ -18336,22 +18336,22 @@
         </is>
       </c>
       <c r="G332" t="n">
-        <v>0.778</v>
+        <v>0.7788</v>
       </c>
       <c r="H332" t="n">
-        <v>0.6495</v>
+        <v>0.6505</v>
       </c>
       <c r="I332" t="n">
-        <v>0.7138</v>
+        <v>0.7146</v>
       </c>
       <c r="J332" t="n">
-        <v>0.222</v>
+        <v>0.2212</v>
       </c>
       <c r="K332" t="n">
-        <v>0.3505</v>
+        <v>0.3495</v>
       </c>
       <c r="L332" t="n">
-        <v>0.2862</v>
+        <v>0.2854</v>
       </c>
       <c r="M332" t="n">
         <v>155</v>
@@ -18390,22 +18390,22 @@
         </is>
       </c>
       <c r="G333" t="n">
-        <v>0.8536</v>
+        <v>0.8546</v>
       </c>
       <c r="H333" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.769</v>
       </c>
       <c r="I333" t="n">
-        <v>0.8106</v>
+        <v>0.8118</v>
       </c>
       <c r="J333" t="n">
-        <v>0.1464</v>
+        <v>0.1454</v>
       </c>
       <c r="K333" t="n">
-        <v>0.2324</v>
+        <v>0.231</v>
       </c>
       <c r="L333" t="n">
-        <v>0.1894</v>
+        <v>0.1882</v>
       </c>
       <c r="M333" t="n">
         <v>155</v>
@@ -18444,22 +18444,22 @@
         </is>
       </c>
       <c r="G334" t="n">
-        <v>0.7917</v>
+        <v>0.7754</v>
       </c>
       <c r="H334" t="n">
-        <v>0.7062</v>
+        <v>0.6849</v>
       </c>
       <c r="I334" t="n">
-        <v>0.749</v>
+        <v>0.7302</v>
       </c>
       <c r="J334" t="n">
-        <v>0.2083</v>
+        <v>0.2246</v>
       </c>
       <c r="K334" t="n">
-        <v>0.2938</v>
+        <v>0.3151</v>
       </c>
       <c r="L334" t="n">
-        <v>0.251</v>
+        <v>0.2698</v>
       </c>
       <c r="M334" t="n">
         <v>155</v>
@@ -18498,22 +18498,22 @@
         </is>
       </c>
       <c r="G335" t="n">
-        <v>0.7526</v>
+        <v>0.7582</v>
       </c>
       <c r="H335" t="n">
-        <v>0.6232</v>
+        <v>0.6309</v>
       </c>
       <c r="I335" t="n">
-        <v>0.6879</v>
+        <v>0.6946</v>
       </c>
       <c r="J335" t="n">
-        <v>0.2474</v>
+        <v>0.2418</v>
       </c>
       <c r="K335" t="n">
-        <v>0.3768</v>
+        <v>0.3691</v>
       </c>
       <c r="L335" t="n">
-        <v>0.3121</v>
+        <v>0.3054</v>
       </c>
       <c r="M335" t="n">
         <v>155</v>
@@ -18606,22 +18606,22 @@
         </is>
       </c>
       <c r="G337" t="n">
-        <v>0.8459</v>
+        <v>0.8479</v>
       </c>
       <c r="H337" t="n">
-        <v>0.752</v>
+        <v>0.7541</v>
       </c>
       <c r="I337" t="n">
-        <v>0.799</v>
+        <v>0.801</v>
       </c>
       <c r="J337" t="n">
-        <v>0.1541</v>
+        <v>0.1521</v>
       </c>
       <c r="K337" t="n">
-        <v>0.248</v>
+        <v>0.2459</v>
       </c>
       <c r="L337" t="n">
-        <v>0.201</v>
+        <v>0.199</v>
       </c>
       <c r="M337" t="n">
         <v>155</v>
@@ -18768,22 +18768,22 @@
         </is>
       </c>
       <c r="G340" t="n">
-        <v>0.726</v>
+        <v>0.736</v>
       </c>
       <c r="H340" t="n">
-        <v>0.5972</v>
+        <v>0.6094000000000001</v>
       </c>
       <c r="I340" t="n">
-        <v>0.6616</v>
+        <v>0.6727</v>
       </c>
       <c r="J340" t="n">
-        <v>0.274</v>
+        <v>0.264</v>
       </c>
       <c r="K340" t="n">
-        <v>0.4028</v>
+        <v>0.3906</v>
       </c>
       <c r="L340" t="n">
-        <v>0.3384</v>
+        <v>0.3273</v>
       </c>
       <c r="M340" t="n">
         <v>155</v>
@@ -19146,22 +19146,22 @@
         </is>
       </c>
       <c r="G347" t="n">
-        <v>0.637</v>
+        <v>0.6005</v>
       </c>
       <c r="H347" t="n">
-        <v>0.4844</v>
+        <v>0.4472</v>
       </c>
       <c r="I347" t="n">
-        <v>0.5607</v>
+        <v>0.5238</v>
       </c>
       <c r="J347" t="n">
-        <v>0.363</v>
+        <v>0.3995</v>
       </c>
       <c r="K347" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.5528</v>
       </c>
       <c r="L347" t="n">
-        <v>0.4393</v>
+        <v>0.4762</v>
       </c>
       <c r="M347" t="n">
         <v>155</v>
@@ -19308,22 +19308,22 @@
         </is>
       </c>
       <c r="G350" t="n">
-        <v>0.7715</v>
+        <v>0.7725</v>
       </c>
       <c r="H350" t="n">
-        <v>0.6466</v>
+        <v>0.6478</v>
       </c>
       <c r="I350" t="n">
-        <v>0.709</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="J350" t="n">
-        <v>0.2285</v>
+        <v>0.2275</v>
       </c>
       <c r="K350" t="n">
-        <v>0.3534</v>
+        <v>0.3522</v>
       </c>
       <c r="L350" t="n">
-        <v>0.291</v>
+        <v>0.2898</v>
       </c>
       <c r="M350" t="n">
         <v>155</v>
@@ -19416,22 +19416,22 @@
         </is>
       </c>
       <c r="G352" t="n">
-        <v>0.2639</v>
+        <v>0.2616</v>
       </c>
       <c r="H352" t="n">
-        <v>0.1707</v>
+        <v>0.169</v>
       </c>
       <c r="I352" t="n">
-        <v>0.2173</v>
+        <v>0.2153</v>
       </c>
       <c r="J352" t="n">
-        <v>0.7361</v>
+        <v>0.7383999999999999</v>
       </c>
       <c r="K352" t="n">
-        <v>0.8293</v>
+        <v>0.831</v>
       </c>
       <c r="L352" t="n">
-        <v>0.7827</v>
+        <v>0.7847</v>
       </c>
       <c r="M352" t="n">
         <v>155</v>
@@ -19470,22 +19470,22 @@
         </is>
       </c>
       <c r="G353" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.531</v>
       </c>
       <c r="H353" t="n">
-        <v>0.3692</v>
+        <v>0.3751</v>
       </c>
       <c r="I353" t="n">
-        <v>0.447</v>
+        <v>0.453</v>
       </c>
       <c r="J353" t="n">
-        <v>0.4753</v>
+        <v>0.469</v>
       </c>
       <c r="K353" t="n">
-        <v>0.6308</v>
+        <v>0.6249</v>
       </c>
       <c r="L353" t="n">
-        <v>0.553</v>
+        <v>0.547</v>
       </c>
       <c r="M353" t="n">
         <v>155</v>
@@ -19527,19 +19527,19 @@
         <v>0.7796999999999999</v>
       </c>
       <c r="H354" t="n">
-        <v>0.6523</v>
+        <v>0.6531</v>
       </c>
       <c r="I354" t="n">
-        <v>0.716</v>
+        <v>0.7164</v>
       </c>
       <c r="J354" t="n">
         <v>0.2203</v>
       </c>
       <c r="K354" t="n">
-        <v>0.3477</v>
+        <v>0.3469</v>
       </c>
       <c r="L354" t="n">
-        <v>0.284</v>
+        <v>0.2836</v>
       </c>
       <c r="M354" t="n">
         <v>155</v>
@@ -19578,22 +19578,22 @@
         </is>
       </c>
       <c r="G355" t="n">
-        <v>0.7488</v>
+        <v>0.7495000000000001</v>
       </c>
       <c r="H355" t="n">
-        <v>0.611</v>
+        <v>0.6119</v>
       </c>
       <c r="I355" t="n">
-        <v>0.6798999999999999</v>
+        <v>0.6807</v>
       </c>
       <c r="J355" t="n">
-        <v>0.2512</v>
+        <v>0.2505</v>
       </c>
       <c r="K355" t="n">
-        <v>0.389</v>
+        <v>0.3881</v>
       </c>
       <c r="L355" t="n">
-        <v>0.3201</v>
+        <v>0.3193</v>
       </c>
       <c r="M355" t="n">
         <v>155</v>
@@ -19632,22 +19632,22 @@
         </is>
       </c>
       <c r="G356" t="n">
-        <v>0.8148</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H356" t="n">
-        <v>0.7107</v>
+        <v>0.7123</v>
       </c>
       <c r="I356" t="n">
-        <v>0.7628</v>
+        <v>0.7642</v>
       </c>
       <c r="J356" t="n">
-        <v>0.1852</v>
+        <v>0.184</v>
       </c>
       <c r="K356" t="n">
-        <v>0.2893</v>
+        <v>0.2877</v>
       </c>
       <c r="L356" t="n">
-        <v>0.2372</v>
+        <v>0.2358</v>
       </c>
       <c r="M356" t="n">
         <v>155</v>
@@ -19794,22 +19794,22 @@
         </is>
       </c>
       <c r="G359" t="n">
-        <v>0.436</v>
+        <v>0.3819</v>
       </c>
       <c r="H359" t="n">
-        <v>0.2947</v>
+        <v>0.2559</v>
       </c>
       <c r="I359" t="n">
-        <v>0.3654</v>
+        <v>0.3189</v>
       </c>
       <c r="J359" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.6181</v>
       </c>
       <c r="K359" t="n">
-        <v>0.7053</v>
+        <v>0.7441</v>
       </c>
       <c r="L359" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.6811</v>
       </c>
       <c r="M359" t="n">
         <v>155</v>
@@ -19902,22 +19902,22 @@
         </is>
       </c>
       <c r="G361" t="n">
-        <v>0.3503</v>
+        <v>0.3466</v>
       </c>
       <c r="H361" t="n">
-        <v>0.2352</v>
+        <v>0.2323</v>
       </c>
       <c r="I361" t="n">
-        <v>0.2928</v>
+        <v>0.2894</v>
       </c>
       <c r="J361" t="n">
-        <v>0.6497000000000001</v>
+        <v>0.6534</v>
       </c>
       <c r="K361" t="n">
-        <v>0.7648</v>
+        <v>0.7677</v>
       </c>
       <c r="L361" t="n">
-        <v>0.7072000000000001</v>
+        <v>0.7106</v>
       </c>
       <c r="M361" t="n">
         <v>155</v>
@@ -20118,22 +20118,22 @@
         </is>
       </c>
       <c r="G365" t="n">
-        <v>0.2625</v>
+        <v>0.2633</v>
       </c>
       <c r="H365" t="n">
-        <v>0.1769</v>
+        <v>0.1775</v>
       </c>
       <c r="I365" t="n">
-        <v>0.2197</v>
+        <v>0.2204</v>
       </c>
       <c r="J365" t="n">
-        <v>0.7375</v>
+        <v>0.7367</v>
       </c>
       <c r="K365" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.8225</v>
       </c>
       <c r="L365" t="n">
-        <v>0.7803</v>
+        <v>0.7796</v>
       </c>
       <c r="M365" t="n">
         <v>155</v>
@@ -20388,22 +20388,22 @@
         </is>
       </c>
       <c r="G370" t="n">
-        <v>0.2239</v>
+        <v>0.2215</v>
       </c>
       <c r="H370" t="n">
         <v>0.1483</v>
       </c>
       <c r="I370" t="n">
-        <v>0.1861</v>
+        <v>0.1849</v>
       </c>
       <c r="J370" t="n">
-        <v>0.7761</v>
+        <v>0.7785</v>
       </c>
       <c r="K370" t="n">
         <v>0.8517</v>
       </c>
       <c r="L370" t="n">
-        <v>0.8139</v>
+        <v>0.8151</v>
       </c>
       <c r="M370" t="n">
         <v>155</v>
@@ -20442,22 +20442,22 @@
         </is>
       </c>
       <c r="G371" t="n">
-        <v>0.506</v>
+        <v>0.5386</v>
       </c>
       <c r="H371" t="n">
-        <v>0.3577</v>
+        <v>0.3871</v>
       </c>
       <c r="I371" t="n">
-        <v>0.4318</v>
+        <v>0.4628</v>
       </c>
       <c r="J371" t="n">
-        <v>0.494</v>
+        <v>0.4614</v>
       </c>
       <c r="K371" t="n">
-        <v>0.6423</v>
+        <v>0.6129</v>
       </c>
       <c r="L371" t="n">
-        <v>0.5682</v>
+        <v>0.5372</v>
       </c>
       <c r="M371" t="n">
         <v>155</v>
@@ -20496,22 +20496,22 @@
         </is>
       </c>
       <c r="G372" t="n">
-        <v>0.5312</v>
+        <v>0.5595</v>
       </c>
       <c r="H372" t="n">
-        <v>0.3795</v>
+        <v>0.4071</v>
       </c>
       <c r="I372" t="n">
-        <v>0.4554</v>
+        <v>0.4833</v>
       </c>
       <c r="J372" t="n">
-        <v>0.4688</v>
+        <v>0.4405</v>
       </c>
       <c r="K372" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.5929</v>
       </c>
       <c r="L372" t="n">
-        <v>0.5446</v>
+        <v>0.5167</v>
       </c>
       <c r="M372" t="n">
         <v>155</v>
@@ -20550,22 +20550,22 @@
         </is>
       </c>
       <c r="G373" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="H373" t="n">
-        <v>0.5916</v>
+        <v>0.6349</v>
       </c>
       <c r="I373" t="n">
-        <v>0.6594</v>
+        <v>0.6978</v>
       </c>
       <c r="J373" t="n">
-        <v>0.2727</v>
+        <v>0.2394</v>
       </c>
       <c r="K373" t="n">
-        <v>0.4084</v>
+        <v>0.3651</v>
       </c>
       <c r="L373" t="n">
-        <v>0.3406</v>
+        <v>0.3022</v>
       </c>
       <c r="M373" t="n">
         <v>155</v>
@@ -20604,22 +20604,22 @@
         </is>
       </c>
       <c r="G374" t="n">
-        <v>0.2478</v>
+        <v>0.2905</v>
       </c>
       <c r="H374" t="n">
-        <v>0.1656</v>
+        <v>0.1908</v>
       </c>
       <c r="I374" t="n">
-        <v>0.2067</v>
+        <v>0.2406</v>
       </c>
       <c r="J374" t="n">
-        <v>0.7522</v>
+        <v>0.7095</v>
       </c>
       <c r="K374" t="n">
-        <v>0.8344</v>
+        <v>0.8092</v>
       </c>
       <c r="L374" t="n">
-        <v>0.7933</v>
+        <v>0.7594</v>
       </c>
       <c r="M374" t="n">
         <v>155</v>
@@ -20658,22 +20658,22 @@
         </is>
       </c>
       <c r="G375" t="n">
-        <v>0.2125</v>
+        <v>0.2226</v>
       </c>
       <c r="H375" t="n">
-        <v>0.1414</v>
+        <v>0.1455</v>
       </c>
       <c r="I375" t="n">
-        <v>0.177</v>
+        <v>0.184</v>
       </c>
       <c r="J375" t="n">
-        <v>0.7875</v>
+        <v>0.7774</v>
       </c>
       <c r="K375" t="n">
-        <v>0.8586</v>
+        <v>0.8545</v>
       </c>
       <c r="L375" t="n">
-        <v>0.823</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="M375" t="n">
         <v>155</v>
@@ -20712,22 +20712,22 @@
         </is>
       </c>
       <c r="G376" t="n">
-        <v>0.4432</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="H376" t="n">
-        <v>0.324</v>
+        <v>0.3758</v>
       </c>
       <c r="I376" t="n">
-        <v>0.3836</v>
+        <v>0.4422</v>
       </c>
       <c r="J376" t="n">
-        <v>0.5568</v>
+        <v>0.4914</v>
       </c>
       <c r="K376" t="n">
-        <v>0.676</v>
+        <v>0.6242</v>
       </c>
       <c r="L376" t="n">
-        <v>0.6163999999999999</v>
+        <v>0.5578</v>
       </c>
       <c r="M376" t="n">
         <v>155</v>
@@ -20766,22 +20766,22 @@
         </is>
       </c>
       <c r="G377" t="n">
-        <v>0.7497</v>
+        <v>0.7726</v>
       </c>
       <c r="H377" t="n">
-        <v>0.6221</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="I377" t="n">
-        <v>0.6859</v>
+        <v>0.7106</v>
       </c>
       <c r="J377" t="n">
-        <v>0.2503</v>
+        <v>0.2274</v>
       </c>
       <c r="K377" t="n">
-        <v>0.3779</v>
+        <v>0.3513</v>
       </c>
       <c r="L377" t="n">
-        <v>0.3141</v>
+        <v>0.2894</v>
       </c>
       <c r="M377" t="n">
         <v>155</v>
@@ -20820,22 +20820,22 @@
         </is>
       </c>
       <c r="G378" t="n">
-        <v>0.6818</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="H378" t="n">
-        <v>0.5324</v>
+        <v>0.5639</v>
       </c>
       <c r="I378" t="n">
-        <v>0.6071</v>
+        <v>0.636</v>
       </c>
       <c r="J378" t="n">
-        <v>0.3182</v>
+        <v>0.2918</v>
       </c>
       <c r="K378" t="n">
-        <v>0.4676</v>
+        <v>0.4361</v>
       </c>
       <c r="L378" t="n">
-        <v>0.3929</v>
+        <v>0.364</v>
       </c>
       <c r="M378" t="n">
         <v>155</v>
@@ -20874,22 +20874,22 @@
         </is>
       </c>
       <c r="G379" t="n">
-        <v>0.7846</v>
+        <v>0.7951</v>
       </c>
       <c r="H379" t="n">
-        <v>0.6866</v>
+        <v>0.6987</v>
       </c>
       <c r="I379" t="n">
-        <v>0.7356</v>
+        <v>0.7469</v>
       </c>
       <c r="J379" t="n">
-        <v>0.2154</v>
+        <v>0.2049</v>
       </c>
       <c r="K379" t="n">
-        <v>0.3134</v>
+        <v>0.3013</v>
       </c>
       <c r="L379" t="n">
-        <v>0.2644</v>
+        <v>0.2531</v>
       </c>
       <c r="M379" t="n">
         <v>155</v>
@@ -20928,22 +20928,22 @@
         </is>
       </c>
       <c r="G380" t="n">
-        <v>0.3783</v>
+        <v>0.4013</v>
       </c>
       <c r="H380" t="n">
-        <v>0.2596</v>
+        <v>0.2842</v>
       </c>
       <c r="I380" t="n">
-        <v>0.319</v>
+        <v>0.3428</v>
       </c>
       <c r="J380" t="n">
-        <v>0.6217</v>
+        <v>0.5987</v>
       </c>
       <c r="K380" t="n">
-        <v>0.7403999999999999</v>
+        <v>0.7158</v>
       </c>
       <c r="L380" t="n">
-        <v>0.681</v>
+        <v>0.6572</v>
       </c>
       <c r="M380" t="n">
         <v>155</v>
@@ -20982,22 +20982,22 @@
         </is>
       </c>
       <c r="G381" t="n">
-        <v>0.3418</v>
+        <v>0.3827</v>
       </c>
       <c r="H381" t="n">
-        <v>0.232</v>
+        <v>0.265</v>
       </c>
       <c r="I381" t="n">
-        <v>0.2869</v>
+        <v>0.3238</v>
       </c>
       <c r="J381" t="n">
-        <v>0.6582</v>
+        <v>0.6173</v>
       </c>
       <c r="K381" t="n">
-        <v>0.768</v>
+        <v>0.735</v>
       </c>
       <c r="L381" t="n">
-        <v>0.7131</v>
+        <v>0.6762</v>
       </c>
       <c r="M381" t="n">
         <v>155</v>
@@ -21198,22 +21198,22 @@
         </is>
       </c>
       <c r="G385" t="n">
-        <v>0.2831</v>
+        <v>0.2825</v>
       </c>
       <c r="H385" t="n">
-        <v>0.1791</v>
+        <v>0.1788</v>
       </c>
       <c r="I385" t="n">
-        <v>0.2311</v>
+        <v>0.2306</v>
       </c>
       <c r="J385" t="n">
-        <v>0.7169</v>
+        <v>0.7175</v>
       </c>
       <c r="K385" t="n">
-        <v>0.8209</v>
+        <v>0.8212</v>
       </c>
       <c r="L385" t="n">
-        <v>0.7689</v>
+        <v>0.7694</v>
       </c>
       <c r="M385" t="n">
         <v>155</v>
@@ -21252,22 +21252,22 @@
         </is>
       </c>
       <c r="G386" t="n">
-        <v>0.5803</v>
+        <v>0.5853</v>
       </c>
       <c r="H386" t="n">
-        <v>0.4176</v>
+        <v>0.4212</v>
       </c>
       <c r="I386" t="n">
-        <v>0.499</v>
+        <v>0.5032</v>
       </c>
       <c r="J386" t="n">
-        <v>0.4197</v>
+        <v>0.4147</v>
       </c>
       <c r="K386" t="n">
-        <v>0.5824</v>
+        <v>0.5788</v>
       </c>
       <c r="L386" t="n">
-        <v>0.501</v>
+        <v>0.4968</v>
       </c>
       <c r="M386" t="n">
         <v>155</v>
@@ -21309,19 +21309,19 @@
         <v>0.7907999999999999</v>
       </c>
       <c r="H387" t="n">
-        <v>0.6738</v>
+        <v>0.6758</v>
       </c>
       <c r="I387" t="n">
-        <v>0.7323</v>
+        <v>0.7333</v>
       </c>
       <c r="J387" t="n">
         <v>0.2092</v>
       </c>
       <c r="K387" t="n">
-        <v>0.3262</v>
+        <v>0.3242</v>
       </c>
       <c r="L387" t="n">
-        <v>0.2677</v>
+        <v>0.2667</v>
       </c>
       <c r="M387" t="n">
         <v>155</v>
@@ -21360,22 +21360,22 @@
         </is>
       </c>
       <c r="G388" t="n">
-        <v>0.7607</v>
+        <v>0.7662</v>
       </c>
       <c r="H388" t="n">
-        <v>0.6267</v>
+        <v>0.6343</v>
       </c>
       <c r="I388" t="n">
-        <v>0.6937</v>
+        <v>0.7002</v>
       </c>
       <c r="J388" t="n">
-        <v>0.2393</v>
+        <v>0.2338</v>
       </c>
       <c r="K388" t="n">
-        <v>0.3733</v>
+        <v>0.3657</v>
       </c>
       <c r="L388" t="n">
-        <v>0.3063</v>
+        <v>0.2998</v>
       </c>
       <c r="M388" t="n">
         <v>155</v>
@@ -21630,22 +21630,22 @@
         </is>
       </c>
       <c r="G393" t="n">
-        <v>0.3752</v>
+        <v>0.367</v>
       </c>
       <c r="H393" t="n">
-        <v>0.2419</v>
+        <v>0.2355</v>
       </c>
       <c r="I393" t="n">
-        <v>0.3086</v>
+        <v>0.3012</v>
       </c>
       <c r="J393" t="n">
-        <v>0.6248</v>
+        <v>0.633</v>
       </c>
       <c r="K393" t="n">
-        <v>0.7581</v>
+        <v>0.7645</v>
       </c>
       <c r="L393" t="n">
-        <v>0.6914</v>
+        <v>0.6988</v>
       </c>
       <c r="M393" t="n">
         <v>155</v>
@@ -21684,22 +21684,22 @@
         </is>
       </c>
       <c r="G394" t="n">
-        <v>0.2635</v>
+        <v>0.2624</v>
       </c>
       <c r="H394" t="n">
-        <v>0.1814</v>
+        <v>0.1805</v>
       </c>
       <c r="I394" t="n">
-        <v>0.2224</v>
+        <v>0.2214</v>
       </c>
       <c r="J394" t="n">
-        <v>0.7365</v>
+        <v>0.7376</v>
       </c>
       <c r="K394" t="n">
-        <v>0.8186</v>
+        <v>0.8195</v>
       </c>
       <c r="L394" t="n">
-        <v>0.7776</v>
+        <v>0.7786</v>
       </c>
       <c r="M394" t="n">
         <v>155</v>
@@ -21738,22 +21738,22 @@
         </is>
       </c>
       <c r="G395" t="n">
-        <v>0.5201</v>
+        <v>0.5266</v>
       </c>
       <c r="H395" t="n">
-        <v>0.3557</v>
+        <v>0.3593</v>
       </c>
       <c r="I395" t="n">
-        <v>0.4379</v>
+        <v>0.443</v>
       </c>
       <c r="J395" t="n">
-        <v>0.4799</v>
+        <v>0.4734</v>
       </c>
       <c r="K395" t="n">
-        <v>0.6443</v>
+        <v>0.6407</v>
       </c>
       <c r="L395" t="n">
-        <v>0.5621</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="M395" t="n">
         <v>155</v>
@@ -21900,22 +21900,22 @@
         </is>
       </c>
       <c r="G398" t="n">
-        <v>0.8154</v>
+        <v>0.8173</v>
       </c>
       <c r="H398" t="n">
-        <v>0.7022</v>
+        <v>0.7048</v>
       </c>
       <c r="I398" t="n">
-        <v>0.7588</v>
+        <v>0.761</v>
       </c>
       <c r="J398" t="n">
-        <v>0.1846</v>
+        <v>0.1827</v>
       </c>
       <c r="K398" t="n">
-        <v>0.2978</v>
+        <v>0.2952</v>
       </c>
       <c r="L398" t="n">
-        <v>0.2412</v>
+        <v>0.239</v>
       </c>
       <c r="M398" t="n">
         <v>155</v>
@@ -22062,22 +22062,22 @@
         </is>
       </c>
       <c r="G401" t="n">
-        <v>0.2095</v>
+        <v>0.2089</v>
       </c>
       <c r="H401" t="n">
-        <v>0.1346</v>
+        <v>0.1342</v>
       </c>
       <c r="I401" t="n">
-        <v>0.172</v>
+        <v>0.1716</v>
       </c>
       <c r="J401" t="n">
-        <v>0.7905</v>
+        <v>0.7911</v>
       </c>
       <c r="K401" t="n">
-        <v>0.8653999999999999</v>
+        <v>0.8658</v>
       </c>
       <c r="L401" t="n">
-        <v>0.828</v>
+        <v>0.8284</v>
       </c>
       <c r="M401" t="n">
         <v>155</v>
@@ -22170,22 +22170,22 @@
         </is>
       </c>
       <c r="G403" t="n">
-        <v>0.2752</v>
+        <v>0.2764</v>
       </c>
       <c r="H403" t="n">
-        <v>0.1802</v>
+        <v>0.1811</v>
       </c>
       <c r="I403" t="n">
-        <v>0.2277</v>
+        <v>0.2288</v>
       </c>
       <c r="J403" t="n">
-        <v>0.7248</v>
+        <v>0.7236</v>
       </c>
       <c r="K403" t="n">
-        <v>0.8198</v>
+        <v>0.8189</v>
       </c>
       <c r="L403" t="n">
-        <v>0.7723</v>
+        <v>0.7712</v>
       </c>
       <c r="M403" t="n">
         <v>155</v>
@@ -22224,22 +22224,22 @@
         </is>
       </c>
       <c r="G404" t="n">
-        <v>0.5629</v>
+        <v>0.5647</v>
       </c>
       <c r="H404" t="n">
-        <v>0.4212</v>
+        <v>0.4231</v>
       </c>
       <c r="I404" t="n">
-        <v>0.492</v>
+        <v>0.4939</v>
       </c>
       <c r="J404" t="n">
-        <v>0.4371</v>
+        <v>0.4353</v>
       </c>
       <c r="K404" t="n">
-        <v>0.5788</v>
+        <v>0.5769</v>
       </c>
       <c r="L404" t="n">
-        <v>0.508</v>
+        <v>0.5061</v>
       </c>
       <c r="M404" t="n">
         <v>155</v>
@@ -22278,22 +22278,22 @@
         </is>
       </c>
       <c r="G405" t="n">
-        <v>0.5201</v>
+        <v>0.5213</v>
       </c>
       <c r="H405" t="n">
-        <v>0.3642</v>
+        <v>0.3652</v>
       </c>
       <c r="I405" t="n">
-        <v>0.4422</v>
+        <v>0.4432</v>
       </c>
       <c r="J405" t="n">
-        <v>0.4799</v>
+        <v>0.4787</v>
       </c>
       <c r="K405" t="n">
-        <v>0.6358</v>
+        <v>0.6348</v>
       </c>
       <c r="L405" t="n">
-        <v>0.5578</v>
+        <v>0.5568</v>
       </c>
       <c r="M405" t="n">
         <v>155</v>
@@ -22386,22 +22386,22 @@
         </is>
       </c>
       <c r="G407" t="n">
-        <v>0.2819</v>
+        <v>0.2797</v>
       </c>
       <c r="H407" t="n">
-        <v>0.1733</v>
+        <v>0.1718</v>
       </c>
       <c r="I407" t="n">
-        <v>0.2276</v>
+        <v>0.2258</v>
       </c>
       <c r="J407" t="n">
-        <v>0.7181</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="K407" t="n">
-        <v>0.8267</v>
+        <v>0.8282</v>
       </c>
       <c r="L407" t="n">
-        <v>0.7724</v>
+        <v>0.7742</v>
       </c>
       <c r="M407" t="n">
         <v>155</v>
@@ -22440,22 +22440,22 @@
         </is>
       </c>
       <c r="G408" t="n">
-        <v>0.2336</v>
+        <v>0.233</v>
       </c>
       <c r="H408" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="I408" t="n">
-        <v>0.1914</v>
+        <v>0.191</v>
       </c>
       <c r="J408" t="n">
-        <v>0.7664</v>
+        <v>0.767</v>
       </c>
       <c r="K408" t="n">
-        <v>0.8507</v>
+        <v>0.8511</v>
       </c>
       <c r="L408" t="n">
-        <v>0.8086</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="M408" t="n">
         <v>155</v>
@@ -22494,22 +22494,22 @@
         </is>
       </c>
       <c r="G409" t="n">
-        <v>0.507</v>
+        <v>0.5049</v>
       </c>
       <c r="H409" t="n">
-        <v>0.355</v>
+        <v>0.3517</v>
       </c>
       <c r="I409" t="n">
-        <v>0.431</v>
+        <v>0.4283</v>
       </c>
       <c r="J409" t="n">
-        <v>0.493</v>
+        <v>0.4951</v>
       </c>
       <c r="K409" t="n">
-        <v>0.645</v>
+        <v>0.6483</v>
       </c>
       <c r="L409" t="n">
-        <v>0.569</v>
+        <v>0.5717</v>
       </c>
       <c r="M409" t="n">
         <v>155</v>
@@ -22548,22 +22548,22 @@
         </is>
       </c>
       <c r="G410" t="n">
-        <v>0.7295</v>
+        <v>0.7356</v>
       </c>
       <c r="H410" t="n">
-        <v>0.5974</v>
+        <v>0.6035</v>
       </c>
       <c r="I410" t="n">
-        <v>0.6635</v>
+        <v>0.6696</v>
       </c>
       <c r="J410" t="n">
-        <v>0.2705</v>
+        <v>0.2644</v>
       </c>
       <c r="K410" t="n">
-        <v>0.4026</v>
+        <v>0.3965</v>
       </c>
       <c r="L410" t="n">
-        <v>0.3365</v>
+        <v>0.3304</v>
       </c>
       <c r="M410" t="n">
         <v>155</v>
@@ -22872,22 +22872,22 @@
         </is>
       </c>
       <c r="G416" t="n">
-        <v>0.7935</v>
+        <v>0.7948</v>
       </c>
       <c r="H416" t="n">
-        <v>0.6679</v>
+        <v>0.6704</v>
       </c>
       <c r="I416" t="n">
-        <v>0.7307</v>
+        <v>0.7326</v>
       </c>
       <c r="J416" t="n">
-        <v>0.2065</v>
+        <v>0.2052</v>
       </c>
       <c r="K416" t="n">
-        <v>0.3321</v>
+        <v>0.3296</v>
       </c>
       <c r="L416" t="n">
-        <v>0.2693</v>
+        <v>0.2674</v>
       </c>
       <c r="M416" t="n">
         <v>155</v>
@@ -22980,22 +22980,22 @@
         </is>
       </c>
       <c r="G418" t="n">
-        <v>0.8381999999999999</v>
+        <v>0.8393</v>
       </c>
       <c r="H418" t="n">
         <v>0.759</v>
       </c>
       <c r="I418" t="n">
-        <v>0.7986</v>
+        <v>0.7992</v>
       </c>
       <c r="J418" t="n">
-        <v>0.1618</v>
+        <v>0.1607</v>
       </c>
       <c r="K418" t="n">
         <v>0.241</v>
       </c>
       <c r="L418" t="n">
-        <v>0.2014</v>
+        <v>0.2008</v>
       </c>
       <c r="M418" t="n">
         <v>155</v>
@@ -23196,22 +23196,22 @@
         </is>
       </c>
       <c r="G422" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8089</v>
       </c>
       <c r="H422" t="n">
-        <v>0.698</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="I422" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.752</v>
       </c>
       <c r="J422" t="n">
-        <v>0.189</v>
+        <v>0.1911</v>
       </c>
       <c r="K422" t="n">
-        <v>0.302</v>
+        <v>0.3049</v>
       </c>
       <c r="L422" t="n">
-        <v>0.2455</v>
+        <v>0.248</v>
       </c>
       <c r="M422" t="n">
         <v>155</v>
@@ -23250,22 +23250,22 @@
         </is>
       </c>
       <c r="G423" t="n">
-        <v>0.7748</v>
+        <v>0.7729</v>
       </c>
       <c r="H423" t="n">
-        <v>0.6473</v>
+        <v>0.6461</v>
       </c>
       <c r="I423" t="n">
-        <v>0.711</v>
+        <v>0.7095</v>
       </c>
       <c r="J423" t="n">
-        <v>0.2252</v>
+        <v>0.2271</v>
       </c>
       <c r="K423" t="n">
-        <v>0.3527</v>
+        <v>0.3539</v>
       </c>
       <c r="L423" t="n">
-        <v>0.289</v>
+        <v>0.2905</v>
       </c>
       <c r="M423" t="n">
         <v>155</v>
@@ -23304,22 +23304,22 @@
         </is>
       </c>
       <c r="G424" t="n">
-        <v>0.8446</v>
+        <v>0.8435</v>
       </c>
       <c r="H424" t="n">
-        <v>0.7582</v>
+        <v>0.7567</v>
       </c>
       <c r="I424" t="n">
-        <v>0.8014</v>
+        <v>0.8001</v>
       </c>
       <c r="J424" t="n">
-        <v>0.1554</v>
+        <v>0.1565</v>
       </c>
       <c r="K424" t="n">
-        <v>0.2418</v>
+        <v>0.2433</v>
       </c>
       <c r="L424" t="n">
-        <v>0.1986</v>
+        <v>0.1999</v>
       </c>
       <c r="M424" t="n">
         <v>155</v>
@@ -23358,22 +23358,22 @@
         </is>
       </c>
       <c r="G425" t="n">
-        <v>0.5062</v>
+        <v>0.4966</v>
       </c>
       <c r="H425" t="n">
-        <v>0.3885</v>
+        <v>0.3772</v>
       </c>
       <c r="I425" t="n">
-        <v>0.4474</v>
+        <v>0.4369</v>
       </c>
       <c r="J425" t="n">
-        <v>0.4938</v>
+        <v>0.5034</v>
       </c>
       <c r="K425" t="n">
-        <v>0.6115</v>
+        <v>0.6228</v>
       </c>
       <c r="L425" t="n">
-        <v>0.5526</v>
+        <v>0.5631</v>
       </c>
       <c r="M425" t="n">
         <v>155</v>
@@ -23412,22 +23412,22 @@
         </is>
       </c>
       <c r="G426" t="n">
-        <v>0.4942</v>
+        <v>0.4897</v>
       </c>
       <c r="H426" t="n">
-        <v>0.3494</v>
+        <v>0.3453</v>
       </c>
       <c r="I426" t="n">
-        <v>0.4218</v>
+        <v>0.4175</v>
       </c>
       <c r="J426" t="n">
-        <v>0.5058</v>
+        <v>0.5103</v>
       </c>
       <c r="K426" t="n">
-        <v>0.6506</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="L426" t="n">
-        <v>0.5782</v>
+        <v>0.5825</v>
       </c>
       <c r="M426" t="n">
         <v>155</v>
@@ -23574,22 +23574,22 @@
         </is>
       </c>
       <c r="G429" t="n">
-        <v>0.2606</v>
+        <v>0.2575</v>
       </c>
       <c r="H429" t="n">
-        <v>0.1711</v>
+        <v>0.1688</v>
       </c>
       <c r="I429" t="n">
-        <v>0.2158</v>
+        <v>0.2132</v>
       </c>
       <c r="J429" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.7425</v>
       </c>
       <c r="K429" t="n">
-        <v>0.8289</v>
+        <v>0.8312</v>
       </c>
       <c r="L429" t="n">
-        <v>0.7842</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="M429" t="n">
         <v>155</v>
@@ -23628,22 +23628,22 @@
         </is>
       </c>
       <c r="G430" t="n">
-        <v>0.222</v>
+        <v>0.2203</v>
       </c>
       <c r="H430" t="n">
-        <v>0.1405</v>
+        <v>0.1394</v>
       </c>
       <c r="I430" t="n">
-        <v>0.1813</v>
+        <v>0.1798</v>
       </c>
       <c r="J430" t="n">
-        <v>0.778</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="K430" t="n">
-        <v>0.8595</v>
+        <v>0.8606</v>
       </c>
       <c r="L430" t="n">
-        <v>0.8187</v>
+        <v>0.8202</v>
       </c>
       <c r="M430" t="n">
         <v>155</v>
@@ -23844,22 +23844,22 @@
         </is>
       </c>
       <c r="G434" t="n">
-        <v>0.2319</v>
+        <v>0.2309</v>
       </c>
       <c r="H434" t="n">
-        <v>0.1529</v>
+        <v>0.1521</v>
       </c>
       <c r="I434" t="n">
-        <v>0.1924</v>
+        <v>0.1915</v>
       </c>
       <c r="J434" t="n">
-        <v>0.7681</v>
+        <v>0.7691</v>
       </c>
       <c r="K434" t="n">
-        <v>0.8471</v>
+        <v>0.8479</v>
       </c>
       <c r="L434" t="n">
-        <v>0.8076</v>
+        <v>0.8085</v>
       </c>
       <c r="M434" t="n">
         <v>155</v>
@@ -23898,22 +23898,22 @@
         </is>
       </c>
       <c r="G435" t="n">
-        <v>0.1985</v>
+        <v>0.1974</v>
       </c>
       <c r="H435" t="n">
-        <v>0.1325</v>
+        <v>0.1317</v>
       </c>
       <c r="I435" t="n">
-        <v>0.1655</v>
+        <v>0.1646</v>
       </c>
       <c r="J435" t="n">
-        <v>0.8015</v>
+        <v>0.8026</v>
       </c>
       <c r="K435" t="n">
-        <v>0.8675</v>
+        <v>0.8683</v>
       </c>
       <c r="L435" t="n">
-        <v>0.8345</v>
+        <v>0.8354</v>
       </c>
       <c r="M435" t="n">
         <v>155</v>
@@ -23955,19 +23955,19 @@
         <v>0.602</v>
       </c>
       <c r="H436" t="n">
-        <v>0.4682</v>
+        <v>0.4671</v>
       </c>
       <c r="I436" t="n">
-        <v>0.5351</v>
+        <v>0.5346</v>
       </c>
       <c r="J436" t="n">
         <v>0.398</v>
       </c>
       <c r="K436" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.5329</v>
       </c>
       <c r="L436" t="n">
-        <v>0.4649</v>
+        <v>0.4654</v>
       </c>
       <c r="M436" t="n">
         <v>155</v>

--- a/nba/public/data/nba_matchup_probs.xlsx
+++ b/nba/public/data/nba_matchup_probs.xlsx
@@ -534,11 +534,11 @@
         <v>0.5948</v>
       </c>
       <c r="M2" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -588,11 +588,11 @@
         <v>0.5758</v>
       </c>
       <c r="M3" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -642,11 +642,11 @@
         <v>0.3089</v>
       </c>
       <c r="M4" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -696,11 +696,11 @@
         <v>0.299</v>
       </c>
       <c r="M5" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -750,11 +750,11 @@
         <v>0.2476</v>
       </c>
       <c r="M6" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -804,11 +804,11 @@
         <v>0.5803</v>
       </c>
       <c r="M7" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -858,11 +858,11 @@
         <v>0.3702</v>
       </c>
       <c r="M8" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -912,11 +912,11 @@
         <v>0.4816</v>
       </c>
       <c r="M9" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -966,11 +966,11 @@
         <v>0.5058</v>
       </c>
       <c r="M10" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -1020,11 +1020,11 @@
         <v>0.548</v>
       </c>
       <c r="M11" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -1074,11 +1074,11 @@
         <v>0.4499</v>
       </c>
       <c r="M12" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -1128,11 +1128,11 @@
         <v>0.2595</v>
       </c>
       <c r="M13" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -1182,11 +1182,11 @@
         <v>0.4684</v>
       </c>
       <c r="M14" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -1236,11 +1236,11 @@
         <v>0.1935</v>
       </c>
       <c r="M15" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -1290,11 +1290,11 @@
         <v>0.5876</v>
       </c>
       <c r="M16" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -1344,11 +1344,11 @@
         <v>0.3782</v>
       </c>
       <c r="M17" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -1398,11 +1398,11 @@
         <v>0.2192</v>
       </c>
       <c r="M18" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -1452,11 +1452,11 @@
         <v>0.3462</v>
       </c>
       <c r="M19" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -1506,11 +1506,11 @@
         <v>0.4294</v>
       </c>
       <c r="M20" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -1560,11 +1560,11 @@
         <v>0.3804</v>
       </c>
       <c r="M21" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -1614,11 +1614,11 @@
         <v>0.224</v>
       </c>
       <c r="M22" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -1668,11 +1668,11 @@
         <v>0.5939</v>
       </c>
       <c r="M23" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -1722,11 +1722,11 @@
         <v>0.6637999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -1776,11 +1776,11 @@
         <v>0.4444</v>
       </c>
       <c r="M25" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -1830,11 +1830,11 @@
         <v>0.2184</v>
       </c>
       <c r="M26" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -1884,11 +1884,11 @@
         <v>0.2648</v>
       </c>
       <c r="M27" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -1938,11 +1938,11 @@
         <v>0.1931</v>
       </c>
       <c r="M28" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -1992,11 +1992,11 @@
         <v>0.5053</v>
       </c>
       <c r="M29" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -2046,11 +2046,11 @@
         <v>0.523</v>
       </c>
       <c r="M30" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -2100,11 +2100,11 @@
         <v>0.48</v>
       </c>
       <c r="M31" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -2154,11 +2154,11 @@
         <v>0.2648</v>
       </c>
       <c r="M32" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -2208,11 +2208,11 @@
         <v>0.2376</v>
       </c>
       <c r="M33" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -2262,11 +2262,11 @@
         <v>0.194</v>
       </c>
       <c r="M34" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -2316,11 +2316,11 @@
         <v>0.4593</v>
       </c>
       <c r="M35" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -2370,11 +2370,11 @@
         <v>0.2775</v>
       </c>
       <c r="M36" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -2424,11 +2424,11 @@
         <v>0.3702</v>
       </c>
       <c r="M37" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -2478,11 +2478,11 @@
         <v>0.4015</v>
       </c>
       <c r="M38" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -2532,11 +2532,11 @@
         <v>0.4321</v>
       </c>
       <c r="M39" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -2586,11 +2586,11 @@
         <v>0.3496</v>
       </c>
       <c r="M40" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -2640,11 +2640,11 @@
         <v>0.1874</v>
       </c>
       <c r="M41" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -2694,11 +2694,11 @@
         <v>0.3724</v>
       </c>
       <c r="M42" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -2748,11 +2748,11 @@
         <v>0.1725</v>
       </c>
       <c r="M43" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -2802,11 +2802,11 @@
         <v>0.4755</v>
       </c>
       <c r="M44" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -2856,11 +2856,11 @@
         <v>0.2758</v>
       </c>
       <c r="M45" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -2910,11 +2910,11 @@
         <v>0.1777</v>
       </c>
       <c r="M46" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -2964,11 +2964,11 @@
         <v>0.2646</v>
       </c>
       <c r="M47" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -3018,11 +3018,11 @@
         <v>0.3138</v>
       </c>
       <c r="M48" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -3072,11 +3072,11 @@
         <v>0.2928</v>
       </c>
       <c r="M49" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -3126,11 +3126,11 @@
         <v>0.1854</v>
       </c>
       <c r="M50" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -3180,11 +3180,11 @@
         <v>0.529</v>
       </c>
       <c r="M51" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -3234,11 +3234,11 @@
         <v>0.595</v>
       </c>
       <c r="M52" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -3288,11 +3288,11 @@
         <v>0.33</v>
       </c>
       <c r="M53" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -3342,11 +3342,11 @@
         <v>0.1881</v>
       </c>
       <c r="M54" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -3396,11 +3396,11 @@
         <v>0.198</v>
       </c>
       <c r="M55" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -3450,11 +3450,11 @@
         <v>0.1766</v>
       </c>
       <c r="M56" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -3504,11 +3504,11 @@
         <v>0.4474</v>
       </c>
       <c r="M57" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -3558,11 +3558,11 @@
         <v>0.4268</v>
       </c>
       <c r="M58" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -3612,11 +3612,11 @@
         <v>0.277</v>
       </c>
       <c r="M59" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -3666,11 +3666,11 @@
         <v>0.2502</v>
       </c>
       <c r="M60" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -3720,11 +3720,11 @@
         <v>0.2044</v>
       </c>
       <c r="M61" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -3774,11 +3774,11 @@
         <v>0.4764</v>
       </c>
       <c r="M62" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -3828,11 +3828,11 @@
         <v>0.2989</v>
       </c>
       <c r="M63" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -3882,11 +3882,11 @@
         <v>0.4004</v>
       </c>
       <c r="M64" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -3936,11 +3936,11 @@
         <v>0.4045</v>
       </c>
       <c r="M65" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -3990,11 +3990,11 @@
         <v>0.4675</v>
       </c>
       <c r="M66" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -4044,11 +4044,11 @@
         <v>0.3584</v>
       </c>
       <c r="M67" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -4098,11 +4098,11 @@
         <v>0.1918</v>
       </c>
       <c r="M68" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -4152,11 +4152,11 @@
         <v>0.3942</v>
       </c>
       <c r="M69" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -4206,11 +4206,11 @@
         <v>0.1894</v>
       </c>
       <c r="M70" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -4260,11 +4260,11 @@
         <v>0.5028</v>
       </c>
       <c r="M71" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -4314,11 +4314,11 @@
         <v>0.3118</v>
       </c>
       <c r="M72" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -4368,11 +4368,11 @@
         <v>0.1854</v>
       </c>
       <c r="M73" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -4422,11 +4422,11 @@
         <v>0.2846</v>
       </c>
       <c r="M74" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -4476,11 +4476,11 @@
         <v>0.3543</v>
       </c>
       <c r="M75" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -4530,11 +4530,11 @@
         <v>0.3152</v>
       </c>
       <c r="M76" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -4584,11 +4584,11 @@
         <v>0.1904</v>
       </c>
       <c r="M77" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -4638,11 +4638,11 @@
         <v>0.5261</v>
       </c>
       <c r="M78" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -4692,11 +4692,11 @@
         <v>0.5989</v>
       </c>
       <c r="M79" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -4746,11 +4746,11 @@
         <v>0.35</v>
       </c>
       <c r="M80" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -4800,11 +4800,11 @@
         <v>0.1921</v>
       </c>
       <c r="M81" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -4854,11 +4854,11 @@
         <v>0.2088</v>
       </c>
       <c r="M82" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -4908,11 +4908,11 @@
         <v>0.1771</v>
       </c>
       <c r="M83" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -4962,11 +4962,11 @@
         <v>0.4593</v>
       </c>
       <c r="M84" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -5016,11 +5016,11 @@
         <v>0.4309</v>
       </c>
       <c r="M85" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -5070,11 +5070,11 @@
         <v>0.4758</v>
       </c>
       <c r="M86" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -5124,11 +5124,11 @@
         <v>0.4</v>
       </c>
       <c r="M87" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -5178,11 +5178,11 @@
         <v>0.7422</v>
       </c>
       <c r="M88" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -5232,11 +5232,11 @@
         <v>0.5453</v>
       </c>
       <c r="M89" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -5286,11 +5286,11 @@
         <v>0.6293</v>
       </c>
       <c r="M90" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -5340,11 +5340,11 @@
         <v>0.6846</v>
       </c>
       <c r="M91" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -5394,11 +5394,11 @@
         <v>0.732</v>
       </c>
       <c r="M92" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -5448,11 +5448,11 @@
         <v>0.5903</v>
       </c>
       <c r="M93" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -5502,11 +5502,11 @@
         <v>0.391</v>
       </c>
       <c r="M94" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -5556,11 +5556,11 @@
         <v>0.6403</v>
       </c>
       <c r="M95" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -5610,11 +5610,11 @@
         <v>0.2928</v>
       </c>
       <c r="M96" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -5664,11 +5664,11 @@
         <v>0.7436</v>
       </c>
       <c r="M97" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -5718,11 +5718,11 @@
         <v>0.5312</v>
       </c>
       <c r="M98" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -5772,11 +5772,11 @@
         <v>0.3481</v>
       </c>
       <c r="M99" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -5826,11 +5826,11 @@
         <v>0.5329</v>
       </c>
       <c r="M100" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -5880,11 +5880,11 @@
         <v>0.5602</v>
       </c>
       <c r="M101" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -5934,11 +5934,11 @@
         <v>0.5422</v>
       </c>
       <c r="M102" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -5988,11 +5988,11 @@
         <v>0.3425</v>
       </c>
       <c r="M103" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -6042,11 +6042,11 @@
         <v>0.7316</v>
       </c>
       <c r="M104" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -6096,11 +6096,11 @@
         <v>0.795</v>
       </c>
       <c r="M105" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -6150,11 +6150,11 @@
         <v>0.583</v>
       </c>
       <c r="M106" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -6204,11 +6204,11 @@
         <v>0.35</v>
       </c>
       <c r="M107" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -6258,11 +6258,11 @@
         <v>0.4077</v>
       </c>
       <c r="M108" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -6312,11 +6312,11 @@
         <v>0.2574</v>
       </c>
       <c r="M109" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -6366,11 +6366,11 @@
         <v>0.6522</v>
       </c>
       <c r="M110" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -6420,11 +6420,11 @@
         <v>0.6762</v>
       </c>
       <c r="M111" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -6474,11 +6474,11 @@
         <v>0.4328</v>
       </c>
       <c r="M112" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -6528,11 +6528,11 @@
         <v>0.7482</v>
       </c>
       <c r="M113" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -6582,11 +6582,11 @@
         <v>0.5590000000000001</v>
       </c>
       <c r="M114" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -6636,11 +6636,11 @@
         <v>0.6441</v>
       </c>
       <c r="M115" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -6690,11 +6690,11 @@
         <v>0.7094</v>
       </c>
       <c r="M116" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -6744,11 +6744,11 @@
         <v>0.758</v>
       </c>
       <c r="M117" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -6798,11 +6798,11 @@
         <v>0.6288</v>
       </c>
       <c r="M118" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -6852,11 +6852,11 @@
         <v>0.4097</v>
       </c>
       <c r="M119" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -6906,11 +6906,11 @@
         <v>0.6479</v>
       </c>
       <c r="M120" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -6960,11 +6960,11 @@
         <v>0.3038</v>
       </c>
       <c r="M121" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -7014,11 +7014,11 @@
         <v>0.7521</v>
       </c>
       <c r="M122" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -7068,11 +7068,11 @@
         <v>0.5580000000000001</v>
       </c>
       <c r="M123" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -7122,11 +7122,11 @@
         <v>0.3591</v>
       </c>
       <c r="M124" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -7176,11 +7176,11 @@
         <v>0.5474</v>
       </c>
       <c r="M125" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -7230,11 +7230,11 @@
         <v>0.5976</v>
       </c>
       <c r="M126" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -7284,11 +7284,11 @@
         <v>0.5800999999999999</v>
       </c>
       <c r="M127" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -7338,11 +7338,11 @@
         <v>0.3786</v>
       </c>
       <c r="M128" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -7392,11 +7392,11 @@
         <v>0.764</v>
       </c>
       <c r="M129" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -7446,11 +7446,11 @@
         <v>0.8110000000000001</v>
       </c>
       <c r="M130" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -7500,11 +7500,11 @@
         <v>0.6259</v>
       </c>
       <c r="M131" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -7554,11 +7554,11 @@
         <v>0.3526</v>
       </c>
       <c r="M132" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -7608,11 +7608,11 @@
         <v>0.4129</v>
       </c>
       <c r="M133" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -7662,11 +7662,11 @@
         <v>0.2867</v>
       </c>
       <c r="M134" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -7716,11 +7716,11 @@
         <v>0.6838</v>
       </c>
       <c r="M135" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -7770,11 +7770,11 @@
         <v>0.6992</v>
       </c>
       <c r="M136" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -7824,11 +7824,11 @@
         <v>0.8045</v>
       </c>
       <c r="M137" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -7878,11 +7878,11 @@
         <v>0.6645</v>
       </c>
       <c r="M138" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -7932,11 +7932,11 @@
         <v>0.7326</v>
       </c>
       <c r="M139" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -7986,11 +7986,11 @@
         <v>0.7874</v>
       </c>
       <c r="M140" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -8040,11 +8040,11 @@
         <v>0.8066</v>
       </c>
       <c r="M141" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -8094,11 +8094,11 @@
         <v>0.7458</v>
       </c>
       <c r="M142" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -8148,11 +8148,11 @@
         <v>0.498</v>
       </c>
       <c r="M143" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -8202,11 +8202,11 @@
         <v>0.7462</v>
       </c>
       <c r="M144" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -8256,11 +8256,11 @@
         <v>0.3898</v>
       </c>
       <c r="M145" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -8310,11 +8310,11 @@
         <v>0.8286</v>
       </c>
       <c r="M146" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -8364,11 +8364,11 @@
         <v>0.6534</v>
       </c>
       <c r="M147" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -8418,11 +8418,11 @@
         <v>0.4254</v>
       </c>
       <c r="M148" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -8472,11 +8472,11 @@
         <v>0.64</v>
       </c>
       <c r="M149" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -8526,11 +8526,11 @@
         <v>0.7106</v>
       </c>
       <c r="M150" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -8580,11 +8580,11 @@
         <v>0.6645</v>
       </c>
       <c r="M151" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -8634,11 +8634,11 @@
         <v>0.4289</v>
       </c>
       <c r="M152" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -8688,11 +8688,11 @@
         <v>0.8306</v>
       </c>
       <c r="M153" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -8742,11 +8742,11 @@
         <v>0.8434</v>
       </c>
       <c r="M154" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -8796,11 +8796,11 @@
         <v>0.7383999999999999</v>
       </c>
       <c r="M155" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -8850,11 +8850,11 @@
         <v>0.4276</v>
       </c>
       <c r="M156" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -8904,11 +8904,11 @@
         <v>0.5046</v>
       </c>
       <c r="M157" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -8958,11 +8958,11 @@
         <v>0.3392</v>
       </c>
       <c r="M158" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -9012,11 +9012,11 @@
         <v>0.763</v>
       </c>
       <c r="M159" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -9066,11 +9066,11 @@
         <v>0.7844</v>
       </c>
       <c r="M160" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -9120,11 +9120,11 @@
         <v>0.3223</v>
       </c>
       <c r="M161" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -9174,11 +9174,11 @@
         <v>0.3979</v>
       </c>
       <c r="M162" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -9228,11 +9228,11 @@
         <v>0.4492</v>
       </c>
       <c r="M163" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -9282,11 +9282,11 @@
         <v>0.4902</v>
       </c>
       <c r="M164" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -9336,11 +9336,11 @@
         <v>0.3826</v>
       </c>
       <c r="M165" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -9390,11 +9390,11 @@
         <v>0.209</v>
       </c>
       <c r="M166" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -9444,11 +9444,11 @@
         <v>0.4157</v>
       </c>
       <c r="M167" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -9498,11 +9498,11 @@
         <v>0.1978</v>
       </c>
       <c r="M168" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -9552,11 +9552,11 @@
         <v>0.536</v>
       </c>
       <c r="M169" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -9606,11 +9606,11 @@
         <v>0.3448</v>
       </c>
       <c r="M170" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -9660,11 +9660,11 @@
         <v>0.1913</v>
       </c>
       <c r="M171" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -9714,11 +9714,11 @@
         <v>0.2944</v>
       </c>
       <c r="M172" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -9768,11 +9768,11 @@
         <v>0.3864</v>
       </c>
       <c r="M173" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -9822,11 +9822,11 @@
         <v>0.3238</v>
       </c>
       <c r="M174" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -9876,11 +9876,11 @@
         <v>0.202</v>
       </c>
       <c r="M175" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -9930,11 +9930,11 @@
         <v>0.554</v>
       </c>
       <c r="M176" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -9984,11 +9984,11 @@
         <v>0.6038</v>
       </c>
       <c r="M177" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -10038,11 +10038,11 @@
         <v>0.3996</v>
       </c>
       <c r="M178" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -10092,11 +10092,11 @@
         <v>0.1888</v>
       </c>
       <c r="M179" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -10146,11 +10146,11 @@
         <v>0.2113</v>
       </c>
       <c r="M180" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -10200,11 +10200,11 @@
         <v>0.1728</v>
       </c>
       <c r="M181" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -10254,11 +10254,11 @@
         <v>0.4726</v>
       </c>
       <c r="M182" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -10308,11 +10308,11 @@
         <v>0.4586</v>
       </c>
       <c r="M183" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -10362,11 +10362,11 @@
         <v>0.5952</v>
       </c>
       <c r="M184" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -10416,11 +10416,11 @@
         <v>0.6579</v>
       </c>
       <c r="M185" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -10470,11 +10470,11 @@
         <v>0.715</v>
       </c>
       <c r="M186" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -10524,11 +10524,11 @@
         <v>0.5636</v>
       </c>
       <c r="M187" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -10578,11 +10578,11 @@
         <v>0.3376</v>
       </c>
       <c r="M188" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -10632,11 +10632,11 @@
         <v>0.5908</v>
       </c>
       <c r="M189" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -10686,11 +10686,11 @@
         <v>0.2459</v>
       </c>
       <c r="M190" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -10740,11 +10740,11 @@
         <v>0.7268</v>
       </c>
       <c r="M191" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -10794,11 +10794,11 @@
         <v>0.5043</v>
       </c>
       <c r="M192" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -10848,11 +10848,11 @@
         <v>0.2893</v>
       </c>
       <c r="M193" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -10902,11 +10902,11 @@
         <v>0.4854</v>
       </c>
       <c r="M194" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -10956,11 +10956,11 @@
         <v>0.547</v>
       </c>
       <c r="M195" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -11010,11 +11010,11 @@
         <v>0.5128</v>
       </c>
       <c r="M196" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -11064,11 +11064,11 @@
         <v>0.2984</v>
       </c>
       <c r="M197" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -11118,11 +11118,11 @@
         <v>0.7306</v>
       </c>
       <c r="M198" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -11172,11 +11172,11 @@
         <v>0.802</v>
       </c>
       <c r="M199" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -11226,11 +11226,11 @@
         <v>0.5397999999999999</v>
       </c>
       <c r="M200" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -11280,11 +11280,11 @@
         <v>0.2947</v>
       </c>
       <c r="M201" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -11334,11 +11334,11 @@
         <v>0.3582</v>
       </c>
       <c r="M202" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -11388,11 +11388,11 @@
         <v>0.2417</v>
       </c>
       <c r="M203" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -11442,11 +11442,11 @@
         <v>0.6562</v>
       </c>
       <c r="M204" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -11496,11 +11496,11 @@
         <v>0.6584</v>
       </c>
       <c r="M205" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -11550,11 +11550,11 @@
         <v>0.5314</v>
       </c>
       <c r="M206" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -11604,11 +11604,11 @@
         <v>0.594</v>
       </c>
       <c r="M207" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -11658,11 +11658,11 @@
         <v>0.4928</v>
       </c>
       <c r="M208" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -11712,11 +11712,11 @@
         <v>0.2515</v>
       </c>
       <c r="M209" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -11766,11 +11766,11 @@
         <v>0.5007</v>
       </c>
       <c r="M210" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -11820,11 +11820,11 @@
         <v>0.2073</v>
       </c>
       <c r="M211" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -11874,11 +11874,11 @@
         <v>0.6328</v>
       </c>
       <c r="M212" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -11928,11 +11928,11 @@
         <v>0.4146</v>
       </c>
       <c r="M213" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -11982,11 +11982,11 @@
         <v>0.23</v>
       </c>
       <c r="M214" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -12036,11 +12036,11 @@
         <v>0.3881</v>
       </c>
       <c r="M215" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -12090,11 +12090,11 @@
         <v>0.4358</v>
       </c>
       <c r="M216" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -12144,11 +12144,11 @@
         <v>0.3914</v>
       </c>
       <c r="M217" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -12198,11 +12198,11 @@
         <v>0.2492</v>
       </c>
       <c r="M218" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -12252,11 +12252,11 @@
         <v>0.6504</v>
       </c>
       <c r="M219" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -12306,11 +12306,11 @@
         <v>0.7266</v>
       </c>
       <c r="M220" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -12360,11 +12360,11 @@
         <v>0.4699</v>
       </c>
       <c r="M221" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -12414,11 +12414,11 @@
         <v>0.2447</v>
       </c>
       <c r="M222" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -12468,11 +12468,11 @@
         <v>0.2634</v>
       </c>
       <c r="M223" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -12522,11 +12522,11 @@
         <v>0.206</v>
       </c>
       <c r="M224" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -12576,11 +12576,11 @@
         <v>0.5682</v>
       </c>
       <c r="M225" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -12630,11 +12630,11 @@
         <v>0.5512</v>
       </c>
       <c r="M226" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -12684,11 +12684,11 @@
         <v>0.5214</v>
       </c>
       <c r="M227" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -12738,11 +12738,11 @@
         <v>0.4536</v>
       </c>
       <c r="M228" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -12792,11 +12792,11 @@
         <v>0.2214</v>
       </c>
       <c r="M229" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -12846,11 +12846,11 @@
         <v>0.4526</v>
       </c>
       <c r="M230" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -12900,11 +12900,11 @@
         <v>0.1972</v>
       </c>
       <c r="M231" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -12954,11 +12954,11 @@
         <v>0.5866</v>
       </c>
       <c r="M232" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -13008,11 +13008,11 @@
         <v>0.3956</v>
       </c>
       <c r="M233" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -13062,11 +13062,11 @@
         <v>0.2052</v>
       </c>
       <c r="M234" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -13116,11 +13116,11 @@
         <v>0.3555</v>
       </c>
       <c r="M235" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -13170,11 +13170,11 @@
         <v>0.4246</v>
       </c>
       <c r="M236" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -13224,11 +13224,11 @@
         <v>0.3814</v>
       </c>
       <c r="M237" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -13278,11 +13278,11 @@
         <v>0.2065</v>
       </c>
       <c r="M238" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -13332,11 +13332,11 @@
         <v>0.5799</v>
       </c>
       <c r="M239" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -13386,11 +13386,11 @@
         <v>0.6482</v>
       </c>
       <c r="M240" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -13440,11 +13440,11 @@
         <v>0.4434</v>
       </c>
       <c r="M241" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -13494,11 +13494,11 @@
         <v>0.2072</v>
       </c>
       <c r="M242" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -13548,11 +13548,11 @@
         <v>0.235</v>
       </c>
       <c r="M243" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -13602,11 +13602,11 @@
         <v>0.1757</v>
       </c>
       <c r="M244" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -13656,11 +13656,11 @@
         <v>0.495</v>
       </c>
       <c r="M245" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -13710,11 +13710,11 @@
         <v>0.4931</v>
       </c>
       <c r="M246" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -13764,11 +13764,11 @@
         <v>0.4112</v>
       </c>
       <c r="M247" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -13818,11 +13818,11 @@
         <v>0.2164</v>
       </c>
       <c r="M248" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -13872,11 +13872,11 @@
         <v>0.4218</v>
       </c>
       <c r="M249" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -13926,11 +13926,11 @@
         <v>0.1952</v>
       </c>
       <c r="M250" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -13980,11 +13980,11 @@
         <v>0.5349</v>
       </c>
       <c r="M251" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -14034,11 +14034,11 @@
         <v>0.3642</v>
       </c>
       <c r="M252" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -14088,11 +14088,11 @@
         <v>0.1956</v>
       </c>
       <c r="M253" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -14142,11 +14142,11 @@
         <v>0.3283</v>
       </c>
       <c r="M254" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -14196,11 +14196,11 @@
         <v>0.391</v>
       </c>
       <c r="M255" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -14250,11 +14250,11 @@
         <v>0.3386</v>
       </c>
       <c r="M256" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -14304,11 +14304,11 @@
         <v>0.1899</v>
       </c>
       <c r="M257" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -14358,11 +14358,11 @@
         <v>0.5397</v>
       </c>
       <c r="M258" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -14412,11 +14412,11 @@
         <v>0.6204</v>
       </c>
       <c r="M259" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -14466,11 +14466,11 @@
         <v>0.3958</v>
       </c>
       <c r="M260" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -14520,11 +14520,11 @@
         <v>0.193</v>
       </c>
       <c r="M261" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -14574,11 +14574,11 @@
         <v>0.2096</v>
       </c>
       <c r="M262" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -14628,11 +14628,11 @@
         <v>0.1722</v>
       </c>
       <c r="M263" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -14682,11 +14682,11 @@
         <v>0.4733</v>
       </c>
       <c r="M264" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -14736,11 +14736,11 @@
         <v>0.4618</v>
       </c>
       <c r="M265" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -14790,11 +14790,11 @@
         <v>0.263</v>
       </c>
       <c r="M266" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -14844,11 +14844,11 @@
         <v>0.533</v>
       </c>
       <c r="M267" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -14898,11 +14898,11 @@
         <v>0.2114</v>
       </c>
       <c r="M268" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -14952,11 +14952,11 @@
         <v>0.6458</v>
       </c>
       <c r="M269" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -15006,11 +15006,11 @@
         <v>0.402</v>
       </c>
       <c r="M270" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -15060,11 +15060,11 @@
         <v>0.2434</v>
       </c>
       <c r="M271" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -15114,11 +15114,11 @@
         <v>0.4104</v>
       </c>
       <c r="M272" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -15168,11 +15168,11 @@
         <v>0.4584</v>
       </c>
       <c r="M273" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -15222,11 +15222,11 @@
         <v>0.4289</v>
       </c>
       <c r="M274" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -15276,11 +15276,11 @@
         <v>0.2516</v>
       </c>
       <c r="M275" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -15330,11 +15330,11 @@
         <v>0.67</v>
       </c>
       <c r="M276" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -15384,11 +15384,11 @@
         <v>0.7294</v>
       </c>
       <c r="M277" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -15438,11 +15438,11 @@
         <v>0.4655</v>
       </c>
       <c r="M278" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -15492,11 +15492,11 @@
         <v>0.2441</v>
       </c>
       <c r="M279" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N279" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -15546,11 +15546,11 @@
         <v>0.2744</v>
       </c>
       <c r="M280" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -15600,11 +15600,11 @@
         <v>0.2092</v>
       </c>
       <c r="M281" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -15654,11 +15654,11 @@
         <v>0.5577</v>
       </c>
       <c r="M282" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -15708,11 +15708,11 @@
         <v>0.579</v>
       </c>
       <c r="M283" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -15762,11 +15762,11 @@
         <v>0.7629</v>
       </c>
       <c r="M284" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -15816,11 +15816,11 @@
         <v>0.3926</v>
       </c>
       <c r="M285" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -15870,11 +15870,11 @@
         <v>0.8169</v>
       </c>
       <c r="M286" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -15924,11 +15924,11 @@
         <v>0.6952</v>
       </c>
       <c r="M287" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -15978,11 +15978,11 @@
         <v>0.4621</v>
       </c>
       <c r="M288" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -16032,11 +16032,11 @@
         <v>0.6472</v>
       </c>
       <c r="M289" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -16086,11 +16086,11 @@
         <v>0.7288</v>
       </c>
       <c r="M290" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -16140,11 +16140,11 @@
         <v>0.6706</v>
       </c>
       <c r="M291" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -16194,11 +16194,11 @@
         <v>0.4661</v>
       </c>
       <c r="M292" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -16248,11 +16248,11 @@
         <v>0.8201000000000001</v>
       </c>
       <c r="M293" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -16302,11 +16302,11 @@
         <v>0.8256</v>
       </c>
       <c r="M294" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -16356,11 +16356,11 @@
         <v>0.7401</v>
       </c>
       <c r="M295" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -16410,11 +16410,11 @@
         <v>0.4628</v>
       </c>
       <c r="M296" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -16464,11 +16464,11 @@
         <v>0.513</v>
       </c>
       <c r="M297" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -16518,11 +16518,11 @@
         <v>0.3674</v>
       </c>
       <c r="M298" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -16572,11 +16572,11 @@
         <v>0.7906</v>
       </c>
       <c r="M299" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -16626,11 +16626,11 @@
         <v>0.7861</v>
       </c>
       <c r="M300" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -16680,11 +16680,11 @@
         <v>0.203</v>
       </c>
       <c r="M301" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -16734,11 +16734,11 @@
         <v>0.6267</v>
       </c>
       <c r="M302" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -16788,11 +16788,11 @@
         <v>0.4038</v>
       </c>
       <c r="M303" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -16842,11 +16842,11 @@
         <v>0.2316</v>
       </c>
       <c r="M304" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -16896,11 +16896,11 @@
         <v>0.3877</v>
       </c>
       <c r="M305" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -16950,11 +16950,11 @@
         <v>0.4448</v>
       </c>
       <c r="M306" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -17004,11 +17004,11 @@
         <v>0.3963</v>
       </c>
       <c r="M307" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -17058,11 +17058,11 @@
         <v>0.243</v>
       </c>
       <c r="M308" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -17112,11 +17112,11 @@
         <v>0.6421</v>
       </c>
       <c r="M309" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -17166,11 +17166,11 @@
         <v>0.7266</v>
       </c>
       <c r="M310" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -17220,11 +17220,11 @@
         <v>0.4631</v>
       </c>
       <c r="M311" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -17274,11 +17274,11 @@
         <v>0.2434</v>
       </c>
       <c r="M312" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -17328,11 +17328,11 @@
         <v>0.2634</v>
       </c>
       <c r="M313" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -17382,11 +17382,11 @@
         <v>0.2115</v>
       </c>
       <c r="M314" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -17436,11 +17436,11 @@
         <v>0.5569</v>
       </c>
       <c r="M315" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -17490,11 +17490,11 @@
         <v>0.5468</v>
       </c>
       <c r="M316" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -17544,11 +17544,11 @@
         <v>0.848</v>
       </c>
       <c r="M317" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -17598,11 +17598,11 @@
         <v>0.7722</v>
       </c>
       <c r="M318" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -17652,11 +17652,11 @@
         <v>0.5574</v>
       </c>
       <c r="M319" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -17706,11 +17706,11 @@
         <v>0.7554999999999999</v>
       </c>
       <c r="M320" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -17760,11 +17760,11 @@
         <v>0.8</v>
       </c>
       <c r="M321" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -17814,11 +17814,11 @@
         <v>0.7802</v>
       </c>
       <c r="M322" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N322" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -17868,11 +17868,11 @@
         <v>0.5704</v>
       </c>
       <c r="M323" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -17922,11 +17922,11 @@
         <v>0.8423</v>
       </c>
       <c r="M324" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -17976,11 +17976,11 @@
         <v>0.8401999999999999</v>
       </c>
       <c r="M325" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -18030,11 +18030,11 @@
         <v>0.8121</v>
       </c>
       <c r="M326" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -18084,11 +18084,11 @@
         <v>0.5608</v>
       </c>
       <c r="M327" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N327" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -18138,11 +18138,11 @@
         <v>0.6337</v>
       </c>
       <c r="M328" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N328" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -18192,11 +18192,11 @@
         <v>0.4635</v>
       </c>
       <c r="M329" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -18246,11 +18246,11 @@
         <v>0.823</v>
       </c>
       <c r="M330" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -18300,11 +18300,11 @@
         <v>0.842</v>
       </c>
       <c r="M331" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -18354,11 +18354,11 @@
         <v>0.2854</v>
       </c>
       <c r="M332" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -18408,11 +18408,11 @@
         <v>0.1882</v>
       </c>
       <c r="M333" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -18462,11 +18462,11 @@
         <v>0.2698</v>
       </c>
       <c r="M334" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -18516,11 +18516,11 @@
         <v>0.3054</v>
       </c>
       <c r="M335" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -18570,11 +18570,11 @@
         <v>0.29</v>
       </c>
       <c r="M336" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -18624,11 +18624,11 @@
         <v>0.199</v>
       </c>
       <c r="M337" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -18678,11 +18678,11 @@
         <v>0.5233</v>
       </c>
       <c r="M338" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -18732,11 +18732,11 @@
         <v>0.5959</v>
       </c>
       <c r="M339" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -18786,11 +18786,11 @@
         <v>0.3273</v>
       </c>
       <c r="M340" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -18840,11 +18840,11 @@
         <v>0.1889</v>
       </c>
       <c r="M341" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -18894,11 +18894,11 @@
         <v>0.2043</v>
       </c>
       <c r="M342" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -18948,11 +18948,11 @@
         <v>0.1706</v>
       </c>
       <c r="M343" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -19002,11 +19002,11 @@
         <v>0.4564</v>
       </c>
       <c r="M344" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -19056,11 +19056,11 @@
         <v>0.4206</v>
       </c>
       <c r="M345" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -19110,11 +19110,11 @@
         <v>0.2752</v>
       </c>
       <c r="M346" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -19164,11 +19164,11 @@
         <v>0.4762</v>
       </c>
       <c r="M347" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -19218,11 +19218,11 @@
         <v>0.5129</v>
       </c>
       <c r="M348" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -19272,11 +19272,11 @@
         <v>0.4868</v>
       </c>
       <c r="M349" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -19326,11 +19326,11 @@
         <v>0.2898</v>
       </c>
       <c r="M350" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -19380,11 +19380,11 @@
         <v>0.7373</v>
       </c>
       <c r="M351" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -19434,11 +19434,11 @@
         <v>0.7847</v>
       </c>
       <c r="M352" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -19488,11 +19488,11 @@
         <v>0.547</v>
       </c>
       <c r="M353" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -19542,11 +19542,11 @@
         <v>0.2836</v>
       </c>
       <c r="M354" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -19596,11 +19596,11 @@
         <v>0.3193</v>
       </c>
       <c r="M355" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N355" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -19650,11 +19650,11 @@
         <v>0.2358</v>
       </c>
       <c r="M356" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N356" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -19704,11 +19704,11 @@
         <v>0.6202</v>
       </c>
       <c r="M357" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N357" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -19758,11 +19758,11 @@
         <v>0.6337</v>
       </c>
       <c r="M358" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N358" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -19812,11 +19812,11 @@
         <v>0.6811</v>
       </c>
       <c r="M359" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N359" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -19866,11 +19866,11 @@
         <v>0.7553</v>
       </c>
       <c r="M360" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N360" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -19920,11 +19920,11 @@
         <v>0.7106</v>
       </c>
       <c r="M361" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N361" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -19974,11 +19974,11 @@
         <v>0.4955</v>
       </c>
       <c r="M362" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N362" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -20028,11 +20028,11 @@
         <v>0.8308</v>
       </c>
       <c r="M363" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N363" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -20082,11 +20082,11 @@
         <v>0.8348</v>
       </c>
       <c r="M364" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N364" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -20136,11 +20136,11 @@
         <v>0.7796</v>
       </c>
       <c r="M365" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N365" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -20190,11 +20190,11 @@
         <v>0.5024</v>
       </c>
       <c r="M366" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N366" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -20244,11 +20244,11 @@
         <v>0.5389</v>
       </c>
       <c r="M367" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N367" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -20298,11 +20298,11 @@
         <v>0.3998</v>
       </c>
       <c r="M368" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N368" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -20352,11 +20352,11 @@
         <v>0.7806</v>
       </c>
       <c r="M369" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N369" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -20406,11 +20406,11 @@
         <v>0.8151</v>
       </c>
       <c r="M370" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N370" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -20460,11 +20460,11 @@
         <v>0.5372</v>
       </c>
       <c r="M371" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N371" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -20514,11 +20514,11 @@
         <v>0.5167</v>
       </c>
       <c r="M372" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N372" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -20568,11 +20568,11 @@
         <v>0.3022</v>
       </c>
       <c r="M373" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N373" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -20622,11 +20622,11 @@
         <v>0.7594</v>
       </c>
       <c r="M374" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N374" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -20676,11 +20676,11 @@
         <v>0.8159999999999999</v>
       </c>
       <c r="M375" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N375" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -20730,11 +20730,11 @@
         <v>0.5578</v>
       </c>
       <c r="M376" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N376" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -20784,11 +20784,11 @@
         <v>0.2894</v>
       </c>
       <c r="M377" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N377" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -20838,11 +20838,11 @@
         <v>0.364</v>
       </c>
       <c r="M378" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N378" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -20892,11 +20892,11 @@
         <v>0.2531</v>
       </c>
       <c r="M379" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N379" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -20946,11 +20946,11 @@
         <v>0.6572</v>
       </c>
       <c r="M380" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N380" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -21000,11 +21000,11 @@
         <v>0.6762</v>
       </c>
       <c r="M381" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N381" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -21054,11 +21054,11 @@
         <v>0.455</v>
       </c>
       <c r="M382" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N382" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -21108,11 +21108,11 @@
         <v>0.27</v>
       </c>
       <c r="M383" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N383" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -21162,11 +21162,11 @@
         <v>0.6816</v>
       </c>
       <c r="M384" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N384" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -21216,11 +21216,11 @@
         <v>0.7694</v>
       </c>
       <c r="M385" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N385" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -21270,11 +21270,11 @@
         <v>0.4968</v>
       </c>
       <c r="M386" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N386" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -21324,11 +21324,11 @@
         <v>0.2667</v>
       </c>
       <c r="M387" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N387" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -21378,11 +21378,11 @@
         <v>0.2998</v>
       </c>
       <c r="M388" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N388" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -21432,11 +21432,11 @@
         <v>0.2069</v>
       </c>
       <c r="M389" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N389" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -21486,11 +21486,11 @@
         <v>0.58</v>
       </c>
       <c r="M390" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N390" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -21540,11 +21540,11 @@
         <v>0.6082</v>
       </c>
       <c r="M391" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N391" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -21594,11 +21594,11 @@
         <v>0.2847</v>
       </c>
       <c r="M392" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N392" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -21648,11 +21648,11 @@
         <v>0.6988</v>
       </c>
       <c r="M393" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N393" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -21702,11 +21702,11 @@
         <v>0.7786</v>
       </c>
       <c r="M394" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N394" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -21756,11 +21756,11 @@
         <v>0.5570000000000001</v>
       </c>
       <c r="M395" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N395" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -21810,11 +21810,11 @@
         <v>0.2786</v>
       </c>
       <c r="M396" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N396" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -21864,11 +21864,11 @@
         <v>0.3555</v>
       </c>
       <c r="M397" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N397" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -21918,11 +21918,11 @@
         <v>0.239</v>
       </c>
       <c r="M398" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N398" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -21972,11 +21972,11 @@
         <v>0.6156</v>
       </c>
       <c r="M399" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N399" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -22026,11 +22026,11 @@
         <v>0.6326000000000001</v>
       </c>
       <c r="M400" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N400" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -22080,11 +22080,11 @@
         <v>0.8284</v>
       </c>
       <c r="M401" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N401" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -22134,11 +22134,11 @@
         <v>0.827</v>
       </c>
       <c r="M402" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N402" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -22188,11 +22188,11 @@
         <v>0.7712</v>
       </c>
       <c r="M403" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N403" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -22242,11 +22242,11 @@
         <v>0.5061</v>
       </c>
       <c r="M404" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N404" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -22296,11 +22296,11 @@
         <v>0.5568</v>
       </c>
       <c r="M405" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N405" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -22350,11 +22350,11 @@
         <v>0.4064</v>
       </c>
       <c r="M406" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N406" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -22404,11 +22404,11 @@
         <v>0.7742</v>
       </c>
       <c r="M407" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N407" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -22458,11 +22458,11 @@
         <v>0.8090000000000001</v>
       </c>
       <c r="M408" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N408" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -22512,11 +22512,11 @@
         <v>0.5717</v>
       </c>
       <c r="M409" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N409" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -22566,11 +22566,11 @@
         <v>0.3304</v>
       </c>
       <c r="M410" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N410" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -22620,11 +22620,11 @@
         <v>0.1975</v>
       </c>
       <c r="M411" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N411" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -22674,11 +22674,11 @@
         <v>0.2182</v>
       </c>
       <c r="M412" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N412" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -22728,11 +22728,11 @@
         <v>0.1843</v>
       </c>
       <c r="M413" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N413" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -22782,11 +22782,11 @@
         <v>0.4322</v>
       </c>
       <c r="M414" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N414" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -22836,11 +22836,11 @@
         <v>0.3731</v>
       </c>
       <c r="M415" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N415" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -22890,11 +22890,11 @@
         <v>0.2674</v>
       </c>
       <c r="M416" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N416" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -22944,11 +22944,11 @@
         <v>0.1928</v>
       </c>
       <c r="M417" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N417" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -22998,11 +22998,11 @@
         <v>0.2008</v>
       </c>
       <c r="M418" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N418" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -23052,11 +23052,11 @@
         <v>0.1791</v>
       </c>
       <c r="M419" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N419" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -23106,11 +23106,11 @@
         <v>0.3279</v>
       </c>
       <c r="M420" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N420" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -23160,11 +23160,11 @@
         <v>0.3024</v>
       </c>
       <c r="M421" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N421" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -23214,11 +23214,11 @@
         <v>0.248</v>
       </c>
       <c r="M422" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N422" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -23268,11 +23268,11 @@
         <v>0.2905</v>
       </c>
       <c r="M423" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N423" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -23322,11 +23322,11 @@
         <v>0.1999</v>
       </c>
       <c r="M424" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N424" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -23376,11 +23376,11 @@
         <v>0.5631</v>
       </c>
       <c r="M425" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N425" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -23430,11 +23430,11 @@
         <v>0.5825</v>
       </c>
       <c r="M426" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N426" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -23484,11 +23484,11 @@
         <v>0.5492</v>
       </c>
       <c r="M427" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N427" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -23538,11 +23538,11 @@
         <v>0.4163</v>
       </c>
       <c r="M428" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N428" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -23592,11 +23592,11 @@
         <v>0.7868000000000001</v>
       </c>
       <c r="M429" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N429" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -23646,11 +23646,11 @@
         <v>0.8202</v>
       </c>
       <c r="M430" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N430" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -23700,11 +23700,11 @@
         <v>0.3186</v>
       </c>
       <c r="M431" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N431" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -23754,11 +23754,11 @@
         <v>0.753</v>
       </c>
       <c r="M432" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N432" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -23808,11 +23808,11 @@
         <v>0.766</v>
       </c>
       <c r="M433" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N433" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -23862,11 +23862,11 @@
         <v>0.8085</v>
       </c>
       <c r="M434" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N434" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -23916,11 +23916,11 @@
         <v>0.8354</v>
       </c>
       <c r="M435" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N435" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>
@@ -23970,11 +23970,11 @@
         <v>0.4654</v>
       </c>
       <c r="M436" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N436" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
     </row>

--- a/nba/public/data/nba_matchup_probs.xlsx
+++ b/nba/public/data/nba_matchup_probs.xlsx
@@ -681,19 +681,19 @@
         <v>0.7945</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6246</v>
+        <v>0.628</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7096</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="J5" t="n">
         <v>0.2055</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3754</v>
+        <v>0.372</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2904</v>
+        <v>0.2888</v>
       </c>
       <c r="M5" t="n">
         <v>164</v>
@@ -732,22 +732,22 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.8241000000000001</v>
+        <v>0.8276</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6977</v>
+        <v>0.7004</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7609</v>
+        <v>0.764</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1759</v>
+        <v>0.1724</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3023</v>
+        <v>0.2996</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2391</v>
+        <v>0.236</v>
       </c>
       <c r="M6" t="n">
         <v>164</v>
@@ -1002,22 +1002,22 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.5033</v>
+        <v>0.5017</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3327</v>
+        <v>0.3307</v>
       </c>
       <c r="I11" t="n">
-        <v>0.418</v>
+        <v>0.4162</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4967</v>
+        <v>0.4983</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6673</v>
+        <v>0.6693</v>
       </c>
       <c r="L11" t="n">
-        <v>0.582</v>
+        <v>0.5838</v>
       </c>
       <c r="M11" t="n">
         <v>164</v>
@@ -1113,19 +1113,19 @@
         <v>0.832</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6652</v>
+        <v>0.6703</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7486</v>
+        <v>0.7512</v>
       </c>
       <c r="J13" t="n">
         <v>0.168</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3348</v>
+        <v>0.3297</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2514</v>
+        <v>0.2488</v>
       </c>
       <c r="M13" t="n">
         <v>164</v>
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.8648</v>
+        <v>0.8661</v>
       </c>
       <c r="H15" t="n">
         <v>0.7592</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.8126</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1352</v>
+        <v>0.1339</v>
       </c>
       <c r="K15" t="n">
         <v>0.2408</v>
       </c>
       <c r="L15" t="n">
-        <v>0.188</v>
+        <v>0.1874</v>
       </c>
       <c r="M15" t="n">
         <v>164</v>
@@ -1272,22 +1272,22 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.4829</v>
+        <v>0.5047</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3036</v>
+        <v>0.3407</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3932</v>
+        <v>0.4227</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5171</v>
+        <v>0.4953</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6964</v>
+        <v>0.6593</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6068</v>
+        <v>0.5773</v>
       </c>
       <c r="M16" t="n">
         <v>164</v>
@@ -1380,22 +1380,22 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.8126</v>
+        <v>0.8139</v>
       </c>
       <c r="H18" t="n">
         <v>0.6903</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7514</v>
+        <v>0.7521</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1874</v>
+        <v>0.1861</v>
       </c>
       <c r="K18" t="n">
         <v>0.3097</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2486</v>
+        <v>0.2479</v>
       </c>
       <c r="M18" t="n">
         <v>164</v>
@@ -1542,22 +1542,22 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.6887</v>
+        <v>0.6918</v>
       </c>
       <c r="H21" t="n">
         <v>0.5451</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6169</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3113</v>
+        <v>0.3082</v>
       </c>
       <c r="K21" t="n">
         <v>0.4549</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3831</v>
+        <v>0.3816</v>
       </c>
       <c r="M21" t="n">
         <v>164</v>
@@ -1596,22 +1596,22 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.8465</v>
+        <v>0.8511</v>
       </c>
       <c r="H22" t="n">
         <v>0.7255</v>
       </c>
       <c r="I22" t="n">
-        <v>0.786</v>
+        <v>0.7883</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1535</v>
+        <v>0.1489</v>
       </c>
       <c r="K22" t="n">
         <v>0.2745</v>
       </c>
       <c r="L22" t="n">
-        <v>0.214</v>
+        <v>0.2117</v>
       </c>
       <c r="M22" t="n">
         <v>164</v>
@@ -1815,19 +1815,19 @@
         <v>0.8459</v>
       </c>
       <c r="H26" t="n">
-        <v>0.71</v>
+        <v>0.714</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7779</v>
+        <v>0.7799</v>
       </c>
       <c r="J26" t="n">
         <v>0.1541</v>
       </c>
       <c r="K26" t="n">
-        <v>0.29</v>
+        <v>0.286</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2221</v>
+        <v>0.2201</v>
       </c>
       <c r="M26" t="n">
         <v>164</v>
@@ -1866,22 +1866,22 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.8456</v>
+        <v>0.8429</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6868</v>
+        <v>0.6807</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7662</v>
+        <v>0.7618</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1544</v>
+        <v>0.1571</v>
       </c>
       <c r="K27" t="n">
-        <v>0.3132</v>
+        <v>0.3193</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2338</v>
+        <v>0.2382</v>
       </c>
       <c r="M27" t="n">
         <v>164</v>
@@ -1974,22 +1974,22 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.5229</v>
+        <v>0.5273</v>
       </c>
       <c r="H29" t="n">
         <v>0.374</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4484</v>
+        <v>0.4506</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4771</v>
+        <v>0.4727</v>
       </c>
       <c r="K29" t="n">
         <v>0.626</v>
       </c>
       <c r="L29" t="n">
-        <v>0.5516</v>
+        <v>0.5494</v>
       </c>
       <c r="M29" t="n">
         <v>164</v>
@@ -2244,22 +2244,22 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.8669</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7684</v>
+        <v>0.7734</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8174</v>
+        <v>0.8202</v>
       </c>
       <c r="J34" t="n">
-        <v>0.1336</v>
+        <v>0.1331</v>
       </c>
       <c r="K34" t="n">
-        <v>0.2316</v>
+        <v>0.2266</v>
       </c>
       <c r="L34" t="n">
-        <v>0.1826</v>
+        <v>0.1798</v>
       </c>
       <c r="M34" t="n">
         <v>164</v>
@@ -2568,22 +2568,22 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.7932</v>
       </c>
       <c r="H40" t="n">
-        <v>0.619</v>
+        <v>0.6192</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7054</v>
+        <v>0.7062</v>
       </c>
       <c r="J40" t="n">
-        <v>0.2082</v>
+        <v>0.2068</v>
       </c>
       <c r="K40" t="n">
-        <v>0.381</v>
+        <v>0.3808</v>
       </c>
       <c r="L40" t="n">
-        <v>0.2946</v>
+        <v>0.2938</v>
       </c>
       <c r="M40" t="n">
         <v>164</v>
@@ -2625,19 +2625,19 @@
         <v>0.8734</v>
       </c>
       <c r="H41" t="n">
-        <v>0.7782</v>
+        <v>0.7813</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8258</v>
+        <v>0.8274</v>
       </c>
       <c r="J41" t="n">
         <v>0.1266</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2218</v>
+        <v>0.2187</v>
       </c>
       <c r="L41" t="n">
-        <v>0.1742</v>
+        <v>0.1726</v>
       </c>
       <c r="M41" t="n">
         <v>164</v>
@@ -2676,22 +2676,22 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.6625</v>
+        <v>0.6657</v>
       </c>
       <c r="H42" t="n">
         <v>0.5251</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5938</v>
+        <v>0.5954</v>
       </c>
       <c r="J42" t="n">
-        <v>0.3375</v>
+        <v>0.3343</v>
       </c>
       <c r="K42" t="n">
         <v>0.4749</v>
       </c>
       <c r="L42" t="n">
-        <v>0.4062</v>
+        <v>0.4046</v>
       </c>
       <c r="M42" t="n">
         <v>164</v>
@@ -2784,22 +2784,22 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.6152</v>
       </c>
       <c r="H44" t="n">
-        <v>0.4938</v>
+        <v>0.5048</v>
       </c>
       <c r="I44" t="n">
-        <v>0.532</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>0.4299</v>
+        <v>0.3848</v>
       </c>
       <c r="K44" t="n">
-        <v>0.5062</v>
+        <v>0.4952</v>
       </c>
       <c r="L44" t="n">
-        <v>0.468</v>
+        <v>0.44</v>
       </c>
       <c r="M44" t="n">
         <v>164</v>
@@ -2838,22 +2838,22 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.8269</v>
+        <v>0.8289</v>
       </c>
       <c r="H45" t="n">
-        <v>0.6751</v>
+        <v>0.6773</v>
       </c>
       <c r="I45" t="n">
-        <v>0.751</v>
+        <v>0.7531</v>
       </c>
       <c r="J45" t="n">
-        <v>0.1731</v>
+        <v>0.1711</v>
       </c>
       <c r="K45" t="n">
-        <v>0.3249</v>
+        <v>0.3227</v>
       </c>
       <c r="L45" t="n">
-        <v>0.249</v>
+        <v>0.2469</v>
       </c>
       <c r="M45" t="n">
         <v>164</v>
@@ -2892,22 +2892,22 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.8594000000000001</v>
+        <v>0.8618</v>
       </c>
       <c r="H46" t="n">
         <v>0.7529</v>
       </c>
       <c r="I46" t="n">
-        <v>0.8062</v>
+        <v>0.8074</v>
       </c>
       <c r="J46" t="n">
-        <v>0.1406</v>
+        <v>0.1382</v>
       </c>
       <c r="K46" t="n">
         <v>0.2471</v>
       </c>
       <c r="L46" t="n">
-        <v>0.1938</v>
+        <v>0.1926</v>
       </c>
       <c r="M46" t="n">
         <v>164</v>
@@ -2946,22 +2946,22 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.7602</v>
+        <v>0.7613</v>
       </c>
       <c r="H47" t="n">
         <v>0.638</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.6996</v>
       </c>
       <c r="J47" t="n">
-        <v>0.2398</v>
+        <v>0.2387</v>
       </c>
       <c r="K47" t="n">
         <v>0.362</v>
       </c>
       <c r="L47" t="n">
-        <v>0.3009</v>
+        <v>0.3004</v>
       </c>
       <c r="M47" t="n">
         <v>164</v>
@@ -3000,22 +3000,22 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.7854</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="H48" t="n">
         <v>0.634</v>
       </c>
       <c r="I48" t="n">
-        <v>0.7097</v>
+        <v>0.7109</v>
       </c>
       <c r="J48" t="n">
-        <v>0.2146</v>
+        <v>0.2122</v>
       </c>
       <c r="K48" t="n">
         <v>0.366</v>
       </c>
       <c r="L48" t="n">
-        <v>0.2903</v>
+        <v>0.2891</v>
       </c>
       <c r="M48" t="n">
         <v>164</v>
@@ -3054,22 +3054,22 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0.7889</v>
+        <v>0.7902</v>
       </c>
       <c r="H49" t="n">
         <v>0.644</v>
       </c>
       <c r="I49" t="n">
-        <v>0.7164</v>
+        <v>0.7171</v>
       </c>
       <c r="J49" t="n">
-        <v>0.2111</v>
+        <v>0.2098</v>
       </c>
       <c r="K49" t="n">
         <v>0.356</v>
       </c>
       <c r="L49" t="n">
-        <v>0.2836</v>
+        <v>0.2829</v>
       </c>
       <c r="M49" t="n">
         <v>164</v>
@@ -3270,22 +3270,22 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.7642</v>
+        <v>0.7661</v>
       </c>
       <c r="H53" t="n">
         <v>0.5956</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6798999999999999</v>
+        <v>0.6808</v>
       </c>
       <c r="J53" t="n">
-        <v>0.2358</v>
+        <v>0.2339</v>
       </c>
       <c r="K53" t="n">
         <v>0.4044</v>
       </c>
       <c r="L53" t="n">
-        <v>0.3201</v>
+        <v>0.3192</v>
       </c>
       <c r="M53" t="n">
         <v>164</v>
@@ -3324,22 +3324,22 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.8839</v>
+        <v>0.885</v>
       </c>
       <c r="H54" t="n">
         <v>0.7709</v>
       </c>
       <c r="I54" t="n">
-        <v>0.8274</v>
+        <v>0.828</v>
       </c>
       <c r="J54" t="n">
-        <v>0.1161</v>
+        <v>0.115</v>
       </c>
       <c r="K54" t="n">
         <v>0.2291</v>
       </c>
       <c r="L54" t="n">
-        <v>0.1726</v>
+        <v>0.172</v>
       </c>
       <c r="M54" t="n">
         <v>164</v>
@@ -3381,19 +3381,19 @@
         <v>0.8875</v>
       </c>
       <c r="H55" t="n">
-        <v>0.7915</v>
+        <v>0.7824</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8395</v>
+        <v>0.835</v>
       </c>
       <c r="J55" t="n">
         <v>0.1125</v>
       </c>
       <c r="K55" t="n">
-        <v>0.2085</v>
+        <v>0.2176</v>
       </c>
       <c r="L55" t="n">
-        <v>0.1605</v>
+        <v>0.165</v>
       </c>
       <c r="M55" t="n">
         <v>164</v>
@@ -3486,22 +3486,22 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.6499</v>
+        <v>0.6529</v>
       </c>
       <c r="H57" t="n">
         <v>0.4544</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5522</v>
+        <v>0.5536</v>
       </c>
       <c r="J57" t="n">
-        <v>0.3501</v>
+        <v>0.3471</v>
       </c>
       <c r="K57" t="n">
         <v>0.5456</v>
       </c>
       <c r="L57" t="n">
-        <v>0.4478</v>
+        <v>0.4464</v>
       </c>
       <c r="M57" t="n">
         <v>164</v>
@@ -3594,22 +3594,22 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.8226</v>
+        <v>0.8247</v>
       </c>
       <c r="H59" t="n">
         <v>0.7265</v>
       </c>
       <c r="I59" t="n">
-        <v>0.7746</v>
+        <v>0.7756</v>
       </c>
       <c r="J59" t="n">
-        <v>0.1774</v>
+        <v>0.1753</v>
       </c>
       <c r="K59" t="n">
         <v>0.2735</v>
       </c>
       <c r="L59" t="n">
-        <v>0.2254</v>
+        <v>0.2244</v>
       </c>
       <c r="M59" t="n">
         <v>164</v>
@@ -3651,19 +3651,19 @@
         <v>0.8323</v>
       </c>
       <c r="H60" t="n">
-        <v>0.7197</v>
+        <v>0.7236</v>
       </c>
       <c r="I60" t="n">
-        <v>0.776</v>
+        <v>0.778</v>
       </c>
       <c r="J60" t="n">
         <v>0.1677</v>
       </c>
       <c r="K60" t="n">
-        <v>0.2803</v>
+        <v>0.2764</v>
       </c>
       <c r="L60" t="n">
-        <v>0.224</v>
+        <v>0.222</v>
       </c>
       <c r="M60" t="n">
         <v>164</v>
@@ -3702,22 +3702,22 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.8552999999999999</v>
+        <v>0.8597</v>
       </c>
       <c r="H61" t="n">
         <v>0.771</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8132</v>
+        <v>0.8154</v>
       </c>
       <c r="J61" t="n">
-        <v>0.1447</v>
+        <v>0.1403</v>
       </c>
       <c r="K61" t="n">
         <v>0.229</v>
       </c>
       <c r="L61" t="n">
-        <v>0.1868</v>
+        <v>0.1846</v>
       </c>
       <c r="M61" t="n">
         <v>164</v>
@@ -3810,22 +3810,22 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.7965</v>
+        <v>0.8003</v>
       </c>
       <c r="H63" t="n">
         <v>0.6428</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7196</v>
+        <v>0.7216</v>
       </c>
       <c r="J63" t="n">
-        <v>0.2035</v>
+        <v>0.1997</v>
       </c>
       <c r="K63" t="n">
         <v>0.3572</v>
       </c>
       <c r="L63" t="n">
-        <v>0.2804</v>
+        <v>0.2784</v>
       </c>
       <c r="M63" t="n">
         <v>164</v>
@@ -3918,22 +3918,22 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0.6997</v>
+        <v>0.7015</v>
       </c>
       <c r="H65" t="n">
-        <v>0.5577</v>
+        <v>0.5593</v>
       </c>
       <c r="I65" t="n">
-        <v>0.6287</v>
+        <v>0.6304</v>
       </c>
       <c r="J65" t="n">
-        <v>0.3003</v>
+        <v>0.2985</v>
       </c>
       <c r="K65" t="n">
-        <v>0.4423</v>
+        <v>0.4407</v>
       </c>
       <c r="L65" t="n">
-        <v>0.3713</v>
+        <v>0.3696</v>
       </c>
       <c r="M65" t="n">
         <v>164</v>
@@ -4242,22 +4242,22 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.569</v>
+        <v>0.6141</v>
       </c>
       <c r="H71" t="n">
-        <v>0.4374</v>
+        <v>0.457</v>
       </c>
       <c r="I71" t="n">
-        <v>0.5032</v>
+        <v>0.5356</v>
       </c>
       <c r="J71" t="n">
-        <v>0.431</v>
+        <v>0.3859</v>
       </c>
       <c r="K71" t="n">
-        <v>0.5626</v>
+        <v>0.543</v>
       </c>
       <c r="L71" t="n">
-        <v>0.4968</v>
+        <v>0.4644</v>
       </c>
       <c r="M71" t="n">
         <v>164</v>
@@ -4296,22 +4296,22 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.8008</v>
+        <v>0.802</v>
       </c>
       <c r="H72" t="n">
         <v>0.6523</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7266</v>
+        <v>0.7272</v>
       </c>
       <c r="J72" t="n">
-        <v>0.1992</v>
+        <v>0.198</v>
       </c>
       <c r="K72" t="n">
         <v>0.3477</v>
       </c>
       <c r="L72" t="n">
-        <v>0.2734</v>
+        <v>0.2728</v>
       </c>
       <c r="M72" t="n">
         <v>164</v>
@@ -4458,22 +4458,22 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.7521</v>
+        <v>0.7538</v>
       </c>
       <c r="H75" t="n">
         <v>0.5977</v>
       </c>
       <c r="I75" t="n">
-        <v>0.6749000000000001</v>
+        <v>0.6758</v>
       </c>
       <c r="J75" t="n">
-        <v>0.2479</v>
+        <v>0.2462</v>
       </c>
       <c r="K75" t="n">
         <v>0.4023</v>
       </c>
       <c r="L75" t="n">
-        <v>0.3251</v>
+        <v>0.3242</v>
       </c>
       <c r="M75" t="n">
         <v>164</v>
@@ -4512,22 +4512,22 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.7931</v>
+        <v>0.7982</v>
       </c>
       <c r="H76" t="n">
-        <v>0.6399</v>
+        <v>0.6439</v>
       </c>
       <c r="I76" t="n">
-        <v>0.7165</v>
+        <v>0.721</v>
       </c>
       <c r="J76" t="n">
-        <v>0.2069</v>
+        <v>0.2018</v>
       </c>
       <c r="K76" t="n">
-        <v>0.3601</v>
+        <v>0.3561</v>
       </c>
       <c r="L76" t="n">
-        <v>0.2835</v>
+        <v>0.279</v>
       </c>
       <c r="M76" t="n">
         <v>164</v>
@@ -4620,22 +4620,22 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.5272</v>
+        <v>0.5281</v>
       </c>
       <c r="H78" t="n">
         <v>0.3592</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4432</v>
+        <v>0.4436</v>
       </c>
       <c r="J78" t="n">
-        <v>0.4728</v>
+        <v>0.4719</v>
       </c>
       <c r="K78" t="n">
         <v>0.6408</v>
       </c>
       <c r="L78" t="n">
-        <v>0.5568</v>
+        <v>0.5564</v>
       </c>
       <c r="M78" t="n">
         <v>164</v>
@@ -4728,22 +4728,22 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.7265</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="H80" t="n">
         <v>0.5754</v>
       </c>
       <c r="I80" t="n">
-        <v>0.651</v>
+        <v>0.6524</v>
       </c>
       <c r="J80" t="n">
-        <v>0.2735</v>
+        <v>0.2707</v>
       </c>
       <c r="K80" t="n">
         <v>0.4246</v>
       </c>
       <c r="L80" t="n">
-        <v>0.349</v>
+        <v>0.3476</v>
       </c>
       <c r="M80" t="n">
         <v>164</v>
@@ -4947,19 +4947,19 @@
         <v>0.6131</v>
       </c>
       <c r="H84" t="n">
-        <v>0.4825</v>
+        <v>0.4849</v>
       </c>
       <c r="I84" t="n">
-        <v>0.5478</v>
+        <v>0.549</v>
       </c>
       <c r="J84" t="n">
         <v>0.3869</v>
       </c>
       <c r="K84" t="n">
-        <v>0.5175</v>
+        <v>0.5151</v>
       </c>
       <c r="L84" t="n">
-        <v>0.4522</v>
+        <v>0.451</v>
       </c>
       <c r="M84" t="n">
         <v>164</v>
@@ -5106,22 +5106,22 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>0.643</v>
+        <v>0.6427</v>
       </c>
       <c r="H87" t="n">
-        <v>0.5003</v>
+        <v>0.503</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5716</v>
+        <v>0.5729</v>
       </c>
       <c r="J87" t="n">
-        <v>0.357</v>
+        <v>0.3573</v>
       </c>
       <c r="K87" t="n">
-        <v>0.4997</v>
+        <v>0.497</v>
       </c>
       <c r="L87" t="n">
-        <v>0.4284</v>
+        <v>0.4271</v>
       </c>
       <c r="M87" t="n">
         <v>164</v>
@@ -5163,19 +5163,19 @@
         <v>0.2804</v>
       </c>
       <c r="H88" t="n">
-        <v>0.1696</v>
+        <v>0.1635</v>
       </c>
       <c r="I88" t="n">
-        <v>0.225</v>
+        <v>0.222</v>
       </c>
       <c r="J88" t="n">
         <v>0.7196</v>
       </c>
       <c r="K88" t="n">
-        <v>0.8304</v>
+        <v>0.8365</v>
       </c>
       <c r="L88" t="n">
-        <v>0.775</v>
+        <v>0.778</v>
       </c>
       <c r="M88" t="n">
         <v>164</v>
@@ -5271,19 +5271,19 @@
         <v>0.3351</v>
       </c>
       <c r="H90" t="n">
-        <v>0.215</v>
+        <v>0.2132</v>
       </c>
       <c r="I90" t="n">
-        <v>0.275</v>
+        <v>0.2742</v>
       </c>
       <c r="J90" t="n">
         <v>0.6649</v>
       </c>
       <c r="K90" t="n">
-        <v>0.785</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="L90" t="n">
-        <v>0.725</v>
+        <v>0.7258</v>
       </c>
       <c r="M90" t="n">
         <v>164</v>
@@ -5322,22 +5322,22 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0.3778</v>
+        <v>0.3796</v>
       </c>
       <c r="H91" t="n">
         <v>0.2349</v>
       </c>
       <c r="I91" t="n">
-        <v>0.3064</v>
+        <v>0.3073</v>
       </c>
       <c r="J91" t="n">
-        <v>0.6222</v>
+        <v>0.6204</v>
       </c>
       <c r="K91" t="n">
         <v>0.7651</v>
       </c>
       <c r="L91" t="n">
-        <v>0.6936</v>
+        <v>0.6927</v>
       </c>
       <c r="M91" t="n">
         <v>164</v>
@@ -5487,19 +5487,19 @@
         <v>0.658</v>
       </c>
       <c r="H94" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.5079</v>
       </c>
       <c r="I94" t="n">
-        <v>0.5802</v>
+        <v>0.583</v>
       </c>
       <c r="J94" t="n">
         <v>0.342</v>
       </c>
       <c r="K94" t="n">
-        <v>0.4975</v>
+        <v>0.4921</v>
       </c>
       <c r="L94" t="n">
-        <v>0.4198</v>
+        <v>0.417</v>
       </c>
       <c r="M94" t="n">
         <v>164</v>
@@ -5646,22 +5646,22 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>0.2647</v>
+        <v>0.287</v>
       </c>
       <c r="H97" t="n">
-        <v>0.1656</v>
+        <v>0.1822</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2152</v>
+        <v>0.2346</v>
       </c>
       <c r="J97" t="n">
-        <v>0.7353</v>
+        <v>0.713</v>
       </c>
       <c r="K97" t="n">
-        <v>0.8344</v>
+        <v>0.8178</v>
       </c>
       <c r="L97" t="n">
-        <v>0.7848000000000001</v>
+        <v>0.7654</v>
       </c>
       <c r="M97" t="n">
         <v>164</v>
@@ -6024,22 +6024,22 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>0.2772</v>
+        <v>0.2753</v>
       </c>
       <c r="H104" t="n">
         <v>0.1574</v>
       </c>
       <c r="I104" t="n">
-        <v>0.2173</v>
+        <v>0.2164</v>
       </c>
       <c r="J104" t="n">
-        <v>0.7228</v>
+        <v>0.7247</v>
       </c>
       <c r="K104" t="n">
         <v>0.8426</v>
       </c>
       <c r="L104" t="n">
-        <v>0.7827</v>
+        <v>0.7836</v>
       </c>
       <c r="M104" t="n">
         <v>164</v>
@@ -6189,19 +6189,19 @@
         <v>0.7000999999999999</v>
       </c>
       <c r="H107" t="n">
-        <v>0.5818</v>
+        <v>0.5854</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6409</v>
+        <v>0.6427</v>
       </c>
       <c r="J107" t="n">
         <v>0.2999</v>
       </c>
       <c r="K107" t="n">
-        <v>0.4182</v>
+        <v>0.4146</v>
       </c>
       <c r="L107" t="n">
-        <v>0.3591</v>
+        <v>0.3573</v>
       </c>
       <c r="M107" t="n">
         <v>164</v>
@@ -6240,22 +6240,22 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>0.6754</v>
+        <v>0.6723</v>
       </c>
       <c r="H108" t="n">
-        <v>0.5309</v>
+        <v>0.5238</v>
       </c>
       <c r="I108" t="n">
-        <v>0.6032</v>
+        <v>0.598</v>
       </c>
       <c r="J108" t="n">
-        <v>0.3246</v>
+        <v>0.3277</v>
       </c>
       <c r="K108" t="n">
-        <v>0.4691</v>
+        <v>0.4762</v>
       </c>
       <c r="L108" t="n">
-        <v>0.3968</v>
+        <v>0.402</v>
       </c>
       <c r="M108" t="n">
         <v>164</v>
@@ -6297,19 +6297,19 @@
         <v>0.7799</v>
       </c>
       <c r="H109" t="n">
-        <v>0.6306</v>
+        <v>0.6297</v>
       </c>
       <c r="I109" t="n">
-        <v>0.7052</v>
+        <v>0.7048</v>
       </c>
       <c r="J109" t="n">
         <v>0.2201</v>
       </c>
       <c r="K109" t="n">
-        <v>0.3694</v>
+        <v>0.3703</v>
       </c>
       <c r="L109" t="n">
-        <v>0.2948</v>
+        <v>0.2952</v>
       </c>
       <c r="M109" t="n">
         <v>164</v>
@@ -6405,19 +6405,19 @@
         <v>0.3564</v>
       </c>
       <c r="H111" t="n">
-        <v>0.2128</v>
+        <v>0.2096</v>
       </c>
       <c r="I111" t="n">
-        <v>0.2846</v>
+        <v>0.283</v>
       </c>
       <c r="J111" t="n">
         <v>0.6435999999999999</v>
       </c>
       <c r="K111" t="n">
-        <v>0.7872</v>
+        <v>0.7904</v>
       </c>
       <c r="L111" t="n">
-        <v>0.7154</v>
+        <v>0.717</v>
       </c>
       <c r="M111" t="n">
         <v>164</v>
@@ -6456,22 +6456,22 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>0.6371</v>
+        <v>0.6409</v>
       </c>
       <c r="H112" t="n">
         <v>0.4718</v>
       </c>
       <c r="I112" t="n">
-        <v>0.5544</v>
+        <v>0.5564</v>
       </c>
       <c r="J112" t="n">
-        <v>0.3629</v>
+        <v>0.3591</v>
       </c>
       <c r="K112" t="n">
         <v>0.5282</v>
       </c>
       <c r="L112" t="n">
-        <v>0.4456</v>
+        <v>0.4436</v>
       </c>
       <c r="M112" t="n">
         <v>164</v>
@@ -6729,19 +6729,19 @@
         <v>0.3087</v>
       </c>
       <c r="H117" t="n">
-        <v>0.1631</v>
+        <v>0.1625</v>
       </c>
       <c r="I117" t="n">
-        <v>0.2359</v>
+        <v>0.2356</v>
       </c>
       <c r="J117" t="n">
         <v>0.6913</v>
       </c>
       <c r="K117" t="n">
-        <v>0.8369</v>
+        <v>0.8375</v>
       </c>
       <c r="L117" t="n">
-        <v>0.7641</v>
+        <v>0.7644</v>
       </c>
       <c r="M117" t="n">
         <v>164</v>
@@ -6837,19 +6837,19 @@
         <v>0.637</v>
       </c>
       <c r="H119" t="n">
-        <v>0.5097</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5734</v>
+        <v>0.5748</v>
       </c>
       <c r="J119" t="n">
         <v>0.363</v>
       </c>
       <c r="K119" t="n">
-        <v>0.4903</v>
+        <v>0.4874</v>
       </c>
       <c r="L119" t="n">
-        <v>0.4266</v>
+        <v>0.4252</v>
       </c>
       <c r="M119" t="n">
         <v>164</v>
@@ -6996,22 +6996,22 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0.2766</v>
+        <v>0.3044</v>
       </c>
       <c r="H122" t="n">
-        <v>0.1647</v>
+        <v>0.1783</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2206</v>
+        <v>0.2414</v>
       </c>
       <c r="J122" t="n">
-        <v>0.7234</v>
+        <v>0.6956</v>
       </c>
       <c r="K122" t="n">
-        <v>0.8353</v>
+        <v>0.8217</v>
       </c>
       <c r="L122" t="n">
-        <v>0.7794</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="M122" t="n">
         <v>164</v>
@@ -7107,19 +7107,19 @@
         <v>0.6153999999999999</v>
       </c>
       <c r="H124" t="n">
-        <v>0.4985</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="I124" t="n">
-        <v>0.5569</v>
+        <v>0.5579</v>
       </c>
       <c r="J124" t="n">
         <v>0.3846</v>
       </c>
       <c r="K124" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.4995</v>
       </c>
       <c r="L124" t="n">
-        <v>0.4431</v>
+        <v>0.4421</v>
       </c>
       <c r="M124" t="n">
         <v>164</v>
@@ -7323,19 +7323,19 @@
         <v>0.7249</v>
       </c>
       <c r="H128" t="n">
-        <v>0.5667</v>
+        <v>0.5687</v>
       </c>
       <c r="I128" t="n">
-        <v>0.6458</v>
+        <v>0.6468</v>
       </c>
       <c r="J128" t="n">
         <v>0.2751</v>
       </c>
       <c r="K128" t="n">
-        <v>0.4333</v>
+        <v>0.4313</v>
       </c>
       <c r="L128" t="n">
-        <v>0.3542</v>
+        <v>0.3532</v>
       </c>
       <c r="M128" t="n">
         <v>164</v>
@@ -7590,22 +7590,22 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.6665</v>
       </c>
       <c r="H133" t="n">
-        <v>0.5178</v>
+        <v>0.5067</v>
       </c>
       <c r="I133" t="n">
-        <v>0.5958</v>
+        <v>0.5866</v>
       </c>
       <c r="J133" t="n">
-        <v>0.3261</v>
+        <v>0.3335</v>
       </c>
       <c r="K133" t="n">
-        <v>0.4822</v>
+        <v>0.4933</v>
       </c>
       <c r="L133" t="n">
-        <v>0.4042</v>
+        <v>0.4134</v>
       </c>
       <c r="M133" t="n">
         <v>164</v>
@@ -7809,19 +7809,19 @@
         <v>0.2437</v>
       </c>
       <c r="H137" t="n">
-        <v>0.1404</v>
+        <v>0.1366</v>
       </c>
       <c r="I137" t="n">
-        <v>0.192</v>
+        <v>0.1901</v>
       </c>
       <c r="J137" t="n">
         <v>0.7563</v>
       </c>
       <c r="K137" t="n">
-        <v>0.8596</v>
+        <v>0.8633999999999999</v>
       </c>
       <c r="L137" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8099</v>
       </c>
       <c r="M137" t="n">
         <v>164</v>
@@ -7863,19 +7863,19 @@
         <v>0.4194</v>
       </c>
       <c r="H138" t="n">
-        <v>0.2565</v>
+        <v>0.2534</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3379</v>
+        <v>0.3364</v>
       </c>
       <c r="J138" t="n">
         <v>0.5806</v>
       </c>
       <c r="K138" t="n">
-        <v>0.7435</v>
+        <v>0.7466</v>
       </c>
       <c r="L138" t="n">
-        <v>0.6621</v>
+        <v>0.6636</v>
       </c>
       <c r="M138" t="n">
         <v>164</v>
@@ -7914,22 +7914,22 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>0.2779</v>
+        <v>0.2761</v>
       </c>
       <c r="H139" t="n">
-        <v>0.1665</v>
+        <v>0.1653</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2222</v>
+        <v>0.2207</v>
       </c>
       <c r="J139" t="n">
-        <v>0.7221</v>
+        <v>0.7239</v>
       </c>
       <c r="K139" t="n">
-        <v>0.8335</v>
+        <v>0.8347</v>
       </c>
       <c r="L139" t="n">
-        <v>0.7778</v>
+        <v>0.7793</v>
       </c>
       <c r="M139" t="n">
         <v>164</v>
@@ -7968,22 +7968,22 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0.3184</v>
+        <v>0.3125</v>
       </c>
       <c r="H140" t="n">
-        <v>0.1819</v>
+        <v>0.1789</v>
       </c>
       <c r="I140" t="n">
-        <v>0.2502</v>
+        <v>0.2457</v>
       </c>
       <c r="J140" t="n">
-        <v>0.6816</v>
+        <v>0.6875</v>
       </c>
       <c r="K140" t="n">
-        <v>0.8181</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="L140" t="n">
-        <v>0.7498</v>
+        <v>0.7543</v>
       </c>
       <c r="M140" t="n">
         <v>164</v>
@@ -8025,19 +8025,19 @@
         <v>0.2558</v>
       </c>
       <c r="H141" t="n">
-        <v>0.1379</v>
+        <v>0.1355</v>
       </c>
       <c r="I141" t="n">
-        <v>0.1969</v>
+        <v>0.1957</v>
       </c>
       <c r="J141" t="n">
         <v>0.7442</v>
       </c>
       <c r="K141" t="n">
-        <v>0.8621</v>
+        <v>0.8645</v>
       </c>
       <c r="L141" t="n">
-        <v>0.8031</v>
+        <v>0.8043</v>
       </c>
       <c r="M141" t="n">
         <v>164</v>
@@ -8076,22 +8076,22 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>0.3546</v>
+        <v>0.3534</v>
       </c>
       <c r="H142" t="n">
         <v>0.2435</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2991</v>
+        <v>0.2984</v>
       </c>
       <c r="J142" t="n">
-        <v>0.6454</v>
+        <v>0.6466</v>
       </c>
       <c r="K142" t="n">
         <v>0.7565</v>
       </c>
       <c r="L142" t="n">
-        <v>0.7009</v>
+        <v>0.7016</v>
       </c>
       <c r="M142" t="n">
         <v>164</v>
@@ -8130,22 +8130,22 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>0.6243</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="H143" t="n">
-        <v>0.4491</v>
+        <v>0.4404</v>
       </c>
       <c r="I143" t="n">
-        <v>0.5367</v>
+        <v>0.5314</v>
       </c>
       <c r="J143" t="n">
-        <v>0.3757</v>
+        <v>0.3775</v>
       </c>
       <c r="K143" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.5596</v>
       </c>
       <c r="L143" t="n">
-        <v>0.4633</v>
+        <v>0.4686</v>
       </c>
       <c r="M143" t="n">
         <v>164</v>
@@ -8187,19 +8187,19 @@
         <v>0.2895</v>
       </c>
       <c r="H144" t="n">
-        <v>0.1719</v>
+        <v>0.1645</v>
       </c>
       <c r="I144" t="n">
-        <v>0.2307</v>
+        <v>0.227</v>
       </c>
       <c r="J144" t="n">
         <v>0.7105</v>
       </c>
       <c r="K144" t="n">
-        <v>0.8280999999999999</v>
+        <v>0.8355</v>
       </c>
       <c r="L144" t="n">
-        <v>0.7693</v>
+        <v>0.773</v>
       </c>
       <c r="M144" t="n">
         <v>164</v>
@@ -8238,22 +8238,22 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>0.6961000000000001</v>
+        <v>0.6925</v>
       </c>
       <c r="H145" t="n">
-        <v>0.5371</v>
+        <v>0.5324</v>
       </c>
       <c r="I145" t="n">
-        <v>0.6166</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J145" t="n">
-        <v>0.3039</v>
+        <v>0.3075</v>
       </c>
       <c r="K145" t="n">
-        <v>0.4629</v>
+        <v>0.4676</v>
       </c>
       <c r="L145" t="n">
-        <v>0.3834</v>
+        <v>0.3876</v>
       </c>
       <c r="M145" t="n">
         <v>164</v>
@@ -8292,22 +8292,22 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>0.2308</v>
+        <v>0.2494</v>
       </c>
       <c r="H146" t="n">
-        <v>0.1368</v>
+        <v>0.1514</v>
       </c>
       <c r="I146" t="n">
-        <v>0.1838</v>
+        <v>0.2004</v>
       </c>
       <c r="J146" t="n">
-        <v>0.7692</v>
+        <v>0.7506</v>
       </c>
       <c r="K146" t="n">
-        <v>0.8632</v>
+        <v>0.8486</v>
       </c>
       <c r="L146" t="n">
-        <v>0.8162</v>
+        <v>0.7996</v>
       </c>
       <c r="M146" t="n">
         <v>164</v>
@@ -8349,19 +8349,19 @@
         <v>0.4283</v>
       </c>
       <c r="H147" t="n">
-        <v>0.2714</v>
+        <v>0.2622</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3498</v>
+        <v>0.3452</v>
       </c>
       <c r="J147" t="n">
         <v>0.5717</v>
       </c>
       <c r="K147" t="n">
-        <v>0.7286</v>
+        <v>0.7378</v>
       </c>
       <c r="L147" t="n">
-        <v>0.6502</v>
+        <v>0.6548</v>
       </c>
       <c r="M147" t="n">
         <v>164</v>
@@ -8400,22 +8400,22 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>0.549</v>
+        <v>0.5383</v>
       </c>
       <c r="H148" t="n">
-        <v>0.454</v>
+        <v>0.4514</v>
       </c>
       <c r="I148" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.4948</v>
       </c>
       <c r="J148" t="n">
-        <v>0.451</v>
+        <v>0.4617</v>
       </c>
       <c r="K148" t="n">
-        <v>0.546</v>
+        <v>0.5486</v>
       </c>
       <c r="L148" t="n">
-        <v>0.4985</v>
+        <v>0.5052</v>
       </c>
       <c r="M148" t="n">
         <v>164</v>
@@ -8454,22 +8454,22 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>0.3501</v>
+        <v>0.351</v>
       </c>
       <c r="H149" t="n">
-        <v>0.2042</v>
+        <v>0.2027</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2772</v>
+        <v>0.2768</v>
       </c>
       <c r="J149" t="n">
-        <v>0.6499</v>
+        <v>0.649</v>
       </c>
       <c r="K149" t="n">
-        <v>0.7958</v>
+        <v>0.7973</v>
       </c>
       <c r="L149" t="n">
-        <v>0.7228</v>
+        <v>0.7232</v>
       </c>
       <c r="M149" t="n">
         <v>164</v>
@@ -8508,22 +8508,22 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0.3746</v>
+        <v>0.3702</v>
       </c>
       <c r="H150" t="n">
-        <v>0.207</v>
+        <v>0.2042</v>
       </c>
       <c r="I150" t="n">
-        <v>0.2908</v>
+        <v>0.2872</v>
       </c>
       <c r="J150" t="n">
-        <v>0.6254</v>
+        <v>0.6298</v>
       </c>
       <c r="K150" t="n">
-        <v>0.793</v>
+        <v>0.7958</v>
       </c>
       <c r="L150" t="n">
-        <v>0.7092000000000001</v>
+        <v>0.7128</v>
       </c>
       <c r="M150" t="n">
         <v>164</v>
@@ -8565,19 +8565,19 @@
         <v>0.4202</v>
       </c>
       <c r="H151" t="n">
-        <v>0.2702</v>
+        <v>0.2663</v>
       </c>
       <c r="I151" t="n">
-        <v>0.3452</v>
+        <v>0.3432</v>
       </c>
       <c r="J151" t="n">
         <v>0.5798</v>
       </c>
       <c r="K151" t="n">
-        <v>0.7298</v>
+        <v>0.7337</v>
       </c>
       <c r="L151" t="n">
-        <v>0.6548</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="M151" t="n">
         <v>164</v>
@@ -8670,22 +8670,22 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>0.2229</v>
+        <v>0.2142</v>
       </c>
       <c r="H153" t="n">
         <v>0.1325</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1777</v>
+        <v>0.1734</v>
       </c>
       <c r="J153" t="n">
-        <v>0.7771</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="K153" t="n">
         <v>0.8675</v>
       </c>
       <c r="L153" t="n">
-        <v>0.8223</v>
+        <v>0.8266</v>
       </c>
       <c r="M153" t="n">
         <v>164</v>
@@ -8724,22 +8724,22 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>0.2382</v>
+        <v>0.2355</v>
       </c>
       <c r="H154" t="n">
-        <v>0.1243</v>
+        <v>0.1238</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1812</v>
+        <v>0.1796</v>
       </c>
       <c r="J154" t="n">
-        <v>0.7618</v>
+        <v>0.7645</v>
       </c>
       <c r="K154" t="n">
-        <v>0.8757</v>
+        <v>0.8762</v>
       </c>
       <c r="L154" t="n">
-        <v>0.8188</v>
+        <v>0.8204</v>
       </c>
       <c r="M154" t="n">
         <v>164</v>
@@ -8778,22 +8778,22 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>0.3336</v>
+        <v>0.3254</v>
       </c>
       <c r="H155" t="n">
-        <v>0.1928</v>
+        <v>0.1906</v>
       </c>
       <c r="I155" t="n">
-        <v>0.2632</v>
+        <v>0.258</v>
       </c>
       <c r="J155" t="n">
-        <v>0.6664</v>
+        <v>0.6746</v>
       </c>
       <c r="K155" t="n">
-        <v>0.8072</v>
+        <v>0.8094</v>
       </c>
       <c r="L155" t="n">
-        <v>0.7368</v>
+        <v>0.742</v>
       </c>
       <c r="M155" t="n">
         <v>164</v>
@@ -8832,22 +8832,22 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>0.6196</v>
+        <v>0.6028</v>
       </c>
       <c r="H156" t="n">
-        <v>0.5008</v>
+        <v>0.4991</v>
       </c>
       <c r="I156" t="n">
-        <v>0.5602</v>
+        <v>0.551</v>
       </c>
       <c r="J156" t="n">
-        <v>0.3804</v>
+        <v>0.3972</v>
       </c>
       <c r="K156" t="n">
-        <v>0.4992</v>
+        <v>0.5009</v>
       </c>
       <c r="L156" t="n">
-        <v>0.4398</v>
+        <v>0.449</v>
       </c>
       <c r="M156" t="n">
         <v>164</v>
@@ -8886,22 +8886,22 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>0.6217</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="H157" t="n">
-        <v>0.4736</v>
+        <v>0.4716</v>
       </c>
       <c r="I157" t="n">
-        <v>0.5476</v>
+        <v>0.537</v>
       </c>
       <c r="J157" t="n">
-        <v>0.3783</v>
+        <v>0.3977</v>
       </c>
       <c r="K157" t="n">
-        <v>0.5264</v>
+        <v>0.5284</v>
       </c>
       <c r="L157" t="n">
-        <v>0.4524</v>
+        <v>0.463</v>
       </c>
       <c r="M157" t="n">
         <v>164</v>
@@ -8940,22 +8940,22 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>0.7035</v>
+        <v>0.6935</v>
       </c>
       <c r="H158" t="n">
         <v>0.5595</v>
       </c>
       <c r="I158" t="n">
-        <v>0.6315</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="J158" t="n">
-        <v>0.2965</v>
+        <v>0.3065</v>
       </c>
       <c r="K158" t="n">
         <v>0.4405</v>
       </c>
       <c r="L158" t="n">
-        <v>0.3685</v>
+        <v>0.3735</v>
       </c>
       <c r="M158" t="n">
         <v>164</v>
@@ -8994,22 +8994,22 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>0.2899</v>
+        <v>0.2828</v>
       </c>
       <c r="H159" t="n">
-        <v>0.1815</v>
+        <v>0.177</v>
       </c>
       <c r="I159" t="n">
-        <v>0.2357</v>
+        <v>0.2299</v>
       </c>
       <c r="J159" t="n">
-        <v>0.7101</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="K159" t="n">
-        <v>0.8185</v>
+        <v>0.823</v>
       </c>
       <c r="L159" t="n">
-        <v>0.7643</v>
+        <v>0.7701</v>
       </c>
       <c r="M159" t="n">
         <v>164</v>
@@ -9048,22 +9048,22 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>0.2992</v>
+        <v>0.2977</v>
       </c>
       <c r="H160" t="n">
-        <v>0.1688</v>
+        <v>0.163</v>
       </c>
       <c r="I160" t="n">
-        <v>0.234</v>
+        <v>0.2304</v>
       </c>
       <c r="J160" t="n">
-        <v>0.7008</v>
+        <v>0.7023</v>
       </c>
       <c r="K160" t="n">
-        <v>0.8312</v>
+        <v>0.837</v>
       </c>
       <c r="L160" t="n">
-        <v>0.766</v>
+        <v>0.7696</v>
       </c>
       <c r="M160" t="n">
         <v>164</v>
@@ -9105,19 +9105,19 @@
         <v>0.7986</v>
       </c>
       <c r="H161" t="n">
-        <v>0.6411</v>
+        <v>0.6456</v>
       </c>
       <c r="I161" t="n">
-        <v>0.7198</v>
+        <v>0.7221</v>
       </c>
       <c r="J161" t="n">
         <v>0.2014</v>
       </c>
       <c r="K161" t="n">
-        <v>0.3589</v>
+        <v>0.3544</v>
       </c>
       <c r="L161" t="n">
-        <v>0.2802</v>
+        <v>0.2779</v>
       </c>
       <c r="M161" t="n">
         <v>164</v>
@@ -9210,22 +9210,22 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>0.7002</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="H163" t="n">
         <v>0.5542</v>
       </c>
       <c r="I163" t="n">
-        <v>0.6272</v>
+        <v>0.6292</v>
       </c>
       <c r="J163" t="n">
-        <v>0.2998</v>
+        <v>0.2959</v>
       </c>
       <c r="K163" t="n">
         <v>0.4458</v>
       </c>
       <c r="L163" t="n">
-        <v>0.3728</v>
+        <v>0.3708</v>
       </c>
       <c r="M163" t="n">
         <v>164</v>
@@ -9321,19 +9321,19 @@
         <v>0.7758</v>
       </c>
       <c r="H165" t="n">
-        <v>0.6008</v>
+        <v>0.6039</v>
       </c>
       <c r="I165" t="n">
-        <v>0.6883</v>
+        <v>0.6899</v>
       </c>
       <c r="J165" t="n">
         <v>0.2242</v>
       </c>
       <c r="K165" t="n">
-        <v>0.3992</v>
+        <v>0.3961</v>
       </c>
       <c r="L165" t="n">
-        <v>0.3117</v>
+        <v>0.3101</v>
       </c>
       <c r="M165" t="n">
         <v>164</v>
@@ -9534,22 +9534,22 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>0.5767</v>
+        <v>0.6166</v>
       </c>
       <c r="H169" t="n">
-        <v>0.4404</v>
+        <v>0.454</v>
       </c>
       <c r="I169" t="n">
-        <v>0.5086000000000001</v>
+        <v>0.5353</v>
       </c>
       <c r="J169" t="n">
-        <v>0.4233</v>
+        <v>0.3834</v>
       </c>
       <c r="K169" t="n">
-        <v>0.5596</v>
+        <v>0.546</v>
       </c>
       <c r="L169" t="n">
-        <v>0.4914</v>
+        <v>0.4647</v>
       </c>
       <c r="M169" t="n">
         <v>164</v>
@@ -9591,19 +9591,19 @@
         <v>0.7996</v>
       </c>
       <c r="H170" t="n">
-        <v>0.6472</v>
+        <v>0.6494</v>
       </c>
       <c r="I170" t="n">
-        <v>0.7234</v>
+        <v>0.7245</v>
       </c>
       <c r="J170" t="n">
         <v>0.2004</v>
       </c>
       <c r="K170" t="n">
-        <v>0.3528</v>
+        <v>0.3506</v>
       </c>
       <c r="L170" t="n">
-        <v>0.2766</v>
+        <v>0.2755</v>
       </c>
       <c r="M170" t="n">
         <v>164</v>
@@ -9699,19 +9699,19 @@
         <v>0.7681</v>
       </c>
       <c r="H172" t="n">
-        <v>0.6122</v>
+        <v>0.6156</v>
       </c>
       <c r="I172" t="n">
-        <v>0.6902</v>
+        <v>0.6919</v>
       </c>
       <c r="J172" t="n">
         <v>0.2319</v>
       </c>
       <c r="K172" t="n">
-        <v>0.3878</v>
+        <v>0.3844</v>
       </c>
       <c r="L172" t="n">
-        <v>0.3098</v>
+        <v>0.3081</v>
       </c>
       <c r="M172" t="n">
         <v>164</v>
@@ -9750,22 +9750,22 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>0.7314000000000001</v>
+        <v>0.7325</v>
       </c>
       <c r="H173" t="n">
         <v>0.589</v>
       </c>
       <c r="I173" t="n">
-        <v>0.6602</v>
+        <v>0.6607</v>
       </c>
       <c r="J173" t="n">
-        <v>0.2686</v>
+        <v>0.2675</v>
       </c>
       <c r="K173" t="n">
         <v>0.411</v>
       </c>
       <c r="L173" t="n">
-        <v>0.3398</v>
+        <v>0.3393</v>
       </c>
       <c r="M173" t="n">
         <v>164</v>
@@ -9807,19 +9807,19 @@
         <v>0.7914</v>
       </c>
       <c r="H174" t="n">
-        <v>0.6251</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="I174" t="n">
-        <v>0.7083</v>
+        <v>0.71</v>
       </c>
       <c r="J174" t="n">
         <v>0.2086</v>
       </c>
       <c r="K174" t="n">
-        <v>0.3749</v>
+        <v>0.3715</v>
       </c>
       <c r="L174" t="n">
-        <v>0.2917</v>
+        <v>0.29</v>
       </c>
       <c r="M174" t="n">
         <v>164</v>
@@ -10077,19 +10077,19 @@
         <v>0.8771</v>
       </c>
       <c r="H179" t="n">
-        <v>0.7858000000000001</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="I179" t="n">
-        <v>0.8314</v>
+        <v>0.833</v>
       </c>
       <c r="J179" t="n">
         <v>0.1229</v>
       </c>
       <c r="K179" t="n">
-        <v>0.2142</v>
+        <v>0.2112</v>
       </c>
       <c r="L179" t="n">
-        <v>0.1686</v>
+        <v>0.167</v>
       </c>
       <c r="M179" t="n">
         <v>164</v>
@@ -10236,22 +10236,22 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0.6482</v>
+        <v>0.6499</v>
       </c>
       <c r="H182" t="n">
         <v>0.4997</v>
       </c>
       <c r="I182" t="n">
-        <v>0.574</v>
+        <v>0.5748</v>
       </c>
       <c r="J182" t="n">
-        <v>0.3518</v>
+        <v>0.3501</v>
       </c>
       <c r="K182" t="n">
         <v>0.5003</v>
       </c>
       <c r="L182" t="n">
-        <v>0.426</v>
+        <v>0.4252</v>
       </c>
       <c r="M182" t="n">
         <v>164</v>
@@ -10290,22 +10290,22 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>0.6532</v>
+        <v>0.6563</v>
       </c>
       <c r="H183" t="n">
         <v>0.5066000000000001</v>
       </c>
       <c r="I183" t="n">
-        <v>0.5799</v>
+        <v>0.5814</v>
       </c>
       <c r="J183" t="n">
-        <v>0.3468</v>
+        <v>0.3437</v>
       </c>
       <c r="K183" t="n">
         <v>0.4934</v>
       </c>
       <c r="L183" t="n">
-        <v>0.4201</v>
+        <v>0.4186</v>
       </c>
       <c r="M183" t="n">
         <v>164</v>
@@ -10344,22 +10344,22 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>0.4185</v>
+        <v>0.4139</v>
       </c>
       <c r="H184" t="n">
         <v>0.2481</v>
       </c>
       <c r="I184" t="n">
-        <v>0.3333</v>
+        <v>0.331</v>
       </c>
       <c r="J184" t="n">
-        <v>0.5815</v>
+        <v>0.5861</v>
       </c>
       <c r="K184" t="n">
         <v>0.7519</v>
       </c>
       <c r="L184" t="n">
-        <v>0.6667</v>
+        <v>0.669</v>
       </c>
       <c r="M184" t="n">
         <v>164</v>
@@ -10452,22 +10452,22 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>0.4111</v>
+        <v>0.4069</v>
       </c>
       <c r="H186" t="n">
         <v>0.2143</v>
       </c>
       <c r="I186" t="n">
-        <v>0.3127</v>
+        <v>0.3106</v>
       </c>
       <c r="J186" t="n">
-        <v>0.5889</v>
+        <v>0.5931</v>
       </c>
       <c r="K186" t="n">
         <v>0.7857</v>
       </c>
       <c r="L186" t="n">
-        <v>0.6873</v>
+        <v>0.6894</v>
       </c>
       <c r="M186" t="n">
         <v>164</v>
@@ -10560,22 +10560,22 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>0.7317</v>
+        <v>0.7345</v>
       </c>
       <c r="H188" t="n">
-        <v>0.6171</v>
+        <v>0.6203</v>
       </c>
       <c r="I188" t="n">
-        <v>0.6744</v>
+        <v>0.6774</v>
       </c>
       <c r="J188" t="n">
-        <v>0.2683</v>
+        <v>0.2655</v>
       </c>
       <c r="K188" t="n">
-        <v>0.3829</v>
+        <v>0.3797</v>
       </c>
       <c r="L188" t="n">
-        <v>0.3256</v>
+        <v>0.3226</v>
       </c>
       <c r="M188" t="n">
         <v>164</v>
@@ -10614,22 +10614,22 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>0.4014</v>
+        <v>0.4015</v>
       </c>
       <c r="H189" t="n">
         <v>0.2544</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3279</v>
+        <v>0.328</v>
       </c>
       <c r="J189" t="n">
-        <v>0.5986</v>
+        <v>0.5985</v>
       </c>
       <c r="K189" t="n">
         <v>0.7456</v>
       </c>
       <c r="L189" t="n">
-        <v>0.6721</v>
+        <v>0.672</v>
       </c>
       <c r="M189" t="n">
         <v>164</v>
@@ -10722,22 +10722,22 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>0.35</v>
+        <v>0.3695</v>
       </c>
       <c r="H191" t="n">
-        <v>0.1974</v>
+        <v>0.2128</v>
       </c>
       <c r="I191" t="n">
-        <v>0.2737</v>
+        <v>0.2912</v>
       </c>
       <c r="J191" t="n">
-        <v>0.65</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="K191" t="n">
-        <v>0.8026</v>
+        <v>0.7872</v>
       </c>
       <c r="L191" t="n">
-        <v>0.7262999999999999</v>
+        <v>0.7088</v>
       </c>
       <c r="M191" t="n">
         <v>164</v>
@@ -11046,22 +11046,22 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>0.7764</v>
+        <v>0.7771</v>
       </c>
       <c r="H197" t="n">
         <v>0.6870000000000001</v>
       </c>
       <c r="I197" t="n">
-        <v>0.7317</v>
+        <v>0.7321</v>
       </c>
       <c r="J197" t="n">
-        <v>0.2236</v>
+        <v>0.2229</v>
       </c>
       <c r="K197" t="n">
         <v>0.313</v>
       </c>
       <c r="L197" t="n">
-        <v>0.2683</v>
+        <v>0.2679</v>
       </c>
       <c r="M197" t="n">
         <v>164</v>
@@ -11208,22 +11208,22 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>0.4796</v>
+        <v>0.4719</v>
       </c>
       <c r="H200" t="n">
         <v>0.3384</v>
       </c>
       <c r="I200" t="n">
-        <v>0.409</v>
+        <v>0.4052</v>
       </c>
       <c r="J200" t="n">
-        <v>0.5204</v>
+        <v>0.5281</v>
       </c>
       <c r="K200" t="n">
         <v>0.6616</v>
       </c>
       <c r="L200" t="n">
-        <v>0.591</v>
+        <v>0.5948</v>
       </c>
       <c r="M200" t="n">
         <v>164</v>
@@ -11316,22 +11316,22 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>0.7604</v>
+        <v>0.7543</v>
       </c>
       <c r="H202" t="n">
-        <v>0.6171</v>
+        <v>0.6109</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6888</v>
+        <v>0.6826</v>
       </c>
       <c r="J202" t="n">
-        <v>0.2396</v>
+        <v>0.2457</v>
       </c>
       <c r="K202" t="n">
-        <v>0.3829</v>
+        <v>0.3891</v>
       </c>
       <c r="L202" t="n">
-        <v>0.3112</v>
+        <v>0.3174</v>
       </c>
       <c r="M202" t="n">
         <v>164</v>
@@ -11370,22 +11370,22 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>0.8216</v>
+        <v>0.8235</v>
       </c>
       <c r="H203" t="n">
         <v>0.697</v>
       </c>
       <c r="I203" t="n">
-        <v>0.7593</v>
+        <v>0.7602</v>
       </c>
       <c r="J203" t="n">
-        <v>0.1784</v>
+        <v>0.1765</v>
       </c>
       <c r="K203" t="n">
         <v>0.303</v>
       </c>
       <c r="L203" t="n">
-        <v>0.2407</v>
+        <v>0.2398</v>
       </c>
       <c r="M203" t="n">
         <v>164</v>
@@ -11802,22 +11802,22 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>0.8655</v>
+        <v>0.8678</v>
       </c>
       <c r="H211" t="n">
         <v>0.7796</v>
       </c>
       <c r="I211" t="n">
-        <v>0.8226</v>
+        <v>0.8237</v>
       </c>
       <c r="J211" t="n">
-        <v>0.1345</v>
+        <v>0.1322</v>
       </c>
       <c r="K211" t="n">
         <v>0.2204</v>
       </c>
       <c r="L211" t="n">
-        <v>0.1774</v>
+        <v>0.1763</v>
       </c>
       <c r="M211" t="n">
         <v>164</v>
@@ -11856,22 +11856,22 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>0.4897</v>
+        <v>0.5125</v>
       </c>
       <c r="H212" t="n">
-        <v>0.3706</v>
+        <v>0.419</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4302</v>
+        <v>0.4658</v>
       </c>
       <c r="J212" t="n">
-        <v>0.5103</v>
+        <v>0.4875</v>
       </c>
       <c r="K212" t="n">
-        <v>0.6294</v>
+        <v>0.581</v>
       </c>
       <c r="L212" t="n">
-        <v>0.5698</v>
+        <v>0.5342</v>
       </c>
       <c r="M212" t="n">
         <v>164</v>
@@ -12018,22 +12018,22 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>0.6513</v>
+        <v>0.6536</v>
       </c>
       <c r="H215" t="n">
         <v>0.5272</v>
       </c>
       <c r="I215" t="n">
-        <v>0.5893</v>
+        <v>0.5904</v>
       </c>
       <c r="J215" t="n">
-        <v>0.3487</v>
+        <v>0.3464</v>
       </c>
       <c r="K215" t="n">
         <v>0.4728</v>
       </c>
       <c r="L215" t="n">
-        <v>0.4107</v>
+        <v>0.4096</v>
       </c>
       <c r="M215" t="n">
         <v>164</v>
@@ -12129,19 +12129,19 @@
         <v>0.748</v>
       </c>
       <c r="H217" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5625</v>
       </c>
       <c r="I217" t="n">
-        <v>0.6545</v>
+        <v>0.6552</v>
       </c>
       <c r="J217" t="n">
         <v>0.252</v>
       </c>
       <c r="K217" t="n">
-        <v>0.439</v>
+        <v>0.4375</v>
       </c>
       <c r="L217" t="n">
-        <v>0.3455</v>
+        <v>0.3448</v>
       </c>
       <c r="M217" t="n">
         <v>164</v>
@@ -12183,19 +12183,19 @@
         <v>0.8579</v>
       </c>
       <c r="H218" t="n">
-        <v>0.7578</v>
+        <v>0.7624</v>
       </c>
       <c r="I218" t="n">
-        <v>0.8078</v>
+        <v>0.8101</v>
       </c>
       <c r="J218" t="n">
         <v>0.1421</v>
       </c>
       <c r="K218" t="n">
-        <v>0.2422</v>
+        <v>0.2376</v>
       </c>
       <c r="L218" t="n">
-        <v>0.1922</v>
+        <v>0.1899</v>
       </c>
       <c r="M218" t="n">
         <v>164</v>
@@ -12291,19 +12291,19 @@
         <v>0.3807</v>
       </c>
       <c r="H220" t="n">
-        <v>0.2491</v>
+        <v>0.248</v>
       </c>
       <c r="I220" t="n">
-        <v>0.3149</v>
+        <v>0.3144</v>
       </c>
       <c r="J220" t="n">
         <v>0.6193</v>
       </c>
       <c r="K220" t="n">
-        <v>0.7509</v>
+        <v>0.752</v>
       </c>
       <c r="L220" t="n">
-        <v>0.6851</v>
+        <v>0.6856</v>
       </c>
       <c r="M220" t="n">
         <v>164</v>
@@ -12396,22 +12396,22 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>0.858</v>
+        <v>0.8608</v>
       </c>
       <c r="H222" t="n">
         <v>0.7388</v>
       </c>
       <c r="I222" t="n">
-        <v>0.7984</v>
+        <v>0.7998</v>
       </c>
       <c r="J222" t="n">
-        <v>0.142</v>
+        <v>0.1392</v>
       </c>
       <c r="K222" t="n">
         <v>0.2612</v>
       </c>
       <c r="L222" t="n">
-        <v>0.2016</v>
+        <v>0.2002</v>
       </c>
       <c r="M222" t="n">
         <v>164</v>
@@ -12450,22 +12450,22 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>0.8653</v>
+        <v>0.863</v>
       </c>
       <c r="H223" t="n">
         <v>0.7209</v>
       </c>
       <c r="I223" t="n">
-        <v>0.7931</v>
+        <v>0.7919</v>
       </c>
       <c r="J223" t="n">
-        <v>0.1347</v>
+        <v>0.137</v>
       </c>
       <c r="K223" t="n">
         <v>0.2791</v>
       </c>
       <c r="L223" t="n">
-        <v>0.2069</v>
+        <v>0.2081</v>
       </c>
       <c r="M223" t="n">
         <v>164</v>
@@ -12507,19 +12507,19 @@
         <v>0.8754999999999999</v>
       </c>
       <c r="H224" t="n">
-        <v>0.7599</v>
+        <v>0.764</v>
       </c>
       <c r="I224" t="n">
-        <v>0.8177</v>
+        <v>0.8198</v>
       </c>
       <c r="J224" t="n">
         <v>0.1245</v>
       </c>
       <c r="K224" t="n">
-        <v>0.2401</v>
+        <v>0.236</v>
       </c>
       <c r="L224" t="n">
-        <v>0.1823</v>
+        <v>0.1802</v>
       </c>
       <c r="M224" t="n">
         <v>164</v>
@@ -12669,19 +12669,19 @@
         <v>0.472</v>
       </c>
       <c r="H227" t="n">
-        <v>0.3501</v>
+        <v>0.344</v>
       </c>
       <c r="I227" t="n">
-        <v>0.411</v>
+        <v>0.408</v>
       </c>
       <c r="J227" t="n">
         <v>0.528</v>
       </c>
       <c r="K227" t="n">
-        <v>0.6499</v>
+        <v>0.656</v>
       </c>
       <c r="L227" t="n">
-        <v>0.589</v>
+        <v>0.592</v>
       </c>
       <c r="M227" t="n">
         <v>164</v>
@@ -12936,22 +12936,22 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>0.4515</v>
+        <v>0.4616</v>
       </c>
       <c r="H232" t="n">
-        <v>0.3152</v>
+        <v>0.3632</v>
       </c>
       <c r="I232" t="n">
-        <v>0.3833</v>
+        <v>0.4124</v>
       </c>
       <c r="J232" t="n">
-        <v>0.5485</v>
+        <v>0.5384</v>
       </c>
       <c r="K232" t="n">
-        <v>0.6848</v>
+        <v>0.6368</v>
       </c>
       <c r="L232" t="n">
-        <v>0.6167</v>
+        <v>0.5876</v>
       </c>
       <c r="M232" t="n">
         <v>164</v>
@@ -13047,19 +13047,19 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="H234" t="n">
-        <v>0.6863</v>
+        <v>0.6886</v>
       </c>
       <c r="I234" t="n">
-        <v>0.7482</v>
+        <v>0.7493</v>
       </c>
       <c r="J234" t="n">
         <v>0.19</v>
       </c>
       <c r="K234" t="n">
-        <v>0.3137</v>
+        <v>0.3114</v>
       </c>
       <c r="L234" t="n">
-        <v>0.2518</v>
+        <v>0.2507</v>
       </c>
       <c r="M234" t="n">
         <v>164</v>
@@ -13260,22 +13260,22 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.8498</v>
       </c>
       <c r="H238" t="n">
-        <v>0.7255</v>
+        <v>0.7282</v>
       </c>
       <c r="I238" t="n">
-        <v>0.7864</v>
+        <v>0.789</v>
       </c>
       <c r="J238" t="n">
-        <v>0.1527</v>
+        <v>0.1502</v>
       </c>
       <c r="K238" t="n">
-        <v>0.2745</v>
+        <v>0.2718</v>
       </c>
       <c r="L238" t="n">
-        <v>0.2136</v>
+        <v>0.211</v>
       </c>
       <c r="M238" t="n">
         <v>164</v>
@@ -13317,19 +13317,19 @@
         <v>0.396</v>
       </c>
       <c r="H239" t="n">
-        <v>0.2363</v>
+        <v>0.2318</v>
       </c>
       <c r="I239" t="n">
-        <v>0.3162</v>
+        <v>0.3139</v>
       </c>
       <c r="J239" t="n">
         <v>0.604</v>
       </c>
       <c r="K239" t="n">
-        <v>0.7637</v>
+        <v>0.7682</v>
       </c>
       <c r="L239" t="n">
-        <v>0.6838</v>
+        <v>0.6861</v>
       </c>
       <c r="M239" t="n">
         <v>164</v>
@@ -13479,19 +13479,19 @@
         <v>0.8351</v>
       </c>
       <c r="H242" t="n">
-        <v>0.7044</v>
+        <v>0.7068</v>
       </c>
       <c r="I242" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.771</v>
       </c>
       <c r="J242" t="n">
         <v>0.1649</v>
       </c>
       <c r="K242" t="n">
-        <v>0.2956</v>
+        <v>0.2932</v>
       </c>
       <c r="L242" t="n">
-        <v>0.2303</v>
+        <v>0.229</v>
       </c>
       <c r="M242" t="n">
         <v>164</v>
@@ -13530,22 +13530,22 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>0.8522999999999999</v>
+        <v>0.8431999999999999</v>
       </c>
       <c r="H243" t="n">
         <v>0.672</v>
       </c>
       <c r="I243" t="n">
-        <v>0.7622</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="J243" t="n">
-        <v>0.1477</v>
+        <v>0.1568</v>
       </c>
       <c r="K243" t="n">
         <v>0.328</v>
       </c>
       <c r="L243" t="n">
-        <v>0.2378</v>
+        <v>0.2424</v>
       </c>
       <c r="M243" t="n">
         <v>164</v>
@@ -13587,19 +13587,19 @@
         <v>0.8811</v>
       </c>
       <c r="H244" t="n">
-        <v>0.7533</v>
+        <v>0.756</v>
       </c>
       <c r="I244" t="n">
-        <v>0.8172</v>
+        <v>0.8186</v>
       </c>
       <c r="J244" t="n">
         <v>0.1189</v>
       </c>
       <c r="K244" t="n">
-        <v>0.2467</v>
+        <v>0.244</v>
       </c>
       <c r="L244" t="n">
-        <v>0.1828</v>
+        <v>0.1814</v>
       </c>
       <c r="M244" t="n">
         <v>164</v>
@@ -13749,19 +13749,19 @@
         <v>0.7625999999999999</v>
       </c>
       <c r="H247" t="n">
-        <v>0.569</v>
+        <v>0.5714</v>
       </c>
       <c r="I247" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.667</v>
       </c>
       <c r="J247" t="n">
         <v>0.2374</v>
       </c>
       <c r="K247" t="n">
-        <v>0.431</v>
+        <v>0.4286</v>
       </c>
       <c r="L247" t="n">
-        <v>0.3342</v>
+        <v>0.333</v>
       </c>
       <c r="M247" t="n">
         <v>164</v>
@@ -13854,22 +13854,22 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.6165</v>
       </c>
       <c r="H249" t="n">
         <v>0.4756</v>
       </c>
       <c r="I249" t="n">
-        <v>0.543</v>
+        <v>0.546</v>
       </c>
       <c r="J249" t="n">
-        <v>0.3896</v>
+        <v>0.3835</v>
       </c>
       <c r="K249" t="n">
         <v>0.5244</v>
       </c>
       <c r="L249" t="n">
-        <v>0.457</v>
+        <v>0.454</v>
       </c>
       <c r="M249" t="n">
         <v>164</v>
@@ -13962,22 +13962,22 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>0.5555</v>
+        <v>0.5975</v>
       </c>
       <c r="H251" t="n">
-        <v>0.396</v>
+        <v>0.4306</v>
       </c>
       <c r="I251" t="n">
-        <v>0.4758</v>
+        <v>0.514</v>
       </c>
       <c r="J251" t="n">
-        <v>0.4445</v>
+        <v>0.4025</v>
       </c>
       <c r="K251" t="n">
-        <v>0.604</v>
+        <v>0.5694</v>
       </c>
       <c r="L251" t="n">
-        <v>0.5242</v>
+        <v>0.486</v>
       </c>
       <c r="M251" t="n">
         <v>164</v>
@@ -14073,19 +14073,19 @@
         <v>0.8505</v>
       </c>
       <c r="H253" t="n">
-        <v>0.7444</v>
+        <v>0.7547</v>
       </c>
       <c r="I253" t="n">
-        <v>0.7974</v>
+        <v>0.8026</v>
       </c>
       <c r="J253" t="n">
         <v>0.1495</v>
       </c>
       <c r="K253" t="n">
-        <v>0.2556</v>
+        <v>0.2453</v>
       </c>
       <c r="L253" t="n">
-        <v>0.2026</v>
+        <v>0.1974</v>
       </c>
       <c r="M253" t="n">
         <v>164</v>
@@ -14178,22 +14178,22 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>0.716</v>
+        <v>0.7176</v>
       </c>
       <c r="H255" t="n">
         <v>0.5521</v>
       </c>
       <c r="I255" t="n">
-        <v>0.634</v>
+        <v>0.6348</v>
       </c>
       <c r="J255" t="n">
-        <v>0.284</v>
+        <v>0.2824</v>
       </c>
       <c r="K255" t="n">
         <v>0.4479</v>
       </c>
       <c r="L255" t="n">
-        <v>0.366</v>
+        <v>0.3652</v>
       </c>
       <c r="M255" t="n">
         <v>164</v>
@@ -14232,22 +14232,22 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>0.7652</v>
+        <v>0.7716</v>
       </c>
       <c r="H256" t="n">
         <v>0.5966</v>
       </c>
       <c r="I256" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.6841</v>
       </c>
       <c r="J256" t="n">
-        <v>0.2348</v>
+        <v>0.2284</v>
       </c>
       <c r="K256" t="n">
         <v>0.4034</v>
       </c>
       <c r="L256" t="n">
-        <v>0.3191</v>
+        <v>0.3159</v>
       </c>
       <c r="M256" t="n">
         <v>164</v>
@@ -14451,19 +14451,19 @@
         <v>0.7111</v>
       </c>
       <c r="H260" t="n">
-        <v>0.5556</v>
+        <v>0.5604</v>
       </c>
       <c r="I260" t="n">
-        <v>0.6334</v>
+        <v>0.6358</v>
       </c>
       <c r="J260" t="n">
         <v>0.2889</v>
       </c>
       <c r="K260" t="n">
-        <v>0.4444</v>
+        <v>0.4396</v>
       </c>
       <c r="L260" t="n">
-        <v>0.3666</v>
+        <v>0.3642</v>
       </c>
       <c r="M260" t="n">
         <v>164</v>
@@ -14667,19 +14667,19 @@
         <v>0.6179</v>
       </c>
       <c r="H264" t="n">
-        <v>0.4643</v>
+        <v>0.4703</v>
       </c>
       <c r="I264" t="n">
-        <v>0.5411</v>
+        <v>0.5441</v>
       </c>
       <c r="J264" t="n">
         <v>0.3821</v>
       </c>
       <c r="K264" t="n">
-        <v>0.5357</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="L264" t="n">
-        <v>0.4589</v>
+        <v>0.4559</v>
       </c>
       <c r="M264" t="n">
         <v>164</v>
@@ -14718,22 +14718,22 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>0.6238</v>
+        <v>0.6252</v>
       </c>
       <c r="H265" t="n">
         <v>0.4942</v>
       </c>
       <c r="I265" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5597</v>
       </c>
       <c r="J265" t="n">
-        <v>0.3762</v>
+        <v>0.3748</v>
       </c>
       <c r="K265" t="n">
         <v>0.5058</v>
       </c>
       <c r="L265" t="n">
-        <v>0.441</v>
+        <v>0.4403</v>
       </c>
       <c r="M265" t="n">
         <v>164</v>
@@ -14829,19 +14829,19 @@
         <v>0.4252</v>
       </c>
       <c r="H267" t="n">
-        <v>0.3073</v>
+        <v>0.3018</v>
       </c>
       <c r="I267" t="n">
-        <v>0.3662</v>
+        <v>0.3635</v>
       </c>
       <c r="J267" t="n">
         <v>0.5748</v>
       </c>
       <c r="K267" t="n">
-        <v>0.6927</v>
+        <v>0.6982</v>
       </c>
       <c r="L267" t="n">
-        <v>0.6338</v>
+        <v>0.6365</v>
       </c>
       <c r="M267" t="n">
         <v>164</v>
@@ -14934,22 +14934,22 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>0.3962</v>
+        <v>0.4194</v>
       </c>
       <c r="H269" t="n">
-        <v>0.2219</v>
+        <v>0.2433</v>
       </c>
       <c r="I269" t="n">
-        <v>0.309</v>
+        <v>0.3314</v>
       </c>
       <c r="J269" t="n">
-        <v>0.6038</v>
+        <v>0.5806</v>
       </c>
       <c r="K269" t="n">
-        <v>0.7781</v>
+        <v>0.7567</v>
       </c>
       <c r="L269" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6686</v>
       </c>
       <c r="M269" t="n">
         <v>164</v>
@@ -15096,22 +15096,22 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>0.5589</v>
+        <v>0.5538</v>
       </c>
       <c r="H272" t="n">
         <v>0.401</v>
       </c>
       <c r="I272" t="n">
-        <v>0.48</v>
+        <v>0.4774</v>
       </c>
       <c r="J272" t="n">
-        <v>0.4411</v>
+        <v>0.4462</v>
       </c>
       <c r="K272" t="n">
         <v>0.599</v>
       </c>
       <c r="L272" t="n">
-        <v>0.52</v>
+        <v>0.5226</v>
       </c>
       <c r="M272" t="n">
         <v>164</v>
@@ -15258,22 +15258,22 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>0.8159</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="H275" t="n">
         <v>0.6731</v>
       </c>
       <c r="I275" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.745</v>
       </c>
       <c r="J275" t="n">
-        <v>0.1841</v>
+        <v>0.183</v>
       </c>
       <c r="K275" t="n">
         <v>0.3269</v>
       </c>
       <c r="L275" t="n">
-        <v>0.2555</v>
+        <v>0.255</v>
       </c>
       <c r="M275" t="n">
         <v>164</v>
@@ -15369,19 +15369,19 @@
         <v>0.3215</v>
       </c>
       <c r="H277" t="n">
-        <v>0.1675</v>
+        <v>0.1651</v>
       </c>
       <c r="I277" t="n">
-        <v>0.2445</v>
+        <v>0.2433</v>
       </c>
       <c r="J277" t="n">
         <v>0.6785</v>
       </c>
       <c r="K277" t="n">
-        <v>0.8325</v>
+        <v>0.8349</v>
       </c>
       <c r="L277" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.7567</v>
       </c>
       <c r="M277" t="n">
         <v>164</v>
@@ -15474,22 +15474,22 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>0.7809</v>
+        <v>0.7816</v>
       </c>
       <c r="H279" t="n">
         <v>0.6748</v>
       </c>
       <c r="I279" t="n">
-        <v>0.7278</v>
+        <v>0.7282</v>
       </c>
       <c r="J279" t="n">
-        <v>0.2191</v>
+        <v>0.2184</v>
       </c>
       <c r="K279" t="n">
         <v>0.3252</v>
       </c>
       <c r="L279" t="n">
-        <v>0.2722</v>
+        <v>0.2718</v>
       </c>
       <c r="M279" t="n">
         <v>164</v>
@@ -15528,22 +15528,22 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.7935</v>
       </c>
       <c r="H280" t="n">
-        <v>0.6594</v>
+        <v>0.6573</v>
       </c>
       <c r="I280" t="n">
-        <v>0.7276</v>
+        <v>0.7254</v>
       </c>
       <c r="J280" t="n">
-        <v>0.2041</v>
+        <v>0.2065</v>
       </c>
       <c r="K280" t="n">
-        <v>0.3406</v>
+        <v>0.3427</v>
       </c>
       <c r="L280" t="n">
-        <v>0.2724</v>
+        <v>0.2746</v>
       </c>
       <c r="M280" t="n">
         <v>164</v>
@@ -15582,22 +15582,22 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>0.8227</v>
+        <v>0.8239</v>
       </c>
       <c r="H281" t="n">
-        <v>0.7282</v>
+        <v>0.7314000000000001</v>
       </c>
       <c r="I281" t="n">
-        <v>0.7754</v>
+        <v>0.7776</v>
       </c>
       <c r="J281" t="n">
-        <v>0.1773</v>
+        <v>0.1761</v>
       </c>
       <c r="K281" t="n">
-        <v>0.2718</v>
+        <v>0.2686</v>
       </c>
       <c r="L281" t="n">
-        <v>0.2246</v>
+        <v>0.2224</v>
       </c>
       <c r="M281" t="n">
         <v>164</v>
@@ -15852,22 +15852,22 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>0.2269</v>
+        <v>0.2458</v>
       </c>
       <c r="H286" t="n">
-        <v>0.1362</v>
+        <v>0.1475</v>
       </c>
       <c r="I286" t="n">
-        <v>0.1816</v>
+        <v>0.1966</v>
       </c>
       <c r="J286" t="n">
-        <v>0.7731</v>
+        <v>0.7542</v>
       </c>
       <c r="K286" t="n">
-        <v>0.8638</v>
+        <v>0.8525</v>
       </c>
       <c r="L286" t="n">
-        <v>0.8184</v>
+        <v>0.8034</v>
       </c>
       <c r="M286" t="n">
         <v>164</v>
@@ -15906,22 +15906,22 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>0.4063</v>
+        <v>0.4032</v>
       </c>
       <c r="H287" t="n">
         <v>0.2732</v>
       </c>
       <c r="I287" t="n">
-        <v>0.3398</v>
+        <v>0.3382</v>
       </c>
       <c r="J287" t="n">
-        <v>0.5937</v>
+        <v>0.5968</v>
       </c>
       <c r="K287" t="n">
         <v>0.7268</v>
       </c>
       <c r="L287" t="n">
-        <v>0.6602</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="M287" t="n">
         <v>164</v>
@@ -16068,22 +16068,22 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>0.3617</v>
+        <v>0.359</v>
       </c>
       <c r="H290" t="n">
-        <v>0.2118</v>
+        <v>0.208</v>
       </c>
       <c r="I290" t="n">
-        <v>0.2868</v>
+        <v>0.2835</v>
       </c>
       <c r="J290" t="n">
-        <v>0.6383</v>
+        <v>0.641</v>
       </c>
       <c r="K290" t="n">
-        <v>0.7882</v>
+        <v>0.792</v>
       </c>
       <c r="L290" t="n">
-        <v>0.7131999999999999</v>
+        <v>0.7165</v>
       </c>
       <c r="M290" t="n">
         <v>164</v>
@@ -16125,19 +16125,19 @@
         <v>0.4107</v>
       </c>
       <c r="H291" t="n">
-        <v>0.2598</v>
+        <v>0.2555</v>
       </c>
       <c r="I291" t="n">
-        <v>0.3352</v>
+        <v>0.3331</v>
       </c>
       <c r="J291" t="n">
         <v>0.5893</v>
       </c>
       <c r="K291" t="n">
-        <v>0.7402</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="L291" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.6669</v>
       </c>
       <c r="M291" t="n">
         <v>164</v>
@@ -16395,19 +16395,19 @@
         <v>0.6088</v>
       </c>
       <c r="H296" t="n">
-        <v>0.4652</v>
+        <v>0.4621</v>
       </c>
       <c r="I296" t="n">
-        <v>0.537</v>
+        <v>0.5354</v>
       </c>
       <c r="J296" t="n">
         <v>0.3912</v>
       </c>
       <c r="K296" t="n">
-        <v>0.5348000000000001</v>
+        <v>0.5379</v>
       </c>
       <c r="L296" t="n">
-        <v>0.463</v>
+        <v>0.4646</v>
       </c>
       <c r="M296" t="n">
         <v>164</v>
@@ -16446,22 +16446,22 @@
         </is>
       </c>
       <c r="G297" t="n">
-        <v>0.5787</v>
+        <v>0.5708</v>
       </c>
       <c r="H297" t="n">
-        <v>0.4779</v>
+        <v>0.471</v>
       </c>
       <c r="I297" t="n">
-        <v>0.5283</v>
+        <v>0.5209</v>
       </c>
       <c r="J297" t="n">
-        <v>0.4213</v>
+        <v>0.4292</v>
       </c>
       <c r="K297" t="n">
-        <v>0.5221</v>
+        <v>0.529</v>
       </c>
       <c r="L297" t="n">
-        <v>0.4717</v>
+        <v>0.4791</v>
       </c>
       <c r="M297" t="n">
         <v>164</v>
@@ -16554,22 +16554,22 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>0.2713</v>
+        <v>0.2722</v>
       </c>
       <c r="H299" t="n">
         <v>0.1845</v>
       </c>
       <c r="I299" t="n">
-        <v>0.2279</v>
+        <v>0.2284</v>
       </c>
       <c r="J299" t="n">
-        <v>0.7287</v>
+        <v>0.7278</v>
       </c>
       <c r="K299" t="n">
         <v>0.8155</v>
       </c>
       <c r="L299" t="n">
-        <v>0.7721</v>
+        <v>0.7716</v>
       </c>
       <c r="M299" t="n">
         <v>164</v>
@@ -16611,19 +16611,19 @@
         <v>0.2887</v>
       </c>
       <c r="H300" t="n">
-        <v>0.1648</v>
+        <v>0.1616</v>
       </c>
       <c r="I300" t="n">
-        <v>0.2268</v>
+        <v>0.2252</v>
       </c>
       <c r="J300" t="n">
         <v>0.7113</v>
       </c>
       <c r="K300" t="n">
-        <v>0.8352000000000001</v>
+        <v>0.8384</v>
       </c>
       <c r="L300" t="n">
-        <v>0.7732</v>
+        <v>0.7748</v>
       </c>
       <c r="M300" t="n">
         <v>164</v>
@@ -16716,22 +16716,22 @@
         </is>
       </c>
       <c r="G302" t="n">
-        <v>0.4901</v>
+        <v>0.5309</v>
       </c>
       <c r="H302" t="n">
-        <v>0.3636</v>
+        <v>0.387</v>
       </c>
       <c r="I302" t="n">
-        <v>0.4268</v>
+        <v>0.459</v>
       </c>
       <c r="J302" t="n">
-        <v>0.5099</v>
+        <v>0.4691</v>
       </c>
       <c r="K302" t="n">
-        <v>0.6364</v>
+        <v>0.613</v>
       </c>
       <c r="L302" t="n">
-        <v>0.5732</v>
+        <v>0.541</v>
       </c>
       <c r="M302" t="n">
         <v>164</v>
@@ -16773,19 +16773,19 @@
         <v>0.737</v>
       </c>
       <c r="H303" t="n">
-        <v>0.6002999999999999</v>
+        <v>0.6022</v>
       </c>
       <c r="I303" t="n">
-        <v>0.6686</v>
+        <v>0.6696</v>
       </c>
       <c r="J303" t="n">
         <v>0.263</v>
       </c>
       <c r="K303" t="n">
-        <v>0.3997</v>
+        <v>0.3978</v>
       </c>
       <c r="L303" t="n">
-        <v>0.3314</v>
+        <v>0.3304</v>
       </c>
       <c r="M303" t="n">
         <v>164</v>
@@ -16827,19 +16827,19 @@
         <v>0.8219</v>
       </c>
       <c r="H304" t="n">
-        <v>0.6956</v>
+        <v>0.6975</v>
       </c>
       <c r="I304" t="n">
-        <v>0.7588</v>
+        <v>0.7597</v>
       </c>
       <c r="J304" t="n">
         <v>0.1781</v>
       </c>
       <c r="K304" t="n">
-        <v>0.3044</v>
+        <v>0.3025</v>
       </c>
       <c r="L304" t="n">
-        <v>0.2412</v>
+        <v>0.2403</v>
       </c>
       <c r="M304" t="n">
         <v>164</v>
@@ -16932,22 +16932,22 @@
         </is>
       </c>
       <c r="G306" t="n">
-        <v>0.6891</v>
+        <v>0.6928</v>
       </c>
       <c r="H306" t="n">
         <v>0.5347</v>
       </c>
       <c r="I306" t="n">
-        <v>0.6119</v>
+        <v>0.6138</v>
       </c>
       <c r="J306" t="n">
-        <v>0.3109</v>
+        <v>0.3072</v>
       </c>
       <c r="K306" t="n">
         <v>0.4653</v>
       </c>
       <c r="L306" t="n">
-        <v>0.3881</v>
+        <v>0.3862</v>
       </c>
       <c r="M306" t="n">
         <v>164</v>
@@ -17043,19 +17043,19 @@
         <v>0.86</v>
       </c>
       <c r="H308" t="n">
-        <v>0.751</v>
+        <v>0.7611</v>
       </c>
       <c r="I308" t="n">
-        <v>0.8055</v>
+        <v>0.8106</v>
       </c>
       <c r="J308" t="n">
         <v>0.14</v>
       </c>
       <c r="K308" t="n">
-        <v>0.249</v>
+        <v>0.2389</v>
       </c>
       <c r="L308" t="n">
-        <v>0.1945</v>
+        <v>0.1894</v>
       </c>
       <c r="M308" t="n">
         <v>164</v>
@@ -17310,22 +17310,22 @@
         </is>
       </c>
       <c r="G313" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.8494</v>
       </c>
       <c r="H313" t="n">
         <v>0.7287</v>
       </c>
       <c r="I313" t="n">
-        <v>0.791</v>
+        <v>0.789</v>
       </c>
       <c r="J313" t="n">
-        <v>0.1467</v>
+        <v>0.1506</v>
       </c>
       <c r="K313" t="n">
         <v>0.2713</v>
       </c>
       <c r="L313" t="n">
-        <v>0.209</v>
+        <v>0.211</v>
       </c>
       <c r="M313" t="n">
         <v>164</v>
@@ -17418,22 +17418,22 @@
         </is>
       </c>
       <c r="G315" t="n">
-        <v>0.5909</v>
+        <v>0.5929</v>
       </c>
       <c r="H315" t="n">
         <v>0.3877</v>
       </c>
       <c r="I315" t="n">
-        <v>0.4893</v>
+        <v>0.4903</v>
       </c>
       <c r="J315" t="n">
-        <v>0.4091</v>
+        <v>0.4071</v>
       </c>
       <c r="K315" t="n">
         <v>0.6123</v>
       </c>
       <c r="L315" t="n">
-        <v>0.5107</v>
+        <v>0.5097</v>
       </c>
       <c r="M315" t="n">
         <v>164</v>
@@ -17475,19 +17475,19 @@
         <v>0.6038</v>
       </c>
       <c r="H316" t="n">
-        <v>0.4285</v>
+        <v>0.44</v>
       </c>
       <c r="I316" t="n">
-        <v>0.5162</v>
+        <v>0.5219</v>
       </c>
       <c r="J316" t="n">
         <v>0.3962</v>
       </c>
       <c r="K316" t="n">
-        <v>0.5715</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L316" t="n">
-        <v>0.4838</v>
+        <v>0.4781</v>
       </c>
       <c r="M316" t="n">
         <v>164</v>
@@ -17526,22 +17526,22 @@
         </is>
       </c>
       <c r="G317" t="n">
-        <v>0.1831</v>
+        <v>0.1987</v>
       </c>
       <c r="H317" t="n">
-        <v>0.1381</v>
+        <v>0.1437</v>
       </c>
       <c r="I317" t="n">
-        <v>0.1606</v>
+        <v>0.1712</v>
       </c>
       <c r="J317" t="n">
-        <v>0.8169</v>
+        <v>0.8013</v>
       </c>
       <c r="K317" t="n">
-        <v>0.8619</v>
+        <v>0.8563</v>
       </c>
       <c r="L317" t="n">
-        <v>0.8394</v>
+        <v>0.8288</v>
       </c>
       <c r="M317" t="n">
         <v>164</v>
@@ -17580,22 +17580,22 @@
         </is>
       </c>
       <c r="G318" t="n">
-        <v>0.3105</v>
+        <v>0.3085</v>
       </c>
       <c r="H318" t="n">
         <v>0.2204</v>
       </c>
       <c r="I318" t="n">
-        <v>0.2654</v>
+        <v>0.2644</v>
       </c>
       <c r="J318" t="n">
-        <v>0.6895</v>
+        <v>0.6915</v>
       </c>
       <c r="K318" t="n">
         <v>0.7796</v>
       </c>
       <c r="L318" t="n">
-        <v>0.7346</v>
+        <v>0.7356</v>
       </c>
       <c r="M318" t="n">
         <v>164</v>
@@ -17745,19 +17745,19 @@
         <v>0.2923</v>
       </c>
       <c r="H321" t="n">
-        <v>0.1735</v>
+        <v>0.17</v>
       </c>
       <c r="I321" t="n">
-        <v>0.2329</v>
+        <v>0.2312</v>
       </c>
       <c r="J321" t="n">
         <v>0.7077</v>
       </c>
       <c r="K321" t="n">
-        <v>0.8265</v>
+        <v>0.83</v>
       </c>
       <c r="L321" t="n">
-        <v>0.7671</v>
+        <v>0.7688</v>
       </c>
       <c r="M321" t="n">
         <v>164</v>
@@ -17796,22 +17796,22 @@
         </is>
       </c>
       <c r="G322" t="n">
-        <v>0.3201</v>
+        <v>0.3181</v>
       </c>
       <c r="H322" t="n">
         <v>0.1677</v>
       </c>
       <c r="I322" t="n">
-        <v>0.2439</v>
+        <v>0.2429</v>
       </c>
       <c r="J322" t="n">
-        <v>0.6798999999999999</v>
+        <v>0.6819</v>
       </c>
       <c r="K322" t="n">
         <v>0.8323</v>
       </c>
       <c r="L322" t="n">
-        <v>0.7561</v>
+        <v>0.7571</v>
       </c>
       <c r="M322" t="n">
         <v>164</v>
@@ -17904,22 +17904,22 @@
         </is>
       </c>
       <c r="G324" t="n">
-        <v>0.1982</v>
+        <v>0.1953</v>
       </c>
       <c r="H324" t="n">
         <v>0.117</v>
       </c>
       <c r="I324" t="n">
-        <v>0.1576</v>
+        <v>0.1562</v>
       </c>
       <c r="J324" t="n">
-        <v>0.8018</v>
+        <v>0.8047</v>
       </c>
       <c r="K324" t="n">
         <v>0.883</v>
       </c>
       <c r="L324" t="n">
-        <v>0.8424</v>
+        <v>0.8438</v>
       </c>
       <c r="M324" t="n">
         <v>164</v>
@@ -18120,22 +18120,22 @@
         </is>
       </c>
       <c r="G328" t="n">
-        <v>0.5071</v>
+        <v>0.5053</v>
       </c>
       <c r="H328" t="n">
-        <v>0.3327</v>
+        <v>0.3114</v>
       </c>
       <c r="I328" t="n">
-        <v>0.4199</v>
+        <v>0.4084</v>
       </c>
       <c r="J328" t="n">
-        <v>0.4929</v>
+        <v>0.4947</v>
       </c>
       <c r="K328" t="n">
-        <v>0.6673</v>
+        <v>0.6886</v>
       </c>
       <c r="L328" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.5916</v>
       </c>
       <c r="M328" t="n">
         <v>164</v>
@@ -18336,22 +18336,22 @@
         </is>
       </c>
       <c r="G332" t="n">
-        <v>0.8144</v>
+        <v>0.7902</v>
       </c>
       <c r="H332" t="n">
-        <v>0.6558</v>
+        <v>0.6409</v>
       </c>
       <c r="I332" t="n">
-        <v>0.7351</v>
+        <v>0.7156</v>
       </c>
       <c r="J332" t="n">
-        <v>0.1856</v>
+        <v>0.2098</v>
       </c>
       <c r="K332" t="n">
-        <v>0.3442</v>
+        <v>0.3591</v>
       </c>
       <c r="L332" t="n">
-        <v>0.2649</v>
+        <v>0.2844</v>
       </c>
       <c r="M332" t="n">
         <v>164</v>
@@ -18390,22 +18390,22 @@
         </is>
       </c>
       <c r="G333" t="n">
-        <v>0.8502999999999999</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="H333" t="n">
-        <v>0.7449</v>
+        <v>0.7327</v>
       </c>
       <c r="I333" t="n">
-        <v>0.7976</v>
+        <v>0.7814</v>
       </c>
       <c r="J333" t="n">
-        <v>0.1497</v>
+        <v>0.1699</v>
       </c>
       <c r="K333" t="n">
-        <v>0.2551</v>
+        <v>0.2673</v>
       </c>
       <c r="L333" t="n">
-        <v>0.2024</v>
+        <v>0.2186</v>
       </c>
       <c r="M333" t="n">
         <v>164</v>
@@ -18444,22 +18444,22 @@
         </is>
       </c>
       <c r="G334" t="n">
-        <v>0.7351</v>
+        <v>0.6846</v>
       </c>
       <c r="H334" t="n">
-        <v>0.6223</v>
+        <v>0.6066</v>
       </c>
       <c r="I334" t="n">
-        <v>0.6787</v>
+        <v>0.6456</v>
       </c>
       <c r="J334" t="n">
-        <v>0.2649</v>
+        <v>0.3154</v>
       </c>
       <c r="K334" t="n">
-        <v>0.3777</v>
+        <v>0.3934</v>
       </c>
       <c r="L334" t="n">
-        <v>0.3213</v>
+        <v>0.3544</v>
       </c>
       <c r="M334" t="n">
         <v>164</v>
@@ -18498,22 +18498,22 @@
         </is>
       </c>
       <c r="G335" t="n">
-        <v>0.764</v>
+        <v>0.7341</v>
       </c>
       <c r="H335" t="n">
-        <v>0.5935</v>
+        <v>0.5726</v>
       </c>
       <c r="I335" t="n">
-        <v>0.6788</v>
+        <v>0.6534</v>
       </c>
       <c r="J335" t="n">
-        <v>0.236</v>
+        <v>0.2659</v>
       </c>
       <c r="K335" t="n">
-        <v>0.4065</v>
+        <v>0.4274</v>
       </c>
       <c r="L335" t="n">
-        <v>0.3212</v>
+        <v>0.3466</v>
       </c>
       <c r="M335" t="n">
         <v>164</v>
@@ -18552,22 +18552,22 @@
         </is>
       </c>
       <c r="G336" t="n">
-        <v>0.7894</v>
+        <v>0.7784</v>
       </c>
       <c r="H336" t="n">
-        <v>0.6268</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="I336" t="n">
-        <v>0.7081</v>
+        <v>0.6944</v>
       </c>
       <c r="J336" t="n">
-        <v>0.2106</v>
+        <v>0.2216</v>
       </c>
       <c r="K336" t="n">
-        <v>0.3732</v>
+        <v>0.3896</v>
       </c>
       <c r="L336" t="n">
-        <v>0.2919</v>
+        <v>0.3056</v>
       </c>
       <c r="M336" t="n">
         <v>164</v>
@@ -18606,22 +18606,22 @@
         </is>
       </c>
       <c r="G337" t="n">
-        <v>0.8764</v>
+        <v>0.8679</v>
       </c>
       <c r="H337" t="n">
-        <v>0.7983</v>
+        <v>0.7847</v>
       </c>
       <c r="I337" t="n">
-        <v>0.8374</v>
+        <v>0.8263</v>
       </c>
       <c r="J337" t="n">
-        <v>0.1236</v>
+        <v>0.1321</v>
       </c>
       <c r="K337" t="n">
-        <v>0.2017</v>
+        <v>0.2153</v>
       </c>
       <c r="L337" t="n">
-        <v>0.1626</v>
+        <v>0.1737</v>
       </c>
       <c r="M337" t="n">
         <v>164</v>
@@ -18660,22 +18660,22 @@
         </is>
       </c>
       <c r="G338" t="n">
-        <v>0.4835</v>
+        <v>0.4527</v>
       </c>
       <c r="H338" t="n">
-        <v>0.3742</v>
+        <v>0.3347</v>
       </c>
       <c r="I338" t="n">
-        <v>0.4288</v>
+        <v>0.3937</v>
       </c>
       <c r="J338" t="n">
-        <v>0.5165</v>
+        <v>0.5473</v>
       </c>
       <c r="K338" t="n">
-        <v>0.6258</v>
+        <v>0.6653</v>
       </c>
       <c r="L338" t="n">
-        <v>0.5712</v>
+        <v>0.6063</v>
       </c>
       <c r="M338" t="n">
         <v>164</v>
@@ -18714,22 +18714,22 @@
         </is>
       </c>
       <c r="G339" t="n">
-        <v>0.4289</v>
+        <v>0.4168</v>
       </c>
       <c r="H339" t="n">
-        <v>0.3339</v>
+        <v>0.2853</v>
       </c>
       <c r="I339" t="n">
-        <v>0.3814</v>
+        <v>0.351</v>
       </c>
       <c r="J339" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="K339" t="n">
-        <v>0.6661</v>
+        <v>0.7147</v>
       </c>
       <c r="L339" t="n">
-        <v>0.6186</v>
+        <v>0.649</v>
       </c>
       <c r="M339" t="n">
         <v>164</v>
@@ -18768,22 +18768,22 @@
         </is>
       </c>
       <c r="G340" t="n">
-        <v>0.7489</v>
+        <v>0.7086</v>
       </c>
       <c r="H340" t="n">
-        <v>0.5794</v>
+        <v>0.5618</v>
       </c>
       <c r="I340" t="n">
-        <v>0.6642</v>
+        <v>0.6352</v>
       </c>
       <c r="J340" t="n">
-        <v>0.2511</v>
+        <v>0.2914</v>
       </c>
       <c r="K340" t="n">
-        <v>0.4206</v>
+        <v>0.4382</v>
       </c>
       <c r="L340" t="n">
-        <v>0.3358</v>
+        <v>0.3648</v>
       </c>
       <c r="M340" t="n">
         <v>164</v>
@@ -18822,22 +18822,22 @@
         </is>
       </c>
       <c r="G341" t="n">
-        <v>0.8744</v>
+        <v>0.8676</v>
       </c>
       <c r="H341" t="n">
-        <v>0.7768</v>
+        <v>0.759</v>
       </c>
       <c r="I341" t="n">
-        <v>0.8256</v>
+        <v>0.8133</v>
       </c>
       <c r="J341" t="n">
-        <v>0.1256</v>
+        <v>0.1324</v>
       </c>
       <c r="K341" t="n">
-        <v>0.2232</v>
+        <v>0.241</v>
       </c>
       <c r="L341" t="n">
-        <v>0.1744</v>
+        <v>0.1867</v>
       </c>
       <c r="M341" t="n">
         <v>164</v>
@@ -18876,22 +18876,22 @@
         </is>
       </c>
       <c r="G342" t="n">
-        <v>0.8875999999999999</v>
+        <v>0.8753</v>
       </c>
       <c r="H342" t="n">
-        <v>0.7592</v>
+        <v>0.7397</v>
       </c>
       <c r="I342" t="n">
-        <v>0.8234</v>
+        <v>0.8075</v>
       </c>
       <c r="J342" t="n">
-        <v>0.1124</v>
+        <v>0.1247</v>
       </c>
       <c r="K342" t="n">
-        <v>0.2408</v>
+        <v>0.2603</v>
       </c>
       <c r="L342" t="n">
-        <v>0.1766</v>
+        <v>0.1925</v>
       </c>
       <c r="M342" t="n">
         <v>164</v>
@@ -18930,22 +18930,22 @@
         </is>
       </c>
       <c r="G343" t="n">
-        <v>0.8793</v>
+        <v>0.8709</v>
       </c>
       <c r="H343" t="n">
-        <v>0.7977</v>
+        <v>0.7841</v>
       </c>
       <c r="I343" t="n">
-        <v>0.8385</v>
+        <v>0.8275</v>
       </c>
       <c r="J343" t="n">
-        <v>0.1207</v>
+        <v>0.1291</v>
       </c>
       <c r="K343" t="n">
-        <v>0.2023</v>
+        <v>0.2159</v>
       </c>
       <c r="L343" t="n">
-        <v>0.1615</v>
+        <v>0.1725</v>
       </c>
       <c r="M343" t="n">
         <v>164</v>
@@ -18984,22 +18984,22 @@
         </is>
       </c>
       <c r="G344" t="n">
-        <v>0.6149</v>
+        <v>0.5826</v>
       </c>
       <c r="H344" t="n">
-        <v>0.4624</v>
+        <v>0.4464</v>
       </c>
       <c r="I344" t="n">
-        <v>0.5386</v>
+        <v>0.5145</v>
       </c>
       <c r="J344" t="n">
-        <v>0.3851</v>
+        <v>0.4174</v>
       </c>
       <c r="K344" t="n">
-        <v>0.5376</v>
+        <v>0.5536</v>
       </c>
       <c r="L344" t="n">
-        <v>0.4614</v>
+        <v>0.4855</v>
       </c>
       <c r="M344" t="n">
         <v>164</v>
@@ -19038,22 +19038,22 @@
         </is>
       </c>
       <c r="G345" t="n">
-        <v>0.6459</v>
+        <v>0.608</v>
       </c>
       <c r="H345" t="n">
-        <v>0.5029</v>
+        <v>0.4811</v>
       </c>
       <c r="I345" t="n">
-        <v>0.5744</v>
+        <v>0.5446</v>
       </c>
       <c r="J345" t="n">
-        <v>0.3541</v>
+        <v>0.392</v>
       </c>
       <c r="K345" t="n">
-        <v>0.4971</v>
+        <v>0.5189</v>
       </c>
       <c r="L345" t="n">
-        <v>0.4256</v>
+        <v>0.4554</v>
       </c>
       <c r="M345" t="n">
         <v>164</v>
@@ -19149,19 +19149,19 @@
         <v>0.5304</v>
       </c>
       <c r="H347" t="n">
-        <v>0.3529</v>
+        <v>0.3498</v>
       </c>
       <c r="I347" t="n">
-        <v>0.4416</v>
+        <v>0.4401</v>
       </c>
       <c r="J347" t="n">
         <v>0.4696</v>
       </c>
       <c r="K347" t="n">
-        <v>0.6471</v>
+        <v>0.6502</v>
       </c>
       <c r="L347" t="n">
-        <v>0.5584</v>
+        <v>0.5599</v>
       </c>
       <c r="M347" t="n">
         <v>164</v>
@@ -19254,22 +19254,22 @@
         </is>
       </c>
       <c r="G349" t="n">
-        <v>0.591</v>
+        <v>0.5919</v>
       </c>
       <c r="H349" t="n">
         <v>0.4346</v>
       </c>
       <c r="I349" t="n">
-        <v>0.5128</v>
+        <v>0.5132</v>
       </c>
       <c r="J349" t="n">
-        <v>0.409</v>
+        <v>0.4081</v>
       </c>
       <c r="K349" t="n">
         <v>0.5654</v>
       </c>
       <c r="L349" t="n">
-        <v>0.4872</v>
+        <v>0.4868</v>
       </c>
       <c r="M349" t="n">
         <v>164</v>
@@ -19308,22 +19308,22 @@
         </is>
       </c>
       <c r="G350" t="n">
-        <v>0.7819</v>
+        <v>0.7829</v>
       </c>
       <c r="H350" t="n">
         <v>0.6461</v>
       </c>
       <c r="I350" t="n">
-        <v>0.714</v>
+        <v>0.7145</v>
       </c>
       <c r="J350" t="n">
-        <v>0.2181</v>
+        <v>0.2171</v>
       </c>
       <c r="K350" t="n">
         <v>0.3539</v>
       </c>
       <c r="L350" t="n">
-        <v>0.286</v>
+        <v>0.2855</v>
       </c>
       <c r="M350" t="n">
         <v>164</v>
@@ -19578,22 +19578,22 @@
         </is>
       </c>
       <c r="G355" t="n">
-        <v>0.7601</v>
+        <v>0.7567</v>
       </c>
       <c r="H355" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.607</v>
       </c>
       <c r="I355" t="n">
-        <v>0.6862</v>
+        <v>0.6819</v>
       </c>
       <c r="J355" t="n">
-        <v>0.2399</v>
+        <v>0.2433</v>
       </c>
       <c r="K355" t="n">
-        <v>0.3876</v>
+        <v>0.393</v>
       </c>
       <c r="L355" t="n">
-        <v>0.3138</v>
+        <v>0.3181</v>
       </c>
       <c r="M355" t="n">
         <v>164</v>
@@ -19632,22 +19632,22 @@
         </is>
       </c>
       <c r="G356" t="n">
-        <v>0.8064</v>
+        <v>0.8083</v>
       </c>
       <c r="H356" t="n">
         <v>0.6909</v>
       </c>
       <c r="I356" t="n">
-        <v>0.7486</v>
+        <v>0.7496</v>
       </c>
       <c r="J356" t="n">
-        <v>0.1936</v>
+        <v>0.1917</v>
       </c>
       <c r="K356" t="n">
         <v>0.3091</v>
       </c>
       <c r="L356" t="n">
-        <v>0.2514</v>
+        <v>0.2504</v>
       </c>
       <c r="M356" t="n">
         <v>164</v>
@@ -19794,22 +19794,22 @@
         </is>
       </c>
       <c r="G359" t="n">
-        <v>0.3785</v>
+        <v>0.3714</v>
       </c>
       <c r="H359" t="n">
         <v>0.2228</v>
       </c>
       <c r="I359" t="n">
-        <v>0.3006</v>
+        <v>0.2971</v>
       </c>
       <c r="J359" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.6286</v>
       </c>
       <c r="K359" t="n">
         <v>0.7772</v>
       </c>
       <c r="L359" t="n">
-        <v>0.6994</v>
+        <v>0.7029</v>
       </c>
       <c r="M359" t="n">
         <v>164</v>
@@ -19956,22 +19956,22 @@
         </is>
       </c>
       <c r="G362" t="n">
-        <v>0.6477000000000001</v>
+        <v>0.6518</v>
       </c>
       <c r="H362" t="n">
         <v>0.5605</v>
       </c>
       <c r="I362" t="n">
-        <v>0.6041</v>
+        <v>0.6062</v>
       </c>
       <c r="J362" t="n">
-        <v>0.3523</v>
+        <v>0.3482</v>
       </c>
       <c r="K362" t="n">
         <v>0.4395</v>
       </c>
       <c r="L362" t="n">
-        <v>0.3959</v>
+        <v>0.3938</v>
       </c>
       <c r="M362" t="n">
         <v>164</v>
@@ -20226,22 +20226,22 @@
         </is>
       </c>
       <c r="G367" t="n">
-        <v>0.6204</v>
+        <v>0.618</v>
       </c>
       <c r="H367" t="n">
         <v>0.4833</v>
       </c>
       <c r="I367" t="n">
-        <v>0.5518</v>
+        <v>0.5506</v>
       </c>
       <c r="J367" t="n">
-        <v>0.3796</v>
+        <v>0.382</v>
       </c>
       <c r="K367" t="n">
         <v>0.5167</v>
       </c>
       <c r="L367" t="n">
-        <v>0.4482</v>
+        <v>0.4494</v>
       </c>
       <c r="M367" t="n">
         <v>164</v>
@@ -20388,22 +20388,22 @@
         </is>
       </c>
       <c r="G370" t="n">
-        <v>0.3026</v>
+        <v>0.3001</v>
       </c>
       <c r="H370" t="n">
-        <v>0.1825</v>
+        <v>0.1811</v>
       </c>
       <c r="I370" t="n">
-        <v>0.2426</v>
+        <v>0.2406</v>
       </c>
       <c r="J370" t="n">
-        <v>0.6974</v>
+        <v>0.6999</v>
       </c>
       <c r="K370" t="n">
-        <v>0.8175</v>
+        <v>0.8189</v>
       </c>
       <c r="L370" t="n">
-        <v>0.7574</v>
+        <v>0.7594</v>
       </c>
       <c r="M370" t="n">
         <v>164</v>
@@ -20499,19 +20499,19 @@
         <v>0.6331</v>
       </c>
       <c r="H372" t="n">
-        <v>0.4706</v>
+        <v>0.4736</v>
       </c>
       <c r="I372" t="n">
-        <v>0.5518</v>
+        <v>0.5534</v>
       </c>
       <c r="J372" t="n">
         <v>0.3669</v>
       </c>
       <c r="K372" t="n">
-        <v>0.5294</v>
+        <v>0.5264</v>
       </c>
       <c r="L372" t="n">
-        <v>0.4482</v>
+        <v>0.4466</v>
       </c>
       <c r="M372" t="n">
         <v>164</v>
@@ -20661,19 +20661,19 @@
         <v>0.3243</v>
       </c>
       <c r="H375" t="n">
-        <v>0.2083</v>
+        <v>0.2094</v>
       </c>
       <c r="I375" t="n">
-        <v>0.2663</v>
+        <v>0.2668</v>
       </c>
       <c r="J375" t="n">
         <v>0.6757</v>
       </c>
       <c r="K375" t="n">
-        <v>0.7917</v>
+        <v>0.7906</v>
       </c>
       <c r="L375" t="n">
-        <v>0.7337</v>
+        <v>0.7332</v>
       </c>
       <c r="M375" t="n">
         <v>164</v>
@@ -20823,19 +20823,19 @@
         <v>0.8131</v>
       </c>
       <c r="H378" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.6314</v>
       </c>
       <c r="I378" t="n">
-        <v>0.7239</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="J378" t="n">
         <v>0.1869</v>
       </c>
       <c r="K378" t="n">
-        <v>0.3654</v>
+        <v>0.3686</v>
       </c>
       <c r="L378" t="n">
-        <v>0.2761</v>
+        <v>0.2777</v>
       </c>
       <c r="M378" t="n">
         <v>164</v>
@@ -20877,19 +20877,19 @@
         <v>0.8428</v>
       </c>
       <c r="H379" t="n">
-        <v>0.7462</v>
+        <v>0.7509</v>
       </c>
       <c r="I379" t="n">
-        <v>0.7945</v>
+        <v>0.7969000000000001</v>
       </c>
       <c r="J379" t="n">
         <v>0.1572</v>
       </c>
       <c r="K379" t="n">
-        <v>0.2538</v>
+        <v>0.2491</v>
       </c>
       <c r="L379" t="n">
-        <v>0.2055</v>
+        <v>0.2031</v>
       </c>
       <c r="M379" t="n">
         <v>164</v>
@@ -20931,19 +20931,19 @@
         <v>0.4619</v>
       </c>
       <c r="H380" t="n">
-        <v>0.3197</v>
+        <v>0.3308</v>
       </c>
       <c r="I380" t="n">
-        <v>0.3908</v>
+        <v>0.3964</v>
       </c>
       <c r="J380" t="n">
         <v>0.5381</v>
       </c>
       <c r="K380" t="n">
-        <v>0.6803</v>
+        <v>0.6692</v>
       </c>
       <c r="L380" t="n">
-        <v>0.6092</v>
+        <v>0.6036</v>
       </c>
       <c r="M380" t="n">
         <v>164</v>
@@ -20982,22 +20982,22 @@
         </is>
       </c>
       <c r="G381" t="n">
-        <v>0.4985</v>
+        <v>0.5135</v>
       </c>
       <c r="H381" t="n">
         <v>0.3302</v>
       </c>
       <c r="I381" t="n">
-        <v>0.4144</v>
+        <v>0.4218</v>
       </c>
       <c r="J381" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.4865</v>
       </c>
       <c r="K381" t="n">
         <v>0.6698</v>
       </c>
       <c r="L381" t="n">
-        <v>0.5856</v>
+        <v>0.5782</v>
       </c>
       <c r="M381" t="n">
         <v>164</v>
@@ -21093,19 +21093,19 @@
         <v>0.8161</v>
       </c>
       <c r="H383" t="n">
-        <v>0.714</v>
+        <v>0.716</v>
       </c>
       <c r="I383" t="n">
-        <v>0.765</v>
+        <v>0.766</v>
       </c>
       <c r="J383" t="n">
         <v>0.1839</v>
       </c>
       <c r="K383" t="n">
-        <v>0.286</v>
+        <v>0.284</v>
       </c>
       <c r="L383" t="n">
-        <v>0.235</v>
+        <v>0.234</v>
       </c>
       <c r="M383" t="n">
         <v>164</v>
@@ -21309,19 +21309,19 @@
         <v>0.797</v>
       </c>
       <c r="H387" t="n">
-        <v>0.6822</v>
+        <v>0.6859</v>
       </c>
       <c r="I387" t="n">
-        <v>0.7396</v>
+        <v>0.7413999999999999</v>
       </c>
       <c r="J387" t="n">
         <v>0.203</v>
       </c>
       <c r="K387" t="n">
-        <v>0.3178</v>
+        <v>0.3141</v>
       </c>
       <c r="L387" t="n">
-        <v>0.2604</v>
+        <v>0.2586</v>
       </c>
       <c r="M387" t="n">
         <v>164</v>
@@ -21360,22 +21360,22 @@
         </is>
       </c>
       <c r="G388" t="n">
-        <v>0.8235</v>
+        <v>0.8222</v>
       </c>
       <c r="H388" t="n">
-        <v>0.6567</v>
+        <v>0.6577</v>
       </c>
       <c r="I388" t="n">
-        <v>0.7401</v>
+        <v>0.74</v>
       </c>
       <c r="J388" t="n">
-        <v>0.1765</v>
+        <v>0.1778</v>
       </c>
       <c r="K388" t="n">
-        <v>0.3433</v>
+        <v>0.3423</v>
       </c>
       <c r="L388" t="n">
-        <v>0.2599</v>
+        <v>0.26</v>
       </c>
       <c r="M388" t="n">
         <v>164</v>
@@ -21414,22 +21414,22 @@
         </is>
       </c>
       <c r="G389" t="n">
-        <v>0.8555</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="H389" t="n">
         <v>0.7269</v>
       </c>
       <c r="I389" t="n">
-        <v>0.7912</v>
+        <v>0.7916</v>
       </c>
       <c r="J389" t="n">
-        <v>0.1445</v>
+        <v>0.1436</v>
       </c>
       <c r="K389" t="n">
         <v>0.2731</v>
       </c>
       <c r="L389" t="n">
-        <v>0.2088</v>
+        <v>0.2084</v>
       </c>
       <c r="M389" t="n">
         <v>164</v>
@@ -21525,19 +21525,19 @@
         <v>0.471</v>
       </c>
       <c r="H391" t="n">
-        <v>0.352</v>
+        <v>0.3493</v>
       </c>
       <c r="I391" t="n">
-        <v>0.4115</v>
+        <v>0.4102</v>
       </c>
       <c r="J391" t="n">
         <v>0.529</v>
       </c>
       <c r="K391" t="n">
-        <v>0.648</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="L391" t="n">
-        <v>0.5885</v>
+        <v>0.5898</v>
       </c>
       <c r="M391" t="n">
         <v>164</v>
@@ -21576,22 +21576,22 @@
         </is>
       </c>
       <c r="G392" t="n">
-        <v>0.7909</v>
+        <v>0.7906</v>
       </c>
       <c r="H392" t="n">
-        <v>0.6545</v>
+        <v>0.6554</v>
       </c>
       <c r="I392" t="n">
-        <v>0.7227</v>
+        <v>0.723</v>
       </c>
       <c r="J392" t="n">
-        <v>0.2091</v>
+        <v>0.2094</v>
       </c>
       <c r="K392" t="n">
-        <v>0.3455</v>
+        <v>0.3446</v>
       </c>
       <c r="L392" t="n">
-        <v>0.2773</v>
+        <v>0.277</v>
       </c>
       <c r="M392" t="n">
         <v>164</v>
@@ -21684,22 +21684,22 @@
         </is>
       </c>
       <c r="G394" t="n">
-        <v>0.2432</v>
+        <v>0.2416</v>
       </c>
       <c r="H394" t="n">
-        <v>0.1864</v>
+        <v>0.1851</v>
       </c>
       <c r="I394" t="n">
-        <v>0.2148</v>
+        <v>0.2134</v>
       </c>
       <c r="J394" t="n">
-        <v>0.7568</v>
+        <v>0.7584</v>
       </c>
       <c r="K394" t="n">
-        <v>0.8136</v>
+        <v>0.8149</v>
       </c>
       <c r="L394" t="n">
-        <v>0.7852</v>
+        <v>0.7866</v>
       </c>
       <c r="M394" t="n">
         <v>164</v>
@@ -21846,22 +21846,22 @@
         </is>
       </c>
       <c r="G397" t="n">
-        <v>0.7333</v>
+        <v>0.7168</v>
       </c>
       <c r="H397" t="n">
-        <v>0.6167</v>
+        <v>0.6122</v>
       </c>
       <c r="I397" t="n">
-        <v>0.675</v>
+        <v>0.6645</v>
       </c>
       <c r="J397" t="n">
-        <v>0.2667</v>
+        <v>0.2832</v>
       </c>
       <c r="K397" t="n">
-        <v>0.3833</v>
+        <v>0.3878</v>
       </c>
       <c r="L397" t="n">
-        <v>0.325</v>
+        <v>0.3355</v>
       </c>
       <c r="M397" t="n">
         <v>164</v>
@@ -21900,22 +21900,22 @@
         </is>
       </c>
       <c r="G398" t="n">
-        <v>0.8145</v>
+        <v>0.8167</v>
       </c>
       <c r="H398" t="n">
         <v>0.6860000000000001</v>
       </c>
       <c r="I398" t="n">
-        <v>0.7503</v>
+        <v>0.7514</v>
       </c>
       <c r="J398" t="n">
-        <v>0.1855</v>
+        <v>0.1833</v>
       </c>
       <c r="K398" t="n">
         <v>0.314</v>
       </c>
       <c r="L398" t="n">
-        <v>0.2497</v>
+        <v>0.2486</v>
       </c>
       <c r="M398" t="n">
         <v>164</v>
@@ -21957,19 +21957,19 @@
         <v>0.4127</v>
       </c>
       <c r="H399" t="n">
-        <v>0.2844</v>
+        <v>0.2819</v>
       </c>
       <c r="I399" t="n">
-        <v>0.3486</v>
+        <v>0.3473</v>
       </c>
       <c r="J399" t="n">
         <v>0.5873</v>
       </c>
       <c r="K399" t="n">
-        <v>0.7156</v>
+        <v>0.7181</v>
       </c>
       <c r="L399" t="n">
-        <v>0.6514</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="M399" t="n">
         <v>164</v>
@@ -22278,22 +22278,22 @@
         </is>
       </c>
       <c r="G405" t="n">
-        <v>0.5312</v>
+        <v>0.5211</v>
       </c>
       <c r="H405" t="n">
-        <v>0.3865</v>
+        <v>0.3699</v>
       </c>
       <c r="I405" t="n">
-        <v>0.4588</v>
+        <v>0.4455</v>
       </c>
       <c r="J405" t="n">
-        <v>0.4688</v>
+        <v>0.4789</v>
       </c>
       <c r="K405" t="n">
-        <v>0.6135</v>
+        <v>0.6301</v>
       </c>
       <c r="L405" t="n">
-        <v>0.5412</v>
+        <v>0.5545</v>
       </c>
       <c r="M405" t="n">
         <v>164</v>
@@ -22389,19 +22389,19 @@
         <v>0.2763</v>
       </c>
       <c r="H407" t="n">
-        <v>0.1562</v>
+        <v>0.155</v>
       </c>
       <c r="I407" t="n">
-        <v>0.2162</v>
+        <v>0.2156</v>
       </c>
       <c r="J407" t="n">
         <v>0.7237</v>
       </c>
       <c r="K407" t="n">
-        <v>0.8438</v>
+        <v>0.845</v>
       </c>
       <c r="L407" t="n">
-        <v>0.7838000000000001</v>
+        <v>0.7844</v>
       </c>
       <c r="M407" t="n">
         <v>164</v>
@@ -22602,22 +22602,22 @@
         </is>
       </c>
       <c r="G411" t="n">
-        <v>0.875</v>
+        <v>0.8789</v>
       </c>
       <c r="H411" t="n">
-        <v>0.7709</v>
+        <v>0.775</v>
       </c>
       <c r="I411" t="n">
-        <v>0.823</v>
+        <v>0.827</v>
       </c>
       <c r="J411" t="n">
-        <v>0.125</v>
+        <v>0.1211</v>
       </c>
       <c r="K411" t="n">
-        <v>0.2291</v>
+        <v>0.225</v>
       </c>
       <c r="L411" t="n">
-        <v>0.177</v>
+        <v>0.173</v>
       </c>
       <c r="M411" t="n">
         <v>164</v>
@@ -22656,22 +22656,22 @@
         </is>
       </c>
       <c r="G412" t="n">
-        <v>0.8852</v>
+        <v>0.8841</v>
       </c>
       <c r="H412" t="n">
         <v>0.771</v>
       </c>
       <c r="I412" t="n">
-        <v>0.8280999999999999</v>
+        <v>0.8276</v>
       </c>
       <c r="J412" t="n">
-        <v>0.1148</v>
+        <v>0.1159</v>
       </c>
       <c r="K412" t="n">
         <v>0.229</v>
       </c>
       <c r="L412" t="n">
-        <v>0.1719</v>
+        <v>0.1724</v>
       </c>
       <c r="M412" t="n">
         <v>164</v>
@@ -22710,22 +22710,22 @@
         </is>
       </c>
       <c r="G413" t="n">
-        <v>0.8878</v>
+        <v>0.8898</v>
       </c>
       <c r="H413" t="n">
         <v>0.7954</v>
       </c>
       <c r="I413" t="n">
-        <v>0.8416</v>
+        <v>0.8426</v>
       </c>
       <c r="J413" t="n">
-        <v>0.1122</v>
+        <v>0.1102</v>
       </c>
       <c r="K413" t="n">
         <v>0.2046</v>
       </c>
       <c r="L413" t="n">
-        <v>0.1584</v>
+        <v>0.1574</v>
       </c>
       <c r="M413" t="n">
         <v>164</v>
@@ -22767,19 +22767,19 @@
         <v>0.7119</v>
       </c>
       <c r="H414" t="n">
-        <v>0.5625</v>
+        <v>0.5684</v>
       </c>
       <c r="I414" t="n">
-        <v>0.6372</v>
+        <v>0.6402</v>
       </c>
       <c r="J414" t="n">
         <v>0.2881</v>
       </c>
       <c r="K414" t="n">
-        <v>0.4375</v>
+        <v>0.4316</v>
       </c>
       <c r="L414" t="n">
-        <v>0.3628</v>
+        <v>0.3598</v>
       </c>
       <c r="M414" t="n">
         <v>164</v>
@@ -22818,22 +22818,22 @@
         </is>
       </c>
       <c r="G415" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.7308</v>
       </c>
       <c r="H415" t="n">
         <v>0.5957</v>
       </c>
       <c r="I415" t="n">
-        <v>0.6615</v>
+        <v>0.6632</v>
       </c>
       <c r="J415" t="n">
-        <v>0.2727</v>
+        <v>0.2692</v>
       </c>
       <c r="K415" t="n">
         <v>0.4043</v>
       </c>
       <c r="L415" t="n">
-        <v>0.3385</v>
+        <v>0.3368</v>
       </c>
       <c r="M415" t="n">
         <v>164</v>
@@ -22926,22 +22926,22 @@
         </is>
       </c>
       <c r="G417" t="n">
-        <v>0.8764999999999999</v>
+        <v>0.8781</v>
       </c>
       <c r="H417" t="n">
         <v>0.7609</v>
       </c>
       <c r="I417" t="n">
-        <v>0.8187</v>
+        <v>0.8195</v>
       </c>
       <c r="J417" t="n">
-        <v>0.1235</v>
+        <v>0.1219</v>
       </c>
       <c r="K417" t="n">
         <v>0.2391</v>
       </c>
       <c r="L417" t="n">
-        <v>0.1813</v>
+        <v>0.1805</v>
       </c>
       <c r="M417" t="n">
         <v>164</v>
@@ -23091,19 +23091,19 @@
         <v>0.7559</v>
       </c>
       <c r="H420" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.6256</v>
       </c>
       <c r="I420" t="n">
-        <v>0.6871</v>
+        <v>0.6908</v>
       </c>
       <c r="J420" t="n">
         <v>0.2441</v>
       </c>
       <c r="K420" t="n">
-        <v>0.3816</v>
+        <v>0.3744</v>
       </c>
       <c r="L420" t="n">
-        <v>0.3129</v>
+        <v>0.3092</v>
       </c>
       <c r="M420" t="n">
         <v>164</v>
@@ -23250,22 +23250,22 @@
         </is>
       </c>
       <c r="G423" t="n">
-        <v>0.8434</v>
+        <v>0.8375</v>
       </c>
       <c r="H423" t="n">
-        <v>0.6662</v>
+        <v>0.6596</v>
       </c>
       <c r="I423" t="n">
-        <v>0.7548</v>
+        <v>0.7486</v>
       </c>
       <c r="J423" t="n">
-        <v>0.1566</v>
+        <v>0.1625</v>
       </c>
       <c r="K423" t="n">
-        <v>0.3338</v>
+        <v>0.3404</v>
       </c>
       <c r="L423" t="n">
-        <v>0.2452</v>
+        <v>0.2514</v>
       </c>
       <c r="M423" t="n">
         <v>164</v>
@@ -23304,22 +23304,22 @@
         </is>
       </c>
       <c r="G424" t="n">
-        <v>0.8576</v>
+        <v>0.86</v>
       </c>
       <c r="H424" t="n">
-        <v>0.7332</v>
+        <v>0.7359</v>
       </c>
       <c r="I424" t="n">
-        <v>0.7954</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="J424" t="n">
-        <v>0.1424</v>
+        <v>0.14</v>
       </c>
       <c r="K424" t="n">
-        <v>0.2668</v>
+        <v>0.2641</v>
       </c>
       <c r="L424" t="n">
-        <v>0.2046</v>
+        <v>0.2021</v>
       </c>
       <c r="M424" t="n">
         <v>164</v>
@@ -23466,22 +23466,22 @@
         </is>
       </c>
       <c r="G427" t="n">
-        <v>0.5226</v>
+        <v>0.5158</v>
       </c>
       <c r="H427" t="n">
-        <v>0.395</v>
+        <v>0.3853</v>
       </c>
       <c r="I427" t="n">
-        <v>0.4588</v>
+        <v>0.4506</v>
       </c>
       <c r="J427" t="n">
-        <v>0.4774</v>
+        <v>0.4842</v>
       </c>
       <c r="K427" t="n">
-        <v>0.605</v>
+        <v>0.6147</v>
       </c>
       <c r="L427" t="n">
-        <v>0.5412</v>
+        <v>0.5494</v>
       </c>
       <c r="M427" t="n">
         <v>164</v>
@@ -23577,19 +23577,19 @@
         <v>0.2919</v>
       </c>
       <c r="H429" t="n">
-        <v>0.1731</v>
+        <v>0.1699</v>
       </c>
       <c r="I429" t="n">
-        <v>0.2325</v>
+        <v>0.2309</v>
       </c>
       <c r="J429" t="n">
         <v>0.7081</v>
       </c>
       <c r="K429" t="n">
-        <v>0.8269</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="L429" t="n">
-        <v>0.7675</v>
+        <v>0.7691</v>
       </c>
       <c r="M429" t="n">
         <v>164</v>
@@ -23631,19 +23631,19 @@
         <v>0.2739</v>
       </c>
       <c r="H430" t="n">
-        <v>0.143</v>
+        <v>0.1419</v>
       </c>
       <c r="I430" t="n">
-        <v>0.2084</v>
+        <v>0.2079</v>
       </c>
       <c r="J430" t="n">
         <v>0.7261</v>
       </c>
       <c r="K430" t="n">
-        <v>0.857</v>
+        <v>0.8581</v>
       </c>
       <c r="L430" t="n">
-        <v>0.7916</v>
+        <v>0.7921</v>
       </c>
       <c r="M430" t="n">
         <v>164</v>
@@ -23682,22 +23682,22 @@
         </is>
       </c>
       <c r="G431" t="n">
-        <v>0.6616</v>
+        <v>0.6802</v>
       </c>
       <c r="H431" t="n">
-        <v>0.5355</v>
+        <v>0.5527</v>
       </c>
       <c r="I431" t="n">
-        <v>0.5985</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="J431" t="n">
-        <v>0.3384</v>
+        <v>0.3198</v>
       </c>
       <c r="K431" t="n">
-        <v>0.4645</v>
+        <v>0.4473</v>
       </c>
       <c r="L431" t="n">
-        <v>0.4015</v>
+        <v>0.3836</v>
       </c>
       <c r="M431" t="n">
         <v>164</v>
@@ -23736,22 +23736,22 @@
         </is>
       </c>
       <c r="G432" t="n">
-        <v>0.2735</v>
+        <v>0.283</v>
       </c>
       <c r="H432" t="n">
-        <v>0.1557</v>
+        <v>0.1576</v>
       </c>
       <c r="I432" t="n">
-        <v>0.2146</v>
+        <v>0.2203</v>
       </c>
       <c r="J432" t="n">
-        <v>0.7265</v>
+        <v>0.717</v>
       </c>
       <c r="K432" t="n">
-        <v>0.8443000000000001</v>
+        <v>0.8424</v>
       </c>
       <c r="L432" t="n">
-        <v>0.7854</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="M432" t="n">
         <v>164</v>
@@ -23790,22 +23790,22 @@
         </is>
       </c>
       <c r="G433" t="n">
-        <v>0.284</v>
+        <v>0.2884</v>
       </c>
       <c r="H433" t="n">
-        <v>0.1524</v>
+        <v>0.1534</v>
       </c>
       <c r="I433" t="n">
-        <v>0.2182</v>
+        <v>0.2209</v>
       </c>
       <c r="J433" t="n">
-        <v>0.716</v>
+        <v>0.7116</v>
       </c>
       <c r="K433" t="n">
-        <v>0.8476</v>
+        <v>0.8466</v>
       </c>
       <c r="L433" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.7791</v>
       </c>
       <c r="M433" t="n">
         <v>164</v>
@@ -23847,19 +23847,19 @@
         <v>0.2552</v>
       </c>
       <c r="H434" t="n">
-        <v>0.1562</v>
+        <v>0.1531</v>
       </c>
       <c r="I434" t="n">
-        <v>0.2057</v>
+        <v>0.2042</v>
       </c>
       <c r="J434" t="n">
         <v>0.7448</v>
       </c>
       <c r="K434" t="n">
-        <v>0.8438</v>
+        <v>0.8469</v>
       </c>
       <c r="L434" t="n">
-        <v>0.7943</v>
+        <v>0.7958</v>
       </c>
       <c r="M434" t="n">
         <v>164</v>
@@ -23898,22 +23898,22 @@
         </is>
       </c>
       <c r="G435" t="n">
-        <v>0.2339</v>
+        <v>0.2283</v>
       </c>
       <c r="H435" t="n">
         <v>0.133</v>
       </c>
       <c r="I435" t="n">
-        <v>0.1834</v>
+        <v>0.1806</v>
       </c>
       <c r="J435" t="n">
-        <v>0.7661</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="K435" t="n">
         <v>0.867</v>
       </c>
       <c r="L435" t="n">
-        <v>0.8166</v>
+        <v>0.8194</v>
       </c>
       <c r="M435" t="n">
         <v>164</v>

--- a/nba/public/data/nba_matchup_probs.xlsx
+++ b/nba/public/data/nba_matchup_probs.xlsx
@@ -570,22 +570,22 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.4781</v>
+        <v>0.4733</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2727</v>
+        <v>0.2693</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3754</v>
+        <v>0.3713</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5219</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.7307</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6246</v>
+        <v>0.6287</v>
       </c>
       <c r="M3" t="n">
         <v>164</v>
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.7956</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6152</v>
+        <v>0.6197</v>
       </c>
       <c r="I4" t="n">
-        <v>0.704</v>
+        <v>0.7076</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2072</v>
+        <v>0.2044</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3848</v>
+        <v>0.3803</v>
       </c>
       <c r="L4" t="n">
-        <v>0.296</v>
+        <v>0.2924</v>
       </c>
       <c r="M4" t="n">
         <v>164</v>
@@ -678,22 +678,22 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.7945</v>
+        <v>0.7982</v>
       </c>
       <c r="H5" t="n">
-        <v>0.628</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.7154</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2055</v>
+        <v>0.2018</v>
       </c>
       <c r="K5" t="n">
-        <v>0.372</v>
+        <v>0.3674</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2888</v>
+        <v>0.2846</v>
       </c>
       <c r="M5" t="n">
         <v>164</v>
@@ -732,22 +732,22 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.8276</v>
+        <v>0.8287</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7004</v>
+        <v>0.7049</v>
       </c>
       <c r="I6" t="n">
-        <v>0.764</v>
+        <v>0.7668</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1724</v>
+        <v>0.1713</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2996</v>
+        <v>0.2951</v>
       </c>
       <c r="L6" t="n">
-        <v>0.236</v>
+        <v>0.2332</v>
       </c>
       <c r="M6" t="n">
         <v>164</v>
@@ -843,19 +843,19 @@
         <v>0.7216</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.5381</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6292</v>
+        <v>0.6298</v>
       </c>
       <c r="J8" t="n">
         <v>0.2784</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4632</v>
+        <v>0.4619</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3708</v>
+        <v>0.3702</v>
       </c>
       <c r="M8" t="n">
         <v>164</v>
@@ -1002,22 +1002,22 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.5017</v>
+        <v>0.5898</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3307</v>
+        <v>0.4658</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4162</v>
+        <v>0.5278</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4983</v>
+        <v>0.4102</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6693</v>
+        <v>0.5342</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5838</v>
+        <v>0.4722</v>
       </c>
       <c r="M11" t="n">
         <v>164</v>
@@ -1110,22 +1110,22 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.832</v>
+        <v>0.8411</v>
       </c>
       <c r="H13" t="n">
         <v>0.6703</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7512</v>
+        <v>0.7557</v>
       </c>
       <c r="J13" t="n">
-        <v>0.168</v>
+        <v>0.1589</v>
       </c>
       <c r="K13" t="n">
         <v>0.3297</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2488</v>
+        <v>0.2443</v>
       </c>
       <c r="M13" t="n">
         <v>164</v>
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.8661</v>
+        <v>0.8678</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7592</v>
+        <v>0.7642</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8126</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1339</v>
+        <v>0.1322</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2408</v>
+        <v>0.2358</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1874</v>
+        <v>0.184</v>
       </c>
       <c r="M15" t="n">
         <v>164</v>
@@ -1380,22 +1380,22 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.8139</v>
+        <v>0.8148</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6903</v>
+        <v>0.6931</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7521</v>
+        <v>0.754</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1861</v>
+        <v>0.1852</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3097</v>
+        <v>0.3069</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2479</v>
+        <v>0.246</v>
       </c>
       <c r="M18" t="n">
         <v>164</v>
@@ -1488,22 +1488,22 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.6428</v>
+        <v>0.6466</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4932</v>
+        <v>0.4914</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.569</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3572</v>
+        <v>0.3534</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5068</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>0.432</v>
+        <v>0.431</v>
       </c>
       <c r="M20" t="n">
         <v>164</v>
@@ -1542,22 +1542,22 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.6918</v>
+        <v>0.6765</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5451</v>
+        <v>0.5315</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.604</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3082</v>
+        <v>0.3235</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4549</v>
+        <v>0.4685</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3816</v>
+        <v>0.396</v>
       </c>
       <c r="M21" t="n">
         <v>164</v>
@@ -1596,22 +1596,22 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.8511</v>
+        <v>0.855</v>
       </c>
       <c r="H22" t="n">
         <v>0.7255</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7883</v>
+        <v>0.7902</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1489</v>
+        <v>0.145</v>
       </c>
       <c r="K22" t="n">
         <v>0.2745</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2117</v>
+        <v>0.2098</v>
       </c>
       <c r="M22" t="n">
         <v>164</v>
@@ -1653,19 +1653,19 @@
         <v>0.3766</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2521</v>
+        <v>0.2514</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3144</v>
+        <v>0.314</v>
       </c>
       <c r="J23" t="n">
         <v>0.6234</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7479</v>
+        <v>0.7486</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6856</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="M23" t="n">
         <v>164</v>
@@ -1707,19 +1707,19 @@
         <v>0.3459</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2295</v>
+        <v>0.225</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2877</v>
+        <v>0.2854</v>
       </c>
       <c r="J24" t="n">
         <v>0.6541</v>
       </c>
       <c r="K24" t="n">
-        <v>0.7705</v>
+        <v>0.775</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7123</v>
+        <v>0.7146</v>
       </c>
       <c r="M24" t="n">
         <v>164</v>
@@ -1758,22 +1758,22 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.5947</v>
+        <v>0.5958</v>
       </c>
       <c r="H25" t="n">
         <v>0.4661</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5304</v>
+        <v>0.531</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4053</v>
+        <v>0.4042</v>
       </c>
       <c r="K25" t="n">
         <v>0.5339</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4696</v>
+        <v>0.469</v>
       </c>
       <c r="M25" t="n">
         <v>164</v>
@@ -1815,19 +1815,19 @@
         <v>0.8459</v>
       </c>
       <c r="H26" t="n">
-        <v>0.714</v>
+        <v>0.7188</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7799</v>
+        <v>0.7824</v>
       </c>
       <c r="J26" t="n">
         <v>0.1541</v>
       </c>
       <c r="K26" t="n">
-        <v>0.286</v>
+        <v>0.2812</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2201</v>
+        <v>0.2176</v>
       </c>
       <c r="M26" t="n">
         <v>164</v>
@@ -1866,22 +1866,22 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.8429</v>
+        <v>0.8461</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6807</v>
+        <v>0.6868</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7618</v>
+        <v>0.7664</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1571</v>
+        <v>0.1539</v>
       </c>
       <c r="K27" t="n">
-        <v>0.3193</v>
+        <v>0.3132</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2382</v>
+        <v>0.2336</v>
       </c>
       <c r="M27" t="n">
         <v>164</v>
@@ -1920,22 +1920,22 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.8633999999999999</v>
+        <v>0.8683</v>
       </c>
       <c r="H28" t="n">
         <v>0.7593</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8114</v>
+        <v>0.8138</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1366</v>
+        <v>0.1317</v>
       </c>
       <c r="K28" t="n">
         <v>0.2407</v>
       </c>
       <c r="L28" t="n">
-        <v>0.1886</v>
+        <v>0.1862</v>
       </c>
       <c r="M28" t="n">
         <v>164</v>
@@ -1974,22 +1974,22 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.5273</v>
+        <v>0.5371</v>
       </c>
       <c r="H29" t="n">
         <v>0.374</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4506</v>
+        <v>0.4556</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4727</v>
+        <v>0.4629</v>
       </c>
       <c r="K29" t="n">
         <v>0.626</v>
       </c>
       <c r="L29" t="n">
-        <v>0.5494</v>
+        <v>0.5444</v>
       </c>
       <c r="M29" t="n">
         <v>164</v>
@@ -2028,22 +2028,22 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.5405</v>
+        <v>0.5456</v>
       </c>
       <c r="H30" t="n">
         <v>0.407</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4738</v>
+        <v>0.4763</v>
       </c>
       <c r="J30" t="n">
-        <v>0.4595</v>
+        <v>0.4544</v>
       </c>
       <c r="K30" t="n">
         <v>0.593</v>
       </c>
       <c r="L30" t="n">
-        <v>0.5262</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="M30" t="n">
         <v>164</v>
@@ -2082,22 +2082,22 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.5928</v>
+        <v>0.5911</v>
       </c>
       <c r="H31" t="n">
         <v>0.4482</v>
       </c>
       <c r="I31" t="n">
-        <v>0.5205</v>
+        <v>0.5196</v>
       </c>
       <c r="J31" t="n">
-        <v>0.4072</v>
+        <v>0.4089</v>
       </c>
       <c r="K31" t="n">
         <v>0.5518</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4795</v>
+        <v>0.4804</v>
       </c>
       <c r="M31" t="n">
         <v>164</v>
@@ -2136,22 +2136,22 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.8357</v>
+        <v>0.8369</v>
       </c>
       <c r="H32" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.7462</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7901</v>
+        <v>0.7916</v>
       </c>
       <c r="J32" t="n">
-        <v>0.1643</v>
+        <v>0.1631</v>
       </c>
       <c r="K32" t="n">
-        <v>0.2555</v>
+        <v>0.2538</v>
       </c>
       <c r="L32" t="n">
-        <v>0.2099</v>
+        <v>0.2084</v>
       </c>
       <c r="M32" t="n">
         <v>164</v>
@@ -2190,22 +2190,22 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.8532</v>
+        <v>0.8582</v>
       </c>
       <c r="H33" t="n">
-        <v>0.7359</v>
+        <v>0.7382</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7946</v>
+        <v>0.7982</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1468</v>
+        <v>0.1418</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2641</v>
+        <v>0.2618</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2054</v>
+        <v>0.2018</v>
       </c>
       <c r="M33" t="n">
         <v>164</v>
@@ -2247,19 +2247,19 @@
         <v>0.8669</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7734</v>
+        <v>0.7817</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8202</v>
+        <v>0.8243</v>
       </c>
       <c r="J34" t="n">
         <v>0.1331</v>
       </c>
       <c r="K34" t="n">
-        <v>0.2266</v>
+        <v>0.2183</v>
       </c>
       <c r="L34" t="n">
-        <v>0.1798</v>
+        <v>0.1757</v>
       </c>
       <c r="M34" t="n">
         <v>164</v>
@@ -2352,22 +2352,22 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.8096</v>
+        <v>0.8116</v>
       </c>
       <c r="H36" t="n">
         <v>0.6888</v>
       </c>
       <c r="I36" t="n">
-        <v>0.7492</v>
+        <v>0.7502</v>
       </c>
       <c r="J36" t="n">
-        <v>0.1904</v>
+        <v>0.1884</v>
       </c>
       <c r="K36" t="n">
         <v>0.3112</v>
       </c>
       <c r="L36" t="n">
-        <v>0.2508</v>
+        <v>0.2498</v>
       </c>
       <c r="M36" t="n">
         <v>164</v>
@@ -2406,22 +2406,22 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.6859</v>
+        <v>0.6894</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5162</v>
+        <v>0.5143</v>
       </c>
       <c r="I37" t="n">
-        <v>0.601</v>
+        <v>0.6018</v>
       </c>
       <c r="J37" t="n">
-        <v>0.3141</v>
+        <v>0.3106</v>
       </c>
       <c r="K37" t="n">
-        <v>0.4838</v>
+        <v>0.4857</v>
       </c>
       <c r="L37" t="n">
-        <v>0.399</v>
+        <v>0.3982</v>
       </c>
       <c r="M37" t="n">
         <v>164</v>
@@ -2460,22 +2460,22 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.7345</v>
+        <v>0.7467</v>
       </c>
       <c r="H38" t="n">
         <v>0.5784</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6564</v>
+        <v>0.6626</v>
       </c>
       <c r="J38" t="n">
-        <v>0.2655</v>
+        <v>0.2533</v>
       </c>
       <c r="K38" t="n">
         <v>0.4216</v>
       </c>
       <c r="L38" t="n">
-        <v>0.3436</v>
+        <v>0.3374</v>
       </c>
       <c r="M38" t="n">
         <v>164</v>
@@ -2514,22 +2514,22 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.6326000000000001</v>
+        <v>0.7235</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4661</v>
+        <v>0.5804</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5494</v>
+        <v>0.652</v>
       </c>
       <c r="J39" t="n">
-        <v>0.3674</v>
+        <v>0.2765</v>
       </c>
       <c r="K39" t="n">
-        <v>0.5339</v>
+        <v>0.4196</v>
       </c>
       <c r="L39" t="n">
-        <v>0.4506</v>
+        <v>0.348</v>
       </c>
       <c r="M39" t="n">
         <v>164</v>
@@ -2568,22 +2568,22 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.7932</v>
+        <v>0.7961</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6192</v>
+        <v>0.6183</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7062</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>0.2068</v>
+        <v>0.2039</v>
       </c>
       <c r="K40" t="n">
-        <v>0.3808</v>
+        <v>0.3817</v>
       </c>
       <c r="L40" t="n">
-        <v>0.2938</v>
+        <v>0.2928</v>
       </c>
       <c r="M40" t="n">
         <v>164</v>
@@ -2838,22 +2838,22 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.8289</v>
+        <v>0.8334</v>
       </c>
       <c r="H45" t="n">
-        <v>0.6773</v>
+        <v>0.6816</v>
       </c>
       <c r="I45" t="n">
-        <v>0.7531</v>
+        <v>0.7575</v>
       </c>
       <c r="J45" t="n">
-        <v>0.1711</v>
+        <v>0.1666</v>
       </c>
       <c r="K45" t="n">
-        <v>0.3227</v>
+        <v>0.3184</v>
       </c>
       <c r="L45" t="n">
-        <v>0.2469</v>
+        <v>0.2425</v>
       </c>
       <c r="M45" t="n">
         <v>164</v>
@@ -2892,22 +2892,22 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.8618</v>
+        <v>0.8623</v>
       </c>
       <c r="H46" t="n">
-        <v>0.7529</v>
+        <v>0.7581</v>
       </c>
       <c r="I46" t="n">
-        <v>0.8074</v>
+        <v>0.8102</v>
       </c>
       <c r="J46" t="n">
-        <v>0.1382</v>
+        <v>0.1377</v>
       </c>
       <c r="K46" t="n">
-        <v>0.2471</v>
+        <v>0.2419</v>
       </c>
       <c r="L46" t="n">
-        <v>0.1926</v>
+        <v>0.1898</v>
       </c>
       <c r="M46" t="n">
         <v>164</v>
@@ -2946,22 +2946,22 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.7613</v>
+        <v>0.7633</v>
       </c>
       <c r="H47" t="n">
-        <v>0.638</v>
+        <v>0.645</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6996</v>
+        <v>0.7042</v>
       </c>
       <c r="J47" t="n">
-        <v>0.2387</v>
+        <v>0.2367</v>
       </c>
       <c r="K47" t="n">
-        <v>0.362</v>
+        <v>0.355</v>
       </c>
       <c r="L47" t="n">
-        <v>0.3004</v>
+        <v>0.2958</v>
       </c>
       <c r="M47" t="n">
         <v>164</v>
@@ -3003,19 +3003,19 @@
         <v>0.7877999999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>0.634</v>
+        <v>0.6382</v>
       </c>
       <c r="I48" t="n">
-        <v>0.7109</v>
+        <v>0.713</v>
       </c>
       <c r="J48" t="n">
         <v>0.2122</v>
       </c>
       <c r="K48" t="n">
-        <v>0.366</v>
+        <v>0.3618</v>
       </c>
       <c r="L48" t="n">
-        <v>0.2891</v>
+        <v>0.287</v>
       </c>
       <c r="M48" t="n">
         <v>164</v>
@@ -3054,22 +3054,22 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0.7902</v>
+        <v>0.7836</v>
       </c>
       <c r="H49" t="n">
-        <v>0.644</v>
+        <v>0.6391</v>
       </c>
       <c r="I49" t="n">
-        <v>0.7171</v>
+        <v>0.7113</v>
       </c>
       <c r="J49" t="n">
-        <v>0.2098</v>
+        <v>0.2164</v>
       </c>
       <c r="K49" t="n">
-        <v>0.356</v>
+        <v>0.3609</v>
       </c>
       <c r="L49" t="n">
-        <v>0.2829</v>
+        <v>0.2887</v>
       </c>
       <c r="M49" t="n">
         <v>164</v>
@@ -3216,22 +3216,22 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0.4639</v>
+        <v>0.4631</v>
       </c>
       <c r="H52" t="n">
         <v>0.3407</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4023</v>
+        <v>0.4019</v>
       </c>
       <c r="J52" t="n">
-        <v>0.5361</v>
+        <v>0.5369</v>
       </c>
       <c r="K52" t="n">
         <v>0.6593</v>
       </c>
       <c r="L52" t="n">
-        <v>0.5977</v>
+        <v>0.5981</v>
       </c>
       <c r="M52" t="n">
         <v>164</v>
@@ -3270,22 +3270,22 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.7661</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="H53" t="n">
         <v>0.5956</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6808</v>
+        <v>0.6832</v>
       </c>
       <c r="J53" t="n">
-        <v>0.2339</v>
+        <v>0.2293</v>
       </c>
       <c r="K53" t="n">
         <v>0.4044</v>
       </c>
       <c r="L53" t="n">
-        <v>0.3192</v>
+        <v>0.3168</v>
       </c>
       <c r="M53" t="n">
         <v>164</v>
@@ -3324,22 +3324,22 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.885</v>
+        <v>0.8865</v>
       </c>
       <c r="H54" t="n">
-        <v>0.7709</v>
+        <v>0.7851</v>
       </c>
       <c r="I54" t="n">
-        <v>0.828</v>
+        <v>0.8358</v>
       </c>
       <c r="J54" t="n">
-        <v>0.115</v>
+        <v>0.1135</v>
       </c>
       <c r="K54" t="n">
-        <v>0.2291</v>
+        <v>0.2149</v>
       </c>
       <c r="L54" t="n">
-        <v>0.172</v>
+        <v>0.1642</v>
       </c>
       <c r="M54" t="n">
         <v>164</v>
@@ -3378,22 +3378,22 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.8875</v>
+        <v>0.8894</v>
       </c>
       <c r="H55" t="n">
-        <v>0.7824</v>
+        <v>0.7915</v>
       </c>
       <c r="I55" t="n">
-        <v>0.835</v>
+        <v>0.8404</v>
       </c>
       <c r="J55" t="n">
-        <v>0.1125</v>
+        <v>0.1106</v>
       </c>
       <c r="K55" t="n">
-        <v>0.2176</v>
+        <v>0.2085</v>
       </c>
       <c r="L55" t="n">
-        <v>0.165</v>
+        <v>0.1596</v>
       </c>
       <c r="M55" t="n">
         <v>164</v>
@@ -3489,19 +3489,19 @@
         <v>0.6529</v>
       </c>
       <c r="H57" t="n">
-        <v>0.4544</v>
+        <v>0.4616</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5536</v>
+        <v>0.5572</v>
       </c>
       <c r="J57" t="n">
         <v>0.3471</v>
       </c>
       <c r="K57" t="n">
-        <v>0.5456</v>
+        <v>0.5384</v>
       </c>
       <c r="L57" t="n">
-        <v>0.4464</v>
+        <v>0.4428</v>
       </c>
       <c r="M57" t="n">
         <v>164</v>
@@ -3543,19 +3543,19 @@
         <v>0.6906</v>
       </c>
       <c r="H58" t="n">
-        <v>0.5235</v>
+        <v>0.5284</v>
       </c>
       <c r="I58" t="n">
-        <v>0.607</v>
+        <v>0.6095</v>
       </c>
       <c r="J58" t="n">
         <v>0.3094</v>
       </c>
       <c r="K58" t="n">
-        <v>0.4765</v>
+        <v>0.4716</v>
       </c>
       <c r="L58" t="n">
-        <v>0.393</v>
+        <v>0.3905</v>
       </c>
       <c r="M58" t="n">
         <v>164</v>
@@ -3594,22 +3594,22 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.8247</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>0.7265</v>
+        <v>0.7297</v>
       </c>
       <c r="I59" t="n">
-        <v>0.7756</v>
+        <v>0.781</v>
       </c>
       <c r="J59" t="n">
-        <v>0.1753</v>
+        <v>0.1678</v>
       </c>
       <c r="K59" t="n">
-        <v>0.2735</v>
+        <v>0.2703</v>
       </c>
       <c r="L59" t="n">
-        <v>0.2244</v>
+        <v>0.219</v>
       </c>
       <c r="M59" t="n">
         <v>164</v>
@@ -3651,19 +3651,19 @@
         <v>0.8323</v>
       </c>
       <c r="H60" t="n">
-        <v>0.7236</v>
+        <v>0.7284</v>
       </c>
       <c r="I60" t="n">
-        <v>0.778</v>
+        <v>0.7804</v>
       </c>
       <c r="J60" t="n">
         <v>0.1677</v>
       </c>
       <c r="K60" t="n">
-        <v>0.2764</v>
+        <v>0.2716</v>
       </c>
       <c r="L60" t="n">
-        <v>0.222</v>
+        <v>0.2196</v>
       </c>
       <c r="M60" t="n">
         <v>164</v>
@@ -3702,22 +3702,22 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.8597</v>
+        <v>0.8615</v>
       </c>
       <c r="H61" t="n">
-        <v>0.771</v>
+        <v>0.7852</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8154</v>
+        <v>0.8234</v>
       </c>
       <c r="J61" t="n">
-        <v>0.1403</v>
+        <v>0.1385</v>
       </c>
       <c r="K61" t="n">
-        <v>0.229</v>
+        <v>0.2148</v>
       </c>
       <c r="L61" t="n">
-        <v>0.1846</v>
+        <v>0.1766</v>
       </c>
       <c r="M61" t="n">
         <v>164</v>
@@ -3813,19 +3813,19 @@
         <v>0.8003</v>
       </c>
       <c r="H63" t="n">
-        <v>0.6428</v>
+        <v>0.6505</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7216</v>
+        <v>0.7254</v>
       </c>
       <c r="J63" t="n">
         <v>0.1997</v>
       </c>
       <c r="K63" t="n">
-        <v>0.3572</v>
+        <v>0.3495</v>
       </c>
       <c r="L63" t="n">
-        <v>0.2784</v>
+        <v>0.2746</v>
       </c>
       <c r="M63" t="n">
         <v>164</v>
@@ -3918,22 +3918,22 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0.7015</v>
+        <v>0.7003</v>
       </c>
       <c r="H65" t="n">
-        <v>0.5593</v>
+        <v>0.5602</v>
       </c>
       <c r="I65" t="n">
-        <v>0.6304</v>
+        <v>0.6302</v>
       </c>
       <c r="J65" t="n">
-        <v>0.2985</v>
+        <v>0.2997</v>
       </c>
       <c r="K65" t="n">
-        <v>0.4407</v>
+        <v>0.4398</v>
       </c>
       <c r="L65" t="n">
-        <v>0.3696</v>
+        <v>0.3698</v>
       </c>
       <c r="M65" t="n">
         <v>164</v>
@@ -3972,22 +3972,22 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.5738</v>
+        <v>0.6884</v>
       </c>
       <c r="H66" t="n">
-        <v>0.4891</v>
+        <v>0.578</v>
       </c>
       <c r="I66" t="n">
-        <v>0.5314</v>
+        <v>0.6332</v>
       </c>
       <c r="J66" t="n">
-        <v>0.4262</v>
+        <v>0.3116</v>
       </c>
       <c r="K66" t="n">
-        <v>0.5109</v>
+        <v>0.422</v>
       </c>
       <c r="L66" t="n">
-        <v>0.4686</v>
+        <v>0.3668</v>
       </c>
       <c r="M66" t="n">
         <v>164</v>
@@ -4026,22 +4026,22 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.7895</v>
+        <v>0.7919</v>
       </c>
       <c r="H67" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.6175</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7024</v>
+        <v>0.7047</v>
       </c>
       <c r="J67" t="n">
-        <v>0.2105</v>
+        <v>0.2081</v>
       </c>
       <c r="K67" t="n">
-        <v>0.3846</v>
+        <v>0.3825</v>
       </c>
       <c r="L67" t="n">
-        <v>0.2976</v>
+        <v>0.2953</v>
       </c>
       <c r="M67" t="n">
         <v>164</v>
@@ -4242,22 +4242,22 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.6141</v>
+        <v>0.6181</v>
       </c>
       <c r="H71" t="n">
-        <v>0.457</v>
+        <v>0.4617</v>
       </c>
       <c r="I71" t="n">
-        <v>0.5356</v>
+        <v>0.5399</v>
       </c>
       <c r="J71" t="n">
-        <v>0.3859</v>
+        <v>0.3819</v>
       </c>
       <c r="K71" t="n">
-        <v>0.543</v>
+        <v>0.5383</v>
       </c>
       <c r="L71" t="n">
-        <v>0.4644</v>
+        <v>0.4601</v>
       </c>
       <c r="M71" t="n">
         <v>164</v>
@@ -4296,22 +4296,22 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.802</v>
+        <v>0.8032</v>
       </c>
       <c r="H72" t="n">
-        <v>0.6523</v>
+        <v>0.6571</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7272</v>
+        <v>0.7302</v>
       </c>
       <c r="J72" t="n">
-        <v>0.198</v>
+        <v>0.1968</v>
       </c>
       <c r="K72" t="n">
-        <v>0.3477</v>
+        <v>0.3429</v>
       </c>
       <c r="L72" t="n">
-        <v>0.2728</v>
+        <v>0.2698</v>
       </c>
       <c r="M72" t="n">
         <v>164</v>
@@ -4350,22 +4350,22 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.8366</v>
+        <v>0.8442</v>
       </c>
       <c r="H73" t="n">
         <v>0.7727000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8047</v>
+        <v>0.8084</v>
       </c>
       <c r="J73" t="n">
-        <v>0.1634</v>
+        <v>0.1558</v>
       </c>
       <c r="K73" t="n">
         <v>0.2273</v>
       </c>
       <c r="L73" t="n">
-        <v>0.1953</v>
+        <v>0.1916</v>
       </c>
       <c r="M73" t="n">
         <v>164</v>
@@ -4407,19 +4407,19 @@
         <v>0.7541</v>
       </c>
       <c r="H74" t="n">
-        <v>0.6074000000000001</v>
+        <v>0.6133</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6808</v>
+        <v>0.6837</v>
       </c>
       <c r="J74" t="n">
         <v>0.2459</v>
       </c>
       <c r="K74" t="n">
-        <v>0.3926</v>
+        <v>0.3867</v>
       </c>
       <c r="L74" t="n">
-        <v>0.3192</v>
+        <v>0.3163</v>
       </c>
       <c r="M74" t="n">
         <v>164</v>
@@ -4458,22 +4458,22 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.7538</v>
+        <v>0.7549</v>
       </c>
       <c r="H75" t="n">
-        <v>0.5977</v>
+        <v>0.6009</v>
       </c>
       <c r="I75" t="n">
-        <v>0.6758</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="J75" t="n">
-        <v>0.2462</v>
+        <v>0.2451</v>
       </c>
       <c r="K75" t="n">
-        <v>0.4023</v>
+        <v>0.3991</v>
       </c>
       <c r="L75" t="n">
-        <v>0.3242</v>
+        <v>0.3221</v>
       </c>
       <c r="M75" t="n">
         <v>164</v>
@@ -4512,22 +4512,22 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.7982</v>
+        <v>0.7931</v>
       </c>
       <c r="H76" t="n">
-        <v>0.6439</v>
+        <v>0.6321</v>
       </c>
       <c r="I76" t="n">
-        <v>0.721</v>
+        <v>0.7126</v>
       </c>
       <c r="J76" t="n">
-        <v>0.2018</v>
+        <v>0.2069</v>
       </c>
       <c r="K76" t="n">
-        <v>0.3561</v>
+        <v>0.3679</v>
       </c>
       <c r="L76" t="n">
-        <v>0.279</v>
+        <v>0.2874</v>
       </c>
       <c r="M76" t="n">
         <v>164</v>
@@ -4620,22 +4620,22 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.5281</v>
+        <v>0.5314</v>
       </c>
       <c r="H78" t="n">
         <v>0.3592</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4436</v>
+        <v>0.4453</v>
       </c>
       <c r="J78" t="n">
-        <v>0.4719</v>
+        <v>0.4686</v>
       </c>
       <c r="K78" t="n">
         <v>0.6408</v>
       </c>
       <c r="L78" t="n">
-        <v>0.5564</v>
+        <v>0.5547</v>
       </c>
       <c r="M78" t="n">
         <v>164</v>
@@ -4674,22 +4674,22 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0.4748</v>
+        <v>0.4745</v>
       </c>
       <c r="H79" t="n">
         <v>0.3511</v>
       </c>
       <c r="I79" t="n">
-        <v>0.413</v>
+        <v>0.4128</v>
       </c>
       <c r="J79" t="n">
-        <v>0.5252</v>
+        <v>0.5255</v>
       </c>
       <c r="K79" t="n">
         <v>0.6489</v>
       </c>
       <c r="L79" t="n">
-        <v>0.587</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="M79" t="n">
         <v>164</v>
@@ -4731,19 +4731,19 @@
         <v>0.7292999999999999</v>
       </c>
       <c r="H80" t="n">
-        <v>0.5754</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>0.6524</v>
+        <v>0.6532</v>
       </c>
       <c r="J80" t="n">
         <v>0.2707</v>
       </c>
       <c r="K80" t="n">
-        <v>0.4246</v>
+        <v>0.4229</v>
       </c>
       <c r="L80" t="n">
-        <v>0.3476</v>
+        <v>0.3468</v>
       </c>
       <c r="M80" t="n">
         <v>164</v>
@@ -4785,19 +4785,19 @@
         <v>0.8757</v>
       </c>
       <c r="H81" t="n">
-        <v>0.7877</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>0.8317</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="J81" t="n">
         <v>0.1243</v>
       </c>
       <c r="K81" t="n">
-        <v>0.2123</v>
+        <v>0.2092</v>
       </c>
       <c r="L81" t="n">
-        <v>0.1683</v>
+        <v>0.1668</v>
       </c>
       <c r="M81" t="n">
         <v>164</v>
@@ -4944,22 +4944,22 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.6131</v>
+        <v>0.615</v>
       </c>
       <c r="H84" t="n">
         <v>0.4849</v>
       </c>
       <c r="I84" t="n">
-        <v>0.549</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="J84" t="n">
-        <v>0.3869</v>
+        <v>0.385</v>
       </c>
       <c r="K84" t="n">
         <v>0.5151</v>
       </c>
       <c r="L84" t="n">
-        <v>0.451</v>
+        <v>0.4501</v>
       </c>
       <c r="M84" t="n">
         <v>164</v>
@@ -4998,22 +4998,22 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0.6398</v>
+        <v>0.6502</v>
       </c>
       <c r="H85" t="n">
-        <v>0.5011</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>0.5704</v>
+        <v>0.5774</v>
       </c>
       <c r="J85" t="n">
-        <v>0.3602</v>
+        <v>0.3498</v>
       </c>
       <c r="K85" t="n">
-        <v>0.4989</v>
+        <v>0.4955</v>
       </c>
       <c r="L85" t="n">
-        <v>0.4296</v>
+        <v>0.4226</v>
       </c>
       <c r="M85" t="n">
         <v>164</v>
@@ -5109,19 +5109,19 @@
         <v>0.6427</v>
       </c>
       <c r="H87" t="n">
-        <v>0.503</v>
+        <v>0.5118</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5729</v>
+        <v>0.5772</v>
       </c>
       <c r="J87" t="n">
         <v>0.3573</v>
       </c>
       <c r="K87" t="n">
-        <v>0.497</v>
+        <v>0.4882</v>
       </c>
       <c r="L87" t="n">
-        <v>0.4271</v>
+        <v>0.4228</v>
       </c>
       <c r="M87" t="n">
         <v>164</v>
@@ -5160,22 +5160,22 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0.2804</v>
+        <v>0.2764</v>
       </c>
       <c r="H88" t="n">
-        <v>0.1635</v>
+        <v>0.1604</v>
       </c>
       <c r="I88" t="n">
-        <v>0.222</v>
+        <v>0.2184</v>
       </c>
       <c r="J88" t="n">
-        <v>0.7196</v>
+        <v>0.7236</v>
       </c>
       <c r="K88" t="n">
-        <v>0.8365</v>
+        <v>0.8396</v>
       </c>
       <c r="L88" t="n">
-        <v>0.778</v>
+        <v>0.7816</v>
       </c>
       <c r="M88" t="n">
         <v>164</v>
@@ -5271,19 +5271,19 @@
         <v>0.3351</v>
       </c>
       <c r="H90" t="n">
-        <v>0.2132</v>
+        <v>0.2071</v>
       </c>
       <c r="I90" t="n">
-        <v>0.2742</v>
+        <v>0.2711</v>
       </c>
       <c r="J90" t="n">
         <v>0.6649</v>
       </c>
       <c r="K90" t="n">
-        <v>0.7868000000000001</v>
+        <v>0.7929</v>
       </c>
       <c r="L90" t="n">
-        <v>0.7258</v>
+        <v>0.7289</v>
       </c>
       <c r="M90" t="n">
         <v>164</v>
@@ -5322,22 +5322,22 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0.3796</v>
+        <v>0.3724</v>
       </c>
       <c r="H91" t="n">
-        <v>0.2349</v>
+        <v>0.2339</v>
       </c>
       <c r="I91" t="n">
-        <v>0.3073</v>
+        <v>0.3032</v>
       </c>
       <c r="J91" t="n">
-        <v>0.6204</v>
+        <v>0.6276</v>
       </c>
       <c r="K91" t="n">
-        <v>0.7651</v>
+        <v>0.7661</v>
       </c>
       <c r="L91" t="n">
-        <v>0.6927</v>
+        <v>0.6968</v>
       </c>
       <c r="M91" t="n">
         <v>164</v>
@@ -5376,22 +5376,22 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>0.3033</v>
+        <v>0.3645</v>
       </c>
       <c r="H92" t="n">
-        <v>0.1701</v>
+        <v>0.2293</v>
       </c>
       <c r="I92" t="n">
-        <v>0.2367</v>
+        <v>0.2969</v>
       </c>
       <c r="J92" t="n">
-        <v>0.6967</v>
+        <v>0.6355</v>
       </c>
       <c r="K92" t="n">
-        <v>0.8299</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="L92" t="n">
-        <v>0.7633</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="M92" t="n">
         <v>164</v>
@@ -5430,22 +5430,22 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>0.4518</v>
+        <v>0.4501</v>
       </c>
       <c r="H93" t="n">
-        <v>0.3168</v>
+        <v>0.3109</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3843</v>
+        <v>0.3805</v>
       </c>
       <c r="J93" t="n">
-        <v>0.5482</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="K93" t="n">
-        <v>0.6832</v>
+        <v>0.6891</v>
       </c>
       <c r="L93" t="n">
-        <v>0.6157</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="M93" t="n">
         <v>164</v>
@@ -5487,19 +5487,19 @@
         <v>0.658</v>
       </c>
       <c r="H94" t="n">
-        <v>0.5079</v>
+        <v>0.5068</v>
       </c>
       <c r="I94" t="n">
-        <v>0.583</v>
+        <v>0.5824</v>
       </c>
       <c r="J94" t="n">
         <v>0.342</v>
       </c>
       <c r="K94" t="n">
-        <v>0.4921</v>
+        <v>0.4932</v>
       </c>
       <c r="L94" t="n">
-        <v>0.417</v>
+        <v>0.4176</v>
       </c>
       <c r="M94" t="n">
         <v>164</v>
@@ -5538,22 +5538,22 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>0.3404</v>
+        <v>0.3332</v>
       </c>
       <c r="H95" t="n">
         <v>0.2026</v>
       </c>
       <c r="I95" t="n">
-        <v>0.2715</v>
+        <v>0.2679</v>
       </c>
       <c r="J95" t="n">
-        <v>0.6596</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="K95" t="n">
         <v>0.7974</v>
       </c>
       <c r="L95" t="n">
-        <v>0.7285</v>
+        <v>0.7321</v>
       </c>
       <c r="M95" t="n">
         <v>164</v>
@@ -5592,22 +5592,22 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>0.7497</v>
+        <v>0.7524</v>
       </c>
       <c r="H96" t="n">
-        <v>0.6052</v>
+        <v>0.608</v>
       </c>
       <c r="I96" t="n">
-        <v>0.6774</v>
+        <v>0.6802</v>
       </c>
       <c r="J96" t="n">
-        <v>0.2503</v>
+        <v>0.2476</v>
       </c>
       <c r="K96" t="n">
-        <v>0.3948</v>
+        <v>0.392</v>
       </c>
       <c r="L96" t="n">
-        <v>0.3226</v>
+        <v>0.3198</v>
       </c>
       <c r="M96" t="n">
         <v>164</v>
@@ -5646,22 +5646,22 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>0.287</v>
+        <v>0.2832</v>
       </c>
       <c r="H97" t="n">
-        <v>0.1822</v>
+        <v>0.1796</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2346</v>
+        <v>0.2314</v>
       </c>
       <c r="J97" t="n">
-        <v>0.713</v>
+        <v>0.7168</v>
       </c>
       <c r="K97" t="n">
-        <v>0.8178</v>
+        <v>0.8204</v>
       </c>
       <c r="L97" t="n">
-        <v>0.7654</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="M97" t="n">
         <v>164</v>
@@ -5754,22 +5754,22 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0.6288</v>
+        <v>0.6327</v>
       </c>
       <c r="H99" t="n">
-        <v>0.4944</v>
+        <v>0.495</v>
       </c>
       <c r="I99" t="n">
-        <v>0.5616</v>
+        <v>0.5638</v>
       </c>
       <c r="J99" t="n">
-        <v>0.3712</v>
+        <v>0.3673</v>
       </c>
       <c r="K99" t="n">
-        <v>0.5056</v>
+        <v>0.505</v>
       </c>
       <c r="L99" t="n">
-        <v>0.4384</v>
+        <v>0.4362</v>
       </c>
       <c r="M99" t="n">
         <v>164</v>
@@ -5811,19 +5811,19 @@
         <v>0.4278</v>
       </c>
       <c r="H100" t="n">
-        <v>0.2882</v>
+        <v>0.283</v>
       </c>
       <c r="I100" t="n">
-        <v>0.358</v>
+        <v>0.3554</v>
       </c>
       <c r="J100" t="n">
         <v>0.5722</v>
       </c>
       <c r="K100" t="n">
-        <v>0.7118</v>
+        <v>0.717</v>
       </c>
       <c r="L100" t="n">
-        <v>0.642</v>
+        <v>0.6446</v>
       </c>
       <c r="M100" t="n">
         <v>164</v>
@@ -5916,22 +5916,22 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>0.466</v>
+        <v>0.4509</v>
       </c>
       <c r="H102" t="n">
-        <v>0.3704</v>
+        <v>0.3568</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4182</v>
+        <v>0.4039</v>
       </c>
       <c r="J102" t="n">
-        <v>0.534</v>
+        <v>0.5491</v>
       </c>
       <c r="K102" t="n">
-        <v>0.6296</v>
+        <v>0.6432</v>
       </c>
       <c r="L102" t="n">
-        <v>0.5818</v>
+        <v>0.5961</v>
       </c>
       <c r="M102" t="n">
         <v>164</v>
@@ -5970,22 +5970,22 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0.7252999999999999</v>
+        <v>0.7271</v>
       </c>
       <c r="H103" t="n">
-        <v>0.6129</v>
+        <v>0.6151</v>
       </c>
       <c r="I103" t="n">
-        <v>0.6691</v>
+        <v>0.6711</v>
       </c>
       <c r="J103" t="n">
-        <v>0.2747</v>
+        <v>0.2729</v>
       </c>
       <c r="K103" t="n">
-        <v>0.3871</v>
+        <v>0.3849</v>
       </c>
       <c r="L103" t="n">
-        <v>0.3309</v>
+        <v>0.3289</v>
       </c>
       <c r="M103" t="n">
         <v>164</v>
@@ -6024,22 +6024,22 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>0.2753</v>
+        <v>0.2707</v>
       </c>
       <c r="H104" t="n">
-        <v>0.1574</v>
+        <v>0.155</v>
       </c>
       <c r="I104" t="n">
-        <v>0.2164</v>
+        <v>0.2128</v>
       </c>
       <c r="J104" t="n">
-        <v>0.7247</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="K104" t="n">
-        <v>0.8426</v>
+        <v>0.845</v>
       </c>
       <c r="L104" t="n">
-        <v>0.7836</v>
+        <v>0.7872</v>
       </c>
       <c r="M104" t="n">
         <v>164</v>
@@ -6078,22 +6078,22 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>0.2725</v>
+        <v>0.2699</v>
       </c>
       <c r="H105" t="n">
-        <v>0.1523</v>
+        <v>0.1481</v>
       </c>
       <c r="I105" t="n">
-        <v>0.2124</v>
+        <v>0.209</v>
       </c>
       <c r="J105" t="n">
-        <v>0.7275</v>
+        <v>0.7301</v>
       </c>
       <c r="K105" t="n">
-        <v>0.8477</v>
+        <v>0.8519</v>
       </c>
       <c r="L105" t="n">
-        <v>0.7876</v>
+        <v>0.791</v>
       </c>
       <c r="M105" t="n">
         <v>164</v>
@@ -6135,19 +6135,19 @@
         <v>0.3951</v>
       </c>
       <c r="H106" t="n">
-        <v>0.2463</v>
+        <v>0.2432</v>
       </c>
       <c r="I106" t="n">
-        <v>0.3207</v>
+        <v>0.3192</v>
       </c>
       <c r="J106" t="n">
         <v>0.6049</v>
       </c>
       <c r="K106" t="n">
-        <v>0.7537</v>
+        <v>0.7568</v>
       </c>
       <c r="L106" t="n">
-        <v>0.6793</v>
+        <v>0.6808</v>
       </c>
       <c r="M106" t="n">
         <v>164</v>
@@ -6186,22 +6186,22 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>0.7000999999999999</v>
+        <v>0.7045</v>
       </c>
       <c r="H107" t="n">
-        <v>0.5854</v>
+        <v>0.5901</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6427</v>
+        <v>0.6473</v>
       </c>
       <c r="J107" t="n">
-        <v>0.2999</v>
+        <v>0.2955</v>
       </c>
       <c r="K107" t="n">
-        <v>0.4146</v>
+        <v>0.4099</v>
       </c>
       <c r="L107" t="n">
-        <v>0.3573</v>
+        <v>0.3527</v>
       </c>
       <c r="M107" t="n">
         <v>164</v>
@@ -6240,22 +6240,22 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>0.6723</v>
+        <v>0.6754</v>
       </c>
       <c r="H108" t="n">
-        <v>0.5238</v>
+        <v>0.5255</v>
       </c>
       <c r="I108" t="n">
-        <v>0.598</v>
+        <v>0.6004</v>
       </c>
       <c r="J108" t="n">
-        <v>0.3277</v>
+        <v>0.3246</v>
       </c>
       <c r="K108" t="n">
-        <v>0.4762</v>
+        <v>0.4745</v>
       </c>
       <c r="L108" t="n">
-        <v>0.402</v>
+        <v>0.3996</v>
       </c>
       <c r="M108" t="n">
         <v>164</v>
@@ -6294,22 +6294,22 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>0.7799</v>
+        <v>0.7825</v>
       </c>
       <c r="H109" t="n">
-        <v>0.6297</v>
+        <v>0.6327</v>
       </c>
       <c r="I109" t="n">
-        <v>0.7048</v>
+        <v>0.7076</v>
       </c>
       <c r="J109" t="n">
-        <v>0.2201</v>
+        <v>0.2175</v>
       </c>
       <c r="K109" t="n">
-        <v>0.3703</v>
+        <v>0.3673</v>
       </c>
       <c r="L109" t="n">
-        <v>0.2952</v>
+        <v>0.2924</v>
       </c>
       <c r="M109" t="n">
         <v>164</v>
@@ -6348,22 +6348,22 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>0.3517</v>
+        <v>0.3472</v>
       </c>
       <c r="H110" t="n">
         <v>0.2533</v>
       </c>
       <c r="I110" t="n">
-        <v>0.3025</v>
+        <v>0.3002</v>
       </c>
       <c r="J110" t="n">
-        <v>0.6483</v>
+        <v>0.6528</v>
       </c>
       <c r="K110" t="n">
         <v>0.7467</v>
       </c>
       <c r="L110" t="n">
-        <v>0.6975</v>
+        <v>0.6998</v>
       </c>
       <c r="M110" t="n">
         <v>164</v>
@@ -6402,22 +6402,22 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>0.3564</v>
+        <v>0.3517</v>
       </c>
       <c r="H111" t="n">
-        <v>0.2096</v>
+        <v>0.2045</v>
       </c>
       <c r="I111" t="n">
-        <v>0.283</v>
+        <v>0.2781</v>
       </c>
       <c r="J111" t="n">
-        <v>0.6435999999999999</v>
+        <v>0.6483</v>
       </c>
       <c r="K111" t="n">
-        <v>0.7904</v>
+        <v>0.7955</v>
       </c>
       <c r="L111" t="n">
-        <v>0.717</v>
+        <v>0.7219</v>
       </c>
       <c r="M111" t="n">
         <v>164</v>
@@ -6510,22 +6510,22 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>0.2812</v>
+        <v>0.2784</v>
       </c>
       <c r="H113" t="n">
-        <v>0.1491</v>
+        <v>0.1465</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2152</v>
+        <v>0.2124</v>
       </c>
       <c r="J113" t="n">
-        <v>0.7188</v>
+        <v>0.7216</v>
       </c>
       <c r="K113" t="n">
-        <v>0.8509</v>
+        <v>0.8535</v>
       </c>
       <c r="L113" t="n">
-        <v>0.7848000000000001</v>
+        <v>0.7876</v>
       </c>
       <c r="M113" t="n">
         <v>164</v>
@@ -6618,22 +6618,22 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>0.3494</v>
+        <v>0.3438</v>
       </c>
       <c r="H115" t="n">
         <v>0.1814</v>
       </c>
       <c r="I115" t="n">
-        <v>0.2654</v>
+        <v>0.2626</v>
       </c>
       <c r="J115" t="n">
-        <v>0.6506</v>
+        <v>0.6562</v>
       </c>
       <c r="K115" t="n">
         <v>0.8186</v>
       </c>
       <c r="L115" t="n">
-        <v>0.7346</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="M115" t="n">
         <v>164</v>
@@ -6675,19 +6675,19 @@
         <v>0.3665</v>
       </c>
       <c r="H116" t="n">
-        <v>0.2271</v>
+        <v>0.2169</v>
       </c>
       <c r="I116" t="n">
-        <v>0.2968</v>
+        <v>0.2917</v>
       </c>
       <c r="J116" t="n">
         <v>0.6335</v>
       </c>
       <c r="K116" t="n">
-        <v>0.7729</v>
+        <v>0.7831</v>
       </c>
       <c r="L116" t="n">
-        <v>0.7032</v>
+        <v>0.7083</v>
       </c>
       <c r="M116" t="n">
         <v>164</v>
@@ -6726,22 +6726,22 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>0.3087</v>
+        <v>0.3749</v>
       </c>
       <c r="H117" t="n">
-        <v>0.1625</v>
+        <v>0.2191</v>
       </c>
       <c r="I117" t="n">
-        <v>0.2356</v>
+        <v>0.297</v>
       </c>
       <c r="J117" t="n">
-        <v>0.6913</v>
+        <v>0.6251</v>
       </c>
       <c r="K117" t="n">
-        <v>0.8375</v>
+        <v>0.7809</v>
       </c>
       <c r="L117" t="n">
-        <v>0.7644</v>
+        <v>0.703</v>
       </c>
       <c r="M117" t="n">
         <v>164</v>
@@ -6780,22 +6780,22 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>0.4362</v>
+        <v>0.4342</v>
       </c>
       <c r="H118" t="n">
-        <v>0.29</v>
+        <v>0.2805</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3631</v>
+        <v>0.3574</v>
       </c>
       <c r="J118" t="n">
-        <v>0.5638</v>
+        <v>0.5658</v>
       </c>
       <c r="K118" t="n">
-        <v>0.71</v>
+        <v>0.7195</v>
       </c>
       <c r="L118" t="n">
-        <v>0.6369</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="M118" t="n">
         <v>164</v>
@@ -6834,22 +6834,22 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0.637</v>
+        <v>0.6403</v>
       </c>
       <c r="H119" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.5203</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5748</v>
+        <v>0.5803</v>
       </c>
       <c r="J119" t="n">
-        <v>0.363</v>
+        <v>0.3597</v>
       </c>
       <c r="K119" t="n">
-        <v>0.4874</v>
+        <v>0.4797</v>
       </c>
       <c r="L119" t="n">
-        <v>0.4252</v>
+        <v>0.4197</v>
       </c>
       <c r="M119" t="n">
         <v>164</v>
@@ -6888,22 +6888,22 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>0.309</v>
+        <v>0.3025</v>
       </c>
       <c r="H120" t="n">
-        <v>0.2028</v>
+        <v>0.1982</v>
       </c>
       <c r="I120" t="n">
-        <v>0.2559</v>
+        <v>0.2503</v>
       </c>
       <c r="J120" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6975</v>
       </c>
       <c r="K120" t="n">
-        <v>0.7972</v>
+        <v>0.8018</v>
       </c>
       <c r="L120" t="n">
-        <v>0.7441</v>
+        <v>0.7497</v>
       </c>
       <c r="M120" t="n">
         <v>164</v>
@@ -6942,22 +6942,22 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>0.7309</v>
+        <v>0.7327</v>
       </c>
       <c r="H121" t="n">
-        <v>0.6002999999999999</v>
+        <v>0.6025</v>
       </c>
       <c r="I121" t="n">
-        <v>0.6656</v>
+        <v>0.6676</v>
       </c>
       <c r="J121" t="n">
-        <v>0.2691</v>
+        <v>0.2673</v>
       </c>
       <c r="K121" t="n">
-        <v>0.3997</v>
+        <v>0.3975</v>
       </c>
       <c r="L121" t="n">
-        <v>0.3344</v>
+        <v>0.3324</v>
       </c>
       <c r="M121" t="n">
         <v>164</v>
@@ -6996,22 +6996,22 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0.3044</v>
+        <v>0.2961</v>
       </c>
       <c r="H122" t="n">
-        <v>0.1783</v>
+        <v>0.175</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2414</v>
+        <v>0.2356</v>
       </c>
       <c r="J122" t="n">
-        <v>0.6956</v>
+        <v>0.7039</v>
       </c>
       <c r="K122" t="n">
-        <v>0.8217</v>
+        <v>0.825</v>
       </c>
       <c r="L122" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.7644</v>
       </c>
       <c r="M122" t="n">
         <v>164</v>
@@ -7104,22 +7104,22 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.6226</v>
       </c>
       <c r="H124" t="n">
         <v>0.5004999999999999</v>
       </c>
       <c r="I124" t="n">
-        <v>0.5579</v>
+        <v>0.5616</v>
       </c>
       <c r="J124" t="n">
-        <v>0.3846</v>
+        <v>0.3774</v>
       </c>
       <c r="K124" t="n">
         <v>0.4995</v>
       </c>
       <c r="L124" t="n">
-        <v>0.4421</v>
+        <v>0.4384</v>
       </c>
       <c r="M124" t="n">
         <v>164</v>
@@ -7215,19 +7215,19 @@
         <v>0.4155</v>
       </c>
       <c r="H126" t="n">
-        <v>0.2737</v>
+        <v>0.271</v>
       </c>
       <c r="I126" t="n">
-        <v>0.3446</v>
+        <v>0.3432</v>
       </c>
       <c r="J126" t="n">
         <v>0.5845</v>
       </c>
       <c r="K126" t="n">
-        <v>0.7262999999999999</v>
+        <v>0.729</v>
       </c>
       <c r="L126" t="n">
-        <v>0.6554</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="M126" t="n">
         <v>164</v>
@@ -7266,22 +7266,22 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>0.4423</v>
+        <v>0.4207</v>
       </c>
       <c r="H127" t="n">
-        <v>0.3509</v>
+        <v>0.3362</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3966</v>
+        <v>0.3784</v>
       </c>
       <c r="J127" t="n">
-        <v>0.5577</v>
+        <v>0.5793</v>
       </c>
       <c r="K127" t="n">
-        <v>0.6491</v>
+        <v>0.6637999999999999</v>
       </c>
       <c r="L127" t="n">
-        <v>0.6034</v>
+        <v>0.6216</v>
       </c>
       <c r="M127" t="n">
         <v>164</v>
@@ -7320,22 +7320,22 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>0.7249</v>
+        <v>0.73</v>
       </c>
       <c r="H128" t="n">
-        <v>0.5687</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="I128" t="n">
-        <v>0.6468</v>
+        <v>0.651</v>
       </c>
       <c r="J128" t="n">
-        <v>0.2751</v>
+        <v>0.27</v>
       </c>
       <c r="K128" t="n">
-        <v>0.4313</v>
+        <v>0.4279</v>
       </c>
       <c r="L128" t="n">
-        <v>0.3532</v>
+        <v>0.349</v>
       </c>
       <c r="M128" t="n">
         <v>164</v>
@@ -7374,22 +7374,22 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>0.2597</v>
+        <v>0.2605</v>
       </c>
       <c r="H129" t="n">
-        <v>0.1463</v>
+        <v>0.1452</v>
       </c>
       <c r="I129" t="n">
-        <v>0.203</v>
+        <v>0.2028</v>
       </c>
       <c r="J129" t="n">
-        <v>0.7403</v>
+        <v>0.7395</v>
       </c>
       <c r="K129" t="n">
-        <v>0.8537</v>
+        <v>0.8548</v>
       </c>
       <c r="L129" t="n">
-        <v>0.797</v>
+        <v>0.7972</v>
       </c>
       <c r="M129" t="n">
         <v>164</v>
@@ -7428,22 +7428,22 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>0.2662</v>
+        <v>0.2621</v>
       </c>
       <c r="H130" t="n">
-        <v>0.1445</v>
+        <v>0.1417</v>
       </c>
       <c r="I130" t="n">
-        <v>0.2053</v>
+        <v>0.2019</v>
       </c>
       <c r="J130" t="n">
-        <v>0.7338</v>
+        <v>0.7379</v>
       </c>
       <c r="K130" t="n">
-        <v>0.8555</v>
+        <v>0.8583</v>
       </c>
       <c r="L130" t="n">
-        <v>0.7947</v>
+        <v>0.7981</v>
       </c>
       <c r="M130" t="n">
         <v>164</v>
@@ -7485,19 +7485,19 @@
         <v>0.4106</v>
       </c>
       <c r="H131" t="n">
-        <v>0.242</v>
+        <v>0.2388</v>
       </c>
       <c r="I131" t="n">
-        <v>0.3263</v>
+        <v>0.3247</v>
       </c>
       <c r="J131" t="n">
         <v>0.5894</v>
       </c>
       <c r="K131" t="n">
-        <v>0.758</v>
+        <v>0.7612</v>
       </c>
       <c r="L131" t="n">
-        <v>0.6737</v>
+        <v>0.6753</v>
       </c>
       <c r="M131" t="n">
         <v>164</v>
@@ -7536,22 +7536,22 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6927</v>
       </c>
       <c r="H132" t="n">
-        <v>0.5544</v>
+        <v>0.5591</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6217</v>
+        <v>0.6259</v>
       </c>
       <c r="J132" t="n">
-        <v>0.311</v>
+        <v>0.3073</v>
       </c>
       <c r="K132" t="n">
-        <v>0.4456</v>
+        <v>0.4409</v>
       </c>
       <c r="L132" t="n">
-        <v>0.3783</v>
+        <v>0.3741</v>
       </c>
       <c r="M132" t="n">
         <v>164</v>
@@ -7590,22 +7590,22 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>0.6665</v>
+        <v>0.669</v>
       </c>
       <c r="H133" t="n">
-        <v>0.5067</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="I133" t="n">
-        <v>0.5866</v>
+        <v>0.5903</v>
       </c>
       <c r="J133" t="n">
-        <v>0.3335</v>
+        <v>0.331</v>
       </c>
       <c r="K133" t="n">
-        <v>0.4933</v>
+        <v>0.4884</v>
       </c>
       <c r="L133" t="n">
-        <v>0.4134</v>
+        <v>0.4097</v>
       </c>
       <c r="M133" t="n">
         <v>164</v>
@@ -7644,22 +7644,22 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="H134" t="n">
-        <v>0.6357</v>
+        <v>0.6427</v>
       </c>
       <c r="I134" t="n">
-        <v>0.7037</v>
+        <v>0.7087</v>
       </c>
       <c r="J134" t="n">
-        <v>0.2283</v>
+        <v>0.2253</v>
       </c>
       <c r="K134" t="n">
-        <v>0.3643</v>
+        <v>0.3573</v>
       </c>
       <c r="L134" t="n">
-        <v>0.2963</v>
+        <v>0.2913</v>
       </c>
       <c r="M134" t="n">
         <v>164</v>
@@ -7698,22 +7698,22 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>0.3293</v>
+        <v>0.3226</v>
       </c>
       <c r="H135" t="n">
-        <v>0.237</v>
+        <v>0.2356</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2832</v>
+        <v>0.2791</v>
       </c>
       <c r="J135" t="n">
-        <v>0.6707</v>
+        <v>0.6774</v>
       </c>
       <c r="K135" t="n">
-        <v>0.763</v>
+        <v>0.7644</v>
       </c>
       <c r="L135" t="n">
-        <v>0.7168</v>
+        <v>0.7209</v>
       </c>
       <c r="M135" t="n">
         <v>164</v>
@@ -7752,22 +7752,22 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>0.3534</v>
+        <v>0.3529</v>
       </c>
       <c r="H136" t="n">
-        <v>0.203</v>
+        <v>0.2004</v>
       </c>
       <c r="I136" t="n">
-        <v>0.2782</v>
+        <v>0.2766</v>
       </c>
       <c r="J136" t="n">
-        <v>0.6466</v>
+        <v>0.6471</v>
       </c>
       <c r="K136" t="n">
-        <v>0.797</v>
+        <v>0.7996</v>
       </c>
       <c r="L136" t="n">
-        <v>0.7218</v>
+        <v>0.7234</v>
       </c>
       <c r="M136" t="n">
         <v>164</v>
@@ -7806,22 +7806,22 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>0.2437</v>
+        <v>0.2289</v>
       </c>
       <c r="H137" t="n">
         <v>0.1366</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1901</v>
+        <v>0.1828</v>
       </c>
       <c r="J137" t="n">
-        <v>0.7563</v>
+        <v>0.7711</v>
       </c>
       <c r="K137" t="n">
         <v>0.8633999999999999</v>
       </c>
       <c r="L137" t="n">
-        <v>0.8099</v>
+        <v>0.8172</v>
       </c>
       <c r="M137" t="n">
         <v>164</v>
@@ -7860,22 +7860,22 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>0.4194</v>
+        <v>0.4212</v>
       </c>
       <c r="H138" t="n">
-        <v>0.2534</v>
+        <v>0.2523</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3364</v>
+        <v>0.3368</v>
       </c>
       <c r="J138" t="n">
-        <v>0.5806</v>
+        <v>0.5788</v>
       </c>
       <c r="K138" t="n">
-        <v>0.7466</v>
+        <v>0.7477</v>
       </c>
       <c r="L138" t="n">
-        <v>0.6636</v>
+        <v>0.6632</v>
       </c>
       <c r="M138" t="n">
         <v>164</v>
@@ -7917,19 +7917,19 @@
         <v>0.2761</v>
       </c>
       <c r="H139" t="n">
-        <v>0.1653</v>
+        <v>0.162</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2207</v>
+        <v>0.219</v>
       </c>
       <c r="J139" t="n">
         <v>0.7239</v>
       </c>
       <c r="K139" t="n">
-        <v>0.8347</v>
+        <v>0.838</v>
       </c>
       <c r="L139" t="n">
-        <v>0.7793</v>
+        <v>0.781</v>
       </c>
       <c r="M139" t="n">
         <v>164</v>
@@ -7968,22 +7968,22 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0.3125</v>
+        <v>0.3083</v>
       </c>
       <c r="H140" t="n">
-        <v>0.1789</v>
+        <v>0.1769</v>
       </c>
       <c r="I140" t="n">
-        <v>0.2457</v>
+        <v>0.2426</v>
       </c>
       <c r="J140" t="n">
-        <v>0.6875</v>
+        <v>0.6917</v>
       </c>
       <c r="K140" t="n">
-        <v>0.8211000000000001</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="L140" t="n">
-        <v>0.7543</v>
+        <v>0.7574</v>
       </c>
       <c r="M140" t="n">
         <v>164</v>
@@ -8022,22 +8022,22 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>0.2558</v>
+        <v>0.3136</v>
       </c>
       <c r="H141" t="n">
-        <v>0.1355</v>
+        <v>0.1762</v>
       </c>
       <c r="I141" t="n">
-        <v>0.1957</v>
+        <v>0.2449</v>
       </c>
       <c r="J141" t="n">
-        <v>0.7442</v>
+        <v>0.6864</v>
       </c>
       <c r="K141" t="n">
-        <v>0.8645</v>
+        <v>0.8238</v>
       </c>
       <c r="L141" t="n">
-        <v>0.8043</v>
+        <v>0.7551</v>
       </c>
       <c r="M141" t="n">
         <v>164</v>
@@ -8076,22 +8076,22 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>0.3534</v>
+        <v>0.3433</v>
       </c>
       <c r="H142" t="n">
-        <v>0.2435</v>
+        <v>0.2394</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2984</v>
+        <v>0.2914</v>
       </c>
       <c r="J142" t="n">
-        <v>0.6466</v>
+        <v>0.6567</v>
       </c>
       <c r="K142" t="n">
-        <v>0.7565</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="L142" t="n">
-        <v>0.7016</v>
+        <v>0.7086</v>
       </c>
       <c r="M142" t="n">
         <v>164</v>
@@ -8133,19 +8133,19 @@
         <v>0.6225000000000001</v>
       </c>
       <c r="H143" t="n">
-        <v>0.4404</v>
+        <v>0.4491</v>
       </c>
       <c r="I143" t="n">
-        <v>0.5314</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="J143" t="n">
         <v>0.3775</v>
       </c>
       <c r="K143" t="n">
-        <v>0.5596</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="L143" t="n">
-        <v>0.4686</v>
+        <v>0.4642</v>
       </c>
       <c r="M143" t="n">
         <v>164</v>
@@ -8184,22 +8184,22 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>0.2895</v>
+        <v>0.2792</v>
       </c>
       <c r="H144" t="n">
         <v>0.1645</v>
       </c>
       <c r="I144" t="n">
-        <v>0.227</v>
+        <v>0.2218</v>
       </c>
       <c r="J144" t="n">
-        <v>0.7105</v>
+        <v>0.7208</v>
       </c>
       <c r="K144" t="n">
         <v>0.8355</v>
       </c>
       <c r="L144" t="n">
-        <v>0.773</v>
+        <v>0.7782</v>
       </c>
       <c r="M144" t="n">
         <v>164</v>
@@ -8241,19 +8241,19 @@
         <v>0.6925</v>
       </c>
       <c r="H145" t="n">
-        <v>0.5324</v>
+        <v>0.5371</v>
       </c>
       <c r="I145" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.6148</v>
       </c>
       <c r="J145" t="n">
         <v>0.3075</v>
       </c>
       <c r="K145" t="n">
-        <v>0.4676</v>
+        <v>0.4629</v>
       </c>
       <c r="L145" t="n">
-        <v>0.3876</v>
+        <v>0.3852</v>
       </c>
       <c r="M145" t="n">
         <v>164</v>
@@ -8292,22 +8292,22 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>0.2494</v>
+        <v>0.2472</v>
       </c>
       <c r="H146" t="n">
-        <v>0.1514</v>
+        <v>0.1481</v>
       </c>
       <c r="I146" t="n">
-        <v>0.2004</v>
+        <v>0.1976</v>
       </c>
       <c r="J146" t="n">
-        <v>0.7506</v>
+        <v>0.7528</v>
       </c>
       <c r="K146" t="n">
-        <v>0.8486</v>
+        <v>0.8519</v>
       </c>
       <c r="L146" t="n">
-        <v>0.7996</v>
+        <v>0.8024</v>
       </c>
       <c r="M146" t="n">
         <v>164</v>
@@ -8349,19 +8349,19 @@
         <v>0.4283</v>
       </c>
       <c r="H147" t="n">
-        <v>0.2622</v>
+        <v>0.2551</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3452</v>
+        <v>0.3417</v>
       </c>
       <c r="J147" t="n">
         <v>0.5717</v>
       </c>
       <c r="K147" t="n">
-        <v>0.7378</v>
+        <v>0.7449</v>
       </c>
       <c r="L147" t="n">
-        <v>0.6548</v>
+        <v>0.6583</v>
       </c>
       <c r="M147" t="n">
         <v>164</v>
@@ -8454,22 +8454,22 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>0.351</v>
+        <v>0.348</v>
       </c>
       <c r="H149" t="n">
-        <v>0.2027</v>
+        <v>0.2018</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2768</v>
+        <v>0.2749</v>
       </c>
       <c r="J149" t="n">
-        <v>0.649</v>
+        <v>0.652</v>
       </c>
       <c r="K149" t="n">
-        <v>0.7973</v>
+        <v>0.7982</v>
       </c>
       <c r="L149" t="n">
-        <v>0.7232</v>
+        <v>0.7251</v>
       </c>
       <c r="M149" t="n">
         <v>164</v>
@@ -8508,22 +8508,22 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0.3702</v>
+        <v>0.3656</v>
       </c>
       <c r="H150" t="n">
         <v>0.2042</v>
       </c>
       <c r="I150" t="n">
-        <v>0.2872</v>
+        <v>0.2849</v>
       </c>
       <c r="J150" t="n">
-        <v>0.6298</v>
+        <v>0.6344</v>
       </c>
       <c r="K150" t="n">
         <v>0.7958</v>
       </c>
       <c r="L150" t="n">
-        <v>0.7128</v>
+        <v>0.7151</v>
       </c>
       <c r="M150" t="n">
         <v>164</v>
@@ -8562,22 +8562,22 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>0.4202</v>
+        <v>0.4056</v>
       </c>
       <c r="H151" t="n">
-        <v>0.2663</v>
+        <v>0.2475</v>
       </c>
       <c r="I151" t="n">
-        <v>0.3432</v>
+        <v>0.3266</v>
       </c>
       <c r="J151" t="n">
-        <v>0.5798</v>
+        <v>0.5944</v>
       </c>
       <c r="K151" t="n">
-        <v>0.7337</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="L151" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.6734</v>
       </c>
       <c r="M151" t="n">
         <v>164</v>
@@ -8670,22 +8670,22 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>0.2142</v>
+        <v>0.212</v>
       </c>
       <c r="H153" t="n">
-        <v>0.1325</v>
+        <v>0.1302</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1734</v>
+        <v>0.1711</v>
       </c>
       <c r="J153" t="n">
-        <v>0.7858000000000001</v>
+        <v>0.788</v>
       </c>
       <c r="K153" t="n">
-        <v>0.8675</v>
+        <v>0.8698</v>
       </c>
       <c r="L153" t="n">
-        <v>0.8266</v>
+        <v>0.8289</v>
       </c>
       <c r="M153" t="n">
         <v>164</v>
@@ -8724,22 +8724,22 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>0.2355</v>
+        <v>0.227</v>
       </c>
       <c r="H154" t="n">
-        <v>0.1238</v>
+        <v>0.12</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1796</v>
+        <v>0.1735</v>
       </c>
       <c r="J154" t="n">
-        <v>0.7645</v>
+        <v>0.773</v>
       </c>
       <c r="K154" t="n">
-        <v>0.8762</v>
+        <v>0.88</v>
       </c>
       <c r="L154" t="n">
-        <v>0.8204</v>
+        <v>0.8265</v>
       </c>
       <c r="M154" t="n">
         <v>164</v>
@@ -8781,19 +8781,19 @@
         <v>0.3254</v>
       </c>
       <c r="H155" t="n">
-        <v>0.1906</v>
+        <v>0.1876</v>
       </c>
       <c r="I155" t="n">
-        <v>0.258</v>
+        <v>0.2565</v>
       </c>
       <c r="J155" t="n">
         <v>0.6746</v>
       </c>
       <c r="K155" t="n">
-        <v>0.8094</v>
+        <v>0.8124</v>
       </c>
       <c r="L155" t="n">
-        <v>0.742</v>
+        <v>0.7435</v>
       </c>
       <c r="M155" t="n">
         <v>164</v>
@@ -8832,22 +8832,22 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>0.6028</v>
+        <v>0.6166</v>
       </c>
       <c r="H156" t="n">
-        <v>0.4991</v>
+        <v>0.5008</v>
       </c>
       <c r="I156" t="n">
-        <v>0.551</v>
+        <v>0.5587</v>
       </c>
       <c r="J156" t="n">
-        <v>0.3972</v>
+        <v>0.3834</v>
       </c>
       <c r="K156" t="n">
-        <v>0.5009</v>
+        <v>0.4992</v>
       </c>
       <c r="L156" t="n">
-        <v>0.449</v>
+        <v>0.4413</v>
       </c>
       <c r="M156" t="n">
         <v>164</v>
@@ -8886,22 +8886,22 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.6063</v>
       </c>
       <c r="H157" t="n">
         <v>0.4716</v>
       </c>
       <c r="I157" t="n">
-        <v>0.537</v>
+        <v>0.539</v>
       </c>
       <c r="J157" t="n">
-        <v>0.3977</v>
+        <v>0.3937</v>
       </c>
       <c r="K157" t="n">
         <v>0.5284</v>
       </c>
       <c r="L157" t="n">
-        <v>0.463</v>
+        <v>0.461</v>
       </c>
       <c r="M157" t="n">
         <v>164</v>
@@ -8940,22 +8940,22 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>0.6935</v>
+        <v>0.6973</v>
       </c>
       <c r="H158" t="n">
         <v>0.5595</v>
       </c>
       <c r="I158" t="n">
-        <v>0.6264999999999999</v>
+        <v>0.6284</v>
       </c>
       <c r="J158" t="n">
-        <v>0.3065</v>
+        <v>0.3027</v>
       </c>
       <c r="K158" t="n">
         <v>0.4405</v>
       </c>
       <c r="L158" t="n">
-        <v>0.3735</v>
+        <v>0.3716</v>
       </c>
       <c r="M158" t="n">
         <v>164</v>
@@ -8997,19 +8997,19 @@
         <v>0.2828</v>
       </c>
       <c r="H159" t="n">
-        <v>0.177</v>
+        <v>0.1734</v>
       </c>
       <c r="I159" t="n">
-        <v>0.2299</v>
+        <v>0.2281</v>
       </c>
       <c r="J159" t="n">
         <v>0.7171999999999999</v>
       </c>
       <c r="K159" t="n">
-        <v>0.823</v>
+        <v>0.8266</v>
       </c>
       <c r="L159" t="n">
-        <v>0.7701</v>
+        <v>0.7719</v>
       </c>
       <c r="M159" t="n">
         <v>164</v>
@@ -9048,22 +9048,22 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>0.2977</v>
+        <v>0.2932</v>
       </c>
       <c r="H160" t="n">
         <v>0.163</v>
       </c>
       <c r="I160" t="n">
-        <v>0.2304</v>
+        <v>0.2281</v>
       </c>
       <c r="J160" t="n">
-        <v>0.7023</v>
+        <v>0.7068</v>
       </c>
       <c r="K160" t="n">
         <v>0.837</v>
       </c>
       <c r="L160" t="n">
-        <v>0.7696</v>
+        <v>0.7719</v>
       </c>
       <c r="M160" t="n">
         <v>164</v>
@@ -9105,19 +9105,19 @@
         <v>0.7986</v>
       </c>
       <c r="H161" t="n">
-        <v>0.6456</v>
+        <v>0.6488</v>
       </c>
       <c r="I161" t="n">
-        <v>0.7221</v>
+        <v>0.7237</v>
       </c>
       <c r="J161" t="n">
         <v>0.2014</v>
       </c>
       <c r="K161" t="n">
-        <v>0.3544</v>
+        <v>0.3512</v>
       </c>
       <c r="L161" t="n">
-        <v>0.2779</v>
+        <v>0.2763</v>
       </c>
       <c r="M161" t="n">
         <v>164</v>
@@ -9156,22 +9156,22 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>0.6609</v>
+        <v>0.6634</v>
       </c>
       <c r="H162" t="n">
-        <v>0.4971</v>
+        <v>0.502</v>
       </c>
       <c r="I162" t="n">
-        <v>0.579</v>
+        <v>0.5827</v>
       </c>
       <c r="J162" t="n">
-        <v>0.3391</v>
+        <v>0.3366</v>
       </c>
       <c r="K162" t="n">
-        <v>0.5029</v>
+        <v>0.498</v>
       </c>
       <c r="L162" t="n">
-        <v>0.421</v>
+        <v>0.4173</v>
       </c>
       <c r="M162" t="n">
         <v>164</v>
@@ -9213,19 +9213,19 @@
         <v>0.7040999999999999</v>
       </c>
       <c r="H163" t="n">
-        <v>0.5542</v>
+        <v>0.5586</v>
       </c>
       <c r="I163" t="n">
-        <v>0.6292</v>
+        <v>0.6314</v>
       </c>
       <c r="J163" t="n">
         <v>0.2959</v>
       </c>
       <c r="K163" t="n">
-        <v>0.4458</v>
+        <v>0.4414</v>
       </c>
       <c r="L163" t="n">
-        <v>0.3708</v>
+        <v>0.3686</v>
       </c>
       <c r="M163" t="n">
         <v>164</v>
@@ -9264,22 +9264,22 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>0.5849</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="H164" t="n">
-        <v>0.4542</v>
+        <v>0.5484</v>
       </c>
       <c r="I164" t="n">
-        <v>0.5196</v>
+        <v>0.6252</v>
       </c>
       <c r="J164" t="n">
-        <v>0.4151</v>
+        <v>0.2979</v>
       </c>
       <c r="K164" t="n">
-        <v>0.5458</v>
+        <v>0.4516</v>
       </c>
       <c r="L164" t="n">
-        <v>0.4804</v>
+        <v>0.3748</v>
       </c>
       <c r="M164" t="n">
         <v>164</v>
@@ -9318,22 +9318,22 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>0.7758</v>
+        <v>0.78</v>
       </c>
       <c r="H165" t="n">
         <v>0.6039</v>
       </c>
       <c r="I165" t="n">
-        <v>0.6899</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="J165" t="n">
-        <v>0.2242</v>
+        <v>0.22</v>
       </c>
       <c r="K165" t="n">
         <v>0.3961</v>
       </c>
       <c r="L165" t="n">
-        <v>0.3101</v>
+        <v>0.308</v>
       </c>
       <c r="M165" t="n">
         <v>164</v>
@@ -9426,22 +9426,22 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>0.6541</v>
+        <v>0.6554</v>
       </c>
       <c r="H167" t="n">
-        <v>0.5239</v>
+        <v>0.5322</v>
       </c>
       <c r="I167" t="n">
-        <v>0.589</v>
+        <v>0.5938</v>
       </c>
       <c r="J167" t="n">
-        <v>0.3459</v>
+        <v>0.3446</v>
       </c>
       <c r="K167" t="n">
-        <v>0.4761</v>
+        <v>0.4678</v>
       </c>
       <c r="L167" t="n">
-        <v>0.411</v>
+        <v>0.4062</v>
       </c>
       <c r="M167" t="n">
         <v>164</v>
@@ -9537,19 +9537,19 @@
         <v>0.6166</v>
       </c>
       <c r="H169" t="n">
-        <v>0.454</v>
+        <v>0.4553</v>
       </c>
       <c r="I169" t="n">
-        <v>0.5353</v>
+        <v>0.536</v>
       </c>
       <c r="J169" t="n">
         <v>0.3834</v>
       </c>
       <c r="K169" t="n">
-        <v>0.546</v>
+        <v>0.5447</v>
       </c>
       <c r="L169" t="n">
-        <v>0.4647</v>
+        <v>0.464</v>
       </c>
       <c r="M169" t="n">
         <v>164</v>
@@ -9588,22 +9588,22 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>0.7996</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="H170" t="n">
-        <v>0.6494</v>
+        <v>0.6561</v>
       </c>
       <c r="I170" t="n">
-        <v>0.7245</v>
+        <v>0.7285</v>
       </c>
       <c r="J170" t="n">
-        <v>0.2004</v>
+        <v>0.1991</v>
       </c>
       <c r="K170" t="n">
-        <v>0.3506</v>
+        <v>0.3439</v>
       </c>
       <c r="L170" t="n">
-        <v>0.2755</v>
+        <v>0.2715</v>
       </c>
       <c r="M170" t="n">
         <v>164</v>
@@ -9642,22 +9642,22 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>0.8478</v>
+        <v>0.8518</v>
       </c>
       <c r="H171" t="n">
-        <v>0.7421</v>
+        <v>0.7474</v>
       </c>
       <c r="I171" t="n">
-        <v>0.795</v>
+        <v>0.7996</v>
       </c>
       <c r="J171" t="n">
-        <v>0.1522</v>
+        <v>0.1482</v>
       </c>
       <c r="K171" t="n">
-        <v>0.2579</v>
+        <v>0.2526</v>
       </c>
       <c r="L171" t="n">
-        <v>0.205</v>
+        <v>0.2004</v>
       </c>
       <c r="M171" t="n">
         <v>164</v>
@@ -9696,22 +9696,22 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>0.7681</v>
+        <v>0.7744</v>
       </c>
       <c r="H172" t="n">
-        <v>0.6156</v>
+        <v>0.6203</v>
       </c>
       <c r="I172" t="n">
-        <v>0.6919</v>
+        <v>0.6973</v>
       </c>
       <c r="J172" t="n">
-        <v>0.2319</v>
+        <v>0.2256</v>
       </c>
       <c r="K172" t="n">
-        <v>0.3844</v>
+        <v>0.3797</v>
       </c>
       <c r="L172" t="n">
-        <v>0.3081</v>
+        <v>0.3027</v>
       </c>
       <c r="M172" t="n">
         <v>164</v>
@@ -9750,22 +9750,22 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>0.7325</v>
+        <v>0.7376</v>
       </c>
       <c r="H173" t="n">
         <v>0.589</v>
       </c>
       <c r="I173" t="n">
-        <v>0.6607</v>
+        <v>0.6633</v>
       </c>
       <c r="J173" t="n">
-        <v>0.2675</v>
+        <v>0.2624</v>
       </c>
       <c r="K173" t="n">
         <v>0.411</v>
       </c>
       <c r="L173" t="n">
-        <v>0.3393</v>
+        <v>0.3367</v>
       </c>
       <c r="M173" t="n">
         <v>164</v>
@@ -9804,22 +9804,22 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>0.7914</v>
+        <v>0.7861</v>
       </c>
       <c r="H174" t="n">
-        <v>0.6284999999999999</v>
+        <v>0.6176</v>
       </c>
       <c r="I174" t="n">
-        <v>0.71</v>
+        <v>0.7019</v>
       </c>
       <c r="J174" t="n">
-        <v>0.2086</v>
+        <v>0.2139</v>
       </c>
       <c r="K174" t="n">
-        <v>0.3715</v>
+        <v>0.3824</v>
       </c>
       <c r="L174" t="n">
-        <v>0.29</v>
+        <v>0.2981</v>
       </c>
       <c r="M174" t="n">
         <v>164</v>
@@ -10023,19 +10023,19 @@
         <v>0.7078</v>
       </c>
       <c r="H178" t="n">
-        <v>0.5753</v>
+        <v>0.5857</v>
       </c>
       <c r="I178" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="J178" t="n">
         <v>0.2922</v>
       </c>
       <c r="K178" t="n">
-        <v>0.4247</v>
+        <v>0.4143</v>
       </c>
       <c r="L178" t="n">
-        <v>0.3584</v>
+        <v>0.3533</v>
       </c>
       <c r="M178" t="n">
         <v>164</v>
@@ -10236,22 +10236,22 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0.6499</v>
+        <v>0.6566</v>
       </c>
       <c r="H182" t="n">
         <v>0.4997</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5748</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="J182" t="n">
-        <v>0.3501</v>
+        <v>0.3434</v>
       </c>
       <c r="K182" t="n">
         <v>0.5003</v>
       </c>
       <c r="L182" t="n">
-        <v>0.4252</v>
+        <v>0.4219</v>
       </c>
       <c r="M182" t="n">
         <v>164</v>
@@ -10290,22 +10290,22 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>0.6563</v>
+        <v>0.6593</v>
       </c>
       <c r="H183" t="n">
-        <v>0.5066000000000001</v>
+        <v>0.5139</v>
       </c>
       <c r="I183" t="n">
-        <v>0.5814</v>
+        <v>0.5866</v>
       </c>
       <c r="J183" t="n">
-        <v>0.3437</v>
+        <v>0.3407</v>
       </c>
       <c r="K183" t="n">
-        <v>0.4934</v>
+        <v>0.4861</v>
       </c>
       <c r="L183" t="n">
-        <v>0.4186</v>
+        <v>0.4134</v>
       </c>
       <c r="M183" t="n">
         <v>164</v>
@@ -10347,19 +10347,19 @@
         <v>0.4139</v>
       </c>
       <c r="H184" t="n">
-        <v>0.2481</v>
+        <v>0.2449</v>
       </c>
       <c r="I184" t="n">
-        <v>0.331</v>
+        <v>0.3294</v>
       </c>
       <c r="J184" t="n">
         <v>0.5861</v>
       </c>
       <c r="K184" t="n">
-        <v>0.7519</v>
+        <v>0.7551</v>
       </c>
       <c r="L184" t="n">
-        <v>0.669</v>
+        <v>0.6706</v>
       </c>
       <c r="M184" t="n">
         <v>164</v>
@@ -10452,22 +10452,22 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>0.4069</v>
+        <v>0.4736</v>
       </c>
       <c r="H186" t="n">
-        <v>0.2143</v>
+        <v>0.2793</v>
       </c>
       <c r="I186" t="n">
-        <v>0.3106</v>
+        <v>0.3764</v>
       </c>
       <c r="J186" t="n">
-        <v>0.5931</v>
+        <v>0.5264</v>
       </c>
       <c r="K186" t="n">
-        <v>0.7857</v>
+        <v>0.7207</v>
       </c>
       <c r="L186" t="n">
-        <v>0.6894</v>
+        <v>0.6236</v>
       </c>
       <c r="M186" t="n">
         <v>164</v>
@@ -10509,19 +10509,19 @@
         <v>0.5286999999999999</v>
       </c>
       <c r="H187" t="n">
-        <v>0.3911</v>
+        <v>0.3902</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4599</v>
+        <v>0.4594</v>
       </c>
       <c r="J187" t="n">
         <v>0.4713</v>
       </c>
       <c r="K187" t="n">
-        <v>0.6089</v>
+        <v>0.6098</v>
       </c>
       <c r="L187" t="n">
-        <v>0.5401</v>
+        <v>0.5406</v>
       </c>
       <c r="M187" t="n">
         <v>164</v>
@@ -10560,22 +10560,22 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>0.7345</v>
+        <v>0.741</v>
       </c>
       <c r="H188" t="n">
         <v>0.6203</v>
       </c>
       <c r="I188" t="n">
-        <v>0.6774</v>
+        <v>0.6806</v>
       </c>
       <c r="J188" t="n">
-        <v>0.2655</v>
+        <v>0.259</v>
       </c>
       <c r="K188" t="n">
         <v>0.3797</v>
       </c>
       <c r="L188" t="n">
-        <v>0.3226</v>
+        <v>0.3194</v>
       </c>
       <c r="M188" t="n">
         <v>164</v>
@@ -10614,22 +10614,22 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>0.4015</v>
+        <v>0.3925</v>
       </c>
       <c r="H189" t="n">
-        <v>0.2544</v>
+        <v>0.251</v>
       </c>
       <c r="I189" t="n">
-        <v>0.328</v>
+        <v>0.3218</v>
       </c>
       <c r="J189" t="n">
-        <v>0.5985</v>
+        <v>0.6075</v>
       </c>
       <c r="K189" t="n">
-        <v>0.7456</v>
+        <v>0.749</v>
       </c>
       <c r="L189" t="n">
-        <v>0.672</v>
+        <v>0.6782</v>
       </c>
       <c r="M189" t="n">
         <v>164</v>
@@ -10668,22 +10668,22 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>0.7964</v>
+        <v>0.7988</v>
       </c>
       <c r="H190" t="n">
-        <v>0.7017</v>
+        <v>0.7044</v>
       </c>
       <c r="I190" t="n">
-        <v>0.749</v>
+        <v>0.7516</v>
       </c>
       <c r="J190" t="n">
-        <v>0.2036</v>
+        <v>0.2012</v>
       </c>
       <c r="K190" t="n">
-        <v>0.2983</v>
+        <v>0.2956</v>
       </c>
       <c r="L190" t="n">
-        <v>0.251</v>
+        <v>0.2484</v>
       </c>
       <c r="M190" t="n">
         <v>164</v>
@@ -10722,22 +10722,22 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>0.3695</v>
+        <v>0.3683</v>
       </c>
       <c r="H191" t="n">
         <v>0.2128</v>
       </c>
       <c r="I191" t="n">
-        <v>0.2912</v>
+        <v>0.2905</v>
       </c>
       <c r="J191" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.6317</v>
       </c>
       <c r="K191" t="n">
         <v>0.7872</v>
       </c>
       <c r="L191" t="n">
-        <v>0.7088</v>
+        <v>0.7095</v>
       </c>
       <c r="M191" t="n">
         <v>164</v>
@@ -10779,19 +10779,19 @@
         <v>0.5469000000000001</v>
       </c>
       <c r="H192" t="n">
-        <v>0.4432</v>
+        <v>0.4412</v>
       </c>
       <c r="I192" t="n">
-        <v>0.495</v>
+        <v>0.494</v>
       </c>
       <c r="J192" t="n">
         <v>0.4531</v>
       </c>
       <c r="K192" t="n">
-        <v>0.5568</v>
+        <v>0.5588</v>
       </c>
       <c r="L192" t="n">
-        <v>0.505</v>
+        <v>0.506</v>
       </c>
       <c r="M192" t="n">
         <v>164</v>
@@ -10884,22 +10884,22 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>0.5153</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="H194" t="n">
-        <v>0.3494</v>
+        <v>0.3455</v>
       </c>
       <c r="I194" t="n">
-        <v>0.4324</v>
+        <v>0.428</v>
       </c>
       <c r="J194" t="n">
-        <v>0.4847</v>
+        <v>0.4894</v>
       </c>
       <c r="K194" t="n">
-        <v>0.6506</v>
+        <v>0.6545</v>
       </c>
       <c r="L194" t="n">
-        <v>0.5676</v>
+        <v>0.572</v>
       </c>
       <c r="M194" t="n">
         <v>164</v>
@@ -10941,19 +10941,19 @@
         <v>0.5088</v>
       </c>
       <c r="H195" t="n">
-        <v>0.389</v>
+        <v>0.3861</v>
       </c>
       <c r="I195" t="n">
-        <v>0.4489</v>
+        <v>0.4474</v>
       </c>
       <c r="J195" t="n">
         <v>0.4912</v>
       </c>
       <c r="K195" t="n">
-        <v>0.611</v>
+        <v>0.6139</v>
       </c>
       <c r="L195" t="n">
-        <v>0.5511</v>
+        <v>0.5526</v>
       </c>
       <c r="M195" t="n">
         <v>164</v>
@@ -10992,22 +10992,22 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>0.5393</v>
+        <v>0.5229</v>
       </c>
       <c r="H196" t="n">
-        <v>0.4165</v>
+        <v>0.3949</v>
       </c>
       <c r="I196" t="n">
-        <v>0.4779</v>
+        <v>0.4589</v>
       </c>
       <c r="J196" t="n">
-        <v>0.4607</v>
+        <v>0.4771</v>
       </c>
       <c r="K196" t="n">
-        <v>0.5835</v>
+        <v>0.6051</v>
       </c>
       <c r="L196" t="n">
-        <v>0.5221</v>
+        <v>0.5411</v>
       </c>
       <c r="M196" t="n">
         <v>164</v>
@@ -11046,22 +11046,22 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>0.7771</v>
+        <v>0.7788</v>
       </c>
       <c r="H197" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6912</v>
       </c>
       <c r="I197" t="n">
-        <v>0.7321</v>
+        <v>0.735</v>
       </c>
       <c r="J197" t="n">
-        <v>0.2229</v>
+        <v>0.2212</v>
       </c>
       <c r="K197" t="n">
-        <v>0.313</v>
+        <v>0.3088</v>
       </c>
       <c r="L197" t="n">
-        <v>0.2679</v>
+        <v>0.265</v>
       </c>
       <c r="M197" t="n">
         <v>164</v>
@@ -11100,22 +11100,22 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>0.2861</v>
+        <v>0.2799</v>
       </c>
       <c r="H198" t="n">
-        <v>0.1612</v>
+        <v>0.1575</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2236</v>
+        <v>0.2187</v>
       </c>
       <c r="J198" t="n">
-        <v>0.7139</v>
+        <v>0.7201</v>
       </c>
       <c r="K198" t="n">
-        <v>0.8388</v>
+        <v>0.8425</v>
       </c>
       <c r="L198" t="n">
-        <v>0.7764</v>
+        <v>0.7813</v>
       </c>
       <c r="M198" t="n">
         <v>164</v>
@@ -11154,22 +11154,22 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>0.2735</v>
+        <v>0.2712</v>
       </c>
       <c r="H199" t="n">
-        <v>0.1636</v>
+        <v>0.1595</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2186</v>
+        <v>0.2154</v>
       </c>
       <c r="J199" t="n">
-        <v>0.7265</v>
+        <v>0.7288</v>
       </c>
       <c r="K199" t="n">
-        <v>0.8364</v>
+        <v>0.8405</v>
       </c>
       <c r="L199" t="n">
-        <v>0.7814</v>
+        <v>0.7846</v>
       </c>
       <c r="M199" t="n">
         <v>164</v>
@@ -11208,22 +11208,22 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>0.4719</v>
+        <v>0.4632</v>
       </c>
       <c r="H200" t="n">
-        <v>0.3384</v>
+        <v>0.3399</v>
       </c>
       <c r="I200" t="n">
-        <v>0.4052</v>
+        <v>0.4015</v>
       </c>
       <c r="J200" t="n">
-        <v>0.5281</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="K200" t="n">
-        <v>0.6616</v>
+        <v>0.6601</v>
       </c>
       <c r="L200" t="n">
-        <v>0.5948</v>
+        <v>0.5985</v>
       </c>
       <c r="M200" t="n">
         <v>164</v>
@@ -11316,22 +11316,22 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>0.7543</v>
+        <v>0.7588</v>
       </c>
       <c r="H202" t="n">
-        <v>0.6109</v>
+        <v>0.617</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6826</v>
+        <v>0.6879</v>
       </c>
       <c r="J202" t="n">
-        <v>0.2457</v>
+        <v>0.2412</v>
       </c>
       <c r="K202" t="n">
-        <v>0.3891</v>
+        <v>0.383</v>
       </c>
       <c r="L202" t="n">
-        <v>0.3174</v>
+        <v>0.3121</v>
       </c>
       <c r="M202" t="n">
         <v>164</v>
@@ -11373,19 +11373,19 @@
         <v>0.8235</v>
       </c>
       <c r="H203" t="n">
-        <v>0.697</v>
+        <v>0.7026</v>
       </c>
       <c r="I203" t="n">
-        <v>0.7602</v>
+        <v>0.763</v>
       </c>
       <c r="J203" t="n">
         <v>0.1765</v>
       </c>
       <c r="K203" t="n">
-        <v>0.303</v>
+        <v>0.2974</v>
       </c>
       <c r="L203" t="n">
-        <v>0.2398</v>
+        <v>0.237</v>
       </c>
       <c r="M203" t="n">
         <v>164</v>
@@ -11427,19 +11427,19 @@
         <v>0.3827</v>
       </c>
       <c r="H204" t="n">
-        <v>0.2678</v>
+        <v>0.2664</v>
       </c>
       <c r="I204" t="n">
-        <v>0.3252</v>
+        <v>0.3246</v>
       </c>
       <c r="J204" t="n">
         <v>0.6173</v>
       </c>
       <c r="K204" t="n">
-        <v>0.7322</v>
+        <v>0.7336</v>
       </c>
       <c r="L204" t="n">
-        <v>0.6748</v>
+        <v>0.6754</v>
       </c>
       <c r="M204" t="n">
         <v>164</v>
@@ -11586,22 +11586,22 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>0.5322</v>
+        <v>0.6148</v>
       </c>
       <c r="H207" t="n">
-        <v>0.3804</v>
+        <v>0.5184</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4563</v>
+        <v>0.5666</v>
       </c>
       <c r="J207" t="n">
-        <v>0.4678</v>
+        <v>0.3852</v>
       </c>
       <c r="K207" t="n">
-        <v>0.6196</v>
+        <v>0.4816</v>
       </c>
       <c r="L207" t="n">
-        <v>0.5437</v>
+        <v>0.4334</v>
       </c>
       <c r="M207" t="n">
         <v>164</v>
@@ -11694,22 +11694,22 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>0.8442</v>
+        <v>0.8489</v>
       </c>
       <c r="H209" t="n">
-        <v>0.7225</v>
+        <v>0.732</v>
       </c>
       <c r="I209" t="n">
-        <v>0.7834</v>
+        <v>0.7904</v>
       </c>
       <c r="J209" t="n">
-        <v>0.1558</v>
+        <v>0.1511</v>
       </c>
       <c r="K209" t="n">
-        <v>0.2775</v>
+        <v>0.268</v>
       </c>
       <c r="L209" t="n">
-        <v>0.2166</v>
+        <v>0.2096</v>
       </c>
       <c r="M209" t="n">
         <v>164</v>
@@ -11751,19 +11751,19 @@
         <v>0.5504</v>
       </c>
       <c r="H210" t="n">
-        <v>0.4156</v>
+        <v>0.4126</v>
       </c>
       <c r="I210" t="n">
-        <v>0.483</v>
+        <v>0.4815</v>
       </c>
       <c r="J210" t="n">
         <v>0.4496</v>
       </c>
       <c r="K210" t="n">
-        <v>0.5844</v>
+        <v>0.5874</v>
       </c>
       <c r="L210" t="n">
-        <v>0.517</v>
+        <v>0.5185</v>
       </c>
       <c r="M210" t="n">
         <v>164</v>
@@ -11802,22 +11802,22 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>0.8678</v>
+        <v>0.8708</v>
       </c>
       <c r="H211" t="n">
-        <v>0.7796</v>
+        <v>0.7843</v>
       </c>
       <c r="I211" t="n">
-        <v>0.8237</v>
+        <v>0.8276</v>
       </c>
       <c r="J211" t="n">
-        <v>0.1322</v>
+        <v>0.1292</v>
       </c>
       <c r="K211" t="n">
-        <v>0.2204</v>
+        <v>0.2157</v>
       </c>
       <c r="L211" t="n">
-        <v>0.1763</v>
+        <v>0.1724</v>
       </c>
       <c r="M211" t="n">
         <v>164</v>
@@ -11913,19 +11913,19 @@
         <v>0.748</v>
       </c>
       <c r="H213" t="n">
-        <v>0.5748</v>
+        <v>0.5834</v>
       </c>
       <c r="I213" t="n">
-        <v>0.6614</v>
+        <v>0.6657</v>
       </c>
       <c r="J213" t="n">
         <v>0.252</v>
       </c>
       <c r="K213" t="n">
-        <v>0.4252</v>
+        <v>0.4166</v>
       </c>
       <c r="L213" t="n">
-        <v>0.3386</v>
+        <v>0.3343</v>
       </c>
       <c r="M213" t="n">
         <v>164</v>
@@ -11964,22 +11964,22 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>0.8243</v>
+        <v>0.8256</v>
       </c>
       <c r="H214" t="n">
-        <v>0.7169</v>
+        <v>0.7187</v>
       </c>
       <c r="I214" t="n">
-        <v>0.7706</v>
+        <v>0.7722</v>
       </c>
       <c r="J214" t="n">
-        <v>0.1757</v>
+        <v>0.1744</v>
       </c>
       <c r="K214" t="n">
-        <v>0.2831</v>
+        <v>0.2813</v>
       </c>
       <c r="L214" t="n">
-        <v>0.2294</v>
+        <v>0.2278</v>
       </c>
       <c r="M214" t="n">
         <v>164</v>
@@ -12126,22 +12126,22 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0.748</v>
+        <v>0.7357</v>
       </c>
       <c r="H217" t="n">
-        <v>0.5625</v>
+        <v>0.5465</v>
       </c>
       <c r="I217" t="n">
-        <v>0.6552</v>
+        <v>0.6411</v>
       </c>
       <c r="J217" t="n">
-        <v>0.252</v>
+        <v>0.2643</v>
       </c>
       <c r="K217" t="n">
-        <v>0.4375</v>
+        <v>0.4535</v>
       </c>
       <c r="L217" t="n">
-        <v>0.3448</v>
+        <v>0.3589</v>
       </c>
       <c r="M217" t="n">
         <v>164</v>
@@ -12180,22 +12180,22 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>0.8579</v>
+        <v>0.8622</v>
       </c>
       <c r="H218" t="n">
-        <v>0.7624</v>
+        <v>0.7665</v>
       </c>
       <c r="I218" t="n">
-        <v>0.8101</v>
+        <v>0.8143</v>
       </c>
       <c r="J218" t="n">
-        <v>0.1421</v>
+        <v>0.1378</v>
       </c>
       <c r="K218" t="n">
-        <v>0.2376</v>
+        <v>0.2335</v>
       </c>
       <c r="L218" t="n">
-        <v>0.1899</v>
+        <v>0.1857</v>
       </c>
       <c r="M218" t="n">
         <v>164</v>
@@ -12234,22 +12234,22 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>0.3977</v>
+        <v>0.3957</v>
       </c>
       <c r="H219" t="n">
-        <v>0.2927</v>
+        <v>0.2873</v>
       </c>
       <c r="I219" t="n">
-        <v>0.3452</v>
+        <v>0.3415</v>
       </c>
       <c r="J219" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="K219" t="n">
-        <v>0.7073</v>
+        <v>0.7127</v>
       </c>
       <c r="L219" t="n">
-        <v>0.6548</v>
+        <v>0.6585</v>
       </c>
       <c r="M219" t="n">
         <v>164</v>
@@ -12288,22 +12288,22 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>0.3807</v>
+        <v>0.3735</v>
       </c>
       <c r="H220" t="n">
         <v>0.248</v>
       </c>
       <c r="I220" t="n">
-        <v>0.3144</v>
+        <v>0.3107</v>
       </c>
       <c r="J220" t="n">
-        <v>0.6193</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="K220" t="n">
         <v>0.752</v>
       </c>
       <c r="L220" t="n">
-        <v>0.6856</v>
+        <v>0.6893</v>
       </c>
       <c r="M220" t="n">
         <v>164</v>
@@ -12399,19 +12399,19 @@
         <v>0.8608</v>
       </c>
       <c r="H222" t="n">
-        <v>0.7388</v>
+        <v>0.7452</v>
       </c>
       <c r="I222" t="n">
-        <v>0.7998</v>
+        <v>0.803</v>
       </c>
       <c r="J222" t="n">
         <v>0.1392</v>
       </c>
       <c r="K222" t="n">
-        <v>0.2612</v>
+        <v>0.2548</v>
       </c>
       <c r="L222" t="n">
-        <v>0.2002</v>
+        <v>0.197</v>
       </c>
       <c r="M222" t="n">
         <v>164</v>
@@ -12450,22 +12450,22 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>0.863</v>
+        <v>0.8653</v>
       </c>
       <c r="H223" t="n">
-        <v>0.7209</v>
+        <v>0.7236</v>
       </c>
       <c r="I223" t="n">
-        <v>0.7919</v>
+        <v>0.7944</v>
       </c>
       <c r="J223" t="n">
-        <v>0.137</v>
+        <v>0.1347</v>
       </c>
       <c r="K223" t="n">
-        <v>0.2791</v>
+        <v>0.2764</v>
       </c>
       <c r="L223" t="n">
-        <v>0.2081</v>
+        <v>0.2056</v>
       </c>
       <c r="M223" t="n">
         <v>164</v>
@@ -12504,22 +12504,22 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>0.8754999999999999</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="H224" t="n">
         <v>0.764</v>
       </c>
       <c r="I224" t="n">
-        <v>0.8198</v>
+        <v>0.8233</v>
       </c>
       <c r="J224" t="n">
-        <v>0.1245</v>
+        <v>0.1174</v>
       </c>
       <c r="K224" t="n">
         <v>0.236</v>
       </c>
       <c r="L224" t="n">
-        <v>0.1802</v>
+        <v>0.1767</v>
       </c>
       <c r="M224" t="n">
         <v>164</v>
@@ -12612,22 +12612,22 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>0.5845</v>
+        <v>0.5876</v>
       </c>
       <c r="H226" t="n">
         <v>0.4576</v>
       </c>
       <c r="I226" t="n">
-        <v>0.521</v>
+        <v>0.5226</v>
       </c>
       <c r="J226" t="n">
-        <v>0.4155</v>
+        <v>0.4124</v>
       </c>
       <c r="K226" t="n">
         <v>0.5424</v>
       </c>
       <c r="L226" t="n">
-        <v>0.479</v>
+        <v>0.4774</v>
       </c>
       <c r="M226" t="n">
         <v>164</v>
@@ -12666,22 +12666,22 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>0.472</v>
+        <v>0.5409</v>
       </c>
       <c r="H227" t="n">
-        <v>0.344</v>
+        <v>0.4508</v>
       </c>
       <c r="I227" t="n">
-        <v>0.408</v>
+        <v>0.4958</v>
       </c>
       <c r="J227" t="n">
-        <v>0.528</v>
+        <v>0.4591</v>
       </c>
       <c r="K227" t="n">
-        <v>0.656</v>
+        <v>0.5492</v>
       </c>
       <c r="L227" t="n">
-        <v>0.592</v>
+        <v>0.5042</v>
       </c>
       <c r="M227" t="n">
         <v>164</v>
@@ -12774,22 +12774,22 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>0.8353</v>
+        <v>0.8387</v>
       </c>
       <c r="H229" t="n">
-        <v>0.6862</v>
+        <v>0.6922</v>
       </c>
       <c r="I229" t="n">
-        <v>0.7608</v>
+        <v>0.7654</v>
       </c>
       <c r="J229" t="n">
-        <v>0.1647</v>
+        <v>0.1613</v>
       </c>
       <c r="K229" t="n">
-        <v>0.3138</v>
+        <v>0.3078</v>
       </c>
       <c r="L229" t="n">
-        <v>0.2392</v>
+        <v>0.2346</v>
       </c>
       <c r="M229" t="n">
         <v>164</v>
@@ -12882,22 +12882,22 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>0.8522</v>
+        <v>0.8566</v>
       </c>
       <c r="H231" t="n">
-        <v>0.7462</v>
+        <v>0.7552</v>
       </c>
       <c r="I231" t="n">
-        <v>0.7992</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="J231" t="n">
-        <v>0.1478</v>
+        <v>0.1434</v>
       </c>
       <c r="K231" t="n">
-        <v>0.2538</v>
+        <v>0.2448</v>
       </c>
       <c r="L231" t="n">
-        <v>0.2008</v>
+        <v>0.1941</v>
       </c>
       <c r="M231" t="n">
         <v>164</v>
@@ -13044,22 +13044,22 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8128</v>
       </c>
       <c r="H234" t="n">
-        <v>0.6886</v>
+        <v>0.6944</v>
       </c>
       <c r="I234" t="n">
-        <v>0.7493</v>
+        <v>0.7536</v>
       </c>
       <c r="J234" t="n">
-        <v>0.19</v>
+        <v>0.1872</v>
       </c>
       <c r="K234" t="n">
-        <v>0.3114</v>
+        <v>0.3056</v>
       </c>
       <c r="L234" t="n">
-        <v>0.2507</v>
+        <v>0.2464</v>
       </c>
       <c r="M234" t="n">
         <v>164</v>
@@ -13098,22 +13098,22 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.6202</v>
       </c>
       <c r="H235" t="n">
         <v>0.4883</v>
       </c>
       <c r="I235" t="n">
-        <v>0.5579</v>
+        <v>0.5542</v>
       </c>
       <c r="J235" t="n">
-        <v>0.3725</v>
+        <v>0.3798</v>
       </c>
       <c r="K235" t="n">
         <v>0.5117</v>
       </c>
       <c r="L235" t="n">
-        <v>0.4421</v>
+        <v>0.4458</v>
       </c>
       <c r="M235" t="n">
         <v>164</v>
@@ -13206,22 +13206,22 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>0.7148</v>
+        <v>0.6973</v>
       </c>
       <c r="H237" t="n">
-        <v>0.51</v>
+        <v>0.486</v>
       </c>
       <c r="I237" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.5916</v>
       </c>
       <c r="J237" t="n">
-        <v>0.2852</v>
+        <v>0.3027</v>
       </c>
       <c r="K237" t="n">
-        <v>0.49</v>
+        <v>0.514</v>
       </c>
       <c r="L237" t="n">
-        <v>0.3876</v>
+        <v>0.4084</v>
       </c>
       <c r="M237" t="n">
         <v>164</v>
@@ -13260,22 +13260,22 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>0.8498</v>
+        <v>0.8504</v>
       </c>
       <c r="H238" t="n">
-        <v>0.7282</v>
+        <v>0.7311</v>
       </c>
       <c r="I238" t="n">
-        <v>0.789</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="J238" t="n">
-        <v>0.1502</v>
+        <v>0.1496</v>
       </c>
       <c r="K238" t="n">
-        <v>0.2718</v>
+        <v>0.2689</v>
       </c>
       <c r="L238" t="n">
-        <v>0.211</v>
+        <v>0.2092</v>
       </c>
       <c r="M238" t="n">
         <v>164</v>
@@ -13314,22 +13314,22 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>0.396</v>
+        <v>0.3933</v>
       </c>
       <c r="H239" t="n">
-        <v>0.2318</v>
+        <v>0.2293</v>
       </c>
       <c r="I239" t="n">
-        <v>0.3139</v>
+        <v>0.3113</v>
       </c>
       <c r="J239" t="n">
-        <v>0.604</v>
+        <v>0.6067</v>
       </c>
       <c r="K239" t="n">
-        <v>0.7682</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="L239" t="n">
-        <v>0.6861</v>
+        <v>0.6887</v>
       </c>
       <c r="M239" t="n">
         <v>164</v>
@@ -13371,19 +13371,19 @@
         <v>0.3742</v>
       </c>
       <c r="H240" t="n">
-        <v>0.2342</v>
+        <v>0.2277</v>
       </c>
       <c r="I240" t="n">
-        <v>0.3042</v>
+        <v>0.301</v>
       </c>
       <c r="J240" t="n">
         <v>0.6258</v>
       </c>
       <c r="K240" t="n">
-        <v>0.7658</v>
+        <v>0.7723</v>
       </c>
       <c r="L240" t="n">
-        <v>0.6958</v>
+        <v>0.699</v>
       </c>
       <c r="M240" t="n">
         <v>164</v>
@@ -13476,22 +13476,22 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>0.8351</v>
+        <v>0.8381</v>
       </c>
       <c r="H242" t="n">
-        <v>0.7068</v>
+        <v>0.7088</v>
       </c>
       <c r="I242" t="n">
-        <v>0.771</v>
+        <v>0.7734</v>
       </c>
       <c r="J242" t="n">
-        <v>0.1649</v>
+        <v>0.1619</v>
       </c>
       <c r="K242" t="n">
-        <v>0.2932</v>
+        <v>0.2912</v>
       </c>
       <c r="L242" t="n">
-        <v>0.229</v>
+        <v>0.2266</v>
       </c>
       <c r="M242" t="n">
         <v>164</v>
@@ -13530,22 +13530,22 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>0.8431999999999999</v>
+        <v>0.8522999999999999</v>
       </c>
       <c r="H243" t="n">
         <v>0.672</v>
       </c>
       <c r="I243" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.7622</v>
       </c>
       <c r="J243" t="n">
-        <v>0.1568</v>
+        <v>0.1477</v>
       </c>
       <c r="K243" t="n">
         <v>0.328</v>
       </c>
       <c r="L243" t="n">
-        <v>0.2424</v>
+        <v>0.2378</v>
       </c>
       <c r="M243" t="n">
         <v>164</v>
@@ -13584,22 +13584,22 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>0.8811</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="H244" t="n">
-        <v>0.756</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="I244" t="n">
-        <v>0.8186</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="J244" t="n">
-        <v>0.1189</v>
+        <v>0.1184</v>
       </c>
       <c r="K244" t="n">
-        <v>0.244</v>
+        <v>0.2394</v>
       </c>
       <c r="L244" t="n">
-        <v>0.1814</v>
+        <v>0.1789</v>
       </c>
       <c r="M244" t="n">
         <v>164</v>
@@ -13746,22 +13746,22 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>0.7625999999999999</v>
+        <v>0.641</v>
       </c>
       <c r="H247" t="n">
-        <v>0.5714</v>
+        <v>0.4984</v>
       </c>
       <c r="I247" t="n">
-        <v>0.667</v>
+        <v>0.5697</v>
       </c>
       <c r="J247" t="n">
-        <v>0.2374</v>
+        <v>0.359</v>
       </c>
       <c r="K247" t="n">
-        <v>0.4286</v>
+        <v>0.5016</v>
       </c>
       <c r="L247" t="n">
-        <v>0.333</v>
+        <v>0.4303</v>
       </c>
       <c r="M247" t="n">
         <v>164</v>
@@ -13800,22 +13800,22 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>0.8545</v>
+        <v>0.8358</v>
       </c>
       <c r="H248" t="n">
-        <v>0.7351</v>
+        <v>0.7035</v>
       </c>
       <c r="I248" t="n">
-        <v>0.7948</v>
+        <v>0.7696</v>
       </c>
       <c r="J248" t="n">
-        <v>0.1455</v>
+        <v>0.1642</v>
       </c>
       <c r="K248" t="n">
-        <v>0.2649</v>
+        <v>0.2965</v>
       </c>
       <c r="L248" t="n">
-        <v>0.2052</v>
+        <v>0.2304</v>
       </c>
       <c r="M248" t="n">
         <v>164</v>
@@ -13854,22 +13854,22 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>0.6165</v>
+        <v>0.4961</v>
       </c>
       <c r="H249" t="n">
-        <v>0.4756</v>
+        <v>0.3731</v>
       </c>
       <c r="I249" t="n">
-        <v>0.546</v>
+        <v>0.4346</v>
       </c>
       <c r="J249" t="n">
-        <v>0.3835</v>
+        <v>0.5039</v>
       </c>
       <c r="K249" t="n">
-        <v>0.5244</v>
+        <v>0.6269</v>
       </c>
       <c r="L249" t="n">
-        <v>0.454</v>
+        <v>0.5654</v>
       </c>
       <c r="M249" t="n">
         <v>164</v>
@@ -13908,22 +13908,22 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>0.8692</v>
+        <v>0.8565</v>
       </c>
       <c r="H250" t="n">
-        <v>0.781</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="I250" t="n">
-        <v>0.8250999999999999</v>
+        <v>0.8055</v>
       </c>
       <c r="J250" t="n">
-        <v>0.1308</v>
+        <v>0.1435</v>
       </c>
       <c r="K250" t="n">
-        <v>0.219</v>
+        <v>0.2455</v>
       </c>
       <c r="L250" t="n">
-        <v>0.1749</v>
+        <v>0.1945</v>
       </c>
       <c r="M250" t="n">
         <v>164</v>
@@ -13962,22 +13962,22 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>0.5975</v>
+        <v>0.4582</v>
       </c>
       <c r="H251" t="n">
-        <v>0.4306</v>
+        <v>0.3566</v>
       </c>
       <c r="I251" t="n">
-        <v>0.514</v>
+        <v>0.4074</v>
       </c>
       <c r="J251" t="n">
-        <v>0.4025</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="K251" t="n">
-        <v>0.5694</v>
+        <v>0.6434</v>
       </c>
       <c r="L251" t="n">
-        <v>0.486</v>
+        <v>0.5926</v>
       </c>
       <c r="M251" t="n">
         <v>164</v>
@@ -14016,22 +14016,22 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>0.8088</v>
+        <v>0.7262</v>
       </c>
       <c r="H252" t="n">
-        <v>0.6219</v>
+        <v>0.5612</v>
       </c>
       <c r="I252" t="n">
-        <v>0.7153</v>
+        <v>0.6437</v>
       </c>
       <c r="J252" t="n">
-        <v>0.1912</v>
+        <v>0.2738</v>
       </c>
       <c r="K252" t="n">
-        <v>0.3781</v>
+        <v>0.4388</v>
       </c>
       <c r="L252" t="n">
-        <v>0.2847</v>
+        <v>0.3563</v>
       </c>
       <c r="M252" t="n">
         <v>164</v>
@@ -14070,22 +14070,22 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>0.8505</v>
+        <v>0.8114</v>
       </c>
       <c r="H253" t="n">
-        <v>0.7547</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="I253" t="n">
-        <v>0.8026</v>
+        <v>0.7538</v>
       </c>
       <c r="J253" t="n">
-        <v>0.1495</v>
+        <v>0.1886</v>
       </c>
       <c r="K253" t="n">
-        <v>0.2453</v>
+        <v>0.3039</v>
       </c>
       <c r="L253" t="n">
-        <v>0.1974</v>
+        <v>0.2462</v>
       </c>
       <c r="M253" t="n">
         <v>164</v>
@@ -14124,22 +14124,22 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>0.7575</v>
+        <v>0.6472</v>
       </c>
       <c r="H254" t="n">
-        <v>0.5629</v>
+        <v>0.4751</v>
       </c>
       <c r="I254" t="n">
-        <v>0.6602</v>
+        <v>0.5612</v>
       </c>
       <c r="J254" t="n">
-        <v>0.2425</v>
+        <v>0.3528</v>
       </c>
       <c r="K254" t="n">
-        <v>0.4371</v>
+        <v>0.5249</v>
       </c>
       <c r="L254" t="n">
-        <v>0.3398</v>
+        <v>0.4388</v>
       </c>
       <c r="M254" t="n">
         <v>164</v>
@@ -14178,22 +14178,22 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>0.7176</v>
+        <v>0.6055</v>
       </c>
       <c r="H255" t="n">
-        <v>0.5521</v>
+        <v>0.4886</v>
       </c>
       <c r="I255" t="n">
-        <v>0.6348</v>
+        <v>0.547</v>
       </c>
       <c r="J255" t="n">
-        <v>0.2824</v>
+        <v>0.3945</v>
       </c>
       <c r="K255" t="n">
-        <v>0.4479</v>
+        <v>0.5114</v>
       </c>
       <c r="L255" t="n">
-        <v>0.3652</v>
+        <v>0.453</v>
       </c>
       <c r="M255" t="n">
         <v>164</v>
@@ -14232,22 +14232,22 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>0.7716</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="H256" t="n">
-        <v>0.5966</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="I256" t="n">
-        <v>0.6841</v>
+        <v>0.6054</v>
       </c>
       <c r="J256" t="n">
-        <v>0.2284</v>
+        <v>0.2969</v>
       </c>
       <c r="K256" t="n">
-        <v>0.4034</v>
+        <v>0.4924</v>
       </c>
       <c r="L256" t="n">
-        <v>0.3159</v>
+        <v>0.3946</v>
       </c>
       <c r="M256" t="n">
         <v>164</v>
@@ -14286,22 +14286,22 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>0.8604000000000001</v>
+        <v>0.8431</v>
       </c>
       <c r="H257" t="n">
-        <v>0.7679</v>
+        <v>0.735</v>
       </c>
       <c r="I257" t="n">
-        <v>0.8142</v>
+        <v>0.789</v>
       </c>
       <c r="J257" t="n">
-        <v>0.1396</v>
+        <v>0.1569</v>
       </c>
       <c r="K257" t="n">
-        <v>0.2321</v>
+        <v>0.265</v>
       </c>
       <c r="L257" t="n">
-        <v>0.1858</v>
+        <v>0.211</v>
       </c>
       <c r="M257" t="n">
         <v>164</v>
@@ -14340,22 +14340,22 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>0.4765</v>
+        <v>0.3621</v>
       </c>
       <c r="H258" t="n">
-        <v>0.3375</v>
+        <v>0.2368</v>
       </c>
       <c r="I258" t="n">
-        <v>0.407</v>
+        <v>0.2994</v>
       </c>
       <c r="J258" t="n">
-        <v>0.5235</v>
+        <v>0.6379</v>
       </c>
       <c r="K258" t="n">
-        <v>0.6625</v>
+        <v>0.7632</v>
       </c>
       <c r="L258" t="n">
-        <v>0.593</v>
+        <v>0.7006</v>
       </c>
       <c r="M258" t="n">
         <v>164</v>
@@ -14394,22 +14394,22 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>0.482</v>
+        <v>0.361</v>
       </c>
       <c r="H259" t="n">
-        <v>0.3287</v>
+        <v>0.2354</v>
       </c>
       <c r="I259" t="n">
-        <v>0.4054</v>
+        <v>0.2982</v>
       </c>
       <c r="J259" t="n">
-        <v>0.518</v>
+        <v>0.639</v>
       </c>
       <c r="K259" t="n">
-        <v>0.6713</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="L259" t="n">
-        <v>0.5946</v>
+        <v>0.7018</v>
       </c>
       <c r="M259" t="n">
         <v>164</v>
@@ -14448,22 +14448,22 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>0.7111</v>
+        <v>0.585</v>
       </c>
       <c r="H260" t="n">
-        <v>0.5604</v>
+        <v>0.4827</v>
       </c>
       <c r="I260" t="n">
-        <v>0.6358</v>
+        <v>0.5338000000000001</v>
       </c>
       <c r="J260" t="n">
-        <v>0.2889</v>
+        <v>0.415</v>
       </c>
       <c r="K260" t="n">
-        <v>0.4396</v>
+        <v>0.5173</v>
       </c>
       <c r="L260" t="n">
-        <v>0.3642</v>
+        <v>0.4662</v>
       </c>
       <c r="M260" t="n">
         <v>164</v>
@@ -14502,22 +14502,22 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>0.8738</v>
+        <v>0.8433</v>
       </c>
       <c r="H261" t="n">
-        <v>0.769</v>
+        <v>0.7175</v>
       </c>
       <c r="I261" t="n">
-        <v>0.8214</v>
+        <v>0.7804</v>
       </c>
       <c r="J261" t="n">
-        <v>0.1262</v>
+        <v>0.1567</v>
       </c>
       <c r="K261" t="n">
-        <v>0.231</v>
+        <v>0.2825</v>
       </c>
       <c r="L261" t="n">
-        <v>0.1786</v>
+        <v>0.2196</v>
       </c>
       <c r="M261" t="n">
         <v>164</v>
@@ -14556,22 +14556,22 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>0.8649</v>
+        <v>0.8399</v>
       </c>
       <c r="H262" t="n">
-        <v>0.7373</v>
+        <v>0.6882</v>
       </c>
       <c r="I262" t="n">
-        <v>0.8011</v>
+        <v>0.764</v>
       </c>
       <c r="J262" t="n">
-        <v>0.1351</v>
+        <v>0.1601</v>
       </c>
       <c r="K262" t="n">
-        <v>0.2627</v>
+        <v>0.3118</v>
       </c>
       <c r="L262" t="n">
-        <v>0.1989</v>
+        <v>0.236</v>
       </c>
       <c r="M262" t="n">
         <v>164</v>
@@ -14610,22 +14610,22 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>0.8881</v>
+        <v>0.876</v>
       </c>
       <c r="H263" t="n">
-        <v>0.7874</v>
+        <v>0.7588</v>
       </c>
       <c r="I263" t="n">
-        <v>0.8378</v>
+        <v>0.8174</v>
       </c>
       <c r="J263" t="n">
-        <v>0.1119</v>
+        <v>0.124</v>
       </c>
       <c r="K263" t="n">
-        <v>0.2126</v>
+        <v>0.2412</v>
       </c>
       <c r="L263" t="n">
-        <v>0.1622</v>
+        <v>0.1826</v>
       </c>
       <c r="M263" t="n">
         <v>164</v>
@@ -14664,22 +14664,22 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>0.6179</v>
+        <v>0.5007</v>
       </c>
       <c r="H264" t="n">
-        <v>0.4703</v>
+        <v>0.3892</v>
       </c>
       <c r="I264" t="n">
-        <v>0.5441</v>
+        <v>0.445</v>
       </c>
       <c r="J264" t="n">
-        <v>0.3821</v>
+        <v>0.4993</v>
       </c>
       <c r="K264" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.6108</v>
       </c>
       <c r="L264" t="n">
-        <v>0.4559</v>
+        <v>0.555</v>
       </c>
       <c r="M264" t="n">
         <v>164</v>
@@ -14718,22 +14718,22 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>0.6252</v>
+        <v>0.4949</v>
       </c>
       <c r="H265" t="n">
-        <v>0.4942</v>
+        <v>0.4292</v>
       </c>
       <c r="I265" t="n">
-        <v>0.5597</v>
+        <v>0.462</v>
       </c>
       <c r="J265" t="n">
-        <v>0.3748</v>
+        <v>0.5051</v>
       </c>
       <c r="K265" t="n">
-        <v>0.5058</v>
+        <v>0.5708</v>
       </c>
       <c r="L265" t="n">
-        <v>0.4403</v>
+        <v>0.538</v>
       </c>
       <c r="M265" t="n">
         <v>164</v>
@@ -14772,22 +14772,22 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>0.7943</v>
+        <v>0.7969000000000001</v>
       </c>
       <c r="H266" t="n">
-        <v>0.6087</v>
+        <v>0.6109</v>
       </c>
       <c r="I266" t="n">
-        <v>0.7015</v>
+        <v>0.7039</v>
       </c>
       <c r="J266" t="n">
-        <v>0.2057</v>
+        <v>0.2031</v>
       </c>
       <c r="K266" t="n">
-        <v>0.3913</v>
+        <v>0.3891</v>
       </c>
       <c r="L266" t="n">
-        <v>0.2985</v>
+        <v>0.2961</v>
       </c>
       <c r="M266" t="n">
         <v>164</v>
@@ -14826,22 +14826,22 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>0.4252</v>
+        <v>0.4206</v>
       </c>
       <c r="H267" t="n">
-        <v>0.3018</v>
+        <v>0.2982</v>
       </c>
       <c r="I267" t="n">
-        <v>0.3635</v>
+        <v>0.3594</v>
       </c>
       <c r="J267" t="n">
-        <v>0.5748</v>
+        <v>0.5794</v>
       </c>
       <c r="K267" t="n">
-        <v>0.6982</v>
+        <v>0.7018</v>
       </c>
       <c r="L267" t="n">
-        <v>0.6365</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="M267" t="n">
         <v>164</v>
@@ -14883,19 +14883,19 @@
         <v>0.8275</v>
       </c>
       <c r="H268" t="n">
-        <v>0.6839</v>
+        <v>0.6948</v>
       </c>
       <c r="I268" t="n">
-        <v>0.7557</v>
+        <v>0.7612</v>
       </c>
       <c r="J268" t="n">
         <v>0.1725</v>
       </c>
       <c r="K268" t="n">
-        <v>0.3161</v>
+        <v>0.3052</v>
       </c>
       <c r="L268" t="n">
-        <v>0.2443</v>
+        <v>0.2388</v>
       </c>
       <c r="M268" t="n">
         <v>164</v>
@@ -15099,19 +15099,19 @@
         <v>0.5538</v>
       </c>
       <c r="H272" t="n">
-        <v>0.401</v>
+        <v>0.3937</v>
       </c>
       <c r="I272" t="n">
-        <v>0.4774</v>
+        <v>0.4738</v>
       </c>
       <c r="J272" t="n">
         <v>0.4462</v>
       </c>
       <c r="K272" t="n">
-        <v>0.599</v>
+        <v>0.6063</v>
       </c>
       <c r="L272" t="n">
-        <v>0.5226</v>
+        <v>0.5262</v>
       </c>
       <c r="M272" t="n">
         <v>164</v>
@@ -15204,22 +15204,22 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>0.6418</v>
+        <v>0.5985</v>
       </c>
       <c r="H274" t="n">
-        <v>0.4532</v>
+        <v>0.4495</v>
       </c>
       <c r="I274" t="n">
-        <v>0.5475</v>
+        <v>0.524</v>
       </c>
       <c r="J274" t="n">
-        <v>0.3582</v>
+        <v>0.4015</v>
       </c>
       <c r="K274" t="n">
-        <v>0.5468</v>
+        <v>0.5505</v>
       </c>
       <c r="L274" t="n">
-        <v>0.4525</v>
+        <v>0.476</v>
       </c>
       <c r="M274" t="n">
         <v>164</v>
@@ -15258,22 +15258,22 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8218</v>
       </c>
       <c r="H275" t="n">
-        <v>0.6731</v>
+        <v>0.6751</v>
       </c>
       <c r="I275" t="n">
-        <v>0.745</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="J275" t="n">
-        <v>0.183</v>
+        <v>0.1782</v>
       </c>
       <c r="K275" t="n">
-        <v>0.3269</v>
+        <v>0.3249</v>
       </c>
       <c r="L275" t="n">
-        <v>0.255</v>
+        <v>0.2515</v>
       </c>
       <c r="M275" t="n">
         <v>164</v>
@@ -15312,22 +15312,22 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>0.3398</v>
+        <v>0.3387</v>
       </c>
       <c r="H276" t="n">
         <v>0.1821</v>
       </c>
       <c r="I276" t="n">
-        <v>0.261</v>
+        <v>0.2604</v>
       </c>
       <c r="J276" t="n">
-        <v>0.6602</v>
+        <v>0.6613</v>
       </c>
       <c r="K276" t="n">
         <v>0.8179</v>
       </c>
       <c r="L276" t="n">
-        <v>0.739</v>
+        <v>0.7396</v>
       </c>
       <c r="M276" t="n">
         <v>164</v>
@@ -15366,22 +15366,22 @@
         </is>
       </c>
       <c r="G277" t="n">
-        <v>0.3215</v>
+        <v>0.3108</v>
       </c>
       <c r="H277" t="n">
         <v>0.1651</v>
       </c>
       <c r="I277" t="n">
-        <v>0.2433</v>
+        <v>0.238</v>
       </c>
       <c r="J277" t="n">
-        <v>0.6785</v>
+        <v>0.6892</v>
       </c>
       <c r="K277" t="n">
         <v>0.8349</v>
       </c>
       <c r="L277" t="n">
-        <v>0.7567</v>
+        <v>0.762</v>
       </c>
       <c r="M277" t="n">
         <v>164</v>
@@ -15423,19 +15423,19 @@
         <v>0.5182</v>
       </c>
       <c r="H278" t="n">
-        <v>0.3858</v>
+        <v>0.3847</v>
       </c>
       <c r="I278" t="n">
-        <v>0.452</v>
+        <v>0.4514</v>
       </c>
       <c r="J278" t="n">
         <v>0.4818</v>
       </c>
       <c r="K278" t="n">
-        <v>0.6142</v>
+        <v>0.6153</v>
       </c>
       <c r="L278" t="n">
-        <v>0.548</v>
+        <v>0.5486</v>
       </c>
       <c r="M278" t="n">
         <v>164</v>
@@ -15474,22 +15474,22 @@
         </is>
       </c>
       <c r="G279" t="n">
-        <v>0.7816</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="H279" t="n">
-        <v>0.6748</v>
+        <v>0.6812</v>
       </c>
       <c r="I279" t="n">
-        <v>0.7282</v>
+        <v>0.7325</v>
       </c>
       <c r="J279" t="n">
-        <v>0.2184</v>
+        <v>0.2162</v>
       </c>
       <c r="K279" t="n">
-        <v>0.3252</v>
+        <v>0.3188</v>
       </c>
       <c r="L279" t="n">
-        <v>0.2718</v>
+        <v>0.2675</v>
       </c>
       <c r="M279" t="n">
         <v>164</v>
@@ -15528,22 +15528,22 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>0.7935</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="H280" t="n">
-        <v>0.6573</v>
+        <v>0.6594</v>
       </c>
       <c r="I280" t="n">
-        <v>0.7254</v>
+        <v>0.7272</v>
       </c>
       <c r="J280" t="n">
-        <v>0.2065</v>
+        <v>0.2051</v>
       </c>
       <c r="K280" t="n">
-        <v>0.3427</v>
+        <v>0.3406</v>
       </c>
       <c r="L280" t="n">
-        <v>0.2746</v>
+        <v>0.2728</v>
       </c>
       <c r="M280" t="n">
         <v>164</v>
@@ -15582,22 +15582,22 @@
         </is>
       </c>
       <c r="G281" t="n">
-        <v>0.8239</v>
+        <v>0.8307</v>
       </c>
       <c r="H281" t="n">
         <v>0.7314000000000001</v>
       </c>
       <c r="I281" t="n">
-        <v>0.7776</v>
+        <v>0.781</v>
       </c>
       <c r="J281" t="n">
-        <v>0.1761</v>
+        <v>0.1693</v>
       </c>
       <c r="K281" t="n">
         <v>0.2686</v>
       </c>
       <c r="L281" t="n">
-        <v>0.2224</v>
+        <v>0.219</v>
       </c>
       <c r="M281" t="n">
         <v>164</v>
@@ -15693,19 +15693,19 @@
         <v>0.4772</v>
       </c>
       <c r="H283" t="n">
-        <v>0.3207</v>
+        <v>0.319</v>
       </c>
       <c r="I283" t="n">
-        <v>0.399</v>
+        <v>0.3981</v>
       </c>
       <c r="J283" t="n">
         <v>0.5228</v>
       </c>
       <c r="K283" t="n">
-        <v>0.6793</v>
+        <v>0.681</v>
       </c>
       <c r="L283" t="n">
-        <v>0.601</v>
+        <v>0.6019</v>
       </c>
       <c r="M283" t="n">
         <v>164</v>
@@ -15744,22 +15744,22 @@
         </is>
       </c>
       <c r="G284" t="n">
-        <v>0.2772</v>
+        <v>0.2664</v>
       </c>
       <c r="H284" t="n">
-        <v>0.1748</v>
+        <v>0.172</v>
       </c>
       <c r="I284" t="n">
-        <v>0.226</v>
+        <v>0.2192</v>
       </c>
       <c r="J284" t="n">
-        <v>0.7228</v>
+        <v>0.7336</v>
       </c>
       <c r="K284" t="n">
-        <v>0.8252</v>
+        <v>0.828</v>
       </c>
       <c r="L284" t="n">
-        <v>0.774</v>
+        <v>0.7808</v>
       </c>
       <c r="M284" t="n">
         <v>164</v>
@@ -15852,22 +15852,22 @@
         </is>
       </c>
       <c r="G286" t="n">
-        <v>0.2458</v>
+        <v>0.2416</v>
       </c>
       <c r="H286" t="n">
-        <v>0.1475</v>
+        <v>0.1394</v>
       </c>
       <c r="I286" t="n">
-        <v>0.1966</v>
+        <v>0.1905</v>
       </c>
       <c r="J286" t="n">
-        <v>0.7542</v>
+        <v>0.7584</v>
       </c>
       <c r="K286" t="n">
-        <v>0.8525</v>
+        <v>0.8606</v>
       </c>
       <c r="L286" t="n">
-        <v>0.8034</v>
+        <v>0.8095</v>
       </c>
       <c r="M286" t="n">
         <v>164</v>
@@ -15909,19 +15909,19 @@
         <v>0.4032</v>
       </c>
       <c r="H287" t="n">
-        <v>0.2732</v>
+        <v>0.2671</v>
       </c>
       <c r="I287" t="n">
-        <v>0.3382</v>
+        <v>0.3352</v>
       </c>
       <c r="J287" t="n">
         <v>0.5968</v>
       </c>
       <c r="K287" t="n">
-        <v>0.7268</v>
+        <v>0.7329</v>
       </c>
       <c r="L287" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="M287" t="n">
         <v>164</v>
@@ -15963,19 +15963,19 @@
         <v>0.5396</v>
       </c>
       <c r="H288" t="n">
-        <v>0.3852</v>
+        <v>0.3792</v>
       </c>
       <c r="I288" t="n">
-        <v>0.4624</v>
+        <v>0.4594</v>
       </c>
       <c r="J288" t="n">
         <v>0.4604</v>
       </c>
       <c r="K288" t="n">
-        <v>0.6148</v>
+        <v>0.6208</v>
       </c>
       <c r="L288" t="n">
-        <v>0.5376</v>
+        <v>0.5406</v>
       </c>
       <c r="M288" t="n">
         <v>164</v>
@@ -16014,22 +16014,22 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>0.3663</v>
+        <v>0.361</v>
       </c>
       <c r="H289" t="n">
-        <v>0.2214</v>
+        <v>0.2152</v>
       </c>
       <c r="I289" t="n">
-        <v>0.2938</v>
+        <v>0.2881</v>
       </c>
       <c r="J289" t="n">
-        <v>0.6337</v>
+        <v>0.639</v>
       </c>
       <c r="K289" t="n">
-        <v>0.7786</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="L289" t="n">
-        <v>0.7062</v>
+        <v>0.7119</v>
       </c>
       <c r="M289" t="n">
         <v>164</v>
@@ -16068,22 +16068,22 @@
         </is>
       </c>
       <c r="G290" t="n">
-        <v>0.359</v>
+        <v>0.3568</v>
       </c>
       <c r="H290" t="n">
-        <v>0.208</v>
+        <v>0.2067</v>
       </c>
       <c r="I290" t="n">
-        <v>0.2835</v>
+        <v>0.2818</v>
       </c>
       <c r="J290" t="n">
-        <v>0.641</v>
+        <v>0.6432</v>
       </c>
       <c r="K290" t="n">
-        <v>0.792</v>
+        <v>0.7933</v>
       </c>
       <c r="L290" t="n">
-        <v>0.7165</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="M290" t="n">
         <v>164</v>
@@ -16122,22 +16122,22 @@
         </is>
       </c>
       <c r="G291" t="n">
-        <v>0.4107</v>
+        <v>0.3822</v>
       </c>
       <c r="H291" t="n">
-        <v>0.2555</v>
+        <v>0.2413</v>
       </c>
       <c r="I291" t="n">
-        <v>0.3331</v>
+        <v>0.3117</v>
       </c>
       <c r="J291" t="n">
-        <v>0.5893</v>
+        <v>0.6178</v>
       </c>
       <c r="K291" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.7587</v>
       </c>
       <c r="L291" t="n">
-        <v>0.6669</v>
+        <v>0.6883</v>
       </c>
       <c r="M291" t="n">
         <v>164</v>
@@ -16230,22 +16230,22 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>0.2221</v>
+        <v>0.219</v>
       </c>
       <c r="H293" t="n">
-        <v>0.126</v>
+        <v>0.1239</v>
       </c>
       <c r="I293" t="n">
-        <v>0.174</v>
+        <v>0.1714</v>
       </c>
       <c r="J293" t="n">
-        <v>0.7779</v>
+        <v>0.781</v>
       </c>
       <c r="K293" t="n">
-        <v>0.874</v>
+        <v>0.8761</v>
       </c>
       <c r="L293" t="n">
-        <v>0.826</v>
+        <v>0.8286</v>
       </c>
       <c r="M293" t="n">
         <v>164</v>
@@ -16338,22 +16338,22 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>0.3408</v>
+        <v>0.3365</v>
       </c>
       <c r="H295" t="n">
-        <v>0.1858</v>
+        <v>0.1828</v>
       </c>
       <c r="I295" t="n">
-        <v>0.2633</v>
+        <v>0.2596</v>
       </c>
       <c r="J295" t="n">
-        <v>0.6592</v>
+        <v>0.6635</v>
       </c>
       <c r="K295" t="n">
-        <v>0.8142</v>
+        <v>0.8172</v>
       </c>
       <c r="L295" t="n">
-        <v>0.7367</v>
+        <v>0.7403999999999999</v>
       </c>
       <c r="M295" t="n">
         <v>164</v>
@@ -16449,19 +16449,19 @@
         <v>0.5708</v>
       </c>
       <c r="H297" t="n">
-        <v>0.471</v>
+        <v>0.4708</v>
       </c>
       <c r="I297" t="n">
-        <v>0.5209</v>
+        <v>0.5208</v>
       </c>
       <c r="J297" t="n">
         <v>0.4292</v>
       </c>
       <c r="K297" t="n">
-        <v>0.529</v>
+        <v>0.5292</v>
       </c>
       <c r="L297" t="n">
-        <v>0.4791</v>
+        <v>0.4792</v>
       </c>
       <c r="M297" t="n">
         <v>164</v>
@@ -16503,19 +16503,19 @@
         <v>0.7098</v>
       </c>
       <c r="H298" t="n">
-        <v>0.5535</v>
+        <v>0.5584</v>
       </c>
       <c r="I298" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.6341</v>
       </c>
       <c r="J298" t="n">
         <v>0.2902</v>
       </c>
       <c r="K298" t="n">
-        <v>0.4465</v>
+        <v>0.4416</v>
       </c>
       <c r="L298" t="n">
-        <v>0.3684</v>
+        <v>0.3659</v>
       </c>
       <c r="M298" t="n">
         <v>164</v>
@@ -16554,22 +16554,22 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>0.2722</v>
+        <v>0.2696</v>
       </c>
       <c r="H299" t="n">
-        <v>0.1845</v>
+        <v>0.1797</v>
       </c>
       <c r="I299" t="n">
-        <v>0.2284</v>
+        <v>0.2246</v>
       </c>
       <c r="J299" t="n">
-        <v>0.7278</v>
+        <v>0.7304</v>
       </c>
       <c r="K299" t="n">
-        <v>0.8155</v>
+        <v>0.8203</v>
       </c>
       <c r="L299" t="n">
-        <v>0.7716</v>
+        <v>0.7754</v>
       </c>
       <c r="M299" t="n">
         <v>164</v>
@@ -16608,22 +16608,22 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>0.2887</v>
+        <v>0.2798</v>
       </c>
       <c r="H300" t="n">
         <v>0.1616</v>
       </c>
       <c r="I300" t="n">
-        <v>0.2252</v>
+        <v>0.2207</v>
       </c>
       <c r="J300" t="n">
-        <v>0.7113</v>
+        <v>0.7202</v>
       </c>
       <c r="K300" t="n">
         <v>0.8384</v>
       </c>
       <c r="L300" t="n">
-        <v>0.7748</v>
+        <v>0.7793</v>
       </c>
       <c r="M300" t="n">
         <v>164</v>
@@ -16665,19 +16665,19 @@
         <v>0.8693</v>
       </c>
       <c r="H301" t="n">
-        <v>0.778</v>
+        <v>0.7812</v>
       </c>
       <c r="I301" t="n">
-        <v>0.8236</v>
+        <v>0.8252</v>
       </c>
       <c r="J301" t="n">
         <v>0.1307</v>
       </c>
       <c r="K301" t="n">
-        <v>0.222</v>
+        <v>0.2188</v>
       </c>
       <c r="L301" t="n">
-        <v>0.1764</v>
+        <v>0.1748</v>
       </c>
       <c r="M301" t="n">
         <v>164</v>
@@ -16716,22 +16716,22 @@
         </is>
       </c>
       <c r="G302" t="n">
-        <v>0.5309</v>
+        <v>0.541</v>
       </c>
       <c r="H302" t="n">
-        <v>0.387</v>
+        <v>0.3887</v>
       </c>
       <c r="I302" t="n">
+        <v>0.4648</v>
+      </c>
+      <c r="J302" t="n">
         <v>0.459</v>
       </c>
-      <c r="J302" t="n">
-        <v>0.4691</v>
-      </c>
       <c r="K302" t="n">
-        <v>0.613</v>
+        <v>0.6113</v>
       </c>
       <c r="L302" t="n">
-        <v>0.541</v>
+        <v>0.5352</v>
       </c>
       <c r="M302" t="n">
         <v>164</v>
@@ -16770,22 +16770,22 @@
         </is>
       </c>
       <c r="G303" t="n">
-        <v>0.737</v>
+        <v>0.7447</v>
       </c>
       <c r="H303" t="n">
-        <v>0.6022</v>
+        <v>0.6077</v>
       </c>
       <c r="I303" t="n">
-        <v>0.6696</v>
+        <v>0.6762</v>
       </c>
       <c r="J303" t="n">
-        <v>0.263</v>
+        <v>0.2553</v>
       </c>
       <c r="K303" t="n">
-        <v>0.3978</v>
+        <v>0.3923</v>
       </c>
       <c r="L303" t="n">
-        <v>0.3304</v>
+        <v>0.3238</v>
       </c>
       <c r="M303" t="n">
         <v>164</v>
@@ -16824,22 +16824,22 @@
         </is>
       </c>
       <c r="G304" t="n">
-        <v>0.8219</v>
+        <v>0.8295</v>
       </c>
       <c r="H304" t="n">
-        <v>0.6975</v>
+        <v>0.7016</v>
       </c>
       <c r="I304" t="n">
-        <v>0.7597</v>
+        <v>0.7655</v>
       </c>
       <c r="J304" t="n">
-        <v>0.1781</v>
+        <v>0.1705</v>
       </c>
       <c r="K304" t="n">
-        <v>0.3025</v>
+        <v>0.2984</v>
       </c>
       <c r="L304" t="n">
-        <v>0.2403</v>
+        <v>0.2345</v>
       </c>
       <c r="M304" t="n">
         <v>164</v>
@@ -16878,22 +16878,22 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>0.6698</v>
+        <v>0.6707</v>
       </c>
       <c r="H305" t="n">
         <v>0.5585</v>
       </c>
       <c r="I305" t="n">
-        <v>0.6142</v>
+        <v>0.6146</v>
       </c>
       <c r="J305" t="n">
-        <v>0.3302</v>
+        <v>0.3293</v>
       </c>
       <c r="K305" t="n">
         <v>0.4415</v>
       </c>
       <c r="L305" t="n">
-        <v>0.3858</v>
+        <v>0.3854</v>
       </c>
       <c r="M305" t="n">
         <v>164</v>
@@ -16986,22 +16986,22 @@
         </is>
       </c>
       <c r="G307" t="n">
-        <v>0.7256</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="H307" t="n">
-        <v>0.5689</v>
+        <v>0.5572</v>
       </c>
       <c r="I307" t="n">
-        <v>0.6472</v>
+        <v>0.6382</v>
       </c>
       <c r="J307" t="n">
-        <v>0.2744</v>
+        <v>0.2807</v>
       </c>
       <c r="K307" t="n">
-        <v>0.4311</v>
+        <v>0.4428</v>
       </c>
       <c r="L307" t="n">
-        <v>0.3528</v>
+        <v>0.3618</v>
       </c>
       <c r="M307" t="n">
         <v>164</v>
@@ -17040,22 +17040,22 @@
         </is>
       </c>
       <c r="G308" t="n">
-        <v>0.86</v>
+        <v>0.8623</v>
       </c>
       <c r="H308" t="n">
         <v>0.7611</v>
       </c>
       <c r="I308" t="n">
-        <v>0.8106</v>
+        <v>0.8117</v>
       </c>
       <c r="J308" t="n">
-        <v>0.14</v>
+        <v>0.1377</v>
       </c>
       <c r="K308" t="n">
         <v>0.2389</v>
       </c>
       <c r="L308" t="n">
-        <v>0.1894</v>
+        <v>0.1883</v>
       </c>
       <c r="M308" t="n">
         <v>164</v>
@@ -17151,19 +17151,19 @@
         <v>0.3791</v>
       </c>
       <c r="H310" t="n">
-        <v>0.2614</v>
+        <v>0.2491</v>
       </c>
       <c r="I310" t="n">
-        <v>0.3203</v>
+        <v>0.3141</v>
       </c>
       <c r="J310" t="n">
         <v>0.6209</v>
       </c>
       <c r="K310" t="n">
-        <v>0.7386</v>
+        <v>0.7509</v>
       </c>
       <c r="L310" t="n">
-        <v>0.6797</v>
+        <v>0.6859</v>
       </c>
       <c r="M310" t="n">
         <v>164</v>
@@ -17256,22 +17256,22 @@
         </is>
       </c>
       <c r="G312" t="n">
-        <v>0.8405</v>
+        <v>0.8453000000000001</v>
       </c>
       <c r="H312" t="n">
-        <v>0.7302999999999999</v>
+        <v>0.7397</v>
       </c>
       <c r="I312" t="n">
-        <v>0.7854</v>
+        <v>0.7925</v>
       </c>
       <c r="J312" t="n">
-        <v>0.1595</v>
+        <v>0.1547</v>
       </c>
       <c r="K312" t="n">
-        <v>0.2697</v>
+        <v>0.2603</v>
       </c>
       <c r="L312" t="n">
-        <v>0.2146</v>
+        <v>0.2075</v>
       </c>
       <c r="M312" t="n">
         <v>164</v>
@@ -17310,22 +17310,22 @@
         </is>
       </c>
       <c r="G313" t="n">
-        <v>0.8494</v>
+        <v>0.8547</v>
       </c>
       <c r="H313" t="n">
         <v>0.7287</v>
       </c>
       <c r="I313" t="n">
-        <v>0.789</v>
+        <v>0.7917</v>
       </c>
       <c r="J313" t="n">
-        <v>0.1506</v>
+        <v>0.1453</v>
       </c>
       <c r="K313" t="n">
         <v>0.2713</v>
       </c>
       <c r="L313" t="n">
-        <v>0.211</v>
+        <v>0.2083</v>
       </c>
       <c r="M313" t="n">
         <v>164</v>
@@ -17364,22 +17364,22 @@
         </is>
       </c>
       <c r="G314" t="n">
-        <v>0.8743</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="H314" t="n">
         <v>0.7781</v>
       </c>
       <c r="I314" t="n">
-        <v>0.8262</v>
+        <v>0.8273</v>
       </c>
       <c r="J314" t="n">
-        <v>0.1257</v>
+        <v>0.1235</v>
       </c>
       <c r="K314" t="n">
         <v>0.2219</v>
       </c>
       <c r="L314" t="n">
-        <v>0.1738</v>
+        <v>0.1727</v>
       </c>
       <c r="M314" t="n">
         <v>164</v>
@@ -17418,22 +17418,22 @@
         </is>
       </c>
       <c r="G315" t="n">
-        <v>0.5929</v>
+        <v>0.5998</v>
       </c>
       <c r="H315" t="n">
-        <v>0.3877</v>
+        <v>0.3912</v>
       </c>
       <c r="I315" t="n">
-        <v>0.4903</v>
+        <v>0.4955</v>
       </c>
       <c r="J315" t="n">
-        <v>0.4071</v>
+        <v>0.4002</v>
       </c>
       <c r="K315" t="n">
-        <v>0.6123</v>
+        <v>0.6088</v>
       </c>
       <c r="L315" t="n">
-        <v>0.5097</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="M315" t="n">
         <v>164</v>
@@ -17472,22 +17472,22 @@
         </is>
       </c>
       <c r="G316" t="n">
-        <v>0.6038</v>
+        <v>0.6016</v>
       </c>
       <c r="H316" t="n">
         <v>0.44</v>
       </c>
       <c r="I316" t="n">
-        <v>0.5219</v>
+        <v>0.5208</v>
       </c>
       <c r="J316" t="n">
-        <v>0.3962</v>
+        <v>0.3984</v>
       </c>
       <c r="K316" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="L316" t="n">
-        <v>0.4781</v>
+        <v>0.4792</v>
       </c>
       <c r="M316" t="n">
         <v>164</v>
@@ -17526,22 +17526,22 @@
         </is>
       </c>
       <c r="G317" t="n">
-        <v>0.1987</v>
+        <v>0.1943</v>
       </c>
       <c r="H317" t="n">
-        <v>0.1437</v>
+        <v>0.1404</v>
       </c>
       <c r="I317" t="n">
-        <v>0.1712</v>
+        <v>0.1674</v>
       </c>
       <c r="J317" t="n">
-        <v>0.8013</v>
+        <v>0.8057</v>
       </c>
       <c r="K317" t="n">
-        <v>0.8563</v>
+        <v>0.8596</v>
       </c>
       <c r="L317" t="n">
-        <v>0.8288</v>
+        <v>0.8326</v>
       </c>
       <c r="M317" t="n">
         <v>164</v>
@@ -17580,22 +17580,22 @@
         </is>
       </c>
       <c r="G318" t="n">
-        <v>0.3085</v>
+        <v>0.3039</v>
       </c>
       <c r="H318" t="n">
-        <v>0.2204</v>
+        <v>0.2177</v>
       </c>
       <c r="I318" t="n">
-        <v>0.2644</v>
+        <v>0.2608</v>
       </c>
       <c r="J318" t="n">
-        <v>0.6915</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="K318" t="n">
-        <v>0.7796</v>
+        <v>0.7823</v>
       </c>
       <c r="L318" t="n">
-        <v>0.7356</v>
+        <v>0.7392</v>
       </c>
       <c r="M318" t="n">
         <v>164</v>
@@ -17634,22 +17634,22 @@
         </is>
       </c>
       <c r="G319" t="n">
-        <v>0.4712</v>
+        <v>0.4699</v>
       </c>
       <c r="H319" t="n">
         <v>0.2896</v>
       </c>
       <c r="I319" t="n">
-        <v>0.3804</v>
+        <v>0.3798</v>
       </c>
       <c r="J319" t="n">
-        <v>0.5288</v>
+        <v>0.5301</v>
       </c>
       <c r="K319" t="n">
         <v>0.7104</v>
       </c>
       <c r="L319" t="n">
-        <v>0.6196</v>
+        <v>0.6202</v>
       </c>
       <c r="M319" t="n">
         <v>164</v>
@@ -17691,19 +17691,19 @@
         <v>0.2658</v>
       </c>
       <c r="H320" t="n">
-        <v>0.1885</v>
+        <v>0.1838</v>
       </c>
       <c r="I320" t="n">
-        <v>0.2272</v>
+        <v>0.2248</v>
       </c>
       <c r="J320" t="n">
         <v>0.7342</v>
       </c>
       <c r="K320" t="n">
-        <v>0.8115</v>
+        <v>0.8162</v>
       </c>
       <c r="L320" t="n">
-        <v>0.7728</v>
+        <v>0.7752</v>
       </c>
       <c r="M320" t="n">
         <v>164</v>
@@ -17742,22 +17742,22 @@
         </is>
       </c>
       <c r="G321" t="n">
-        <v>0.2923</v>
+        <v>0.2834</v>
       </c>
       <c r="H321" t="n">
-        <v>0.17</v>
+        <v>0.1668</v>
       </c>
       <c r="I321" t="n">
-        <v>0.2312</v>
+        <v>0.2251</v>
       </c>
       <c r="J321" t="n">
-        <v>0.7077</v>
+        <v>0.7166</v>
       </c>
       <c r="K321" t="n">
-        <v>0.83</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="L321" t="n">
-        <v>0.7688</v>
+        <v>0.7749</v>
       </c>
       <c r="M321" t="n">
         <v>164</v>
@@ -17796,22 +17796,22 @@
         </is>
       </c>
       <c r="G322" t="n">
-        <v>0.3181</v>
+        <v>0.3007</v>
       </c>
       <c r="H322" t="n">
-        <v>0.1677</v>
+        <v>0.1551</v>
       </c>
       <c r="I322" t="n">
-        <v>0.2429</v>
+        <v>0.2279</v>
       </c>
       <c r="J322" t="n">
-        <v>0.6819</v>
+        <v>0.6993</v>
       </c>
       <c r="K322" t="n">
-        <v>0.8323</v>
+        <v>0.8449</v>
       </c>
       <c r="L322" t="n">
-        <v>0.7571</v>
+        <v>0.7721</v>
       </c>
       <c r="M322" t="n">
         <v>164</v>
@@ -18012,22 +18012,22 @@
         </is>
       </c>
       <c r="G326" t="n">
-        <v>0.2594</v>
+        <v>0.2502</v>
       </c>
       <c r="H326" t="n">
         <v>0.1634</v>
       </c>
       <c r="I326" t="n">
-        <v>0.2114</v>
+        <v>0.2068</v>
       </c>
       <c r="J326" t="n">
-        <v>0.7406</v>
+        <v>0.7498</v>
       </c>
       <c r="K326" t="n">
         <v>0.8366</v>
       </c>
       <c r="L326" t="n">
-        <v>0.7886</v>
+        <v>0.7932</v>
       </c>
       <c r="M326" t="n">
         <v>164</v>
@@ -18228,22 +18228,22 @@
         </is>
       </c>
       <c r="G330" t="n">
-        <v>0.2569</v>
+        <v>0.2529</v>
       </c>
       <c r="H330" t="n">
-        <v>0.1464</v>
+        <v>0.1426</v>
       </c>
       <c r="I330" t="n">
-        <v>0.2016</v>
+        <v>0.1978</v>
       </c>
       <c r="J330" t="n">
-        <v>0.7431</v>
+        <v>0.7471</v>
       </c>
       <c r="K330" t="n">
-        <v>0.8536</v>
+        <v>0.8574000000000001</v>
       </c>
       <c r="L330" t="n">
-        <v>0.7984</v>
+        <v>0.8022</v>
       </c>
       <c r="M330" t="n">
         <v>164</v>
@@ -18282,22 +18282,22 @@
         </is>
       </c>
       <c r="G331" t="n">
-        <v>0.2262</v>
+        <v>0.2213</v>
       </c>
       <c r="H331" t="n">
-        <v>0.1347</v>
+        <v>0.1319</v>
       </c>
       <c r="I331" t="n">
-        <v>0.1804</v>
+        <v>0.1766</v>
       </c>
       <c r="J331" t="n">
-        <v>0.7738</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="K331" t="n">
-        <v>0.8653</v>
+        <v>0.8681</v>
       </c>
       <c r="L331" t="n">
-        <v>0.8196</v>
+        <v>0.8234</v>
       </c>
       <c r="M331" t="n">
         <v>164</v>
@@ -18336,22 +18336,22 @@
         </is>
       </c>
       <c r="G332" t="n">
-        <v>0.7902</v>
+        <v>0.7952</v>
       </c>
       <c r="H332" t="n">
         <v>0.6409</v>
       </c>
       <c r="I332" t="n">
-        <v>0.7156</v>
+        <v>0.7181</v>
       </c>
       <c r="J332" t="n">
-        <v>0.2098</v>
+        <v>0.2048</v>
       </c>
       <c r="K332" t="n">
         <v>0.3591</v>
       </c>
       <c r="L332" t="n">
-        <v>0.2844</v>
+        <v>0.2819</v>
       </c>
       <c r="M332" t="n">
         <v>164</v>
@@ -18390,22 +18390,22 @@
         </is>
       </c>
       <c r="G333" t="n">
-        <v>0.8300999999999999</v>
+        <v>0.8334</v>
       </c>
       <c r="H333" t="n">
-        <v>0.7327</v>
+        <v>0.7353</v>
       </c>
       <c r="I333" t="n">
-        <v>0.7814</v>
+        <v>0.7844</v>
       </c>
       <c r="J333" t="n">
-        <v>0.1699</v>
+        <v>0.1666</v>
       </c>
       <c r="K333" t="n">
-        <v>0.2673</v>
+        <v>0.2647</v>
       </c>
       <c r="L333" t="n">
-        <v>0.2186</v>
+        <v>0.2156</v>
       </c>
       <c r="M333" t="n">
         <v>164</v>
@@ -18498,22 +18498,22 @@
         </is>
       </c>
       <c r="G335" t="n">
-        <v>0.7341</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="H335" t="n">
         <v>0.5726</v>
       </c>
       <c r="I335" t="n">
-        <v>0.6534</v>
+        <v>0.655</v>
       </c>
       <c r="J335" t="n">
-        <v>0.2659</v>
+        <v>0.2626</v>
       </c>
       <c r="K335" t="n">
         <v>0.4274</v>
       </c>
       <c r="L335" t="n">
-        <v>0.3466</v>
+        <v>0.345</v>
       </c>
       <c r="M335" t="n">
         <v>164</v>
@@ -18552,22 +18552,22 @@
         </is>
       </c>
       <c r="G336" t="n">
-        <v>0.7784</v>
+        <v>0.7637</v>
       </c>
       <c r="H336" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.5982</v>
       </c>
       <c r="I336" t="n">
-        <v>0.6944</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="J336" t="n">
-        <v>0.2216</v>
+        <v>0.2363</v>
       </c>
       <c r="K336" t="n">
-        <v>0.3896</v>
+        <v>0.4018</v>
       </c>
       <c r="L336" t="n">
-        <v>0.3056</v>
+        <v>0.3191</v>
       </c>
       <c r="M336" t="n">
         <v>164</v>
@@ -18606,22 +18606,22 @@
         </is>
       </c>
       <c r="G337" t="n">
-        <v>0.8679</v>
+        <v>0.8714</v>
       </c>
       <c r="H337" t="n">
         <v>0.7847</v>
       </c>
       <c r="I337" t="n">
-        <v>0.8263</v>
+        <v>0.828</v>
       </c>
       <c r="J337" t="n">
-        <v>0.1321</v>
+        <v>0.1286</v>
       </c>
       <c r="K337" t="n">
         <v>0.2153</v>
       </c>
       <c r="L337" t="n">
-        <v>0.1737</v>
+        <v>0.172</v>
       </c>
       <c r="M337" t="n">
         <v>164</v>
@@ -18663,19 +18663,19 @@
         <v>0.4527</v>
       </c>
       <c r="H338" t="n">
-        <v>0.3347</v>
+        <v>0.3338</v>
       </c>
       <c r="I338" t="n">
-        <v>0.3937</v>
+        <v>0.3932</v>
       </c>
       <c r="J338" t="n">
         <v>0.5473</v>
       </c>
       <c r="K338" t="n">
-        <v>0.6653</v>
+        <v>0.6662</v>
       </c>
       <c r="L338" t="n">
-        <v>0.6063</v>
+        <v>0.6068</v>
       </c>
       <c r="M338" t="n">
         <v>164</v>
@@ -18714,22 +18714,22 @@
         </is>
       </c>
       <c r="G339" t="n">
-        <v>0.4168</v>
+        <v>0.4186</v>
       </c>
       <c r="H339" t="n">
-        <v>0.2853</v>
+        <v>0.2801</v>
       </c>
       <c r="I339" t="n">
-        <v>0.351</v>
+        <v>0.3494</v>
       </c>
       <c r="J339" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.5814</v>
       </c>
       <c r="K339" t="n">
-        <v>0.7147</v>
+        <v>0.7199</v>
       </c>
       <c r="L339" t="n">
-        <v>0.649</v>
+        <v>0.6506</v>
       </c>
       <c r="M339" t="n">
         <v>164</v>
@@ -18825,19 +18825,19 @@
         <v>0.8676</v>
       </c>
       <c r="H341" t="n">
-        <v>0.759</v>
+        <v>0.7633</v>
       </c>
       <c r="I341" t="n">
-        <v>0.8133</v>
+        <v>0.8154</v>
       </c>
       <c r="J341" t="n">
         <v>0.1324</v>
       </c>
       <c r="K341" t="n">
-        <v>0.241</v>
+        <v>0.2367</v>
       </c>
       <c r="L341" t="n">
-        <v>0.1867</v>
+        <v>0.1846</v>
       </c>
       <c r="M341" t="n">
         <v>164</v>
@@ -18876,22 +18876,22 @@
         </is>
       </c>
       <c r="G342" t="n">
-        <v>0.8753</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="H342" t="n">
-        <v>0.7397</v>
+        <v>0.7451</v>
       </c>
       <c r="I342" t="n">
-        <v>0.8075</v>
+        <v>0.8113</v>
       </c>
       <c r="J342" t="n">
-        <v>0.1247</v>
+        <v>0.1225</v>
       </c>
       <c r="K342" t="n">
-        <v>0.2603</v>
+        <v>0.2549</v>
       </c>
       <c r="L342" t="n">
-        <v>0.1925</v>
+        <v>0.1887</v>
       </c>
       <c r="M342" t="n">
         <v>164</v>
@@ -18930,22 +18930,22 @@
         </is>
       </c>
       <c r="G343" t="n">
-        <v>0.8709</v>
+        <v>0.8756</v>
       </c>
       <c r="H343" t="n">
         <v>0.7841</v>
       </c>
       <c r="I343" t="n">
-        <v>0.8275</v>
+        <v>0.8298</v>
       </c>
       <c r="J343" t="n">
-        <v>0.1291</v>
+        <v>0.1244</v>
       </c>
       <c r="K343" t="n">
         <v>0.2159</v>
       </c>
       <c r="L343" t="n">
-        <v>0.1725</v>
+        <v>0.1702</v>
       </c>
       <c r="M343" t="n">
         <v>164</v>
@@ -18984,22 +18984,22 @@
         </is>
       </c>
       <c r="G344" t="n">
-        <v>0.5826</v>
+        <v>0.5964</v>
       </c>
       <c r="H344" t="n">
         <v>0.4464</v>
       </c>
       <c r="I344" t="n">
-        <v>0.5145</v>
+        <v>0.5214</v>
       </c>
       <c r="J344" t="n">
-        <v>0.4174</v>
+        <v>0.4036</v>
       </c>
       <c r="K344" t="n">
         <v>0.5536</v>
       </c>
       <c r="L344" t="n">
-        <v>0.4855</v>
+        <v>0.4786</v>
       </c>
       <c r="M344" t="n">
         <v>164</v>
@@ -19038,22 +19038,22 @@
         </is>
       </c>
       <c r="G345" t="n">
-        <v>0.608</v>
+        <v>0.6089</v>
       </c>
       <c r="H345" t="n">
         <v>0.4811</v>
       </c>
       <c r="I345" t="n">
-        <v>0.5446</v>
+        <v>0.545</v>
       </c>
       <c r="J345" t="n">
-        <v>0.392</v>
+        <v>0.3911</v>
       </c>
       <c r="K345" t="n">
         <v>0.5189</v>
       </c>
       <c r="L345" t="n">
-        <v>0.4554</v>
+        <v>0.455</v>
       </c>
       <c r="M345" t="n">
         <v>164</v>
@@ -19092,22 +19092,22 @@
         </is>
       </c>
       <c r="G346" t="n">
-        <v>0.7213000000000001</v>
+        <v>0.7249</v>
       </c>
       <c r="H346" t="n">
         <v>0.5649999999999999</v>
       </c>
       <c r="I346" t="n">
-        <v>0.6432</v>
+        <v>0.6449</v>
       </c>
       <c r="J346" t="n">
-        <v>0.2787</v>
+        <v>0.2751</v>
       </c>
       <c r="K346" t="n">
         <v>0.435</v>
       </c>
       <c r="L346" t="n">
-        <v>0.3568</v>
+        <v>0.3551</v>
       </c>
       <c r="M346" t="n">
         <v>164</v>
@@ -19146,22 +19146,22 @@
         </is>
       </c>
       <c r="G347" t="n">
-        <v>0.5304</v>
+        <v>0.5254</v>
       </c>
       <c r="H347" t="n">
         <v>0.3498</v>
       </c>
       <c r="I347" t="n">
-        <v>0.4401</v>
+        <v>0.4376</v>
       </c>
       <c r="J347" t="n">
-        <v>0.4696</v>
+        <v>0.4746</v>
       </c>
       <c r="K347" t="n">
         <v>0.6502</v>
       </c>
       <c r="L347" t="n">
-        <v>0.5599</v>
+        <v>0.5624</v>
       </c>
       <c r="M347" t="n">
         <v>164</v>
@@ -19254,22 +19254,22 @@
         </is>
       </c>
       <c r="G349" t="n">
-        <v>0.5919</v>
+        <v>0.5613</v>
       </c>
       <c r="H349" t="n">
-        <v>0.4346</v>
+        <v>0.4315</v>
       </c>
       <c r="I349" t="n">
-        <v>0.5132</v>
+        <v>0.4964</v>
       </c>
       <c r="J349" t="n">
-        <v>0.4081</v>
+        <v>0.4387</v>
       </c>
       <c r="K349" t="n">
-        <v>0.5654</v>
+        <v>0.5685</v>
       </c>
       <c r="L349" t="n">
-        <v>0.4868</v>
+        <v>0.5036</v>
       </c>
       <c r="M349" t="n">
         <v>164</v>
@@ -19308,22 +19308,22 @@
         </is>
       </c>
       <c r="G350" t="n">
-        <v>0.7829</v>
+        <v>0.785</v>
       </c>
       <c r="H350" t="n">
         <v>0.6461</v>
       </c>
       <c r="I350" t="n">
-        <v>0.7145</v>
+        <v>0.7156</v>
       </c>
       <c r="J350" t="n">
-        <v>0.2171</v>
+        <v>0.215</v>
       </c>
       <c r="K350" t="n">
         <v>0.3539</v>
       </c>
       <c r="L350" t="n">
-        <v>0.2855</v>
+        <v>0.2844</v>
       </c>
       <c r="M350" t="n">
         <v>164</v>
@@ -19365,19 +19365,19 @@
         <v>0.2932</v>
       </c>
       <c r="H351" t="n">
-        <v>0.1655</v>
+        <v>0.1635</v>
       </c>
       <c r="I351" t="n">
-        <v>0.2294</v>
+        <v>0.2284</v>
       </c>
       <c r="J351" t="n">
         <v>0.7068</v>
       </c>
       <c r="K351" t="n">
-        <v>0.8345</v>
+        <v>0.8365</v>
       </c>
       <c r="L351" t="n">
-        <v>0.7706</v>
+        <v>0.7716</v>
       </c>
       <c r="M351" t="n">
         <v>164</v>
@@ -19416,22 +19416,22 @@
         </is>
       </c>
       <c r="G352" t="n">
-        <v>0.2798</v>
+        <v>0.2759</v>
       </c>
       <c r="H352" t="n">
-        <v>0.1583</v>
+        <v>0.1545</v>
       </c>
       <c r="I352" t="n">
-        <v>0.219</v>
+        <v>0.2152</v>
       </c>
       <c r="J352" t="n">
-        <v>0.7202</v>
+        <v>0.7241</v>
       </c>
       <c r="K352" t="n">
-        <v>0.8417</v>
+        <v>0.8455</v>
       </c>
       <c r="L352" t="n">
-        <v>0.781</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="M352" t="n">
         <v>164</v>
@@ -19473,19 +19473,19 @@
         <v>0.4851</v>
       </c>
       <c r="H353" t="n">
-        <v>0.3197</v>
+        <v>0.3131</v>
       </c>
       <c r="I353" t="n">
-        <v>0.4024</v>
+        <v>0.3991</v>
       </c>
       <c r="J353" t="n">
         <v>0.5149</v>
       </c>
       <c r="K353" t="n">
-        <v>0.6803</v>
+        <v>0.6869</v>
       </c>
       <c r="L353" t="n">
-        <v>0.5976</v>
+        <v>0.6009</v>
       </c>
       <c r="M353" t="n">
         <v>164</v>
@@ -19524,22 +19524,22 @@
         </is>
       </c>
       <c r="G354" t="n">
-        <v>0.7413</v>
+        <v>0.7441</v>
       </c>
       <c r="H354" t="n">
-        <v>0.6133999999999999</v>
+        <v>0.622</v>
       </c>
       <c r="I354" t="n">
-        <v>0.6773</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="J354" t="n">
-        <v>0.2587</v>
+        <v>0.2559</v>
       </c>
       <c r="K354" t="n">
-        <v>0.3866</v>
+        <v>0.378</v>
       </c>
       <c r="L354" t="n">
-        <v>0.3227</v>
+        <v>0.317</v>
       </c>
       <c r="M354" t="n">
         <v>164</v>
@@ -19578,22 +19578,22 @@
         </is>
       </c>
       <c r="G355" t="n">
-        <v>0.7567</v>
+        <v>0.7601</v>
       </c>
       <c r="H355" t="n">
-        <v>0.607</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="I355" t="n">
-        <v>0.6819</v>
+        <v>0.6862</v>
       </c>
       <c r="J355" t="n">
-        <v>0.2433</v>
+        <v>0.2399</v>
       </c>
       <c r="K355" t="n">
-        <v>0.393</v>
+        <v>0.3876</v>
       </c>
       <c r="L355" t="n">
-        <v>0.3181</v>
+        <v>0.3138</v>
       </c>
       <c r="M355" t="n">
         <v>164</v>
@@ -19632,22 +19632,22 @@
         </is>
       </c>
       <c r="G356" t="n">
-        <v>0.8083</v>
+        <v>0.8118</v>
       </c>
       <c r="H356" t="n">
-        <v>0.6909</v>
+        <v>0.6954</v>
       </c>
       <c r="I356" t="n">
-        <v>0.7496</v>
+        <v>0.7536</v>
       </c>
       <c r="J356" t="n">
-        <v>0.1917</v>
+        <v>0.1882</v>
       </c>
       <c r="K356" t="n">
-        <v>0.3091</v>
+        <v>0.3046</v>
       </c>
       <c r="L356" t="n">
-        <v>0.2504</v>
+        <v>0.2464</v>
       </c>
       <c r="M356" t="n">
         <v>164</v>
@@ -19794,22 +19794,22 @@
         </is>
       </c>
       <c r="G359" t="n">
-        <v>0.3714</v>
+        <v>0.3723</v>
       </c>
       <c r="H359" t="n">
         <v>0.2228</v>
       </c>
       <c r="I359" t="n">
-        <v>0.2971</v>
+        <v>0.2976</v>
       </c>
       <c r="J359" t="n">
-        <v>0.6286</v>
+        <v>0.6277</v>
       </c>
       <c r="K359" t="n">
         <v>0.7772</v>
       </c>
       <c r="L359" t="n">
-        <v>0.7029</v>
+        <v>0.7024</v>
       </c>
       <c r="M359" t="n">
         <v>164</v>
@@ -19848,22 +19848,22 @@
         </is>
       </c>
       <c r="G360" t="n">
-        <v>0.3739</v>
+        <v>0.3694</v>
       </c>
       <c r="H360" t="n">
-        <v>0.2304</v>
+        <v>0.2274</v>
       </c>
       <c r="I360" t="n">
-        <v>0.3022</v>
+        <v>0.2984</v>
       </c>
       <c r="J360" t="n">
-        <v>0.6261</v>
+        <v>0.6306</v>
       </c>
       <c r="K360" t="n">
-        <v>0.7696</v>
+        <v>0.7726</v>
       </c>
       <c r="L360" t="n">
-        <v>0.6978</v>
+        <v>0.7016</v>
       </c>
       <c r="M360" t="n">
         <v>164</v>
@@ -19902,22 +19902,22 @@
         </is>
       </c>
       <c r="G361" t="n">
-        <v>0.4203</v>
+        <v>0.42</v>
       </c>
       <c r="H361" t="n">
-        <v>0.3148</v>
+        <v>0.2698</v>
       </c>
       <c r="I361" t="n">
-        <v>0.3676</v>
+        <v>0.3449</v>
       </c>
       <c r="J361" t="n">
-        <v>0.5797</v>
+        <v>0.58</v>
       </c>
       <c r="K361" t="n">
-        <v>0.6852</v>
+        <v>0.7302</v>
       </c>
       <c r="L361" t="n">
-        <v>0.6324</v>
+        <v>0.6551</v>
       </c>
       <c r="M361" t="n">
         <v>164</v>
@@ -19956,22 +19956,22 @@
         </is>
       </c>
       <c r="G362" t="n">
-        <v>0.6518</v>
+        <v>0.6756</v>
       </c>
       <c r="H362" t="n">
         <v>0.5605</v>
       </c>
       <c r="I362" t="n">
-        <v>0.6062</v>
+        <v>0.618</v>
       </c>
       <c r="J362" t="n">
-        <v>0.3482</v>
+        <v>0.3244</v>
       </c>
       <c r="K362" t="n">
         <v>0.4395</v>
       </c>
       <c r="L362" t="n">
-        <v>0.3938</v>
+        <v>0.382</v>
       </c>
       <c r="M362" t="n">
         <v>164</v>
@@ -20010,22 +20010,22 @@
         </is>
       </c>
       <c r="G363" t="n">
-        <v>0.2611</v>
+        <v>0.2528</v>
       </c>
       <c r="H363" t="n">
         <v>0.1386</v>
       </c>
       <c r="I363" t="n">
-        <v>0.1998</v>
+        <v>0.1957</v>
       </c>
       <c r="J363" t="n">
-        <v>0.7389</v>
+        <v>0.7472</v>
       </c>
       <c r="K363" t="n">
         <v>0.8614000000000001</v>
       </c>
       <c r="L363" t="n">
-        <v>0.8002</v>
+        <v>0.8043</v>
       </c>
       <c r="M363" t="n">
         <v>164</v>
@@ -20064,22 +20064,22 @@
         </is>
       </c>
       <c r="G364" t="n">
-        <v>0.2531</v>
+        <v>0.2504</v>
       </c>
       <c r="H364" t="n">
-        <v>0.134</v>
+        <v>0.1335</v>
       </c>
       <c r="I364" t="n">
-        <v>0.1936</v>
+        <v>0.192</v>
       </c>
       <c r="J364" t="n">
-        <v>0.7469</v>
+        <v>0.7496</v>
       </c>
       <c r="K364" t="n">
-        <v>0.866</v>
+        <v>0.8665</v>
       </c>
       <c r="L364" t="n">
-        <v>0.8064</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="M364" t="n">
         <v>164</v>
@@ -20118,22 +20118,22 @@
         </is>
       </c>
       <c r="G365" t="n">
-        <v>0.3502</v>
+        <v>0.3394</v>
       </c>
       <c r="H365" t="n">
         <v>0.2203</v>
       </c>
       <c r="I365" t="n">
-        <v>0.2852</v>
+        <v>0.2798</v>
       </c>
       <c r="J365" t="n">
-        <v>0.6498</v>
+        <v>0.6606</v>
       </c>
       <c r="K365" t="n">
         <v>0.7796999999999999</v>
       </c>
       <c r="L365" t="n">
-        <v>0.7148</v>
+        <v>0.7202</v>
       </c>
       <c r="M365" t="n">
         <v>164</v>
@@ -20172,22 +20172,22 @@
         </is>
       </c>
       <c r="G366" t="n">
-        <v>0.6317</v>
+        <v>0.6364</v>
       </c>
       <c r="H366" t="n">
         <v>0.5403</v>
       </c>
       <c r="I366" t="n">
-        <v>0.586</v>
+        <v>0.5883</v>
       </c>
       <c r="J366" t="n">
-        <v>0.3683</v>
+        <v>0.3636</v>
       </c>
       <c r="K366" t="n">
         <v>0.4597</v>
       </c>
       <c r="L366" t="n">
-        <v>0.414</v>
+        <v>0.4117</v>
       </c>
       <c r="M366" t="n">
         <v>164</v>
@@ -20280,22 +20280,22 @@
         </is>
       </c>
       <c r="G368" t="n">
-        <v>0.7203000000000001</v>
+        <v>0.7256</v>
       </c>
       <c r="H368" t="n">
-        <v>0.5854</v>
+        <v>0.59</v>
       </c>
       <c r="I368" t="n">
-        <v>0.6528</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="J368" t="n">
-        <v>0.2797</v>
+        <v>0.2744</v>
       </c>
       <c r="K368" t="n">
-        <v>0.4146</v>
+        <v>0.41</v>
       </c>
       <c r="L368" t="n">
-        <v>0.3472</v>
+        <v>0.3422</v>
       </c>
       <c r="M368" t="n">
         <v>164</v>
@@ -20334,22 +20334,22 @@
         </is>
       </c>
       <c r="G369" t="n">
-        <v>0.3082</v>
+        <v>0.3017</v>
       </c>
       <c r="H369" t="n">
-        <v>0.2087</v>
+        <v>0.2099</v>
       </c>
       <c r="I369" t="n">
-        <v>0.2584</v>
+        <v>0.2558</v>
       </c>
       <c r="J369" t="n">
-        <v>0.6918</v>
+        <v>0.6983</v>
       </c>
       <c r="K369" t="n">
-        <v>0.7913</v>
+        <v>0.7901</v>
       </c>
       <c r="L369" t="n">
-        <v>0.7416</v>
+        <v>0.7442</v>
       </c>
       <c r="M369" t="n">
         <v>164</v>
@@ -20388,22 +20388,22 @@
         </is>
       </c>
       <c r="G370" t="n">
-        <v>0.3001</v>
+        <v>0.2964</v>
       </c>
       <c r="H370" t="n">
-        <v>0.1811</v>
+        <v>0.1775</v>
       </c>
       <c r="I370" t="n">
-        <v>0.2406</v>
+        <v>0.237</v>
       </c>
       <c r="J370" t="n">
-        <v>0.6999</v>
+        <v>0.7036</v>
       </c>
       <c r="K370" t="n">
-        <v>0.8189</v>
+        <v>0.8225</v>
       </c>
       <c r="L370" t="n">
-        <v>0.7594</v>
+        <v>0.763</v>
       </c>
       <c r="M370" t="n">
         <v>164</v>
@@ -20496,22 +20496,22 @@
         </is>
       </c>
       <c r="G372" t="n">
-        <v>0.6331</v>
+        <v>0.6051</v>
       </c>
       <c r="H372" t="n">
-        <v>0.4736</v>
+        <v>0.459</v>
       </c>
       <c r="I372" t="n">
-        <v>0.5534</v>
+        <v>0.532</v>
       </c>
       <c r="J372" t="n">
-        <v>0.3669</v>
+        <v>0.3949</v>
       </c>
       <c r="K372" t="n">
-        <v>0.5264</v>
+        <v>0.541</v>
       </c>
       <c r="L372" t="n">
-        <v>0.4466</v>
+        <v>0.468</v>
       </c>
       <c r="M372" t="n">
         <v>164</v>
@@ -20550,22 +20550,22 @@
         </is>
       </c>
       <c r="G373" t="n">
-        <v>0.8336</v>
+        <v>0.8386</v>
       </c>
       <c r="H373" t="n">
-        <v>0.7198</v>
+        <v>0.7252999999999999</v>
       </c>
       <c r="I373" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.7819</v>
       </c>
       <c r="J373" t="n">
-        <v>0.1664</v>
+        <v>0.1614</v>
       </c>
       <c r="K373" t="n">
-        <v>0.2802</v>
+        <v>0.2747</v>
       </c>
       <c r="L373" t="n">
-        <v>0.2233</v>
+        <v>0.2181</v>
       </c>
       <c r="M373" t="n">
         <v>164</v>
@@ -20607,19 +20607,19 @@
         <v>0.3264</v>
       </c>
       <c r="H374" t="n">
-        <v>0.2021</v>
+        <v>0.2008</v>
       </c>
       <c r="I374" t="n">
-        <v>0.2642</v>
+        <v>0.2636</v>
       </c>
       <c r="J374" t="n">
         <v>0.6736</v>
       </c>
       <c r="K374" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.7992</v>
       </c>
       <c r="L374" t="n">
-        <v>0.7358</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="M374" t="n">
         <v>164</v>
@@ -20658,22 +20658,22 @@
         </is>
       </c>
       <c r="G375" t="n">
-        <v>0.3243</v>
+        <v>0.3167</v>
       </c>
       <c r="H375" t="n">
         <v>0.2094</v>
       </c>
       <c r="I375" t="n">
-        <v>0.2668</v>
+        <v>0.263</v>
       </c>
       <c r="J375" t="n">
-        <v>0.6757</v>
+        <v>0.6833</v>
       </c>
       <c r="K375" t="n">
         <v>0.7906</v>
       </c>
       <c r="L375" t="n">
-        <v>0.7332</v>
+        <v>0.737</v>
       </c>
       <c r="M375" t="n">
         <v>164</v>
@@ -20766,22 +20766,22 @@
         </is>
       </c>
       <c r="G377" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8171</v>
       </c>
       <c r="H377" t="n">
-        <v>0.6978</v>
+        <v>0.7019</v>
       </c>
       <c r="I377" t="n">
-        <v>0.7534</v>
+        <v>0.7595</v>
       </c>
       <c r="J377" t="n">
-        <v>0.191</v>
+        <v>0.1829</v>
       </c>
       <c r="K377" t="n">
-        <v>0.3022</v>
+        <v>0.2981</v>
       </c>
       <c r="L377" t="n">
-        <v>0.2466</v>
+        <v>0.2405</v>
       </c>
       <c r="M377" t="n">
         <v>164</v>
@@ -20823,19 +20823,19 @@
         <v>0.8131</v>
       </c>
       <c r="H378" t="n">
-        <v>0.6314</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="I378" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.7239</v>
       </c>
       <c r="J378" t="n">
         <v>0.1869</v>
       </c>
       <c r="K378" t="n">
-        <v>0.3686</v>
+        <v>0.3654</v>
       </c>
       <c r="L378" t="n">
-        <v>0.2777</v>
+        <v>0.2761</v>
       </c>
       <c r="M378" t="n">
         <v>164</v>
@@ -20874,22 +20874,22 @@
         </is>
       </c>
       <c r="G379" t="n">
-        <v>0.8428</v>
+        <v>0.8475</v>
       </c>
       <c r="H379" t="n">
-        <v>0.7509</v>
+        <v>0.7551</v>
       </c>
       <c r="I379" t="n">
-        <v>0.7969000000000001</v>
+        <v>0.8013</v>
       </c>
       <c r="J379" t="n">
-        <v>0.1572</v>
+        <v>0.1525</v>
       </c>
       <c r="K379" t="n">
-        <v>0.2491</v>
+        <v>0.2449</v>
       </c>
       <c r="L379" t="n">
-        <v>0.2031</v>
+        <v>0.1987</v>
       </c>
       <c r="M379" t="n">
         <v>164</v>
@@ -20928,22 +20928,22 @@
         </is>
       </c>
       <c r="G380" t="n">
-        <v>0.4619</v>
+        <v>0.4665</v>
       </c>
       <c r="H380" t="n">
         <v>0.3308</v>
       </c>
       <c r="I380" t="n">
-        <v>0.3964</v>
+        <v>0.3986</v>
       </c>
       <c r="J380" t="n">
-        <v>0.5381</v>
+        <v>0.5335</v>
       </c>
       <c r="K380" t="n">
         <v>0.6692</v>
       </c>
       <c r="L380" t="n">
-        <v>0.6036</v>
+        <v>0.6014</v>
       </c>
       <c r="M380" t="n">
         <v>164</v>
@@ -20985,19 +20985,19 @@
         <v>0.5135</v>
       </c>
       <c r="H381" t="n">
-        <v>0.3302</v>
+        <v>0.3318</v>
       </c>
       <c r="I381" t="n">
-        <v>0.4218</v>
+        <v>0.4226</v>
       </c>
       <c r="J381" t="n">
         <v>0.4865</v>
       </c>
       <c r="K381" t="n">
-        <v>0.6698</v>
+        <v>0.6682</v>
       </c>
       <c r="L381" t="n">
-        <v>0.5782</v>
+        <v>0.5774</v>
       </c>
       <c r="M381" t="n">
         <v>164</v>
@@ -21036,22 +21036,22 @@
         </is>
       </c>
       <c r="G382" t="n">
-        <v>0.6277</v>
+        <v>0.5866</v>
       </c>
       <c r="H382" t="n">
-        <v>0.4654</v>
+        <v>0.4616</v>
       </c>
       <c r="I382" t="n">
-        <v>0.5466</v>
+        <v>0.5241</v>
       </c>
       <c r="J382" t="n">
-        <v>0.3723</v>
+        <v>0.4134</v>
       </c>
       <c r="K382" t="n">
-        <v>0.5346</v>
+        <v>0.5384</v>
       </c>
       <c r="L382" t="n">
-        <v>0.4534</v>
+        <v>0.4759</v>
       </c>
       <c r="M382" t="n">
         <v>164</v>
@@ -21090,22 +21090,22 @@
         </is>
       </c>
       <c r="G383" t="n">
-        <v>0.8161</v>
+        <v>0.8185</v>
       </c>
       <c r="H383" t="n">
-        <v>0.716</v>
+        <v>0.7178</v>
       </c>
       <c r="I383" t="n">
-        <v>0.766</v>
+        <v>0.7682</v>
       </c>
       <c r="J383" t="n">
-        <v>0.1839</v>
+        <v>0.1815</v>
       </c>
       <c r="K383" t="n">
-        <v>0.284</v>
+        <v>0.2822</v>
       </c>
       <c r="L383" t="n">
-        <v>0.234</v>
+        <v>0.2318</v>
       </c>
       <c r="M383" t="n">
         <v>164</v>
@@ -21144,22 +21144,22 @@
         </is>
       </c>
       <c r="G384" t="n">
-        <v>0.3459</v>
+        <v>0.3398</v>
       </c>
       <c r="H384" t="n">
-        <v>0.1853</v>
+        <v>0.1834</v>
       </c>
       <c r="I384" t="n">
-        <v>0.2656</v>
+        <v>0.2616</v>
       </c>
       <c r="J384" t="n">
-        <v>0.6541</v>
+        <v>0.6602</v>
       </c>
       <c r="K384" t="n">
-        <v>0.8147</v>
+        <v>0.8166</v>
       </c>
       <c r="L384" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.7383999999999999</v>
       </c>
       <c r="M384" t="n">
         <v>164</v>
@@ -21198,22 +21198,22 @@
         </is>
       </c>
       <c r="G385" t="n">
-        <v>0.3196</v>
+        <v>0.3093</v>
       </c>
       <c r="H385" t="n">
         <v>0.1762</v>
       </c>
       <c r="I385" t="n">
-        <v>0.2479</v>
+        <v>0.2428</v>
       </c>
       <c r="J385" t="n">
-        <v>0.6804</v>
+        <v>0.6907</v>
       </c>
       <c r="K385" t="n">
         <v>0.8238</v>
       </c>
       <c r="L385" t="n">
-        <v>0.7521</v>
+        <v>0.7572</v>
       </c>
       <c r="M385" t="n">
         <v>164</v>
@@ -21306,22 +21306,22 @@
         </is>
       </c>
       <c r="G387" t="n">
-        <v>0.797</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="H387" t="n">
-        <v>0.6859</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="I387" t="n">
-        <v>0.7413999999999999</v>
+        <v>0.744</v>
       </c>
       <c r="J387" t="n">
-        <v>0.203</v>
+        <v>0.2001</v>
       </c>
       <c r="K387" t="n">
-        <v>0.3141</v>
+        <v>0.312</v>
       </c>
       <c r="L387" t="n">
-        <v>0.2586</v>
+        <v>0.256</v>
       </c>
       <c r="M387" t="n">
         <v>164</v>
@@ -21363,19 +21363,19 @@
         <v>0.8222</v>
       </c>
       <c r="H388" t="n">
-        <v>0.6577</v>
+        <v>0.6567</v>
       </c>
       <c r="I388" t="n">
-        <v>0.74</v>
+        <v>0.7393999999999999</v>
       </c>
       <c r="J388" t="n">
         <v>0.1778</v>
       </c>
       <c r="K388" t="n">
-        <v>0.3423</v>
+        <v>0.3433</v>
       </c>
       <c r="L388" t="n">
-        <v>0.26</v>
+        <v>0.2606</v>
       </c>
       <c r="M388" t="n">
         <v>164</v>
@@ -21414,22 +21414,22 @@
         </is>
       </c>
       <c r="G389" t="n">
-        <v>0.8564000000000001</v>
+        <v>0.863</v>
       </c>
       <c r="H389" t="n">
-        <v>0.7269</v>
+        <v>0.7328</v>
       </c>
       <c r="I389" t="n">
-        <v>0.7916</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="J389" t="n">
-        <v>0.1436</v>
+        <v>0.137</v>
       </c>
       <c r="K389" t="n">
-        <v>0.2731</v>
+        <v>0.2672</v>
       </c>
       <c r="L389" t="n">
-        <v>0.2084</v>
+        <v>0.2021</v>
       </c>
       <c r="M389" t="n">
         <v>164</v>
@@ -21468,22 +21468,22 @@
         </is>
       </c>
       <c r="G390" t="n">
-        <v>0.4526</v>
+        <v>0.4555</v>
       </c>
       <c r="H390" t="n">
         <v>0.3195</v>
       </c>
       <c r="I390" t="n">
-        <v>0.386</v>
+        <v>0.3875</v>
       </c>
       <c r="J390" t="n">
-        <v>0.5474</v>
+        <v>0.5445</v>
       </c>
       <c r="K390" t="n">
         <v>0.6805</v>
       </c>
       <c r="L390" t="n">
-        <v>0.614</v>
+        <v>0.6125</v>
       </c>
       <c r="M390" t="n">
         <v>164</v>
@@ -21576,22 +21576,22 @@
         </is>
       </c>
       <c r="G392" t="n">
-        <v>0.7906</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="H392" t="n">
-        <v>0.6554</v>
+        <v>0.6815</v>
       </c>
       <c r="I392" t="n">
-        <v>0.723</v>
+        <v>0.7417</v>
       </c>
       <c r="J392" t="n">
-        <v>0.2094</v>
+        <v>0.1981</v>
       </c>
       <c r="K392" t="n">
-        <v>0.3446</v>
+        <v>0.3185</v>
       </c>
       <c r="L392" t="n">
-        <v>0.277</v>
+        <v>0.2583</v>
       </c>
       <c r="M392" t="n">
         <v>164</v>
@@ -21630,22 +21630,22 @@
         </is>
       </c>
       <c r="G393" t="n">
-        <v>0.275</v>
+        <v>0.2827</v>
       </c>
       <c r="H393" t="n">
-        <v>0.189</v>
+        <v>0.1934</v>
       </c>
       <c r="I393" t="n">
-        <v>0.232</v>
+        <v>0.238</v>
       </c>
       <c r="J393" t="n">
-        <v>0.725</v>
+        <v>0.7173</v>
       </c>
       <c r="K393" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8066</v>
       </c>
       <c r="L393" t="n">
-        <v>0.768</v>
+        <v>0.762</v>
       </c>
       <c r="M393" t="n">
         <v>164</v>
@@ -21684,22 +21684,22 @@
         </is>
       </c>
       <c r="G394" t="n">
-        <v>0.2416</v>
+        <v>0.2472</v>
       </c>
       <c r="H394" t="n">
-        <v>0.1851</v>
+        <v>0.1939</v>
       </c>
       <c r="I394" t="n">
-        <v>0.2134</v>
+        <v>0.2206</v>
       </c>
       <c r="J394" t="n">
-        <v>0.7584</v>
+        <v>0.7528</v>
       </c>
       <c r="K394" t="n">
-        <v>0.8149</v>
+        <v>0.8061</v>
       </c>
       <c r="L394" t="n">
-        <v>0.7866</v>
+        <v>0.7794</v>
       </c>
       <c r="M394" t="n">
         <v>164</v>
@@ -21738,22 +21738,22 @@
         </is>
       </c>
       <c r="G395" t="n">
-        <v>0.5066000000000001</v>
+        <v>0.524</v>
       </c>
       <c r="H395" t="n">
-        <v>0.3157</v>
+        <v>0.3393</v>
       </c>
       <c r="I395" t="n">
-        <v>0.4112</v>
+        <v>0.4316</v>
       </c>
       <c r="J395" t="n">
-        <v>0.4934</v>
+        <v>0.476</v>
       </c>
       <c r="K395" t="n">
-        <v>0.6843</v>
+        <v>0.6607</v>
       </c>
       <c r="L395" t="n">
-        <v>0.5888</v>
+        <v>0.5684</v>
       </c>
       <c r="M395" t="n">
         <v>164</v>
@@ -21792,22 +21792,22 @@
         </is>
       </c>
       <c r="G396" t="n">
-        <v>0.7547</v>
+        <v>0.7811</v>
       </c>
       <c r="H396" t="n">
-        <v>0.6489</v>
+        <v>0.6632</v>
       </c>
       <c r="I396" t="n">
-        <v>0.7018</v>
+        <v>0.7222</v>
       </c>
       <c r="J396" t="n">
-        <v>0.2453</v>
+        <v>0.2189</v>
       </c>
       <c r="K396" t="n">
-        <v>0.3511</v>
+        <v>0.3368</v>
       </c>
       <c r="L396" t="n">
-        <v>0.2982</v>
+        <v>0.2778</v>
       </c>
       <c r="M396" t="n">
         <v>164</v>
@@ -21846,22 +21846,22 @@
         </is>
       </c>
       <c r="G397" t="n">
-        <v>0.7168</v>
+        <v>0.7431</v>
       </c>
       <c r="H397" t="n">
-        <v>0.6122</v>
+        <v>0.6339</v>
       </c>
       <c r="I397" t="n">
-        <v>0.6645</v>
+        <v>0.6885</v>
       </c>
       <c r="J397" t="n">
-        <v>0.2832</v>
+        <v>0.2569</v>
       </c>
       <c r="K397" t="n">
-        <v>0.3878</v>
+        <v>0.3661</v>
       </c>
       <c r="L397" t="n">
-        <v>0.3355</v>
+        <v>0.3115</v>
       </c>
       <c r="M397" t="n">
         <v>164</v>
@@ -21900,22 +21900,22 @@
         </is>
       </c>
       <c r="G398" t="n">
-        <v>0.8167</v>
+        <v>0.8257</v>
       </c>
       <c r="H398" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="I398" t="n">
-        <v>0.7514</v>
+        <v>0.7678</v>
       </c>
       <c r="J398" t="n">
-        <v>0.1833</v>
+        <v>0.1743</v>
       </c>
       <c r="K398" t="n">
-        <v>0.314</v>
+        <v>0.29</v>
       </c>
       <c r="L398" t="n">
-        <v>0.2486</v>
+        <v>0.2322</v>
       </c>
       <c r="M398" t="n">
         <v>164</v>
@@ -21954,22 +21954,22 @@
         </is>
       </c>
       <c r="G399" t="n">
-        <v>0.4127</v>
+        <v>0.4303</v>
       </c>
       <c r="H399" t="n">
-        <v>0.2819</v>
+        <v>0.311</v>
       </c>
       <c r="I399" t="n">
-        <v>0.3473</v>
+        <v>0.3707</v>
       </c>
       <c r="J399" t="n">
-        <v>0.5873</v>
+        <v>0.5697</v>
       </c>
       <c r="K399" t="n">
-        <v>0.7181</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L399" t="n">
-        <v>0.6526999999999999</v>
+        <v>0.6293</v>
       </c>
       <c r="M399" t="n">
         <v>164</v>
@@ -22008,22 +22008,22 @@
         </is>
       </c>
       <c r="G400" t="n">
-        <v>0.4252</v>
+        <v>0.4405</v>
       </c>
       <c r="H400" t="n">
-        <v>0.2752</v>
+        <v>0.2798</v>
       </c>
       <c r="I400" t="n">
-        <v>0.3502</v>
+        <v>0.3601</v>
       </c>
       <c r="J400" t="n">
-        <v>0.5748</v>
+        <v>0.5595</v>
       </c>
       <c r="K400" t="n">
-        <v>0.7248</v>
+        <v>0.7202</v>
       </c>
       <c r="L400" t="n">
-        <v>0.6498</v>
+        <v>0.6399</v>
       </c>
       <c r="M400" t="n">
         <v>164</v>
@@ -22062,22 +22062,22 @@
         </is>
       </c>
       <c r="G401" t="n">
-        <v>0.2087</v>
+        <v>0.2057</v>
       </c>
       <c r="H401" t="n">
-        <v>0.1213</v>
+        <v>0.1192</v>
       </c>
       <c r="I401" t="n">
-        <v>0.165</v>
+        <v>0.1624</v>
       </c>
       <c r="J401" t="n">
-        <v>0.7913</v>
+        <v>0.7943</v>
       </c>
       <c r="K401" t="n">
-        <v>0.8787</v>
+        <v>0.8808</v>
       </c>
       <c r="L401" t="n">
-        <v>0.835</v>
+        <v>0.8376</v>
       </c>
       <c r="M401" t="n">
         <v>164</v>
@@ -22170,22 +22170,22 @@
         </is>
       </c>
       <c r="G403" t="n">
-        <v>0.28</v>
+        <v>0.2744</v>
       </c>
       <c r="H403" t="n">
-        <v>0.1633</v>
+        <v>0.16</v>
       </c>
       <c r="I403" t="n">
-        <v>0.2216</v>
+        <v>0.2172</v>
       </c>
       <c r="J403" t="n">
-        <v>0.72</v>
+        <v>0.7256</v>
       </c>
       <c r="K403" t="n">
-        <v>0.8367</v>
+        <v>0.84</v>
       </c>
       <c r="L403" t="n">
-        <v>0.7784</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="M403" t="n">
         <v>164</v>
@@ -22227,19 +22227,19 @@
         <v>0.5485</v>
       </c>
       <c r="H404" t="n">
-        <v>0.4055</v>
+        <v>0.4045</v>
       </c>
       <c r="I404" t="n">
-        <v>0.477</v>
+        <v>0.4765</v>
       </c>
       <c r="J404" t="n">
         <v>0.4515</v>
       </c>
       <c r="K404" t="n">
-        <v>0.5945</v>
+        <v>0.5955</v>
       </c>
       <c r="L404" t="n">
-        <v>0.523</v>
+        <v>0.5235</v>
       </c>
       <c r="M404" t="n">
         <v>164</v>
@@ -22335,19 +22335,19 @@
         <v>0.6141</v>
       </c>
       <c r="H406" t="n">
-        <v>0.5167</v>
+        <v>0.5196</v>
       </c>
       <c r="I406" t="n">
-        <v>0.5654</v>
+        <v>0.5668</v>
       </c>
       <c r="J406" t="n">
         <v>0.3859</v>
       </c>
       <c r="K406" t="n">
-        <v>0.4833</v>
+        <v>0.4804</v>
       </c>
       <c r="L406" t="n">
-        <v>0.4346</v>
+        <v>0.4332</v>
       </c>
       <c r="M406" t="n">
         <v>164</v>
@@ -22386,22 +22386,22 @@
         </is>
       </c>
       <c r="G407" t="n">
-        <v>0.2763</v>
+        <v>0.2736</v>
       </c>
       <c r="H407" t="n">
-        <v>0.155</v>
+        <v>0.1519</v>
       </c>
       <c r="I407" t="n">
-        <v>0.2156</v>
+        <v>0.2128</v>
       </c>
       <c r="J407" t="n">
-        <v>0.7237</v>
+        <v>0.7264</v>
       </c>
       <c r="K407" t="n">
-        <v>0.845</v>
+        <v>0.8481</v>
       </c>
       <c r="L407" t="n">
-        <v>0.7844</v>
+        <v>0.7872</v>
       </c>
       <c r="M407" t="n">
         <v>164</v>
@@ -22440,22 +22440,22 @@
         </is>
       </c>
       <c r="G408" t="n">
-        <v>0.2451</v>
+        <v>0.2348</v>
       </c>
       <c r="H408" t="n">
         <v>0.1346</v>
       </c>
       <c r="I408" t="n">
-        <v>0.1899</v>
+        <v>0.1847</v>
       </c>
       <c r="J408" t="n">
-        <v>0.7549</v>
+        <v>0.7652</v>
       </c>
       <c r="K408" t="n">
         <v>0.8653999999999999</v>
       </c>
       <c r="L408" t="n">
-        <v>0.8101</v>
+        <v>0.8153</v>
       </c>
       <c r="M408" t="n">
         <v>164</v>
@@ -22494,22 +22494,22 @@
         </is>
       </c>
       <c r="G409" t="n">
-        <v>0.4793</v>
+        <v>0.4751</v>
       </c>
       <c r="H409" t="n">
-        <v>0.4173</v>
+        <v>0.4154</v>
       </c>
       <c r="I409" t="n">
-        <v>0.4483</v>
+        <v>0.4452</v>
       </c>
       <c r="J409" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.5249</v>
       </c>
       <c r="K409" t="n">
-        <v>0.5827</v>
+        <v>0.5846</v>
       </c>
       <c r="L409" t="n">
-        <v>0.5517</v>
+        <v>0.5548</v>
       </c>
       <c r="M409" t="n">
         <v>164</v>
@@ -22551,19 +22551,19 @@
         <v>0.7812</v>
       </c>
       <c r="H410" t="n">
-        <v>0.6393</v>
+        <v>0.6544</v>
       </c>
       <c r="I410" t="n">
-        <v>0.7103</v>
+        <v>0.7178</v>
       </c>
       <c r="J410" t="n">
         <v>0.2188</v>
       </c>
       <c r="K410" t="n">
-        <v>0.3607</v>
+        <v>0.3456</v>
       </c>
       <c r="L410" t="n">
-        <v>0.2897</v>
+        <v>0.2822</v>
       </c>
       <c r="M410" t="n">
         <v>164</v>
@@ -22602,22 +22602,22 @@
         </is>
       </c>
       <c r="G411" t="n">
-        <v>0.8789</v>
+        <v>0.8821</v>
       </c>
       <c r="H411" t="n">
         <v>0.775</v>
       </c>
       <c r="I411" t="n">
-        <v>0.827</v>
+        <v>0.8286</v>
       </c>
       <c r="J411" t="n">
-        <v>0.1211</v>
+        <v>0.1179</v>
       </c>
       <c r="K411" t="n">
         <v>0.225</v>
       </c>
       <c r="L411" t="n">
-        <v>0.173</v>
+        <v>0.1714</v>
       </c>
       <c r="M411" t="n">
         <v>164</v>
@@ -22656,22 +22656,22 @@
         </is>
       </c>
       <c r="G412" t="n">
-        <v>0.8841</v>
+        <v>0.8867</v>
       </c>
       <c r="H412" t="n">
-        <v>0.771</v>
+        <v>0.7759</v>
       </c>
       <c r="I412" t="n">
-        <v>0.8276</v>
+        <v>0.8313</v>
       </c>
       <c r="J412" t="n">
-        <v>0.1159</v>
+        <v>0.1133</v>
       </c>
       <c r="K412" t="n">
-        <v>0.229</v>
+        <v>0.2241</v>
       </c>
       <c r="L412" t="n">
-        <v>0.1724</v>
+        <v>0.1687</v>
       </c>
       <c r="M412" t="n">
         <v>164</v>
@@ -22713,19 +22713,19 @@
         <v>0.8898</v>
       </c>
       <c r="H413" t="n">
-        <v>0.7954</v>
+        <v>0.7984</v>
       </c>
       <c r="I413" t="n">
-        <v>0.8426</v>
+        <v>0.8441</v>
       </c>
       <c r="J413" t="n">
         <v>0.1102</v>
       </c>
       <c r="K413" t="n">
-        <v>0.2046</v>
+        <v>0.2016</v>
       </c>
       <c r="L413" t="n">
-        <v>0.1574</v>
+        <v>0.1559</v>
       </c>
       <c r="M413" t="n">
         <v>164</v>
@@ -22767,19 +22767,19 @@
         <v>0.7119</v>
       </c>
       <c r="H414" t="n">
-        <v>0.5684</v>
+        <v>0.5743</v>
       </c>
       <c r="I414" t="n">
-        <v>0.6402</v>
+        <v>0.6431</v>
       </c>
       <c r="J414" t="n">
         <v>0.2881</v>
       </c>
       <c r="K414" t="n">
-        <v>0.4316</v>
+        <v>0.4257</v>
       </c>
       <c r="L414" t="n">
-        <v>0.3598</v>
+        <v>0.3569</v>
       </c>
       <c r="M414" t="n">
         <v>164</v>
@@ -22818,22 +22818,22 @@
         </is>
       </c>
       <c r="G415" t="n">
-        <v>0.7308</v>
+        <v>0.7343</v>
       </c>
       <c r="H415" t="n">
         <v>0.5957</v>
       </c>
       <c r="I415" t="n">
-        <v>0.6632</v>
+        <v>0.665</v>
       </c>
       <c r="J415" t="n">
-        <v>0.2692</v>
+        <v>0.2657</v>
       </c>
       <c r="K415" t="n">
         <v>0.4043</v>
       </c>
       <c r="L415" t="n">
-        <v>0.3368</v>
+        <v>0.335</v>
       </c>
       <c r="M415" t="n">
         <v>164</v>
@@ -22872,22 +22872,22 @@
         </is>
       </c>
       <c r="G416" t="n">
-        <v>0.8024</v>
+        <v>0.8051</v>
       </c>
       <c r="H416" t="n">
-        <v>0.6585</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="I416" t="n">
-        <v>0.7304</v>
+        <v>0.734</v>
       </c>
       <c r="J416" t="n">
-        <v>0.1976</v>
+        <v>0.1949</v>
       </c>
       <c r="K416" t="n">
-        <v>0.3415</v>
+        <v>0.3372</v>
       </c>
       <c r="L416" t="n">
-        <v>0.2696</v>
+        <v>0.266</v>
       </c>
       <c r="M416" t="n">
         <v>164</v>
@@ -22929,19 +22929,19 @@
         <v>0.8781</v>
       </c>
       <c r="H417" t="n">
-        <v>0.7609</v>
+        <v>0.7756</v>
       </c>
       <c r="I417" t="n">
-        <v>0.8195</v>
+        <v>0.8268</v>
       </c>
       <c r="J417" t="n">
         <v>0.1219</v>
       </c>
       <c r="K417" t="n">
-        <v>0.2391</v>
+        <v>0.2244</v>
       </c>
       <c r="L417" t="n">
-        <v>0.1805</v>
+        <v>0.1732</v>
       </c>
       <c r="M417" t="n">
         <v>164</v>
@@ -22980,22 +22980,22 @@
         </is>
       </c>
       <c r="G418" t="n">
-        <v>0.873</v>
+        <v>0.8752</v>
       </c>
       <c r="H418" t="n">
         <v>0.7887999999999999</v>
       </c>
       <c r="I418" t="n">
-        <v>0.8309</v>
+        <v>0.832</v>
       </c>
       <c r="J418" t="n">
-        <v>0.127</v>
+        <v>0.1248</v>
       </c>
       <c r="K418" t="n">
         <v>0.2112</v>
       </c>
       <c r="L418" t="n">
-        <v>0.1691</v>
+        <v>0.168</v>
       </c>
       <c r="M418" t="n">
         <v>164</v>
@@ -23088,22 +23088,22 @@
         </is>
       </c>
       <c r="G420" t="n">
-        <v>0.7559</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="H420" t="n">
-        <v>0.6256</v>
+        <v>0.6246</v>
       </c>
       <c r="I420" t="n">
-        <v>0.6908</v>
+        <v>0.6911</v>
       </c>
       <c r="J420" t="n">
-        <v>0.2441</v>
+        <v>0.2424</v>
       </c>
       <c r="K420" t="n">
-        <v>0.3744</v>
+        <v>0.3754</v>
       </c>
       <c r="L420" t="n">
-        <v>0.3092</v>
+        <v>0.3089</v>
       </c>
       <c r="M420" t="n">
         <v>164</v>
@@ -23142,22 +23142,22 @@
         </is>
       </c>
       <c r="G421" t="n">
-        <v>0.7491</v>
+        <v>0.7534</v>
       </c>
       <c r="H421" t="n">
-        <v>0.6248</v>
+        <v>0.6343</v>
       </c>
       <c r="I421" t="n">
-        <v>0.6869</v>
+        <v>0.6938</v>
       </c>
       <c r="J421" t="n">
-        <v>0.2509</v>
+        <v>0.2466</v>
       </c>
       <c r="K421" t="n">
-        <v>0.3752</v>
+        <v>0.3657</v>
       </c>
       <c r="L421" t="n">
-        <v>0.3131</v>
+        <v>0.3062</v>
       </c>
       <c r="M421" t="n">
         <v>164</v>
@@ -23196,22 +23196,22 @@
         </is>
       </c>
       <c r="G422" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8164</v>
       </c>
       <c r="H422" t="n">
-        <v>0.6885</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="I422" t="n">
-        <v>0.7508</v>
+        <v>0.7547</v>
       </c>
       <c r="J422" t="n">
-        <v>0.187</v>
+        <v>0.1836</v>
       </c>
       <c r="K422" t="n">
-        <v>0.3115</v>
+        <v>0.307</v>
       </c>
       <c r="L422" t="n">
-        <v>0.2492</v>
+        <v>0.2453</v>
       </c>
       <c r="M422" t="n">
         <v>164</v>
@@ -23250,22 +23250,22 @@
         </is>
       </c>
       <c r="G423" t="n">
-        <v>0.8375</v>
+        <v>0.8434</v>
       </c>
       <c r="H423" t="n">
-        <v>0.6596</v>
+        <v>0.6662</v>
       </c>
       <c r="I423" t="n">
-        <v>0.7486</v>
+        <v>0.7548</v>
       </c>
       <c r="J423" t="n">
-        <v>0.1625</v>
+        <v>0.1566</v>
       </c>
       <c r="K423" t="n">
-        <v>0.3404</v>
+        <v>0.3338</v>
       </c>
       <c r="L423" t="n">
-        <v>0.2514</v>
+        <v>0.2452</v>
       </c>
       <c r="M423" t="n">
         <v>164</v>
@@ -23304,22 +23304,22 @@
         </is>
       </c>
       <c r="G424" t="n">
-        <v>0.86</v>
+        <v>0.8606</v>
       </c>
       <c r="H424" t="n">
-        <v>0.7359</v>
+        <v>0.7387</v>
       </c>
       <c r="I424" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.7996</v>
       </c>
       <c r="J424" t="n">
-        <v>0.14</v>
+        <v>0.1394</v>
       </c>
       <c r="K424" t="n">
-        <v>0.2641</v>
+        <v>0.2613</v>
       </c>
       <c r="L424" t="n">
-        <v>0.2021</v>
+        <v>0.2004</v>
       </c>
       <c r="M424" t="n">
         <v>164</v>
@@ -23415,19 +23415,19 @@
         <v>0.4991</v>
       </c>
       <c r="H426" t="n">
-        <v>0.3578</v>
+        <v>0.3611</v>
       </c>
       <c r="I426" t="n">
-        <v>0.4284</v>
+        <v>0.4301</v>
       </c>
       <c r="J426" t="n">
         <v>0.5009</v>
       </c>
       <c r="K426" t="n">
-        <v>0.6422</v>
+        <v>0.6389</v>
       </c>
       <c r="L426" t="n">
-        <v>0.5716</v>
+        <v>0.5699</v>
       </c>
       <c r="M426" t="n">
         <v>164</v>
@@ -23520,22 +23520,22 @@
         </is>
       </c>
       <c r="G428" t="n">
-        <v>0.6434</v>
+        <v>0.6479</v>
       </c>
       <c r="H428" t="n">
-        <v>0.5199</v>
+        <v>0.522</v>
       </c>
       <c r="I428" t="n">
-        <v>0.5816</v>
+        <v>0.585</v>
       </c>
       <c r="J428" t="n">
-        <v>0.3566</v>
+        <v>0.3521</v>
       </c>
       <c r="K428" t="n">
-        <v>0.4801</v>
+        <v>0.478</v>
       </c>
       <c r="L428" t="n">
-        <v>0.4184</v>
+        <v>0.415</v>
       </c>
       <c r="M428" t="n">
         <v>164</v>
@@ -23574,22 +23574,22 @@
         </is>
       </c>
       <c r="G429" t="n">
-        <v>0.2919</v>
+        <v>0.2905</v>
       </c>
       <c r="H429" t="n">
-        <v>0.1699</v>
+        <v>0.167</v>
       </c>
       <c r="I429" t="n">
-        <v>0.2309</v>
+        <v>0.2288</v>
       </c>
       <c r="J429" t="n">
-        <v>0.7081</v>
+        <v>0.7095</v>
       </c>
       <c r="K429" t="n">
-        <v>0.8300999999999999</v>
+        <v>0.833</v>
       </c>
       <c r="L429" t="n">
-        <v>0.7691</v>
+        <v>0.7712</v>
       </c>
       <c r="M429" t="n">
         <v>164</v>
@@ -23628,22 +23628,22 @@
         </is>
       </c>
       <c r="G430" t="n">
-        <v>0.2739</v>
+        <v>0.2713</v>
       </c>
       <c r="H430" t="n">
-        <v>0.1419</v>
+        <v>0.139</v>
       </c>
       <c r="I430" t="n">
-        <v>0.2079</v>
+        <v>0.2052</v>
       </c>
       <c r="J430" t="n">
-        <v>0.7261</v>
+        <v>0.7287</v>
       </c>
       <c r="K430" t="n">
-        <v>0.8581</v>
+        <v>0.861</v>
       </c>
       <c r="L430" t="n">
-        <v>0.7921</v>
+        <v>0.7948</v>
       </c>
       <c r="M430" t="n">
         <v>164</v>
@@ -23682,22 +23682,22 @@
         </is>
       </c>
       <c r="G431" t="n">
-        <v>0.6802</v>
+        <v>0.6819</v>
       </c>
       <c r="H431" t="n">
         <v>0.5527</v>
       </c>
       <c r="I431" t="n">
-        <v>0.6163999999999999</v>
+        <v>0.6173</v>
       </c>
       <c r="J431" t="n">
-        <v>0.3198</v>
+        <v>0.3181</v>
       </c>
       <c r="K431" t="n">
         <v>0.4473</v>
       </c>
       <c r="L431" t="n">
-        <v>0.3836</v>
+        <v>0.3827</v>
       </c>
       <c r="M431" t="n">
         <v>164</v>
@@ -23736,22 +23736,22 @@
         </is>
       </c>
       <c r="G432" t="n">
-        <v>0.283</v>
+        <v>0.2767</v>
       </c>
       <c r="H432" t="n">
         <v>0.1576</v>
       </c>
       <c r="I432" t="n">
-        <v>0.2203</v>
+        <v>0.2172</v>
       </c>
       <c r="J432" t="n">
-        <v>0.717</v>
+        <v>0.7233000000000001</v>
       </c>
       <c r="K432" t="n">
         <v>0.8424</v>
       </c>
       <c r="L432" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="M432" t="n">
         <v>164</v>
@@ -23790,22 +23790,22 @@
         </is>
       </c>
       <c r="G433" t="n">
-        <v>0.2884</v>
+        <v>0.284</v>
       </c>
       <c r="H433" t="n">
-        <v>0.1534</v>
+        <v>0.1524</v>
       </c>
       <c r="I433" t="n">
-        <v>0.2209</v>
+        <v>0.2182</v>
       </c>
       <c r="J433" t="n">
-        <v>0.7116</v>
+        <v>0.716</v>
       </c>
       <c r="K433" t="n">
-        <v>0.8466</v>
+        <v>0.8476</v>
       </c>
       <c r="L433" t="n">
-        <v>0.7791</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="M433" t="n">
         <v>164</v>
@@ -23847,19 +23847,19 @@
         <v>0.2552</v>
       </c>
       <c r="H434" t="n">
-        <v>0.1531</v>
+        <v>0.1508</v>
       </c>
       <c r="I434" t="n">
-        <v>0.2042</v>
+        <v>0.203</v>
       </c>
       <c r="J434" t="n">
         <v>0.7448</v>
       </c>
       <c r="K434" t="n">
-        <v>0.8469</v>
+        <v>0.8492</v>
       </c>
       <c r="L434" t="n">
-        <v>0.7958</v>
+        <v>0.797</v>
       </c>
       <c r="M434" t="n">
         <v>164</v>
@@ -23901,19 +23901,19 @@
         <v>0.2283</v>
       </c>
       <c r="H435" t="n">
-        <v>0.133</v>
+        <v>0.1307</v>
       </c>
       <c r="I435" t="n">
-        <v>0.1806</v>
+        <v>0.1795</v>
       </c>
       <c r="J435" t="n">
         <v>0.7717000000000001</v>
       </c>
       <c r="K435" t="n">
-        <v>0.867</v>
+        <v>0.8693</v>
       </c>
       <c r="L435" t="n">
-        <v>0.8194</v>
+        <v>0.8205</v>
       </c>
       <c r="M435" t="n">
         <v>164</v>
@@ -23955,19 +23955,19 @@
         <v>0.5849</v>
       </c>
       <c r="H436" t="n">
-        <v>0.4553</v>
+        <v>0.4543</v>
       </c>
       <c r="I436" t="n">
-        <v>0.5201</v>
+        <v>0.5196</v>
       </c>
       <c r="J436" t="n">
         <v>0.4151</v>
       </c>
       <c r="K436" t="n">
-        <v>0.5447</v>
+        <v>0.5457</v>
       </c>
       <c r="L436" t="n">
-        <v>0.4799</v>
+        <v>0.4804</v>
       </c>
       <c r="M436" t="n">
         <v>164</v>

--- a/nba/public/data/nba_matchup_probs.xlsx
+++ b/nba/public/data/nba_matchup_probs.xlsx
@@ -843,19 +843,19 @@
         <v>0.7216</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5381</v>
+        <v>0.5417</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6298</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="J8" t="n">
         <v>0.2784</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4619</v>
+        <v>0.4583</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3702</v>
+        <v>0.3684</v>
       </c>
       <c r="M8" t="n">
         <v>164</v>
@@ -1221,19 +1221,19 @@
         <v>0.8678</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7642</v>
+        <v>0.7739</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8208</v>
       </c>
       <c r="J15" t="n">
         <v>0.1322</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2358</v>
+        <v>0.2261</v>
       </c>
       <c r="L15" t="n">
-        <v>0.184</v>
+        <v>0.1792</v>
       </c>
       <c r="M15" t="n">
         <v>164</v>
@@ -1380,22 +1380,22 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.8148</v>
+        <v>0.8126</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6931</v>
+        <v>0.6911</v>
       </c>
       <c r="I18" t="n">
-        <v>0.754</v>
+        <v>0.7518</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1852</v>
+        <v>0.1874</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3069</v>
+        <v>0.3089</v>
       </c>
       <c r="L18" t="n">
-        <v>0.246</v>
+        <v>0.2482</v>
       </c>
       <c r="M18" t="n">
         <v>164</v>
@@ -2028,22 +2028,22 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.5456</v>
+        <v>0.5218</v>
       </c>
       <c r="H30" t="n">
-        <v>0.407</v>
+        <v>0.4053</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4763</v>
+        <v>0.4636</v>
       </c>
       <c r="J30" t="n">
-        <v>0.4544</v>
+        <v>0.4782</v>
       </c>
       <c r="K30" t="n">
-        <v>0.593</v>
+        <v>0.5947</v>
       </c>
       <c r="L30" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.5364</v>
       </c>
       <c r="M30" t="n">
         <v>164</v>
@@ -2193,19 +2193,19 @@
         <v>0.8582</v>
       </c>
       <c r="H33" t="n">
-        <v>0.7382</v>
+        <v>0.74</v>
       </c>
       <c r="I33" t="n">
-        <v>0.7982</v>
+        <v>0.7991</v>
       </c>
       <c r="J33" t="n">
         <v>0.1418</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2618</v>
+        <v>0.26</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2018</v>
+        <v>0.2009</v>
       </c>
       <c r="M33" t="n">
         <v>164</v>
@@ -2892,22 +2892,22 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.8623</v>
+        <v>0.8594000000000001</v>
       </c>
       <c r="H46" t="n">
-        <v>0.7581</v>
+        <v>0.7529</v>
       </c>
       <c r="I46" t="n">
-        <v>0.8102</v>
+        <v>0.8062</v>
       </c>
       <c r="J46" t="n">
-        <v>0.1377</v>
+        <v>0.1406</v>
       </c>
       <c r="K46" t="n">
-        <v>0.2419</v>
+        <v>0.2471</v>
       </c>
       <c r="L46" t="n">
-        <v>0.1898</v>
+        <v>0.1938</v>
       </c>
       <c r="M46" t="n">
         <v>164</v>
@@ -3540,22 +3540,22 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.6906</v>
+        <v>0.6728</v>
       </c>
       <c r="H58" t="n">
-        <v>0.5284</v>
+        <v>0.5187</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6095</v>
+        <v>0.5958</v>
       </c>
       <c r="J58" t="n">
-        <v>0.3094</v>
+        <v>0.3272</v>
       </c>
       <c r="K58" t="n">
-        <v>0.4716</v>
+        <v>0.4813</v>
       </c>
       <c r="L58" t="n">
-        <v>0.3905</v>
+        <v>0.4042</v>
       </c>
       <c r="M58" t="n">
         <v>164</v>
@@ -4350,22 +4350,22 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.8442</v>
+        <v>0.8366</v>
       </c>
       <c r="H73" t="n">
         <v>0.7727000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8084</v>
+        <v>0.8047</v>
       </c>
       <c r="J73" t="n">
-        <v>0.1558</v>
+        <v>0.1634</v>
       </c>
       <c r="K73" t="n">
         <v>0.2273</v>
       </c>
       <c r="L73" t="n">
-        <v>0.1916</v>
+        <v>0.1953</v>
       </c>
       <c r="M73" t="n">
         <v>164</v>
@@ -4404,22 +4404,22 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0.7541</v>
+        <v>0.7565</v>
       </c>
       <c r="H74" t="n">
         <v>0.6133</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6837</v>
+        <v>0.6849</v>
       </c>
       <c r="J74" t="n">
-        <v>0.2459</v>
+        <v>0.2435</v>
       </c>
       <c r="K74" t="n">
         <v>0.3867</v>
       </c>
       <c r="L74" t="n">
-        <v>0.3163</v>
+        <v>0.3151</v>
       </c>
       <c r="M74" t="n">
         <v>164</v>
@@ -4458,22 +4458,22 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.7549</v>
+        <v>0.7571</v>
       </c>
       <c r="H75" t="n">
         <v>0.6009</v>
       </c>
       <c r="I75" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.679</v>
       </c>
       <c r="J75" t="n">
-        <v>0.2451</v>
+        <v>0.2429</v>
       </c>
       <c r="K75" t="n">
         <v>0.3991</v>
       </c>
       <c r="L75" t="n">
-        <v>0.3221</v>
+        <v>0.321</v>
       </c>
       <c r="M75" t="n">
         <v>164</v>
@@ -4998,22 +4998,22 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0.6502</v>
+        <v>0.6398</v>
       </c>
       <c r="H85" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.4883</v>
       </c>
       <c r="I85" t="n">
-        <v>0.5774</v>
+        <v>0.5641</v>
       </c>
       <c r="J85" t="n">
-        <v>0.3498</v>
+        <v>0.3602</v>
       </c>
       <c r="K85" t="n">
-        <v>0.4955</v>
+        <v>0.5117</v>
       </c>
       <c r="L85" t="n">
-        <v>0.4226</v>
+        <v>0.4359</v>
       </c>
       <c r="M85" t="n">
         <v>164</v>
@@ -5160,22 +5160,22 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0.2764</v>
+        <v>0.2717</v>
       </c>
       <c r="H88" t="n">
         <v>0.1604</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2184</v>
+        <v>0.216</v>
       </c>
       <c r="J88" t="n">
-        <v>0.7236</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="K88" t="n">
         <v>0.8396</v>
       </c>
       <c r="L88" t="n">
-        <v>0.7816</v>
+        <v>0.784</v>
       </c>
       <c r="M88" t="n">
         <v>164</v>
@@ -5754,22 +5754,22 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0.6327</v>
+        <v>0.628</v>
       </c>
       <c r="H99" t="n">
-        <v>0.495</v>
+        <v>0.4944</v>
       </c>
       <c r="I99" t="n">
-        <v>0.5638</v>
+        <v>0.5612</v>
       </c>
       <c r="J99" t="n">
-        <v>0.3673</v>
+        <v>0.372</v>
       </c>
       <c r="K99" t="n">
-        <v>0.505</v>
+        <v>0.5056</v>
       </c>
       <c r="L99" t="n">
-        <v>0.4362</v>
+        <v>0.4388</v>
       </c>
       <c r="M99" t="n">
         <v>164</v>
@@ -6402,22 +6402,22 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>0.3517</v>
+        <v>0.3441</v>
       </c>
       <c r="H111" t="n">
-        <v>0.2045</v>
+        <v>0.2</v>
       </c>
       <c r="I111" t="n">
-        <v>0.2781</v>
+        <v>0.272</v>
       </c>
       <c r="J111" t="n">
-        <v>0.6483</v>
+        <v>0.6559</v>
       </c>
       <c r="K111" t="n">
-        <v>0.7955</v>
+        <v>0.8</v>
       </c>
       <c r="L111" t="n">
-        <v>0.7219</v>
+        <v>0.728</v>
       </c>
       <c r="M111" t="n">
         <v>164</v>
@@ -6729,19 +6729,19 @@
         <v>0.3749</v>
       </c>
       <c r="H117" t="n">
-        <v>0.2191</v>
+        <v>0.2203</v>
       </c>
       <c r="I117" t="n">
-        <v>0.297</v>
+        <v>0.2976</v>
       </c>
       <c r="J117" t="n">
         <v>0.6251</v>
       </c>
       <c r="K117" t="n">
-        <v>0.7809</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="L117" t="n">
-        <v>0.703</v>
+        <v>0.7024</v>
       </c>
       <c r="M117" t="n">
         <v>164</v>
@@ -7104,22 +7104,22 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.6226</v>
+        <v>0.6029</v>
       </c>
       <c r="H124" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.4985</v>
       </c>
       <c r="I124" t="n">
-        <v>0.5616</v>
+        <v>0.5507</v>
       </c>
       <c r="J124" t="n">
-        <v>0.3774</v>
+        <v>0.3971</v>
       </c>
       <c r="K124" t="n">
-        <v>0.4995</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="L124" t="n">
-        <v>0.4384</v>
+        <v>0.4493</v>
       </c>
       <c r="M124" t="n">
         <v>164</v>
@@ -7752,22 +7752,22 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>0.3529</v>
+        <v>0.3379</v>
       </c>
       <c r="H136" t="n">
-        <v>0.2004</v>
+        <v>0.1836</v>
       </c>
       <c r="I136" t="n">
-        <v>0.2766</v>
+        <v>0.2608</v>
       </c>
       <c r="J136" t="n">
-        <v>0.6471</v>
+        <v>0.6621</v>
       </c>
       <c r="K136" t="n">
-        <v>0.7996</v>
+        <v>0.8164</v>
       </c>
       <c r="L136" t="n">
-        <v>0.7234</v>
+        <v>0.7392</v>
       </c>
       <c r="M136" t="n">
         <v>164</v>
@@ -8400,22 +8400,22 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>0.5383</v>
+        <v>0.5357</v>
       </c>
       <c r="H148" t="n">
-        <v>0.4514</v>
+        <v>0.4429</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4948</v>
+        <v>0.4893</v>
       </c>
       <c r="J148" t="n">
-        <v>0.4617</v>
+        <v>0.4643</v>
       </c>
       <c r="K148" t="n">
-        <v>0.5486</v>
+        <v>0.5571</v>
       </c>
       <c r="L148" t="n">
-        <v>0.5052</v>
+        <v>0.5107</v>
       </c>
       <c r="M148" t="n">
         <v>164</v>
@@ -8940,22 +8940,22 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>0.6973</v>
+        <v>0.7019</v>
       </c>
       <c r="H158" t="n">
         <v>0.5595</v>
       </c>
       <c r="I158" t="n">
-        <v>0.6284</v>
+        <v>0.6307</v>
       </c>
       <c r="J158" t="n">
-        <v>0.3027</v>
+        <v>0.2981</v>
       </c>
       <c r="K158" t="n">
         <v>0.4405</v>
       </c>
       <c r="L158" t="n">
-        <v>0.3716</v>
+        <v>0.3693</v>
       </c>
       <c r="M158" t="n">
         <v>164</v>
@@ -9048,22 +9048,22 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>0.2932</v>
+        <v>0.2837</v>
       </c>
       <c r="H160" t="n">
-        <v>0.163</v>
+        <v>0.1549</v>
       </c>
       <c r="I160" t="n">
-        <v>0.2281</v>
+        <v>0.2193</v>
       </c>
       <c r="J160" t="n">
-        <v>0.7068</v>
+        <v>0.7163</v>
       </c>
       <c r="K160" t="n">
-        <v>0.837</v>
+        <v>0.8451</v>
       </c>
       <c r="L160" t="n">
-        <v>0.7719</v>
+        <v>0.7806999999999999</v>
       </c>
       <c r="M160" t="n">
         <v>164</v>
@@ -9642,22 +9642,22 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>0.8518</v>
+        <v>0.8478</v>
       </c>
       <c r="H171" t="n">
-        <v>0.7474</v>
+        <v>0.7421</v>
       </c>
       <c r="I171" t="n">
-        <v>0.7996</v>
+        <v>0.795</v>
       </c>
       <c r="J171" t="n">
-        <v>0.1482</v>
+        <v>0.1522</v>
       </c>
       <c r="K171" t="n">
-        <v>0.2526</v>
+        <v>0.2579</v>
       </c>
       <c r="L171" t="n">
-        <v>0.2004</v>
+        <v>0.205</v>
       </c>
       <c r="M171" t="n">
         <v>164</v>
@@ -10236,22 +10236,22 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0.6566</v>
+        <v>0.6607</v>
       </c>
       <c r="H182" t="n">
         <v>0.4997</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.5802</v>
       </c>
       <c r="J182" t="n">
-        <v>0.3434</v>
+        <v>0.3393</v>
       </c>
       <c r="K182" t="n">
         <v>0.5003</v>
       </c>
       <c r="L182" t="n">
-        <v>0.4219</v>
+        <v>0.4198</v>
       </c>
       <c r="M182" t="n">
         <v>164</v>
@@ -10290,22 +10290,22 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>0.6593</v>
+        <v>0.649</v>
       </c>
       <c r="H183" t="n">
-        <v>0.5139</v>
+        <v>0.4952</v>
       </c>
       <c r="I183" t="n">
-        <v>0.5866</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="J183" t="n">
-        <v>0.3407</v>
+        <v>0.351</v>
       </c>
       <c r="K183" t="n">
-        <v>0.4861</v>
+        <v>0.5048</v>
       </c>
       <c r="L183" t="n">
-        <v>0.4134</v>
+        <v>0.4279</v>
       </c>
       <c r="M183" t="n">
         <v>164</v>
@@ -10830,22 +10830,22 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.7194</v>
       </c>
       <c r="H193" t="n">
-        <v>0.5541</v>
+        <v>0.5537</v>
       </c>
       <c r="I193" t="n">
-        <v>0.6442</v>
+        <v>0.6365</v>
       </c>
       <c r="J193" t="n">
-        <v>0.2656</v>
+        <v>0.2806</v>
       </c>
       <c r="K193" t="n">
-        <v>0.4459</v>
+        <v>0.4463</v>
       </c>
       <c r="L193" t="n">
-        <v>0.3558</v>
+        <v>0.3635</v>
       </c>
       <c r="M193" t="n">
         <v>164</v>
@@ -11478,22 +11478,22 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>0.4158</v>
+        <v>0.4017</v>
       </c>
       <c r="H205" t="n">
-        <v>0.2463</v>
+        <v>0.2364</v>
       </c>
       <c r="I205" t="n">
-        <v>0.331</v>
+        <v>0.319</v>
       </c>
       <c r="J205" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="K205" t="n">
-        <v>0.7537</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="L205" t="n">
-        <v>0.669</v>
+        <v>0.681</v>
       </c>
       <c r="M205" t="n">
         <v>164</v>
@@ -11964,22 +11964,22 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>0.8256</v>
+        <v>0.8202</v>
       </c>
       <c r="H214" t="n">
-        <v>0.7187</v>
+        <v>0.7106</v>
       </c>
       <c r="I214" t="n">
-        <v>0.7722</v>
+        <v>0.7654</v>
       </c>
       <c r="J214" t="n">
-        <v>0.1744</v>
+        <v>0.1798</v>
       </c>
       <c r="K214" t="n">
-        <v>0.2813</v>
+        <v>0.2894</v>
       </c>
       <c r="L214" t="n">
-        <v>0.2278</v>
+        <v>0.2346</v>
       </c>
       <c r="M214" t="n">
         <v>164</v>
@@ -12612,22 +12612,22 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>0.5876</v>
+        <v>0.5669</v>
       </c>
       <c r="H226" t="n">
-        <v>0.4576</v>
+        <v>0.4527</v>
       </c>
       <c r="I226" t="n">
-        <v>0.5226</v>
+        <v>0.5098</v>
       </c>
       <c r="J226" t="n">
-        <v>0.4124</v>
+        <v>0.4331</v>
       </c>
       <c r="K226" t="n">
-        <v>0.5424</v>
+        <v>0.5473</v>
       </c>
       <c r="L226" t="n">
-        <v>0.4774</v>
+        <v>0.4902</v>
       </c>
       <c r="M226" t="n">
         <v>164</v>
@@ -13044,22 +13044,22 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>0.8128</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H234" t="n">
-        <v>0.6944</v>
+        <v>0.6815</v>
       </c>
       <c r="I234" t="n">
-        <v>0.7536</v>
+        <v>0.7458</v>
       </c>
       <c r="J234" t="n">
-        <v>0.1872</v>
+        <v>0.19</v>
       </c>
       <c r="K234" t="n">
-        <v>0.3056</v>
+        <v>0.3185</v>
       </c>
       <c r="L234" t="n">
-        <v>0.2464</v>
+        <v>0.2542</v>
       </c>
       <c r="M234" t="n">
         <v>164</v>
@@ -13479,19 +13479,19 @@
         <v>0.8381</v>
       </c>
       <c r="H242" t="n">
-        <v>0.7088</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="I242" t="n">
-        <v>0.7734</v>
+        <v>0.7752</v>
       </c>
       <c r="J242" t="n">
         <v>0.1619</v>
       </c>
       <c r="K242" t="n">
-        <v>0.2912</v>
+        <v>0.2878</v>
       </c>
       <c r="L242" t="n">
-        <v>0.2266</v>
+        <v>0.2248</v>
       </c>
       <c r="M242" t="n">
         <v>164</v>
@@ -13692,22 +13692,22 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>0.5007</v>
+        <v>0.4889</v>
       </c>
       <c r="H246" t="n">
-        <v>0.4137</v>
+        <v>0.4023</v>
       </c>
       <c r="I246" t="n">
-        <v>0.4572</v>
+        <v>0.4456</v>
       </c>
       <c r="J246" t="n">
-        <v>0.4993</v>
+        <v>0.5111</v>
       </c>
       <c r="K246" t="n">
-        <v>0.5863</v>
+        <v>0.5977</v>
       </c>
       <c r="L246" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.5544</v>
       </c>
       <c r="M246" t="n">
         <v>164</v>
@@ -14070,22 +14070,22 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>0.8114</v>
+        <v>0.8001</v>
       </c>
       <c r="H253" t="n">
-        <v>0.6961000000000001</v>
+        <v>0.6839</v>
       </c>
       <c r="I253" t="n">
-        <v>0.7538</v>
+        <v>0.742</v>
       </c>
       <c r="J253" t="n">
-        <v>0.1886</v>
+        <v>0.1999</v>
       </c>
       <c r="K253" t="n">
-        <v>0.3039</v>
+        <v>0.3161</v>
       </c>
       <c r="L253" t="n">
-        <v>0.2462</v>
+        <v>0.258</v>
       </c>
       <c r="M253" t="n">
         <v>164</v>
@@ -14286,22 +14286,22 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>0.8431</v>
+        <v>0.8458</v>
       </c>
       <c r="H257" t="n">
         <v>0.735</v>
       </c>
       <c r="I257" t="n">
-        <v>0.789</v>
+        <v>0.7904</v>
       </c>
       <c r="J257" t="n">
-        <v>0.1569</v>
+        <v>0.1542</v>
       </c>
       <c r="K257" t="n">
         <v>0.265</v>
       </c>
       <c r="L257" t="n">
-        <v>0.211</v>
+        <v>0.2096</v>
       </c>
       <c r="M257" t="n">
         <v>164</v>
@@ -14397,19 +14397,19 @@
         <v>0.361</v>
       </c>
       <c r="H259" t="n">
-        <v>0.2354</v>
+        <v>0.2331</v>
       </c>
       <c r="I259" t="n">
-        <v>0.2982</v>
+        <v>0.297</v>
       </c>
       <c r="J259" t="n">
         <v>0.639</v>
       </c>
       <c r="K259" t="n">
-        <v>0.7645999999999999</v>
+        <v>0.7669</v>
       </c>
       <c r="L259" t="n">
-        <v>0.7018</v>
+        <v>0.703</v>
       </c>
       <c r="M259" t="n">
         <v>164</v>
@@ -14718,22 +14718,22 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>0.4949</v>
+        <v>0.4729</v>
       </c>
       <c r="H265" t="n">
-        <v>0.4292</v>
+        <v>0.4214</v>
       </c>
       <c r="I265" t="n">
-        <v>0.462</v>
+        <v>0.4472</v>
       </c>
       <c r="J265" t="n">
-        <v>0.5051</v>
+        <v>0.5271</v>
       </c>
       <c r="K265" t="n">
-        <v>0.5708</v>
+        <v>0.5786</v>
       </c>
       <c r="L265" t="n">
-        <v>0.538</v>
+        <v>0.5528</v>
       </c>
       <c r="M265" t="n">
         <v>164</v>
@@ -15042,22 +15042,22 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>0.7435</v>
+        <v>0.7316</v>
       </c>
       <c r="H271" t="n">
-        <v>0.5924</v>
+        <v>0.5878</v>
       </c>
       <c r="I271" t="n">
-        <v>0.668</v>
+        <v>0.6597</v>
       </c>
       <c r="J271" t="n">
-        <v>0.2565</v>
+        <v>0.2684</v>
       </c>
       <c r="K271" t="n">
-        <v>0.4076</v>
+        <v>0.4122</v>
       </c>
       <c r="L271" t="n">
-        <v>0.332</v>
+        <v>0.3403</v>
       </c>
       <c r="M271" t="n">
         <v>164</v>
@@ -15312,22 +15312,22 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>0.3387</v>
+        <v>0.3343</v>
       </c>
       <c r="H276" t="n">
         <v>0.1821</v>
       </c>
       <c r="I276" t="n">
-        <v>0.2604</v>
+        <v>0.2582</v>
       </c>
       <c r="J276" t="n">
-        <v>0.6613</v>
+        <v>0.6657</v>
       </c>
       <c r="K276" t="n">
         <v>0.8179</v>
       </c>
       <c r="L276" t="n">
-        <v>0.7396</v>
+        <v>0.7418</v>
       </c>
       <c r="M276" t="n">
         <v>164</v>
@@ -15690,22 +15690,22 @@
         </is>
       </c>
       <c r="G283" t="n">
-        <v>0.4772</v>
+        <v>0.4614</v>
       </c>
       <c r="H283" t="n">
-        <v>0.319</v>
+        <v>0.2904</v>
       </c>
       <c r="I283" t="n">
-        <v>0.3981</v>
+        <v>0.3759</v>
       </c>
       <c r="J283" t="n">
-        <v>0.5228</v>
+        <v>0.5386</v>
       </c>
       <c r="K283" t="n">
-        <v>0.681</v>
+        <v>0.7096</v>
       </c>
       <c r="L283" t="n">
-        <v>0.6019</v>
+        <v>0.6241</v>
       </c>
       <c r="M283" t="n">
         <v>164</v>
@@ -15960,22 +15960,22 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>0.5396</v>
+        <v>0.5349</v>
       </c>
       <c r="H288" t="n">
-        <v>0.3792</v>
+        <v>0.36</v>
       </c>
       <c r="I288" t="n">
-        <v>0.4594</v>
+        <v>0.4474</v>
       </c>
       <c r="J288" t="n">
-        <v>0.4604</v>
+        <v>0.4651</v>
       </c>
       <c r="K288" t="n">
-        <v>0.6208</v>
+        <v>0.64</v>
       </c>
       <c r="L288" t="n">
-        <v>0.5406</v>
+        <v>0.5526</v>
       </c>
       <c r="M288" t="n">
         <v>164</v>
@@ -16608,22 +16608,22 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>0.2798</v>
+        <v>0.2742</v>
       </c>
       <c r="H300" t="n">
-        <v>0.1616</v>
+        <v>0.1583</v>
       </c>
       <c r="I300" t="n">
-        <v>0.2207</v>
+        <v>0.2162</v>
       </c>
       <c r="J300" t="n">
-        <v>0.7202</v>
+        <v>0.7258</v>
       </c>
       <c r="K300" t="n">
-        <v>0.8384</v>
+        <v>0.8417</v>
       </c>
       <c r="L300" t="n">
-        <v>0.7793</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="M300" t="n">
         <v>164</v>
@@ -16824,22 +16824,22 @@
         </is>
       </c>
       <c r="G304" t="n">
-        <v>0.8295</v>
+        <v>0.8196</v>
       </c>
       <c r="H304" t="n">
-        <v>0.7016</v>
+        <v>0.6956</v>
       </c>
       <c r="I304" t="n">
-        <v>0.7655</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="J304" t="n">
-        <v>0.1705</v>
+        <v>0.1804</v>
       </c>
       <c r="K304" t="n">
-        <v>0.2984</v>
+        <v>0.3044</v>
       </c>
       <c r="L304" t="n">
-        <v>0.2345</v>
+        <v>0.2424</v>
       </c>
       <c r="M304" t="n">
         <v>164</v>
@@ -17472,22 +17472,22 @@
         </is>
       </c>
       <c r="G316" t="n">
-        <v>0.6016</v>
+        <v>0.5985</v>
       </c>
       <c r="H316" t="n">
-        <v>0.44</v>
+        <v>0.4231</v>
       </c>
       <c r="I316" t="n">
-        <v>0.5208</v>
+        <v>0.5108</v>
       </c>
       <c r="J316" t="n">
-        <v>0.3984</v>
+        <v>0.4015</v>
       </c>
       <c r="K316" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5769</v>
       </c>
       <c r="L316" t="n">
-        <v>0.4792</v>
+        <v>0.4892</v>
       </c>
       <c r="M316" t="n">
         <v>164</v>
@@ -17634,22 +17634,22 @@
         </is>
       </c>
       <c r="G319" t="n">
-        <v>0.4699</v>
+        <v>0.4548</v>
       </c>
       <c r="H319" t="n">
-        <v>0.2896</v>
+        <v>0.2862</v>
       </c>
       <c r="I319" t="n">
-        <v>0.3798</v>
+        <v>0.3705</v>
       </c>
       <c r="J319" t="n">
-        <v>0.5301</v>
+        <v>0.5452</v>
       </c>
       <c r="K319" t="n">
-        <v>0.7104</v>
+        <v>0.7138</v>
       </c>
       <c r="L319" t="n">
-        <v>0.6202</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="M319" t="n">
         <v>164</v>
@@ -18282,22 +18282,22 @@
         </is>
       </c>
       <c r="G331" t="n">
-        <v>0.2213</v>
+        <v>0.2131</v>
       </c>
       <c r="H331" t="n">
-        <v>0.1319</v>
+        <v>0.1278</v>
       </c>
       <c r="I331" t="n">
-        <v>0.1766</v>
+        <v>0.1704</v>
       </c>
       <c r="J331" t="n">
-        <v>0.7786999999999999</v>
+        <v>0.7869</v>
       </c>
       <c r="K331" t="n">
-        <v>0.8681</v>
+        <v>0.8722</v>
       </c>
       <c r="L331" t="n">
-        <v>0.8234</v>
+        <v>0.8296</v>
       </c>
       <c r="M331" t="n">
         <v>164</v>
@@ -18390,22 +18390,22 @@
         </is>
       </c>
       <c r="G333" t="n">
-        <v>0.8334</v>
+        <v>0.8288</v>
       </c>
       <c r="H333" t="n">
-        <v>0.7353</v>
+        <v>0.7335</v>
       </c>
       <c r="I333" t="n">
-        <v>0.7844</v>
+        <v>0.7812</v>
       </c>
       <c r="J333" t="n">
-        <v>0.1666</v>
+        <v>0.1712</v>
       </c>
       <c r="K333" t="n">
-        <v>0.2647</v>
+        <v>0.2665</v>
       </c>
       <c r="L333" t="n">
-        <v>0.2156</v>
+        <v>0.2188</v>
       </c>
       <c r="M333" t="n">
         <v>164</v>
@@ -18501,19 +18501,19 @@
         <v>0.7374000000000001</v>
       </c>
       <c r="H335" t="n">
-        <v>0.5726</v>
+        <v>0.5707</v>
       </c>
       <c r="I335" t="n">
-        <v>0.655</v>
+        <v>0.654</v>
       </c>
       <c r="J335" t="n">
         <v>0.2626</v>
       </c>
       <c r="K335" t="n">
-        <v>0.4274</v>
+        <v>0.4293</v>
       </c>
       <c r="L335" t="n">
-        <v>0.345</v>
+        <v>0.346</v>
       </c>
       <c r="M335" t="n">
         <v>164</v>
@@ -18552,22 +18552,22 @@
         </is>
       </c>
       <c r="G336" t="n">
-        <v>0.7637</v>
+        <v>0.7667</v>
       </c>
       <c r="H336" t="n">
         <v>0.5982</v>
       </c>
       <c r="I336" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.6824</v>
       </c>
       <c r="J336" t="n">
-        <v>0.2363</v>
+        <v>0.2333</v>
       </c>
       <c r="K336" t="n">
         <v>0.4018</v>
       </c>
       <c r="L336" t="n">
-        <v>0.3191</v>
+        <v>0.3176</v>
       </c>
       <c r="M336" t="n">
         <v>164</v>
@@ -18876,22 +18876,22 @@
         </is>
       </c>
       <c r="G342" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.878</v>
       </c>
       <c r="H342" t="n">
         <v>0.7451</v>
       </c>
       <c r="I342" t="n">
-        <v>0.8113</v>
+        <v>0.8116</v>
       </c>
       <c r="J342" t="n">
-        <v>0.1225</v>
+        <v>0.122</v>
       </c>
       <c r="K342" t="n">
         <v>0.2549</v>
       </c>
       <c r="L342" t="n">
-        <v>0.1887</v>
+        <v>0.1884</v>
       </c>
       <c r="M342" t="n">
         <v>164</v>
@@ -19038,22 +19038,22 @@
         </is>
       </c>
       <c r="G345" t="n">
-        <v>0.6089</v>
+        <v>0.5909</v>
       </c>
       <c r="H345" t="n">
-        <v>0.4811</v>
+        <v>0.4692</v>
       </c>
       <c r="I345" t="n">
-        <v>0.545</v>
+        <v>0.53</v>
       </c>
       <c r="J345" t="n">
-        <v>0.3911</v>
+        <v>0.4091</v>
       </c>
       <c r="K345" t="n">
-        <v>0.5189</v>
+        <v>0.5308</v>
       </c>
       <c r="L345" t="n">
-        <v>0.455</v>
+        <v>0.47</v>
       </c>
       <c r="M345" t="n">
         <v>164</v>
@@ -19092,22 +19092,22 @@
         </is>
       </c>
       <c r="G346" t="n">
-        <v>0.7249</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="H346" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.5491</v>
       </c>
       <c r="I346" t="n">
-        <v>0.6449</v>
+        <v>0.6337</v>
       </c>
       <c r="J346" t="n">
-        <v>0.2751</v>
+        <v>0.2818</v>
       </c>
       <c r="K346" t="n">
-        <v>0.435</v>
+        <v>0.4509</v>
       </c>
       <c r="L346" t="n">
-        <v>0.3551</v>
+        <v>0.3663</v>
       </c>
       <c r="M346" t="n">
         <v>164</v>
@@ -19308,22 +19308,22 @@
         </is>
       </c>
       <c r="G350" t="n">
-        <v>0.785</v>
+        <v>0.7889</v>
       </c>
       <c r="H350" t="n">
         <v>0.6461</v>
       </c>
       <c r="I350" t="n">
-        <v>0.7156</v>
+        <v>0.7175</v>
       </c>
       <c r="J350" t="n">
-        <v>0.215</v>
+        <v>0.2111</v>
       </c>
       <c r="K350" t="n">
         <v>0.3539</v>
       </c>
       <c r="L350" t="n">
-        <v>0.2844</v>
+        <v>0.2825</v>
       </c>
       <c r="M350" t="n">
         <v>164</v>
@@ -19740,22 +19740,22 @@
         </is>
       </c>
       <c r="G358" t="n">
-        <v>0.419</v>
+        <v>0.4155</v>
       </c>
       <c r="H358" t="n">
-        <v>0.2654</v>
+        <v>0.2487</v>
       </c>
       <c r="I358" t="n">
-        <v>0.3422</v>
+        <v>0.3321</v>
       </c>
       <c r="J358" t="n">
-        <v>0.581</v>
+        <v>0.5845</v>
       </c>
       <c r="K358" t="n">
-        <v>0.7346</v>
+        <v>0.7513</v>
       </c>
       <c r="L358" t="n">
-        <v>0.6578000000000001</v>
+        <v>0.6679</v>
       </c>
       <c r="M358" t="n">
         <v>164</v>
@@ -19794,22 +19794,22 @@
         </is>
       </c>
       <c r="G359" t="n">
-        <v>0.3723</v>
+        <v>0.3785</v>
       </c>
       <c r="H359" t="n">
-        <v>0.2228</v>
+        <v>0.2258</v>
       </c>
       <c r="I359" t="n">
-        <v>0.2976</v>
+        <v>0.3022</v>
       </c>
       <c r="J359" t="n">
-        <v>0.6277</v>
+        <v>0.6215000000000001</v>
       </c>
       <c r="K359" t="n">
-        <v>0.7772</v>
+        <v>0.7742</v>
       </c>
       <c r="L359" t="n">
-        <v>0.7024</v>
+        <v>0.6978</v>
       </c>
       <c r="M359" t="n">
         <v>164</v>
@@ -19848,22 +19848,22 @@
         </is>
       </c>
       <c r="G360" t="n">
-        <v>0.3694</v>
+        <v>0.3739</v>
       </c>
       <c r="H360" t="n">
-        <v>0.2274</v>
+        <v>0.2491</v>
       </c>
       <c r="I360" t="n">
-        <v>0.2984</v>
+        <v>0.3115</v>
       </c>
       <c r="J360" t="n">
-        <v>0.6306</v>
+        <v>0.6261</v>
       </c>
       <c r="K360" t="n">
-        <v>0.7726</v>
+        <v>0.7509</v>
       </c>
       <c r="L360" t="n">
-        <v>0.7016</v>
+        <v>0.6885</v>
       </c>
       <c r="M360" t="n">
         <v>164</v>
@@ -19902,22 +19902,22 @@
         </is>
       </c>
       <c r="G361" t="n">
-        <v>0.42</v>
+        <v>0.4182</v>
       </c>
       <c r="H361" t="n">
-        <v>0.2698</v>
+        <v>0.2808</v>
       </c>
       <c r="I361" t="n">
-        <v>0.3449</v>
+        <v>0.3495</v>
       </c>
       <c r="J361" t="n">
-        <v>0.58</v>
+        <v>0.5818</v>
       </c>
       <c r="K361" t="n">
-        <v>0.7302</v>
+        <v>0.7192</v>
       </c>
       <c r="L361" t="n">
-        <v>0.6551</v>
+        <v>0.6505</v>
       </c>
       <c r="M361" t="n">
         <v>164</v>
@@ -19956,22 +19956,22 @@
         </is>
       </c>
       <c r="G362" t="n">
-        <v>0.6756</v>
+        <v>0.6793</v>
       </c>
       <c r="H362" t="n">
-        <v>0.5605</v>
+        <v>0.5701000000000001</v>
       </c>
       <c r="I362" t="n">
-        <v>0.618</v>
+        <v>0.6247</v>
       </c>
       <c r="J362" t="n">
-        <v>0.3244</v>
+        <v>0.3207</v>
       </c>
       <c r="K362" t="n">
-        <v>0.4395</v>
+        <v>0.4299</v>
       </c>
       <c r="L362" t="n">
-        <v>0.382</v>
+        <v>0.3753</v>
       </c>
       <c r="M362" t="n">
         <v>164</v>
@@ -20010,22 +20010,22 @@
         </is>
       </c>
       <c r="G363" t="n">
-        <v>0.2528</v>
+        <v>0.2611</v>
       </c>
       <c r="H363" t="n">
-        <v>0.1386</v>
+        <v>0.1414</v>
       </c>
       <c r="I363" t="n">
-        <v>0.1957</v>
+        <v>0.2012</v>
       </c>
       <c r="J363" t="n">
-        <v>0.7472</v>
+        <v>0.7389</v>
       </c>
       <c r="K363" t="n">
-        <v>0.8614000000000001</v>
+        <v>0.8586</v>
       </c>
       <c r="L363" t="n">
-        <v>0.8043</v>
+        <v>0.7988</v>
       </c>
       <c r="M363" t="n">
         <v>164</v>
@@ -20064,22 +20064,22 @@
         </is>
       </c>
       <c r="G364" t="n">
-        <v>0.2504</v>
+        <v>0.2557</v>
       </c>
       <c r="H364" t="n">
-        <v>0.1335</v>
+        <v>0.134</v>
       </c>
       <c r="I364" t="n">
-        <v>0.192</v>
+        <v>0.1948</v>
       </c>
       <c r="J364" t="n">
-        <v>0.7496</v>
+        <v>0.7443</v>
       </c>
       <c r="K364" t="n">
-        <v>0.8665</v>
+        <v>0.866</v>
       </c>
       <c r="L364" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8052</v>
       </c>
       <c r="M364" t="n">
         <v>164</v>
@@ -20118,22 +20118,22 @@
         </is>
       </c>
       <c r="G365" t="n">
-        <v>0.3394</v>
+        <v>0.3506</v>
       </c>
       <c r="H365" t="n">
-        <v>0.2203</v>
+        <v>0.2243</v>
       </c>
       <c r="I365" t="n">
-        <v>0.2798</v>
+        <v>0.2874</v>
       </c>
       <c r="J365" t="n">
-        <v>0.6606</v>
+        <v>0.6494</v>
       </c>
       <c r="K365" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="L365" t="n">
-        <v>0.7202</v>
+        <v>0.7126</v>
       </c>
       <c r="M365" t="n">
         <v>164</v>
@@ -20172,22 +20172,22 @@
         </is>
       </c>
       <c r="G366" t="n">
-        <v>0.6364</v>
+        <v>0.6505</v>
       </c>
       <c r="H366" t="n">
-        <v>0.5403</v>
+        <v>0.5423</v>
       </c>
       <c r="I366" t="n">
-        <v>0.5883</v>
+        <v>0.5964</v>
       </c>
       <c r="J366" t="n">
-        <v>0.3636</v>
+        <v>0.3495</v>
       </c>
       <c r="K366" t="n">
-        <v>0.4597</v>
+        <v>0.4577</v>
       </c>
       <c r="L366" t="n">
-        <v>0.4117</v>
+        <v>0.4036</v>
       </c>
       <c r="M366" t="n">
         <v>164</v>
@@ -20226,22 +20226,22 @@
         </is>
       </c>
       <c r="G367" t="n">
-        <v>0.618</v>
+        <v>0.622</v>
       </c>
       <c r="H367" t="n">
-        <v>0.4833</v>
+        <v>0.4968</v>
       </c>
       <c r="I367" t="n">
-        <v>0.5506</v>
+        <v>0.5594</v>
       </c>
       <c r="J367" t="n">
-        <v>0.382</v>
+        <v>0.378</v>
       </c>
       <c r="K367" t="n">
-        <v>0.5167</v>
+        <v>0.5032</v>
       </c>
       <c r="L367" t="n">
-        <v>0.4494</v>
+        <v>0.4406</v>
       </c>
       <c r="M367" t="n">
         <v>164</v>
@@ -20280,22 +20280,22 @@
         </is>
       </c>
       <c r="G368" t="n">
-        <v>0.7256</v>
+        <v>0.7331</v>
       </c>
       <c r="H368" t="n">
-        <v>0.59</v>
+        <v>0.5996</v>
       </c>
       <c r="I368" t="n">
-        <v>0.6578000000000001</v>
+        <v>0.6664</v>
       </c>
       <c r="J368" t="n">
-        <v>0.2744</v>
+        <v>0.2669</v>
       </c>
       <c r="K368" t="n">
-        <v>0.41</v>
+        <v>0.4004</v>
       </c>
       <c r="L368" t="n">
-        <v>0.3422</v>
+        <v>0.3336</v>
       </c>
       <c r="M368" t="n">
         <v>164</v>
@@ -20334,22 +20334,22 @@
         </is>
       </c>
       <c r="G369" t="n">
-        <v>0.3017</v>
+        <v>0.3175</v>
       </c>
       <c r="H369" t="n">
-        <v>0.2099</v>
+        <v>0.2194</v>
       </c>
       <c r="I369" t="n">
-        <v>0.2558</v>
+        <v>0.2684</v>
       </c>
       <c r="J369" t="n">
-        <v>0.6983</v>
+        <v>0.6825</v>
       </c>
       <c r="K369" t="n">
-        <v>0.7901</v>
+        <v>0.7806</v>
       </c>
       <c r="L369" t="n">
-        <v>0.7442</v>
+        <v>0.7316</v>
       </c>
       <c r="M369" t="n">
         <v>164</v>
@@ -20391,19 +20391,19 @@
         <v>0.2964</v>
       </c>
       <c r="H370" t="n">
-        <v>0.1775</v>
+        <v>0.175</v>
       </c>
       <c r="I370" t="n">
-        <v>0.237</v>
+        <v>0.2357</v>
       </c>
       <c r="J370" t="n">
         <v>0.7036</v>
       </c>
       <c r="K370" t="n">
-        <v>0.8225</v>
+        <v>0.825</v>
       </c>
       <c r="L370" t="n">
-        <v>0.763</v>
+        <v>0.7643</v>
       </c>
       <c r="M370" t="n">
         <v>164</v>
@@ -20874,22 +20874,22 @@
         </is>
       </c>
       <c r="G379" t="n">
-        <v>0.8475</v>
+        <v>0.8514</v>
       </c>
       <c r="H379" t="n">
         <v>0.7551</v>
       </c>
       <c r="I379" t="n">
-        <v>0.8013</v>
+        <v>0.8032</v>
       </c>
       <c r="J379" t="n">
-        <v>0.1525</v>
+        <v>0.1486</v>
       </c>
       <c r="K379" t="n">
         <v>0.2449</v>
       </c>
       <c r="L379" t="n">
-        <v>0.1987</v>
+        <v>0.1968</v>
       </c>
       <c r="M379" t="n">
         <v>164</v>
@@ -20982,22 +20982,22 @@
         </is>
       </c>
       <c r="G381" t="n">
-        <v>0.5135</v>
+        <v>0.4838</v>
       </c>
       <c r="H381" t="n">
-        <v>0.3318</v>
+        <v>0.3316</v>
       </c>
       <c r="I381" t="n">
-        <v>0.4226</v>
+        <v>0.4077</v>
       </c>
       <c r="J381" t="n">
-        <v>0.4865</v>
+        <v>0.5162</v>
       </c>
       <c r="K381" t="n">
-        <v>0.6682</v>
+        <v>0.6684</v>
       </c>
       <c r="L381" t="n">
-        <v>0.5774</v>
+        <v>0.5923</v>
       </c>
       <c r="M381" t="n">
         <v>164</v>
@@ -21522,22 +21522,22 @@
         </is>
       </c>
       <c r="G391" t="n">
-        <v>0.471</v>
+        <v>0.4594</v>
       </c>
       <c r="H391" t="n">
-        <v>0.3493</v>
+        <v>0.3171</v>
       </c>
       <c r="I391" t="n">
-        <v>0.4102</v>
+        <v>0.3882</v>
       </c>
       <c r="J391" t="n">
-        <v>0.529</v>
+        <v>0.5406</v>
       </c>
       <c r="K391" t="n">
-        <v>0.6506999999999999</v>
+        <v>0.6829</v>
       </c>
       <c r="L391" t="n">
-        <v>0.5898</v>
+        <v>0.6118</v>
       </c>
       <c r="M391" t="n">
         <v>164</v>
@@ -22008,22 +22008,22 @@
         </is>
       </c>
       <c r="G400" t="n">
-        <v>0.4405</v>
+        <v>0.4347</v>
       </c>
       <c r="H400" t="n">
-        <v>0.2798</v>
+        <v>0.2752</v>
       </c>
       <c r="I400" t="n">
-        <v>0.3601</v>
+        <v>0.355</v>
       </c>
       <c r="J400" t="n">
-        <v>0.5595</v>
+        <v>0.5653</v>
       </c>
       <c r="K400" t="n">
-        <v>0.7202</v>
+        <v>0.7248</v>
       </c>
       <c r="L400" t="n">
-        <v>0.6399</v>
+        <v>0.645</v>
       </c>
       <c r="M400" t="n">
         <v>164</v>
@@ -22440,22 +22440,22 @@
         </is>
       </c>
       <c r="G408" t="n">
-        <v>0.2348</v>
+        <v>0.2298</v>
       </c>
       <c r="H408" t="n">
-        <v>0.1346</v>
+        <v>0.1318</v>
       </c>
       <c r="I408" t="n">
-        <v>0.1847</v>
+        <v>0.1808</v>
       </c>
       <c r="J408" t="n">
-        <v>0.7652</v>
+        <v>0.7702</v>
       </c>
       <c r="K408" t="n">
-        <v>0.8653999999999999</v>
+        <v>0.8682</v>
       </c>
       <c r="L408" t="n">
-        <v>0.8153</v>
+        <v>0.8192</v>
       </c>
       <c r="M408" t="n">
         <v>164</v>
@@ -22818,22 +22818,22 @@
         </is>
       </c>
       <c r="G415" t="n">
-        <v>0.7343</v>
+        <v>0.7226</v>
       </c>
       <c r="H415" t="n">
-        <v>0.5957</v>
+        <v>0.5824</v>
       </c>
       <c r="I415" t="n">
-        <v>0.665</v>
+        <v>0.6525</v>
       </c>
       <c r="J415" t="n">
-        <v>0.2657</v>
+        <v>0.2774</v>
       </c>
       <c r="K415" t="n">
-        <v>0.4043</v>
+        <v>0.4176</v>
       </c>
       <c r="L415" t="n">
-        <v>0.335</v>
+        <v>0.3475</v>
       </c>
       <c r="M415" t="n">
         <v>164</v>
@@ -23142,22 +23142,22 @@
         </is>
       </c>
       <c r="G421" t="n">
-        <v>0.7534</v>
+        <v>0.7459</v>
       </c>
       <c r="H421" t="n">
-        <v>0.6343</v>
+        <v>0.6191</v>
       </c>
       <c r="I421" t="n">
-        <v>0.6938</v>
+        <v>0.6825</v>
       </c>
       <c r="J421" t="n">
-        <v>0.2466</v>
+        <v>0.2541</v>
       </c>
       <c r="K421" t="n">
-        <v>0.3657</v>
+        <v>0.3809</v>
       </c>
       <c r="L421" t="n">
-        <v>0.3062</v>
+        <v>0.3175</v>
       </c>
       <c r="M421" t="n">
         <v>164</v>
@@ -23412,22 +23412,22 @@
         </is>
       </c>
       <c r="G426" t="n">
-        <v>0.4991</v>
+        <v>0.4814</v>
       </c>
       <c r="H426" t="n">
-        <v>0.3611</v>
+        <v>0.3489</v>
       </c>
       <c r="I426" t="n">
-        <v>0.4301</v>
+        <v>0.4152</v>
       </c>
       <c r="J426" t="n">
-        <v>0.5009</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="K426" t="n">
-        <v>0.6389</v>
+        <v>0.6511</v>
       </c>
       <c r="L426" t="n">
-        <v>0.5699</v>
+        <v>0.5848</v>
       </c>
       <c r="M426" t="n">
         <v>164</v>
@@ -23628,22 +23628,22 @@
         </is>
       </c>
       <c r="G430" t="n">
-        <v>0.2713</v>
+        <v>0.2613</v>
       </c>
       <c r="H430" t="n">
-        <v>0.139</v>
+        <v>0.1323</v>
       </c>
       <c r="I430" t="n">
-        <v>0.2052</v>
+        <v>0.1968</v>
       </c>
       <c r="J430" t="n">
-        <v>0.7287</v>
+        <v>0.7387</v>
       </c>
       <c r="K430" t="n">
-        <v>0.861</v>
+        <v>0.8677</v>
       </c>
       <c r="L430" t="n">
-        <v>0.7948</v>
+        <v>0.8032</v>
       </c>
       <c r="M430" t="n">
         <v>164</v>
@@ -23736,22 +23736,22 @@
         </is>
       </c>
       <c r="G432" t="n">
-        <v>0.2767</v>
+        <v>0.2733</v>
       </c>
       <c r="H432" t="n">
         <v>0.1576</v>
       </c>
       <c r="I432" t="n">
-        <v>0.2172</v>
+        <v>0.2154</v>
       </c>
       <c r="J432" t="n">
-        <v>0.7233000000000001</v>
+        <v>0.7267</v>
       </c>
       <c r="K432" t="n">
         <v>0.8424</v>
       </c>
       <c r="L432" t="n">
-        <v>0.7828000000000001</v>
+        <v>0.7846</v>
       </c>
       <c r="M432" t="n">
         <v>164</v>
@@ -23790,22 +23790,22 @@
         </is>
       </c>
       <c r="G433" t="n">
-        <v>0.284</v>
+        <v>0.2741</v>
       </c>
       <c r="H433" t="n">
-        <v>0.1524</v>
+        <v>0.1409</v>
       </c>
       <c r="I433" t="n">
-        <v>0.2182</v>
+        <v>0.2075</v>
       </c>
       <c r="J433" t="n">
-        <v>0.716</v>
+        <v>0.7259</v>
       </c>
       <c r="K433" t="n">
-        <v>0.8476</v>
+        <v>0.8591</v>
       </c>
       <c r="L433" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.7925</v>
       </c>
       <c r="M433" t="n">
         <v>164</v>
@@ -23898,22 +23898,22 @@
         </is>
       </c>
       <c r="G435" t="n">
-        <v>0.2283</v>
+        <v>0.2191</v>
       </c>
       <c r="H435" t="n">
-        <v>0.1307</v>
+        <v>0.1302</v>
       </c>
       <c r="I435" t="n">
-        <v>0.1795</v>
+        <v>0.1746</v>
       </c>
       <c r="J435" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.7809</v>
       </c>
       <c r="K435" t="n">
-        <v>0.8693</v>
+        <v>0.8698</v>
       </c>
       <c r="L435" t="n">
-        <v>0.8205</v>
+        <v>0.8254</v>
       </c>
       <c r="M435" t="n">
         <v>164</v>
@@ -23952,22 +23952,22 @@
         </is>
       </c>
       <c r="G436" t="n">
-        <v>0.5849</v>
+        <v>0.5799</v>
       </c>
       <c r="H436" t="n">
-        <v>0.4543</v>
+        <v>0.4298</v>
       </c>
       <c r="I436" t="n">
-        <v>0.5196</v>
+        <v>0.5048</v>
       </c>
       <c r="J436" t="n">
-        <v>0.4151</v>
+        <v>0.4201</v>
       </c>
       <c r="K436" t="n">
-        <v>0.5457</v>
+        <v>0.5702</v>
       </c>
       <c r="L436" t="n">
-        <v>0.4804</v>
+        <v>0.4952</v>
       </c>
       <c r="M436" t="n">
         <v>164</v>

--- a/nba/public/data/nba_matchup_probs.xlsx
+++ b/nba/public/data/nba_matchup_probs.xlsx
@@ -1380,22 +1380,22 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.8126</v>
+        <v>0.8054</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6911</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7518</v>
+        <v>0.7447</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1874</v>
+        <v>0.1946</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3089</v>
+        <v>0.316</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2482</v>
+        <v>0.2553</v>
       </c>
       <c r="M18" t="n">
         <v>164</v>
@@ -1596,22 +1596,22 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.855</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="H22" t="n">
         <v>0.7255</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7902</v>
+        <v>0.791</v>
       </c>
       <c r="J22" t="n">
-        <v>0.145</v>
+        <v>0.1436</v>
       </c>
       <c r="K22" t="n">
         <v>0.2745</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2098</v>
+        <v>0.209</v>
       </c>
       <c r="M22" t="n">
         <v>164</v>
@@ -1974,22 +1974,22 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.5371</v>
+        <v>0.5436</v>
       </c>
       <c r="H29" t="n">
         <v>0.374</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4556</v>
+        <v>0.4588</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4629</v>
+        <v>0.4564</v>
       </c>
       <c r="K29" t="n">
         <v>0.626</v>
       </c>
       <c r="L29" t="n">
-        <v>0.5444</v>
+        <v>0.5412</v>
       </c>
       <c r="M29" t="n">
         <v>164</v>
@@ -2460,22 +2460,22 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.7467</v>
+        <v>0.7487</v>
       </c>
       <c r="H38" t="n">
         <v>0.5784</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6626</v>
+        <v>0.6636</v>
       </c>
       <c r="J38" t="n">
-        <v>0.2533</v>
+        <v>0.2513</v>
       </c>
       <c r="K38" t="n">
         <v>0.4216</v>
       </c>
       <c r="L38" t="n">
-        <v>0.3374</v>
+        <v>0.3364</v>
       </c>
       <c r="M38" t="n">
         <v>164</v>
@@ -2895,19 +2895,19 @@
         <v>0.8594000000000001</v>
       </c>
       <c r="H46" t="n">
-        <v>0.7529</v>
+        <v>0.7448</v>
       </c>
       <c r="I46" t="n">
-        <v>0.8062</v>
+        <v>0.8021</v>
       </c>
       <c r="J46" t="n">
         <v>0.1406</v>
       </c>
       <c r="K46" t="n">
-        <v>0.2471</v>
+        <v>0.2552</v>
       </c>
       <c r="L46" t="n">
-        <v>0.1938</v>
+        <v>0.1979</v>
       </c>
       <c r="M46" t="n">
         <v>164</v>
@@ -3540,22 +3540,22 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.6728</v>
+        <v>0.6763</v>
       </c>
       <c r="H58" t="n">
         <v>0.5187</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5958</v>
+        <v>0.5975</v>
       </c>
       <c r="J58" t="n">
-        <v>0.3272</v>
+        <v>0.3237</v>
       </c>
       <c r="K58" t="n">
         <v>0.4813</v>
       </c>
       <c r="L58" t="n">
-        <v>0.4042</v>
+        <v>0.4025</v>
       </c>
       <c r="M58" t="n">
         <v>164</v>
@@ -4350,22 +4350,22 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.8366</v>
+        <v>0.8316</v>
       </c>
       <c r="H73" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.7687</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8047</v>
+        <v>0.8002</v>
       </c>
       <c r="J73" t="n">
-        <v>0.1634</v>
+        <v>0.1684</v>
       </c>
       <c r="K73" t="n">
-        <v>0.2273</v>
+        <v>0.2313</v>
       </c>
       <c r="L73" t="n">
-        <v>0.1953</v>
+        <v>0.1998</v>
       </c>
       <c r="M73" t="n">
         <v>164</v>
@@ -4731,19 +4731,19 @@
         <v>0.7292999999999999</v>
       </c>
       <c r="H80" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.5784</v>
       </c>
       <c r="I80" t="n">
-        <v>0.6532</v>
+        <v>0.6538</v>
       </c>
       <c r="J80" t="n">
         <v>0.2707</v>
       </c>
       <c r="K80" t="n">
-        <v>0.4229</v>
+        <v>0.4216</v>
       </c>
       <c r="L80" t="n">
-        <v>0.3468</v>
+        <v>0.3462</v>
       </c>
       <c r="M80" t="n">
         <v>164</v>
@@ -5325,19 +5325,19 @@
         <v>0.3724</v>
       </c>
       <c r="H91" t="n">
-        <v>0.2339</v>
+        <v>0.2351</v>
       </c>
       <c r="I91" t="n">
-        <v>0.3032</v>
+        <v>0.3038</v>
       </c>
       <c r="J91" t="n">
         <v>0.6276</v>
       </c>
       <c r="K91" t="n">
-        <v>0.7661</v>
+        <v>0.7649</v>
       </c>
       <c r="L91" t="n">
-        <v>0.6968</v>
+        <v>0.6962</v>
       </c>
       <c r="M91" t="n">
         <v>164</v>
@@ -5754,22 +5754,22 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0.628</v>
+        <v>0.6092</v>
       </c>
       <c r="H99" t="n">
-        <v>0.4944</v>
+        <v>0.494</v>
       </c>
       <c r="I99" t="n">
-        <v>0.5612</v>
+        <v>0.5516</v>
       </c>
       <c r="J99" t="n">
-        <v>0.372</v>
+        <v>0.3908</v>
       </c>
       <c r="K99" t="n">
-        <v>0.5056</v>
+        <v>0.506</v>
       </c>
       <c r="L99" t="n">
-        <v>0.4388</v>
+        <v>0.4484</v>
       </c>
       <c r="M99" t="n">
         <v>164</v>
@@ -6675,19 +6675,19 @@
         <v>0.3665</v>
       </c>
       <c r="H116" t="n">
-        <v>0.2169</v>
+        <v>0.2151</v>
       </c>
       <c r="I116" t="n">
-        <v>0.2917</v>
+        <v>0.2908</v>
       </c>
       <c r="J116" t="n">
         <v>0.6335</v>
       </c>
       <c r="K116" t="n">
-        <v>0.7831</v>
+        <v>0.7849</v>
       </c>
       <c r="L116" t="n">
-        <v>0.7083</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="M116" t="n">
         <v>164</v>
@@ -6834,22 +6834,22 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0.6403</v>
+        <v>0.6412</v>
       </c>
       <c r="H119" t="n">
         <v>0.5203</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5803</v>
+        <v>0.5808</v>
       </c>
       <c r="J119" t="n">
-        <v>0.3597</v>
+        <v>0.3588</v>
       </c>
       <c r="K119" t="n">
         <v>0.4797</v>
       </c>
       <c r="L119" t="n">
-        <v>0.4197</v>
+        <v>0.4192</v>
       </c>
       <c r="M119" t="n">
         <v>164</v>
@@ -7104,22 +7104,22 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.6029</v>
+        <v>0.5775</v>
       </c>
       <c r="H124" t="n">
-        <v>0.4985</v>
+        <v>0.4866</v>
       </c>
       <c r="I124" t="n">
-        <v>0.5507</v>
+        <v>0.532</v>
       </c>
       <c r="J124" t="n">
-        <v>0.3971</v>
+        <v>0.4225</v>
       </c>
       <c r="K124" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.5134</v>
       </c>
       <c r="L124" t="n">
-        <v>0.4493</v>
+        <v>0.468</v>
       </c>
       <c r="M124" t="n">
         <v>164</v>
@@ -7374,22 +7374,22 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>0.2605</v>
+        <v>0.258</v>
       </c>
       <c r="H129" t="n">
         <v>0.1452</v>
       </c>
       <c r="I129" t="n">
-        <v>0.2028</v>
+        <v>0.2016</v>
       </c>
       <c r="J129" t="n">
-        <v>0.7395</v>
+        <v>0.742</v>
       </c>
       <c r="K129" t="n">
         <v>0.8548</v>
       </c>
       <c r="L129" t="n">
-        <v>0.7972</v>
+        <v>0.7984</v>
       </c>
       <c r="M129" t="n">
         <v>164</v>
@@ -8238,22 +8238,22 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>0.6925</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="H145" t="n">
         <v>0.5371</v>
       </c>
       <c r="I145" t="n">
-        <v>0.6148</v>
+        <v>0.6166</v>
       </c>
       <c r="J145" t="n">
-        <v>0.3075</v>
+        <v>0.3039</v>
       </c>
       <c r="K145" t="n">
         <v>0.4629</v>
       </c>
       <c r="L145" t="n">
-        <v>0.3852</v>
+        <v>0.3834</v>
       </c>
       <c r="M145" t="n">
         <v>164</v>
@@ -8400,22 +8400,22 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>0.5357</v>
+        <v>0.534</v>
       </c>
       <c r="H148" t="n">
-        <v>0.4429</v>
+        <v>0.4213</v>
       </c>
       <c r="I148" t="n">
-        <v>0.4893</v>
+        <v>0.4776</v>
       </c>
       <c r="J148" t="n">
-        <v>0.4643</v>
+        <v>0.466</v>
       </c>
       <c r="K148" t="n">
-        <v>0.5571</v>
+        <v>0.5787</v>
       </c>
       <c r="L148" t="n">
-        <v>0.5107</v>
+        <v>0.5224</v>
       </c>
       <c r="M148" t="n">
         <v>164</v>
@@ -8670,22 +8670,22 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>0.212</v>
+        <v>0.2095</v>
       </c>
       <c r="H153" t="n">
         <v>0.1302</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1711</v>
+        <v>0.1698</v>
       </c>
       <c r="J153" t="n">
-        <v>0.788</v>
+        <v>0.7905</v>
       </c>
       <c r="K153" t="n">
         <v>0.8698</v>
       </c>
       <c r="L153" t="n">
-        <v>0.8289</v>
+        <v>0.8302</v>
       </c>
       <c r="M153" t="n">
         <v>164</v>
@@ -9048,22 +9048,22 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>0.2837</v>
+        <v>0.2846</v>
       </c>
       <c r="H160" t="n">
         <v>0.1549</v>
       </c>
       <c r="I160" t="n">
-        <v>0.2193</v>
+        <v>0.2198</v>
       </c>
       <c r="J160" t="n">
-        <v>0.7163</v>
+        <v>0.7154</v>
       </c>
       <c r="K160" t="n">
         <v>0.8451</v>
       </c>
       <c r="L160" t="n">
-        <v>0.7806999999999999</v>
+        <v>0.7802</v>
       </c>
       <c r="M160" t="n">
         <v>164</v>
@@ -9159,19 +9159,19 @@
         <v>0.6634</v>
       </c>
       <c r="H162" t="n">
-        <v>0.502</v>
+        <v>0.504</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5827</v>
+        <v>0.5837</v>
       </c>
       <c r="J162" t="n">
         <v>0.3366</v>
       </c>
       <c r="K162" t="n">
-        <v>0.498</v>
+        <v>0.496</v>
       </c>
       <c r="L162" t="n">
-        <v>0.4173</v>
+        <v>0.4163</v>
       </c>
       <c r="M162" t="n">
         <v>164</v>
@@ -9267,19 +9267,19 @@
         <v>0.7020999999999999</v>
       </c>
       <c r="H164" t="n">
-        <v>0.5484</v>
+        <v>0.5556</v>
       </c>
       <c r="I164" t="n">
-        <v>0.6252</v>
+        <v>0.6288</v>
       </c>
       <c r="J164" t="n">
         <v>0.2979</v>
       </c>
       <c r="K164" t="n">
-        <v>0.4516</v>
+        <v>0.4444</v>
       </c>
       <c r="L164" t="n">
-        <v>0.3748</v>
+        <v>0.3712</v>
       </c>
       <c r="M164" t="n">
         <v>164</v>
@@ -9642,22 +9642,22 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>0.8478</v>
+        <v>0.839</v>
       </c>
       <c r="H171" t="n">
         <v>0.7421</v>
       </c>
       <c r="I171" t="n">
-        <v>0.795</v>
+        <v>0.7906</v>
       </c>
       <c r="J171" t="n">
-        <v>0.1522</v>
+        <v>0.161</v>
       </c>
       <c r="K171" t="n">
         <v>0.2579</v>
       </c>
       <c r="L171" t="n">
-        <v>0.205</v>
+        <v>0.2094</v>
       </c>
       <c r="M171" t="n">
         <v>164</v>
@@ -9753,19 +9753,19 @@
         <v>0.7376</v>
       </c>
       <c r="H173" t="n">
-        <v>0.589</v>
+        <v>0.5918</v>
       </c>
       <c r="I173" t="n">
-        <v>0.6633</v>
+        <v>0.6647</v>
       </c>
       <c r="J173" t="n">
         <v>0.2624</v>
       </c>
       <c r="K173" t="n">
-        <v>0.411</v>
+        <v>0.4082</v>
       </c>
       <c r="L173" t="n">
-        <v>0.3367</v>
+        <v>0.3353</v>
       </c>
       <c r="M173" t="n">
         <v>164</v>
@@ -10830,22 +10830,22 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>0.7194</v>
+        <v>0.7038</v>
       </c>
       <c r="H193" t="n">
-        <v>0.5537</v>
+        <v>0.552</v>
       </c>
       <c r="I193" t="n">
-        <v>0.6365</v>
+        <v>0.6279</v>
       </c>
       <c r="J193" t="n">
-        <v>0.2806</v>
+        <v>0.2962</v>
       </c>
       <c r="K193" t="n">
-        <v>0.4463</v>
+        <v>0.448</v>
       </c>
       <c r="L193" t="n">
-        <v>0.3635</v>
+        <v>0.3721</v>
       </c>
       <c r="M193" t="n">
         <v>164</v>
@@ -11964,22 +11964,22 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>0.8202</v>
+        <v>0.8174</v>
       </c>
       <c r="H214" t="n">
-        <v>0.7106</v>
+        <v>0.7056</v>
       </c>
       <c r="I214" t="n">
-        <v>0.7654</v>
+        <v>0.7615</v>
       </c>
       <c r="J214" t="n">
-        <v>0.1798</v>
+        <v>0.1826</v>
       </c>
       <c r="K214" t="n">
-        <v>0.2894</v>
+        <v>0.2944</v>
       </c>
       <c r="L214" t="n">
-        <v>0.2346</v>
+        <v>0.2385</v>
       </c>
       <c r="M214" t="n">
         <v>164</v>
@@ -12180,22 +12180,22 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>0.8622</v>
+        <v>0.8658</v>
       </c>
       <c r="H218" t="n">
         <v>0.7665</v>
       </c>
       <c r="I218" t="n">
-        <v>0.8143</v>
+        <v>0.8161</v>
       </c>
       <c r="J218" t="n">
-        <v>0.1378</v>
+        <v>0.1342</v>
       </c>
       <c r="K218" t="n">
         <v>0.2335</v>
       </c>
       <c r="L218" t="n">
-        <v>0.1857</v>
+        <v>0.1839</v>
       </c>
       <c r="M218" t="n">
         <v>164</v>
@@ -13044,22 +13044,22 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7989000000000001</v>
       </c>
       <c r="H234" t="n">
-        <v>0.6815</v>
+        <v>0.6733</v>
       </c>
       <c r="I234" t="n">
-        <v>0.7458</v>
+        <v>0.7361</v>
       </c>
       <c r="J234" t="n">
-        <v>0.19</v>
+        <v>0.2011</v>
       </c>
       <c r="K234" t="n">
-        <v>0.3185</v>
+        <v>0.3267</v>
       </c>
       <c r="L234" t="n">
-        <v>0.2542</v>
+        <v>0.2639</v>
       </c>
       <c r="M234" t="n">
         <v>164</v>
@@ -13209,19 +13209,19 @@
         <v>0.6973</v>
       </c>
       <c r="H237" t="n">
-        <v>0.486</v>
+        <v>0.4927</v>
       </c>
       <c r="I237" t="n">
-        <v>0.5916</v>
+        <v>0.595</v>
       </c>
       <c r="J237" t="n">
         <v>0.3027</v>
       </c>
       <c r="K237" t="n">
-        <v>0.514</v>
+        <v>0.5073</v>
       </c>
       <c r="L237" t="n">
-        <v>0.4084</v>
+        <v>0.405</v>
       </c>
       <c r="M237" t="n">
         <v>164</v>
@@ -14070,22 +14070,22 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>0.8001</v>
+        <v>0.7973</v>
       </c>
       <c r="H253" t="n">
-        <v>0.6839</v>
+        <v>0.6798</v>
       </c>
       <c r="I253" t="n">
-        <v>0.742</v>
+        <v>0.7386</v>
       </c>
       <c r="J253" t="n">
-        <v>0.1999</v>
+        <v>0.2027</v>
       </c>
       <c r="K253" t="n">
-        <v>0.3161</v>
+        <v>0.3202</v>
       </c>
       <c r="L253" t="n">
-        <v>0.258</v>
+        <v>0.2614</v>
       </c>
       <c r="M253" t="n">
         <v>164</v>
@@ -15042,22 +15042,22 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>0.7316</v>
+        <v>0.7237</v>
       </c>
       <c r="H271" t="n">
-        <v>0.5878</v>
+        <v>0.5765</v>
       </c>
       <c r="I271" t="n">
-        <v>0.6597</v>
+        <v>0.6501</v>
       </c>
       <c r="J271" t="n">
-        <v>0.2684</v>
+        <v>0.2763</v>
       </c>
       <c r="K271" t="n">
-        <v>0.4122</v>
+        <v>0.4235</v>
       </c>
       <c r="L271" t="n">
-        <v>0.3403</v>
+        <v>0.3499</v>
       </c>
       <c r="M271" t="n">
         <v>164</v>
@@ -15528,22 +15528,22 @@
         </is>
       </c>
       <c r="G280" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="H280" t="n">
         <v>0.6594</v>
       </c>
       <c r="I280" t="n">
-        <v>0.7272</v>
+        <v>0.7276</v>
       </c>
       <c r="J280" t="n">
-        <v>0.2051</v>
+        <v>0.2041</v>
       </c>
       <c r="K280" t="n">
         <v>0.3406</v>
       </c>
       <c r="L280" t="n">
-        <v>0.2728</v>
+        <v>0.2724</v>
       </c>
       <c r="M280" t="n">
         <v>164</v>
@@ -15960,22 +15960,22 @@
         </is>
       </c>
       <c r="G288" t="n">
-        <v>0.5349</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="H288" t="n">
-        <v>0.36</v>
+        <v>0.3549</v>
       </c>
       <c r="I288" t="n">
-        <v>0.4474</v>
+        <v>0.4378</v>
       </c>
       <c r="J288" t="n">
-        <v>0.4651</v>
+        <v>0.4793</v>
       </c>
       <c r="K288" t="n">
-        <v>0.64</v>
+        <v>0.6451</v>
       </c>
       <c r="L288" t="n">
-        <v>0.5526</v>
+        <v>0.5622</v>
       </c>
       <c r="M288" t="n">
         <v>164</v>
@@ -16824,22 +16824,22 @@
         </is>
       </c>
       <c r="G304" t="n">
-        <v>0.8196</v>
+        <v>0.8162</v>
       </c>
       <c r="H304" t="n">
-        <v>0.6956</v>
+        <v>0.6911</v>
       </c>
       <c r="I304" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.7536</v>
       </c>
       <c r="J304" t="n">
-        <v>0.1804</v>
+        <v>0.1838</v>
       </c>
       <c r="K304" t="n">
-        <v>0.3044</v>
+        <v>0.3089</v>
       </c>
       <c r="L304" t="n">
-        <v>0.2424</v>
+        <v>0.2464</v>
       </c>
       <c r="M304" t="n">
         <v>164</v>
@@ -17367,19 +17367,19 @@
         <v>0.8764999999999999</v>
       </c>
       <c r="H314" t="n">
-        <v>0.7781</v>
+        <v>0.7813</v>
       </c>
       <c r="I314" t="n">
-        <v>0.8273</v>
+        <v>0.8289</v>
       </c>
       <c r="J314" t="n">
         <v>0.1235</v>
       </c>
       <c r="K314" t="n">
-        <v>0.2219</v>
+        <v>0.2187</v>
       </c>
       <c r="L314" t="n">
-        <v>0.1727</v>
+        <v>0.1711</v>
       </c>
       <c r="M314" t="n">
         <v>164</v>
@@ -17526,22 +17526,22 @@
         </is>
       </c>
       <c r="G317" t="n">
-        <v>0.1943</v>
+        <v>0.1859</v>
       </c>
       <c r="H317" t="n">
         <v>0.1404</v>
       </c>
       <c r="I317" t="n">
-        <v>0.1674</v>
+        <v>0.1632</v>
       </c>
       <c r="J317" t="n">
-        <v>0.8057</v>
+        <v>0.8141</v>
       </c>
       <c r="K317" t="n">
         <v>0.8596</v>
       </c>
       <c r="L317" t="n">
-        <v>0.8326</v>
+        <v>0.8368</v>
       </c>
       <c r="M317" t="n">
         <v>164</v>
@@ -17634,22 +17634,22 @@
         </is>
       </c>
       <c r="G319" t="n">
-        <v>0.4548</v>
+        <v>0.4376</v>
       </c>
       <c r="H319" t="n">
-        <v>0.2862</v>
+        <v>0.2833</v>
       </c>
       <c r="I319" t="n">
-        <v>0.3705</v>
+        <v>0.3604</v>
       </c>
       <c r="J319" t="n">
-        <v>0.5452</v>
+        <v>0.5624</v>
       </c>
       <c r="K319" t="n">
-        <v>0.7138</v>
+        <v>0.7167</v>
       </c>
       <c r="L319" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="M319" t="n">
         <v>164</v>
@@ -18015,19 +18015,19 @@
         <v>0.2502</v>
       </c>
       <c r="H326" t="n">
-        <v>0.1634</v>
+        <v>0.1585</v>
       </c>
       <c r="I326" t="n">
-        <v>0.2068</v>
+        <v>0.2043</v>
       </c>
       <c r="J326" t="n">
         <v>0.7498</v>
       </c>
       <c r="K326" t="n">
-        <v>0.8366</v>
+        <v>0.8415</v>
       </c>
       <c r="L326" t="n">
-        <v>0.7932</v>
+        <v>0.7957</v>
       </c>
       <c r="M326" t="n">
         <v>164</v>
@@ -18390,22 +18390,22 @@
         </is>
       </c>
       <c r="G333" t="n">
-        <v>0.8288</v>
+        <v>0.8225</v>
       </c>
       <c r="H333" t="n">
-        <v>0.7335</v>
+        <v>0.7298</v>
       </c>
       <c r="I333" t="n">
-        <v>0.7812</v>
+        <v>0.7762</v>
       </c>
       <c r="J333" t="n">
-        <v>0.1712</v>
+        <v>0.1775</v>
       </c>
       <c r="K333" t="n">
-        <v>0.2665</v>
+        <v>0.2702</v>
       </c>
       <c r="L333" t="n">
-        <v>0.2188</v>
+        <v>0.2238</v>
       </c>
       <c r="M333" t="n">
         <v>164</v>
@@ -19092,22 +19092,22 @@
         </is>
       </c>
       <c r="G346" t="n">
-        <v>0.7181999999999999</v>
+        <v>0.7175</v>
       </c>
       <c r="H346" t="n">
         <v>0.5491</v>
       </c>
       <c r="I346" t="n">
-        <v>0.6337</v>
+        <v>0.6333</v>
       </c>
       <c r="J346" t="n">
-        <v>0.2818</v>
+        <v>0.2825</v>
       </c>
       <c r="K346" t="n">
         <v>0.4509</v>
       </c>
       <c r="L346" t="n">
-        <v>0.3663</v>
+        <v>0.3667</v>
       </c>
       <c r="M346" t="n">
         <v>164</v>
@@ -19794,22 +19794,22 @@
         </is>
       </c>
       <c r="G359" t="n">
-        <v>0.3785</v>
+        <v>0.3908</v>
       </c>
       <c r="H359" t="n">
-        <v>0.2258</v>
+        <v>0.2283</v>
       </c>
       <c r="I359" t="n">
-        <v>0.3022</v>
+        <v>0.3096</v>
       </c>
       <c r="J359" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.6092</v>
       </c>
       <c r="K359" t="n">
-        <v>0.7742</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="L359" t="n">
-        <v>0.6978</v>
+        <v>0.6904</v>
       </c>
       <c r="M359" t="n">
         <v>164</v>
@@ -19848,22 +19848,22 @@
         </is>
       </c>
       <c r="G360" t="n">
-        <v>0.3739</v>
+        <v>0.385</v>
       </c>
       <c r="H360" t="n">
-        <v>0.2491</v>
+        <v>0.2488</v>
       </c>
       <c r="I360" t="n">
-        <v>0.3115</v>
+        <v>0.3169</v>
       </c>
       <c r="J360" t="n">
-        <v>0.6261</v>
+        <v>0.615</v>
       </c>
       <c r="K360" t="n">
-        <v>0.7509</v>
+        <v>0.7512</v>
       </c>
       <c r="L360" t="n">
-        <v>0.6885</v>
+        <v>0.6831</v>
       </c>
       <c r="M360" t="n">
         <v>164</v>
@@ -19902,22 +19902,22 @@
         </is>
       </c>
       <c r="G361" t="n">
-        <v>0.4182</v>
+        <v>0.4186</v>
       </c>
       <c r="H361" t="n">
-        <v>0.2808</v>
+        <v>0.2946</v>
       </c>
       <c r="I361" t="n">
-        <v>0.3495</v>
+        <v>0.3566</v>
       </c>
       <c r="J361" t="n">
-        <v>0.5818</v>
+        <v>0.5814</v>
       </c>
       <c r="K361" t="n">
-        <v>0.7192</v>
+        <v>0.7054</v>
       </c>
       <c r="L361" t="n">
-        <v>0.6505</v>
+        <v>0.6434</v>
       </c>
       <c r="M361" t="n">
         <v>164</v>
@@ -19956,22 +19956,22 @@
         </is>
       </c>
       <c r="G362" t="n">
-        <v>0.6793</v>
+        <v>0.6915</v>
       </c>
       <c r="H362" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.5786</v>
       </c>
       <c r="I362" t="n">
-        <v>0.6247</v>
+        <v>0.635</v>
       </c>
       <c r="J362" t="n">
-        <v>0.3207</v>
+        <v>0.3085</v>
       </c>
       <c r="K362" t="n">
-        <v>0.4299</v>
+        <v>0.4214</v>
       </c>
       <c r="L362" t="n">
-        <v>0.3753</v>
+        <v>0.365</v>
       </c>
       <c r="M362" t="n">
         <v>164</v>
@@ -20010,22 +20010,22 @@
         </is>
       </c>
       <c r="G363" t="n">
-        <v>0.2611</v>
+        <v>0.2669</v>
       </c>
       <c r="H363" t="n">
-        <v>0.1414</v>
+        <v>0.147</v>
       </c>
       <c r="I363" t="n">
-        <v>0.2012</v>
+        <v>0.207</v>
       </c>
       <c r="J363" t="n">
-        <v>0.7389</v>
+        <v>0.7331</v>
       </c>
       <c r="K363" t="n">
-        <v>0.8586</v>
+        <v>0.853</v>
       </c>
       <c r="L363" t="n">
-        <v>0.7988</v>
+        <v>0.793</v>
       </c>
       <c r="M363" t="n">
         <v>164</v>
@@ -20067,19 +20067,19 @@
         <v>0.2557</v>
       </c>
       <c r="H364" t="n">
-        <v>0.134</v>
+        <v>0.1363</v>
       </c>
       <c r="I364" t="n">
-        <v>0.1948</v>
+        <v>0.196</v>
       </c>
       <c r="J364" t="n">
         <v>0.7443</v>
       </c>
       <c r="K364" t="n">
-        <v>0.866</v>
+        <v>0.8637</v>
       </c>
       <c r="L364" t="n">
-        <v>0.8052</v>
+        <v>0.804</v>
       </c>
       <c r="M364" t="n">
         <v>164</v>
@@ -20118,22 +20118,22 @@
         </is>
       </c>
       <c r="G365" t="n">
-        <v>0.3506</v>
+        <v>0.3622</v>
       </c>
       <c r="H365" t="n">
-        <v>0.2243</v>
+        <v>0.231</v>
       </c>
       <c r="I365" t="n">
-        <v>0.2874</v>
+        <v>0.2966</v>
       </c>
       <c r="J365" t="n">
-        <v>0.6494</v>
+        <v>0.6378</v>
       </c>
       <c r="K365" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.769</v>
       </c>
       <c r="L365" t="n">
-        <v>0.7126</v>
+        <v>0.7034</v>
       </c>
       <c r="M365" t="n">
         <v>164</v>
@@ -20172,22 +20172,22 @@
         </is>
       </c>
       <c r="G366" t="n">
-        <v>0.6505</v>
+        <v>0.6539</v>
       </c>
       <c r="H366" t="n">
-        <v>0.5423</v>
+        <v>0.5613</v>
       </c>
       <c r="I366" t="n">
-        <v>0.5964</v>
+        <v>0.6076</v>
       </c>
       <c r="J366" t="n">
-        <v>0.3495</v>
+        <v>0.3461</v>
       </c>
       <c r="K366" t="n">
-        <v>0.4577</v>
+        <v>0.4387</v>
       </c>
       <c r="L366" t="n">
-        <v>0.4036</v>
+        <v>0.3924</v>
       </c>
       <c r="M366" t="n">
         <v>164</v>
@@ -20226,22 +20226,22 @@
         </is>
       </c>
       <c r="G367" t="n">
-        <v>0.622</v>
+        <v>0.6437</v>
       </c>
       <c r="H367" t="n">
         <v>0.4968</v>
       </c>
       <c r="I367" t="n">
-        <v>0.5594</v>
+        <v>0.5702</v>
       </c>
       <c r="J367" t="n">
-        <v>0.378</v>
+        <v>0.3563</v>
       </c>
       <c r="K367" t="n">
         <v>0.5032</v>
       </c>
       <c r="L367" t="n">
-        <v>0.4406</v>
+        <v>0.4298</v>
       </c>
       <c r="M367" t="n">
         <v>164</v>
@@ -20280,22 +20280,22 @@
         </is>
       </c>
       <c r="G368" t="n">
-        <v>0.7331</v>
+        <v>0.7389</v>
       </c>
       <c r="H368" t="n">
-        <v>0.5996</v>
+        <v>0.6076</v>
       </c>
       <c r="I368" t="n">
-        <v>0.6664</v>
+        <v>0.6732</v>
       </c>
       <c r="J368" t="n">
-        <v>0.2669</v>
+        <v>0.2611</v>
       </c>
       <c r="K368" t="n">
-        <v>0.4004</v>
+        <v>0.3924</v>
       </c>
       <c r="L368" t="n">
-        <v>0.3336</v>
+        <v>0.3268</v>
       </c>
       <c r="M368" t="n">
         <v>164</v>
@@ -20334,22 +20334,22 @@
         </is>
       </c>
       <c r="G369" t="n">
-        <v>0.3175</v>
+        <v>0.3179</v>
       </c>
       <c r="H369" t="n">
-        <v>0.2194</v>
+        <v>0.2281</v>
       </c>
       <c r="I369" t="n">
-        <v>0.2684</v>
+        <v>0.273</v>
       </c>
       <c r="J369" t="n">
-        <v>0.6825</v>
+        <v>0.6821</v>
       </c>
       <c r="K369" t="n">
-        <v>0.7806</v>
+        <v>0.7719</v>
       </c>
       <c r="L369" t="n">
-        <v>0.7316</v>
+        <v>0.727</v>
       </c>
       <c r="M369" t="n">
         <v>164</v>
@@ -20388,22 +20388,22 @@
         </is>
       </c>
       <c r="G370" t="n">
-        <v>0.2964</v>
+        <v>0.3026</v>
       </c>
       <c r="H370" t="n">
-        <v>0.175</v>
+        <v>0.1825</v>
       </c>
       <c r="I370" t="n">
-        <v>0.2357</v>
+        <v>0.2426</v>
       </c>
       <c r="J370" t="n">
-        <v>0.7036</v>
+        <v>0.6974</v>
       </c>
       <c r="K370" t="n">
-        <v>0.825</v>
+        <v>0.8175</v>
       </c>
       <c r="L370" t="n">
-        <v>0.7643</v>
+        <v>0.7574</v>
       </c>
       <c r="M370" t="n">
         <v>164</v>
@@ -20496,22 +20496,22 @@
         </is>
       </c>
       <c r="G372" t="n">
-        <v>0.6051</v>
+        <v>0.6149</v>
       </c>
       <c r="H372" t="n">
         <v>0.459</v>
       </c>
       <c r="I372" t="n">
-        <v>0.532</v>
+        <v>0.537</v>
       </c>
       <c r="J372" t="n">
-        <v>0.3949</v>
+        <v>0.3851</v>
       </c>
       <c r="K372" t="n">
         <v>0.541</v>
       </c>
       <c r="L372" t="n">
-        <v>0.468</v>
+        <v>0.463</v>
       </c>
       <c r="M372" t="n">
         <v>164</v>
@@ -21360,22 +21360,22 @@
         </is>
       </c>
       <c r="G388" t="n">
-        <v>0.8222</v>
+        <v>0.8235</v>
       </c>
       <c r="H388" t="n">
         <v>0.6567</v>
       </c>
       <c r="I388" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.7401</v>
       </c>
       <c r="J388" t="n">
-        <v>0.1778</v>
+        <v>0.1765</v>
       </c>
       <c r="K388" t="n">
         <v>0.3433</v>
       </c>
       <c r="L388" t="n">
-        <v>0.2606</v>
+        <v>0.2599</v>
       </c>
       <c r="M388" t="n">
         <v>164</v>
@@ -22389,19 +22389,19 @@
         <v>0.2736</v>
       </c>
       <c r="H407" t="n">
-        <v>0.1519</v>
+        <v>0.151</v>
       </c>
       <c r="I407" t="n">
-        <v>0.2128</v>
+        <v>0.2123</v>
       </c>
       <c r="J407" t="n">
         <v>0.7264</v>
       </c>
       <c r="K407" t="n">
-        <v>0.8481</v>
+        <v>0.849</v>
       </c>
       <c r="L407" t="n">
-        <v>0.7872</v>
+        <v>0.7877</v>
       </c>
       <c r="M407" t="n">
         <v>164</v>
@@ -23577,19 +23577,19 @@
         <v>0.2905</v>
       </c>
       <c r="H429" t="n">
-        <v>0.167</v>
+        <v>0.165</v>
       </c>
       <c r="I429" t="n">
-        <v>0.2288</v>
+        <v>0.2278</v>
       </c>
       <c r="J429" t="n">
         <v>0.7095</v>
       </c>
       <c r="K429" t="n">
-        <v>0.833</v>
+        <v>0.835</v>
       </c>
       <c r="L429" t="n">
-        <v>0.7712</v>
+        <v>0.7722</v>
       </c>
       <c r="M429" t="n">
         <v>164</v>

--- a/nba/public/data/nba_matchup_probs.xlsx
+++ b/nba/public/data/nba_matchup_probs.xlsx
@@ -710,19 +710,19 @@
         <v>0.4679</v>
       </c>
       <c r="H3">
-        <v>0.2987</v>
+        <v>0.3025</v>
       </c>
       <c r="I3">
-        <v>0.3833</v>
+        <v>0.3852</v>
       </c>
       <c r="J3">
         <v>0.5321</v>
       </c>
       <c r="K3">
-        <v>0.7013</v>
+        <v>0.6975</v>
       </c>
       <c r="L3">
-        <v>0.6167</v>
+        <v>0.6148</v>
       </c>
       <c r="M3">
         <v>168</v>
@@ -751,22 +751,22 @@
         <v>46</v>
       </c>
       <c r="G4">
-        <v>0.8154</v>
+        <v>0.8166</v>
       </c>
       <c r="H4">
-        <v>0.673</v>
+        <v>0.6751</v>
       </c>
       <c r="I4">
-        <v>0.7442</v>
+        <v>0.7458</v>
       </c>
       <c r="J4">
-        <v>0.1846</v>
+        <v>0.1834</v>
       </c>
       <c r="K4">
-        <v>0.327</v>
+        <v>0.3249</v>
       </c>
       <c r="L4">
-        <v>0.2558</v>
+        <v>0.2542</v>
       </c>
       <c r="M4">
         <v>168</v>
@@ -795,22 +795,22 @@
         <v>47</v>
       </c>
       <c r="G5">
-        <v>0.8414</v>
+        <v>0.8381999999999999</v>
       </c>
       <c r="H5">
-        <v>0.7028</v>
+        <v>0.6969</v>
       </c>
       <c r="I5">
-        <v>0.7721</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="J5">
-        <v>0.1586</v>
+        <v>0.1618</v>
       </c>
       <c r="K5">
-        <v>0.2972</v>
+        <v>0.3031</v>
       </c>
       <c r="L5">
-        <v>0.2279</v>
+        <v>0.2324</v>
       </c>
       <c r="M5">
         <v>168</v>
@@ -839,22 +839,22 @@
         <v>48</v>
       </c>
       <c r="G6">
-        <v>0.8204</v>
+        <v>0.8162</v>
       </c>
       <c r="H6">
-        <v>0.6879</v>
+        <v>0.6837</v>
       </c>
       <c r="I6">
-        <v>0.7542</v>
+        <v>0.75</v>
       </c>
       <c r="J6">
-        <v>0.1796</v>
+        <v>0.1838</v>
       </c>
       <c r="K6">
-        <v>0.3121</v>
+        <v>0.3163</v>
       </c>
       <c r="L6">
-        <v>0.2458</v>
+        <v>0.25</v>
       </c>
       <c r="M6">
         <v>168</v>
@@ -883,22 +883,22 @@
         <v>49</v>
       </c>
       <c r="G7">
-        <v>0.5984</v>
+        <v>0.4578</v>
       </c>
       <c r="H7">
-        <v>0.427</v>
+        <v>0.3217</v>
       </c>
       <c r="I7">
-        <v>0.5127</v>
+        <v>0.3898</v>
       </c>
       <c r="J7">
-        <v>0.4016</v>
+        <v>0.5422</v>
       </c>
       <c r="K7">
-        <v>0.573</v>
+        <v>0.6783</v>
       </c>
       <c r="L7">
-        <v>0.4873</v>
+        <v>0.6102</v>
       </c>
       <c r="M7">
         <v>168</v>
@@ -1015,22 +1015,22 @@
         <v>52</v>
       </c>
       <c r="G10">
-        <v>0.6085</v>
+        <v>0.6036</v>
       </c>
       <c r="H10">
         <v>0.4615</v>
       </c>
       <c r="I10">
-        <v>0.535</v>
+        <v>0.5326</v>
       </c>
       <c r="J10">
-        <v>0.3915</v>
+        <v>0.3964</v>
       </c>
       <c r="K10">
         <v>0.5385</v>
       </c>
       <c r="L10">
-        <v>0.465</v>
+        <v>0.4674</v>
       </c>
       <c r="M10">
         <v>168</v>
@@ -1059,22 +1059,22 @@
         <v>53</v>
       </c>
       <c r="G11">
-        <v>0.7000999999999999</v>
+        <v>0.6952</v>
       </c>
       <c r="H11">
-        <v>0.5457</v>
+        <v>0.5409</v>
       </c>
       <c r="I11">
-        <v>0.6229</v>
+        <v>0.618</v>
       </c>
       <c r="J11">
-        <v>0.2999</v>
+        <v>0.3048</v>
       </c>
       <c r="K11">
-        <v>0.4543</v>
+        <v>0.4591</v>
       </c>
       <c r="L11">
-        <v>0.3771</v>
+        <v>0.382</v>
       </c>
       <c r="M11">
         <v>168</v>
@@ -1103,22 +1103,22 @@
         <v>54</v>
       </c>
       <c r="G12">
-        <v>0.6649</v>
+        <v>0.6639</v>
       </c>
       <c r="H12">
         <v>0.4953</v>
       </c>
       <c r="I12">
-        <v>0.5800999999999999</v>
+        <v>0.5796</v>
       </c>
       <c r="J12">
-        <v>0.3351</v>
+        <v>0.3361</v>
       </c>
       <c r="K12">
         <v>0.5047</v>
       </c>
       <c r="L12">
-        <v>0.4199</v>
+        <v>0.4204</v>
       </c>
       <c r="M12">
         <v>168</v>
@@ -1150,19 +1150,19 @@
         <v>0.8457</v>
       </c>
       <c r="H13">
-        <v>0.6937</v>
+        <v>0.6819</v>
       </c>
       <c r="I13">
-        <v>0.7697000000000001</v>
+        <v>0.7638</v>
       </c>
       <c r="J13">
         <v>0.1543</v>
       </c>
       <c r="K13">
-        <v>0.3063</v>
+        <v>0.3181</v>
       </c>
       <c r="L13">
-        <v>0.2303</v>
+        <v>0.2362</v>
       </c>
       <c r="M13">
         <v>168</v>
@@ -1191,22 +1191,22 @@
         <v>56</v>
       </c>
       <c r="G14">
-        <v>0.6047</v>
+        <v>0.6022</v>
       </c>
       <c r="H14">
         <v>0.457</v>
       </c>
       <c r="I14">
-        <v>0.5308</v>
+        <v>0.5296</v>
       </c>
       <c r="J14">
-        <v>0.3953</v>
+        <v>0.3978</v>
       </c>
       <c r="K14">
         <v>0.543</v>
       </c>
       <c r="L14">
-        <v>0.4692</v>
+        <v>0.4704</v>
       </c>
       <c r="M14">
         <v>168</v>
@@ -1238,19 +1238,19 @@
         <v>0.8745000000000001</v>
       </c>
       <c r="H15">
-        <v>0.7659</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="I15">
-        <v>0.8202</v>
+        <v>0.8186</v>
       </c>
       <c r="J15">
         <v>0.1255</v>
       </c>
       <c r="K15">
-        <v>0.2341</v>
+        <v>0.2374</v>
       </c>
       <c r="L15">
-        <v>0.1798</v>
+        <v>0.1814</v>
       </c>
       <c r="M15">
         <v>168</v>
@@ -1279,22 +1279,22 @@
         <v>58</v>
       </c>
       <c r="G16">
-        <v>0.4758</v>
+        <v>0.4776</v>
       </c>
       <c r="H16">
-        <v>0.308</v>
+        <v>0.3194</v>
       </c>
       <c r="I16">
-        <v>0.3919</v>
+        <v>0.3985</v>
       </c>
       <c r="J16">
-        <v>0.5242</v>
+        <v>0.5224</v>
       </c>
       <c r="K16">
-        <v>0.6919999999999999</v>
+        <v>0.6806</v>
       </c>
       <c r="L16">
-        <v>0.6081</v>
+        <v>0.6015</v>
       </c>
       <c r="M16">
         <v>168</v>
@@ -1323,22 +1323,22 @@
         <v>59</v>
       </c>
       <c r="G17">
-        <v>0.7076</v>
+        <v>0.696</v>
       </c>
       <c r="H17">
         <v>0.5518</v>
       </c>
       <c r="I17">
-        <v>0.6297</v>
+        <v>0.6239</v>
       </c>
       <c r="J17">
-        <v>0.2924</v>
+        <v>0.304</v>
       </c>
       <c r="K17">
         <v>0.4482</v>
       </c>
       <c r="L17">
-        <v>0.3703</v>
+        <v>0.3761</v>
       </c>
       <c r="M17">
         <v>168</v>
@@ -1367,22 +1367,22 @@
         <v>60</v>
       </c>
       <c r="G18">
-        <v>0.8318</v>
+        <v>0.825</v>
       </c>
       <c r="H18">
-        <v>0.7095</v>
+        <v>0.7055</v>
       </c>
       <c r="I18">
-        <v>0.7707000000000001</v>
+        <v>0.7652</v>
       </c>
       <c r="J18">
-        <v>0.1682</v>
+        <v>0.175</v>
       </c>
       <c r="K18">
-        <v>0.2905</v>
+        <v>0.2945</v>
       </c>
       <c r="L18">
-        <v>0.2293</v>
+        <v>0.2348</v>
       </c>
       <c r="M18">
         <v>168</v>
@@ -1499,22 +1499,22 @@
         <v>63</v>
       </c>
       <c r="G21">
-        <v>0.6744</v>
+        <v>0.6706</v>
       </c>
       <c r="H21">
         <v>0.533</v>
       </c>
       <c r="I21">
-        <v>0.6037</v>
+        <v>0.6018</v>
       </c>
       <c r="J21">
-        <v>0.3256</v>
+        <v>0.3294</v>
       </c>
       <c r="K21">
         <v>0.467</v>
       </c>
       <c r="L21">
-        <v>0.3963</v>
+        <v>0.3982</v>
       </c>
       <c r="M21">
         <v>168</v>
@@ -1543,22 +1543,22 @@
         <v>64</v>
       </c>
       <c r="G22">
-        <v>0.8652</v>
+        <v>0.8633999999999999</v>
       </c>
       <c r="H22">
-        <v>0.7532</v>
+        <v>0.7376</v>
       </c>
       <c r="I22">
-        <v>0.8092</v>
+        <v>0.8005</v>
       </c>
       <c r="J22">
-        <v>0.1348</v>
+        <v>0.1366</v>
       </c>
       <c r="K22">
-        <v>0.2468</v>
+        <v>0.2624</v>
       </c>
       <c r="L22">
-        <v>0.1908</v>
+        <v>0.1995</v>
       </c>
       <c r="M22">
         <v>168</v>
@@ -1587,22 +1587,22 @@
         <v>65</v>
       </c>
       <c r="G23">
-        <v>0.3951</v>
+        <v>0.3968</v>
       </c>
       <c r="H23">
         <v>0.2585</v>
       </c>
       <c r="I23">
-        <v>0.3268</v>
+        <v>0.3276</v>
       </c>
       <c r="J23">
-        <v>0.6049</v>
+        <v>0.6032</v>
       </c>
       <c r="K23">
         <v>0.7415</v>
       </c>
       <c r="L23">
-        <v>0.6732</v>
+        <v>0.6724</v>
       </c>
       <c r="M23">
         <v>168</v>
@@ -1634,19 +1634,19 @@
         <v>0.3541</v>
       </c>
       <c r="H24">
-        <v>0.2433</v>
+        <v>0.241</v>
       </c>
       <c r="I24">
-        <v>0.2987</v>
+        <v>0.2976</v>
       </c>
       <c r="J24">
         <v>0.6459</v>
       </c>
       <c r="K24">
-        <v>0.7567</v>
+        <v>0.759</v>
       </c>
       <c r="L24">
-        <v>0.7013</v>
+        <v>0.7024</v>
       </c>
       <c r="M24">
         <v>168</v>
@@ -1675,22 +1675,22 @@
         <v>67</v>
       </c>
       <c r="G25">
-        <v>0.6163</v>
+        <v>0.5901</v>
       </c>
       <c r="H25">
-        <v>0.4907</v>
+        <v>0.4817</v>
       </c>
       <c r="I25">
-        <v>0.5535</v>
+        <v>0.5359</v>
       </c>
       <c r="J25">
-        <v>0.3837</v>
+        <v>0.4099</v>
       </c>
       <c r="K25">
-        <v>0.5093</v>
+        <v>0.5183</v>
       </c>
       <c r="L25">
-        <v>0.4465</v>
+        <v>0.4641</v>
       </c>
       <c r="M25">
         <v>168</v>
@@ -1719,22 +1719,22 @@
         <v>68</v>
       </c>
       <c r="G26">
-        <v>0.8522999999999999</v>
+        <v>0.8437</v>
       </c>
       <c r="H26">
-        <v>0.7344000000000001</v>
+        <v>0.7199</v>
       </c>
       <c r="I26">
-        <v>0.7934</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="J26">
-        <v>0.1477</v>
+        <v>0.1563</v>
       </c>
       <c r="K26">
-        <v>0.2656</v>
+        <v>0.2801</v>
       </c>
       <c r="L26">
-        <v>0.2066</v>
+        <v>0.2182</v>
       </c>
       <c r="M26">
         <v>168</v>
@@ -1763,22 +1763,22 @@
         <v>69</v>
       </c>
       <c r="G27">
-        <v>0.8505</v>
+        <v>0.8499</v>
       </c>
       <c r="H27">
-        <v>0.7000999999999999</v>
+        <v>0.6942</v>
       </c>
       <c r="I27">
-        <v>0.7753</v>
+        <v>0.772</v>
       </c>
       <c r="J27">
-        <v>0.1495</v>
+        <v>0.1501</v>
       </c>
       <c r="K27">
-        <v>0.2999</v>
+        <v>0.3058</v>
       </c>
       <c r="L27">
-        <v>0.2247</v>
+        <v>0.228</v>
       </c>
       <c r="M27">
         <v>168</v>
@@ -1807,22 +1807,22 @@
         <v>70</v>
       </c>
       <c r="G28">
-        <v>0.8581</v>
+        <v>0.8576</v>
       </c>
       <c r="H28">
-        <v>0.7558</v>
+        <v>0.7531</v>
       </c>
       <c r="I28">
-        <v>0.8070000000000001</v>
+        <v>0.8054</v>
       </c>
       <c r="J28">
-        <v>0.1419</v>
+        <v>0.1424</v>
       </c>
       <c r="K28">
-        <v>0.2442</v>
+        <v>0.2469</v>
       </c>
       <c r="L28">
-        <v>0.193</v>
+        <v>0.1946</v>
       </c>
       <c r="M28">
         <v>168</v>
@@ -1851,22 +1851,22 @@
         <v>71</v>
       </c>
       <c r="G29">
-        <v>0.5202</v>
+        <v>0.5137</v>
       </c>
       <c r="H29">
         <v>0.3651</v>
       </c>
       <c r="I29">
-        <v>0.4426</v>
+        <v>0.4394</v>
       </c>
       <c r="J29">
-        <v>0.4798</v>
+        <v>0.4863</v>
       </c>
       <c r="K29">
         <v>0.6349</v>
       </c>
       <c r="L29">
-        <v>0.5574</v>
+        <v>0.5606</v>
       </c>
       <c r="M29">
         <v>168</v>
@@ -1895,22 +1895,22 @@
         <v>73</v>
       </c>
       <c r="G30">
-        <v>0.5131</v>
+        <v>0.5079</v>
       </c>
       <c r="H30">
         <v>0.3846</v>
       </c>
       <c r="I30">
-        <v>0.4488</v>
+        <v>0.4462</v>
       </c>
       <c r="J30">
-        <v>0.4869</v>
+        <v>0.4921</v>
       </c>
       <c r="K30">
         <v>0.6153999999999999</v>
       </c>
       <c r="L30">
-        <v>0.5512</v>
+        <v>0.5538</v>
       </c>
       <c r="M30">
         <v>168</v>
@@ -1983,22 +1983,22 @@
         <v>46</v>
       </c>
       <c r="G32">
-        <v>0.8867</v>
+        <v>0.8878</v>
       </c>
       <c r="H32">
         <v>0.7771</v>
       </c>
       <c r="I32">
-        <v>0.8319</v>
+        <v>0.8324</v>
       </c>
       <c r="J32">
-        <v>0.1133</v>
+        <v>0.1122</v>
       </c>
       <c r="K32">
         <v>0.2229</v>
       </c>
       <c r="L32">
-        <v>0.1681</v>
+        <v>0.1676</v>
       </c>
       <c r="M32">
         <v>168</v>
@@ -2030,19 +2030,19 @@
         <v>0.8918</v>
       </c>
       <c r="H33">
-        <v>0.7883</v>
+        <v>0.7852</v>
       </c>
       <c r="I33">
-        <v>0.84</v>
+        <v>0.8385</v>
       </c>
       <c r="J33">
         <v>0.1082</v>
       </c>
       <c r="K33">
-        <v>0.2117</v>
+        <v>0.2148</v>
       </c>
       <c r="L33">
-        <v>0.16</v>
+        <v>0.1615</v>
       </c>
       <c r="M33">
         <v>168</v>
@@ -2071,22 +2071,22 @@
         <v>48</v>
       </c>
       <c r="G34">
-        <v>0.8808</v>
+        <v>0.8804</v>
       </c>
       <c r="H34">
-        <v>0.7594</v>
+        <v>0.7568</v>
       </c>
       <c r="I34">
-        <v>0.8201000000000001</v>
+        <v>0.8186</v>
       </c>
       <c r="J34">
-        <v>0.1192</v>
+        <v>0.1196</v>
       </c>
       <c r="K34">
-        <v>0.2406</v>
+        <v>0.2432</v>
       </c>
       <c r="L34">
-        <v>0.1799</v>
+        <v>0.1814</v>
       </c>
       <c r="M34">
         <v>168</v>
@@ -2115,22 +2115,22 @@
         <v>49</v>
       </c>
       <c r="G35">
-        <v>0.7433999999999999</v>
+        <v>0.6238</v>
       </c>
       <c r="H35">
-        <v>0.5969</v>
+        <v>0.4995</v>
       </c>
       <c r="I35">
-        <v>0.6702</v>
+        <v>0.5616</v>
       </c>
       <c r="J35">
-        <v>0.2566</v>
+        <v>0.3762</v>
       </c>
       <c r="K35">
-        <v>0.4031</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="L35">
-        <v>0.3298</v>
+        <v>0.4384</v>
       </c>
       <c r="M35">
         <v>168</v>
@@ -2159,22 +2159,22 @@
         <v>50</v>
       </c>
       <c r="G36">
-        <v>0.8357</v>
+        <v>0.8333</v>
       </c>
       <c r="H36">
         <v>0.6891</v>
       </c>
       <c r="I36">
-        <v>0.7624</v>
+        <v>0.7612</v>
       </c>
       <c r="J36">
-        <v>0.1643</v>
+        <v>0.1667</v>
       </c>
       <c r="K36">
         <v>0.3109</v>
       </c>
       <c r="L36">
-        <v>0.2376</v>
+        <v>0.2388</v>
       </c>
       <c r="M36">
         <v>168</v>
@@ -2206,19 +2206,19 @@
         <v>0.7027</v>
       </c>
       <c r="H37">
-        <v>0.5421</v>
+        <v>0.5374</v>
       </c>
       <c r="I37">
-        <v>0.6224</v>
+        <v>0.62</v>
       </c>
       <c r="J37">
         <v>0.2973</v>
       </c>
       <c r="K37">
-        <v>0.4579</v>
+        <v>0.4626</v>
       </c>
       <c r="L37">
-        <v>0.3776</v>
+        <v>0.38</v>
       </c>
       <c r="M37">
         <v>168</v>
@@ -2247,22 +2247,22 @@
         <v>52</v>
       </c>
       <c r="G38">
-        <v>0.7609</v>
+        <v>0.7583</v>
       </c>
       <c r="H38">
-        <v>0.6126</v>
+        <v>0.6047</v>
       </c>
       <c r="I38">
-        <v>0.6868</v>
+        <v>0.6815</v>
       </c>
       <c r="J38">
-        <v>0.2391</v>
+        <v>0.2417</v>
       </c>
       <c r="K38">
-        <v>0.3874</v>
+        <v>0.3953</v>
       </c>
       <c r="L38">
-        <v>0.3132</v>
+        <v>0.3185</v>
       </c>
       <c r="M38">
         <v>168</v>
@@ -2294,19 +2294,19 @@
         <v>0.8121</v>
       </c>
       <c r="H39">
-        <v>0.6850000000000001</v>
+        <v>0.6731</v>
       </c>
       <c r="I39">
-        <v>0.7486</v>
+        <v>0.7426</v>
       </c>
       <c r="J39">
         <v>0.1879</v>
       </c>
       <c r="K39">
-        <v>0.315</v>
+        <v>0.3269</v>
       </c>
       <c r="L39">
-        <v>0.2514</v>
+        <v>0.2574</v>
       </c>
       <c r="M39">
         <v>168</v>
@@ -2338,19 +2338,19 @@
         <v>0.8127</v>
       </c>
       <c r="H40">
-        <v>0.6362</v>
+        <v>0.6273</v>
       </c>
       <c r="I40">
-        <v>0.7244</v>
+        <v>0.72</v>
       </c>
       <c r="J40">
         <v>0.1873</v>
       </c>
       <c r="K40">
-        <v>0.3638</v>
+        <v>0.3727</v>
       </c>
       <c r="L40">
-        <v>0.2756</v>
+        <v>0.28</v>
       </c>
       <c r="M40">
         <v>168</v>
@@ -2423,22 +2423,22 @@
         <v>56</v>
       </c>
       <c r="G42">
-        <v>0.7817</v>
+        <v>0.7718</v>
       </c>
       <c r="H42">
         <v>0.6042999999999999</v>
       </c>
       <c r="I42">
-        <v>0.6929999999999999</v>
+        <v>0.6881</v>
       </c>
       <c r="J42">
-        <v>0.2183</v>
+        <v>0.2282</v>
       </c>
       <c r="K42">
         <v>0.3957</v>
       </c>
       <c r="L42">
-        <v>0.307</v>
+        <v>0.3119</v>
       </c>
       <c r="M42">
         <v>168</v>
@@ -2511,22 +2511,22 @@
         <v>58</v>
       </c>
       <c r="G44">
-        <v>0.6108</v>
+        <v>0.6099</v>
       </c>
       <c r="H44">
         <v>0.5392</v>
       </c>
       <c r="I44">
-        <v>0.575</v>
+        <v>0.5746</v>
       </c>
       <c r="J44">
-        <v>0.3892</v>
+        <v>0.3901</v>
       </c>
       <c r="K44">
         <v>0.4608</v>
       </c>
       <c r="L44">
-        <v>0.425</v>
+        <v>0.4254</v>
       </c>
       <c r="M44">
         <v>168</v>
@@ -2555,22 +2555,22 @@
         <v>59</v>
       </c>
       <c r="G45">
-        <v>0.8352000000000001</v>
+        <v>0.8334</v>
       </c>
       <c r="H45">
         <v>0.6812</v>
       </c>
       <c r="I45">
-        <v>0.7582</v>
+        <v>0.7573</v>
       </c>
       <c r="J45">
-        <v>0.1648</v>
+        <v>0.1666</v>
       </c>
       <c r="K45">
         <v>0.3188</v>
       </c>
       <c r="L45">
-        <v>0.2418</v>
+        <v>0.2427</v>
       </c>
       <c r="M45">
         <v>168</v>
@@ -2602,19 +2602,19 @@
         <v>0.8797</v>
       </c>
       <c r="H46">
-        <v>0.7794</v>
+        <v>0.765</v>
       </c>
       <c r="I46">
-        <v>0.8296</v>
+        <v>0.8224</v>
       </c>
       <c r="J46">
         <v>0.1203</v>
       </c>
       <c r="K46">
-        <v>0.2206</v>
+        <v>0.235</v>
       </c>
       <c r="L46">
-        <v>0.1704</v>
+        <v>0.1776</v>
       </c>
       <c r="M46">
         <v>168</v>
@@ -2643,22 +2643,22 @@
         <v>61</v>
       </c>
       <c r="G47">
-        <v>0.8053</v>
+        <v>0.8026</v>
       </c>
       <c r="H47">
         <v>0.6661</v>
       </c>
       <c r="I47">
-        <v>0.7357</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="J47">
-        <v>0.1947</v>
+        <v>0.1974</v>
       </c>
       <c r="K47">
         <v>0.3339</v>
       </c>
       <c r="L47">
-        <v>0.2643</v>
+        <v>0.2656</v>
       </c>
       <c r="M47">
         <v>168</v>
@@ -2687,22 +2687,22 @@
         <v>62</v>
       </c>
       <c r="G48">
-        <v>0.8008</v>
+        <v>0.7994</v>
       </c>
       <c r="H48">
-        <v>0.6636</v>
+        <v>0.6615</v>
       </c>
       <c r="I48">
-        <v>0.7322</v>
+        <v>0.7304</v>
       </c>
       <c r="J48">
-        <v>0.1992</v>
+        <v>0.2006</v>
       </c>
       <c r="K48">
-        <v>0.3364</v>
+        <v>0.3385</v>
       </c>
       <c r="L48">
-        <v>0.2678</v>
+        <v>0.2696</v>
       </c>
       <c r="M48">
         <v>168</v>
@@ -2731,22 +2731,22 @@
         <v>63</v>
       </c>
       <c r="G49">
-        <v>0.7965</v>
+        <v>0.7953</v>
       </c>
       <c r="H49">
-        <v>0.6615</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="I49">
-        <v>0.729</v>
+        <v>0.7261</v>
       </c>
       <c r="J49">
-        <v>0.2035</v>
+        <v>0.2047</v>
       </c>
       <c r="K49">
-        <v>0.3385</v>
+        <v>0.3432</v>
       </c>
       <c r="L49">
-        <v>0.271</v>
+        <v>0.2739</v>
       </c>
       <c r="M49">
         <v>168</v>
@@ -2819,22 +2819,22 @@
         <v>65</v>
       </c>
       <c r="G51">
-        <v>0.5503</v>
+        <v>0.5493</v>
       </c>
       <c r="H51">
         <v>0.4039</v>
       </c>
       <c r="I51">
-        <v>0.4771</v>
+        <v>0.4766</v>
       </c>
       <c r="J51">
-        <v>0.4497</v>
+        <v>0.4507</v>
       </c>
       <c r="K51">
         <v>0.5961</v>
       </c>
       <c r="L51">
-        <v>0.5229</v>
+        <v>0.5234</v>
       </c>
       <c r="M51">
         <v>168</v>
@@ -2863,22 +2863,22 @@
         <v>66</v>
       </c>
       <c r="G52">
-        <v>0.5119</v>
+        <v>0.5087</v>
       </c>
       <c r="H52">
         <v>0.3702</v>
       </c>
       <c r="I52">
-        <v>0.441</v>
+        <v>0.4394</v>
       </c>
       <c r="J52">
-        <v>0.4881</v>
+        <v>0.4913</v>
       </c>
       <c r="K52">
         <v>0.6298</v>
       </c>
       <c r="L52">
-        <v>0.5590000000000001</v>
+        <v>0.5606</v>
       </c>
       <c r="M52">
         <v>168</v>
@@ -2907,22 +2907,22 @@
         <v>67</v>
       </c>
       <c r="G53">
-        <v>0.7893</v>
+        <v>0.7824</v>
       </c>
       <c r="H53">
-        <v>0.6394</v>
+        <v>0.6281</v>
       </c>
       <c r="I53">
-        <v>0.7144</v>
+        <v>0.7052</v>
       </c>
       <c r="J53">
-        <v>0.2107</v>
+        <v>0.2176</v>
       </c>
       <c r="K53">
-        <v>0.3606</v>
+        <v>0.3719</v>
       </c>
       <c r="L53">
-        <v>0.2856</v>
+        <v>0.2948</v>
       </c>
       <c r="M53">
         <v>168</v>
@@ -2951,22 +2951,22 @@
         <v>68</v>
       </c>
       <c r="G54">
-        <v>0.8949</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="H54">
-        <v>0.7906</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="I54">
-        <v>0.8428</v>
+        <v>0.8342000000000001</v>
       </c>
       <c r="J54">
-        <v>0.1051</v>
+        <v>0.1084</v>
       </c>
       <c r="K54">
-        <v>0.2094</v>
+        <v>0.2233</v>
       </c>
       <c r="L54">
-        <v>0.1572</v>
+        <v>0.1658</v>
       </c>
       <c r="M54">
         <v>168</v>
@@ -2998,19 +2998,19 @@
         <v>0.897</v>
       </c>
       <c r="H55">
-        <v>0.7926</v>
+        <v>0.7896</v>
       </c>
       <c r="I55">
-        <v>0.8448</v>
+        <v>0.8433</v>
       </c>
       <c r="J55">
         <v>0.103</v>
       </c>
       <c r="K55">
-        <v>0.2074</v>
+        <v>0.2104</v>
       </c>
       <c r="L55">
-        <v>0.1552</v>
+        <v>0.1567</v>
       </c>
       <c r="M55">
         <v>168</v>
@@ -3083,22 +3083,22 @@
         <v>71</v>
       </c>
       <c r="G57">
-        <v>0.6686</v>
+        <v>0.6641</v>
       </c>
       <c r="H57">
         <v>0.491</v>
       </c>
       <c r="I57">
-        <v>0.5798</v>
+        <v>0.5776</v>
       </c>
       <c r="J57">
-        <v>0.3314</v>
+        <v>0.3359</v>
       </c>
       <c r="K57">
         <v>0.509</v>
       </c>
       <c r="L57">
-        <v>0.4202</v>
+        <v>0.4224</v>
       </c>
       <c r="M57">
         <v>168</v>
@@ -3127,22 +3127,22 @@
         <v>73</v>
       </c>
       <c r="G58">
-        <v>0.6829</v>
+        <v>0.6805</v>
       </c>
       <c r="H58">
-        <v>0.5339</v>
+        <v>0.5295</v>
       </c>
       <c r="I58">
-        <v>0.6084000000000001</v>
+        <v>0.605</v>
       </c>
       <c r="J58">
-        <v>0.3171</v>
+        <v>0.3195</v>
       </c>
       <c r="K58">
-        <v>0.4661</v>
+        <v>0.4705</v>
       </c>
       <c r="L58">
-        <v>0.3916</v>
+        <v>0.395</v>
       </c>
       <c r="M58">
         <v>168</v>
@@ -3171,22 +3171,22 @@
         <v>46</v>
       </c>
       <c r="G59">
-        <v>0.8457</v>
+        <v>0.8472</v>
       </c>
       <c r="H59">
         <v>0.7615</v>
       </c>
       <c r="I59">
-        <v>0.8036</v>
+        <v>0.8043</v>
       </c>
       <c r="J59">
-        <v>0.1543</v>
+        <v>0.1528</v>
       </c>
       <c r="K59">
         <v>0.2385</v>
       </c>
       <c r="L59">
-        <v>0.1964</v>
+        <v>0.1957</v>
       </c>
       <c r="M59">
         <v>168</v>
@@ -3218,19 +3218,19 @@
         <v>0.8645</v>
       </c>
       <c r="H60">
-        <v>0.7814</v>
+        <v>0.7783</v>
       </c>
       <c r="I60">
-        <v>0.823</v>
+        <v>0.8214</v>
       </c>
       <c r="J60">
         <v>0.1355</v>
       </c>
       <c r="K60">
-        <v>0.2186</v>
+        <v>0.2217</v>
       </c>
       <c r="L60">
-        <v>0.177</v>
+        <v>0.1786</v>
       </c>
       <c r="M60">
         <v>168</v>
@@ -3259,22 +3259,22 @@
         <v>48</v>
       </c>
       <c r="G61">
-        <v>0.8466</v>
+        <v>0.846</v>
       </c>
       <c r="H61">
-        <v>0.7585</v>
+        <v>0.7558</v>
       </c>
       <c r="I61">
-        <v>0.8026</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="J61">
-        <v>0.1534</v>
+        <v>0.154</v>
       </c>
       <c r="K61">
-        <v>0.2415</v>
+        <v>0.2442</v>
       </c>
       <c r="L61">
-        <v>0.1974</v>
+        <v>0.1991</v>
       </c>
       <c r="M61">
         <v>168</v>
@@ -3303,22 +3303,22 @@
         <v>49</v>
       </c>
       <c r="G62">
-        <v>0.6919999999999999</v>
+        <v>0.5729</v>
       </c>
       <c r="H62">
-        <v>0.5438</v>
+        <v>0.4435</v>
       </c>
       <c r="I62">
-        <v>0.6179</v>
+        <v>0.5082</v>
       </c>
       <c r="J62">
-        <v>0.308</v>
+        <v>0.4271</v>
       </c>
       <c r="K62">
-        <v>0.4562</v>
+        <v>0.5565</v>
       </c>
       <c r="L62">
-        <v>0.3821</v>
+        <v>0.4918</v>
       </c>
       <c r="M62">
         <v>168</v>
@@ -3347,22 +3347,22 @@
         <v>50</v>
       </c>
       <c r="G63">
-        <v>0.7783</v>
+        <v>0.776</v>
       </c>
       <c r="H63">
-        <v>0.6363</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="I63">
-        <v>0.7073</v>
+        <v>0.7028</v>
       </c>
       <c r="J63">
-        <v>0.2217</v>
+        <v>0.224</v>
       </c>
       <c r="K63">
-        <v>0.3637</v>
+        <v>0.3705</v>
       </c>
       <c r="L63">
-        <v>0.2927</v>
+        <v>0.2972</v>
       </c>
       <c r="M63">
         <v>168</v>
@@ -3391,22 +3391,22 @@
         <v>51</v>
       </c>
       <c r="G64">
-        <v>0.6545</v>
+        <v>0.6506</v>
       </c>
       <c r="H64">
-        <v>0.4889</v>
+        <v>0.4841</v>
       </c>
       <c r="I64">
-        <v>0.5717</v>
+        <v>0.5674</v>
       </c>
       <c r="J64">
-        <v>0.3455</v>
+        <v>0.3494</v>
       </c>
       <c r="K64">
-        <v>0.5111</v>
+        <v>0.5159</v>
       </c>
       <c r="L64">
-        <v>0.4283</v>
+        <v>0.4326</v>
       </c>
       <c r="M64">
         <v>168</v>
@@ -3435,22 +3435,22 @@
         <v>52</v>
       </c>
       <c r="G65">
-        <v>0.6921</v>
+        <v>0.6929</v>
       </c>
       <c r="H65">
-        <v>0.5469000000000001</v>
+        <v>0.5427</v>
       </c>
       <c r="I65">
-        <v>0.6195000000000001</v>
+        <v>0.6178</v>
       </c>
       <c r="J65">
-        <v>0.3079</v>
+        <v>0.3071</v>
       </c>
       <c r="K65">
-        <v>0.4531</v>
+        <v>0.4573</v>
       </c>
       <c r="L65">
-        <v>0.3805</v>
+        <v>0.3822</v>
       </c>
       <c r="M65">
         <v>168</v>
@@ -3482,19 +3482,19 @@
         <v>0.7485000000000001</v>
       </c>
       <c r="H66">
-        <v>0.6274</v>
+        <v>0.6146</v>
       </c>
       <c r="I66">
-        <v>0.6879999999999999</v>
+        <v>0.6816</v>
       </c>
       <c r="J66">
         <v>0.2515</v>
       </c>
       <c r="K66">
-        <v>0.3726</v>
+        <v>0.3854</v>
       </c>
       <c r="L66">
-        <v>0.312</v>
+        <v>0.3184</v>
       </c>
       <c r="M66">
         <v>168</v>
@@ -3523,22 +3523,22 @@
         <v>54</v>
       </c>
       <c r="G67">
-        <v>0.7869</v>
+        <v>0.7845</v>
       </c>
       <c r="H67">
-        <v>0.6065</v>
+        <v>0.6021</v>
       </c>
       <c r="I67">
-        <v>0.6967</v>
+        <v>0.6933</v>
       </c>
       <c r="J67">
-        <v>0.2131</v>
+        <v>0.2155</v>
       </c>
       <c r="K67">
-        <v>0.3935</v>
+        <v>0.3979</v>
       </c>
       <c r="L67">
-        <v>0.3033</v>
+        <v>0.3067</v>
       </c>
       <c r="M67">
         <v>168</v>
@@ -3611,22 +3611,22 @@
         <v>56</v>
       </c>
       <c r="G69">
-        <v>0.726</v>
+        <v>0.7156</v>
       </c>
       <c r="H69">
-        <v>0.578</v>
+        <v>0.5709</v>
       </c>
       <c r="I69">
-        <v>0.652</v>
+        <v>0.6432</v>
       </c>
       <c r="J69">
-        <v>0.274</v>
+        <v>0.2844</v>
       </c>
       <c r="K69">
-        <v>0.422</v>
+        <v>0.4291</v>
       </c>
       <c r="L69">
-        <v>0.348</v>
+        <v>0.3568</v>
       </c>
       <c r="M69">
         <v>168</v>
@@ -3699,22 +3699,22 @@
         <v>58</v>
       </c>
       <c r="G71">
-        <v>0.5358000000000001</v>
+        <v>0.5317</v>
       </c>
       <c r="H71">
         <v>0.4263</v>
       </c>
       <c r="I71">
-        <v>0.481</v>
+        <v>0.479</v>
       </c>
       <c r="J71">
-        <v>0.4642</v>
+        <v>0.4683</v>
       </c>
       <c r="K71">
         <v>0.5737</v>
       </c>
       <c r="L71">
-        <v>0.519</v>
+        <v>0.521</v>
       </c>
       <c r="M71">
         <v>168</v>
@@ -3743,22 +3743,22 @@
         <v>59</v>
       </c>
       <c r="G72">
-        <v>0.7854</v>
+        <v>0.7842</v>
       </c>
       <c r="H72">
         <v>0.6351</v>
       </c>
       <c r="I72">
-        <v>0.7103</v>
+        <v>0.7096</v>
       </c>
       <c r="J72">
-        <v>0.2146</v>
+        <v>0.2158</v>
       </c>
       <c r="K72">
         <v>0.3649</v>
       </c>
       <c r="L72">
-        <v>0.2897</v>
+        <v>0.2904</v>
       </c>
       <c r="M72">
         <v>168</v>
@@ -3790,19 +3790,19 @@
         <v>0.8418</v>
       </c>
       <c r="H73">
-        <v>0.787</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="I73">
-        <v>0.8144</v>
+        <v>0.8098</v>
       </c>
       <c r="J73">
         <v>0.1582</v>
       </c>
       <c r="K73">
-        <v>0.213</v>
+        <v>0.2223</v>
       </c>
       <c r="L73">
-        <v>0.1856</v>
+        <v>0.1902</v>
       </c>
       <c r="M73">
         <v>168</v>
@@ -3875,22 +3875,22 @@
         <v>62</v>
       </c>
       <c r="G75">
-        <v>0.7564</v>
+        <v>0.7536</v>
       </c>
       <c r="H75">
-        <v>0.5829</v>
+        <v>0.5797</v>
       </c>
       <c r="I75">
-        <v>0.6696</v>
+        <v>0.6666</v>
       </c>
       <c r="J75">
-        <v>0.2436</v>
+        <v>0.2464</v>
       </c>
       <c r="K75">
-        <v>0.4171</v>
+        <v>0.4203</v>
       </c>
       <c r="L75">
-        <v>0.3304</v>
+        <v>0.3334</v>
       </c>
       <c r="M75">
         <v>168</v>
@@ -3919,22 +3919,22 @@
         <v>63</v>
       </c>
       <c r="G76">
-        <v>0.7809</v>
+        <v>0.7796</v>
       </c>
       <c r="H76">
-        <v>0.6254999999999999</v>
+        <v>0.6232</v>
       </c>
       <c r="I76">
-        <v>0.7032</v>
+        <v>0.7014</v>
       </c>
       <c r="J76">
-        <v>0.2191</v>
+        <v>0.2204</v>
       </c>
       <c r="K76">
-        <v>0.3745</v>
+        <v>0.3768</v>
       </c>
       <c r="L76">
-        <v>0.2968</v>
+        <v>0.2986</v>
       </c>
       <c r="M76">
         <v>168</v>
@@ -4007,22 +4007,22 @@
         <v>65</v>
       </c>
       <c r="G78">
-        <v>0.5106000000000001</v>
+        <v>0.5064</v>
       </c>
       <c r="H78">
         <v>0.3554</v>
       </c>
       <c r="I78">
-        <v>0.433</v>
+        <v>0.4309</v>
       </c>
       <c r="J78">
-        <v>0.4894</v>
+        <v>0.4936</v>
       </c>
       <c r="K78">
         <v>0.6446</v>
       </c>
       <c r="L78">
-        <v>0.5669999999999999</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="M78">
         <v>168</v>
@@ -4051,22 +4051,22 @@
         <v>66</v>
       </c>
       <c r="G79">
-        <v>0.4601</v>
+        <v>0.4561</v>
       </c>
       <c r="H79">
         <v>0.3466</v>
       </c>
       <c r="I79">
-        <v>0.4034</v>
+        <v>0.4014</v>
       </c>
       <c r="J79">
-        <v>0.5399</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="K79">
         <v>0.6534</v>
       </c>
       <c r="L79">
-        <v>0.5966</v>
+        <v>0.5986</v>
       </c>
       <c r="M79">
         <v>168</v>
@@ -4095,22 +4095,22 @@
         <v>67</v>
       </c>
       <c r="G80">
-        <v>0.7199</v>
+        <v>0.7107</v>
       </c>
       <c r="H80">
-        <v>0.586</v>
+        <v>0.5704</v>
       </c>
       <c r="I80">
-        <v>0.6529</v>
+        <v>0.6405</v>
       </c>
       <c r="J80">
-        <v>0.2801</v>
+        <v>0.2893</v>
       </c>
       <c r="K80">
-        <v>0.414</v>
+        <v>0.4296</v>
       </c>
       <c r="L80">
-        <v>0.3471</v>
+        <v>0.3595</v>
       </c>
       <c r="M80">
         <v>168</v>
@@ -4139,22 +4139,22 @@
         <v>68</v>
       </c>
       <c r="G81">
-        <v>0.8838</v>
+        <v>0.8802</v>
       </c>
       <c r="H81">
-        <v>0.7952</v>
+        <v>0.7814</v>
       </c>
       <c r="I81">
-        <v>0.8395</v>
+        <v>0.8308</v>
       </c>
       <c r="J81">
-        <v>0.1162</v>
+        <v>0.1198</v>
       </c>
       <c r="K81">
-        <v>0.2048</v>
+        <v>0.2186</v>
       </c>
       <c r="L81">
-        <v>0.1605</v>
+        <v>0.1692</v>
       </c>
       <c r="M81">
         <v>168</v>
@@ -4186,19 +4186,19 @@
         <v>0.8791</v>
       </c>
       <c r="H82">
-        <v>0.7786999999999999</v>
+        <v>0.7755</v>
       </c>
       <c r="I82">
-        <v>0.8289</v>
+        <v>0.8273</v>
       </c>
       <c r="J82">
         <v>0.1209</v>
       </c>
       <c r="K82">
-        <v>0.2213</v>
+        <v>0.2245</v>
       </c>
       <c r="L82">
-        <v>0.1711</v>
+        <v>0.1727</v>
       </c>
       <c r="M82">
         <v>168</v>
@@ -4271,22 +4271,22 @@
         <v>71</v>
       </c>
       <c r="G84">
-        <v>0.6163999999999999</v>
+        <v>0.6146</v>
       </c>
       <c r="H84">
-        <v>0.48</v>
+        <v>0.4758</v>
       </c>
       <c r="I84">
-        <v>0.5482</v>
+        <v>0.5452</v>
       </c>
       <c r="J84">
-        <v>0.3836</v>
+        <v>0.3854</v>
       </c>
       <c r="K84">
-        <v>0.52</v>
+        <v>0.5242</v>
       </c>
       <c r="L84">
-        <v>0.4518</v>
+        <v>0.4548</v>
       </c>
       <c r="M84">
         <v>168</v>
@@ -4315,22 +4315,22 @@
         <v>73</v>
       </c>
       <c r="G85">
-        <v>0.6425</v>
+        <v>0.6399</v>
       </c>
       <c r="H85">
-        <v>0.4772</v>
+        <v>0.4694</v>
       </c>
       <c r="I85">
-        <v>0.5598</v>
+        <v>0.5546</v>
       </c>
       <c r="J85">
-        <v>0.3575</v>
+        <v>0.3601</v>
       </c>
       <c r="K85">
-        <v>0.5228</v>
+        <v>0.5306</v>
       </c>
       <c r="L85">
-        <v>0.4402</v>
+        <v>0.4454</v>
       </c>
       <c r="M85">
         <v>168</v>
@@ -4359,22 +4359,22 @@
         <v>47</v>
       </c>
       <c r="G86">
-        <v>0.6137</v>
+        <v>0.5841</v>
       </c>
       <c r="H86">
-        <v>0.4765</v>
+        <v>0.4728</v>
       </c>
       <c r="I86">
-        <v>0.5451</v>
+        <v>0.5284</v>
       </c>
       <c r="J86">
-        <v>0.3863</v>
+        <v>0.4159</v>
       </c>
       <c r="K86">
-        <v>0.5235</v>
+        <v>0.5272</v>
       </c>
       <c r="L86">
-        <v>0.4549</v>
+        <v>0.4716</v>
       </c>
       <c r="M86">
         <v>168</v>
@@ -4403,22 +4403,22 @@
         <v>48</v>
       </c>
       <c r="G87">
-        <v>0.5593</v>
+        <v>0.5575</v>
       </c>
       <c r="H87">
-        <v>0.4483</v>
+        <v>0.4302</v>
       </c>
       <c r="I87">
-        <v>0.5038</v>
+        <v>0.4938</v>
       </c>
       <c r="J87">
-        <v>0.4407</v>
+        <v>0.4425</v>
       </c>
       <c r="K87">
-        <v>0.5517</v>
+        <v>0.5698</v>
       </c>
       <c r="L87">
-        <v>0.4962</v>
+        <v>0.5062</v>
       </c>
       <c r="M87">
         <v>168</v>
@@ -4447,22 +4447,22 @@
         <v>49</v>
       </c>
       <c r="G88">
-        <v>0.3109</v>
+        <v>0.2451</v>
       </c>
       <c r="H88">
-        <v>0.201</v>
+        <v>0.1434</v>
       </c>
       <c r="I88">
-        <v>0.256</v>
+        <v>0.1942</v>
       </c>
       <c r="J88">
-        <v>0.6891</v>
+        <v>0.7549</v>
       </c>
       <c r="K88">
-        <v>0.799</v>
+        <v>0.8566</v>
       </c>
       <c r="L88">
-        <v>0.744</v>
+        <v>0.8058</v>
       </c>
       <c r="M88">
         <v>168</v>
@@ -4491,22 +4491,22 @@
         <v>50</v>
       </c>
       <c r="G89">
-        <v>0.4322</v>
+        <v>0.4273</v>
       </c>
       <c r="H89">
-        <v>0.279</v>
+        <v>0.2708</v>
       </c>
       <c r="I89">
-        <v>0.3556</v>
+        <v>0.349</v>
       </c>
       <c r="J89">
-        <v>0.5678</v>
+        <v>0.5727</v>
       </c>
       <c r="K89">
-        <v>0.721</v>
+        <v>0.7292</v>
       </c>
       <c r="L89">
-        <v>0.6444</v>
+        <v>0.651</v>
       </c>
       <c r="M89">
         <v>168</v>
@@ -4538,19 +4538,19 @@
         <v>0.2981</v>
       </c>
       <c r="H90">
-        <v>0.1572</v>
+        <v>0.1548</v>
       </c>
       <c r="I90">
-        <v>0.2276</v>
+        <v>0.2264</v>
       </c>
       <c r="J90">
         <v>0.7019</v>
       </c>
       <c r="K90">
-        <v>0.8428</v>
+        <v>0.8452</v>
       </c>
       <c r="L90">
-        <v>0.7724</v>
+        <v>0.7736</v>
       </c>
       <c r="M90">
         <v>168</v>
@@ -4579,22 +4579,22 @@
         <v>52</v>
       </c>
       <c r="G91">
-        <v>0.3335</v>
+        <v>0.322</v>
       </c>
       <c r="H91">
-        <v>0.1822</v>
+        <v>0.1791</v>
       </c>
       <c r="I91">
-        <v>0.2579</v>
+        <v>0.2506</v>
       </c>
       <c r="J91">
-        <v>0.6665</v>
+        <v>0.678</v>
       </c>
       <c r="K91">
-        <v>0.8178</v>
+        <v>0.8209</v>
       </c>
       <c r="L91">
-        <v>0.7421</v>
+        <v>0.7494</v>
       </c>
       <c r="M91">
         <v>168</v>
@@ -4623,22 +4623,22 @@
         <v>53</v>
       </c>
       <c r="G92">
-        <v>0.4198</v>
+        <v>0.4088</v>
       </c>
       <c r="H92">
-        <v>0.3057</v>
+        <v>0.299</v>
       </c>
       <c r="I92">
-        <v>0.3628</v>
+        <v>0.3539</v>
       </c>
       <c r="J92">
-        <v>0.5802</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="K92">
-        <v>0.6943</v>
+        <v>0.701</v>
       </c>
       <c r="L92">
-        <v>0.6372</v>
+        <v>0.6461</v>
       </c>
       <c r="M92">
         <v>168</v>
@@ -4667,22 +4667,22 @@
         <v>54</v>
       </c>
       <c r="G93">
-        <v>0.387</v>
+        <v>0.3762</v>
       </c>
       <c r="H93">
-        <v>0.2439</v>
+        <v>0.2446</v>
       </c>
       <c r="I93">
-        <v>0.3154</v>
+        <v>0.3104</v>
       </c>
       <c r="J93">
-        <v>0.613</v>
+        <v>0.6238</v>
       </c>
       <c r="K93">
-        <v>0.7561</v>
+        <v>0.7554</v>
       </c>
       <c r="L93">
-        <v>0.6846</v>
+        <v>0.6896</v>
       </c>
       <c r="M93">
         <v>168</v>
@@ -4711,22 +4711,22 @@
         <v>55</v>
       </c>
       <c r="G94">
-        <v>0.6424</v>
+        <v>0.6162</v>
       </c>
       <c r="H94">
-        <v>0.4885</v>
+        <v>0.4824</v>
       </c>
       <c r="I94">
-        <v>0.5654</v>
+        <v>0.5493</v>
       </c>
       <c r="J94">
-        <v>0.3576</v>
+        <v>0.3838</v>
       </c>
       <c r="K94">
-        <v>0.5115</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="L94">
-        <v>0.4346</v>
+        <v>0.4507</v>
       </c>
       <c r="M94">
         <v>168</v>
@@ -4755,22 +4755,22 @@
         <v>56</v>
       </c>
       <c r="G95">
-        <v>0.3601</v>
+        <v>0.354</v>
       </c>
       <c r="H95">
-        <v>0.2215</v>
+        <v>0.2111</v>
       </c>
       <c r="I95">
-        <v>0.2908</v>
+        <v>0.2825</v>
       </c>
       <c r="J95">
-        <v>0.6399</v>
+        <v>0.646</v>
       </c>
       <c r="K95">
-        <v>0.7785</v>
+        <v>0.7889</v>
       </c>
       <c r="L95">
-        <v>0.7092000000000001</v>
+        <v>0.7175</v>
       </c>
       <c r="M95">
         <v>168</v>
@@ -4799,22 +4799,22 @@
         <v>57</v>
       </c>
       <c r="G96">
-        <v>0.7451</v>
+        <v>0.7345</v>
       </c>
       <c r="H96">
-        <v>0.5677</v>
+        <v>0.5585</v>
       </c>
       <c r="I96">
-        <v>0.6564</v>
+        <v>0.6465</v>
       </c>
       <c r="J96">
-        <v>0.2549</v>
+        <v>0.2655</v>
       </c>
       <c r="K96">
-        <v>0.4323</v>
+        <v>0.4415</v>
       </c>
       <c r="L96">
-        <v>0.3436</v>
+        <v>0.3535</v>
       </c>
       <c r="M96">
         <v>168</v>
@@ -4846,19 +4846,19 @@
         <v>0.2356</v>
       </c>
       <c r="H97">
-        <v>0.1416</v>
+        <v>0.1392</v>
       </c>
       <c r="I97">
-        <v>0.1886</v>
+        <v>0.1874</v>
       </c>
       <c r="J97">
         <v>0.7644</v>
       </c>
       <c r="K97">
-        <v>0.8584000000000001</v>
+        <v>0.8608</v>
       </c>
       <c r="L97">
-        <v>0.8114</v>
+        <v>0.8126</v>
       </c>
       <c r="M97">
         <v>168</v>
@@ -4887,22 +4887,22 @@
         <v>59</v>
       </c>
       <c r="G98">
-        <v>0.4289</v>
+        <v>0.4243</v>
       </c>
       <c r="H98">
-        <v>0.306</v>
+        <v>0.2852</v>
       </c>
       <c r="I98">
-        <v>0.3674</v>
+        <v>0.3548</v>
       </c>
       <c r="J98">
-        <v>0.5711000000000001</v>
+        <v>0.5757</v>
       </c>
       <c r="K98">
-        <v>0.694</v>
+        <v>0.7148</v>
       </c>
       <c r="L98">
-        <v>0.6326000000000001</v>
+        <v>0.6452</v>
       </c>
       <c r="M98">
         <v>168</v>
@@ -4931,22 +4931,22 @@
         <v>60</v>
       </c>
       <c r="G99">
-        <v>0.5767</v>
+        <v>0.5656</v>
       </c>
       <c r="H99">
-        <v>0.4721</v>
+        <v>0.4609</v>
       </c>
       <c r="I99">
-        <v>0.5244</v>
+        <v>0.5132</v>
       </c>
       <c r="J99">
-        <v>0.4233</v>
+        <v>0.4344</v>
       </c>
       <c r="K99">
-        <v>0.5279</v>
+        <v>0.5391</v>
       </c>
       <c r="L99">
-        <v>0.4756</v>
+        <v>0.4868</v>
       </c>
       <c r="M99">
         <v>168</v>
@@ -4975,22 +4975,22 @@
         <v>61</v>
       </c>
       <c r="G100">
-        <v>0.3751</v>
+        <v>0.372</v>
       </c>
       <c r="H100">
-        <v>0.253</v>
+        <v>0.2502</v>
       </c>
       <c r="I100">
-        <v>0.314</v>
+        <v>0.3111</v>
       </c>
       <c r="J100">
-        <v>0.6249</v>
+        <v>0.628</v>
       </c>
       <c r="K100">
-        <v>0.747</v>
+        <v>0.7498</v>
       </c>
       <c r="L100">
-        <v>0.6860000000000001</v>
+        <v>0.6889</v>
       </c>
       <c r="M100">
         <v>168</v>
@@ -5019,22 +5019,22 @@
         <v>62</v>
       </c>
       <c r="G101">
-        <v>0.3866</v>
+        <v>0.3809</v>
       </c>
       <c r="H101">
-        <v>0.224</v>
+        <v>0.2211</v>
       </c>
       <c r="I101">
-        <v>0.3053</v>
+        <v>0.301</v>
       </c>
       <c r="J101">
-        <v>0.6133999999999999</v>
+        <v>0.6191</v>
       </c>
       <c r="K101">
-        <v>0.776</v>
+        <v>0.7789</v>
       </c>
       <c r="L101">
-        <v>0.6947</v>
+        <v>0.699</v>
       </c>
       <c r="M101">
         <v>168</v>
@@ -5063,22 +5063,22 @@
         <v>63</v>
       </c>
       <c r="G102">
-        <v>0.4224</v>
+        <v>0.4115</v>
       </c>
       <c r="H102">
-        <v>0.2756</v>
+        <v>0.264</v>
       </c>
       <c r="I102">
-        <v>0.349</v>
+        <v>0.3378</v>
       </c>
       <c r="J102">
-        <v>0.5776</v>
+        <v>0.5885</v>
       </c>
       <c r="K102">
-        <v>0.7244</v>
+        <v>0.736</v>
       </c>
       <c r="L102">
-        <v>0.651</v>
+        <v>0.6622</v>
       </c>
       <c r="M102">
         <v>168</v>
@@ -5107,22 +5107,22 @@
         <v>64</v>
       </c>
       <c r="G103">
-        <v>0.7030999999999999</v>
+        <v>0.6781</v>
       </c>
       <c r="H103">
-        <v>0.5817</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="I103">
-        <v>0.6424</v>
+        <v>0.6276</v>
       </c>
       <c r="J103">
-        <v>0.2969</v>
+        <v>0.3219</v>
       </c>
       <c r="K103">
-        <v>0.4183</v>
+        <v>0.4229</v>
       </c>
       <c r="L103">
-        <v>0.3576</v>
+        <v>0.3724</v>
       </c>
       <c r="M103">
         <v>168</v>
@@ -5151,22 +5151,22 @@
         <v>65</v>
       </c>
       <c r="G104">
-        <v>0.2416</v>
+        <v>0.2392</v>
       </c>
       <c r="H104">
-        <v>0.1315</v>
+        <v>0.1292</v>
       </c>
       <c r="I104">
-        <v>0.1866</v>
+        <v>0.1842</v>
       </c>
       <c r="J104">
-        <v>0.7584</v>
+        <v>0.7608</v>
       </c>
       <c r="K104">
-        <v>0.8685</v>
+        <v>0.8708</v>
       </c>
       <c r="L104">
-        <v>0.8134</v>
+        <v>0.8158</v>
       </c>
       <c r="M104">
         <v>168</v>
@@ -5195,22 +5195,22 @@
         <v>66</v>
       </c>
       <c r="G105">
-        <v>0.2368</v>
+        <v>0.2317</v>
       </c>
       <c r="H105">
-        <v>0.1299</v>
+        <v>0.1272</v>
       </c>
       <c r="I105">
-        <v>0.1834</v>
+        <v>0.1794</v>
       </c>
       <c r="J105">
-        <v>0.7632</v>
+        <v>0.7683</v>
       </c>
       <c r="K105">
-        <v>0.8701</v>
+        <v>0.8728</v>
       </c>
       <c r="L105">
-        <v>0.8166</v>
+        <v>0.8206</v>
       </c>
       <c r="M105">
         <v>168</v>
@@ -5239,22 +5239,22 @@
         <v>67</v>
       </c>
       <c r="G106">
-        <v>0.3477</v>
+        <v>0.3412</v>
       </c>
       <c r="H106">
-        <v>0.2132</v>
+        <v>0.2034</v>
       </c>
       <c r="I106">
-        <v>0.2804</v>
+        <v>0.2723</v>
       </c>
       <c r="J106">
-        <v>0.6523</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="K106">
-        <v>0.7868000000000001</v>
+        <v>0.7966</v>
       </c>
       <c r="L106">
-        <v>0.7196</v>
+        <v>0.7277</v>
       </c>
       <c r="M106">
         <v>168</v>
@@ -5283,22 +5283,22 @@
         <v>68</v>
       </c>
       <c r="G107">
-        <v>0.6696</v>
+        <v>0.6461</v>
       </c>
       <c r="H107">
-        <v>0.5714</v>
+        <v>0.5506</v>
       </c>
       <c r="I107">
-        <v>0.6205000000000001</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="J107">
-        <v>0.3304</v>
+        <v>0.3539</v>
       </c>
       <c r="K107">
-        <v>0.4286</v>
+        <v>0.4494</v>
       </c>
       <c r="L107">
-        <v>0.3795</v>
+        <v>0.4017</v>
       </c>
       <c r="M107">
         <v>168</v>
@@ -5327,22 +5327,22 @@
         <v>69</v>
       </c>
       <c r="G108">
-        <v>0.6398</v>
+        <v>0.601</v>
       </c>
       <c r="H108">
-        <v>0.5007</v>
+        <v>0.4969</v>
       </c>
       <c r="I108">
-        <v>0.5702</v>
+        <v>0.549</v>
       </c>
       <c r="J108">
-        <v>0.3602</v>
+        <v>0.399</v>
       </c>
       <c r="K108">
-        <v>0.4993</v>
+        <v>0.5031</v>
       </c>
       <c r="L108">
-        <v>0.4298</v>
+        <v>0.451</v>
       </c>
       <c r="M108">
         <v>168</v>
@@ -5371,22 +5371,22 @@
         <v>70</v>
       </c>
       <c r="G109">
-        <v>0.744</v>
+        <v>0.7262999999999999</v>
       </c>
       <c r="H109">
-        <v>0.5607</v>
+        <v>0.5587</v>
       </c>
       <c r="I109">
-        <v>0.6524</v>
+        <v>0.6425</v>
       </c>
       <c r="J109">
-        <v>0.256</v>
+        <v>0.2737</v>
       </c>
       <c r="K109">
-        <v>0.4393</v>
+        <v>0.4413</v>
       </c>
       <c r="L109">
-        <v>0.3476</v>
+        <v>0.3575</v>
       </c>
       <c r="M109">
         <v>168</v>
@@ -5415,22 +5415,22 @@
         <v>71</v>
       </c>
       <c r="G110">
-        <v>0.3119</v>
+        <v>0.3078</v>
       </c>
       <c r="H110">
-        <v>0.1918</v>
+        <v>0.1778</v>
       </c>
       <c r="I110">
-        <v>0.2518</v>
+        <v>0.2428</v>
       </c>
       <c r="J110">
-        <v>0.6881</v>
+        <v>0.6922</v>
       </c>
       <c r="K110">
-        <v>0.8082</v>
+        <v>0.8222</v>
       </c>
       <c r="L110">
-        <v>0.7482</v>
+        <v>0.7572</v>
       </c>
       <c r="M110">
         <v>168</v>
@@ -5459,22 +5459,22 @@
         <v>73</v>
       </c>
       <c r="G111">
-        <v>0.3028</v>
+        <v>0.2967</v>
       </c>
       <c r="H111">
-        <v>0.1633</v>
+        <v>0.1603</v>
       </c>
       <c r="I111">
-        <v>0.233</v>
+        <v>0.2285</v>
       </c>
       <c r="J111">
-        <v>0.6972</v>
+        <v>0.7033</v>
       </c>
       <c r="K111">
-        <v>0.8367</v>
+        <v>0.8397</v>
       </c>
       <c r="L111">
-        <v>0.767</v>
+        <v>0.7715</v>
       </c>
       <c r="M111">
         <v>168</v>
@@ -5503,22 +5503,22 @@
         <v>48</v>
       </c>
       <c r="G112">
-        <v>0.509</v>
+        <v>0.5202</v>
       </c>
       <c r="H112">
-        <v>0.3851</v>
+        <v>0.3835</v>
       </c>
       <c r="I112">
-        <v>0.447</v>
+        <v>0.4518</v>
       </c>
       <c r="J112">
-        <v>0.491</v>
+        <v>0.4798</v>
       </c>
       <c r="K112">
-        <v>0.6149</v>
+        <v>0.6165</v>
       </c>
       <c r="L112">
-        <v>0.553</v>
+        <v>0.5482</v>
       </c>
       <c r="M112">
         <v>168</v>
@@ -5547,22 +5547,22 @@
         <v>49</v>
       </c>
       <c r="G113">
-        <v>0.2956</v>
+        <v>0.2391</v>
       </c>
       <c r="H113">
-        <v>0.1757</v>
+        <v>0.1371</v>
       </c>
       <c r="I113">
-        <v>0.2356</v>
+        <v>0.1881</v>
       </c>
       <c r="J113">
-        <v>0.7044</v>
+        <v>0.7609</v>
       </c>
       <c r="K113">
-        <v>0.8243</v>
+        <v>0.8629</v>
       </c>
       <c r="L113">
-        <v>0.7644</v>
+        <v>0.8119</v>
       </c>
       <c r="M113">
         <v>168</v>
@@ -5591,22 +5591,22 @@
         <v>50</v>
       </c>
       <c r="G114">
-        <v>0.3707</v>
+        <v>0.3728</v>
       </c>
       <c r="H114">
-        <v>0.2276</v>
+        <v>0.2292</v>
       </c>
       <c r="I114">
-        <v>0.2991</v>
+        <v>0.301</v>
       </c>
       <c r="J114">
-        <v>0.6293</v>
+        <v>0.6272</v>
       </c>
       <c r="K114">
-        <v>0.7724</v>
+        <v>0.7708</v>
       </c>
       <c r="L114">
-        <v>0.7009</v>
+        <v>0.699</v>
       </c>
       <c r="M114">
         <v>168</v>
@@ -5635,22 +5635,22 @@
         <v>51</v>
       </c>
       <c r="G115">
-        <v>0.2898</v>
+        <v>0.2967</v>
       </c>
       <c r="H115">
         <v>0.1376</v>
       </c>
       <c r="I115">
-        <v>0.2137</v>
+        <v>0.2172</v>
       </c>
       <c r="J115">
-        <v>0.7102000000000001</v>
+        <v>0.7033</v>
       </c>
       <c r="K115">
         <v>0.8624000000000001</v>
       </c>
       <c r="L115">
-        <v>0.7863</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="M115">
         <v>168</v>
@@ -5679,22 +5679,22 @@
         <v>52</v>
       </c>
       <c r="G116">
-        <v>0.3134</v>
+        <v>0.318</v>
       </c>
       <c r="H116">
-        <v>0.1563</v>
+        <v>0.1573</v>
       </c>
       <c r="I116">
-        <v>0.2348</v>
+        <v>0.2376</v>
       </c>
       <c r="J116">
-        <v>0.6866</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="K116">
-        <v>0.8437</v>
+        <v>0.8427</v>
       </c>
       <c r="L116">
-        <v>0.7652</v>
+        <v>0.7624</v>
       </c>
       <c r="M116">
         <v>168</v>
@@ -5726,19 +5726,19 @@
         <v>0.3748</v>
       </c>
       <c r="H117">
-        <v>0.2403</v>
+        <v>0.2443</v>
       </c>
       <c r="I117">
-        <v>0.3076</v>
+        <v>0.3096</v>
       </c>
       <c r="J117">
         <v>0.6252</v>
       </c>
       <c r="K117">
-        <v>0.7597</v>
+        <v>0.7557</v>
       </c>
       <c r="L117">
-        <v>0.6924</v>
+        <v>0.6904</v>
       </c>
       <c r="M117">
         <v>168</v>
@@ -5770,19 +5770,19 @@
         <v>0.3495</v>
       </c>
       <c r="H118">
-        <v>0.2288</v>
+        <v>0.231</v>
       </c>
       <c r="I118">
-        <v>0.2892</v>
+        <v>0.2902</v>
       </c>
       <c r="J118">
         <v>0.6505</v>
       </c>
       <c r="K118">
-        <v>0.7712</v>
+        <v>0.769</v>
       </c>
       <c r="L118">
-        <v>0.7108</v>
+        <v>0.7098</v>
       </c>
       <c r="M118">
         <v>168</v>
@@ -5811,22 +5811,22 @@
         <v>55</v>
       </c>
       <c r="G119">
-        <v>0.5954</v>
+        <v>0.5939</v>
       </c>
       <c r="H119">
         <v>0.4713</v>
       </c>
       <c r="I119">
-        <v>0.5334</v>
+        <v>0.5326</v>
       </c>
       <c r="J119">
-        <v>0.4046</v>
+        <v>0.4061</v>
       </c>
       <c r="K119">
         <v>0.5286999999999999</v>
       </c>
       <c r="L119">
-        <v>0.4666</v>
+        <v>0.4674</v>
       </c>
       <c r="M119">
         <v>168</v>
@@ -5855,22 +5855,22 @@
         <v>56</v>
       </c>
       <c r="G120">
-        <v>0.3155</v>
+        <v>0.3175</v>
       </c>
       <c r="H120">
-        <v>0.1951</v>
+        <v>0.1965</v>
       </c>
       <c r="I120">
-        <v>0.2553</v>
+        <v>0.257</v>
       </c>
       <c r="J120">
-        <v>0.6845</v>
+        <v>0.6825</v>
       </c>
       <c r="K120">
-        <v>0.8048999999999999</v>
+        <v>0.8035</v>
       </c>
       <c r="L120">
-        <v>0.7447</v>
+        <v>0.743</v>
       </c>
       <c r="M120">
         <v>168</v>
@@ -5946,19 +5946,19 @@
         <v>0.2297</v>
       </c>
       <c r="H122">
-        <v>0.1197</v>
+        <v>0.1242</v>
       </c>
       <c r="I122">
-        <v>0.1747</v>
+        <v>0.177</v>
       </c>
       <c r="J122">
         <v>0.7703</v>
       </c>
       <c r="K122">
-        <v>0.8803</v>
+        <v>0.8758</v>
       </c>
       <c r="L122">
-        <v>0.8253</v>
+        <v>0.823</v>
       </c>
       <c r="M122">
         <v>168</v>
@@ -5987,22 +5987,22 @@
         <v>59</v>
       </c>
       <c r="G123">
-        <v>0.3834</v>
+        <v>0.3954</v>
       </c>
       <c r="H123">
         <v>0.2447</v>
       </c>
       <c r="I123">
-        <v>0.314</v>
+        <v>0.32</v>
       </c>
       <c r="J123">
-        <v>0.6166</v>
+        <v>0.6046</v>
       </c>
       <c r="K123">
         <v>0.7553</v>
       </c>
       <c r="L123">
-        <v>0.6860000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="M123">
         <v>168</v>
@@ -6075,22 +6075,22 @@
         <v>61</v>
       </c>
       <c r="G125">
-        <v>0.3648</v>
+        <v>0.3726</v>
       </c>
       <c r="H125">
-        <v>0.2167</v>
+        <v>0.2207</v>
       </c>
       <c r="I125">
-        <v>0.2908</v>
+        <v>0.2966</v>
       </c>
       <c r="J125">
-        <v>0.6352</v>
+        <v>0.6274</v>
       </c>
       <c r="K125">
-        <v>0.7833</v>
+        <v>0.7793</v>
       </c>
       <c r="L125">
-        <v>0.7092000000000001</v>
+        <v>0.7034</v>
       </c>
       <c r="M125">
         <v>168</v>
@@ -6122,19 +6122,19 @@
         <v>0.3487</v>
       </c>
       <c r="H126">
-        <v>0.188</v>
+        <v>0.1928</v>
       </c>
       <c r="I126">
-        <v>0.2684</v>
+        <v>0.2708</v>
       </c>
       <c r="J126">
         <v>0.6513</v>
       </c>
       <c r="K126">
-        <v>0.8120000000000001</v>
+        <v>0.8072</v>
       </c>
       <c r="L126">
-        <v>0.7316</v>
+        <v>0.7292</v>
       </c>
       <c r="M126">
         <v>168</v>
@@ -6163,22 +6163,22 @@
         <v>63</v>
       </c>
       <c r="G127">
-        <v>0.3917</v>
+        <v>0.3918</v>
       </c>
       <c r="H127">
-        <v>0.2198</v>
+        <v>0.2224</v>
       </c>
       <c r="I127">
-        <v>0.3057</v>
+        <v>0.3071</v>
       </c>
       <c r="J127">
-        <v>0.6083</v>
+        <v>0.6082</v>
       </c>
       <c r="K127">
-        <v>0.7802</v>
+        <v>0.7776</v>
       </c>
       <c r="L127">
-        <v>0.6943</v>
+        <v>0.6929</v>
       </c>
       <c r="M127">
         <v>168</v>
@@ -6207,22 +6207,22 @@
         <v>64</v>
       </c>
       <c r="G128">
-        <v>0.6673</v>
+        <v>0.6615</v>
       </c>
       <c r="H128">
-        <v>0.5406</v>
+        <v>0.5386</v>
       </c>
       <c r="I128">
-        <v>0.604</v>
+        <v>0.6</v>
       </c>
       <c r="J128">
-        <v>0.3327</v>
+        <v>0.3385</v>
       </c>
       <c r="K128">
-        <v>0.4594</v>
+        <v>0.4614</v>
       </c>
       <c r="L128">
-        <v>0.396</v>
+        <v>0.4</v>
       </c>
       <c r="M128">
         <v>168</v>
@@ -6254,19 +6254,19 @@
         <v>0.2272</v>
       </c>
       <c r="H129">
-        <v>0.1184</v>
+        <v>0.1228</v>
       </c>
       <c r="I129">
-        <v>0.1728</v>
+        <v>0.175</v>
       </c>
       <c r="J129">
         <v>0.7728</v>
       </c>
       <c r="K129">
-        <v>0.8816000000000001</v>
+        <v>0.8772</v>
       </c>
       <c r="L129">
-        <v>0.8272</v>
+        <v>0.825</v>
       </c>
       <c r="M129">
         <v>168</v>
@@ -6298,19 +6298,19 @@
         <v>0.2301</v>
       </c>
       <c r="H130">
-        <v>0.1176</v>
+        <v>0.1188</v>
       </c>
       <c r="I130">
-        <v>0.1738</v>
+        <v>0.1744</v>
       </c>
       <c r="J130">
         <v>0.7699</v>
       </c>
       <c r="K130">
-        <v>0.8824</v>
+        <v>0.8812</v>
       </c>
       <c r="L130">
-        <v>0.8262</v>
+        <v>0.8256</v>
       </c>
       <c r="M130">
         <v>168</v>
@@ -6342,19 +6342,19 @@
         <v>0.3332</v>
       </c>
       <c r="H131">
-        <v>0.1841</v>
+        <v>0.1763</v>
       </c>
       <c r="I131">
-        <v>0.2586</v>
+        <v>0.2548</v>
       </c>
       <c r="J131">
         <v>0.6667999999999999</v>
       </c>
       <c r="K131">
-        <v>0.8159</v>
+        <v>0.8237</v>
       </c>
       <c r="L131">
-        <v>0.7413999999999999</v>
+        <v>0.7452</v>
       </c>
       <c r="M131">
         <v>168</v>
@@ -6383,22 +6383,22 @@
         <v>68</v>
       </c>
       <c r="G132">
-        <v>0.6375999999999999</v>
+        <v>0.632</v>
       </c>
       <c r="H132">
-        <v>0.5183</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="I132">
-        <v>0.578</v>
+        <v>0.5718</v>
       </c>
       <c r="J132">
-        <v>0.3624</v>
+        <v>0.368</v>
       </c>
       <c r="K132">
-        <v>0.4817</v>
+        <v>0.4884</v>
       </c>
       <c r="L132">
-        <v>0.422</v>
+        <v>0.4282</v>
       </c>
       <c r="M132">
         <v>168</v>
@@ -6515,22 +6515,22 @@
         <v>71</v>
       </c>
       <c r="G135">
-        <v>0.2705</v>
+        <v>0.2751</v>
       </c>
       <c r="H135">
         <v>0.1732</v>
       </c>
       <c r="I135">
-        <v>0.2218</v>
+        <v>0.2242</v>
       </c>
       <c r="J135">
-        <v>0.7295</v>
+        <v>0.7249</v>
       </c>
       <c r="K135">
         <v>0.8268</v>
       </c>
       <c r="L135">
-        <v>0.7782</v>
+        <v>0.7758</v>
       </c>
       <c r="M135">
         <v>168</v>
@@ -6562,19 +6562,19 @@
         <v>0.2781</v>
       </c>
       <c r="H136">
-        <v>0.1436</v>
+        <v>0.1494</v>
       </c>
       <c r="I136">
-        <v>0.2108</v>
+        <v>0.2138</v>
       </c>
       <c r="J136">
         <v>0.7219</v>
       </c>
       <c r="K136">
-        <v>0.8564000000000001</v>
+        <v>0.8506</v>
       </c>
       <c r="L136">
-        <v>0.7892</v>
+        <v>0.7862</v>
       </c>
       <c r="M136">
         <v>168</v>
@@ -6603,22 +6603,22 @@
         <v>49</v>
       </c>
       <c r="G137">
-        <v>0.3213</v>
+        <v>0.2541</v>
       </c>
       <c r="H137">
-        <v>0.1966</v>
+        <v>0.1457</v>
       </c>
       <c r="I137">
-        <v>0.259</v>
+        <v>0.1999</v>
       </c>
       <c r="J137">
-        <v>0.6787</v>
+        <v>0.7459</v>
       </c>
       <c r="K137">
-        <v>0.8034</v>
+        <v>0.8542999999999999</v>
       </c>
       <c r="L137">
-        <v>0.741</v>
+        <v>0.8001</v>
       </c>
       <c r="M137">
         <v>168</v>
@@ -6650,19 +6650,19 @@
         <v>0.4174</v>
       </c>
       <c r="H138">
-        <v>0.2627</v>
+        <v>0.2662</v>
       </c>
       <c r="I138">
-        <v>0.34</v>
+        <v>0.3418</v>
       </c>
       <c r="J138">
         <v>0.5826</v>
       </c>
       <c r="K138">
-        <v>0.7373</v>
+        <v>0.7338</v>
       </c>
       <c r="L138">
-        <v>0.66</v>
+        <v>0.6582</v>
       </c>
       <c r="M138">
         <v>168</v>
@@ -6691,22 +6691,22 @@
         <v>51</v>
       </c>
       <c r="G139">
-        <v>0.2853</v>
+        <v>0.2873</v>
       </c>
       <c r="H139">
         <v>0.1673</v>
       </c>
       <c r="I139">
-        <v>0.2263</v>
+        <v>0.2273</v>
       </c>
       <c r="J139">
-        <v>0.7147</v>
+        <v>0.7127</v>
       </c>
       <c r="K139">
         <v>0.8327</v>
       </c>
       <c r="L139">
-        <v>0.7737000000000001</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="M139">
         <v>168</v>
@@ -6779,22 +6779,22 @@
         <v>53</v>
       </c>
       <c r="G141">
-        <v>0.4782</v>
+        <v>0.473</v>
       </c>
       <c r="H141">
         <v>0.2879</v>
       </c>
       <c r="I141">
-        <v>0.383</v>
+        <v>0.3804</v>
       </c>
       <c r="J141">
-        <v>0.5218</v>
+        <v>0.527</v>
       </c>
       <c r="K141">
         <v>0.7121</v>
       </c>
       <c r="L141">
-        <v>0.617</v>
+        <v>0.6196</v>
       </c>
       <c r="M141">
         <v>168</v>
@@ -6826,19 +6826,19 @@
         <v>0.3612</v>
       </c>
       <c r="H142">
-        <v>0.2509</v>
+        <v>0.2559</v>
       </c>
       <c r="I142">
-        <v>0.3061</v>
+        <v>0.3086</v>
       </c>
       <c r="J142">
         <v>0.6388</v>
       </c>
       <c r="K142">
-        <v>0.7491</v>
+        <v>0.7441</v>
       </c>
       <c r="L142">
-        <v>0.6939</v>
+        <v>0.6914</v>
       </c>
       <c r="M142">
         <v>168</v>
@@ -6870,19 +6870,19 @@
         <v>0.6669</v>
       </c>
       <c r="H143">
-        <v>0.4736</v>
+        <v>0.4691</v>
       </c>
       <c r="I143">
-        <v>0.5702</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="J143">
         <v>0.3331</v>
       </c>
       <c r="K143">
-        <v>0.5264</v>
+        <v>0.5309</v>
       </c>
       <c r="L143">
-        <v>0.4298</v>
+        <v>0.432</v>
       </c>
       <c r="M143">
         <v>168</v>
@@ -6914,19 +6914,19 @@
         <v>0.3482</v>
       </c>
       <c r="H144">
-        <v>0.2134</v>
+        <v>0.2164</v>
       </c>
       <c r="I144">
-        <v>0.2808</v>
+        <v>0.2823</v>
       </c>
       <c r="J144">
         <v>0.6518</v>
       </c>
       <c r="K144">
-        <v>0.7866</v>
+        <v>0.7836</v>
       </c>
       <c r="L144">
-        <v>0.7192</v>
+        <v>0.7177</v>
       </c>
       <c r="M144">
         <v>168</v>
@@ -6958,19 +6958,19 @@
         <v>0.721</v>
       </c>
       <c r="H145">
-        <v>0.5775</v>
+        <v>0.5785</v>
       </c>
       <c r="I145">
-        <v>0.6492</v>
+        <v>0.6498</v>
       </c>
       <c r="J145">
         <v>0.279</v>
       </c>
       <c r="K145">
-        <v>0.4225</v>
+        <v>0.4215</v>
       </c>
       <c r="L145">
-        <v>0.3508</v>
+        <v>0.3502</v>
       </c>
       <c r="M145">
         <v>168</v>
@@ -6999,22 +6999,22 @@
         <v>58</v>
       </c>
       <c r="G146">
-        <v>0.2564</v>
+        <v>0.2583</v>
       </c>
       <c r="H146">
-        <v>0.1493</v>
+        <v>0.1503</v>
       </c>
       <c r="I146">
-        <v>0.2028</v>
+        <v>0.2043</v>
       </c>
       <c r="J146">
-        <v>0.7436</v>
+        <v>0.7417</v>
       </c>
       <c r="K146">
-        <v>0.8507</v>
+        <v>0.8497</v>
       </c>
       <c r="L146">
-        <v>0.7972</v>
+        <v>0.7957</v>
       </c>
       <c r="M146">
         <v>168</v>
@@ -7087,22 +7087,22 @@
         <v>60</v>
       </c>
       <c r="G148">
-        <v>0.6071</v>
+        <v>0.596</v>
       </c>
       <c r="H148">
-        <v>0.4843</v>
+        <v>0.4822</v>
       </c>
       <c r="I148">
-        <v>0.5457</v>
+        <v>0.5391</v>
       </c>
       <c r="J148">
-        <v>0.3929</v>
+        <v>0.404</v>
       </c>
       <c r="K148">
-        <v>0.5157</v>
+        <v>0.5178</v>
       </c>
       <c r="L148">
-        <v>0.4543</v>
+        <v>0.4609</v>
       </c>
       <c r="M148">
         <v>168</v>
@@ -7131,22 +7131,22 @@
         <v>61</v>
       </c>
       <c r="G149">
-        <v>0.3848</v>
+        <v>0.3839</v>
       </c>
       <c r="H149">
-        <v>0.2273</v>
+        <v>0.2298</v>
       </c>
       <c r="I149">
-        <v>0.306</v>
+        <v>0.3068</v>
       </c>
       <c r="J149">
-        <v>0.6152</v>
+        <v>0.6161</v>
       </c>
       <c r="K149">
-        <v>0.7727000000000001</v>
+        <v>0.7702</v>
       </c>
       <c r="L149">
-        <v>0.694</v>
+        <v>0.6932</v>
       </c>
       <c r="M149">
         <v>168</v>
@@ -7175,22 +7175,22 @@
         <v>62</v>
       </c>
       <c r="G150">
-        <v>0.3845</v>
+        <v>0.3872</v>
       </c>
       <c r="H150">
-        <v>0.213</v>
+        <v>0.2158</v>
       </c>
       <c r="I150">
-        <v>0.2988</v>
+        <v>0.3015</v>
       </c>
       <c r="J150">
-        <v>0.6155</v>
+        <v>0.6128</v>
       </c>
       <c r="K150">
-        <v>0.787</v>
+        <v>0.7842</v>
       </c>
       <c r="L150">
-        <v>0.7012</v>
+        <v>0.6985</v>
       </c>
       <c r="M150">
         <v>168</v>
@@ -7263,22 +7263,22 @@
         <v>64</v>
       </c>
       <c r="G152">
-        <v>0.6913</v>
+        <v>0.6899</v>
       </c>
       <c r="H152">
         <v>0.5767</v>
       </c>
       <c r="I152">
-        <v>0.634</v>
+        <v>0.6333</v>
       </c>
       <c r="J152">
-        <v>0.3087</v>
+        <v>0.3101</v>
       </c>
       <c r="K152">
         <v>0.4233</v>
       </c>
       <c r="L152">
-        <v>0.366</v>
+        <v>0.3667</v>
       </c>
       <c r="M152">
         <v>168</v>
@@ -7307,22 +7307,22 @@
         <v>65</v>
       </c>
       <c r="G153">
-        <v>0.241</v>
+        <v>0.2428</v>
       </c>
       <c r="H153">
-        <v>0.1383</v>
+        <v>0.1392</v>
       </c>
       <c r="I153">
-        <v>0.1896</v>
+        <v>0.191</v>
       </c>
       <c r="J153">
-        <v>0.759</v>
+        <v>0.7572</v>
       </c>
       <c r="K153">
-        <v>0.8617</v>
+        <v>0.8608</v>
       </c>
       <c r="L153">
-        <v>0.8104</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="M153">
         <v>168</v>
@@ -7351,22 +7351,22 @@
         <v>66</v>
       </c>
       <c r="G154">
-        <v>0.2491</v>
+        <v>0.2547</v>
       </c>
       <c r="H154">
-        <v>0.1329</v>
+        <v>0.1346</v>
       </c>
       <c r="I154">
-        <v>0.191</v>
+        <v>0.1946</v>
       </c>
       <c r="J154">
-        <v>0.7509</v>
+        <v>0.7453</v>
       </c>
       <c r="K154">
-        <v>0.8671</v>
+        <v>0.8653999999999999</v>
       </c>
       <c r="L154">
-        <v>0.8090000000000001</v>
+        <v>0.8054</v>
       </c>
       <c r="M154">
         <v>168</v>
@@ -7395,22 +7395,22 @@
         <v>67</v>
       </c>
       <c r="G155">
-        <v>0.3409</v>
+        <v>0.3375</v>
       </c>
       <c r="H155">
-        <v>0.2056</v>
+        <v>0.1949</v>
       </c>
       <c r="I155">
-        <v>0.2732</v>
+        <v>0.2662</v>
       </c>
       <c r="J155">
-        <v>0.6591</v>
+        <v>0.6625</v>
       </c>
       <c r="K155">
-        <v>0.7944</v>
+        <v>0.8051</v>
       </c>
       <c r="L155">
-        <v>0.7268</v>
+        <v>0.7338</v>
       </c>
       <c r="M155">
         <v>168</v>
@@ -7439,22 +7439,22 @@
         <v>68</v>
       </c>
       <c r="G156">
-        <v>0.6618000000000001</v>
+        <v>0.6424</v>
       </c>
       <c r="H156">
-        <v>0.5304</v>
+        <v>0.5284</v>
       </c>
       <c r="I156">
-        <v>0.5961</v>
+        <v>0.5854</v>
       </c>
       <c r="J156">
-        <v>0.3382</v>
+        <v>0.3576</v>
       </c>
       <c r="K156">
-        <v>0.4696</v>
+        <v>0.4716</v>
       </c>
       <c r="L156">
-        <v>0.4039</v>
+        <v>0.4146</v>
       </c>
       <c r="M156">
         <v>168</v>
@@ -7527,22 +7527,22 @@
         <v>70</v>
       </c>
       <c r="G158">
-        <v>0.7185</v>
+        <v>0.7148</v>
       </c>
       <c r="H158">
         <v>0.5674</v>
       </c>
       <c r="I158">
-        <v>0.643</v>
+        <v>0.6411</v>
       </c>
       <c r="J158">
-        <v>0.2815</v>
+        <v>0.2852</v>
       </c>
       <c r="K158">
         <v>0.4326</v>
       </c>
       <c r="L158">
-        <v>0.357</v>
+        <v>0.3589</v>
       </c>
       <c r="M158">
         <v>168</v>
@@ -7574,19 +7574,19 @@
         <v>0.3041</v>
       </c>
       <c r="H159">
-        <v>0.1877</v>
+        <v>0.1884</v>
       </c>
       <c r="I159">
-        <v>0.2459</v>
+        <v>0.2462</v>
       </c>
       <c r="J159">
         <v>0.6959</v>
       </c>
       <c r="K159">
-        <v>0.8123</v>
+        <v>0.8116</v>
       </c>
       <c r="L159">
-        <v>0.7541</v>
+        <v>0.7538</v>
       </c>
       <c r="M159">
         <v>168</v>
@@ -7615,22 +7615,22 @@
         <v>73</v>
       </c>
       <c r="G160">
-        <v>0.292</v>
+        <v>0.2932</v>
       </c>
       <c r="H160">
-        <v>0.1639</v>
+        <v>0.1656</v>
       </c>
       <c r="I160">
-        <v>0.228</v>
+        <v>0.2294</v>
       </c>
       <c r="J160">
-        <v>0.708</v>
+        <v>0.7068</v>
       </c>
       <c r="K160">
-        <v>0.8361</v>
+        <v>0.8344</v>
       </c>
       <c r="L160">
-        <v>0.772</v>
+        <v>0.7706</v>
       </c>
       <c r="M160">
         <v>168</v>
@@ -7659,22 +7659,22 @@
         <v>50</v>
       </c>
       <c r="G161">
-        <v>0.6756</v>
+        <v>0.7849</v>
       </c>
       <c r="H161">
-        <v>0.5073</v>
+        <v>0.6177</v>
       </c>
       <c r="I161">
-        <v>0.5914</v>
+        <v>0.7013</v>
       </c>
       <c r="J161">
-        <v>0.3244</v>
+        <v>0.2151</v>
       </c>
       <c r="K161">
-        <v>0.4927</v>
+        <v>0.3823</v>
       </c>
       <c r="L161">
-        <v>0.4086</v>
+        <v>0.2987</v>
       </c>
       <c r="M161">
         <v>168</v>
@@ -7703,22 +7703,22 @@
         <v>51</v>
       </c>
       <c r="G162">
-        <v>0.532</v>
+        <v>0.6574</v>
       </c>
       <c r="H162">
-        <v>0.3976</v>
+        <v>0.5017</v>
       </c>
       <c r="I162">
-        <v>0.4648</v>
+        <v>0.5796</v>
       </c>
       <c r="J162">
-        <v>0.468</v>
+        <v>0.3426</v>
       </c>
       <c r="K162">
-        <v>0.6024</v>
+        <v>0.4983</v>
       </c>
       <c r="L162">
-        <v>0.5352</v>
+        <v>0.4204</v>
       </c>
       <c r="M162">
         <v>168</v>
@@ -7747,22 +7747,22 @@
         <v>52</v>
       </c>
       <c r="G163">
-        <v>0.5800999999999999</v>
+        <v>0.6882</v>
       </c>
       <c r="H163">
-        <v>0.4422</v>
+        <v>0.5434</v>
       </c>
       <c r="I163">
-        <v>0.5112</v>
+        <v>0.6158</v>
       </c>
       <c r="J163">
-        <v>0.4199</v>
+        <v>0.3118</v>
       </c>
       <c r="K163">
-        <v>0.5578</v>
+        <v>0.4566</v>
       </c>
       <c r="L163">
-        <v>0.4888</v>
+        <v>0.3842</v>
       </c>
       <c r="M163">
         <v>168</v>
@@ -7791,22 +7791,22 @@
         <v>53</v>
       </c>
       <c r="G164">
-        <v>0.679</v>
+        <v>0.7437</v>
       </c>
       <c r="H164">
-        <v>0.5392</v>
+        <v>0.6232</v>
       </c>
       <c r="I164">
-        <v>0.6091</v>
+        <v>0.6834</v>
       </c>
       <c r="J164">
-        <v>0.321</v>
+        <v>0.2563</v>
       </c>
       <c r="K164">
-        <v>0.4608</v>
+        <v>0.3768</v>
       </c>
       <c r="L164">
-        <v>0.3909</v>
+        <v>0.3166</v>
       </c>
       <c r="M164">
         <v>168</v>
@@ -7835,22 +7835,22 @@
         <v>54</v>
       </c>
       <c r="G165">
-        <v>0.6649</v>
+        <v>0.773</v>
       </c>
       <c r="H165">
-        <v>0.4741</v>
+        <v>0.5891999999999999</v>
       </c>
       <c r="I165">
-        <v>0.5695</v>
+        <v>0.6811</v>
       </c>
       <c r="J165">
-        <v>0.3351</v>
+        <v>0.227</v>
       </c>
       <c r="K165">
-        <v>0.5259</v>
+        <v>0.4108</v>
       </c>
       <c r="L165">
-        <v>0.4305</v>
+        <v>0.3189</v>
       </c>
       <c r="M165">
         <v>168</v>
@@ -7879,22 +7879,22 @@
         <v>55</v>
       </c>
       <c r="G166">
-        <v>0.8358</v>
+        <v>0.8602</v>
       </c>
       <c r="H166">
-        <v>0.7179</v>
+        <v>0.7585</v>
       </c>
       <c r="I166">
-        <v>0.7768</v>
+        <v>0.8094</v>
       </c>
       <c r="J166">
-        <v>0.1642</v>
+        <v>0.1398</v>
       </c>
       <c r="K166">
-        <v>0.2821</v>
+        <v>0.2415</v>
       </c>
       <c r="L166">
-        <v>0.2232</v>
+        <v>0.1906</v>
       </c>
       <c r="M166">
         <v>168</v>
@@ -7923,22 +7923,22 @@
         <v>56</v>
       </c>
       <c r="G167">
-        <v>0.5869</v>
+        <v>0.7121</v>
       </c>
       <c r="H167">
-        <v>0.4655</v>
+        <v>0.5736</v>
       </c>
       <c r="I167">
-        <v>0.5262</v>
+        <v>0.6428</v>
       </c>
       <c r="J167">
-        <v>0.4131</v>
+        <v>0.2879</v>
       </c>
       <c r="K167">
-        <v>0.5345</v>
+        <v>0.4264</v>
       </c>
       <c r="L167">
-        <v>0.4738</v>
+        <v>0.3572</v>
       </c>
       <c r="M167">
         <v>168</v>
@@ -7967,22 +7967,22 @@
         <v>57</v>
       </c>
       <c r="G168">
-        <v>0.8551</v>
+        <v>0.8706</v>
       </c>
       <c r="H168">
-        <v>0.7576000000000001</v>
+        <v>0.7886</v>
       </c>
       <c r="I168">
-        <v>0.8064</v>
+        <v>0.8296</v>
       </c>
       <c r="J168">
-        <v>0.1449</v>
+        <v>0.1294</v>
       </c>
       <c r="K168">
-        <v>0.2424</v>
+        <v>0.2114</v>
       </c>
       <c r="L168">
-        <v>0.1936</v>
+        <v>0.1704</v>
       </c>
       <c r="M168">
         <v>168</v>
@@ -8011,22 +8011,22 @@
         <v>58</v>
       </c>
       <c r="G169">
-        <v>0.4373</v>
+        <v>0.549</v>
       </c>
       <c r="H169">
-        <v>0.3035</v>
+        <v>0.4256</v>
       </c>
       <c r="I169">
-        <v>0.3704</v>
+        <v>0.4873</v>
       </c>
       <c r="J169">
-        <v>0.5627</v>
+        <v>0.451</v>
       </c>
       <c r="K169">
-        <v>0.6965</v>
+        <v>0.5744</v>
       </c>
       <c r="L169">
-        <v>0.6296</v>
+        <v>0.5127</v>
       </c>
       <c r="M169">
         <v>168</v>
@@ -8055,22 +8055,22 @@
         <v>59</v>
       </c>
       <c r="G170">
-        <v>0.68</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="H170">
-        <v>0.5547</v>
+        <v>0.6329</v>
       </c>
       <c r="I170">
-        <v>0.6173999999999999</v>
+        <v>0.7088</v>
       </c>
       <c r="J170">
-        <v>0.32</v>
+        <v>0.2152</v>
       </c>
       <c r="K170">
-        <v>0.4453</v>
+        <v>0.3671</v>
       </c>
       <c r="L170">
-        <v>0.3826</v>
+        <v>0.2912</v>
       </c>
       <c r="M170">
         <v>168</v>
@@ -8099,22 +8099,22 @@
         <v>60</v>
       </c>
       <c r="G171">
-        <v>0.8038</v>
+        <v>0.8505</v>
       </c>
       <c r="H171">
-        <v>0.6965</v>
+        <v>0.7633</v>
       </c>
       <c r="I171">
-        <v>0.7502</v>
+        <v>0.8069</v>
       </c>
       <c r="J171">
-        <v>0.1962</v>
+        <v>0.1495</v>
       </c>
       <c r="K171">
-        <v>0.3035</v>
+        <v>0.2367</v>
       </c>
       <c r="L171">
-        <v>0.2498</v>
+        <v>0.1931</v>
       </c>
       <c r="M171">
         <v>168</v>
@@ -8143,22 +8143,22 @@
         <v>61</v>
       </c>
       <c r="G172">
-        <v>0.6676</v>
+        <v>0.7756</v>
       </c>
       <c r="H172">
-        <v>0.4821</v>
+        <v>0.6216</v>
       </c>
       <c r="I172">
-        <v>0.5748</v>
+        <v>0.6986</v>
       </c>
       <c r="J172">
-        <v>0.3324</v>
+        <v>0.2244</v>
       </c>
       <c r="K172">
-        <v>0.5179</v>
+        <v>0.3784</v>
       </c>
       <c r="L172">
-        <v>0.4252</v>
+        <v>0.3014</v>
       </c>
       <c r="M172">
         <v>168</v>
@@ -8187,22 +8187,22 @@
         <v>62</v>
       </c>
       <c r="G173">
-        <v>0.6158</v>
+        <v>0.7294</v>
       </c>
       <c r="H173">
-        <v>0.4873</v>
+        <v>0.5897</v>
       </c>
       <c r="I173">
-        <v>0.5516</v>
+        <v>0.6596</v>
       </c>
       <c r="J173">
-        <v>0.3842</v>
+        <v>0.2706</v>
       </c>
       <c r="K173">
-        <v>0.5127</v>
+        <v>0.4103</v>
       </c>
       <c r="L173">
-        <v>0.4484</v>
+        <v>0.3404</v>
       </c>
       <c r="M173">
         <v>168</v>
@@ -8231,22 +8231,22 @@
         <v>63</v>
       </c>
       <c r="G174">
-        <v>0.6732</v>
+        <v>0.7761</v>
       </c>
       <c r="H174">
-        <v>0.5245</v>
+        <v>0.6029</v>
       </c>
       <c r="I174">
-        <v>0.5988</v>
+        <v>0.6895</v>
       </c>
       <c r="J174">
-        <v>0.3268</v>
+        <v>0.2239</v>
       </c>
       <c r="K174">
-        <v>0.4755</v>
+        <v>0.3971</v>
       </c>
       <c r="L174">
-        <v>0.4012</v>
+        <v>0.3105</v>
       </c>
       <c r="M174">
         <v>168</v>
@@ -8275,22 +8275,22 @@
         <v>64</v>
       </c>
       <c r="G175">
-        <v>0.8443000000000001</v>
+        <v>0.8697</v>
       </c>
       <c r="H175">
-        <v>0.7542</v>
+        <v>0.7975</v>
       </c>
       <c r="I175">
-        <v>0.7992</v>
+        <v>0.8336</v>
       </c>
       <c r="J175">
-        <v>0.1557</v>
+        <v>0.1303</v>
       </c>
       <c r="K175">
-        <v>0.2458</v>
+        <v>0.2025</v>
       </c>
       <c r="L175">
-        <v>0.2008</v>
+        <v>0.1664</v>
       </c>
       <c r="M175">
         <v>168</v>
@@ -8319,22 +8319,22 @@
         <v>65</v>
       </c>
       <c r="G176">
-        <v>0.3959</v>
+        <v>0.5199</v>
       </c>
       <c r="H176">
-        <v>0.2387</v>
+        <v>0.3427</v>
       </c>
       <c r="I176">
-        <v>0.3173</v>
+        <v>0.4313</v>
       </c>
       <c r="J176">
-        <v>0.6041</v>
+        <v>0.4801</v>
       </c>
       <c r="K176">
-        <v>0.7613</v>
+        <v>0.6573</v>
       </c>
       <c r="L176">
-        <v>0.6827</v>
+        <v>0.5687</v>
       </c>
       <c r="M176">
         <v>168</v>
@@ -8363,22 +8363,22 @@
         <v>66</v>
       </c>
       <c r="G177">
-        <v>0.3642</v>
+        <v>0.4839</v>
       </c>
       <c r="H177">
-        <v>0.2278</v>
+        <v>0.3347</v>
       </c>
       <c r="I177">
-        <v>0.296</v>
+        <v>0.4093</v>
       </c>
       <c r="J177">
-        <v>0.6358</v>
+        <v>0.5161</v>
       </c>
       <c r="K177">
-        <v>0.7722</v>
+        <v>0.6653</v>
       </c>
       <c r="L177">
-        <v>0.704</v>
+        <v>0.5907</v>
       </c>
       <c r="M177">
         <v>168</v>
@@ -8407,22 +8407,22 @@
         <v>67</v>
       </c>
       <c r="G178">
-        <v>0.5815</v>
+        <v>0.6841</v>
       </c>
       <c r="H178">
-        <v>0.4386</v>
+        <v>0.5639</v>
       </c>
       <c r="I178">
-        <v>0.51</v>
+        <v>0.624</v>
       </c>
       <c r="J178">
-        <v>0.4185</v>
+        <v>0.3159</v>
       </c>
       <c r="K178">
-        <v>0.5614</v>
+        <v>0.4361</v>
       </c>
       <c r="L178">
-        <v>0.49</v>
+        <v>0.376</v>
       </c>
       <c r="M178">
         <v>168</v>
@@ -8451,22 +8451,22 @@
         <v>68</v>
       </c>
       <c r="G179">
-        <v>0.8472</v>
+        <v>0.8823</v>
       </c>
       <c r="H179">
-        <v>0.7245</v>
+        <v>0.7709</v>
       </c>
       <c r="I179">
-        <v>0.7858000000000001</v>
+        <v>0.8266</v>
       </c>
       <c r="J179">
-        <v>0.1528</v>
+        <v>0.1177</v>
       </c>
       <c r="K179">
-        <v>0.2755</v>
+        <v>0.2291</v>
       </c>
       <c r="L179">
-        <v>0.2142</v>
+        <v>0.1734</v>
       </c>
       <c r="M179">
         <v>168</v>
@@ -8495,22 +8495,22 @@
         <v>69</v>
       </c>
       <c r="G180">
-        <v>0.839</v>
+        <v>0.8749</v>
       </c>
       <c r="H180">
-        <v>0.7156</v>
+        <v>0.7708</v>
       </c>
       <c r="I180">
-        <v>0.7773</v>
+        <v>0.8228</v>
       </c>
       <c r="J180">
-        <v>0.161</v>
+        <v>0.1251</v>
       </c>
       <c r="K180">
-        <v>0.2844</v>
+        <v>0.2292</v>
       </c>
       <c r="L180">
-        <v>0.2227</v>
+        <v>0.1772</v>
       </c>
       <c r="M180">
         <v>168</v>
@@ -8539,22 +8539,22 @@
         <v>70</v>
       </c>
       <c r="G181">
-        <v>0.8522999999999999</v>
+        <v>0.8889</v>
       </c>
       <c r="H181">
-        <v>0.7482</v>
+        <v>0.8004</v>
       </c>
       <c r="I181">
-        <v>0.8002</v>
+        <v>0.8446</v>
       </c>
       <c r="J181">
-        <v>0.1477</v>
+        <v>0.1111</v>
       </c>
       <c r="K181">
-        <v>0.2518</v>
+        <v>0.1996</v>
       </c>
       <c r="L181">
-        <v>0.1998</v>
+        <v>0.1554</v>
       </c>
       <c r="M181">
         <v>168</v>
@@ -8583,22 +8583,22 @@
         <v>71</v>
       </c>
       <c r="G182">
-        <v>0.5293</v>
+        <v>0.6481</v>
       </c>
       <c r="H182">
-        <v>0.4125</v>
+        <v>0.4902</v>
       </c>
       <c r="I182">
-        <v>0.4709</v>
+        <v>0.5692</v>
       </c>
       <c r="J182">
-        <v>0.4707</v>
+        <v>0.3519</v>
       </c>
       <c r="K182">
-        <v>0.5875</v>
+        <v>0.5098</v>
       </c>
       <c r="L182">
-        <v>0.5291</v>
+        <v>0.4308</v>
       </c>
       <c r="M182">
         <v>168</v>
@@ -8627,22 +8627,22 @@
         <v>73</v>
       </c>
       <c r="G183">
-        <v>0.5007</v>
+        <v>0.6234</v>
       </c>
       <c r="H183">
-        <v>0.359</v>
+        <v>0.4572</v>
       </c>
       <c r="I183">
-        <v>0.4298</v>
+        <v>0.5403</v>
       </c>
       <c r="J183">
-        <v>0.4993</v>
+        <v>0.3766</v>
       </c>
       <c r="K183">
-        <v>0.641</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="L183">
-        <v>0.5702</v>
+        <v>0.4597</v>
       </c>
       <c r="M183">
         <v>168</v>
@@ -8674,19 +8674,19 @@
         <v>0.4297</v>
       </c>
       <c r="H184">
-        <v>0.2528</v>
+        <v>0.2565</v>
       </c>
       <c r="I184">
-        <v>0.3413</v>
+        <v>0.3431</v>
       </c>
       <c r="J184">
         <v>0.5703</v>
       </c>
       <c r="K184">
-        <v>0.7472</v>
+        <v>0.7435</v>
       </c>
       <c r="L184">
-        <v>0.6587</v>
+        <v>0.6569</v>
       </c>
       <c r="M184">
         <v>168</v>
@@ -8762,19 +8762,19 @@
         <v>0.6173999999999999</v>
       </c>
       <c r="H186">
-        <v>0.4146</v>
+        <v>0.4071</v>
       </c>
       <c r="I186">
-        <v>0.516</v>
+        <v>0.5122</v>
       </c>
       <c r="J186">
         <v>0.3826</v>
       </c>
       <c r="K186">
-        <v>0.5854</v>
+        <v>0.5929</v>
       </c>
       <c r="L186">
-        <v>0.484</v>
+        <v>0.4878</v>
       </c>
       <c r="M186">
         <v>168</v>
@@ -8938,19 +8938,19 @@
         <v>0.8239</v>
       </c>
       <c r="H190">
-        <v>0.7201</v>
+        <v>0.7192</v>
       </c>
       <c r="I190">
-        <v>0.772</v>
+        <v>0.7716</v>
       </c>
       <c r="J190">
         <v>0.1761</v>
       </c>
       <c r="K190">
-        <v>0.2799</v>
+        <v>0.2808</v>
       </c>
       <c r="L190">
-        <v>0.228</v>
+        <v>0.2284</v>
       </c>
       <c r="M190">
         <v>168</v>
@@ -8982,19 +8982,19 @@
         <v>0.3506</v>
       </c>
       <c r="H191">
-        <v>0.2106</v>
+        <v>0.2134</v>
       </c>
       <c r="I191">
-        <v>0.2806</v>
+        <v>0.282</v>
       </c>
       <c r="J191">
         <v>0.6494</v>
       </c>
       <c r="K191">
-        <v>0.7894</v>
+        <v>0.7866</v>
       </c>
       <c r="L191">
-        <v>0.7194</v>
+        <v>0.718</v>
       </c>
       <c r="M191">
         <v>168</v>
@@ -9070,19 +9070,19 @@
         <v>0.7744</v>
       </c>
       <c r="H193">
-        <v>0.6092</v>
+        <v>0.5991</v>
       </c>
       <c r="I193">
-        <v>0.6918</v>
+        <v>0.6868</v>
       </c>
       <c r="J193">
         <v>0.2256</v>
       </c>
       <c r="K193">
-        <v>0.3908</v>
+        <v>0.4009</v>
       </c>
       <c r="L193">
-        <v>0.3082</v>
+        <v>0.3132</v>
       </c>
       <c r="M193">
         <v>168</v>
@@ -9114,19 +9114,19 @@
         <v>0.537</v>
       </c>
       <c r="H194">
-        <v>0.4165</v>
+        <v>0.4175</v>
       </c>
       <c r="I194">
-        <v>0.4768</v>
+        <v>0.4772</v>
       </c>
       <c r="J194">
         <v>0.463</v>
       </c>
       <c r="K194">
-        <v>0.5835</v>
+        <v>0.5825</v>
       </c>
       <c r="L194">
-        <v>0.5232</v>
+        <v>0.5228</v>
       </c>
       <c r="M194">
         <v>168</v>
@@ -9202,19 +9202,19 @@
         <v>0.5683</v>
       </c>
       <c r="H196">
-        <v>0.4207</v>
+        <v>0.419</v>
       </c>
       <c r="I196">
-        <v>0.4945</v>
+        <v>0.4936</v>
       </c>
       <c r="J196">
         <v>0.4317</v>
       </c>
       <c r="K196">
-        <v>0.5793</v>
+        <v>0.581</v>
       </c>
       <c r="L196">
-        <v>0.5054999999999999</v>
+        <v>0.5064</v>
       </c>
       <c r="M196">
         <v>168</v>
@@ -9246,19 +9246,19 @@
         <v>0.7996</v>
       </c>
       <c r="H197">
-        <v>0.7208</v>
+        <v>0.7093</v>
       </c>
       <c r="I197">
-        <v>0.7602</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="J197">
         <v>0.2004</v>
       </c>
       <c r="K197">
-        <v>0.2792</v>
+        <v>0.2907</v>
       </c>
       <c r="L197">
-        <v>0.2398</v>
+        <v>0.2455</v>
       </c>
       <c r="M197">
         <v>168</v>
@@ -9290,19 +9290,19 @@
         <v>0.3123</v>
       </c>
       <c r="H198">
-        <v>0.1778</v>
+        <v>0.1803</v>
       </c>
       <c r="I198">
-        <v>0.245</v>
+        <v>0.2463</v>
       </c>
       <c r="J198">
         <v>0.6877</v>
       </c>
       <c r="K198">
-        <v>0.8222</v>
+        <v>0.8197</v>
       </c>
       <c r="L198">
-        <v>0.755</v>
+        <v>0.7537</v>
       </c>
       <c r="M198">
         <v>168</v>
@@ -9375,22 +9375,22 @@
         <v>67</v>
       </c>
       <c r="G200">
-        <v>0.464</v>
+        <v>0.4622</v>
       </c>
       <c r="H200">
-        <v>0.3808</v>
+        <v>0.354</v>
       </c>
       <c r="I200">
-        <v>0.4224</v>
+        <v>0.4081</v>
       </c>
       <c r="J200">
-        <v>0.536</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="K200">
-        <v>0.6192</v>
+        <v>0.646</v>
       </c>
       <c r="L200">
-        <v>0.5776</v>
+        <v>0.5919</v>
       </c>
       <c r="M200">
         <v>168</v>
@@ -9419,22 +9419,22 @@
         <v>68</v>
       </c>
       <c r="G201">
-        <v>0.7895</v>
+        <v>0.7831</v>
       </c>
       <c r="H201">
-        <v>0.6793</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="I201">
-        <v>0.7344000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="J201">
-        <v>0.2105</v>
+        <v>0.2169</v>
       </c>
       <c r="K201">
-        <v>0.3207</v>
+        <v>0.3432</v>
       </c>
       <c r="L201">
-        <v>0.2656</v>
+        <v>0.28</v>
       </c>
       <c r="M201">
         <v>168</v>
@@ -9463,22 +9463,22 @@
         <v>69</v>
       </c>
       <c r="G202">
-        <v>0.7935</v>
+        <v>0.791</v>
       </c>
       <c r="H202">
-        <v>0.6391</v>
+        <v>0.6361</v>
       </c>
       <c r="I202">
-        <v>0.7163</v>
+        <v>0.7136</v>
       </c>
       <c r="J202">
-        <v>0.2065</v>
+        <v>0.209</v>
       </c>
       <c r="K202">
-        <v>0.3609</v>
+        <v>0.3639</v>
       </c>
       <c r="L202">
-        <v>0.2837</v>
+        <v>0.2864</v>
       </c>
       <c r="M202">
         <v>168</v>
@@ -9507,22 +9507,22 @@
         <v>70</v>
       </c>
       <c r="G203">
-        <v>0.8314</v>
+        <v>0.8288</v>
       </c>
       <c r="H203">
         <v>0.7062</v>
       </c>
       <c r="I203">
-        <v>0.7688</v>
+        <v>0.7675</v>
       </c>
       <c r="J203">
-        <v>0.1686</v>
+        <v>0.1712</v>
       </c>
       <c r="K203">
         <v>0.2938</v>
       </c>
       <c r="L203">
-        <v>0.2312</v>
+        <v>0.2325</v>
       </c>
       <c r="M203">
         <v>168</v>
@@ -9551,22 +9551,22 @@
         <v>71</v>
       </c>
       <c r="G204">
-        <v>0.4198</v>
+        <v>0.4146</v>
       </c>
       <c r="H204">
-        <v>0.2908</v>
+        <v>0.2928</v>
       </c>
       <c r="I204">
-        <v>0.3553</v>
+        <v>0.3537</v>
       </c>
       <c r="J204">
-        <v>0.5802</v>
+        <v>0.5854</v>
       </c>
       <c r="K204">
-        <v>0.7092000000000001</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="L204">
-        <v>0.6447000000000001</v>
+        <v>0.6463</v>
       </c>
       <c r="M204">
         <v>168</v>
@@ -9595,22 +9595,22 @@
         <v>73</v>
       </c>
       <c r="G205">
-        <v>0.4246</v>
+        <v>0.4229</v>
       </c>
       <c r="H205">
-        <v>0.2745</v>
+        <v>0.2585</v>
       </c>
       <c r="I205">
-        <v>0.3496</v>
+        <v>0.3407</v>
       </c>
       <c r="J205">
-        <v>0.5754</v>
+        <v>0.5770999999999999</v>
       </c>
       <c r="K205">
-        <v>0.7255</v>
+        <v>0.7415</v>
       </c>
       <c r="L205">
-        <v>0.6504</v>
+        <v>0.6593</v>
       </c>
       <c r="M205">
         <v>168</v>
@@ -9683,22 +9683,22 @@
         <v>53</v>
       </c>
       <c r="G207">
-        <v>0.7115</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="H207">
         <v>0.5986</v>
       </c>
       <c r="I207">
-        <v>0.655</v>
+        <v>0.6534</v>
       </c>
       <c r="J207">
-        <v>0.2885</v>
+        <v>0.2918</v>
       </c>
       <c r="K207">
         <v>0.4014</v>
       </c>
       <c r="L207">
-        <v>0.345</v>
+        <v>0.3466</v>
       </c>
       <c r="M207">
         <v>168</v>
@@ -9727,22 +9727,22 @@
         <v>54</v>
       </c>
       <c r="G208">
-        <v>0.7025</v>
+        <v>0.6999</v>
       </c>
       <c r="H208">
         <v>0.5286999999999999</v>
       </c>
       <c r="I208">
-        <v>0.6156</v>
+        <v>0.6143</v>
       </c>
       <c r="J208">
-        <v>0.2975</v>
+        <v>0.3001</v>
       </c>
       <c r="K208">
         <v>0.4713</v>
       </c>
       <c r="L208">
-        <v>0.3844</v>
+        <v>0.3857</v>
       </c>
       <c r="M208">
         <v>168</v>
@@ -9771,22 +9771,22 @@
         <v>55</v>
       </c>
       <c r="G209">
-        <v>0.8612</v>
+        <v>0.8542</v>
       </c>
       <c r="H209">
         <v>0.7346</v>
       </c>
       <c r="I209">
-        <v>0.7979000000000001</v>
+        <v>0.7944</v>
       </c>
       <c r="J209">
-        <v>0.1388</v>
+        <v>0.1458</v>
       </c>
       <c r="K209">
         <v>0.2654</v>
       </c>
       <c r="L209">
-        <v>0.2021</v>
+        <v>0.2056</v>
       </c>
       <c r="M209">
         <v>168</v>
@@ -9815,22 +9815,22 @@
         <v>56</v>
       </c>
       <c r="G210">
-        <v>0.6354</v>
+        <v>0.6309</v>
       </c>
       <c r="H210">
-        <v>0.503</v>
+        <v>0.4995</v>
       </c>
       <c r="I210">
-        <v>0.5692</v>
+        <v>0.5652</v>
       </c>
       <c r="J210">
-        <v>0.3646</v>
+        <v>0.3691</v>
       </c>
       <c r="K210">
-        <v>0.497</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="L210">
-        <v>0.4308</v>
+        <v>0.4348</v>
       </c>
       <c r="M210">
         <v>168</v>
@@ -9859,22 +9859,22 @@
         <v>57</v>
       </c>
       <c r="G211">
-        <v>0.881</v>
+        <v>0.879</v>
       </c>
       <c r="H211">
         <v>0.7966</v>
       </c>
       <c r="I211">
-        <v>0.8388</v>
+        <v>0.8378</v>
       </c>
       <c r="J211">
-        <v>0.119</v>
+        <v>0.121</v>
       </c>
       <c r="K211">
         <v>0.2034</v>
       </c>
       <c r="L211">
-        <v>0.1612</v>
+        <v>0.1622</v>
       </c>
       <c r="M211">
         <v>168</v>
@@ -9903,22 +9903,22 @@
         <v>58</v>
       </c>
       <c r="G212">
-        <v>0.4973</v>
+        <v>0.4994</v>
       </c>
       <c r="H212">
-        <v>0.3688</v>
+        <v>0.3812</v>
       </c>
       <c r="I212">
-        <v>0.4331</v>
+        <v>0.4403</v>
       </c>
       <c r="J212">
-        <v>0.5027</v>
+        <v>0.5006</v>
       </c>
       <c r="K212">
-        <v>0.6312</v>
+        <v>0.6188</v>
       </c>
       <c r="L212">
-        <v>0.5669</v>
+        <v>0.5597</v>
       </c>
       <c r="M212">
         <v>168</v>
@@ -9947,22 +9947,22 @@
         <v>59</v>
       </c>
       <c r="G213">
-        <v>0.7562</v>
+        <v>0.7575</v>
       </c>
       <c r="H213">
-        <v>0.5639999999999999</v>
+        <v>0.5564</v>
       </c>
       <c r="I213">
-        <v>0.6601</v>
+        <v>0.6569</v>
       </c>
       <c r="J213">
-        <v>0.2438</v>
+        <v>0.2425</v>
       </c>
       <c r="K213">
-        <v>0.436</v>
+        <v>0.4436</v>
       </c>
       <c r="L213">
-        <v>0.3399</v>
+        <v>0.3431</v>
       </c>
       <c r="M213">
         <v>168</v>
@@ -9991,22 +9991,22 @@
         <v>60</v>
       </c>
       <c r="G214">
-        <v>0.8425</v>
+        <v>0.8415</v>
       </c>
       <c r="H214">
-        <v>0.7205</v>
+        <v>0.7186</v>
       </c>
       <c r="I214">
-        <v>0.7815</v>
+        <v>0.78</v>
       </c>
       <c r="J214">
-        <v>0.1575</v>
+        <v>0.1585</v>
       </c>
       <c r="K214">
-        <v>0.2795</v>
+        <v>0.2814</v>
       </c>
       <c r="L214">
-        <v>0.2185</v>
+        <v>0.22</v>
       </c>
       <c r="M214">
         <v>168</v>
@@ -10038,19 +10038,19 @@
         <v>0.6986</v>
       </c>
       <c r="H215">
-        <v>0.5486</v>
+        <v>0.5457</v>
       </c>
       <c r="I215">
-        <v>0.6236</v>
+        <v>0.6222</v>
       </c>
       <c r="J215">
         <v>0.3014</v>
       </c>
       <c r="K215">
-        <v>0.4514</v>
+        <v>0.4543</v>
       </c>
       <c r="L215">
-        <v>0.3764</v>
+        <v>0.3778</v>
       </c>
       <c r="M215">
         <v>168</v>
@@ -10123,22 +10123,22 @@
         <v>63</v>
       </c>
       <c r="G217">
-        <v>0.7316</v>
+        <v>0.728</v>
       </c>
       <c r="H217">
         <v>0.5627</v>
       </c>
       <c r="I217">
-        <v>0.6472</v>
+        <v>0.6454</v>
       </c>
       <c r="J217">
-        <v>0.2684</v>
+        <v>0.272</v>
       </c>
       <c r="K217">
         <v>0.4373</v>
       </c>
       <c r="L217">
-        <v>0.3528</v>
+        <v>0.3546</v>
       </c>
       <c r="M217">
         <v>168</v>
@@ -10167,22 +10167,22 @@
         <v>64</v>
       </c>
       <c r="G218">
-        <v>0.8766</v>
+        <v>0.872</v>
       </c>
       <c r="H218">
         <v>0.7689</v>
       </c>
       <c r="I218">
-        <v>0.8228</v>
+        <v>0.8204</v>
       </c>
       <c r="J218">
-        <v>0.1234</v>
+        <v>0.128</v>
       </c>
       <c r="K218">
         <v>0.2311</v>
       </c>
       <c r="L218">
-        <v>0.1772</v>
+        <v>0.1796</v>
       </c>
       <c r="M218">
         <v>168</v>
@@ -10211,22 +10211,22 @@
         <v>65</v>
       </c>
       <c r="G219">
-        <v>0.4188</v>
+        <v>0.4208</v>
       </c>
       <c r="H219">
-        <v>0.3045</v>
+        <v>0.3102</v>
       </c>
       <c r="I219">
-        <v>0.3617</v>
+        <v>0.3655</v>
       </c>
       <c r="J219">
-        <v>0.5812</v>
+        <v>0.5792</v>
       </c>
       <c r="K219">
-        <v>0.6955</v>
+        <v>0.6898</v>
       </c>
       <c r="L219">
-        <v>0.6383</v>
+        <v>0.6345</v>
       </c>
       <c r="M219">
         <v>168</v>
@@ -10299,22 +10299,22 @@
         <v>67</v>
       </c>
       <c r="G221">
-        <v>0.6591</v>
+        <v>0.6521</v>
       </c>
       <c r="H221">
-        <v>0.5279</v>
+        <v>0.5137</v>
       </c>
       <c r="I221">
-        <v>0.5935</v>
+        <v>0.5829</v>
       </c>
       <c r="J221">
-        <v>0.3409</v>
+        <v>0.3479</v>
       </c>
       <c r="K221">
-        <v>0.4721</v>
+        <v>0.4863</v>
       </c>
       <c r="L221">
-        <v>0.4065</v>
+        <v>0.4171</v>
       </c>
       <c r="M221">
         <v>168</v>
@@ -10343,22 +10343,22 @@
         <v>68</v>
       </c>
       <c r="G222">
-        <v>0.8757</v>
+        <v>0.8626</v>
       </c>
       <c r="H222">
-        <v>0.7477</v>
+        <v>0.738</v>
       </c>
       <c r="I222">
-        <v>0.8117</v>
+        <v>0.8003</v>
       </c>
       <c r="J222">
-        <v>0.1243</v>
+        <v>0.1374</v>
       </c>
       <c r="K222">
-        <v>0.2523</v>
+        <v>0.262</v>
       </c>
       <c r="L222">
-        <v>0.1883</v>
+        <v>0.1997</v>
       </c>
       <c r="M222">
         <v>168</v>
@@ -10390,19 +10390,19 @@
         <v>0.8683</v>
       </c>
       <c r="H223">
-        <v>0.7333</v>
+        <v>0.7306</v>
       </c>
       <c r="I223">
-        <v>0.8008</v>
+        <v>0.7994</v>
       </c>
       <c r="J223">
         <v>0.1317</v>
       </c>
       <c r="K223">
-        <v>0.2667</v>
+        <v>0.2694</v>
       </c>
       <c r="L223">
-        <v>0.1992</v>
+        <v>0.2006</v>
       </c>
       <c r="M223">
         <v>168</v>
@@ -10431,22 +10431,22 @@
         <v>70</v>
       </c>
       <c r="G224">
-        <v>0.876</v>
+        <v>0.8738</v>
       </c>
       <c r="H224">
         <v>0.7557</v>
       </c>
       <c r="I224">
-        <v>0.8158</v>
+        <v>0.8148</v>
       </c>
       <c r="J224">
-        <v>0.124</v>
+        <v>0.1262</v>
       </c>
       <c r="K224">
         <v>0.2443</v>
       </c>
       <c r="L224">
-        <v>0.1842</v>
+        <v>0.1852</v>
       </c>
       <c r="M224">
         <v>168</v>
@@ -10475,22 +10475,22 @@
         <v>71</v>
       </c>
       <c r="G225">
-        <v>0.5642</v>
+        <v>0.5574</v>
       </c>
       <c r="H225">
-        <v>0.4337</v>
+        <v>0.4217</v>
       </c>
       <c r="I225">
-        <v>0.499</v>
+        <v>0.4896</v>
       </c>
       <c r="J225">
-        <v>0.4358</v>
+        <v>0.4426</v>
       </c>
       <c r="K225">
-        <v>0.5663</v>
+        <v>0.5783</v>
       </c>
       <c r="L225">
-        <v>0.501</v>
+        <v>0.5104</v>
       </c>
       <c r="M225">
         <v>168</v>
@@ -10566,19 +10566,19 @@
         <v>0.6663</v>
       </c>
       <c r="H227">
-        <v>0.5372</v>
+        <v>0.5382</v>
       </c>
       <c r="I227">
-        <v>0.6018</v>
+        <v>0.6022</v>
       </c>
       <c r="J227">
         <v>0.3337</v>
       </c>
       <c r="K227">
-        <v>0.4628</v>
+        <v>0.4618</v>
       </c>
       <c r="L227">
-        <v>0.3982</v>
+        <v>0.3978</v>
       </c>
       <c r="M227">
         <v>168</v>
@@ -10651,22 +10651,22 @@
         <v>55</v>
       </c>
       <c r="G229">
-        <v>0.8445</v>
+        <v>0.8439</v>
       </c>
       <c r="H229">
         <v>0.7012</v>
       </c>
       <c r="I229">
-        <v>0.7728</v>
+        <v>0.7726</v>
       </c>
       <c r="J229">
-        <v>0.1555</v>
+        <v>0.1561</v>
       </c>
       <c r="K229">
         <v>0.2988</v>
       </c>
       <c r="L229">
-        <v>0.2272</v>
+        <v>0.2274</v>
       </c>
       <c r="M229">
         <v>168</v>
@@ -10739,22 +10739,22 @@
         <v>57</v>
       </c>
       <c r="G231">
-        <v>0.8667</v>
+        <v>0.8643999999999999</v>
       </c>
       <c r="H231">
         <v>0.7667</v>
       </c>
       <c r="I231">
-        <v>0.8167</v>
+        <v>0.8156</v>
       </c>
       <c r="J231">
-        <v>0.1333</v>
+        <v>0.1356</v>
       </c>
       <c r="K231">
         <v>0.2333</v>
       </c>
       <c r="L231">
-        <v>0.1833</v>
+        <v>0.1844</v>
       </c>
       <c r="M231">
         <v>168</v>
@@ -10827,22 +10827,22 @@
         <v>59</v>
       </c>
       <c r="G233">
-        <v>0.6862</v>
+        <v>0.6853</v>
       </c>
       <c r="H233">
         <v>0.5514</v>
       </c>
       <c r="I233">
-        <v>0.6188</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="J233">
-        <v>0.3138</v>
+        <v>0.3147</v>
       </c>
       <c r="K233">
         <v>0.4486</v>
       </c>
       <c r="L233">
-        <v>0.3812</v>
+        <v>0.3816</v>
       </c>
       <c r="M233">
         <v>168</v>
@@ -10874,19 +10874,19 @@
         <v>0.8238</v>
       </c>
       <c r="H234">
-        <v>0.7052</v>
+        <v>0.702</v>
       </c>
       <c r="I234">
-        <v>0.7645</v>
+        <v>0.7629</v>
       </c>
       <c r="J234">
         <v>0.1762</v>
       </c>
       <c r="K234">
-        <v>0.2948</v>
+        <v>0.298</v>
       </c>
       <c r="L234">
-        <v>0.2355</v>
+        <v>0.2371</v>
       </c>
       <c r="M234">
         <v>168</v>
@@ -10959,22 +10959,22 @@
         <v>62</v>
       </c>
       <c r="G236">
-        <v>0.6398</v>
+        <v>0.6177</v>
       </c>
       <c r="H236">
-        <v>0.5083</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="I236">
-        <v>0.574</v>
+        <v>0.5622</v>
       </c>
       <c r="J236">
-        <v>0.3602</v>
+        <v>0.3823</v>
       </c>
       <c r="K236">
-        <v>0.4917</v>
+        <v>0.4934</v>
       </c>
       <c r="L236">
-        <v>0.426</v>
+        <v>0.4378</v>
       </c>
       <c r="M236">
         <v>168</v>
@@ -11047,22 +11047,22 @@
         <v>64</v>
       </c>
       <c r="G238">
-        <v>0.8608</v>
+        <v>0.8603</v>
       </c>
       <c r="H238">
-        <v>0.7466</v>
+        <v>0.7438</v>
       </c>
       <c r="I238">
-        <v>0.8037</v>
+        <v>0.802</v>
       </c>
       <c r="J238">
-        <v>0.1392</v>
+        <v>0.1397</v>
       </c>
       <c r="K238">
-        <v>0.2534</v>
+        <v>0.2562</v>
       </c>
       <c r="L238">
-        <v>0.1963</v>
+        <v>0.198</v>
       </c>
       <c r="M238">
         <v>168</v>
@@ -11094,19 +11094,19 @@
         <v>0.3717</v>
       </c>
       <c r="H239">
-        <v>0.2472</v>
+        <v>0.2505</v>
       </c>
       <c r="I239">
-        <v>0.3094</v>
+        <v>0.3111</v>
       </c>
       <c r="J239">
         <v>0.6283</v>
       </c>
       <c r="K239">
-        <v>0.7528</v>
+        <v>0.7495000000000001</v>
       </c>
       <c r="L239">
-        <v>0.6906</v>
+        <v>0.6889</v>
       </c>
       <c r="M239">
         <v>168</v>
@@ -11138,19 +11138,19 @@
         <v>0.3731</v>
       </c>
       <c r="H240">
-        <v>0.23</v>
+        <v>0.2261</v>
       </c>
       <c r="I240">
-        <v>0.3016</v>
+        <v>0.2996</v>
       </c>
       <c r="J240">
         <v>0.6269</v>
       </c>
       <c r="K240">
-        <v>0.77</v>
+        <v>0.7739</v>
       </c>
       <c r="L240">
-        <v>0.6984</v>
+        <v>0.7004</v>
       </c>
       <c r="M240">
         <v>168</v>
@@ -11179,22 +11179,22 @@
         <v>67</v>
       </c>
       <c r="G241">
-        <v>0.5812</v>
+        <v>0.5704</v>
       </c>
       <c r="H241">
-        <v>0.4804</v>
+        <v>0.4682</v>
       </c>
       <c r="I241">
-        <v>0.5308</v>
+        <v>0.5193</v>
       </c>
       <c r="J241">
-        <v>0.4188</v>
+        <v>0.4296</v>
       </c>
       <c r="K241">
-        <v>0.5196</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="L241">
-        <v>0.4692</v>
+        <v>0.4807</v>
       </c>
       <c r="M241">
         <v>168</v>
@@ -11223,22 +11223,22 @@
         <v>68</v>
       </c>
       <c r="G242">
-        <v>0.8604000000000001</v>
+        <v>0.8522</v>
       </c>
       <c r="H242">
-        <v>0.7138</v>
+        <v>0.708</v>
       </c>
       <c r="I242">
-        <v>0.7871</v>
+        <v>0.7801</v>
       </c>
       <c r="J242">
-        <v>0.1396</v>
+        <v>0.1478</v>
       </c>
       <c r="K242">
-        <v>0.2862</v>
+        <v>0.292</v>
       </c>
       <c r="L242">
-        <v>0.2129</v>
+        <v>0.2199</v>
       </c>
       <c r="M242">
         <v>168</v>
@@ -11267,22 +11267,22 @@
         <v>69</v>
       </c>
       <c r="G243">
-        <v>0.8483000000000001</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="H243">
-        <v>0.6985</v>
+        <v>0.694</v>
       </c>
       <c r="I243">
-        <v>0.7734</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="J243">
-        <v>0.1517</v>
+        <v>0.1527</v>
       </c>
       <c r="K243">
-        <v>0.3015</v>
+        <v>0.306</v>
       </c>
       <c r="L243">
-        <v>0.2266</v>
+        <v>0.2293</v>
       </c>
       <c r="M243">
         <v>168</v>
@@ -11311,22 +11311,22 @@
         <v>70</v>
       </c>
       <c r="G244">
-        <v>0.8709</v>
+        <v>0.8691</v>
       </c>
       <c r="H244">
         <v>0.7426</v>
       </c>
       <c r="I244">
-        <v>0.8068</v>
+        <v>0.8058</v>
       </c>
       <c r="J244">
-        <v>0.1291</v>
+        <v>0.1309</v>
       </c>
       <c r="K244">
         <v>0.2574</v>
       </c>
       <c r="L244">
-        <v>0.1932</v>
+        <v>0.1942</v>
       </c>
       <c r="M244">
         <v>168</v>
@@ -11355,22 +11355,22 @@
         <v>71</v>
       </c>
       <c r="G245">
-        <v>0.5137</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="H245">
         <v>0.363</v>
       </c>
       <c r="I245">
-        <v>0.4384</v>
+        <v>0.4363</v>
       </c>
       <c r="J245">
-        <v>0.4863</v>
+        <v>0.4904</v>
       </c>
       <c r="K245">
         <v>0.637</v>
       </c>
       <c r="L245">
-        <v>0.5616</v>
+        <v>0.5637</v>
       </c>
       <c r="M245">
         <v>168</v>
@@ -11402,19 +11402,19 @@
         <v>0.4649</v>
       </c>
       <c r="H246">
-        <v>0.4013</v>
+        <v>0.3994</v>
       </c>
       <c r="I246">
-        <v>0.4331</v>
+        <v>0.4322</v>
       </c>
       <c r="J246">
         <v>0.5351</v>
       </c>
       <c r="K246">
-        <v>0.5987</v>
+        <v>0.6006</v>
       </c>
       <c r="L246">
-        <v>0.5669</v>
+        <v>0.5678</v>
       </c>
       <c r="M246">
         <v>168</v>
@@ -11443,22 +11443,22 @@
         <v>54</v>
       </c>
       <c r="G247">
-        <v>0.5497</v>
+        <v>0.5569</v>
       </c>
       <c r="H247">
-        <v>0.3608</v>
+        <v>0.3671</v>
       </c>
       <c r="I247">
-        <v>0.4552</v>
+        <v>0.462</v>
       </c>
       <c r="J247">
-        <v>0.4503</v>
+        <v>0.4431</v>
       </c>
       <c r="K247">
-        <v>0.6392</v>
+        <v>0.6329</v>
       </c>
       <c r="L247">
-        <v>0.5448</v>
+        <v>0.538</v>
       </c>
       <c r="M247">
         <v>168</v>
@@ -11490,19 +11490,19 @@
         <v>0.7764</v>
       </c>
       <c r="H248">
-        <v>0.6243</v>
+        <v>0.6137</v>
       </c>
       <c r="I248">
-        <v>0.7004</v>
+        <v>0.695</v>
       </c>
       <c r="J248">
         <v>0.2236</v>
       </c>
       <c r="K248">
-        <v>0.3757</v>
+        <v>0.3863</v>
       </c>
       <c r="L248">
-        <v>0.2996</v>
+        <v>0.305</v>
       </c>
       <c r="M248">
         <v>168</v>
@@ -11531,22 +11531,22 @@
         <v>56</v>
       </c>
       <c r="G249">
-        <v>0.4714</v>
+        <v>0.4797</v>
       </c>
       <c r="H249">
         <v>0.3402</v>
       </c>
       <c r="I249">
-        <v>0.4058</v>
+        <v>0.41</v>
       </c>
       <c r="J249">
-        <v>0.5286</v>
+        <v>0.5203</v>
       </c>
       <c r="K249">
         <v>0.6598000000000001</v>
       </c>
       <c r="L249">
-        <v>0.5942</v>
+        <v>0.59</v>
       </c>
       <c r="M249">
         <v>168</v>
@@ -11663,22 +11663,22 @@
         <v>59</v>
       </c>
       <c r="G252">
-        <v>0.5981</v>
+        <v>0.6011</v>
       </c>
       <c r="H252">
-        <v>0.4089</v>
+        <v>0.4116</v>
       </c>
       <c r="I252">
-        <v>0.5034999999999999</v>
+        <v>0.5064</v>
       </c>
       <c r="J252">
-        <v>0.4019</v>
+        <v>0.3989</v>
       </c>
       <c r="K252">
-        <v>0.5911</v>
+        <v>0.5884</v>
       </c>
       <c r="L252">
-        <v>0.4965</v>
+        <v>0.4936</v>
       </c>
       <c r="M252">
         <v>168</v>
@@ -11751,22 +11751,22 @@
         <v>61</v>
       </c>
       <c r="G254">
-        <v>0.5661</v>
+        <v>0.5713</v>
       </c>
       <c r="H254">
-        <v>0.3759</v>
+        <v>0.3776</v>
       </c>
       <c r="I254">
-        <v>0.471</v>
+        <v>0.4744</v>
       </c>
       <c r="J254">
-        <v>0.4339</v>
+        <v>0.4287</v>
       </c>
       <c r="K254">
-        <v>0.6241</v>
+        <v>0.6224</v>
       </c>
       <c r="L254">
-        <v>0.529</v>
+        <v>0.5256</v>
       </c>
       <c r="M254">
         <v>168</v>
@@ -11795,22 +11795,22 @@
         <v>62</v>
       </c>
       <c r="G255">
-        <v>0.5304</v>
+        <v>0.534</v>
       </c>
       <c r="H255">
-        <v>0.3654</v>
+        <v>0.3684</v>
       </c>
       <c r="I255">
-        <v>0.4479</v>
+        <v>0.4512</v>
       </c>
       <c r="J255">
-        <v>0.4696</v>
+        <v>0.466</v>
       </c>
       <c r="K255">
-        <v>0.6346000000000001</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="L255">
-        <v>0.5521</v>
+        <v>0.5488</v>
       </c>
       <c r="M255">
         <v>168</v>
@@ -11883,22 +11883,22 @@
         <v>64</v>
       </c>
       <c r="G257">
-        <v>0.8057</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="H257">
-        <v>0.6916</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="I257">
-        <v>0.7486</v>
+        <v>0.744</v>
       </c>
       <c r="J257">
-        <v>0.1943</v>
+        <v>0.1971</v>
       </c>
       <c r="K257">
-        <v>0.3084</v>
+        <v>0.315</v>
       </c>
       <c r="L257">
-        <v>0.2514</v>
+        <v>0.256</v>
       </c>
       <c r="M257">
         <v>168</v>
@@ -11927,22 +11927,22 @@
         <v>65</v>
       </c>
       <c r="G258">
-        <v>0.3061</v>
+        <v>0.3071</v>
       </c>
       <c r="H258">
         <v>0.1882</v>
       </c>
       <c r="I258">
-        <v>0.2472</v>
+        <v>0.2476</v>
       </c>
       <c r="J258">
-        <v>0.6939</v>
+        <v>0.6929</v>
       </c>
       <c r="K258">
         <v>0.8118</v>
       </c>
       <c r="L258">
-        <v>0.7528</v>
+        <v>0.7524</v>
       </c>
       <c r="M258">
         <v>168</v>
@@ -11971,22 +11971,22 @@
         <v>66</v>
       </c>
       <c r="G259">
-        <v>0.2885</v>
+        <v>0.2984</v>
       </c>
       <c r="H259">
         <v>0.1865</v>
       </c>
       <c r="I259">
-        <v>0.2375</v>
+        <v>0.2424</v>
       </c>
       <c r="J259">
-        <v>0.7115</v>
+        <v>0.7016</v>
       </c>
       <c r="K259">
         <v>0.8135</v>
       </c>
       <c r="L259">
-        <v>0.7625</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="M259">
         <v>168</v>
@@ -12015,22 +12015,22 @@
         <v>67</v>
       </c>
       <c r="G260">
-        <v>0.504</v>
+        <v>0.4987</v>
       </c>
       <c r="H260">
-        <v>0.3504</v>
+        <v>0.345</v>
       </c>
       <c r="I260">
-        <v>0.4272</v>
+        <v>0.4218</v>
       </c>
       <c r="J260">
-        <v>0.496</v>
+        <v>0.5013</v>
       </c>
       <c r="K260">
-        <v>0.6496</v>
+        <v>0.655</v>
       </c>
       <c r="L260">
-        <v>0.5728</v>
+        <v>0.5782</v>
       </c>
       <c r="M260">
         <v>168</v>
@@ -12059,22 +12059,22 @@
         <v>68</v>
       </c>
       <c r="G261">
-        <v>0.7789</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="H261">
-        <v>0.6425999999999999</v>
+        <v>0.614</v>
       </c>
       <c r="I261">
-        <v>0.7108</v>
+        <v>0.6908</v>
       </c>
       <c r="J261">
-        <v>0.2211</v>
+        <v>0.2324</v>
       </c>
       <c r="K261">
-        <v>0.3574</v>
+        <v>0.386</v>
       </c>
       <c r="L261">
-        <v>0.2892</v>
+        <v>0.3092</v>
       </c>
       <c r="M261">
         <v>168</v>
@@ -12191,22 +12191,22 @@
         <v>71</v>
       </c>
       <c r="G264">
-        <v>0.4105</v>
+        <v>0.4154</v>
       </c>
       <c r="H264">
         <v>0.2728</v>
       </c>
       <c r="I264">
-        <v>0.3416</v>
+        <v>0.3441</v>
       </c>
       <c r="J264">
-        <v>0.5895</v>
+        <v>0.5846</v>
       </c>
       <c r="K264">
         <v>0.7272</v>
       </c>
       <c r="L264">
-        <v>0.6584</v>
+        <v>0.6559</v>
       </c>
       <c r="M264">
         <v>168</v>
@@ -12238,19 +12238,19 @@
         <v>0.3909</v>
       </c>
       <c r="H265">
-        <v>0.2746</v>
+        <v>0.2779</v>
       </c>
       <c r="I265">
-        <v>0.3328</v>
+        <v>0.3344</v>
       </c>
       <c r="J265">
         <v>0.6091</v>
       </c>
       <c r="K265">
-        <v>0.7254</v>
+        <v>0.7221</v>
       </c>
       <c r="L265">
-        <v>0.6672</v>
+        <v>0.6656</v>
       </c>
       <c r="M265">
         <v>168</v>
@@ -12279,22 +12279,22 @@
         <v>55</v>
       </c>
       <c r="G266">
-        <v>0.8051</v>
+        <v>0.8012</v>
       </c>
       <c r="H266">
-        <v>0.6353</v>
+        <v>0.6309</v>
       </c>
       <c r="I266">
-        <v>0.7202</v>
+        <v>0.7161</v>
       </c>
       <c r="J266">
-        <v>0.1949</v>
+        <v>0.1988</v>
       </c>
       <c r="K266">
-        <v>0.3647</v>
+        <v>0.3691</v>
       </c>
       <c r="L266">
-        <v>0.2798</v>
+        <v>0.2839</v>
       </c>
       <c r="M266">
         <v>168</v>
@@ -12367,22 +12367,22 @@
         <v>57</v>
       </c>
       <c r="G268">
-        <v>0.8312</v>
+        <v>0.826</v>
       </c>
       <c r="H268">
-        <v>0.7272999999999999</v>
+        <v>0.7228</v>
       </c>
       <c r="I268">
-        <v>0.7792</v>
+        <v>0.7744</v>
       </c>
       <c r="J268">
-        <v>0.1688</v>
+        <v>0.174</v>
       </c>
       <c r="K268">
-        <v>0.2727</v>
+        <v>0.2772</v>
       </c>
       <c r="L268">
-        <v>0.2208</v>
+        <v>0.2256</v>
       </c>
       <c r="M268">
         <v>168</v>
@@ -12414,19 +12414,19 @@
         <v>0.4133</v>
       </c>
       <c r="H269">
-        <v>0.2226</v>
+        <v>0.2258</v>
       </c>
       <c r="I269">
-        <v>0.318</v>
+        <v>0.3196</v>
       </c>
       <c r="J269">
         <v>0.5867</v>
       </c>
       <c r="K269">
-        <v>0.7774</v>
+        <v>0.7742</v>
       </c>
       <c r="L269">
-        <v>0.6820000000000001</v>
+        <v>0.6804</v>
       </c>
       <c r="M269">
         <v>168</v>
@@ -12455,22 +12455,22 @@
         <v>59</v>
       </c>
       <c r="G270">
-        <v>0.5999</v>
+        <v>0.5857</v>
       </c>
       <c r="H270">
-        <v>0.4998</v>
+        <v>0.498</v>
       </c>
       <c r="I270">
-        <v>0.5498</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="J270">
-        <v>0.4001</v>
+        <v>0.4143</v>
       </c>
       <c r="K270">
-        <v>0.5002</v>
+        <v>0.502</v>
       </c>
       <c r="L270">
-        <v>0.4502</v>
+        <v>0.4582</v>
       </c>
       <c r="M270">
         <v>168</v>
@@ -12499,22 +12499,22 @@
         <v>60</v>
       </c>
       <c r="G271">
-        <v>0.7665999999999999</v>
+        <v>0.7635</v>
       </c>
       <c r="H271">
         <v>0.6342</v>
       </c>
       <c r="I271">
-        <v>0.7004</v>
+        <v>0.6988</v>
       </c>
       <c r="J271">
-        <v>0.2334</v>
+        <v>0.2365</v>
       </c>
       <c r="K271">
         <v>0.3658</v>
       </c>
       <c r="L271">
-        <v>0.2996</v>
+        <v>0.3012</v>
       </c>
       <c r="M271">
         <v>168</v>
@@ -12546,19 +12546,19 @@
         <v>0.5717</v>
       </c>
       <c r="H272">
-        <v>0.4227</v>
+        <v>0.4341</v>
       </c>
       <c r="I272">
-        <v>0.4972</v>
+        <v>0.5029</v>
       </c>
       <c r="J272">
         <v>0.4283</v>
       </c>
       <c r="K272">
-        <v>0.5773</v>
+        <v>0.5659</v>
       </c>
       <c r="L272">
-        <v>0.5028</v>
+        <v>0.4971</v>
       </c>
       <c r="M272">
         <v>168</v>
@@ -12631,22 +12631,22 @@
         <v>63</v>
       </c>
       <c r="G274">
-        <v>0.6349</v>
+        <v>0.6301</v>
       </c>
       <c r="H274">
         <v>0.4521</v>
       </c>
       <c r="I274">
-        <v>0.5435</v>
+        <v>0.5411</v>
       </c>
       <c r="J274">
-        <v>0.3651</v>
+        <v>0.3699</v>
       </c>
       <c r="K274">
         <v>0.5479000000000001</v>
       </c>
       <c r="L274">
-        <v>0.4565</v>
+        <v>0.4589</v>
       </c>
       <c r="M274">
         <v>168</v>
@@ -12675,22 +12675,22 @@
         <v>64</v>
       </c>
       <c r="G275">
-        <v>0.8295</v>
+        <v>0.8266</v>
       </c>
       <c r="H275">
-        <v>0.6982</v>
+        <v>0.6954</v>
       </c>
       <c r="I275">
-        <v>0.7638</v>
+        <v>0.761</v>
       </c>
       <c r="J275">
-        <v>0.1705</v>
+        <v>0.1734</v>
       </c>
       <c r="K275">
-        <v>0.3018</v>
+        <v>0.3046</v>
       </c>
       <c r="L275">
-        <v>0.2362</v>
+        <v>0.239</v>
       </c>
       <c r="M275">
         <v>168</v>
@@ -12722,19 +12722,19 @@
         <v>0.3605</v>
       </c>
       <c r="H276">
-        <v>0.1908</v>
+        <v>0.1936</v>
       </c>
       <c r="I276">
-        <v>0.2756</v>
+        <v>0.277</v>
       </c>
       <c r="J276">
         <v>0.6395</v>
       </c>
       <c r="K276">
-        <v>0.8092</v>
+        <v>0.8064</v>
       </c>
       <c r="L276">
-        <v>0.7244</v>
+        <v>0.723</v>
       </c>
       <c r="M276">
         <v>168</v>
@@ -12807,22 +12807,22 @@
         <v>67</v>
       </c>
       <c r="G278">
-        <v>0.534</v>
+        <v>0.5298</v>
       </c>
       <c r="H278">
-        <v>0.378</v>
+        <v>0.3637</v>
       </c>
       <c r="I278">
-        <v>0.456</v>
+        <v>0.4468</v>
       </c>
       <c r="J278">
-        <v>0.466</v>
+        <v>0.4702</v>
       </c>
       <c r="K278">
-        <v>0.622</v>
+        <v>0.6363</v>
       </c>
       <c r="L278">
-        <v>0.544</v>
+        <v>0.5532</v>
       </c>
       <c r="M278">
         <v>168</v>
@@ -12851,22 +12851,22 @@
         <v>68</v>
       </c>
       <c r="G279">
-        <v>0.8053</v>
+        <v>0.7988</v>
       </c>
       <c r="H279">
-        <v>0.6882</v>
+        <v>0.6742</v>
       </c>
       <c r="I279">
-        <v>0.7468</v>
+        <v>0.7365</v>
       </c>
       <c r="J279">
-        <v>0.1947</v>
+        <v>0.2012</v>
       </c>
       <c r="K279">
-        <v>0.3118</v>
+        <v>0.3258</v>
       </c>
       <c r="L279">
-        <v>0.2532</v>
+        <v>0.2635</v>
       </c>
       <c r="M279">
         <v>168</v>
@@ -12895,22 +12895,22 @@
         <v>69</v>
       </c>
       <c r="G280">
-        <v>0.8107</v>
+        <v>0.8052</v>
       </c>
       <c r="H280">
         <v>0.6627999999999999</v>
       </c>
       <c r="I280">
-        <v>0.7368</v>
+        <v>0.734</v>
       </c>
       <c r="J280">
-        <v>0.1893</v>
+        <v>0.1948</v>
       </c>
       <c r="K280">
         <v>0.3372</v>
       </c>
       <c r="L280">
-        <v>0.2632</v>
+        <v>0.266</v>
       </c>
       <c r="M280">
         <v>168</v>
@@ -12939,22 +12939,22 @@
         <v>70</v>
       </c>
       <c r="G281">
-        <v>0.8277</v>
+        <v>0.8244</v>
       </c>
       <c r="H281">
-        <v>0.7292999999999999</v>
+        <v>0.7251</v>
       </c>
       <c r="I281">
-        <v>0.7785</v>
+        <v>0.7748</v>
       </c>
       <c r="J281">
-        <v>0.1723</v>
+        <v>0.1756</v>
       </c>
       <c r="K281">
-        <v>0.2707</v>
+        <v>0.2749</v>
       </c>
       <c r="L281">
-        <v>0.2215</v>
+        <v>0.2252</v>
       </c>
       <c r="M281">
         <v>168</v>
@@ -12983,22 +12983,22 @@
         <v>71</v>
       </c>
       <c r="G282">
-        <v>0.4681</v>
+        <v>0.4649</v>
       </c>
       <c r="H282">
         <v>0.3007</v>
       </c>
       <c r="I282">
-        <v>0.3844</v>
+        <v>0.3828</v>
       </c>
       <c r="J282">
-        <v>0.5319</v>
+        <v>0.5351</v>
       </c>
       <c r="K282">
         <v>0.6993</v>
       </c>
       <c r="L282">
-        <v>0.6156</v>
+        <v>0.6172</v>
       </c>
       <c r="M282">
         <v>168</v>
@@ -13027,22 +13027,22 @@
         <v>73</v>
       </c>
       <c r="G283">
-        <v>0.4752</v>
+        <v>0.4611</v>
       </c>
       <c r="H283">
         <v>0.3117</v>
       </c>
       <c r="I283">
-        <v>0.3934</v>
+        <v>0.3864</v>
       </c>
       <c r="J283">
-        <v>0.5248</v>
+        <v>0.5389</v>
       </c>
       <c r="K283">
         <v>0.6883</v>
       </c>
       <c r="L283">
-        <v>0.6066</v>
+        <v>0.6136</v>
       </c>
       <c r="M283">
         <v>168</v>
@@ -13115,22 +13115,22 @@
         <v>57</v>
       </c>
       <c r="G285">
-        <v>0.6577</v>
+        <v>0.6528</v>
       </c>
       <c r="H285">
-        <v>0.5191</v>
+        <v>0.5149</v>
       </c>
       <c r="I285">
-        <v>0.5884</v>
+        <v>0.5838</v>
       </c>
       <c r="J285">
-        <v>0.3423</v>
+        <v>0.3472</v>
       </c>
       <c r="K285">
-        <v>0.4809</v>
+        <v>0.4851</v>
       </c>
       <c r="L285">
-        <v>0.4116</v>
+        <v>0.4162</v>
       </c>
       <c r="M285">
         <v>168</v>
@@ -13203,22 +13203,22 @@
         <v>59</v>
       </c>
       <c r="G287">
-        <v>0.3897</v>
+        <v>0.3918</v>
       </c>
       <c r="H287">
-        <v>0.2392</v>
+        <v>0.2421</v>
       </c>
       <c r="I287">
-        <v>0.3144</v>
+        <v>0.317</v>
       </c>
       <c r="J287">
-        <v>0.6103</v>
+        <v>0.6082</v>
       </c>
       <c r="K287">
-        <v>0.7608</v>
+        <v>0.7579</v>
       </c>
       <c r="L287">
-        <v>0.6856</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="M287">
         <v>168</v>
@@ -13250,19 +13250,19 @@
         <v>0.534</v>
       </c>
       <c r="H288">
-        <v>0.3873</v>
+        <v>0.3851</v>
       </c>
       <c r="I288">
-        <v>0.4606</v>
+        <v>0.4596</v>
       </c>
       <c r="J288">
         <v>0.466</v>
       </c>
       <c r="K288">
-        <v>0.6127</v>
+        <v>0.6149</v>
       </c>
       <c r="L288">
-        <v>0.5394</v>
+        <v>0.5404</v>
       </c>
       <c r="M288">
         <v>168</v>
@@ -13294,19 +13294,19 @@
         <v>0.3644</v>
       </c>
       <c r="H289">
-        <v>0.226</v>
+        <v>0.2335</v>
       </c>
       <c r="I289">
-        <v>0.2952</v>
+        <v>0.299</v>
       </c>
       <c r="J289">
         <v>0.6356000000000001</v>
       </c>
       <c r="K289">
-        <v>0.774</v>
+        <v>0.7665</v>
       </c>
       <c r="L289">
-        <v>0.7048</v>
+        <v>0.701</v>
       </c>
       <c r="M289">
         <v>168</v>
@@ -13338,19 +13338,19 @@
         <v>0.3394</v>
       </c>
       <c r="H290">
-        <v>0.1809</v>
+        <v>0.1889</v>
       </c>
       <c r="I290">
-        <v>0.2602</v>
+        <v>0.2642</v>
       </c>
       <c r="J290">
         <v>0.6606</v>
       </c>
       <c r="K290">
-        <v>0.8191000000000001</v>
+        <v>0.8111</v>
       </c>
       <c r="L290">
-        <v>0.7398</v>
+        <v>0.7358</v>
       </c>
       <c r="M290">
         <v>168</v>
@@ -13379,22 +13379,22 @@
         <v>63</v>
       </c>
       <c r="G291">
-        <v>0.3649</v>
+        <v>0.3699</v>
       </c>
       <c r="H291">
-        <v>0.2381</v>
+        <v>0.2395</v>
       </c>
       <c r="I291">
-        <v>0.3015</v>
+        <v>0.3047</v>
       </c>
       <c r="J291">
-        <v>0.6351</v>
+        <v>0.6301</v>
       </c>
       <c r="K291">
-        <v>0.7619</v>
+        <v>0.7605</v>
       </c>
       <c r="L291">
-        <v>0.6985</v>
+        <v>0.6953</v>
       </c>
       <c r="M291">
         <v>168</v>
@@ -13599,22 +13599,22 @@
         <v>68</v>
       </c>
       <c r="G296">
-        <v>0.6315</v>
+        <v>0.6153</v>
       </c>
       <c r="H296">
-        <v>0.4537</v>
+        <v>0.4454</v>
       </c>
       <c r="I296">
-        <v>0.5426</v>
+        <v>0.5304</v>
       </c>
       <c r="J296">
-        <v>0.3685</v>
+        <v>0.3847</v>
       </c>
       <c r="K296">
-        <v>0.5463</v>
+        <v>0.5546</v>
       </c>
       <c r="L296">
-        <v>0.4574</v>
+        <v>0.4696</v>
       </c>
       <c r="M296">
         <v>168</v>
@@ -13646,19 +13646,19 @@
         <v>0.5887</v>
       </c>
       <c r="H297">
-        <v>0.4431</v>
+        <v>0.4506</v>
       </c>
       <c r="I297">
-        <v>0.5159</v>
+        <v>0.5196</v>
       </c>
       <c r="J297">
         <v>0.4113</v>
       </c>
       <c r="K297">
-        <v>0.5569</v>
+        <v>0.5494</v>
       </c>
       <c r="L297">
-        <v>0.4841</v>
+        <v>0.4804</v>
       </c>
       <c r="M297">
         <v>168</v>
@@ -13731,22 +13731,22 @@
         <v>71</v>
       </c>
       <c r="G299">
-        <v>0.2579</v>
+        <v>0.2636</v>
       </c>
       <c r="H299">
-        <v>0.1666</v>
+        <v>0.1689</v>
       </c>
       <c r="I299">
-        <v>0.2122</v>
+        <v>0.2162</v>
       </c>
       <c r="J299">
-        <v>0.7421</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="K299">
-        <v>0.8334</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="L299">
-        <v>0.7877999999999999</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="M299">
         <v>168</v>
@@ -13778,19 +13778,19 @@
         <v>0.2624</v>
       </c>
       <c r="H300">
-        <v>0.151</v>
+        <v>0.1556</v>
       </c>
       <c r="I300">
-        <v>0.2067</v>
+        <v>0.209</v>
       </c>
       <c r="J300">
         <v>0.7376</v>
       </c>
       <c r="K300">
-        <v>0.849</v>
+        <v>0.8444</v>
       </c>
       <c r="L300">
-        <v>0.7933</v>
+        <v>0.791</v>
       </c>
       <c r="M300">
         <v>168</v>
@@ -13822,19 +13822,19 @@
         <v>0.8454</v>
       </c>
       <c r="H301">
-        <v>0.7531</v>
+        <v>0.7484</v>
       </c>
       <c r="I301">
-        <v>0.7992</v>
+        <v>0.7969000000000001</v>
       </c>
       <c r="J301">
         <v>0.1546</v>
       </c>
       <c r="K301">
-        <v>0.2469</v>
+        <v>0.2516</v>
       </c>
       <c r="L301">
-        <v>0.2008</v>
+        <v>0.2031</v>
       </c>
       <c r="M301">
         <v>168</v>
@@ -13866,19 +13866,19 @@
         <v>0.4234</v>
       </c>
       <c r="H302">
-        <v>0.2687</v>
+        <v>0.272</v>
       </c>
       <c r="I302">
-        <v>0.346</v>
+        <v>0.3477</v>
       </c>
       <c r="J302">
         <v>0.5766</v>
       </c>
       <c r="K302">
-        <v>0.7313</v>
+        <v>0.728</v>
       </c>
       <c r="L302">
-        <v>0.654</v>
+        <v>0.6523</v>
       </c>
       <c r="M302">
         <v>168</v>
@@ -13907,22 +13907,22 @@
         <v>59</v>
       </c>
       <c r="G303">
-        <v>0.6394</v>
+        <v>0.6344</v>
       </c>
       <c r="H303">
-        <v>0.5275</v>
+        <v>0.5233</v>
       </c>
       <c r="I303">
-        <v>0.5834</v>
+        <v>0.5788</v>
       </c>
       <c r="J303">
-        <v>0.3606</v>
+        <v>0.3656</v>
       </c>
       <c r="K303">
-        <v>0.4725</v>
+        <v>0.4767</v>
       </c>
       <c r="L303">
-        <v>0.4166</v>
+        <v>0.4212</v>
       </c>
       <c r="M303">
         <v>168</v>
@@ -13954,19 +13954,19 @@
         <v>0.7973</v>
       </c>
       <c r="H304">
-        <v>0.6785</v>
+        <v>0.6718</v>
       </c>
       <c r="I304">
-        <v>0.7379</v>
+        <v>0.7346</v>
       </c>
       <c r="J304">
         <v>0.2027</v>
       </c>
       <c r="K304">
-        <v>0.3215</v>
+        <v>0.3282</v>
       </c>
       <c r="L304">
-        <v>0.2621</v>
+        <v>0.2654</v>
       </c>
       <c r="M304">
         <v>168</v>
@@ -13998,19 +13998,19 @@
         <v>0.617</v>
       </c>
       <c r="H305">
-        <v>0.4537</v>
+        <v>0.4546</v>
       </c>
       <c r="I305">
-        <v>0.5354</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="J305">
         <v>0.383</v>
       </c>
       <c r="K305">
-        <v>0.5463</v>
+        <v>0.5454</v>
       </c>
       <c r="L305">
-        <v>0.4646</v>
+        <v>0.4642</v>
       </c>
       <c r="M305">
         <v>168</v>
@@ -14083,22 +14083,22 @@
         <v>63</v>
       </c>
       <c r="G307">
-        <v>0.6705</v>
+        <v>0.6522</v>
       </c>
       <c r="H307">
-        <v>0.496</v>
+        <v>0.4943</v>
       </c>
       <c r="I307">
-        <v>0.5833</v>
+        <v>0.5732</v>
       </c>
       <c r="J307">
-        <v>0.3295</v>
+        <v>0.3478</v>
       </c>
       <c r="K307">
-        <v>0.504</v>
+        <v>0.5057</v>
       </c>
       <c r="L307">
-        <v>0.4167</v>
+        <v>0.4268</v>
       </c>
       <c r="M307">
         <v>168</v>
@@ -14130,19 +14130,19 @@
         <v>0.8444</v>
       </c>
       <c r="H308">
-        <v>0.7138</v>
+        <v>0.7033</v>
       </c>
       <c r="I308">
-        <v>0.7791</v>
+        <v>0.7738</v>
       </c>
       <c r="J308">
         <v>0.1556</v>
       </c>
       <c r="K308">
-        <v>0.2862</v>
+        <v>0.2967</v>
       </c>
       <c r="L308">
-        <v>0.2209</v>
+        <v>0.2262</v>
       </c>
       <c r="M308">
         <v>168</v>
@@ -14259,22 +14259,22 @@
         <v>67</v>
       </c>
       <c r="G311">
-        <v>0.5669</v>
+        <v>0.5651</v>
       </c>
       <c r="H311">
-        <v>0.4385</v>
+        <v>0.4192</v>
       </c>
       <c r="I311">
-        <v>0.5027</v>
+        <v>0.4922</v>
       </c>
       <c r="J311">
-        <v>0.4331</v>
+        <v>0.4349</v>
       </c>
       <c r="K311">
-        <v>0.5615</v>
+        <v>0.5808</v>
       </c>
       <c r="L311">
-        <v>0.4973</v>
+        <v>0.5078</v>
       </c>
       <c r="M311">
         <v>168</v>
@@ -14303,22 +14303,22 @@
         <v>68</v>
       </c>
       <c r="G312">
-        <v>0.8174</v>
+        <v>0.8082</v>
       </c>
       <c r="H312">
-        <v>0.7161999999999999</v>
+        <v>0.6989</v>
       </c>
       <c r="I312">
-        <v>0.7668</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="J312">
-        <v>0.1826</v>
+        <v>0.1918</v>
       </c>
       <c r="K312">
-        <v>0.2838</v>
+        <v>0.3011</v>
       </c>
       <c r="L312">
-        <v>0.2332</v>
+        <v>0.2465</v>
       </c>
       <c r="M312">
         <v>168</v>
@@ -14347,22 +14347,22 @@
         <v>69</v>
       </c>
       <c r="G313">
-        <v>0.8232</v>
+        <v>0.821</v>
       </c>
       <c r="H313">
-        <v>0.6947</v>
+        <v>0.6919</v>
       </c>
       <c r="I313">
-        <v>0.759</v>
+        <v>0.7564</v>
       </c>
       <c r="J313">
-        <v>0.1768</v>
+        <v>0.179</v>
       </c>
       <c r="K313">
-        <v>0.3053</v>
+        <v>0.3081</v>
       </c>
       <c r="L313">
-        <v>0.241</v>
+        <v>0.2436</v>
       </c>
       <c r="M313">
         <v>168</v>
@@ -14391,22 +14391,22 @@
         <v>70</v>
       </c>
       <c r="G314">
-        <v>0.8433</v>
+        <v>0.8401</v>
       </c>
       <c r="H314">
-        <v>0.719</v>
+        <v>0.7164</v>
       </c>
       <c r="I314">
-        <v>0.7812</v>
+        <v>0.7782</v>
       </c>
       <c r="J314">
-        <v>0.1567</v>
+        <v>0.1599</v>
       </c>
       <c r="K314">
-        <v>0.281</v>
+        <v>0.2836</v>
       </c>
       <c r="L314">
-        <v>0.2188</v>
+        <v>0.2218</v>
       </c>
       <c r="M314">
         <v>168</v>
@@ -14435,22 +14435,22 @@
         <v>71</v>
       </c>
       <c r="G315">
-        <v>0.4912</v>
+        <v>0.491</v>
       </c>
       <c r="H315">
         <v>0.347</v>
       </c>
       <c r="I315">
-        <v>0.4191</v>
+        <v>0.419</v>
       </c>
       <c r="J315">
-        <v>0.5088</v>
+        <v>0.509</v>
       </c>
       <c r="K315">
         <v>0.653</v>
       </c>
       <c r="L315">
-        <v>0.5809</v>
+        <v>0.581</v>
       </c>
       <c r="M315">
         <v>168</v>
@@ -14655,22 +14655,22 @@
         <v>61</v>
       </c>
       <c r="G320">
-        <v>0.2554</v>
+        <v>0.2659</v>
       </c>
       <c r="H320">
         <v>0.1852</v>
       </c>
       <c r="I320">
-        <v>0.2203</v>
+        <v>0.2256</v>
       </c>
       <c r="J320">
-        <v>0.7446</v>
+        <v>0.7341</v>
       </c>
       <c r="K320">
         <v>0.8148</v>
       </c>
       <c r="L320">
-        <v>0.7796999999999999</v>
+        <v>0.7744</v>
       </c>
       <c r="M320">
         <v>168</v>
@@ -14699,22 +14699,22 @@
         <v>62</v>
       </c>
       <c r="G321">
-        <v>0.2618</v>
+        <v>0.2672</v>
       </c>
       <c r="H321">
-        <v>0.1423</v>
+        <v>0.1447</v>
       </c>
       <c r="I321">
-        <v>0.202</v>
+        <v>0.206</v>
       </c>
       <c r="J321">
-        <v>0.7382</v>
+        <v>0.7328</v>
       </c>
       <c r="K321">
-        <v>0.8577</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="L321">
-        <v>0.798</v>
+        <v>0.794</v>
       </c>
       <c r="M321">
         <v>168</v>
@@ -14743,22 +14743,22 @@
         <v>63</v>
       </c>
       <c r="G322">
-        <v>0.2898</v>
+        <v>0.2988</v>
       </c>
       <c r="H322">
-        <v>0.1484</v>
+        <v>0.1514</v>
       </c>
       <c r="I322">
-        <v>0.2191</v>
+        <v>0.2251</v>
       </c>
       <c r="J322">
-        <v>0.7102000000000001</v>
+        <v>0.7012</v>
       </c>
       <c r="K322">
-        <v>0.8516</v>
+        <v>0.8486</v>
       </c>
       <c r="L322">
-        <v>0.7809</v>
+        <v>0.7749</v>
       </c>
       <c r="M322">
         <v>168</v>
@@ -14919,22 +14919,22 @@
         <v>67</v>
       </c>
       <c r="G326">
-        <v>0.2359</v>
+        <v>0.2262</v>
       </c>
       <c r="H326">
         <v>0.1435</v>
       </c>
       <c r="I326">
-        <v>0.1897</v>
+        <v>0.1849</v>
       </c>
       <c r="J326">
-        <v>0.7641</v>
+        <v>0.7738</v>
       </c>
       <c r="K326">
         <v>0.8565</v>
       </c>
       <c r="L326">
-        <v>0.8103</v>
+        <v>0.8151</v>
       </c>
       <c r="M326">
         <v>168</v>
@@ -14963,22 +14963,22 @@
         <v>68</v>
       </c>
       <c r="G327">
-        <v>0.5333</v>
+        <v>0.5273</v>
       </c>
       <c r="H327">
-        <v>0.3472</v>
+        <v>0.3433</v>
       </c>
       <c r="I327">
-        <v>0.4402</v>
+        <v>0.4353</v>
       </c>
       <c r="J327">
-        <v>0.4667</v>
+        <v>0.4727</v>
       </c>
       <c r="K327">
-        <v>0.6528</v>
+        <v>0.6567</v>
       </c>
       <c r="L327">
-        <v>0.5598</v>
+        <v>0.5647</v>
       </c>
       <c r="M327">
         <v>168</v>
@@ -15007,22 +15007,22 @@
         <v>69</v>
       </c>
       <c r="G328">
-        <v>0.4884</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="H328">
         <v>0.3114</v>
       </c>
       <c r="I328">
-        <v>0.3999</v>
+        <v>0.4074</v>
       </c>
       <c r="J328">
-        <v>0.5116000000000001</v>
+        <v>0.4965</v>
       </c>
       <c r="K328">
         <v>0.6886</v>
       </c>
       <c r="L328">
-        <v>0.6001</v>
+        <v>0.5926</v>
       </c>
       <c r="M328">
         <v>168</v>
@@ -15051,22 +15051,22 @@
         <v>70</v>
       </c>
       <c r="G329">
-        <v>0.5901</v>
+        <v>0.5949</v>
       </c>
       <c r="H329">
-        <v>0.422</v>
+        <v>0.4294</v>
       </c>
       <c r="I329">
-        <v>0.506</v>
+        <v>0.5122</v>
       </c>
       <c r="J329">
-        <v>0.4099</v>
+        <v>0.4051</v>
       </c>
       <c r="K329">
-        <v>0.578</v>
+        <v>0.5706</v>
       </c>
       <c r="L329">
-        <v>0.494</v>
+        <v>0.4878</v>
       </c>
       <c r="M329">
         <v>168</v>
@@ -15095,22 +15095,22 @@
         <v>71</v>
       </c>
       <c r="G330">
-        <v>0.2457</v>
+        <v>0.2483</v>
       </c>
       <c r="H330">
         <v>0.1347</v>
       </c>
       <c r="I330">
-        <v>0.1902</v>
+        <v>0.1915</v>
       </c>
       <c r="J330">
-        <v>0.7543</v>
+        <v>0.7517</v>
       </c>
       <c r="K330">
         <v>0.8653</v>
       </c>
       <c r="L330">
-        <v>0.8098</v>
+        <v>0.8085</v>
       </c>
       <c r="M330">
         <v>168</v>
@@ -15139,22 +15139,22 @@
         <v>73</v>
       </c>
       <c r="G331">
-        <v>0.2092</v>
+        <v>0.2138</v>
       </c>
       <c r="H331">
-        <v>0.119</v>
+        <v>0.1206</v>
       </c>
       <c r="I331">
-        <v>0.1641</v>
+        <v>0.1672</v>
       </c>
       <c r="J331">
-        <v>0.7907999999999999</v>
+        <v>0.7862</v>
       </c>
       <c r="K331">
-        <v>0.881</v>
+        <v>0.8794</v>
       </c>
       <c r="L331">
-        <v>0.8359</v>
+        <v>0.8328</v>
       </c>
       <c r="M331">
         <v>168</v>
@@ -15183,22 +15183,22 @@
         <v>59</v>
       </c>
       <c r="G332">
-        <v>0.8129</v>
+        <v>0.8101</v>
       </c>
       <c r="H332">
-        <v>0.6415999999999999</v>
+        <v>0.6415</v>
       </c>
       <c r="I332">
-        <v>0.7272</v>
+        <v>0.7258</v>
       </c>
       <c r="J332">
-        <v>0.1871</v>
+        <v>0.1899</v>
       </c>
       <c r="K332">
-        <v>0.3584</v>
+        <v>0.3585</v>
       </c>
       <c r="L332">
-        <v>0.2728</v>
+        <v>0.2742</v>
       </c>
       <c r="M332">
         <v>168</v>
@@ -15227,22 +15227,22 @@
         <v>60</v>
       </c>
       <c r="G333">
-        <v>0.8579</v>
+        <v>0.8574000000000001</v>
       </c>
       <c r="H333">
-        <v>0.7554</v>
+        <v>0.7508</v>
       </c>
       <c r="I333">
-        <v>0.8066</v>
+        <v>0.8041</v>
       </c>
       <c r="J333">
-        <v>0.1421</v>
+        <v>0.1426</v>
       </c>
       <c r="K333">
-        <v>0.2446</v>
+        <v>0.2492</v>
       </c>
       <c r="L333">
-        <v>0.1934</v>
+        <v>0.1959</v>
       </c>
       <c r="M333">
         <v>168</v>
@@ -15271,22 +15271,22 @@
         <v>61</v>
       </c>
       <c r="G334">
-        <v>0.7603</v>
+        <v>0.7594</v>
       </c>
       <c r="H334">
         <v>0.6447000000000001</v>
       </c>
       <c r="I334">
-        <v>0.7025</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="J334">
-        <v>0.2397</v>
+        <v>0.2406</v>
       </c>
       <c r="K334">
         <v>0.3553</v>
       </c>
       <c r="L334">
-        <v>0.2975</v>
+        <v>0.2979</v>
       </c>
       <c r="M334">
         <v>168</v>
@@ -15315,22 +15315,22 @@
         <v>62</v>
       </c>
       <c r="G335">
-        <v>0.7632</v>
+        <v>0.7599</v>
       </c>
       <c r="H335">
-        <v>0.5926</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="I335">
-        <v>0.6778999999999999</v>
+        <v>0.675</v>
       </c>
       <c r="J335">
-        <v>0.2368</v>
+        <v>0.2401</v>
       </c>
       <c r="K335">
-        <v>0.4074</v>
+        <v>0.4098</v>
       </c>
       <c r="L335">
-        <v>0.3221</v>
+        <v>0.325</v>
       </c>
       <c r="M335">
         <v>168</v>
@@ -15362,19 +15362,19 @@
         <v>0.771</v>
       </c>
       <c r="H336">
-        <v>0.6262</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="I336">
-        <v>0.6986</v>
+        <v>0.6947</v>
       </c>
       <c r="J336">
         <v>0.229</v>
       </c>
       <c r="K336">
-        <v>0.3738</v>
+        <v>0.3816</v>
       </c>
       <c r="L336">
-        <v>0.3014</v>
+        <v>0.3053</v>
       </c>
       <c r="M336">
         <v>168</v>
@@ -15406,19 +15406,19 @@
         <v>0.8866000000000001</v>
       </c>
       <c r="H337">
-        <v>0.8002</v>
+        <v>0.7973</v>
       </c>
       <c r="I337">
-        <v>0.8434</v>
+        <v>0.842</v>
       </c>
       <c r="J337">
         <v>0.1134</v>
       </c>
       <c r="K337">
-        <v>0.1998</v>
+        <v>0.2027</v>
       </c>
       <c r="L337">
-        <v>0.1566</v>
+        <v>0.158</v>
       </c>
       <c r="M337">
         <v>168</v>
@@ -15491,22 +15491,22 @@
         <v>66</v>
       </c>
       <c r="G339">
-        <v>0.4373</v>
+        <v>0.4317</v>
       </c>
       <c r="H339">
-        <v>0.3405</v>
+        <v>0.3381</v>
       </c>
       <c r="I339">
-        <v>0.3889</v>
+        <v>0.3849</v>
       </c>
       <c r="J339">
-        <v>0.5627</v>
+        <v>0.5683</v>
       </c>
       <c r="K339">
-        <v>0.6595</v>
+        <v>0.6619</v>
       </c>
       <c r="L339">
-        <v>0.6111</v>
+        <v>0.6151</v>
       </c>
       <c r="M339">
         <v>168</v>
@@ -15535,22 +15535,22 @@
         <v>67</v>
       </c>
       <c r="G340">
-        <v>0.7425</v>
+        <v>0.7239</v>
       </c>
       <c r="H340">
-        <v>0.5703</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="I340">
-        <v>0.6564</v>
+        <v>0.643</v>
       </c>
       <c r="J340">
-        <v>0.2575</v>
+        <v>0.2761</v>
       </c>
       <c r="K340">
-        <v>0.4297</v>
+        <v>0.438</v>
       </c>
       <c r="L340">
-        <v>0.3436</v>
+        <v>0.357</v>
       </c>
       <c r="M340">
         <v>168</v>
@@ -15579,22 +15579,22 @@
         <v>68</v>
       </c>
       <c r="G341">
-        <v>0.888</v>
+        <v>0.8839</v>
       </c>
       <c r="H341">
-        <v>0.7781</v>
+        <v>0.7647</v>
       </c>
       <c r="I341">
-        <v>0.833</v>
+        <v>0.8243</v>
       </c>
       <c r="J341">
-        <v>0.112</v>
+        <v>0.1161</v>
       </c>
       <c r="K341">
-        <v>0.2219</v>
+        <v>0.2353</v>
       </c>
       <c r="L341">
-        <v>0.167</v>
+        <v>0.1757</v>
       </c>
       <c r="M341">
         <v>168</v>
@@ -15623,22 +15623,22 @@
         <v>69</v>
       </c>
       <c r="G342">
-        <v>0.8871</v>
+        <v>0.8829</v>
       </c>
       <c r="H342">
         <v>0.7706</v>
       </c>
       <c r="I342">
-        <v>0.8288</v>
+        <v>0.8268</v>
       </c>
       <c r="J342">
-        <v>0.1129</v>
+        <v>0.1171</v>
       </c>
       <c r="K342">
         <v>0.2294</v>
       </c>
       <c r="L342">
-        <v>0.1712</v>
+        <v>0.1732</v>
       </c>
       <c r="M342">
         <v>168</v>
@@ -15667,22 +15667,22 @@
         <v>70</v>
       </c>
       <c r="G343">
-        <v>0.8806</v>
+        <v>0.8778</v>
       </c>
       <c r="H343">
-        <v>0.7907999999999999</v>
+        <v>0.7862</v>
       </c>
       <c r="I343">
-        <v>0.8357</v>
+        <v>0.832</v>
       </c>
       <c r="J343">
-        <v>0.1194</v>
+        <v>0.1222</v>
       </c>
       <c r="K343">
-        <v>0.2092</v>
+        <v>0.2138</v>
       </c>
       <c r="L343">
-        <v>0.1643</v>
+        <v>0.168</v>
       </c>
       <c r="M343">
         <v>168</v>
@@ -15711,22 +15711,22 @@
         <v>71</v>
       </c>
       <c r="G344">
-        <v>0.6269</v>
+        <v>0.6271</v>
       </c>
       <c r="H344">
-        <v>0.4595</v>
+        <v>0.4604</v>
       </c>
       <c r="I344">
-        <v>0.5432</v>
+        <v>0.5438</v>
       </c>
       <c r="J344">
-        <v>0.3731</v>
+        <v>0.3729</v>
       </c>
       <c r="K344">
-        <v>0.5405</v>
+        <v>0.5396</v>
       </c>
       <c r="L344">
-        <v>0.4568</v>
+        <v>0.4562</v>
       </c>
       <c r="M344">
         <v>168</v>
@@ -15755,22 +15755,22 @@
         <v>73</v>
       </c>
       <c r="G345">
-        <v>0.6266</v>
+        <v>0.6228</v>
       </c>
       <c r="H345">
         <v>0.4655</v>
       </c>
       <c r="I345">
-        <v>0.546</v>
+        <v>0.5442</v>
       </c>
       <c r="J345">
-        <v>0.3734</v>
+        <v>0.3772</v>
       </c>
       <c r="K345">
         <v>0.5345</v>
       </c>
       <c r="L345">
-        <v>0.454</v>
+        <v>0.4558</v>
       </c>
       <c r="M345">
         <v>168</v>
@@ -15799,22 +15799,22 @@
         <v>60</v>
       </c>
       <c r="G346">
-        <v>0.7481</v>
+        <v>0.7456</v>
       </c>
       <c r="H346">
-        <v>0.6086</v>
+        <v>0.6027</v>
       </c>
       <c r="I346">
-        <v>0.6784</v>
+        <v>0.6742</v>
       </c>
       <c r="J346">
-        <v>0.2519</v>
+        <v>0.2544</v>
       </c>
       <c r="K346">
-        <v>0.3914</v>
+        <v>0.3973</v>
       </c>
       <c r="L346">
-        <v>0.3216</v>
+        <v>0.3258</v>
       </c>
       <c r="M346">
         <v>168</v>
@@ -15843,22 +15843,22 @@
         <v>61</v>
       </c>
       <c r="G347">
-        <v>0.5364</v>
+        <v>0.5391</v>
       </c>
       <c r="H347">
-        <v>0.3988</v>
+        <v>0.4002</v>
       </c>
       <c r="I347">
-        <v>0.4676</v>
+        <v>0.4696</v>
       </c>
       <c r="J347">
-        <v>0.4636</v>
+        <v>0.4609</v>
       </c>
       <c r="K347">
-        <v>0.6012</v>
+        <v>0.5998</v>
       </c>
       <c r="L347">
-        <v>0.5324</v>
+        <v>0.5304</v>
       </c>
       <c r="M347">
         <v>168</v>
@@ -15975,22 +15975,22 @@
         <v>64</v>
       </c>
       <c r="G350">
-        <v>0.8043</v>
+        <v>0.8031</v>
       </c>
       <c r="H350">
-        <v>0.6942</v>
+        <v>0.6921</v>
       </c>
       <c r="I350">
-        <v>0.7492</v>
+        <v>0.7476</v>
       </c>
       <c r="J350">
-        <v>0.1957</v>
+        <v>0.1969</v>
       </c>
       <c r="K350">
-        <v>0.3058</v>
+        <v>0.3079</v>
       </c>
       <c r="L350">
-        <v>0.2508</v>
+        <v>0.2524</v>
       </c>
       <c r="M350">
         <v>168</v>
@@ -16022,19 +16022,19 @@
         <v>0.3026</v>
       </c>
       <c r="H351">
-        <v>0.1666</v>
+        <v>0.1686</v>
       </c>
       <c r="I351">
-        <v>0.2346</v>
+        <v>0.2356</v>
       </c>
       <c r="J351">
         <v>0.6974</v>
       </c>
       <c r="K351">
-        <v>0.8334</v>
+        <v>0.8314</v>
       </c>
       <c r="L351">
-        <v>0.7654</v>
+        <v>0.7644</v>
       </c>
       <c r="M351">
         <v>168</v>
@@ -16107,22 +16107,22 @@
         <v>67</v>
       </c>
       <c r="G353">
-        <v>0.495</v>
+        <v>0.4923</v>
       </c>
       <c r="H353">
-        <v>0.349</v>
+        <v>0.3421</v>
       </c>
       <c r="I353">
-        <v>0.422</v>
+        <v>0.4172</v>
       </c>
       <c r="J353">
-        <v>0.505</v>
+        <v>0.5077</v>
       </c>
       <c r="K353">
-        <v>0.651</v>
+        <v>0.6579</v>
       </c>
       <c r="L353">
-        <v>0.578</v>
+        <v>0.5828</v>
       </c>
       <c r="M353">
         <v>168</v>
@@ -16151,22 +16151,22 @@
         <v>68</v>
       </c>
       <c r="G354">
-        <v>0.7756</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="H354">
-        <v>0.6718</v>
+        <v>0.6626</v>
       </c>
       <c r="I354">
-        <v>0.7237</v>
+        <v>0.7136</v>
       </c>
       <c r="J354">
-        <v>0.2244</v>
+        <v>0.2354</v>
       </c>
       <c r="K354">
-        <v>0.3282</v>
+        <v>0.3374</v>
       </c>
       <c r="L354">
-        <v>0.2763</v>
+        <v>0.2864</v>
       </c>
       <c r="M354">
         <v>168</v>
@@ -16195,22 +16195,22 @@
         <v>69</v>
       </c>
       <c r="G355">
-        <v>0.7852</v>
+        <v>0.7827</v>
       </c>
       <c r="H355">
-        <v>0.6327</v>
+        <v>0.6246</v>
       </c>
       <c r="I355">
-        <v>0.709</v>
+        <v>0.7036</v>
       </c>
       <c r="J355">
-        <v>0.2148</v>
+        <v>0.2173</v>
       </c>
       <c r="K355">
-        <v>0.3673</v>
+        <v>0.3754</v>
       </c>
       <c r="L355">
-        <v>0.291</v>
+        <v>0.2964</v>
       </c>
       <c r="M355">
         <v>168</v>
@@ -16239,22 +16239,22 @@
         <v>70</v>
       </c>
       <c r="G356">
-        <v>0.8022</v>
+        <v>0.7993</v>
       </c>
       <c r="H356">
-        <v>0.6914</v>
+        <v>0.6901</v>
       </c>
       <c r="I356">
-        <v>0.7468</v>
+        <v>0.7447</v>
       </c>
       <c r="J356">
-        <v>0.1978</v>
+        <v>0.2007</v>
       </c>
       <c r="K356">
-        <v>0.3086</v>
+        <v>0.3099</v>
       </c>
       <c r="L356">
-        <v>0.2532</v>
+        <v>0.2553</v>
       </c>
       <c r="M356">
         <v>168</v>
@@ -16371,22 +16371,22 @@
         <v>61</v>
       </c>
       <c r="G359">
-        <v>0.3658</v>
+        <v>0.3708</v>
       </c>
       <c r="H359">
-        <v>0.2293</v>
+        <v>0.2306</v>
       </c>
       <c r="I359">
-        <v>0.2976</v>
+        <v>0.3007</v>
       </c>
       <c r="J359">
-        <v>0.6342</v>
+        <v>0.6292</v>
       </c>
       <c r="K359">
-        <v>0.7707000000000001</v>
+        <v>0.7694</v>
       </c>
       <c r="L359">
-        <v>0.7024</v>
+        <v>0.6993</v>
       </c>
       <c r="M359">
         <v>168</v>
@@ -16415,22 +16415,22 @@
         <v>62</v>
       </c>
       <c r="G360">
-        <v>0.3389</v>
+        <v>0.343</v>
       </c>
       <c r="H360">
-        <v>0.2109</v>
+        <v>0.2175</v>
       </c>
       <c r="I360">
-        <v>0.2749</v>
+        <v>0.2802</v>
       </c>
       <c r="J360">
-        <v>0.6611</v>
+        <v>0.657</v>
       </c>
       <c r="K360">
-        <v>0.7891</v>
+        <v>0.7825</v>
       </c>
       <c r="L360">
-        <v>0.7251</v>
+        <v>0.7198</v>
       </c>
       <c r="M360">
         <v>168</v>
@@ -16459,22 +16459,22 @@
         <v>63</v>
       </c>
       <c r="G361">
-        <v>0.4011</v>
+        <v>0.4057</v>
       </c>
       <c r="H361">
-        <v>0.2381</v>
+        <v>0.2412</v>
       </c>
       <c r="I361">
-        <v>0.3196</v>
+        <v>0.3234</v>
       </c>
       <c r="J361">
-        <v>0.5989</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="K361">
-        <v>0.7619</v>
+        <v>0.7588</v>
       </c>
       <c r="L361">
-        <v>0.6804</v>
+        <v>0.6766</v>
       </c>
       <c r="M361">
         <v>168</v>
@@ -16506,19 +16506,19 @@
         <v>0.6582</v>
       </c>
       <c r="H362">
-        <v>0.5725</v>
+        <v>0.5538</v>
       </c>
       <c r="I362">
-        <v>0.6153999999999999</v>
+        <v>0.606</v>
       </c>
       <c r="J362">
         <v>0.3418</v>
       </c>
       <c r="K362">
-        <v>0.4275</v>
+        <v>0.4462</v>
       </c>
       <c r="L362">
-        <v>0.3846</v>
+        <v>0.394</v>
       </c>
       <c r="M362">
         <v>168</v>
@@ -16547,22 +16547,22 @@
         <v>65</v>
       </c>
       <c r="G363">
-        <v>0.2438</v>
+        <v>0.2485</v>
       </c>
       <c r="H363">
         <v>0.1365</v>
       </c>
       <c r="I363">
-        <v>0.1901</v>
+        <v>0.1925</v>
       </c>
       <c r="J363">
-        <v>0.7562</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="K363">
         <v>0.8635</v>
       </c>
       <c r="L363">
-        <v>0.8099</v>
+        <v>0.8075</v>
       </c>
       <c r="M363">
         <v>168</v>
@@ -16591,22 +16591,22 @@
         <v>66</v>
       </c>
       <c r="G364">
-        <v>0.2447</v>
+        <v>0.2493</v>
       </c>
       <c r="H364">
         <v>0.132</v>
       </c>
       <c r="I364">
-        <v>0.1884</v>
+        <v>0.1906</v>
       </c>
       <c r="J364">
-        <v>0.7553</v>
+        <v>0.7507</v>
       </c>
       <c r="K364">
         <v>0.868</v>
       </c>
       <c r="L364">
-        <v>0.8116</v>
+        <v>0.8094</v>
       </c>
       <c r="M364">
         <v>168</v>
@@ -16635,22 +16635,22 @@
         <v>67</v>
       </c>
       <c r="G365">
-        <v>0.3121</v>
+        <v>0.3097</v>
       </c>
       <c r="H365">
-        <v>0.2033</v>
+        <v>0.1977</v>
       </c>
       <c r="I365">
-        <v>0.2577</v>
+        <v>0.2537</v>
       </c>
       <c r="J365">
-        <v>0.6879</v>
+        <v>0.6903</v>
       </c>
       <c r="K365">
-        <v>0.7967</v>
+        <v>0.8023</v>
       </c>
       <c r="L365">
-        <v>0.7423</v>
+        <v>0.7463</v>
       </c>
       <c r="M365">
         <v>168</v>
@@ -16679,22 +16679,22 @@
         <v>68</v>
       </c>
       <c r="G366">
-        <v>0.6269</v>
+        <v>0.6155</v>
       </c>
       <c r="H366">
-        <v>0.5485</v>
+        <v>0.5209</v>
       </c>
       <c r="I366">
-        <v>0.5877</v>
+        <v>0.5682</v>
       </c>
       <c r="J366">
-        <v>0.3731</v>
+        <v>0.3845</v>
       </c>
       <c r="K366">
-        <v>0.4515</v>
+        <v>0.4791</v>
       </c>
       <c r="L366">
-        <v>0.4123</v>
+        <v>0.4318</v>
       </c>
       <c r="M366">
         <v>168</v>
@@ -16723,22 +16723,22 @@
         <v>69</v>
       </c>
       <c r="G367">
-        <v>0.6152</v>
+        <v>0.615</v>
       </c>
       <c r="H367">
         <v>0.4879</v>
       </c>
       <c r="I367">
-        <v>0.5516</v>
+        <v>0.5514</v>
       </c>
       <c r="J367">
-        <v>0.3848</v>
+        <v>0.385</v>
       </c>
       <c r="K367">
         <v>0.5121</v>
       </c>
       <c r="L367">
-        <v>0.4484</v>
+        <v>0.4486</v>
       </c>
       <c r="M367">
         <v>168</v>
@@ -16858,19 +16858,19 @@
         <v>0.2825</v>
       </c>
       <c r="H370">
-        <v>0.1573</v>
+        <v>0.1597</v>
       </c>
       <c r="I370">
-        <v>0.2199</v>
+        <v>0.2211</v>
       </c>
       <c r="J370">
         <v>0.7175</v>
       </c>
       <c r="K370">
-        <v>0.8427</v>
+        <v>0.8403</v>
       </c>
       <c r="L370">
-        <v>0.7801</v>
+        <v>0.7789</v>
       </c>
       <c r="M370">
         <v>168</v>
@@ -16987,22 +16987,22 @@
         <v>64</v>
       </c>
       <c r="G373">
-        <v>0.8378</v>
+        <v>0.8286</v>
       </c>
       <c r="H373">
         <v>0.7229</v>
       </c>
       <c r="I373">
-        <v>0.7804</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="J373">
-        <v>0.1622</v>
+        <v>0.1714</v>
       </c>
       <c r="K373">
         <v>0.2771</v>
       </c>
       <c r="L373">
-        <v>0.2196</v>
+        <v>0.2243</v>
       </c>
       <c r="M373">
         <v>168</v>
@@ -17034,19 +17034,19 @@
         <v>0.3329</v>
       </c>
       <c r="H374">
-        <v>0.198</v>
+        <v>0.1987</v>
       </c>
       <c r="I374">
-        <v>0.2654</v>
+        <v>0.2658</v>
       </c>
       <c r="J374">
         <v>0.6671</v>
       </c>
       <c r="K374">
-        <v>0.802</v>
+        <v>0.8013</v>
       </c>
       <c r="L374">
-        <v>0.7346</v>
+        <v>0.7342</v>
       </c>
       <c r="M374">
         <v>168</v>
@@ -17119,22 +17119,22 @@
         <v>67</v>
       </c>
       <c r="G376">
-        <v>0.5058</v>
+        <v>0.4895</v>
       </c>
       <c r="H376">
-        <v>0.4304</v>
+        <v>0.4156</v>
       </c>
       <c r="I376">
-        <v>0.4681</v>
+        <v>0.4526</v>
       </c>
       <c r="J376">
-        <v>0.4942</v>
+        <v>0.5105</v>
       </c>
       <c r="K376">
-        <v>0.5696</v>
+        <v>0.5844</v>
       </c>
       <c r="L376">
-        <v>0.5319</v>
+        <v>0.5474</v>
       </c>
       <c r="M376">
         <v>168</v>
@@ -17163,22 +17163,22 @@
         <v>68</v>
       </c>
       <c r="G377">
-        <v>0.8091</v>
+        <v>0.799</v>
       </c>
       <c r="H377">
-        <v>0.7019</v>
+        <v>0.6911</v>
       </c>
       <c r="I377">
-        <v>0.7554999999999999</v>
+        <v>0.745</v>
       </c>
       <c r="J377">
-        <v>0.1909</v>
+        <v>0.201</v>
       </c>
       <c r="K377">
-        <v>0.2981</v>
+        <v>0.3089</v>
       </c>
       <c r="L377">
-        <v>0.2445</v>
+        <v>0.255</v>
       </c>
       <c r="M377">
         <v>168</v>
@@ -17210,19 +17210,19 @@
         <v>0.8209</v>
       </c>
       <c r="H378">
-        <v>0.6516999999999999</v>
+        <v>0.644</v>
       </c>
       <c r="I378">
-        <v>0.7363</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="J378">
         <v>0.1791</v>
       </c>
       <c r="K378">
-        <v>0.3483</v>
+        <v>0.356</v>
       </c>
       <c r="L378">
-        <v>0.2637</v>
+        <v>0.2676</v>
       </c>
       <c r="M378">
         <v>168</v>
@@ -17254,19 +17254,19 @@
         <v>0.8268</v>
       </c>
       <c r="H379">
-        <v>0.7306</v>
+        <v>0.7259</v>
       </c>
       <c r="I379">
-        <v>0.7786999999999999</v>
+        <v>0.7764</v>
       </c>
       <c r="J379">
         <v>0.1732</v>
       </c>
       <c r="K379">
-        <v>0.2694</v>
+        <v>0.2741</v>
       </c>
       <c r="L379">
-        <v>0.2213</v>
+        <v>0.2236</v>
       </c>
       <c r="M379">
         <v>168</v>
@@ -17298,19 +17298,19 @@
         <v>0.4677</v>
       </c>
       <c r="H380">
-        <v>0.3161</v>
+        <v>0.3079</v>
       </c>
       <c r="I380">
-        <v>0.3919</v>
+        <v>0.3878</v>
       </c>
       <c r="J380">
         <v>0.5323</v>
       </c>
       <c r="K380">
-        <v>0.6839</v>
+        <v>0.6921</v>
       </c>
       <c r="L380">
-        <v>0.6081</v>
+        <v>0.6122</v>
       </c>
       <c r="M380">
         <v>168</v>
@@ -17342,19 +17342,19 @@
         <v>0.4798</v>
       </c>
       <c r="H381">
-        <v>0.2953</v>
+        <v>0.2918</v>
       </c>
       <c r="I381">
-        <v>0.3876</v>
+        <v>0.3858</v>
       </c>
       <c r="J381">
         <v>0.5202</v>
       </c>
       <c r="K381">
-        <v>0.7047</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="L381">
-        <v>0.6124000000000001</v>
+        <v>0.6142</v>
       </c>
       <c r="M381">
         <v>168</v>
@@ -17427,22 +17427,22 @@
         <v>64</v>
       </c>
       <c r="G383">
-        <v>0.83</v>
+        <v>0.8246</v>
       </c>
       <c r="H383">
-        <v>0.7197</v>
+        <v>0.7137</v>
       </c>
       <c r="I383">
-        <v>0.7748</v>
+        <v>0.7692</v>
       </c>
       <c r="J383">
-        <v>0.17</v>
+        <v>0.1754</v>
       </c>
       <c r="K383">
-        <v>0.2803</v>
+        <v>0.2863</v>
       </c>
       <c r="L383">
-        <v>0.2252</v>
+        <v>0.2308</v>
       </c>
       <c r="M383">
         <v>168</v>
@@ -17471,22 +17471,22 @@
         <v>65</v>
       </c>
       <c r="G384">
-        <v>0.3376</v>
+        <v>0.3402</v>
       </c>
       <c r="H384">
-        <v>0.2011</v>
+        <v>0.2025</v>
       </c>
       <c r="I384">
-        <v>0.2694</v>
+        <v>0.2714</v>
       </c>
       <c r="J384">
-        <v>0.6624</v>
+        <v>0.6598000000000001</v>
       </c>
       <c r="K384">
-        <v>0.7989000000000001</v>
+        <v>0.7975</v>
       </c>
       <c r="L384">
-        <v>0.7306</v>
+        <v>0.7286</v>
       </c>
       <c r="M384">
         <v>168</v>
@@ -17515,22 +17515,22 @@
         <v>66</v>
       </c>
       <c r="G385">
-        <v>0.3202</v>
+        <v>0.321</v>
       </c>
       <c r="H385">
-        <v>0.173</v>
+        <v>0.1736</v>
       </c>
       <c r="I385">
-        <v>0.2466</v>
+        <v>0.2473</v>
       </c>
       <c r="J385">
-        <v>0.6798</v>
+        <v>0.679</v>
       </c>
       <c r="K385">
-        <v>0.827</v>
+        <v>0.8264</v>
       </c>
       <c r="L385">
-        <v>0.7534</v>
+        <v>0.7527</v>
       </c>
       <c r="M385">
         <v>168</v>
@@ -17559,22 +17559,22 @@
         <v>67</v>
       </c>
       <c r="G386">
-        <v>0.5221</v>
+        <v>0.52</v>
       </c>
       <c r="H386">
-        <v>0.4175</v>
+        <v>0.3968</v>
       </c>
       <c r="I386">
-        <v>0.4698</v>
+        <v>0.4584</v>
       </c>
       <c r="J386">
-        <v>0.4779</v>
+        <v>0.48</v>
       </c>
       <c r="K386">
-        <v>0.5825</v>
+        <v>0.6032</v>
       </c>
       <c r="L386">
-        <v>0.5302</v>
+        <v>0.5416</v>
       </c>
       <c r="M386">
         <v>168</v>
@@ -17603,22 +17603,22 @@
         <v>68</v>
       </c>
       <c r="G387">
-        <v>0.8124</v>
+        <v>0.803</v>
       </c>
       <c r="H387">
-        <v>0.6840000000000001</v>
+        <v>0.6652</v>
       </c>
       <c r="I387">
-        <v>0.7482</v>
+        <v>0.7341</v>
       </c>
       <c r="J387">
-        <v>0.1876</v>
+        <v>0.197</v>
       </c>
       <c r="K387">
-        <v>0.316</v>
+        <v>0.3348</v>
       </c>
       <c r="L387">
-        <v>0.2518</v>
+        <v>0.2659</v>
       </c>
       <c r="M387">
         <v>168</v>
@@ -17647,22 +17647,22 @@
         <v>69</v>
       </c>
       <c r="G388">
-        <v>0.8368</v>
+        <v>0.8324</v>
       </c>
       <c r="H388">
-        <v>0.6554</v>
+        <v>0.6485</v>
       </c>
       <c r="I388">
-        <v>0.7461</v>
+        <v>0.7405</v>
       </c>
       <c r="J388">
-        <v>0.1632</v>
+        <v>0.1676</v>
       </c>
       <c r="K388">
-        <v>0.3446</v>
+        <v>0.3515</v>
       </c>
       <c r="L388">
-        <v>0.2539</v>
+        <v>0.2595</v>
       </c>
       <c r="M388">
         <v>168</v>
@@ -17691,22 +17691,22 @@
         <v>70</v>
       </c>
       <c r="G389">
-        <v>0.8478</v>
+        <v>0.8441</v>
       </c>
       <c r="H389">
-        <v>0.7189</v>
+        <v>0.7127</v>
       </c>
       <c r="I389">
-        <v>0.7834</v>
+        <v>0.7784</v>
       </c>
       <c r="J389">
-        <v>0.1522</v>
+        <v>0.1559</v>
       </c>
       <c r="K389">
-        <v>0.2811</v>
+        <v>0.2873</v>
       </c>
       <c r="L389">
-        <v>0.2166</v>
+        <v>0.2216</v>
       </c>
       <c r="M389">
         <v>168</v>
@@ -17779,22 +17779,22 @@
         <v>73</v>
       </c>
       <c r="G391">
-        <v>0.4476</v>
+        <v>0.4456</v>
       </c>
       <c r="H391">
-        <v>0.2925</v>
+        <v>0.287</v>
       </c>
       <c r="I391">
-        <v>0.37</v>
+        <v>0.3663</v>
       </c>
       <c r="J391">
-        <v>0.5524</v>
+        <v>0.5544</v>
       </c>
       <c r="K391">
-        <v>0.7075</v>
+        <v>0.713</v>
       </c>
       <c r="L391">
-        <v>0.63</v>
+        <v>0.6337</v>
       </c>
       <c r="M391">
         <v>168</v>
@@ -17823,22 +17823,22 @@
         <v>64</v>
       </c>
       <c r="G392">
-        <v>0.8143</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="H392">
-        <v>0.6721</v>
+        <v>0.6696</v>
       </c>
       <c r="I392">
-        <v>0.7432</v>
+        <v>0.7393</v>
       </c>
       <c r="J392">
-        <v>0.1857</v>
+        <v>0.191</v>
       </c>
       <c r="K392">
-        <v>0.3279</v>
+        <v>0.3304</v>
       </c>
       <c r="L392">
-        <v>0.2568</v>
+        <v>0.2607</v>
       </c>
       <c r="M392">
         <v>168</v>
@@ -17867,22 +17867,22 @@
         <v>65</v>
       </c>
       <c r="G393">
-        <v>0.2864</v>
+        <v>0.2969</v>
       </c>
       <c r="H393">
         <v>0.1968</v>
       </c>
       <c r="I393">
-        <v>0.2416</v>
+        <v>0.2468</v>
       </c>
       <c r="J393">
-        <v>0.7136</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="K393">
         <v>0.8032</v>
       </c>
       <c r="L393">
-        <v>0.7584</v>
+        <v>0.7532</v>
       </c>
       <c r="M393">
         <v>168</v>
@@ -17914,19 +17914,19 @@
         <v>0.2514</v>
       </c>
       <c r="H394">
-        <v>0.1951</v>
+        <v>0.1974</v>
       </c>
       <c r="I394">
-        <v>0.2232</v>
+        <v>0.2244</v>
       </c>
       <c r="J394">
         <v>0.7486</v>
       </c>
       <c r="K394">
-        <v>0.8048999999999999</v>
+        <v>0.8026</v>
       </c>
       <c r="L394">
-        <v>0.7768</v>
+        <v>0.7756</v>
       </c>
       <c r="M394">
         <v>168</v>
@@ -17955,22 +17955,22 @@
         <v>67</v>
       </c>
       <c r="G395">
-        <v>0.5208</v>
+        <v>0.501</v>
       </c>
       <c r="H395">
-        <v>0.3711</v>
+        <v>0.3675</v>
       </c>
       <c r="I395">
-        <v>0.446</v>
+        <v>0.4342</v>
       </c>
       <c r="J395">
-        <v>0.4792</v>
+        <v>0.499</v>
       </c>
       <c r="K395">
-        <v>0.6289</v>
+        <v>0.6325</v>
       </c>
       <c r="L395">
-        <v>0.554</v>
+        <v>0.5658</v>
       </c>
       <c r="M395">
         <v>168</v>
@@ -17999,22 +17999,22 @@
         <v>68</v>
       </c>
       <c r="G396">
-        <v>0.7885</v>
+        <v>0.7771</v>
       </c>
       <c r="H396">
-        <v>0.6634</v>
+        <v>0.6541</v>
       </c>
       <c r="I396">
-        <v>0.726</v>
+        <v>0.7156</v>
       </c>
       <c r="J396">
-        <v>0.2115</v>
+        <v>0.2229</v>
       </c>
       <c r="K396">
-        <v>0.3366</v>
+        <v>0.3459</v>
       </c>
       <c r="L396">
-        <v>0.274</v>
+        <v>0.2844</v>
       </c>
       <c r="M396">
         <v>168</v>
@@ -18043,22 +18043,22 @@
         <v>69</v>
       </c>
       <c r="G397">
-        <v>0.7593</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="H397">
-        <v>0.6301</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="I397">
-        <v>0.6947</v>
+        <v>0.6906</v>
       </c>
       <c r="J397">
-        <v>0.2407</v>
+        <v>0.2434</v>
       </c>
       <c r="K397">
-        <v>0.3699</v>
+        <v>0.3755</v>
       </c>
       <c r="L397">
-        <v>0.3053</v>
+        <v>0.3094</v>
       </c>
       <c r="M397">
         <v>168</v>
@@ -18090,19 +18090,19 @@
         <v>0.8209</v>
       </c>
       <c r="H398">
-        <v>0.6913</v>
+        <v>0.6844</v>
       </c>
       <c r="I398">
-        <v>0.7561</v>
+        <v>0.7526</v>
       </c>
       <c r="J398">
         <v>0.1791</v>
       </c>
       <c r="K398">
-        <v>0.3087</v>
+        <v>0.3156</v>
       </c>
       <c r="L398">
-        <v>0.2439</v>
+        <v>0.2474</v>
       </c>
       <c r="M398">
         <v>168</v>
@@ -18219,22 +18219,22 @@
         <v>65</v>
       </c>
       <c r="G401">
-        <v>0.2061</v>
+        <v>0.2091</v>
       </c>
       <c r="H401">
         <v>0.1176</v>
       </c>
       <c r="I401">
-        <v>0.1618</v>
+        <v>0.1634</v>
       </c>
       <c r="J401">
-        <v>0.7939000000000001</v>
+        <v>0.7909</v>
       </c>
       <c r="K401">
         <v>0.8824</v>
       </c>
       <c r="L401">
-        <v>0.8381999999999999</v>
+        <v>0.8366</v>
       </c>
       <c r="M401">
         <v>168</v>
@@ -18307,22 +18307,22 @@
         <v>67</v>
       </c>
       <c r="G403">
-        <v>0.2712</v>
+        <v>0.2667</v>
       </c>
       <c r="H403">
-        <v>0.1556</v>
+        <v>0.151</v>
       </c>
       <c r="I403">
-        <v>0.2134</v>
+        <v>0.2088</v>
       </c>
       <c r="J403">
-        <v>0.7288</v>
+        <v>0.7333</v>
       </c>
       <c r="K403">
-        <v>0.8444</v>
+        <v>0.849</v>
       </c>
       <c r="L403">
-        <v>0.7866</v>
+        <v>0.7912</v>
       </c>
       <c r="M403">
         <v>168</v>
@@ -18351,22 +18351,22 @@
         <v>68</v>
       </c>
       <c r="G404">
-        <v>0.5616</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="H404">
-        <v>0.3915</v>
+        <v>0.3877</v>
       </c>
       <c r="I404">
-        <v>0.4766</v>
+        <v>0.4663</v>
       </c>
       <c r="J404">
-        <v>0.4384</v>
+        <v>0.4551</v>
       </c>
       <c r="K404">
-        <v>0.6085</v>
+        <v>0.6123</v>
       </c>
       <c r="L404">
-        <v>0.5234</v>
+        <v>0.5337</v>
       </c>
       <c r="M404">
         <v>168</v>
@@ -18398,19 +18398,19 @@
         <v>0.5195</v>
       </c>
       <c r="H405">
-        <v>0.3709</v>
+        <v>0.3748</v>
       </c>
       <c r="I405">
-        <v>0.4452</v>
+        <v>0.4472</v>
       </c>
       <c r="J405">
         <v>0.4805</v>
       </c>
       <c r="K405">
-        <v>0.6291</v>
+        <v>0.6252</v>
       </c>
       <c r="L405">
-        <v>0.5548</v>
+        <v>0.5528</v>
       </c>
       <c r="M405">
         <v>168</v>
@@ -18483,22 +18483,22 @@
         <v>71</v>
       </c>
       <c r="G407">
-        <v>0.2665</v>
+        <v>0.2707</v>
       </c>
       <c r="H407">
-        <v>0.1451</v>
+        <v>0.148</v>
       </c>
       <c r="I407">
-        <v>0.2058</v>
+        <v>0.2094</v>
       </c>
       <c r="J407">
-        <v>0.7335</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="K407">
-        <v>0.8549</v>
+        <v>0.852</v>
       </c>
       <c r="L407">
-        <v>0.7942</v>
+        <v>0.7906</v>
       </c>
       <c r="M407">
         <v>168</v>
@@ -18527,22 +18527,22 @@
         <v>73</v>
       </c>
       <c r="G408">
-        <v>0.219</v>
+        <v>0.2229</v>
       </c>
       <c r="H408">
-        <v>0.1221</v>
+        <v>0.126</v>
       </c>
       <c r="I408">
-        <v>0.1706</v>
+        <v>0.1744</v>
       </c>
       <c r="J408">
-        <v>0.781</v>
+        <v>0.7771</v>
       </c>
       <c r="K408">
-        <v>0.8779</v>
+        <v>0.874</v>
       </c>
       <c r="L408">
-        <v>0.8294</v>
+        <v>0.8256</v>
       </c>
       <c r="M408">
         <v>168</v>
@@ -18571,22 +18571,22 @@
         <v>66</v>
       </c>
       <c r="G409">
-        <v>0.4657</v>
+        <v>0.4585</v>
       </c>
       <c r="H409">
-        <v>0.4089</v>
+        <v>0.4063</v>
       </c>
       <c r="I409">
-        <v>0.4373</v>
+        <v>0.4324</v>
       </c>
       <c r="J409">
-        <v>0.5343</v>
+        <v>0.5415</v>
       </c>
       <c r="K409">
-        <v>0.5911</v>
+        <v>0.5937</v>
       </c>
       <c r="L409">
-        <v>0.5627</v>
+        <v>0.5676</v>
       </c>
       <c r="M409">
         <v>168</v>
@@ -18615,22 +18615,22 @@
         <v>67</v>
       </c>
       <c r="G410">
-        <v>0.7803</v>
+        <v>0.7673</v>
       </c>
       <c r="H410">
-        <v>0.6423</v>
+        <v>0.635</v>
       </c>
       <c r="I410">
-        <v>0.7113</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="J410">
-        <v>0.2197</v>
+        <v>0.2327</v>
       </c>
       <c r="K410">
-        <v>0.3577</v>
+        <v>0.365</v>
       </c>
       <c r="L410">
-        <v>0.2887</v>
+        <v>0.2989</v>
       </c>
       <c r="M410">
         <v>168</v>
@@ -18659,22 +18659,22 @@
         <v>68</v>
       </c>
       <c r="G411">
-        <v>0.8801</v>
+        <v>0.8757</v>
       </c>
       <c r="H411">
-        <v>0.776</v>
+        <v>0.7625</v>
       </c>
       <c r="I411">
-        <v>0.828</v>
+        <v>0.8191000000000001</v>
       </c>
       <c r="J411">
-        <v>0.1199</v>
+        <v>0.1243</v>
       </c>
       <c r="K411">
-        <v>0.224</v>
+        <v>0.2375</v>
       </c>
       <c r="L411">
-        <v>0.172</v>
+        <v>0.1809</v>
       </c>
       <c r="M411">
         <v>168</v>
@@ -18703,22 +18703,22 @@
         <v>69</v>
       </c>
       <c r="G412">
-        <v>0.884</v>
+        <v>0.8796</v>
       </c>
       <c r="H412">
         <v>0.7704</v>
       </c>
       <c r="I412">
-        <v>0.8272</v>
+        <v>0.825</v>
       </c>
       <c r="J412">
-        <v>0.116</v>
+        <v>0.1204</v>
       </c>
       <c r="K412">
         <v>0.2296</v>
       </c>
       <c r="L412">
-        <v>0.1728</v>
+        <v>0.175</v>
       </c>
       <c r="M412">
         <v>168</v>
@@ -18747,22 +18747,22 @@
         <v>70</v>
       </c>
       <c r="G413">
-        <v>0.8878</v>
+        <v>0.8852</v>
       </c>
       <c r="H413">
-        <v>0.7806</v>
+        <v>0.7758</v>
       </c>
       <c r="I413">
-        <v>0.8342000000000001</v>
+        <v>0.8305</v>
       </c>
       <c r="J413">
-        <v>0.1122</v>
+        <v>0.1148</v>
       </c>
       <c r="K413">
-        <v>0.2194</v>
+        <v>0.2242</v>
       </c>
       <c r="L413">
-        <v>0.1658</v>
+        <v>0.1695</v>
       </c>
       <c r="M413">
         <v>168</v>
@@ -18794,19 +18794,19 @@
         <v>0.6953</v>
       </c>
       <c r="H414">
-        <v>0.5555</v>
+        <v>0.5496</v>
       </c>
       <c r="I414">
-        <v>0.6254</v>
+        <v>0.6224</v>
       </c>
       <c r="J414">
         <v>0.3047</v>
       </c>
       <c r="K414">
-        <v>0.4445</v>
+        <v>0.4504</v>
       </c>
       <c r="L414">
-        <v>0.3746</v>
+        <v>0.3776</v>
       </c>
       <c r="M414">
         <v>168</v>
@@ -18835,22 +18835,22 @@
         <v>73</v>
       </c>
       <c r="G415">
-        <v>0.6977</v>
+        <v>0.6942</v>
       </c>
       <c r="H415">
         <v>0.5316</v>
       </c>
       <c r="I415">
-        <v>0.6146</v>
+        <v>0.6129</v>
       </c>
       <c r="J415">
-        <v>0.3023</v>
+        <v>0.3058</v>
       </c>
       <c r="K415">
         <v>0.4684</v>
       </c>
       <c r="L415">
-        <v>0.3854</v>
+        <v>0.3871</v>
       </c>
       <c r="M415">
         <v>168</v>
@@ -18879,22 +18879,22 @@
         <v>67</v>
       </c>
       <c r="G416">
-        <v>0.7971</v>
+        <v>0.7907</v>
       </c>
       <c r="H416">
-        <v>0.6774</v>
+        <v>0.6623</v>
       </c>
       <c r="I416">
-        <v>0.7372</v>
+        <v>0.7265</v>
       </c>
       <c r="J416">
-        <v>0.2029</v>
+        <v>0.2093</v>
       </c>
       <c r="K416">
-        <v>0.3226</v>
+        <v>0.3377</v>
       </c>
       <c r="L416">
-        <v>0.2628</v>
+        <v>0.2735</v>
       </c>
       <c r="M416">
         <v>168</v>
@@ -18923,22 +18923,22 @@
         <v>68</v>
       </c>
       <c r="G417">
-        <v>0.8767</v>
+        <v>0.8728</v>
       </c>
       <c r="H417">
-        <v>0.7742</v>
+        <v>0.7657</v>
       </c>
       <c r="I417">
-        <v>0.8254</v>
+        <v>0.8192</v>
       </c>
       <c r="J417">
-        <v>0.1233</v>
+        <v>0.1272</v>
       </c>
       <c r="K417">
-        <v>0.2258</v>
+        <v>0.2343</v>
       </c>
       <c r="L417">
-        <v>0.1746</v>
+        <v>0.1808</v>
       </c>
       <c r="M417">
         <v>168</v>
@@ -18967,22 +18967,22 @@
         <v>69</v>
       </c>
       <c r="G418">
-        <v>0.8725000000000001</v>
+        <v>0.8708</v>
       </c>
       <c r="H418">
         <v>0.7755</v>
       </c>
       <c r="I418">
-        <v>0.824</v>
+        <v>0.8232</v>
       </c>
       <c r="J418">
-        <v>0.1275</v>
+        <v>0.1292</v>
       </c>
       <c r="K418">
         <v>0.2245</v>
       </c>
       <c r="L418">
-        <v>0.176</v>
+        <v>0.1768</v>
       </c>
       <c r="M418">
         <v>168</v>
@@ -19011,22 +19011,22 @@
         <v>70</v>
       </c>
       <c r="G419">
-        <v>0.887</v>
+        <v>0.8855</v>
       </c>
       <c r="H419">
-        <v>0.7749</v>
+        <v>0.7701</v>
       </c>
       <c r="I419">
-        <v>0.831</v>
+        <v>0.8278</v>
       </c>
       <c r="J419">
-        <v>0.113</v>
+        <v>0.1145</v>
       </c>
       <c r="K419">
-        <v>0.2251</v>
+        <v>0.2299</v>
       </c>
       <c r="L419">
-        <v>0.169</v>
+        <v>0.1722</v>
       </c>
       <c r="M419">
         <v>168</v>
@@ -19099,22 +19099,22 @@
         <v>73</v>
       </c>
       <c r="G421">
-        <v>0.7229</v>
+        <v>0.7217</v>
       </c>
       <c r="H421">
-        <v>0.6</v>
+        <v>0.6019</v>
       </c>
       <c r="I421">
-        <v>0.6614</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="J421">
-        <v>0.2771</v>
+        <v>0.2783</v>
       </c>
       <c r="K421">
-        <v>0.4</v>
+        <v>0.3981</v>
       </c>
       <c r="L421">
-        <v>0.3386</v>
+        <v>0.3382</v>
       </c>
       <c r="M421">
         <v>168</v>
@@ -19143,22 +19143,22 @@
         <v>68</v>
       </c>
       <c r="G422">
-        <v>0.8391999999999999</v>
+        <v>0.8361</v>
       </c>
       <c r="H422">
-        <v>0.7004</v>
+        <v>0.698</v>
       </c>
       <c r="I422">
-        <v>0.7698</v>
+        <v>0.767</v>
       </c>
       <c r="J422">
-        <v>0.1608</v>
+        <v>0.1639</v>
       </c>
       <c r="K422">
-        <v>0.2996</v>
+        <v>0.302</v>
       </c>
       <c r="L422">
-        <v>0.2302</v>
+        <v>0.233</v>
       </c>
       <c r="M422">
         <v>168</v>
@@ -19187,22 +19187,22 @@
         <v>69</v>
       </c>
       <c r="G423">
-        <v>0.8442</v>
+        <v>0.851</v>
       </c>
       <c r="H423">
-        <v>0.6742</v>
+        <v>0.6784</v>
       </c>
       <c r="I423">
-        <v>0.7592</v>
+        <v>0.7647</v>
       </c>
       <c r="J423">
-        <v>0.1558</v>
+        <v>0.149</v>
       </c>
       <c r="K423">
-        <v>0.3258</v>
+        <v>0.3216</v>
       </c>
       <c r="L423">
-        <v>0.2408</v>
+        <v>0.2353</v>
       </c>
       <c r="M423">
         <v>168</v>
@@ -19234,19 +19234,19 @@
         <v>0.8507</v>
       </c>
       <c r="H424">
-        <v>0.729</v>
+        <v>0.7356</v>
       </c>
       <c r="I424">
-        <v>0.7897999999999999</v>
+        <v>0.7932</v>
       </c>
       <c r="J424">
         <v>0.1493</v>
       </c>
       <c r="K424">
-        <v>0.271</v>
+        <v>0.2644</v>
       </c>
       <c r="L424">
-        <v>0.2102</v>
+        <v>0.2068</v>
       </c>
       <c r="M424">
         <v>168</v>
@@ -19275,22 +19275,22 @@
         <v>71</v>
       </c>
       <c r="G425">
-        <v>0.4865</v>
+        <v>0.4949</v>
       </c>
       <c r="H425">
-        <v>0.3507</v>
+        <v>0.3623</v>
       </c>
       <c r="I425">
-        <v>0.4186</v>
+        <v>0.4286</v>
       </c>
       <c r="J425">
-        <v>0.5135</v>
+        <v>0.5051</v>
       </c>
       <c r="K425">
-        <v>0.6493</v>
+        <v>0.6377</v>
       </c>
       <c r="L425">
-        <v>0.5814</v>
+        <v>0.5714</v>
       </c>
       <c r="M425">
         <v>168</v>
@@ -19319,22 +19319,22 @@
         <v>73</v>
       </c>
       <c r="G426">
-        <v>0.4742</v>
+        <v>0.492</v>
       </c>
       <c r="H426">
-        <v>0.3348</v>
+        <v>0.3479</v>
       </c>
       <c r="I426">
-        <v>0.4045</v>
+        <v>0.42</v>
       </c>
       <c r="J426">
-        <v>0.5258</v>
+        <v>0.508</v>
       </c>
       <c r="K426">
-        <v>0.6652</v>
+        <v>0.6521</v>
       </c>
       <c r="L426">
-        <v>0.5955</v>
+        <v>0.58</v>
       </c>
       <c r="M426">
         <v>168</v>
@@ -19363,22 +19363,22 @@
         <v>69</v>
       </c>
       <c r="G427">
-        <v>0.5145999999999999</v>
+        <v>0.5232</v>
       </c>
       <c r="H427">
-        <v>0.398</v>
+        <v>0.4003</v>
       </c>
       <c r="I427">
-        <v>0.4563</v>
+        <v>0.4618</v>
       </c>
       <c r="J427">
-        <v>0.4854</v>
+        <v>0.4768</v>
       </c>
       <c r="K427">
-        <v>0.602</v>
+        <v>0.5997</v>
       </c>
       <c r="L427">
-        <v>0.5437</v>
+        <v>0.5382</v>
       </c>
       <c r="M427">
         <v>168</v>
@@ -19407,22 +19407,22 @@
         <v>70</v>
       </c>
       <c r="G428">
-        <v>0.6094000000000001</v>
+        <v>0.638</v>
       </c>
       <c r="H428">
-        <v>0.5014999999999999</v>
+        <v>0.5131</v>
       </c>
       <c r="I428">
-        <v>0.5554</v>
+        <v>0.5756</v>
       </c>
       <c r="J428">
-        <v>0.3906</v>
+        <v>0.362</v>
       </c>
       <c r="K428">
-        <v>0.4985</v>
+        <v>0.4869</v>
       </c>
       <c r="L428">
-        <v>0.4446</v>
+        <v>0.4244</v>
       </c>
       <c r="M428">
         <v>168</v>
@@ -19451,22 +19451,22 @@
         <v>71</v>
       </c>
       <c r="G429">
-        <v>0.295</v>
+        <v>0.3065</v>
       </c>
       <c r="H429">
-        <v>0.1687</v>
+        <v>0.1788</v>
       </c>
       <c r="I429">
-        <v>0.2318</v>
+        <v>0.2426</v>
       </c>
       <c r="J429">
-        <v>0.705</v>
+        <v>0.6935</v>
       </c>
       <c r="K429">
-        <v>0.8313</v>
+        <v>0.8212</v>
       </c>
       <c r="L429">
-        <v>0.7682</v>
+        <v>0.7574</v>
       </c>
       <c r="M429">
         <v>168</v>
@@ -19495,22 +19495,22 @@
         <v>73</v>
       </c>
       <c r="G430">
-        <v>0.2507</v>
+        <v>0.2572</v>
       </c>
       <c r="H430">
-        <v>0.1328</v>
+        <v>0.1391</v>
       </c>
       <c r="I430">
-        <v>0.1917</v>
+        <v>0.1982</v>
       </c>
       <c r="J430">
-        <v>0.7493</v>
+        <v>0.7428</v>
       </c>
       <c r="K430">
-        <v>0.8672</v>
+        <v>0.8609</v>
       </c>
       <c r="L430">
-        <v>0.8083</v>
+        <v>0.8018</v>
       </c>
       <c r="M430">
         <v>168</v>
@@ -19583,22 +19583,22 @@
         <v>71</v>
       </c>
       <c r="G432">
-        <v>0.278</v>
+        <v>0.2843</v>
       </c>
       <c r="H432">
         <v>0.1576</v>
       </c>
       <c r="I432">
-        <v>0.2178</v>
+        <v>0.221</v>
       </c>
       <c r="J432">
-        <v>0.722</v>
+        <v>0.7157</v>
       </c>
       <c r="K432">
         <v>0.8424</v>
       </c>
       <c r="L432">
-        <v>0.7822</v>
+        <v>0.779</v>
       </c>
       <c r="M432">
         <v>168</v>
@@ -19630,19 +19630,19 @@
         <v>0.2652</v>
       </c>
       <c r="H433">
-        <v>0.1289</v>
+        <v>0.1369</v>
       </c>
       <c r="I433">
-        <v>0.197</v>
+        <v>0.201</v>
       </c>
       <c r="J433">
         <v>0.7348</v>
       </c>
       <c r="K433">
-        <v>0.8711</v>
+        <v>0.8631</v>
       </c>
       <c r="L433">
-        <v>0.803</v>
+        <v>0.799</v>
       </c>
       <c r="M433">
         <v>168</v>
@@ -19671,22 +19671,22 @@
         <v>71</v>
       </c>
       <c r="G434">
-        <v>0.2667</v>
+        <v>0.2717</v>
       </c>
       <c r="H434">
-        <v>0.166</v>
+        <v>0.168</v>
       </c>
       <c r="I434">
-        <v>0.2164</v>
+        <v>0.2198</v>
       </c>
       <c r="J434">
-        <v>0.7333</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="K434">
-        <v>0.834</v>
+        <v>0.832</v>
       </c>
       <c r="L434">
-        <v>0.7836</v>
+        <v>0.7802</v>
       </c>
       <c r="M434">
         <v>168</v>
@@ -19715,22 +19715,22 @@
         <v>73</v>
       </c>
       <c r="G435">
-        <v>0.2381</v>
+        <v>0.2417</v>
       </c>
       <c r="H435">
         <v>0.1292</v>
       </c>
       <c r="I435">
-        <v>0.1836</v>
+        <v>0.1854</v>
       </c>
       <c r="J435">
-        <v>0.7619</v>
+        <v>0.7583</v>
       </c>
       <c r="K435">
         <v>0.8708</v>
       </c>
       <c r="L435">
-        <v>0.8164</v>
+        <v>0.8146</v>
       </c>
       <c r="M435">
         <v>168</v>

--- a/nba/public/data/nba_matchup_probs.xlsx
+++ b/nba/public/data/nba_matchup_probs.xlsx
@@ -839,22 +839,22 @@
         <v>48</v>
       </c>
       <c r="G6">
-        <v>0.8365</v>
+        <v>0.8413</v>
       </c>
       <c r="H6">
         <v>0.7193000000000001</v>
       </c>
       <c r="I6">
-        <v>0.7779</v>
+        <v>0.7803</v>
       </c>
       <c r="J6">
-        <v>0.1635</v>
+        <v>0.1587</v>
       </c>
       <c r="K6">
         <v>0.2807</v>
       </c>
       <c r="L6">
-        <v>0.2221</v>
+        <v>0.2197</v>
       </c>
       <c r="M6">
         <v>179</v>
@@ -1015,22 +1015,22 @@
         <v>52</v>
       </c>
       <c r="G10">
-        <v>0.6209</v>
+        <v>0.628</v>
       </c>
       <c r="H10">
-        <v>0.4756</v>
+        <v>0.4776</v>
       </c>
       <c r="I10">
-        <v>0.5482</v>
+        <v>0.5528</v>
       </c>
       <c r="J10">
-        <v>0.3791</v>
+        <v>0.372</v>
       </c>
       <c r="K10">
-        <v>0.5244</v>
+        <v>0.5224</v>
       </c>
       <c r="L10">
-        <v>0.4518</v>
+        <v>0.4472</v>
       </c>
       <c r="M10">
         <v>179</v>
@@ -1323,22 +1323,22 @@
         <v>59</v>
       </c>
       <c r="G17">
-        <v>0.6828</v>
+        <v>0.6865</v>
       </c>
       <c r="H17">
-        <v>0.5212</v>
+        <v>0.5259</v>
       </c>
       <c r="I17">
-        <v>0.602</v>
+        <v>0.6062</v>
       </c>
       <c r="J17">
-        <v>0.3172</v>
+        <v>0.3135</v>
       </c>
       <c r="K17">
-        <v>0.4788</v>
+        <v>0.4741</v>
       </c>
       <c r="L17">
-        <v>0.398</v>
+        <v>0.3938</v>
       </c>
       <c r="M17">
         <v>179</v>
@@ -1367,22 +1367,22 @@
         <v>60</v>
       </c>
       <c r="G18">
-        <v>0.8187</v>
+        <v>0.8217</v>
       </c>
       <c r="H18">
         <v>0.7007</v>
       </c>
       <c r="I18">
-        <v>0.7597</v>
+        <v>0.7612</v>
       </c>
       <c r="J18">
-        <v>0.1813</v>
+        <v>0.1783</v>
       </c>
       <c r="K18">
         <v>0.2993</v>
       </c>
       <c r="L18">
-        <v>0.2403</v>
+        <v>0.2388</v>
       </c>
       <c r="M18">
         <v>179</v>
@@ -1455,22 +1455,22 @@
         <v>62</v>
       </c>
       <c r="G20">
-        <v>0.6455</v>
+        <v>0.6545</v>
       </c>
       <c r="H20">
         <v>0.485</v>
       </c>
       <c r="I20">
-        <v>0.5652</v>
+        <v>0.5698</v>
       </c>
       <c r="J20">
-        <v>0.3545</v>
+        <v>0.3455</v>
       </c>
       <c r="K20">
         <v>0.515</v>
       </c>
       <c r="L20">
-        <v>0.4348</v>
+        <v>0.4302</v>
       </c>
       <c r="M20">
         <v>179</v>
@@ -1499,22 +1499,22 @@
         <v>63</v>
       </c>
       <c r="G21">
-        <v>0.6454</v>
+        <v>0.6761</v>
       </c>
       <c r="H21">
-        <v>0.508</v>
+        <v>0.5172</v>
       </c>
       <c r="I21">
-        <v>0.5767</v>
+        <v>0.5966</v>
       </c>
       <c r="J21">
-        <v>0.3546</v>
+        <v>0.3239</v>
       </c>
       <c r="K21">
-        <v>0.492</v>
+        <v>0.4828</v>
       </c>
       <c r="L21">
-        <v>0.4233</v>
+        <v>0.4034</v>
       </c>
       <c r="M21">
         <v>179</v>
@@ -1675,22 +1675,22 @@
         <v>67</v>
       </c>
       <c r="G25">
-        <v>0.5867</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="H25">
-        <v>0.4636</v>
+        <v>0.4654</v>
       </c>
       <c r="I25">
-        <v>0.5252</v>
+        <v>0.5338000000000001</v>
       </c>
       <c r="J25">
-        <v>0.4133</v>
+        <v>0.3977</v>
       </c>
       <c r="K25">
-        <v>0.5364</v>
+        <v>0.5346</v>
       </c>
       <c r="L25">
-        <v>0.4748</v>
+        <v>0.4662</v>
       </c>
       <c r="M25">
         <v>179</v>
@@ -1895,7 +1895,7 @@
         <v>73</v>
       </c>
       <c r="G30">
-        <v>0.5824</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="H30">
         <v>0.4397</v>
@@ -1904,7 +1904,7 @@
         <v>0.511</v>
       </c>
       <c r="J30">
-        <v>0.4176</v>
+        <v>0.4178</v>
       </c>
       <c r="K30">
         <v>0.5603</v>
@@ -2027,22 +2027,22 @@
         <v>47</v>
       </c>
       <c r="G33">
-        <v>0.8819</v>
+        <v>0.884</v>
       </c>
       <c r="H33">
         <v>0.759</v>
       </c>
       <c r="I33">
-        <v>0.8204</v>
+        <v>0.8215</v>
       </c>
       <c r="J33">
-        <v>0.1181</v>
+        <v>0.116</v>
       </c>
       <c r="K33">
         <v>0.241</v>
       </c>
       <c r="L33">
-        <v>0.1796</v>
+        <v>0.1785</v>
       </c>
       <c r="M33">
         <v>179</v>
@@ -2247,22 +2247,22 @@
         <v>52</v>
       </c>
       <c r="G38">
-        <v>0.746</v>
+        <v>0.7502</v>
       </c>
       <c r="H38">
         <v>0.5906</v>
       </c>
       <c r="I38">
-        <v>0.6683</v>
+        <v>0.6704</v>
       </c>
       <c r="J38">
-        <v>0.254</v>
+        <v>0.2498</v>
       </c>
       <c r="K38">
         <v>0.4094</v>
       </c>
       <c r="L38">
-        <v>0.3317</v>
+        <v>0.3296</v>
       </c>
       <c r="M38">
         <v>179</v>
@@ -2294,7 +2294,7 @@
         <v>0.7524</v>
       </c>
       <c r="H39">
-        <v>0.6121</v>
+        <v>0.6119</v>
       </c>
       <c r="I39">
         <v>0.6822</v>
@@ -2303,7 +2303,7 @@
         <v>0.2476</v>
       </c>
       <c r="K39">
-        <v>0.3879</v>
+        <v>0.3881</v>
       </c>
       <c r="L39">
         <v>0.3178</v>
@@ -2423,22 +2423,22 @@
         <v>56</v>
       </c>
       <c r="G42">
-        <v>0.7469</v>
+        <v>0.7501</v>
       </c>
       <c r="H42">
         <v>0.541</v>
       </c>
       <c r="I42">
-        <v>0.644</v>
+        <v>0.6456</v>
       </c>
       <c r="J42">
-        <v>0.2531</v>
+        <v>0.2499</v>
       </c>
       <c r="K42">
         <v>0.459</v>
       </c>
       <c r="L42">
-        <v>0.356</v>
+        <v>0.3544</v>
       </c>
       <c r="M42">
         <v>179</v>
@@ -2555,22 +2555,22 @@
         <v>59</v>
       </c>
       <c r="G45">
-        <v>0.7904</v>
+        <v>0.7969000000000001</v>
       </c>
       <c r="H45">
-        <v>0.6452</v>
+        <v>0.6489</v>
       </c>
       <c r="I45">
-        <v>0.7178</v>
+        <v>0.7229</v>
       </c>
       <c r="J45">
-        <v>0.2096</v>
+        <v>0.2031</v>
       </c>
       <c r="K45">
-        <v>0.3548</v>
+        <v>0.3511</v>
       </c>
       <c r="L45">
-        <v>0.2822</v>
+        <v>0.2771</v>
       </c>
       <c r="M45">
         <v>179</v>
@@ -2602,19 +2602,19 @@
         <v>0.87</v>
       </c>
       <c r="H46">
-        <v>0.7591</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="I46">
-        <v>0.8146</v>
+        <v>0.8168</v>
       </c>
       <c r="J46">
         <v>0.13</v>
       </c>
       <c r="K46">
-        <v>0.2409</v>
+        <v>0.2364</v>
       </c>
       <c r="L46">
-        <v>0.1854</v>
+        <v>0.1832</v>
       </c>
       <c r="M46">
         <v>179</v>
@@ -2646,19 +2646,19 @@
         <v>0.7841</v>
       </c>
       <c r="H47">
-        <v>0.6447000000000001</v>
+        <v>0.6403</v>
       </c>
       <c r="I47">
-        <v>0.7144</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="J47">
         <v>0.2159</v>
       </c>
       <c r="K47">
-        <v>0.3553</v>
+        <v>0.3597</v>
       </c>
       <c r="L47">
-        <v>0.2856</v>
+        <v>0.2878</v>
       </c>
       <c r="M47">
         <v>179</v>
@@ -2690,19 +2690,19 @@
         <v>0.7852</v>
       </c>
       <c r="H48">
-        <v>0.6405999999999999</v>
+        <v>0.6451</v>
       </c>
       <c r="I48">
-        <v>0.7129</v>
+        <v>0.7151</v>
       </c>
       <c r="J48">
         <v>0.2148</v>
       </c>
       <c r="K48">
-        <v>0.3594</v>
+        <v>0.3549</v>
       </c>
       <c r="L48">
-        <v>0.2871</v>
+        <v>0.2849</v>
       </c>
       <c r="M48">
         <v>179</v>
@@ -2731,22 +2731,22 @@
         <v>63</v>
       </c>
       <c r="G49">
-        <v>0.7717000000000001</v>
+        <v>0.7883</v>
       </c>
       <c r="H49">
-        <v>0.6344</v>
+        <v>0.6533</v>
       </c>
       <c r="I49">
-        <v>0.703</v>
+        <v>0.7208</v>
       </c>
       <c r="J49">
-        <v>0.2283</v>
+        <v>0.2117</v>
       </c>
       <c r="K49">
-        <v>0.3656</v>
+        <v>0.3467</v>
       </c>
       <c r="L49">
-        <v>0.297</v>
+        <v>0.2792</v>
       </c>
       <c r="M49">
         <v>179</v>
@@ -2866,19 +2866,19 @@
         <v>0.6432</v>
       </c>
       <c r="H52">
-        <v>0.4896</v>
+        <v>0.494</v>
       </c>
       <c r="I52">
-        <v>0.5664</v>
+        <v>0.5686</v>
       </c>
       <c r="J52">
         <v>0.3568</v>
       </c>
       <c r="K52">
-        <v>0.5104</v>
+        <v>0.506</v>
       </c>
       <c r="L52">
-        <v>0.4336</v>
+        <v>0.4314</v>
       </c>
       <c r="M52">
         <v>179</v>
@@ -2907,22 +2907,22 @@
         <v>67</v>
       </c>
       <c r="G53">
-        <v>0.7306</v>
+        <v>0.7444</v>
       </c>
       <c r="H53">
-        <v>0.5770999999999999</v>
+        <v>0.5805</v>
       </c>
       <c r="I53">
-        <v>0.6538</v>
+        <v>0.6624</v>
       </c>
       <c r="J53">
-        <v>0.2694</v>
+        <v>0.2556</v>
       </c>
       <c r="K53">
-        <v>0.4229</v>
+        <v>0.4195</v>
       </c>
       <c r="L53">
-        <v>0.3462</v>
+        <v>0.3376</v>
       </c>
       <c r="M53">
         <v>179</v>
@@ -3391,22 +3391,22 @@
         <v>51</v>
       </c>
       <c r="G64">
-        <v>0.6878</v>
+        <v>0.6891</v>
       </c>
       <c r="H64">
         <v>0.4954</v>
       </c>
       <c r="I64">
-        <v>0.5916</v>
+        <v>0.5923</v>
       </c>
       <c r="J64">
-        <v>0.3122</v>
+        <v>0.3109</v>
       </c>
       <c r="K64">
         <v>0.5046</v>
       </c>
       <c r="L64">
-        <v>0.4084</v>
+        <v>0.4077</v>
       </c>
       <c r="M64">
         <v>179</v>
@@ -3438,19 +3438,19 @@
         <v>0.7081</v>
       </c>
       <c r="H65">
-        <v>0.5655</v>
+        <v>0.5633</v>
       </c>
       <c r="I65">
-        <v>0.6368</v>
+        <v>0.6357</v>
       </c>
       <c r="J65">
         <v>0.2919</v>
       </c>
       <c r="K65">
-        <v>0.4345</v>
+        <v>0.4367</v>
       </c>
       <c r="L65">
-        <v>0.3632</v>
+        <v>0.3643</v>
       </c>
       <c r="M65">
         <v>179</v>
@@ -3523,22 +3523,22 @@
         <v>54</v>
       </c>
       <c r="G67">
-        <v>0.7764</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="H67">
         <v>0.5899</v>
       </c>
       <c r="I67">
-        <v>0.6831</v>
+        <v>0.6838</v>
       </c>
       <c r="J67">
-        <v>0.2236</v>
+        <v>0.2223</v>
       </c>
       <c r="K67">
         <v>0.4101</v>
       </c>
       <c r="L67">
-        <v>0.3169</v>
+        <v>0.3162</v>
       </c>
       <c r="M67">
         <v>179</v>
@@ -3614,19 +3614,19 @@
         <v>0.7064</v>
       </c>
       <c r="H69">
-        <v>0.5575</v>
+        <v>0.5628</v>
       </c>
       <c r="I69">
-        <v>0.632</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="J69">
         <v>0.2936</v>
       </c>
       <c r="K69">
-        <v>0.4425</v>
+        <v>0.4372</v>
       </c>
       <c r="L69">
-        <v>0.368</v>
+        <v>0.3654</v>
       </c>
       <c r="M69">
         <v>179</v>
@@ -3743,22 +3743,22 @@
         <v>59</v>
       </c>
       <c r="G72">
-        <v>0.7781</v>
+        <v>0.7794</v>
       </c>
       <c r="H72">
-        <v>0.5958</v>
+        <v>0.5981</v>
       </c>
       <c r="I72">
-        <v>0.6869</v>
+        <v>0.6888</v>
       </c>
       <c r="J72">
-        <v>0.2219</v>
+        <v>0.2206</v>
       </c>
       <c r="K72">
-        <v>0.4042</v>
+        <v>0.4019</v>
       </c>
       <c r="L72">
-        <v>0.3131</v>
+        <v>0.3112</v>
       </c>
       <c r="M72">
         <v>179</v>
@@ -3875,22 +3875,22 @@
         <v>62</v>
       </c>
       <c r="G75">
-        <v>0.762</v>
+        <v>0.7634</v>
       </c>
       <c r="H75">
         <v>0.5554</v>
       </c>
       <c r="I75">
-        <v>0.6587</v>
+        <v>0.6594</v>
       </c>
       <c r="J75">
-        <v>0.238</v>
+        <v>0.2366</v>
       </c>
       <c r="K75">
         <v>0.4446</v>
       </c>
       <c r="L75">
-        <v>0.3413</v>
+        <v>0.3406</v>
       </c>
       <c r="M75">
         <v>179</v>
@@ -3919,22 +3919,22 @@
         <v>63</v>
       </c>
       <c r="G76">
-        <v>0.7687</v>
+        <v>0.7852</v>
       </c>
       <c r="H76">
-        <v>0.599</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="I76">
-        <v>0.6839</v>
+        <v>0.6988</v>
       </c>
       <c r="J76">
-        <v>0.2313</v>
+        <v>0.2148</v>
       </c>
       <c r="K76">
-        <v>0.401</v>
+        <v>0.3876</v>
       </c>
       <c r="L76">
-        <v>0.3161</v>
+        <v>0.3012</v>
       </c>
       <c r="M76">
         <v>179</v>
@@ -4095,22 +4095,22 @@
         <v>67</v>
       </c>
       <c r="G80">
-        <v>0.7082000000000001</v>
+        <v>0.715</v>
       </c>
       <c r="H80">
-        <v>0.5289</v>
+        <v>0.5352</v>
       </c>
       <c r="I80">
-        <v>0.6186</v>
+        <v>0.6251</v>
       </c>
       <c r="J80">
-        <v>0.2918</v>
+        <v>0.285</v>
       </c>
       <c r="K80">
-        <v>0.4711</v>
+        <v>0.4648</v>
       </c>
       <c r="L80">
-        <v>0.3814</v>
+        <v>0.3749</v>
       </c>
       <c r="M80">
         <v>179</v>
@@ -4274,19 +4274,19 @@
         <v>0.5664</v>
       </c>
       <c r="H84">
-        <v>0.4245</v>
+        <v>0.4314</v>
       </c>
       <c r="I84">
-        <v>0.4954</v>
+        <v>0.4989</v>
       </c>
       <c r="J84">
         <v>0.4336</v>
       </c>
       <c r="K84">
-        <v>0.5755</v>
+        <v>0.5686</v>
       </c>
       <c r="L84">
-        <v>0.5046</v>
+        <v>0.5011</v>
       </c>
       <c r="M84">
         <v>179</v>
@@ -4318,19 +4318,19 @@
         <v>0.6738</v>
       </c>
       <c r="H85">
-        <v>0.5249</v>
+        <v>0.5254</v>
       </c>
       <c r="I85">
-        <v>0.5994</v>
+        <v>0.5996</v>
       </c>
       <c r="J85">
         <v>0.3262</v>
       </c>
       <c r="K85">
-        <v>0.4751</v>
+        <v>0.4746</v>
       </c>
       <c r="L85">
-        <v>0.4006</v>
+        <v>0.4004</v>
       </c>
       <c r="M85">
         <v>179</v>
@@ -4494,19 +4494,19 @@
         <v>0.3817</v>
       </c>
       <c r="H89">
-        <v>0.2119</v>
+        <v>0.208</v>
       </c>
       <c r="I89">
-        <v>0.2968</v>
+        <v>0.2948</v>
       </c>
       <c r="J89">
         <v>0.6183</v>
       </c>
       <c r="K89">
-        <v>0.7881</v>
+        <v>0.792</v>
       </c>
       <c r="L89">
-        <v>0.7032</v>
+        <v>0.7052</v>
       </c>
       <c r="M89">
         <v>179</v>
@@ -4887,22 +4887,22 @@
         <v>59</v>
       </c>
       <c r="G98">
-        <v>0.3505</v>
+        <v>0.3495</v>
       </c>
       <c r="H98">
-        <v>0.2181</v>
+        <v>0.2196</v>
       </c>
       <c r="I98">
-        <v>0.2843</v>
+        <v>0.2845</v>
       </c>
       <c r="J98">
-        <v>0.6495</v>
+        <v>0.6505</v>
       </c>
       <c r="K98">
-        <v>0.7819</v>
+        <v>0.7804</v>
       </c>
       <c r="L98">
-        <v>0.7157</v>
+        <v>0.7155</v>
       </c>
       <c r="M98">
         <v>179</v>
@@ -4978,19 +4978,19 @@
         <v>0.3618</v>
       </c>
       <c r="H100">
-        <v>0.198</v>
+        <v>0.1944</v>
       </c>
       <c r="I100">
-        <v>0.2799</v>
+        <v>0.2781</v>
       </c>
       <c r="J100">
         <v>0.6382</v>
       </c>
       <c r="K100">
-        <v>0.802</v>
+        <v>0.8056</v>
       </c>
       <c r="L100">
-        <v>0.7201</v>
+        <v>0.7219</v>
       </c>
       <c r="M100">
         <v>179</v>
@@ -5063,22 +5063,22 @@
         <v>63</v>
       </c>
       <c r="G102">
-        <v>0.3659</v>
+        <v>0.3751</v>
       </c>
       <c r="H102">
-        <v>0.2102</v>
+        <v>0.2259</v>
       </c>
       <c r="I102">
-        <v>0.2881</v>
+        <v>0.3005</v>
       </c>
       <c r="J102">
-        <v>0.6341</v>
+        <v>0.6249</v>
       </c>
       <c r="K102">
-        <v>0.7897999999999999</v>
+        <v>0.7741</v>
       </c>
       <c r="L102">
-        <v>0.7119</v>
+        <v>0.6995</v>
       </c>
       <c r="M102">
         <v>179</v>
@@ -5239,22 +5239,22 @@
         <v>67</v>
       </c>
       <c r="G106">
-        <v>0.2996</v>
+        <v>0.3055</v>
       </c>
       <c r="H106">
-        <v>0.148</v>
+        <v>0.1505</v>
       </c>
       <c r="I106">
-        <v>0.2238</v>
+        <v>0.228</v>
       </c>
       <c r="J106">
-        <v>0.7004</v>
+        <v>0.6945</v>
       </c>
       <c r="K106">
-        <v>0.852</v>
+        <v>0.8495</v>
       </c>
       <c r="L106">
-        <v>0.7762</v>
+        <v>0.772</v>
       </c>
       <c r="M106">
         <v>179</v>
@@ -5415,22 +5415,22 @@
         <v>71</v>
       </c>
       <c r="G110">
-        <v>0.2559</v>
+        <v>0.2522</v>
       </c>
       <c r="H110">
         <v>0.1324</v>
       </c>
       <c r="I110">
-        <v>0.1942</v>
+        <v>0.1923</v>
       </c>
       <c r="J110">
-        <v>0.7441</v>
+        <v>0.7478</v>
       </c>
       <c r="K110">
         <v>0.8676</v>
       </c>
       <c r="L110">
-        <v>0.8058</v>
+        <v>0.8077</v>
       </c>
       <c r="M110">
         <v>179</v>
@@ -5459,22 +5459,22 @@
         <v>73</v>
       </c>
       <c r="G111">
-        <v>0.2848</v>
+        <v>0.2818</v>
       </c>
       <c r="H111">
         <v>0.1603</v>
       </c>
       <c r="I111">
-        <v>0.2226</v>
+        <v>0.221</v>
       </c>
       <c r="J111">
-        <v>0.7151999999999999</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="K111">
         <v>0.8397</v>
       </c>
       <c r="L111">
-        <v>0.7774</v>
+        <v>0.779</v>
       </c>
       <c r="M111">
         <v>179</v>
@@ -5635,22 +5635,22 @@
         <v>51</v>
       </c>
       <c r="G115">
-        <v>0.3143</v>
+        <v>0.3142</v>
       </c>
       <c r="H115">
-        <v>0.1587</v>
+        <v>0.1575</v>
       </c>
       <c r="I115">
-        <v>0.2365</v>
+        <v>0.2358</v>
       </c>
       <c r="J115">
-        <v>0.6857</v>
+        <v>0.6858</v>
       </c>
       <c r="K115">
-        <v>0.8413</v>
+        <v>0.8425</v>
       </c>
       <c r="L115">
-        <v>0.7635</v>
+        <v>0.7642</v>
       </c>
       <c r="M115">
         <v>179</v>
@@ -5679,22 +5679,22 @@
         <v>52</v>
       </c>
       <c r="G116">
-        <v>0.3386</v>
+        <v>0.3455</v>
       </c>
       <c r="H116">
         <v>0.1752</v>
       </c>
       <c r="I116">
-        <v>0.2569</v>
+        <v>0.2603</v>
       </c>
       <c r="J116">
-        <v>0.6614</v>
+        <v>0.6545</v>
       </c>
       <c r="K116">
         <v>0.8248</v>
       </c>
       <c r="L116">
-        <v>0.7431</v>
+        <v>0.7397</v>
       </c>
       <c r="M116">
         <v>179</v>
@@ -5899,22 +5899,22 @@
         <v>57</v>
       </c>
       <c r="G121">
-        <v>0.7375</v>
+        <v>0.7373</v>
       </c>
       <c r="H121">
         <v>0.5495</v>
       </c>
       <c r="I121">
-        <v>0.6435</v>
+        <v>0.6434</v>
       </c>
       <c r="J121">
-        <v>0.2625</v>
+        <v>0.2627</v>
       </c>
       <c r="K121">
         <v>0.4505</v>
       </c>
       <c r="L121">
-        <v>0.3565</v>
+        <v>0.3566</v>
       </c>
       <c r="M121">
         <v>179</v>
@@ -6122,19 +6122,19 @@
         <v>0.3751</v>
       </c>
       <c r="H126">
-        <v>0.1871</v>
+        <v>0.1891</v>
       </c>
       <c r="I126">
-        <v>0.2811</v>
+        <v>0.2821</v>
       </c>
       <c r="J126">
         <v>0.6249</v>
       </c>
       <c r="K126">
-        <v>0.8129</v>
+        <v>0.8109</v>
       </c>
       <c r="L126">
-        <v>0.7189</v>
+        <v>0.7179</v>
       </c>
       <c r="M126">
         <v>179</v>
@@ -6163,22 +6163,22 @@
         <v>63</v>
       </c>
       <c r="G127">
-        <v>0.391</v>
+        <v>0.4043</v>
       </c>
       <c r="H127">
-        <v>0.2202</v>
+        <v>0.2535</v>
       </c>
       <c r="I127">
-        <v>0.3056</v>
+        <v>0.3289</v>
       </c>
       <c r="J127">
-        <v>0.609</v>
+        <v>0.5957</v>
       </c>
       <c r="K127">
-        <v>0.7798</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="L127">
-        <v>0.6944</v>
+        <v>0.6711</v>
       </c>
       <c r="M127">
         <v>179</v>
@@ -6339,22 +6339,22 @@
         <v>67</v>
       </c>
       <c r="G131">
-        <v>0.3473</v>
+        <v>0.3503</v>
       </c>
       <c r="H131">
-        <v>0.1562</v>
+        <v>0.1586</v>
       </c>
       <c r="I131">
-        <v>0.2518</v>
+        <v>0.2544</v>
       </c>
       <c r="J131">
-        <v>0.6526999999999999</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="K131">
-        <v>0.8438</v>
+        <v>0.8414</v>
       </c>
       <c r="L131">
-        <v>0.7482</v>
+        <v>0.7456</v>
       </c>
       <c r="M131">
         <v>179</v>
@@ -6738,19 +6738,19 @@
         <v>0.3174</v>
       </c>
       <c r="H140">
-        <v>0.1648</v>
+        <v>0.1714</v>
       </c>
       <c r="I140">
-        <v>0.2411</v>
+        <v>0.2444</v>
       </c>
       <c r="J140">
         <v>0.6826</v>
       </c>
       <c r="K140">
-        <v>0.8352000000000001</v>
+        <v>0.8286</v>
       </c>
       <c r="L140">
-        <v>0.7589</v>
+        <v>0.7556</v>
       </c>
       <c r="M140">
         <v>179</v>
@@ -6914,19 +6914,19 @@
         <v>0.3</v>
       </c>
       <c r="H144">
-        <v>0.1754</v>
+        <v>0.1721</v>
       </c>
       <c r="I144">
-        <v>0.2377</v>
+        <v>0.236</v>
       </c>
       <c r="J144">
         <v>0.7</v>
       </c>
       <c r="K144">
-        <v>0.8246</v>
+        <v>0.8279</v>
       </c>
       <c r="L144">
-        <v>0.7623</v>
+        <v>0.764</v>
       </c>
       <c r="M144">
         <v>179</v>
@@ -7043,22 +7043,22 @@
         <v>59</v>
       </c>
       <c r="G147">
-        <v>0.3391</v>
+        <v>0.346</v>
       </c>
       <c r="H147">
-        <v>0.2005</v>
+        <v>0.2051</v>
       </c>
       <c r="I147">
-        <v>0.2698</v>
+        <v>0.2755</v>
       </c>
       <c r="J147">
-        <v>0.6609</v>
+        <v>0.654</v>
       </c>
       <c r="K147">
-        <v>0.7995</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="L147">
-        <v>0.7302</v>
+        <v>0.7245</v>
       </c>
       <c r="M147">
         <v>179</v>
@@ -7175,22 +7175,22 @@
         <v>62</v>
       </c>
       <c r="G150">
-        <v>0.3318</v>
+        <v>0.3309</v>
       </c>
       <c r="H150">
         <v>0.1867</v>
       </c>
       <c r="I150">
-        <v>0.2592</v>
+        <v>0.2588</v>
       </c>
       <c r="J150">
-        <v>0.6682</v>
+        <v>0.6691</v>
       </c>
       <c r="K150">
         <v>0.8133</v>
       </c>
       <c r="L150">
-        <v>0.7408</v>
+        <v>0.7412</v>
       </c>
       <c r="M150">
         <v>179</v>
@@ -7219,22 +7219,22 @@
         <v>63</v>
       </c>
       <c r="G151">
-        <v>0.3642</v>
+        <v>0.3771</v>
       </c>
       <c r="H151">
-        <v>0.197</v>
+        <v>0.2073</v>
       </c>
       <c r="I151">
-        <v>0.2806</v>
+        <v>0.2922</v>
       </c>
       <c r="J151">
-        <v>0.6358</v>
+        <v>0.6229</v>
       </c>
       <c r="K151">
-        <v>0.803</v>
+        <v>0.7927</v>
       </c>
       <c r="L151">
-        <v>0.7194</v>
+        <v>0.7078</v>
       </c>
       <c r="M151">
         <v>179</v>
@@ -7310,19 +7310,19 @@
         <v>0.2577</v>
       </c>
       <c r="H153">
-        <v>0.1418</v>
+        <v>0.1396</v>
       </c>
       <c r="I153">
-        <v>0.1997</v>
+        <v>0.1986</v>
       </c>
       <c r="J153">
         <v>0.7423</v>
       </c>
       <c r="K153">
-        <v>0.8582</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="L153">
-        <v>0.8003</v>
+        <v>0.8014</v>
       </c>
       <c r="M153">
         <v>179</v>
@@ -7354,19 +7354,19 @@
         <v>0.2987</v>
       </c>
       <c r="H154">
-        <v>0.1981</v>
+        <v>0.1975</v>
       </c>
       <c r="I154">
-        <v>0.2484</v>
+        <v>0.2481</v>
       </c>
       <c r="J154">
         <v>0.7013</v>
       </c>
       <c r="K154">
-        <v>0.8018999999999999</v>
+        <v>0.8025</v>
       </c>
       <c r="L154">
-        <v>0.7516</v>
+        <v>0.7519</v>
       </c>
       <c r="M154">
         <v>179</v>
@@ -7395,22 +7395,22 @@
         <v>67</v>
       </c>
       <c r="G155">
-        <v>0.2873</v>
+        <v>0.2922</v>
       </c>
       <c r="H155">
         <v>0.1558</v>
       </c>
       <c r="I155">
-        <v>0.2216</v>
+        <v>0.224</v>
       </c>
       <c r="J155">
-        <v>0.7127</v>
+        <v>0.7078</v>
       </c>
       <c r="K155">
         <v>0.8442</v>
       </c>
       <c r="L155">
-        <v>0.7784</v>
+        <v>0.776</v>
       </c>
       <c r="M155">
         <v>179</v>
@@ -7703,22 +7703,22 @@
         <v>51</v>
       </c>
       <c r="G162">
-        <v>0.6807</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="H162">
         <v>0.5163</v>
       </c>
       <c r="I162">
-        <v>0.5985</v>
+        <v>0.5992</v>
       </c>
       <c r="J162">
-        <v>0.3193</v>
+        <v>0.318</v>
       </c>
       <c r="K162">
         <v>0.4837</v>
       </c>
       <c r="L162">
-        <v>0.4015</v>
+        <v>0.4008</v>
       </c>
       <c r="M162">
         <v>179</v>
@@ -7750,19 +7750,19 @@
         <v>0.7305</v>
       </c>
       <c r="H163">
-        <v>0.5647</v>
+        <v>0.5686</v>
       </c>
       <c r="I163">
-        <v>0.6476</v>
+        <v>0.6496</v>
       </c>
       <c r="J163">
         <v>0.2695</v>
       </c>
       <c r="K163">
-        <v>0.4353</v>
+        <v>0.4314</v>
       </c>
       <c r="L163">
-        <v>0.3524</v>
+        <v>0.3504</v>
       </c>
       <c r="M163">
         <v>179</v>
@@ -7835,22 +7835,22 @@
         <v>54</v>
       </c>
       <c r="G165">
-        <v>0.7798</v>
+        <v>0.7811</v>
       </c>
       <c r="H165">
         <v>0.5772</v>
       </c>
       <c r="I165">
-        <v>0.6785</v>
+        <v>0.6792</v>
       </c>
       <c r="J165">
-        <v>0.2202</v>
+        <v>0.2189</v>
       </c>
       <c r="K165">
         <v>0.4228</v>
       </c>
       <c r="L165">
-        <v>0.3215</v>
+        <v>0.3208</v>
       </c>
       <c r="M165">
         <v>179</v>
@@ -7926,19 +7926,19 @@
         <v>0.7055</v>
       </c>
       <c r="H167">
-        <v>0.573</v>
+        <v>0.5783</v>
       </c>
       <c r="I167">
-        <v>0.6392</v>
+        <v>0.6419</v>
       </c>
       <c r="J167">
         <v>0.2945</v>
       </c>
       <c r="K167">
-        <v>0.427</v>
+        <v>0.4217</v>
       </c>
       <c r="L167">
-        <v>0.3608</v>
+        <v>0.3581</v>
       </c>
       <c r="M167">
         <v>179</v>
@@ -8055,22 +8055,22 @@
         <v>59</v>
       </c>
       <c r="G170">
-        <v>0.7858000000000001</v>
+        <v>0.787</v>
       </c>
       <c r="H170">
-        <v>0.6113</v>
+        <v>0.6136</v>
       </c>
       <c r="I170">
-        <v>0.6986</v>
+        <v>0.7003</v>
       </c>
       <c r="J170">
-        <v>0.2142</v>
+        <v>0.213</v>
       </c>
       <c r="K170">
-        <v>0.3887</v>
+        <v>0.3864</v>
       </c>
       <c r="L170">
-        <v>0.3014</v>
+        <v>0.2997</v>
       </c>
       <c r="M170">
         <v>179</v>
@@ -8187,22 +8187,22 @@
         <v>62</v>
       </c>
       <c r="G173">
-        <v>0.7423999999999999</v>
+        <v>0.7438</v>
       </c>
       <c r="H173">
         <v>0.5921999999999999</v>
       </c>
       <c r="I173">
-        <v>0.6673</v>
+        <v>0.668</v>
       </c>
       <c r="J173">
-        <v>0.2576</v>
+        <v>0.2562</v>
       </c>
       <c r="K173">
         <v>0.4078</v>
       </c>
       <c r="L173">
-        <v>0.3327</v>
+        <v>0.332</v>
       </c>
       <c r="M173">
         <v>179</v>
@@ -8231,22 +8231,22 @@
         <v>63</v>
       </c>
       <c r="G174">
-        <v>0.7735</v>
+        <v>0.7883</v>
       </c>
       <c r="H174">
-        <v>0.5846</v>
+        <v>0.598</v>
       </c>
       <c r="I174">
-        <v>0.679</v>
+        <v>0.6931</v>
       </c>
       <c r="J174">
-        <v>0.2265</v>
+        <v>0.2117</v>
       </c>
       <c r="K174">
-        <v>0.4154</v>
+        <v>0.402</v>
       </c>
       <c r="L174">
-        <v>0.321</v>
+        <v>0.3069</v>
       </c>
       <c r="M174">
         <v>179</v>
@@ -8407,22 +8407,22 @@
         <v>67</v>
       </c>
       <c r="G178">
-        <v>0.7010999999999999</v>
+        <v>0.7135</v>
       </c>
       <c r="H178">
-        <v>0.5574</v>
+        <v>0.5636</v>
       </c>
       <c r="I178">
-        <v>0.6292</v>
+        <v>0.6385</v>
       </c>
       <c r="J178">
-        <v>0.2989</v>
+        <v>0.2865</v>
       </c>
       <c r="K178">
-        <v>0.4426</v>
+        <v>0.4364</v>
       </c>
       <c r="L178">
-        <v>0.3708</v>
+        <v>0.3615</v>
       </c>
       <c r="M178">
         <v>179</v>
@@ -8586,19 +8586,19 @@
         <v>0.624</v>
       </c>
       <c r="H182">
-        <v>0.4328</v>
+        <v>0.4397</v>
       </c>
       <c r="I182">
-        <v>0.5284</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="J182">
         <v>0.376</v>
       </c>
       <c r="K182">
-        <v>0.5672</v>
+        <v>0.5603</v>
       </c>
       <c r="L182">
-        <v>0.4716</v>
+        <v>0.4682</v>
       </c>
       <c r="M182">
         <v>179</v>
@@ -8630,19 +8630,19 @@
         <v>0.7056</v>
       </c>
       <c r="H183">
-        <v>0.5443</v>
+        <v>0.5448</v>
       </c>
       <c r="I183">
-        <v>0.625</v>
+        <v>0.6252</v>
       </c>
       <c r="J183">
         <v>0.2944</v>
       </c>
       <c r="K183">
-        <v>0.4557</v>
+        <v>0.4552</v>
       </c>
       <c r="L183">
-        <v>0.375</v>
+        <v>0.3748</v>
       </c>
       <c r="M183">
         <v>179</v>
@@ -8715,22 +8715,22 @@
         <v>52</v>
       </c>
       <c r="G185">
-        <v>0.4998</v>
+        <v>0.5091</v>
       </c>
       <c r="H185">
-        <v>0.3514</v>
+        <v>0.3525</v>
       </c>
       <c r="I185">
-        <v>0.4256</v>
+        <v>0.4308</v>
       </c>
       <c r="J185">
-        <v>0.5002</v>
+        <v>0.4909</v>
       </c>
       <c r="K185">
-        <v>0.6486</v>
+        <v>0.6475</v>
       </c>
       <c r="L185">
-        <v>0.5744</v>
+        <v>0.5692</v>
       </c>
       <c r="M185">
         <v>179</v>
@@ -8935,22 +8935,22 @@
         <v>57</v>
       </c>
       <c r="G190">
-        <v>0.8368</v>
+        <v>0.8383</v>
       </c>
       <c r="H190">
         <v>0.7257</v>
       </c>
       <c r="I190">
-        <v>0.7812</v>
+        <v>0.782</v>
       </c>
       <c r="J190">
-        <v>0.1632</v>
+        <v>0.1617</v>
       </c>
       <c r="K190">
         <v>0.2743</v>
       </c>
       <c r="L190">
-        <v>0.2188</v>
+        <v>0.218</v>
       </c>
       <c r="M190">
         <v>179</v>
@@ -9023,22 +9023,22 @@
         <v>59</v>
       </c>
       <c r="G192">
-        <v>0.577</v>
+        <v>0.5851</v>
       </c>
       <c r="H192">
         <v>0.4295</v>
       </c>
       <c r="I192">
-        <v>0.5032</v>
+        <v>0.5073</v>
       </c>
       <c r="J192">
-        <v>0.423</v>
+        <v>0.4149</v>
       </c>
       <c r="K192">
         <v>0.5705</v>
       </c>
       <c r="L192">
-        <v>0.4968</v>
+        <v>0.4927</v>
       </c>
       <c r="M192">
         <v>179</v>
@@ -9067,22 +9067,22 @@
         <v>60</v>
       </c>
       <c r="G193">
-        <v>0.7857</v>
+        <v>0.7867</v>
       </c>
       <c r="H193">
         <v>0.6098</v>
       </c>
       <c r="I193">
-        <v>0.6978</v>
+        <v>0.6982</v>
       </c>
       <c r="J193">
-        <v>0.2143</v>
+        <v>0.2133</v>
       </c>
       <c r="K193">
         <v>0.3902</v>
       </c>
       <c r="L193">
-        <v>0.3022</v>
+        <v>0.3018</v>
       </c>
       <c r="M193">
         <v>179</v>
@@ -9155,22 +9155,22 @@
         <v>62</v>
       </c>
       <c r="G195">
-        <v>0.5185999999999999</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="H195">
-        <v>0.3982</v>
+        <v>0.3998</v>
       </c>
       <c r="I195">
-        <v>0.4584</v>
+        <v>0.4688</v>
       </c>
       <c r="J195">
-        <v>0.4814</v>
+        <v>0.4622</v>
       </c>
       <c r="K195">
-        <v>0.6018</v>
+        <v>0.6002</v>
       </c>
       <c r="L195">
-        <v>0.5416</v>
+        <v>0.5312</v>
       </c>
       <c r="M195">
         <v>179</v>
@@ -9199,22 +9199,22 @@
         <v>63</v>
       </c>
       <c r="G196">
-        <v>0.5358000000000001</v>
+        <v>0.5889</v>
       </c>
       <c r="H196">
-        <v>0.4032</v>
+        <v>0.4149</v>
       </c>
       <c r="I196">
-        <v>0.4695</v>
+        <v>0.5019</v>
       </c>
       <c r="J196">
-        <v>0.4642</v>
+        <v>0.4111</v>
       </c>
       <c r="K196">
-        <v>0.5968</v>
+        <v>0.5851</v>
       </c>
       <c r="L196">
-        <v>0.5305</v>
+        <v>0.4981</v>
       </c>
       <c r="M196">
         <v>179</v>
@@ -9375,22 +9375,22 @@
         <v>67</v>
       </c>
       <c r="G200">
-        <v>0.4707</v>
+        <v>0.4848</v>
       </c>
       <c r="H200">
-        <v>0.3475</v>
+        <v>0.3553</v>
       </c>
       <c r="I200">
-        <v>0.4091</v>
+        <v>0.42</v>
       </c>
       <c r="J200">
-        <v>0.5293</v>
+        <v>0.5152</v>
       </c>
       <c r="K200">
-        <v>0.6525</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="L200">
-        <v>0.5909</v>
+        <v>0.58</v>
       </c>
       <c r="M200">
         <v>179</v>
@@ -9419,22 +9419,22 @@
         <v>68</v>
       </c>
       <c r="G201">
-        <v>0.7916</v>
+        <v>0.793</v>
       </c>
       <c r="H201">
         <v>0.666</v>
       </c>
       <c r="I201">
-        <v>0.7288</v>
+        <v>0.7295</v>
       </c>
       <c r="J201">
-        <v>0.2084</v>
+        <v>0.207</v>
       </c>
       <c r="K201">
         <v>0.334</v>
       </c>
       <c r="L201">
-        <v>0.2712</v>
+        <v>0.2705</v>
       </c>
       <c r="M201">
         <v>179</v>
@@ -9466,19 +9466,19 @@
         <v>0.8064</v>
       </c>
       <c r="H202">
-        <v>0.6465</v>
+        <v>0.6492</v>
       </c>
       <c r="I202">
-        <v>0.7264</v>
+        <v>0.7278</v>
       </c>
       <c r="J202">
         <v>0.1936</v>
       </c>
       <c r="K202">
-        <v>0.3535</v>
+        <v>0.3508</v>
       </c>
       <c r="L202">
-        <v>0.2736</v>
+        <v>0.2722</v>
       </c>
       <c r="M202">
         <v>179</v>
@@ -9551,22 +9551,22 @@
         <v>71</v>
       </c>
       <c r="G204">
-        <v>0.3895</v>
+        <v>0.3923</v>
       </c>
       <c r="H204">
         <v>0.2537</v>
       </c>
       <c r="I204">
-        <v>0.3216</v>
+        <v>0.323</v>
       </c>
       <c r="J204">
-        <v>0.6105</v>
+        <v>0.6077</v>
       </c>
       <c r="K204">
         <v>0.7463</v>
       </c>
       <c r="L204">
-        <v>0.6784</v>
+        <v>0.677</v>
       </c>
       <c r="M204">
         <v>179</v>
@@ -9595,22 +9595,22 @@
         <v>73</v>
       </c>
       <c r="G205">
-        <v>0.4791</v>
+        <v>0.4692</v>
       </c>
       <c r="H205">
         <v>0.3254</v>
       </c>
       <c r="I205">
-        <v>0.4022</v>
+        <v>0.3973</v>
       </c>
       <c r="J205">
-        <v>0.5209</v>
+        <v>0.5308</v>
       </c>
       <c r="K205">
         <v>0.6746</v>
       </c>
       <c r="L205">
-        <v>0.5978</v>
+        <v>0.6027</v>
       </c>
       <c r="M205">
         <v>179</v>
@@ -9642,19 +9642,19 @@
         <v>0.5921</v>
       </c>
       <c r="H206">
-        <v>0.4914</v>
+        <v>0.4916</v>
       </c>
       <c r="I206">
-        <v>0.5417</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="J206">
         <v>0.4079</v>
       </c>
       <c r="K206">
-        <v>0.5086000000000001</v>
+        <v>0.5084</v>
       </c>
       <c r="L206">
-        <v>0.4583</v>
+        <v>0.4582</v>
       </c>
       <c r="M206">
         <v>179</v>
@@ -9903,22 +9903,22 @@
         <v>58</v>
       </c>
       <c r="G212">
-        <v>0.4847</v>
+        <v>0.4838</v>
       </c>
       <c r="H212">
-        <v>0.3189</v>
+        <v>0.3174</v>
       </c>
       <c r="I212">
-        <v>0.4018</v>
+        <v>0.4006</v>
       </c>
       <c r="J212">
-        <v>0.5153</v>
+        <v>0.5162</v>
       </c>
       <c r="K212">
-        <v>0.6811</v>
+        <v>0.6826</v>
       </c>
       <c r="L212">
-        <v>0.5982</v>
+        <v>0.5994</v>
       </c>
       <c r="M212">
         <v>179</v>
@@ -9947,22 +9947,22 @@
         <v>59</v>
       </c>
       <c r="G213">
-        <v>0.6724</v>
+        <v>0.6741</v>
       </c>
       <c r="H213">
         <v>0.5248</v>
       </c>
       <c r="I213">
-        <v>0.5986</v>
+        <v>0.5994</v>
       </c>
       <c r="J213">
-        <v>0.3276</v>
+        <v>0.3259</v>
       </c>
       <c r="K213">
         <v>0.4752</v>
       </c>
       <c r="L213">
-        <v>0.4014</v>
+        <v>0.4006</v>
       </c>
       <c r="M213">
         <v>179</v>
@@ -9991,22 +9991,22 @@
         <v>60</v>
       </c>
       <c r="G214">
-        <v>0.8193</v>
+        <v>0.8214</v>
       </c>
       <c r="H214">
-        <v>0.7112000000000001</v>
+        <v>0.711</v>
       </c>
       <c r="I214">
-        <v>0.7652</v>
+        <v>0.7662</v>
       </c>
       <c r="J214">
-        <v>0.1807</v>
+        <v>0.1786</v>
       </c>
       <c r="K214">
-        <v>0.2888</v>
+        <v>0.289</v>
       </c>
       <c r="L214">
-        <v>0.2348</v>
+        <v>0.2338</v>
       </c>
       <c r="M214">
         <v>179</v>
@@ -10123,22 +10123,22 @@
         <v>63</v>
       </c>
       <c r="G217">
-        <v>0.6643</v>
+        <v>0.6884</v>
       </c>
       <c r="H217">
-        <v>0.5159</v>
+        <v>0.555</v>
       </c>
       <c r="I217">
-        <v>0.5901</v>
+        <v>0.6217</v>
       </c>
       <c r="J217">
-        <v>0.3357</v>
+        <v>0.3116</v>
       </c>
       <c r="K217">
-        <v>0.4841</v>
+        <v>0.445</v>
       </c>
       <c r="L217">
-        <v>0.4099</v>
+        <v>0.3783</v>
       </c>
       <c r="M217">
         <v>179</v>
@@ -10258,19 +10258,19 @@
         <v>0.5673</v>
       </c>
       <c r="H220">
-        <v>0.3864</v>
+        <v>0.3876</v>
       </c>
       <c r="I220">
-        <v>0.4768</v>
+        <v>0.4774</v>
       </c>
       <c r="J220">
         <v>0.4327</v>
       </c>
       <c r="K220">
-        <v>0.6136</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="L220">
-        <v>0.5232</v>
+        <v>0.5226</v>
       </c>
       <c r="M220">
         <v>179</v>
@@ -10299,22 +10299,22 @@
         <v>67</v>
       </c>
       <c r="G221">
-        <v>0.6091</v>
+        <v>0.611</v>
       </c>
       <c r="H221">
-        <v>0.4222</v>
+        <v>0.4442</v>
       </c>
       <c r="I221">
-        <v>0.5155999999999999</v>
+        <v>0.5276</v>
       </c>
       <c r="J221">
-        <v>0.3909</v>
+        <v>0.389</v>
       </c>
       <c r="K221">
-        <v>0.5778</v>
+        <v>0.5558</v>
       </c>
       <c r="L221">
-        <v>0.4844</v>
+        <v>0.4724</v>
       </c>
       <c r="M221">
         <v>179</v>
@@ -10519,22 +10519,22 @@
         <v>73</v>
       </c>
       <c r="G226">
-        <v>0.6057</v>
+        <v>0.6037</v>
       </c>
       <c r="H226">
-        <v>0.4237</v>
+        <v>0.4141</v>
       </c>
       <c r="I226">
-        <v>0.5147</v>
+        <v>0.5089</v>
       </c>
       <c r="J226">
-        <v>0.3943</v>
+        <v>0.3963</v>
       </c>
       <c r="K226">
-        <v>0.5763</v>
+        <v>0.5859</v>
       </c>
       <c r="L226">
-        <v>0.4853</v>
+        <v>0.4911</v>
       </c>
       <c r="M226">
         <v>179</v>
@@ -10566,19 +10566,19 @@
         <v>0.5821</v>
       </c>
       <c r="H227">
-        <v>0.4478</v>
+        <v>0.4447</v>
       </c>
       <c r="I227">
-        <v>0.515</v>
+        <v>0.5134</v>
       </c>
       <c r="J227">
         <v>0.4179</v>
       </c>
       <c r="K227">
-        <v>0.5522</v>
+        <v>0.5553</v>
       </c>
       <c r="L227">
-        <v>0.485</v>
+        <v>0.4866</v>
       </c>
       <c r="M227">
         <v>179</v>
@@ -10607,22 +10607,22 @@
         <v>54</v>
       </c>
       <c r="G228">
-        <v>0.6339</v>
+        <v>0.631</v>
       </c>
       <c r="H228">
         <v>0.4799</v>
       </c>
       <c r="I228">
-        <v>0.5569</v>
+        <v>0.5554</v>
       </c>
       <c r="J228">
-        <v>0.3661</v>
+        <v>0.369</v>
       </c>
       <c r="K228">
         <v>0.5201</v>
       </c>
       <c r="L228">
-        <v>0.4431</v>
+        <v>0.4446</v>
       </c>
       <c r="M228">
         <v>179</v>
@@ -10695,22 +10695,22 @@
         <v>56</v>
       </c>
       <c r="G230">
-        <v>0.5098</v>
+        <v>0.5026</v>
       </c>
       <c r="H230">
-        <v>0.4086</v>
+        <v>0.4061</v>
       </c>
       <c r="I230">
-        <v>0.4592</v>
+        <v>0.4544</v>
       </c>
       <c r="J230">
-        <v>0.4902</v>
+        <v>0.4974</v>
       </c>
       <c r="K230">
-        <v>0.5914</v>
+        <v>0.5939</v>
       </c>
       <c r="L230">
-        <v>0.5407999999999999</v>
+        <v>0.5456</v>
       </c>
       <c r="M230">
         <v>179</v>
@@ -10786,19 +10786,19 @@
         <v>0.4105</v>
       </c>
       <c r="H232">
-        <v>0.2716</v>
+        <v>0.2665</v>
       </c>
       <c r="I232">
-        <v>0.341</v>
+        <v>0.3385</v>
       </c>
       <c r="J232">
         <v>0.5895</v>
       </c>
       <c r="K232">
-        <v>0.7284</v>
+        <v>0.7335</v>
       </c>
       <c r="L232">
-        <v>0.659</v>
+        <v>0.6615</v>
       </c>
       <c r="M232">
         <v>179</v>
@@ -10827,22 +10827,22 @@
         <v>59</v>
       </c>
       <c r="G233">
-        <v>0.6419</v>
+        <v>0.645</v>
       </c>
       <c r="H233">
         <v>0.4979</v>
       </c>
       <c r="I233">
-        <v>0.5699</v>
+        <v>0.5714</v>
       </c>
       <c r="J233">
-        <v>0.3581</v>
+        <v>0.355</v>
       </c>
       <c r="K233">
         <v>0.5021</v>
       </c>
       <c r="L233">
-        <v>0.4301</v>
+        <v>0.4286</v>
       </c>
       <c r="M233">
         <v>179</v>
@@ -10918,19 +10918,19 @@
         <v>0.6324</v>
       </c>
       <c r="H235">
-        <v>0.4829</v>
+        <v>0.4773</v>
       </c>
       <c r="I235">
-        <v>0.5576</v>
+        <v>0.5548</v>
       </c>
       <c r="J235">
         <v>0.3676</v>
       </c>
       <c r="K235">
-        <v>0.5171</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="L235">
-        <v>0.4424</v>
+        <v>0.4452</v>
       </c>
       <c r="M235">
         <v>179</v>
@@ -11003,22 +11003,22 @@
         <v>63</v>
       </c>
       <c r="G237">
-        <v>0.6508</v>
+        <v>0.6943</v>
       </c>
       <c r="H237">
-        <v>0.459</v>
+        <v>0.4685</v>
       </c>
       <c r="I237">
-        <v>0.5548999999999999</v>
+        <v>0.5814</v>
       </c>
       <c r="J237">
-        <v>0.3492</v>
+        <v>0.3057</v>
       </c>
       <c r="K237">
-        <v>0.541</v>
+        <v>0.5315</v>
       </c>
       <c r="L237">
-        <v>0.4451</v>
+        <v>0.4186</v>
       </c>
       <c r="M237">
         <v>179</v>
@@ -11091,22 +11091,22 @@
         <v>65</v>
       </c>
       <c r="G239">
-        <v>0.4534</v>
+        <v>0.4515</v>
       </c>
       <c r="H239">
-        <v>0.3044</v>
+        <v>0.2998</v>
       </c>
       <c r="I239">
-        <v>0.3789</v>
+        <v>0.3757</v>
       </c>
       <c r="J239">
-        <v>0.5466</v>
+        <v>0.5485</v>
       </c>
       <c r="K239">
-        <v>0.6956</v>
+        <v>0.7002</v>
       </c>
       <c r="L239">
-        <v>0.6211</v>
+        <v>0.6243</v>
       </c>
       <c r="M239">
         <v>179</v>
@@ -11138,19 +11138,19 @@
         <v>0.5315</v>
       </c>
       <c r="H240">
-        <v>0.3549</v>
+        <v>0.3482</v>
       </c>
       <c r="I240">
-        <v>0.4432</v>
+        <v>0.4398</v>
       </c>
       <c r="J240">
         <v>0.4685</v>
       </c>
       <c r="K240">
-        <v>0.6451</v>
+        <v>0.6518</v>
       </c>
       <c r="L240">
-        <v>0.5568</v>
+        <v>0.5602</v>
       </c>
       <c r="M240">
         <v>179</v>
@@ -11179,22 +11179,22 @@
         <v>67</v>
       </c>
       <c r="G241">
-        <v>0.5195</v>
+        <v>0.5314</v>
       </c>
       <c r="H241">
-        <v>0.419</v>
+        <v>0.4257</v>
       </c>
       <c r="I241">
-        <v>0.4692</v>
+        <v>0.4786</v>
       </c>
       <c r="J241">
-        <v>0.4805</v>
+        <v>0.4686</v>
       </c>
       <c r="K241">
-        <v>0.581</v>
+        <v>0.5743</v>
       </c>
       <c r="L241">
-        <v>0.5308</v>
+        <v>0.5214</v>
       </c>
       <c r="M241">
         <v>179</v>
@@ -11223,22 +11223,22 @@
         <v>68</v>
       </c>
       <c r="G242">
-        <v>0.8421999999999999</v>
+        <v>0.8414</v>
       </c>
       <c r="H242">
         <v>0.6971000000000001</v>
       </c>
       <c r="I242">
-        <v>0.7696</v>
+        <v>0.7692</v>
       </c>
       <c r="J242">
-        <v>0.1578</v>
+        <v>0.1586</v>
       </c>
       <c r="K242">
         <v>0.3029</v>
       </c>
       <c r="L242">
-        <v>0.2304</v>
+        <v>0.2308</v>
       </c>
       <c r="M242">
         <v>179</v>
@@ -11399,22 +11399,22 @@
         <v>73</v>
       </c>
       <c r="G246">
-        <v>0.5262</v>
+        <v>0.522</v>
       </c>
       <c r="H246">
-        <v>0.4165</v>
+        <v>0.4117</v>
       </c>
       <c r="I246">
-        <v>0.4714</v>
+        <v>0.4668</v>
       </c>
       <c r="J246">
-        <v>0.4738</v>
+        <v>0.478</v>
       </c>
       <c r="K246">
-        <v>0.5835</v>
+        <v>0.5883</v>
       </c>
       <c r="L246">
-        <v>0.5286</v>
+        <v>0.5332</v>
       </c>
       <c r="M246">
         <v>179</v>
@@ -11487,22 +11487,22 @@
         <v>55</v>
       </c>
       <c r="G248">
-        <v>0.8207</v>
+        <v>0.8228</v>
       </c>
       <c r="H248">
-        <v>0.6725</v>
+        <v>0.6754</v>
       </c>
       <c r="I248">
-        <v>0.7466</v>
+        <v>0.7491</v>
       </c>
       <c r="J248">
-        <v>0.1793</v>
+        <v>0.1772</v>
       </c>
       <c r="K248">
-        <v>0.3275</v>
+        <v>0.3246</v>
       </c>
       <c r="L248">
-        <v>0.2534</v>
+        <v>0.2509</v>
       </c>
       <c r="M248">
         <v>179</v>
@@ -11663,22 +11663,22 @@
         <v>59</v>
       </c>
       <c r="G252">
-        <v>0.5855</v>
+        <v>0.5828</v>
       </c>
       <c r="H252">
-        <v>0.48</v>
+        <v>0.4895</v>
       </c>
       <c r="I252">
-        <v>0.5328000000000001</v>
+        <v>0.5362</v>
       </c>
       <c r="J252">
-        <v>0.4145</v>
+        <v>0.4172</v>
       </c>
       <c r="K252">
-        <v>0.52</v>
+        <v>0.5105</v>
       </c>
       <c r="L252">
-        <v>0.4672</v>
+        <v>0.4638</v>
       </c>
       <c r="M252">
         <v>179</v>
@@ -11839,22 +11839,22 @@
         <v>63</v>
       </c>
       <c r="G256">
-        <v>0.6136</v>
+        <v>0.6277</v>
       </c>
       <c r="H256">
-        <v>0.4534</v>
+        <v>0.4788</v>
       </c>
       <c r="I256">
-        <v>0.5335</v>
+        <v>0.5532</v>
       </c>
       <c r="J256">
-        <v>0.3864</v>
+        <v>0.3723</v>
       </c>
       <c r="K256">
-        <v>0.5466</v>
+        <v>0.5212</v>
       </c>
       <c r="L256">
-        <v>0.4665</v>
+        <v>0.4468</v>
       </c>
       <c r="M256">
         <v>179</v>
@@ -11930,19 +11930,19 @@
         <v>0.4122</v>
       </c>
       <c r="H258">
-        <v>0.2839</v>
+        <v>0.2831</v>
       </c>
       <c r="I258">
-        <v>0.348</v>
+        <v>0.3476</v>
       </c>
       <c r="J258">
         <v>0.5878</v>
       </c>
       <c r="K258">
-        <v>0.7161</v>
+        <v>0.7169</v>
       </c>
       <c r="L258">
-        <v>0.652</v>
+        <v>0.6524</v>
       </c>
       <c r="M258">
         <v>179</v>
@@ -12018,19 +12018,19 @@
         <v>0.5318000000000001</v>
       </c>
       <c r="H260">
-        <v>0.3659</v>
+        <v>0.3943</v>
       </c>
       <c r="I260">
-        <v>0.4488</v>
+        <v>0.463</v>
       </c>
       <c r="J260">
         <v>0.4682</v>
       </c>
       <c r="K260">
-        <v>0.6341</v>
+        <v>0.6057</v>
       </c>
       <c r="L260">
-        <v>0.5512</v>
+        <v>0.537</v>
       </c>
       <c r="M260">
         <v>179</v>
@@ -12106,19 +12106,19 @@
         <v>0.8276</v>
       </c>
       <c r="H262">
-        <v>0.6839</v>
+        <v>0.6834</v>
       </c>
       <c r="I262">
-        <v>0.7557</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="J262">
         <v>0.1724</v>
       </c>
       <c r="K262">
-        <v>0.3161</v>
+        <v>0.3166</v>
       </c>
       <c r="L262">
-        <v>0.2443</v>
+        <v>0.2445</v>
       </c>
       <c r="M262">
         <v>179</v>
@@ -12238,19 +12238,19 @@
         <v>0.5231</v>
       </c>
       <c r="H265">
-        <v>0.371</v>
+        <v>0.3596</v>
       </c>
       <c r="I265">
-        <v>0.447</v>
+        <v>0.4414</v>
       </c>
       <c r="J265">
         <v>0.4769</v>
       </c>
       <c r="K265">
-        <v>0.629</v>
+        <v>0.6404</v>
       </c>
       <c r="L265">
-        <v>0.553</v>
+        <v>0.5586</v>
       </c>
       <c r="M265">
         <v>179</v>
@@ -12455,22 +12455,22 @@
         <v>59</v>
       </c>
       <c r="G270">
-        <v>0.5721000000000001</v>
+        <v>0.5747</v>
       </c>
       <c r="H270">
-        <v>0.4307</v>
+        <v>0.4414</v>
       </c>
       <c r="I270">
-        <v>0.5014</v>
+        <v>0.508</v>
       </c>
       <c r="J270">
-        <v>0.4279</v>
+        <v>0.4253</v>
       </c>
       <c r="K270">
-        <v>0.5693</v>
+        <v>0.5586</v>
       </c>
       <c r="L270">
-        <v>0.4986</v>
+        <v>0.492</v>
       </c>
       <c r="M270">
         <v>179</v>
@@ -12590,19 +12590,19 @@
         <v>0.5647</v>
       </c>
       <c r="H273">
-        <v>0.3876</v>
+        <v>0.3915</v>
       </c>
       <c r="I273">
-        <v>0.4762</v>
+        <v>0.4781</v>
       </c>
       <c r="J273">
         <v>0.4353</v>
       </c>
       <c r="K273">
-        <v>0.6124000000000001</v>
+        <v>0.6085</v>
       </c>
       <c r="L273">
-        <v>0.5238</v>
+        <v>0.5219</v>
       </c>
       <c r="M273">
         <v>179</v>
@@ -12631,22 +12631,22 @@
         <v>63</v>
       </c>
       <c r="G274">
-        <v>0.5845</v>
+        <v>0.6038</v>
       </c>
       <c r="H274">
-        <v>0.4271</v>
+        <v>0.4477</v>
       </c>
       <c r="I274">
-        <v>0.5058</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="J274">
-        <v>0.4155</v>
+        <v>0.3962</v>
       </c>
       <c r="K274">
-        <v>0.5729</v>
+        <v>0.5523</v>
       </c>
       <c r="L274">
-        <v>0.4942</v>
+        <v>0.4743</v>
       </c>
       <c r="M274">
         <v>179</v>
@@ -12807,22 +12807,22 @@
         <v>67</v>
       </c>
       <c r="G278">
-        <v>0.5143</v>
+        <v>0.5195</v>
       </c>
       <c r="H278">
-        <v>0.3437</v>
+        <v>0.3551</v>
       </c>
       <c r="I278">
-        <v>0.429</v>
+        <v>0.4373</v>
       </c>
       <c r="J278">
-        <v>0.4857</v>
+        <v>0.4805</v>
       </c>
       <c r="K278">
-        <v>0.6563</v>
+        <v>0.6449</v>
       </c>
       <c r="L278">
-        <v>0.571</v>
+        <v>0.5627</v>
       </c>
       <c r="M278">
         <v>179</v>
@@ -13203,22 +13203,22 @@
         <v>59</v>
       </c>
       <c r="G287">
-        <v>0.3876</v>
+        <v>0.3907</v>
       </c>
       <c r="H287">
-        <v>0.2152</v>
+        <v>0.2177</v>
       </c>
       <c r="I287">
-        <v>0.3014</v>
+        <v>0.3042</v>
       </c>
       <c r="J287">
-        <v>0.6124000000000001</v>
+        <v>0.6093</v>
       </c>
       <c r="K287">
-        <v>0.7848000000000001</v>
+        <v>0.7823</v>
       </c>
       <c r="L287">
-        <v>0.6986</v>
+        <v>0.6958</v>
       </c>
       <c r="M287">
         <v>179</v>
@@ -13379,22 +13379,22 @@
         <v>63</v>
       </c>
       <c r="G291">
-        <v>0.3652</v>
+        <v>0.3773</v>
       </c>
       <c r="H291">
-        <v>0.2178</v>
+        <v>0.2336</v>
       </c>
       <c r="I291">
-        <v>0.2915</v>
+        <v>0.3054</v>
       </c>
       <c r="J291">
-        <v>0.6348</v>
+        <v>0.6227</v>
       </c>
       <c r="K291">
-        <v>0.7822</v>
+        <v>0.7664</v>
       </c>
       <c r="L291">
-        <v>0.7085</v>
+        <v>0.6946</v>
       </c>
       <c r="M291">
         <v>179</v>
@@ -13555,22 +13555,22 @@
         <v>67</v>
       </c>
       <c r="G295">
-        <v>0.3261</v>
+        <v>0.3303</v>
       </c>
       <c r="H295">
-        <v>0.1634</v>
+        <v>0.1667</v>
       </c>
       <c r="I295">
-        <v>0.2448</v>
+        <v>0.2485</v>
       </c>
       <c r="J295">
-        <v>0.6739000000000001</v>
+        <v>0.6697</v>
       </c>
       <c r="K295">
-        <v>0.8366</v>
+        <v>0.8333</v>
       </c>
       <c r="L295">
-        <v>0.7552</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="M295">
         <v>179</v>
@@ -13866,19 +13866,19 @@
         <v>0.4421</v>
       </c>
       <c r="H302">
-        <v>0.2929</v>
+        <v>0.2914</v>
       </c>
       <c r="I302">
-        <v>0.3675</v>
+        <v>0.3668</v>
       </c>
       <c r="J302">
         <v>0.5579</v>
       </c>
       <c r="K302">
-        <v>0.7071</v>
+        <v>0.7086</v>
       </c>
       <c r="L302">
-        <v>0.6325</v>
+        <v>0.6332</v>
       </c>
       <c r="M302">
         <v>179</v>
@@ -13907,22 +13907,22 @@
         <v>59</v>
       </c>
       <c r="G303">
-        <v>0.6473</v>
+        <v>0.6623</v>
       </c>
       <c r="H303">
-        <v>0.506</v>
+        <v>0.508</v>
       </c>
       <c r="I303">
-        <v>0.5766</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="J303">
-        <v>0.3527</v>
+        <v>0.3377</v>
       </c>
       <c r="K303">
-        <v>0.494</v>
+        <v>0.492</v>
       </c>
       <c r="L303">
-        <v>0.4234</v>
+        <v>0.4148</v>
       </c>
       <c r="M303">
         <v>179</v>
@@ -14083,22 +14083,22 @@
         <v>63</v>
       </c>
       <c r="G307">
-        <v>0.6354</v>
+        <v>0.6797</v>
       </c>
       <c r="H307">
-        <v>0.486</v>
+        <v>0.4898</v>
       </c>
       <c r="I307">
-        <v>0.5607</v>
+        <v>0.5848</v>
       </c>
       <c r="J307">
-        <v>0.3646</v>
+        <v>0.3203</v>
       </c>
       <c r="K307">
-        <v>0.514</v>
+        <v>0.5102</v>
       </c>
       <c r="L307">
-        <v>0.4393</v>
+        <v>0.4152</v>
       </c>
       <c r="M307">
         <v>179</v>
@@ -14259,22 +14259,22 @@
         <v>67</v>
       </c>
       <c r="G311">
-        <v>0.5624</v>
+        <v>0.5715</v>
       </c>
       <c r="H311">
-        <v>0.4249</v>
+        <v>0.4268</v>
       </c>
       <c r="I311">
-        <v>0.4936</v>
+        <v>0.4992</v>
       </c>
       <c r="J311">
-        <v>0.4376</v>
+        <v>0.4285</v>
       </c>
       <c r="K311">
-        <v>0.5750999999999999</v>
+        <v>0.5732</v>
       </c>
       <c r="L311">
-        <v>0.5064</v>
+        <v>0.5008</v>
       </c>
       <c r="M311">
         <v>179</v>
@@ -14347,22 +14347,22 @@
         <v>69</v>
       </c>
       <c r="G313">
-        <v>0.8411999999999999</v>
+        <v>0.8423</v>
       </c>
       <c r="H313">
         <v>0.7027</v>
       </c>
       <c r="I313">
-        <v>0.7719</v>
+        <v>0.7725</v>
       </c>
       <c r="J313">
-        <v>0.1588</v>
+        <v>0.1577</v>
       </c>
       <c r="K313">
         <v>0.2973</v>
       </c>
       <c r="L313">
-        <v>0.2281</v>
+        <v>0.2275</v>
       </c>
       <c r="M313">
         <v>179</v>
@@ -14567,22 +14567,22 @@
         <v>59</v>
       </c>
       <c r="G318">
-        <v>0.276</v>
+        <v>0.2787</v>
       </c>
       <c r="H318">
-        <v>0.1556</v>
+        <v>0.1582</v>
       </c>
       <c r="I318">
-        <v>0.2158</v>
+        <v>0.2184</v>
       </c>
       <c r="J318">
-        <v>0.724</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="K318">
-        <v>0.8444</v>
+        <v>0.8418</v>
       </c>
       <c r="L318">
-        <v>0.7842</v>
+        <v>0.7816</v>
       </c>
       <c r="M318">
         <v>179</v>
@@ -14743,22 +14743,22 @@
         <v>63</v>
       </c>
       <c r="G322">
-        <v>0.2768</v>
+        <v>0.2883</v>
       </c>
       <c r="H322">
-        <v>0.1405</v>
+        <v>0.1435</v>
       </c>
       <c r="I322">
-        <v>0.2086</v>
+        <v>0.2159</v>
       </c>
       <c r="J322">
-        <v>0.7232</v>
+        <v>0.7117</v>
       </c>
       <c r="K322">
-        <v>0.8595</v>
+        <v>0.8565</v>
       </c>
       <c r="L322">
-        <v>0.7914</v>
+        <v>0.7841</v>
       </c>
       <c r="M322">
         <v>179</v>
@@ -14919,22 +14919,22 @@
         <v>67</v>
       </c>
       <c r="G326">
-        <v>0.2252</v>
+        <v>0.2349</v>
       </c>
       <c r="H326">
-        <v>0.1323</v>
+        <v>0.1346</v>
       </c>
       <c r="I326">
-        <v>0.1788</v>
+        <v>0.1848</v>
       </c>
       <c r="J326">
-        <v>0.7748</v>
+        <v>0.7651</v>
       </c>
       <c r="K326">
-        <v>0.8677</v>
+        <v>0.8653999999999999</v>
       </c>
       <c r="L326">
-        <v>0.8212</v>
+        <v>0.8152</v>
       </c>
       <c r="M326">
         <v>179</v>
@@ -15142,19 +15142,19 @@
         <v>0.2183</v>
       </c>
       <c r="H331">
-        <v>0.1285</v>
+        <v>0.1263</v>
       </c>
       <c r="I331">
-        <v>0.1734</v>
+        <v>0.1723</v>
       </c>
       <c r="J331">
         <v>0.7817</v>
       </c>
       <c r="K331">
-        <v>0.8715000000000001</v>
+        <v>0.8737</v>
       </c>
       <c r="L331">
-        <v>0.8266</v>
+        <v>0.8277</v>
       </c>
       <c r="M331">
         <v>179</v>
@@ -15183,22 +15183,22 @@
         <v>59</v>
       </c>
       <c r="G332">
-        <v>0.7783</v>
+        <v>0.7808</v>
       </c>
       <c r="H332">
-        <v>0.6195000000000001</v>
+        <v>0.6238</v>
       </c>
       <c r="I332">
-        <v>0.6989</v>
+        <v>0.7023</v>
       </c>
       <c r="J332">
-        <v>0.2217</v>
+        <v>0.2192</v>
       </c>
       <c r="K332">
-        <v>0.3805</v>
+        <v>0.3762</v>
       </c>
       <c r="L332">
-        <v>0.3011</v>
+        <v>0.2977</v>
       </c>
       <c r="M332">
         <v>179</v>
@@ -15359,22 +15359,22 @@
         <v>63</v>
       </c>
       <c r="G336">
-        <v>0.7768</v>
+        <v>0.7906</v>
       </c>
       <c r="H336">
-        <v>0.6126</v>
+        <v>0.6286</v>
       </c>
       <c r="I336">
-        <v>0.6947</v>
+        <v>0.7096</v>
       </c>
       <c r="J336">
-        <v>0.2232</v>
+        <v>0.2094</v>
       </c>
       <c r="K336">
-        <v>0.3874</v>
+        <v>0.3714</v>
       </c>
       <c r="L336">
-        <v>0.3053</v>
+        <v>0.2904</v>
       </c>
       <c r="M336">
         <v>179</v>
@@ -15535,22 +15535,22 @@
         <v>67</v>
       </c>
       <c r="G340">
-        <v>0.7058</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="H340">
-        <v>0.5423</v>
+        <v>0.5668</v>
       </c>
       <c r="I340">
-        <v>0.624</v>
+        <v>0.6425</v>
       </c>
       <c r="J340">
-        <v>0.2942</v>
+        <v>0.2818</v>
       </c>
       <c r="K340">
-        <v>0.4577</v>
+        <v>0.4332</v>
       </c>
       <c r="L340">
-        <v>0.376</v>
+        <v>0.3575</v>
       </c>
       <c r="M340">
         <v>179</v>
@@ -15579,22 +15579,22 @@
         <v>68</v>
       </c>
       <c r="G341">
-        <v>0.8898</v>
+        <v>0.8928</v>
       </c>
       <c r="H341">
         <v>0.7762</v>
       </c>
       <c r="I341">
-        <v>0.833</v>
+        <v>0.8345</v>
       </c>
       <c r="J341">
-        <v>0.1102</v>
+        <v>0.1072</v>
       </c>
       <c r="K341">
         <v>0.2238</v>
       </c>
       <c r="L341">
-        <v>0.167</v>
+        <v>0.1655</v>
       </c>
       <c r="M341">
         <v>179</v>
@@ -15755,22 +15755,22 @@
         <v>73</v>
       </c>
       <c r="G345">
-        <v>0.6871</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H345">
-        <v>0.531</v>
+        <v>0.5304</v>
       </c>
       <c r="I345">
-        <v>0.6091</v>
+        <v>0.6072</v>
       </c>
       <c r="J345">
-        <v>0.3129</v>
+        <v>0.316</v>
       </c>
       <c r="K345">
-        <v>0.469</v>
+        <v>0.4696</v>
       </c>
       <c r="L345">
-        <v>0.3909</v>
+        <v>0.3928</v>
       </c>
       <c r="M345">
         <v>179</v>
@@ -15799,22 +15799,22 @@
         <v>60</v>
       </c>
       <c r="G346">
-        <v>0.7704</v>
+        <v>0.7678</v>
       </c>
       <c r="H346">
-        <v>0.6178</v>
+        <v>0.6151</v>
       </c>
       <c r="I346">
-        <v>0.6941000000000001</v>
+        <v>0.6914</v>
       </c>
       <c r="J346">
-        <v>0.2296</v>
+        <v>0.2322</v>
       </c>
       <c r="K346">
-        <v>0.3822</v>
+        <v>0.3849</v>
       </c>
       <c r="L346">
-        <v>0.3059</v>
+        <v>0.3086</v>
       </c>
       <c r="M346">
         <v>179</v>
@@ -15843,22 +15843,22 @@
         <v>61</v>
       </c>
       <c r="G347">
-        <v>0.5612</v>
+        <v>0.5589</v>
       </c>
       <c r="H347">
-        <v>0.4526</v>
+        <v>0.4458</v>
       </c>
       <c r="I347">
-        <v>0.5069</v>
+        <v>0.5024</v>
       </c>
       <c r="J347">
-        <v>0.4388</v>
+        <v>0.4411</v>
       </c>
       <c r="K347">
-        <v>0.5474</v>
+        <v>0.5542</v>
       </c>
       <c r="L347">
-        <v>0.4931</v>
+        <v>0.4976</v>
       </c>
       <c r="M347">
         <v>179</v>
@@ -15887,22 +15887,22 @@
         <v>62</v>
       </c>
       <c r="G348">
-        <v>0.5373</v>
+        <v>0.5329</v>
       </c>
       <c r="H348">
-        <v>0.4401</v>
+        <v>0.4375</v>
       </c>
       <c r="I348">
-        <v>0.4887</v>
+        <v>0.4852</v>
       </c>
       <c r="J348">
-        <v>0.4627</v>
+        <v>0.4671</v>
       </c>
       <c r="K348">
-        <v>0.5599</v>
+        <v>0.5625</v>
       </c>
       <c r="L348">
-        <v>0.5113</v>
+        <v>0.5148</v>
       </c>
       <c r="M348">
         <v>179</v>
@@ -15931,22 +15931,22 @@
         <v>63</v>
       </c>
       <c r="G349">
-        <v>0.552</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="H349">
-        <v>0.4399</v>
+        <v>0.4606</v>
       </c>
       <c r="I349">
-        <v>0.496</v>
+        <v>0.5158</v>
       </c>
       <c r="J349">
-        <v>0.448</v>
+        <v>0.4289</v>
       </c>
       <c r="K349">
-        <v>0.5601</v>
+        <v>0.5394</v>
       </c>
       <c r="L349">
-        <v>0.504</v>
+        <v>0.4842</v>
       </c>
       <c r="M349">
         <v>179</v>
@@ -15975,22 +15975,22 @@
         <v>64</v>
       </c>
       <c r="G350">
-        <v>0.8329</v>
+        <v>0.8262</v>
       </c>
       <c r="H350">
         <v>0.6833</v>
       </c>
       <c r="I350">
-        <v>0.7581</v>
+        <v>0.7548</v>
       </c>
       <c r="J350">
-        <v>0.1671</v>
+        <v>0.1738</v>
       </c>
       <c r="K350">
         <v>0.3167</v>
       </c>
       <c r="L350">
-        <v>0.2419</v>
+        <v>0.2452</v>
       </c>
       <c r="M350">
         <v>179</v>
@@ -16019,22 +16019,22 @@
         <v>65</v>
       </c>
       <c r="G351">
-        <v>0.3788</v>
+        <v>0.3749</v>
       </c>
       <c r="H351">
-        <v>0.2604</v>
+        <v>0.254</v>
       </c>
       <c r="I351">
-        <v>0.3196</v>
+        <v>0.3144</v>
       </c>
       <c r="J351">
-        <v>0.6212</v>
+        <v>0.6251</v>
       </c>
       <c r="K351">
-        <v>0.7396</v>
+        <v>0.746</v>
       </c>
       <c r="L351">
-        <v>0.6804</v>
+        <v>0.6856</v>
       </c>
       <c r="M351">
         <v>179</v>
@@ -16066,19 +16066,19 @@
         <v>0.4722</v>
       </c>
       <c r="H352">
-        <v>0.3011</v>
+        <v>0.3</v>
       </c>
       <c r="I352">
-        <v>0.3866</v>
+        <v>0.3861</v>
       </c>
       <c r="J352">
         <v>0.5278</v>
       </c>
       <c r="K352">
-        <v>0.6989</v>
+        <v>0.7</v>
       </c>
       <c r="L352">
-        <v>0.6133999999999999</v>
+        <v>0.6139</v>
       </c>
       <c r="M352">
         <v>179</v>
@@ -16110,19 +16110,19 @@
         <v>0.5004</v>
       </c>
       <c r="H353">
-        <v>0.3544</v>
+        <v>0.3582</v>
       </c>
       <c r="I353">
-        <v>0.4274</v>
+        <v>0.4293</v>
       </c>
       <c r="J353">
         <v>0.4996</v>
       </c>
       <c r="K353">
-        <v>0.6456</v>
+        <v>0.6418</v>
       </c>
       <c r="L353">
-        <v>0.5726</v>
+        <v>0.5707</v>
       </c>
       <c r="M353">
         <v>179</v>
@@ -16151,22 +16151,22 @@
         <v>68</v>
       </c>
       <c r="G354">
-        <v>0.7939000000000001</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="H354">
-        <v>0.6635</v>
+        <v>0.6583</v>
       </c>
       <c r="I354">
-        <v>0.7287</v>
+        <v>0.7221</v>
       </c>
       <c r="J354">
-        <v>0.2061</v>
+        <v>0.2142</v>
       </c>
       <c r="K354">
-        <v>0.3365</v>
+        <v>0.3417</v>
       </c>
       <c r="L354">
-        <v>0.2713</v>
+        <v>0.2779</v>
       </c>
       <c r="M354">
         <v>179</v>
@@ -16198,19 +16198,19 @@
         <v>0.8164</v>
       </c>
       <c r="H355">
-        <v>0.6504</v>
+        <v>0.6394</v>
       </c>
       <c r="I355">
-        <v>0.7334000000000001</v>
+        <v>0.7279</v>
       </c>
       <c r="J355">
         <v>0.1836</v>
       </c>
       <c r="K355">
-        <v>0.3496</v>
+        <v>0.3606</v>
       </c>
       <c r="L355">
-        <v>0.2666</v>
+        <v>0.2721</v>
       </c>
       <c r="M355">
         <v>179</v>
@@ -16242,19 +16242,19 @@
         <v>0.8247</v>
       </c>
       <c r="H356">
-        <v>0.7118</v>
+        <v>0.7055</v>
       </c>
       <c r="I356">
-        <v>0.7682</v>
+        <v>0.7651</v>
       </c>
       <c r="J356">
         <v>0.1753</v>
       </c>
       <c r="K356">
-        <v>0.2882</v>
+        <v>0.2945</v>
       </c>
       <c r="L356">
-        <v>0.2318</v>
+        <v>0.2349</v>
       </c>
       <c r="M356">
         <v>179</v>
@@ -16283,22 +16283,22 @@
         <v>71</v>
       </c>
       <c r="G357">
-        <v>0.3865</v>
+        <v>0.3861</v>
       </c>
       <c r="H357">
-        <v>0.2498</v>
+        <v>0.2374</v>
       </c>
       <c r="I357">
-        <v>0.3182</v>
+        <v>0.3117</v>
       </c>
       <c r="J357">
-        <v>0.6135</v>
+        <v>0.6139</v>
       </c>
       <c r="K357">
-        <v>0.7502</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="L357">
-        <v>0.6818</v>
+        <v>0.6883</v>
       </c>
       <c r="M357">
         <v>179</v>
@@ -16327,22 +16327,22 @@
         <v>73</v>
       </c>
       <c r="G358">
-        <v>0.4904</v>
+        <v>0.4848</v>
       </c>
       <c r="H358">
-        <v>0.3147</v>
+        <v>0.3109</v>
       </c>
       <c r="I358">
-        <v>0.4025</v>
+        <v>0.3979</v>
       </c>
       <c r="J358">
-        <v>0.5096000000000001</v>
+        <v>0.5152</v>
       </c>
       <c r="K358">
-        <v>0.6853</v>
+        <v>0.6891</v>
       </c>
       <c r="L358">
-        <v>0.5975</v>
+        <v>0.6021</v>
       </c>
       <c r="M358">
         <v>179</v>
@@ -16374,19 +16374,19 @@
         <v>0.381</v>
       </c>
       <c r="H359">
-        <v>0.2201</v>
+        <v>0.2194</v>
       </c>
       <c r="I359">
-        <v>0.3006</v>
+        <v>0.3002</v>
       </c>
       <c r="J359">
         <v>0.619</v>
       </c>
       <c r="K359">
-        <v>0.7799</v>
+        <v>0.7806</v>
       </c>
       <c r="L359">
-        <v>0.6994</v>
+        <v>0.6998</v>
       </c>
       <c r="M359">
         <v>179</v>
@@ -16459,22 +16459,22 @@
         <v>63</v>
       </c>
       <c r="G361">
-        <v>0.3581</v>
+        <v>0.3887</v>
       </c>
       <c r="H361">
-        <v>0.2064</v>
+        <v>0.2223</v>
       </c>
       <c r="I361">
-        <v>0.2822</v>
+        <v>0.3055</v>
       </c>
       <c r="J361">
-        <v>0.6419</v>
+        <v>0.6113</v>
       </c>
       <c r="K361">
-        <v>0.7936</v>
+        <v>0.7776999999999999</v>
       </c>
       <c r="L361">
-        <v>0.7178</v>
+        <v>0.6945</v>
       </c>
       <c r="M361">
         <v>179</v>
@@ -16635,22 +16635,22 @@
         <v>67</v>
       </c>
       <c r="G365">
-        <v>0.2997</v>
+        <v>0.3037</v>
       </c>
       <c r="H365">
-        <v>0.1884</v>
+        <v>0.1908</v>
       </c>
       <c r="I365">
-        <v>0.244</v>
+        <v>0.2473</v>
       </c>
       <c r="J365">
-        <v>0.7003</v>
+        <v>0.6963</v>
       </c>
       <c r="K365">
-        <v>0.8116</v>
+        <v>0.8092</v>
       </c>
       <c r="L365">
-        <v>0.756</v>
+        <v>0.7527</v>
       </c>
       <c r="M365">
         <v>179</v>
@@ -16855,22 +16855,22 @@
         <v>73</v>
       </c>
       <c r="G370">
-        <v>0.3172</v>
+        <v>0.3126</v>
       </c>
       <c r="H370">
-        <v>0.1974</v>
+        <v>0.196</v>
       </c>
       <c r="I370">
-        <v>0.2573</v>
+        <v>0.2543</v>
       </c>
       <c r="J370">
-        <v>0.6828</v>
+        <v>0.6874</v>
       </c>
       <c r="K370">
-        <v>0.8026</v>
+        <v>0.804</v>
       </c>
       <c r="L370">
-        <v>0.7427</v>
+        <v>0.7457</v>
       </c>
       <c r="M370">
         <v>179</v>
@@ -16943,22 +16943,22 @@
         <v>63</v>
       </c>
       <c r="G372">
-        <v>0.5374</v>
+        <v>0.5709</v>
       </c>
       <c r="H372">
-        <v>0.4267</v>
+        <v>0.449</v>
       </c>
       <c r="I372">
-        <v>0.482</v>
+        <v>0.51</v>
       </c>
       <c r="J372">
-        <v>0.4626</v>
+        <v>0.4291</v>
       </c>
       <c r="K372">
-        <v>0.5733</v>
+        <v>0.551</v>
       </c>
       <c r="L372">
-        <v>0.518</v>
+        <v>0.49</v>
       </c>
       <c r="M372">
         <v>179</v>
@@ -17119,22 +17119,22 @@
         <v>67</v>
       </c>
       <c r="G376">
-        <v>0.485</v>
+        <v>0.4871</v>
       </c>
       <c r="H376">
-        <v>0.3533</v>
+        <v>0.3732</v>
       </c>
       <c r="I376">
-        <v>0.4192</v>
+        <v>0.4302</v>
       </c>
       <c r="J376">
-        <v>0.515</v>
+        <v>0.5129</v>
       </c>
       <c r="K376">
-        <v>0.6467000000000001</v>
+        <v>0.6268</v>
       </c>
       <c r="L376">
-        <v>0.5808</v>
+        <v>0.5698</v>
       </c>
       <c r="M376">
         <v>179</v>
@@ -17210,19 +17210,19 @@
         <v>0.8232</v>
       </c>
       <c r="H378">
-        <v>0.6338</v>
+        <v>0.6328</v>
       </c>
       <c r="I378">
-        <v>0.7285</v>
+        <v>0.728</v>
       </c>
       <c r="J378">
         <v>0.1768</v>
       </c>
       <c r="K378">
-        <v>0.3662</v>
+        <v>0.3672</v>
       </c>
       <c r="L378">
-        <v>0.2715</v>
+        <v>0.272</v>
       </c>
       <c r="M378">
         <v>179</v>
@@ -17383,22 +17383,22 @@
         <v>63</v>
       </c>
       <c r="G382">
-        <v>0.5698</v>
+        <v>0.5914</v>
       </c>
       <c r="H382">
-        <v>0.4224</v>
+        <v>0.4456</v>
       </c>
       <c r="I382">
-        <v>0.4961</v>
+        <v>0.5185</v>
       </c>
       <c r="J382">
-        <v>0.4302</v>
+        <v>0.4086</v>
       </c>
       <c r="K382">
-        <v>0.5776</v>
+        <v>0.5544</v>
       </c>
       <c r="L382">
-        <v>0.5039</v>
+        <v>0.4815</v>
       </c>
       <c r="M382">
         <v>179</v>
@@ -17515,22 +17515,22 @@
         <v>66</v>
       </c>
       <c r="G385">
-        <v>0.5003</v>
+        <v>0.4975</v>
       </c>
       <c r="H385">
         <v>0.3294</v>
       </c>
       <c r="I385">
-        <v>0.4148</v>
+        <v>0.4134</v>
       </c>
       <c r="J385">
-        <v>0.4997</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="K385">
         <v>0.6706</v>
       </c>
       <c r="L385">
-        <v>0.5852000000000001</v>
+        <v>0.5866</v>
       </c>
       <c r="M385">
         <v>179</v>
@@ -17559,22 +17559,22 @@
         <v>67</v>
       </c>
       <c r="G386">
-        <v>0.5177</v>
+        <v>0.5198</v>
       </c>
       <c r="H386">
-        <v>0.3718</v>
+        <v>0.3872</v>
       </c>
       <c r="I386">
-        <v>0.4448</v>
+        <v>0.4535</v>
       </c>
       <c r="J386">
-        <v>0.4823</v>
+        <v>0.4802</v>
       </c>
       <c r="K386">
-        <v>0.6282</v>
+        <v>0.6128</v>
       </c>
       <c r="L386">
-        <v>0.5552</v>
+        <v>0.5465</v>
       </c>
       <c r="M386">
         <v>179</v>
@@ -17603,22 +17603,22 @@
         <v>68</v>
       </c>
       <c r="G387">
-        <v>0.8175</v>
+        <v>0.8149</v>
       </c>
       <c r="H387">
         <v>0.6685</v>
       </c>
       <c r="I387">
-        <v>0.743</v>
+        <v>0.7417</v>
       </c>
       <c r="J387">
-        <v>0.1825</v>
+        <v>0.1851</v>
       </c>
       <c r="K387">
         <v>0.3315</v>
       </c>
       <c r="L387">
-        <v>0.257</v>
+        <v>0.2583</v>
       </c>
       <c r="M387">
         <v>179</v>
@@ -17647,22 +17647,22 @@
         <v>69</v>
       </c>
       <c r="G388">
-        <v>0.8378</v>
+        <v>0.8373</v>
       </c>
       <c r="H388">
         <v>0.6661</v>
       </c>
       <c r="I388">
-        <v>0.752</v>
+        <v>0.7517</v>
       </c>
       <c r="J388">
-        <v>0.1622</v>
+        <v>0.1627</v>
       </c>
       <c r="K388">
         <v>0.3339</v>
       </c>
       <c r="L388">
-        <v>0.248</v>
+        <v>0.2483</v>
       </c>
       <c r="M388">
         <v>179</v>
@@ -17738,19 +17738,19 @@
         <v>0.3995</v>
       </c>
       <c r="H390">
-        <v>0.2644</v>
+        <v>0.262</v>
       </c>
       <c r="I390">
-        <v>0.332</v>
+        <v>0.3308</v>
       </c>
       <c r="J390">
         <v>0.6005</v>
       </c>
       <c r="K390">
-        <v>0.7356</v>
+        <v>0.738</v>
       </c>
       <c r="L390">
-        <v>0.668</v>
+        <v>0.6692</v>
       </c>
       <c r="M390">
         <v>179</v>
@@ -17823,22 +17823,22 @@
         <v>64</v>
       </c>
       <c r="G392">
-        <v>0.8233</v>
+        <v>0.8138</v>
       </c>
       <c r="H392">
-        <v>0.696</v>
+        <v>0.6754</v>
       </c>
       <c r="I392">
-        <v>0.7596000000000001</v>
+        <v>0.7446</v>
       </c>
       <c r="J392">
-        <v>0.1767</v>
+        <v>0.1862</v>
       </c>
       <c r="K392">
-        <v>0.304</v>
+        <v>0.3246</v>
       </c>
       <c r="L392">
-        <v>0.2404</v>
+        <v>0.2554</v>
       </c>
       <c r="M392">
         <v>179</v>
@@ -17867,22 +17867,22 @@
         <v>65</v>
       </c>
       <c r="G393">
-        <v>0.3709</v>
+        <v>0.3296</v>
       </c>
       <c r="H393">
-        <v>0.3064</v>
+        <v>0.2725</v>
       </c>
       <c r="I393">
-        <v>0.3386</v>
+        <v>0.3011</v>
       </c>
       <c r="J393">
-        <v>0.6291</v>
+        <v>0.6704</v>
       </c>
       <c r="K393">
-        <v>0.6936</v>
+        <v>0.7275</v>
       </c>
       <c r="L393">
-        <v>0.6614</v>
+        <v>0.6989</v>
       </c>
       <c r="M393">
         <v>179</v>
@@ -17911,22 +17911,22 @@
         <v>66</v>
       </c>
       <c r="G394">
-        <v>0.446</v>
+        <v>0.4232</v>
       </c>
       <c r="H394">
-        <v>0.3702</v>
+        <v>0.3544</v>
       </c>
       <c r="I394">
-        <v>0.4081</v>
+        <v>0.3888</v>
       </c>
       <c r="J394">
-        <v>0.554</v>
+        <v>0.5768</v>
       </c>
       <c r="K394">
-        <v>0.6298</v>
+        <v>0.6456</v>
       </c>
       <c r="L394">
-        <v>0.5919</v>
+        <v>0.6112</v>
       </c>
       <c r="M394">
         <v>179</v>
@@ -17955,22 +17955,22 @@
         <v>67</v>
       </c>
       <c r="G395">
-        <v>0.5083</v>
+        <v>0.508</v>
       </c>
       <c r="H395">
-        <v>0.3532</v>
+        <v>0.3392</v>
       </c>
       <c r="I395">
-        <v>0.4308</v>
+        <v>0.4236</v>
       </c>
       <c r="J395">
-        <v>0.4917</v>
+        <v>0.492</v>
       </c>
       <c r="K395">
-        <v>0.6468</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="L395">
-        <v>0.5692</v>
+        <v>0.5764</v>
       </c>
       <c r="M395">
         <v>179</v>
@@ -17999,22 +17999,22 @@
         <v>68</v>
       </c>
       <c r="G396">
-        <v>0.7963</v>
+        <v>0.7869</v>
       </c>
       <c r="H396">
-        <v>0.6891</v>
+        <v>0.6643</v>
       </c>
       <c r="I396">
-        <v>0.7427</v>
+        <v>0.7256</v>
       </c>
       <c r="J396">
-        <v>0.2037</v>
+        <v>0.2131</v>
       </c>
       <c r="K396">
-        <v>0.3109</v>
+        <v>0.3357</v>
       </c>
       <c r="L396">
-        <v>0.2573</v>
+        <v>0.2744</v>
       </c>
       <c r="M396">
         <v>179</v>
@@ -18043,22 +18043,22 @@
         <v>69</v>
       </c>
       <c r="G397">
-        <v>0.7987</v>
+        <v>0.7892</v>
       </c>
       <c r="H397">
-        <v>0.6474</v>
+        <v>0.6254</v>
       </c>
       <c r="I397">
-        <v>0.723</v>
+        <v>0.7073</v>
       </c>
       <c r="J397">
-        <v>0.2013</v>
+        <v>0.2108</v>
       </c>
       <c r="K397">
-        <v>0.3526</v>
+        <v>0.3746</v>
       </c>
       <c r="L397">
-        <v>0.277</v>
+        <v>0.2927</v>
       </c>
       <c r="M397">
         <v>179</v>
@@ -18087,22 +18087,22 @@
         <v>70</v>
       </c>
       <c r="G398">
-        <v>0.8401</v>
+        <v>0.8299</v>
       </c>
       <c r="H398">
-        <v>0.7107</v>
+        <v>0.6977</v>
       </c>
       <c r="I398">
-        <v>0.7754</v>
+        <v>0.7638</v>
       </c>
       <c r="J398">
-        <v>0.1599</v>
+        <v>0.1701</v>
       </c>
       <c r="K398">
-        <v>0.2893</v>
+        <v>0.3023</v>
       </c>
       <c r="L398">
-        <v>0.2246</v>
+        <v>0.2362</v>
       </c>
       <c r="M398">
         <v>179</v>
@@ -18131,22 +18131,22 @@
         <v>71</v>
       </c>
       <c r="G399">
-        <v>0.3917</v>
+        <v>0.3814</v>
       </c>
       <c r="H399">
-        <v>0.2746</v>
+        <v>0.2408</v>
       </c>
       <c r="I399">
-        <v>0.3332</v>
+        <v>0.3111</v>
       </c>
       <c r="J399">
-        <v>0.6083</v>
+        <v>0.6186</v>
       </c>
       <c r="K399">
-        <v>0.7254</v>
+        <v>0.7592</v>
       </c>
       <c r="L399">
-        <v>0.6667999999999999</v>
+        <v>0.6889</v>
       </c>
       <c r="M399">
         <v>179</v>
@@ -18175,22 +18175,22 @@
         <v>73</v>
       </c>
       <c r="G400">
-        <v>0.5203</v>
+        <v>0.4984</v>
       </c>
       <c r="H400">
-        <v>0.307</v>
+        <v>0.2836</v>
       </c>
       <c r="I400">
-        <v>0.4136</v>
+        <v>0.391</v>
       </c>
       <c r="J400">
-        <v>0.4797</v>
+        <v>0.5016</v>
       </c>
       <c r="K400">
-        <v>0.6929999999999999</v>
+        <v>0.7164</v>
       </c>
       <c r="L400">
-        <v>0.5864</v>
+        <v>0.609</v>
       </c>
       <c r="M400">
         <v>179</v>
@@ -18310,19 +18310,19 @@
         <v>0.2675</v>
       </c>
       <c r="H403">
-        <v>0.1303</v>
+        <v>0.1352</v>
       </c>
       <c r="I403">
-        <v>0.1989</v>
+        <v>0.2014</v>
       </c>
       <c r="J403">
         <v>0.7325</v>
       </c>
       <c r="K403">
-        <v>0.8697</v>
+        <v>0.8648</v>
       </c>
       <c r="L403">
-        <v>0.8011</v>
+        <v>0.7986</v>
       </c>
       <c r="M403">
         <v>179</v>
@@ -18530,19 +18530,19 @@
         <v>0.2254</v>
       </c>
       <c r="H408">
-        <v>0.1402</v>
+        <v>0.1388</v>
       </c>
       <c r="I408">
-        <v>0.1828</v>
+        <v>0.1821</v>
       </c>
       <c r="J408">
         <v>0.7746</v>
       </c>
       <c r="K408">
-        <v>0.8598</v>
+        <v>0.8612</v>
       </c>
       <c r="L408">
-        <v>0.8172</v>
+        <v>0.8179</v>
       </c>
       <c r="M408">
         <v>179</v>
@@ -18615,22 +18615,22 @@
         <v>67</v>
       </c>
       <c r="G410">
-        <v>0.6793</v>
+        <v>0.6808</v>
       </c>
       <c r="H410">
-        <v>0.5164</v>
+        <v>0.5415</v>
       </c>
       <c r="I410">
-        <v>0.5978</v>
+        <v>0.6112</v>
       </c>
       <c r="J410">
-        <v>0.3207</v>
+        <v>0.3192</v>
       </c>
       <c r="K410">
-        <v>0.4836</v>
+        <v>0.4585</v>
       </c>
       <c r="L410">
-        <v>0.4022</v>
+        <v>0.3888</v>
       </c>
       <c r="M410">
         <v>179</v>
@@ -18659,22 +18659,22 @@
         <v>68</v>
       </c>
       <c r="G411">
-        <v>0.8529</v>
+        <v>0.8547</v>
       </c>
       <c r="H411">
         <v>0.7349</v>
       </c>
       <c r="I411">
-        <v>0.7939000000000001</v>
+        <v>0.7948</v>
       </c>
       <c r="J411">
-        <v>0.1471</v>
+        <v>0.1453</v>
       </c>
       <c r="K411">
         <v>0.2651</v>
       </c>
       <c r="L411">
-        <v>0.2061</v>
+        <v>0.2052</v>
       </c>
       <c r="M411">
         <v>179</v>
@@ -18838,19 +18838,19 @@
         <v>0.6859</v>
       </c>
       <c r="H415">
-        <v>0.4838</v>
+        <v>0.4796</v>
       </c>
       <c r="I415">
-        <v>0.5848</v>
+        <v>0.5828</v>
       </c>
       <c r="J415">
         <v>0.3141</v>
       </c>
       <c r="K415">
-        <v>0.5162</v>
+        <v>0.5204</v>
       </c>
       <c r="L415">
-        <v>0.4152</v>
+        <v>0.4172</v>
       </c>
       <c r="M415">
         <v>179</v>
@@ -18879,22 +18879,22 @@
         <v>67</v>
       </c>
       <c r="G416">
-        <v>0.6423</v>
+        <v>0.6454</v>
       </c>
       <c r="H416">
-        <v>0.4584</v>
+        <v>0.464</v>
       </c>
       <c r="I416">
-        <v>0.5504</v>
+        <v>0.5547</v>
       </c>
       <c r="J416">
-        <v>0.3577</v>
+        <v>0.3546</v>
       </c>
       <c r="K416">
-        <v>0.5416</v>
+        <v>0.536</v>
       </c>
       <c r="L416">
-        <v>0.4496</v>
+        <v>0.4453</v>
       </c>
       <c r="M416">
         <v>179</v>
@@ -19143,22 +19143,22 @@
         <v>68</v>
       </c>
       <c r="G422">
-        <v>0.853</v>
+        <v>0.8492</v>
       </c>
       <c r="H422">
-        <v>0.6915</v>
+        <v>0.6869</v>
       </c>
       <c r="I422">
-        <v>0.7722</v>
+        <v>0.768</v>
       </c>
       <c r="J422">
-        <v>0.147</v>
+        <v>0.1508</v>
       </c>
       <c r="K422">
-        <v>0.3085</v>
+        <v>0.3131</v>
       </c>
       <c r="L422">
-        <v>0.2278</v>
+        <v>0.232</v>
       </c>
       <c r="M422">
         <v>179</v>
@@ -19187,22 +19187,22 @@
         <v>69</v>
       </c>
       <c r="G423">
-        <v>0.8605</v>
+        <v>0.854</v>
       </c>
       <c r="H423">
-        <v>0.7062</v>
+        <v>0.7022</v>
       </c>
       <c r="I423">
-        <v>0.7834</v>
+        <v>0.7781</v>
       </c>
       <c r="J423">
-        <v>0.1395</v>
+        <v>0.146</v>
       </c>
       <c r="K423">
-        <v>0.2938</v>
+        <v>0.2978</v>
       </c>
       <c r="L423">
-        <v>0.2166</v>
+        <v>0.2219</v>
       </c>
       <c r="M423">
         <v>179</v>
@@ -19231,22 +19231,22 @@
         <v>70</v>
       </c>
       <c r="G424">
-        <v>0.8637</v>
+        <v>0.8613</v>
       </c>
       <c r="H424">
-        <v>0.7413</v>
+        <v>0.7388</v>
       </c>
       <c r="I424">
-        <v>0.8025</v>
+        <v>0.8</v>
       </c>
       <c r="J424">
-        <v>0.1363</v>
+        <v>0.1387</v>
       </c>
       <c r="K424">
-        <v>0.2587</v>
+        <v>0.2612</v>
       </c>
       <c r="L424">
-        <v>0.1975</v>
+        <v>0.2</v>
       </c>
       <c r="M424">
         <v>179</v>
@@ -19275,22 +19275,22 @@
         <v>71</v>
       </c>
       <c r="G425">
-        <v>0.4478</v>
+        <v>0.441</v>
       </c>
       <c r="H425">
-        <v>0.3556</v>
+        <v>0.3473</v>
       </c>
       <c r="I425">
-        <v>0.4017</v>
+        <v>0.3942</v>
       </c>
       <c r="J425">
-        <v>0.5522</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="K425">
-        <v>0.6444</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="L425">
-        <v>0.5983000000000001</v>
+        <v>0.6058</v>
       </c>
       <c r="M425">
         <v>179</v>
@@ -19319,22 +19319,22 @@
         <v>73</v>
       </c>
       <c r="G426">
-        <v>0.5644</v>
+        <v>0.5464</v>
       </c>
       <c r="H426">
-        <v>0.4298</v>
+        <v>0.4207</v>
       </c>
       <c r="I426">
-        <v>0.4971</v>
+        <v>0.4836</v>
       </c>
       <c r="J426">
-        <v>0.4356</v>
+        <v>0.4536</v>
       </c>
       <c r="K426">
-        <v>0.5702</v>
+        <v>0.5793</v>
       </c>
       <c r="L426">
-        <v>0.5029</v>
+        <v>0.5164</v>
       </c>
       <c r="M426">
         <v>179</v>
@@ -19498,19 +19498,19 @@
         <v>0.2788</v>
       </c>
       <c r="H430">
-        <v>0.1517</v>
+        <v>0.1507</v>
       </c>
       <c r="I430">
-        <v>0.2152</v>
+        <v>0.2148</v>
       </c>
       <c r="J430">
         <v>0.7212</v>
       </c>
       <c r="K430">
-        <v>0.8483000000000001</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="L430">
-        <v>0.7848000000000001</v>
+        <v>0.7852</v>
       </c>
       <c r="M430">
         <v>179</v>
@@ -19627,22 +19627,22 @@
         <v>73</v>
       </c>
       <c r="G433">
-        <v>0.2775</v>
+        <v>0.2736</v>
       </c>
       <c r="H433">
         <v>0.1373</v>
       </c>
       <c r="I433">
-        <v>0.2074</v>
+        <v>0.2054</v>
       </c>
       <c r="J433">
-        <v>0.7225</v>
+        <v>0.7264</v>
       </c>
       <c r="K433">
         <v>0.8627</v>
       </c>
       <c r="L433">
-        <v>0.7926</v>
+        <v>0.7946</v>
       </c>
       <c r="M433">
         <v>179</v>
@@ -19674,19 +19674,19 @@
         <v>0.2526</v>
       </c>
       <c r="H434">
-        <v>0.1328</v>
+        <v>0.1302</v>
       </c>
       <c r="I434">
-        <v>0.1927</v>
+        <v>0.1914</v>
       </c>
       <c r="J434">
         <v>0.7474</v>
       </c>
       <c r="K434">
-        <v>0.8672</v>
+        <v>0.8698</v>
       </c>
       <c r="L434">
-        <v>0.8073</v>
+        <v>0.8086</v>
       </c>
       <c r="M434">
         <v>179</v>
@@ -19715,22 +19715,22 @@
         <v>73</v>
       </c>
       <c r="G435">
-        <v>0.2435</v>
+        <v>0.2411</v>
       </c>
       <c r="H435">
-        <v>0.1407</v>
+        <v>0.1383</v>
       </c>
       <c r="I435">
-        <v>0.1921</v>
+        <v>0.1897</v>
       </c>
       <c r="J435">
-        <v>0.7565</v>
+        <v>0.7589</v>
       </c>
       <c r="K435">
-        <v>0.8593</v>
+        <v>0.8617</v>
       </c>
       <c r="L435">
-        <v>0.8079</v>
+        <v>0.8103</v>
       </c>
       <c r="M435">
         <v>179</v>
@@ -19762,19 +19762,19 @@
         <v>0.6656</v>
       </c>
       <c r="H436">
-        <v>0.5263</v>
+        <v>0.5189</v>
       </c>
       <c r="I436">
-        <v>0.596</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="J436">
         <v>0.3344</v>
       </c>
       <c r="K436">
-        <v>0.4737</v>
+        <v>0.4811</v>
       </c>
       <c r="L436">
-        <v>0.404</v>
+        <v>0.4078</v>
       </c>
       <c r="M436">
         <v>179</v>

--- a/nba/public/data/nba_matchup_probs.xlsx
+++ b/nba/public/data/nba_matchup_probs.xlsx
@@ -238,7 +238,7 @@
     <t>CHA</t>
   </si>
   <si>
-    <t>2026-04-22</t>
+    <t>2026-04-23</t>
   </si>
 </sst>
 </file>
@@ -666,22 +666,22 @@
         <v>0.3741</v>
       </c>
       <c r="H2">
-        <v>0.2323</v>
+        <v>0.2304</v>
       </c>
       <c r="I2">
-        <v>0.3032</v>
+        <v>0.3022</v>
       </c>
       <c r="J2">
         <v>0.6259</v>
       </c>
       <c r="K2">
-        <v>0.7677</v>
+        <v>0.7696</v>
       </c>
       <c r="L2">
-        <v>0.6968</v>
+        <v>0.6978</v>
       </c>
       <c r="M2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N2" t="s">
         <v>74</v>
@@ -725,7 +725,7 @@
         <v>0.6384</v>
       </c>
       <c r="M3">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N3" t="s">
         <v>74</v>
@@ -754,22 +754,22 @@
         <v>0.8280999999999999</v>
       </c>
       <c r="H4">
-        <v>0.6923</v>
+        <v>0.6989</v>
       </c>
       <c r="I4">
-        <v>0.7602</v>
+        <v>0.7635</v>
       </c>
       <c r="J4">
         <v>0.1719</v>
       </c>
       <c r="K4">
-        <v>0.3077</v>
+        <v>0.3011</v>
       </c>
       <c r="L4">
-        <v>0.2398</v>
+        <v>0.2365</v>
       </c>
       <c r="M4">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N4" t="s">
         <v>74</v>
@@ -795,25 +795,25 @@
         <v>47</v>
       </c>
       <c r="G5">
-        <v>0.8263</v>
+        <v>0.8171</v>
       </c>
       <c r="H5">
-        <v>0.6725</v>
+        <v>0.6637</v>
       </c>
       <c r="I5">
-        <v>0.7494</v>
+        <v>0.7403999999999999</v>
       </c>
       <c r="J5">
-        <v>0.1737</v>
+        <v>0.1829</v>
       </c>
       <c r="K5">
-        <v>0.3275</v>
+        <v>0.3363</v>
       </c>
       <c r="L5">
-        <v>0.2506</v>
+        <v>0.2596</v>
       </c>
       <c r="M5">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N5" t="s">
         <v>74</v>
@@ -839,25 +839,25 @@
         <v>48</v>
       </c>
       <c r="G6">
-        <v>0.8277</v>
+        <v>0.8305</v>
       </c>
       <c r="H6">
         <v>0.7048</v>
       </c>
       <c r="I6">
-        <v>0.7662</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="J6">
-        <v>0.1723</v>
+        <v>0.1695</v>
       </c>
       <c r="K6">
         <v>0.2952</v>
       </c>
       <c r="L6">
-        <v>0.2338</v>
+        <v>0.2324</v>
       </c>
       <c r="M6">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N6" t="s">
         <v>74</v>
@@ -886,22 +886,22 @@
         <v>0.4332</v>
       </c>
       <c r="H7">
-        <v>0.2779</v>
+        <v>0.2764</v>
       </c>
       <c r="I7">
-        <v>0.3555</v>
+        <v>0.3548</v>
       </c>
       <c r="J7">
         <v>0.5668</v>
       </c>
       <c r="K7">
-        <v>0.7221</v>
+        <v>0.7236</v>
       </c>
       <c r="L7">
-        <v>0.6445</v>
+        <v>0.6452</v>
       </c>
       <c r="M7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N7" t="s">
         <v>74</v>
@@ -945,7 +945,7 @@
         <v>0.4166</v>
       </c>
       <c r="M8">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N8" t="s">
         <v>74</v>
@@ -989,7 +989,7 @@
         <v>0.5444</v>
       </c>
       <c r="M9">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N9" t="s">
         <v>74</v>
@@ -1033,7 +1033,7 @@
         <v>0.4646</v>
       </c>
       <c r="M10">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N10" t="s">
         <v>74</v>
@@ -1077,7 +1077,7 @@
         <v>0.4746</v>
       </c>
       <c r="M11">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N11" t="s">
         <v>74</v>
@@ -1121,7 +1121,7 @@
         <v>0.4442</v>
       </c>
       <c r="M12">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N12" t="s">
         <v>74</v>
@@ -1165,7 +1165,7 @@
         <v>0.2575</v>
       </c>
       <c r="M13">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N13" t="s">
         <v>74</v>
@@ -1209,7 +1209,7 @@
         <v>0.5237000000000001</v>
       </c>
       <c r="M14">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N14" t="s">
         <v>74</v>
@@ -1253,7 +1253,7 @@
         <v>0.182</v>
       </c>
       <c r="M15">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N15" t="s">
         <v>74</v>
@@ -1297,7 +1297,7 @@
         <v>0.616</v>
       </c>
       <c r="M16">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N16" t="s">
         <v>74</v>
@@ -1323,25 +1323,25 @@
         <v>59</v>
       </c>
       <c r="G17">
-        <v>0.6039</v>
+        <v>0.613</v>
       </c>
       <c r="H17">
-        <v>0.4663</v>
+        <v>0.4673</v>
       </c>
       <c r="I17">
-        <v>0.5351</v>
+        <v>0.5402</v>
       </c>
       <c r="J17">
-        <v>0.3961</v>
+        <v>0.387</v>
       </c>
       <c r="K17">
-        <v>0.5337</v>
+        <v>0.5327</v>
       </c>
       <c r="L17">
-        <v>0.4649</v>
+        <v>0.4598</v>
       </c>
       <c r="M17">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N17" t="s">
         <v>74</v>
@@ -1367,25 +1367,25 @@
         <v>60</v>
       </c>
       <c r="G18">
-        <v>0.8085</v>
+        <v>0.8122</v>
       </c>
       <c r="H18">
         <v>0.695</v>
       </c>
       <c r="I18">
-        <v>0.7517</v>
+        <v>0.7536</v>
       </c>
       <c r="J18">
-        <v>0.1915</v>
+        <v>0.1878</v>
       </c>
       <c r="K18">
         <v>0.305</v>
       </c>
       <c r="L18">
-        <v>0.2483</v>
+        <v>0.2464</v>
       </c>
       <c r="M18">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N18" t="s">
         <v>74</v>
@@ -1429,7 +1429,7 @@
         <v>0.4204</v>
       </c>
       <c r="M19">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N19" t="s">
         <v>74</v>
@@ -1455,25 +1455,25 @@
         <v>62</v>
       </c>
       <c r="G20">
-        <v>0.6377</v>
+        <v>0.658</v>
       </c>
       <c r="H20">
-        <v>0.4819</v>
+        <v>0.4907</v>
       </c>
       <c r="I20">
-        <v>0.5598</v>
+        <v>0.5744</v>
       </c>
       <c r="J20">
-        <v>0.3623</v>
+        <v>0.342</v>
       </c>
       <c r="K20">
-        <v>0.5181</v>
+        <v>0.5093</v>
       </c>
       <c r="L20">
-        <v>0.4402</v>
+        <v>0.4256</v>
       </c>
       <c r="M20">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N20" t="s">
         <v>74</v>
@@ -1517,7 +1517,7 @@
         <v>0.4233</v>
       </c>
       <c r="M21">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N21" t="s">
         <v>74</v>
@@ -1543,25 +1543,25 @@
         <v>64</v>
       </c>
       <c r="G22">
-        <v>0.852</v>
+        <v>0.8535</v>
       </c>
       <c r="H22">
         <v>0.7177</v>
       </c>
       <c r="I22">
-        <v>0.7849</v>
+        <v>0.7856</v>
       </c>
       <c r="J22">
-        <v>0.148</v>
+        <v>0.1465</v>
       </c>
       <c r="K22">
         <v>0.2823</v>
       </c>
       <c r="L22">
-        <v>0.2151</v>
+        <v>0.2144</v>
       </c>
       <c r="M22">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N22" t="s">
         <v>74</v>
@@ -1605,7 +1605,7 @@
         <v>0.6684</v>
       </c>
       <c r="M23">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N23" t="s">
         <v>74</v>
@@ -1631,25 +1631,25 @@
         <v>66</v>
       </c>
       <c r="G24">
-        <v>0.3485</v>
+        <v>0.3506</v>
       </c>
       <c r="H24">
-        <v>0.2239</v>
+        <v>0.2262</v>
       </c>
       <c r="I24">
-        <v>0.2862</v>
+        <v>0.2884</v>
       </c>
       <c r="J24">
-        <v>0.6515</v>
+        <v>0.6494</v>
       </c>
       <c r="K24">
-        <v>0.7761</v>
+        <v>0.7738</v>
       </c>
       <c r="L24">
-        <v>0.7138</v>
+        <v>0.7116</v>
       </c>
       <c r="M24">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N24" t="s">
         <v>74</v>
@@ -1693,7 +1693,7 @@
         <v>0.5011</v>
       </c>
       <c r="M25">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N25" t="s">
         <v>74</v>
@@ -1737,7 +1737,7 @@
         <v>0.2279</v>
       </c>
       <c r="M26">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N26" t="s">
         <v>74</v>
@@ -1766,22 +1766,22 @@
         <v>0.8492</v>
       </c>
       <c r="H27">
-        <v>0.6955</v>
+        <v>0.7005</v>
       </c>
       <c r="I27">
-        <v>0.7724</v>
+        <v>0.7748</v>
       </c>
       <c r="J27">
         <v>0.1508</v>
       </c>
       <c r="K27">
-        <v>0.3045</v>
+        <v>0.2995</v>
       </c>
       <c r="L27">
-        <v>0.2276</v>
+        <v>0.2252</v>
       </c>
       <c r="M27">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N27" t="s">
         <v>74</v>
@@ -1807,25 +1807,25 @@
         <v>70</v>
       </c>
       <c r="G28">
-        <v>0.8585</v>
+        <v>0.8568</v>
       </c>
       <c r="H28">
-        <v>0.7494</v>
+        <v>0.7519</v>
       </c>
       <c r="I28">
-        <v>0.8038999999999999</v>
+        <v>0.8044</v>
       </c>
       <c r="J28">
-        <v>0.1415</v>
+        <v>0.1432</v>
       </c>
       <c r="K28">
-        <v>0.2506</v>
+        <v>0.2481</v>
       </c>
       <c r="L28">
-        <v>0.1961</v>
+        <v>0.1956</v>
       </c>
       <c r="M28">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N28" t="s">
         <v>74</v>
@@ -1851,25 +1851,25 @@
         <v>71</v>
       </c>
       <c r="G29">
-        <v>0.4314</v>
+        <v>0.4371</v>
       </c>
       <c r="H29">
-        <v>0.3021</v>
+        <v>0.3086</v>
       </c>
       <c r="I29">
-        <v>0.3668</v>
+        <v>0.3728</v>
       </c>
       <c r="J29">
-        <v>0.5686</v>
+        <v>0.5629</v>
       </c>
       <c r="K29">
-        <v>0.6979</v>
+        <v>0.6914</v>
       </c>
       <c r="L29">
-        <v>0.6332</v>
+        <v>0.6272</v>
       </c>
       <c r="M29">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N29" t="s">
         <v>74</v>
@@ -1913,7 +1913,7 @@
         <v>0.5145</v>
       </c>
       <c r="M30">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N30" t="s">
         <v>74</v>
@@ -1957,7 +1957,7 @@
         <v>0.4293</v>
       </c>
       <c r="M31">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N31" t="s">
         <v>74</v>
@@ -2001,7 +2001,7 @@
         <v>0.1533</v>
       </c>
       <c r="M32">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N32" t="s">
         <v>74</v>
@@ -2027,25 +2027,25 @@
         <v>47</v>
       </c>
       <c r="G33">
-        <v>0.8887</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="H33">
-        <v>0.779</v>
+        <v>0.768</v>
       </c>
       <c r="I33">
-        <v>0.8338</v>
+        <v>0.8263</v>
       </c>
       <c r="J33">
-        <v>0.1113</v>
+        <v>0.1154</v>
       </c>
       <c r="K33">
-        <v>0.221</v>
+        <v>0.232</v>
       </c>
       <c r="L33">
-        <v>0.1662</v>
+        <v>0.1737</v>
       </c>
       <c r="M33">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N33" t="s">
         <v>74</v>
@@ -2089,7 +2089,7 @@
         <v>0.1568</v>
       </c>
       <c r="M34">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N34" t="s">
         <v>74</v>
@@ -2118,22 +2118,22 @@
         <v>0.6317</v>
       </c>
       <c r="H35">
-        <v>0.5206</v>
+        <v>0.5263</v>
       </c>
       <c r="I35">
-        <v>0.5760999999999999</v>
+        <v>0.579</v>
       </c>
       <c r="J35">
         <v>0.3683</v>
       </c>
       <c r="K35">
-        <v>0.4794</v>
+        <v>0.4737</v>
       </c>
       <c r="L35">
-        <v>0.4239</v>
+        <v>0.421</v>
       </c>
       <c r="M35">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N35" t="s">
         <v>74</v>
@@ -2177,7 +2177,7 @@
         <v>0.2445</v>
       </c>
       <c r="M36">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N36" t="s">
         <v>74</v>
@@ -2203,25 +2203,25 @@
         <v>51</v>
       </c>
       <c r="G37">
-        <v>0.709</v>
+        <v>0.7098</v>
       </c>
       <c r="H37">
         <v>0.5558</v>
       </c>
       <c r="I37">
-        <v>0.6324</v>
+        <v>0.6328</v>
       </c>
       <c r="J37">
-        <v>0.291</v>
+        <v>0.2902</v>
       </c>
       <c r="K37">
         <v>0.4442</v>
       </c>
       <c r="L37">
-        <v>0.3676</v>
+        <v>0.3672</v>
       </c>
       <c r="M37">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N37" t="s">
         <v>74</v>
@@ -2247,25 +2247,25 @@
         <v>52</v>
       </c>
       <c r="G38">
-        <v>0.7849</v>
+        <v>0.787</v>
       </c>
       <c r="H38">
-        <v>0.622</v>
+        <v>0.6217</v>
       </c>
       <c r="I38">
-        <v>0.7034</v>
+        <v>0.7044</v>
       </c>
       <c r="J38">
-        <v>0.2151</v>
+        <v>0.213</v>
       </c>
       <c r="K38">
-        <v>0.378</v>
+        <v>0.3783</v>
       </c>
       <c r="L38">
-        <v>0.2966</v>
+        <v>0.2956</v>
       </c>
       <c r="M38">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N38" t="s">
         <v>74</v>
@@ -2294,22 +2294,22 @@
         <v>0.7557</v>
       </c>
       <c r="H39">
-        <v>0.6176</v>
+        <v>0.6203</v>
       </c>
       <c r="I39">
-        <v>0.6866</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="J39">
         <v>0.2443</v>
       </c>
       <c r="K39">
-        <v>0.3824</v>
+        <v>0.3797</v>
       </c>
       <c r="L39">
-        <v>0.3134</v>
+        <v>0.312</v>
       </c>
       <c r="M39">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N39" t="s">
         <v>74</v>
@@ -2353,7 +2353,7 @@
         <v>0.2685</v>
       </c>
       <c r="M40">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N40" t="s">
         <v>74</v>
@@ -2397,7 +2397,7 @@
         <v>0.1661</v>
       </c>
       <c r="M41">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N41" t="s">
         <v>74</v>
@@ -2441,7 +2441,7 @@
         <v>0.3469</v>
       </c>
       <c r="M42">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N42" t="s">
         <v>74</v>
@@ -2485,7 +2485,7 @@
         <v>0.1502</v>
       </c>
       <c r="M43">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N43" t="s">
         <v>74</v>
@@ -2529,7 +2529,7 @@
         <v>0.4157</v>
       </c>
       <c r="M44">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N44" t="s">
         <v>74</v>
@@ -2555,25 +2555,25 @@
         <v>59</v>
       </c>
       <c r="G45">
-        <v>0.7948</v>
+        <v>0.8016</v>
       </c>
       <c r="H45">
-        <v>0.6504</v>
+        <v>0.6637</v>
       </c>
       <c r="I45">
-        <v>0.7226</v>
+        <v>0.7326</v>
       </c>
       <c r="J45">
-        <v>0.2052</v>
+        <v>0.1984</v>
       </c>
       <c r="K45">
-        <v>0.3496</v>
+        <v>0.3363</v>
       </c>
       <c r="L45">
-        <v>0.2774</v>
+        <v>0.2674</v>
       </c>
       <c r="M45">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N45" t="s">
         <v>74</v>
@@ -2617,7 +2617,7 @@
         <v>0.173</v>
       </c>
       <c r="M46">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N46" t="s">
         <v>74</v>
@@ -2643,25 +2643,25 @@
         <v>61</v>
       </c>
       <c r="G47">
-        <v>0.8149999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="H47">
         <v>0.6737</v>
       </c>
       <c r="I47">
-        <v>0.7444</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="J47">
-        <v>0.185</v>
+        <v>0.187</v>
       </c>
       <c r="K47">
         <v>0.3263</v>
       </c>
       <c r="L47">
-        <v>0.2556</v>
+        <v>0.2566</v>
       </c>
       <c r="M47">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N47" t="s">
         <v>74</v>
@@ -2687,25 +2687,25 @@
         <v>62</v>
       </c>
       <c r="G48">
-        <v>0.8174</v>
+        <v>0.8324</v>
       </c>
       <c r="H48">
-        <v>0.6841</v>
+        <v>0.6849</v>
       </c>
       <c r="I48">
-        <v>0.7508</v>
+        <v>0.7587</v>
       </c>
       <c r="J48">
-        <v>0.1826</v>
+        <v>0.1676</v>
       </c>
       <c r="K48">
-        <v>0.3159</v>
+        <v>0.3151</v>
       </c>
       <c r="L48">
-        <v>0.2492</v>
+        <v>0.2413</v>
       </c>
       <c r="M48">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N48" t="s">
         <v>74</v>
@@ -2731,25 +2731,25 @@
         <v>63</v>
       </c>
       <c r="G49">
-        <v>0.8052</v>
+        <v>0.8067</v>
       </c>
       <c r="H49">
         <v>0.6758</v>
       </c>
       <c r="I49">
-        <v>0.7405</v>
+        <v>0.7412</v>
       </c>
       <c r="J49">
-        <v>0.1948</v>
+        <v>0.1933</v>
       </c>
       <c r="K49">
         <v>0.3242</v>
       </c>
       <c r="L49">
-        <v>0.2595</v>
+        <v>0.2588</v>
       </c>
       <c r="M49">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N49" t="s">
         <v>74</v>
@@ -2793,7 +2793,7 @@
         <v>0.1548</v>
       </c>
       <c r="M50">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N50" t="s">
         <v>74</v>
@@ -2837,7 +2837,7 @@
         <v>0.4853</v>
       </c>
       <c r="M51">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N51" t="s">
         <v>74</v>
@@ -2863,25 +2863,25 @@
         <v>66</v>
       </c>
       <c r="G52">
-        <v>0.4934</v>
+        <v>0.4862</v>
       </c>
       <c r="H52">
-        <v>0.3715</v>
+        <v>0.3728</v>
       </c>
       <c r="I52">
-        <v>0.4324</v>
+        <v>0.4295</v>
       </c>
       <c r="J52">
-        <v>0.5066000000000001</v>
+        <v>0.5138</v>
       </c>
       <c r="K52">
-        <v>0.6284999999999999</v>
+        <v>0.6272</v>
       </c>
       <c r="L52">
-        <v>0.5676</v>
+        <v>0.5705</v>
       </c>
       <c r="M52">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N52" t="s">
         <v>74</v>
@@ -2910,22 +2910,22 @@
         <v>0.7739</v>
       </c>
       <c r="H53">
-        <v>0.6212</v>
+        <v>0.6224</v>
       </c>
       <c r="I53">
-        <v>0.6976</v>
+        <v>0.6982</v>
       </c>
       <c r="J53">
         <v>0.2261</v>
       </c>
       <c r="K53">
-        <v>0.3788</v>
+        <v>0.3776</v>
       </c>
       <c r="L53">
-        <v>0.3024</v>
+        <v>0.3018</v>
       </c>
       <c r="M53">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N53" t="s">
         <v>74</v>
@@ -2951,25 +2951,25 @@
         <v>68</v>
       </c>
       <c r="G54">
-        <v>0.894</v>
+        <v>0.8955</v>
       </c>
       <c r="H54">
         <v>0.7783</v>
       </c>
       <c r="I54">
-        <v>0.8362000000000001</v>
+        <v>0.8369</v>
       </c>
       <c r="J54">
-        <v>0.106</v>
+        <v>0.1045</v>
       </c>
       <c r="K54">
         <v>0.2217</v>
       </c>
       <c r="L54">
-        <v>0.1638</v>
+        <v>0.1631</v>
       </c>
       <c r="M54">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N54" t="s">
         <v>74</v>
@@ -3013,7 +3013,7 @@
         <v>0.1532</v>
       </c>
       <c r="M55">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N55" t="s">
         <v>74</v>
@@ -3057,7 +3057,7 @@
         <v>0.157</v>
       </c>
       <c r="M56">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N56" t="s">
         <v>74</v>
@@ -3083,25 +3083,25 @@
         <v>71</v>
       </c>
       <c r="G57">
-        <v>0.6187</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="H57">
-        <v>0.4341</v>
+        <v>0.4464</v>
       </c>
       <c r="I57">
-        <v>0.5264</v>
+        <v>0.5374</v>
       </c>
       <c r="J57">
-        <v>0.3813</v>
+        <v>0.3715</v>
       </c>
       <c r="K57">
-        <v>0.5659</v>
+        <v>0.5536</v>
       </c>
       <c r="L57">
-        <v>0.4736</v>
+        <v>0.4626</v>
       </c>
       <c r="M57">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N57" t="s">
         <v>74</v>
@@ -3127,25 +3127,25 @@
         <v>73</v>
       </c>
       <c r="G58">
-        <v>0.7421</v>
+        <v>0.7443</v>
       </c>
       <c r="H58">
         <v>0.5774</v>
       </c>
       <c r="I58">
-        <v>0.6598000000000001</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="J58">
-        <v>0.2579</v>
+        <v>0.2557</v>
       </c>
       <c r="K58">
         <v>0.4226</v>
       </c>
       <c r="L58">
-        <v>0.3402</v>
+        <v>0.3392</v>
       </c>
       <c r="M58">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N58" t="s">
         <v>74</v>
@@ -3189,7 +3189,7 @@
         <v>0.1793</v>
       </c>
       <c r="M59">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N59" t="s">
         <v>74</v>
@@ -3215,25 +3215,25 @@
         <v>47</v>
       </c>
       <c r="G60">
-        <v>0.8597</v>
+        <v>0.8547</v>
       </c>
       <c r="H60">
-        <v>0.7661</v>
+        <v>0.7547</v>
       </c>
       <c r="I60">
-        <v>0.8129</v>
+        <v>0.8047</v>
       </c>
       <c r="J60">
-        <v>0.1403</v>
+        <v>0.1453</v>
       </c>
       <c r="K60">
-        <v>0.2339</v>
+        <v>0.2453</v>
       </c>
       <c r="L60">
-        <v>0.1871</v>
+        <v>0.1953</v>
       </c>
       <c r="M60">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N60" t="s">
         <v>74</v>
@@ -3277,7 +3277,7 @@
         <v>0.1763</v>
       </c>
       <c r="M61">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N61" t="s">
         <v>74</v>
@@ -3321,7 +3321,7 @@
         <v>0.504</v>
       </c>
       <c r="M62">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N62" t="s">
         <v>74</v>
@@ -3350,22 +3350,22 @@
         <v>0.7839</v>
       </c>
       <c r="H63">
-        <v>0.62</v>
+        <v>0.6209</v>
       </c>
       <c r="I63">
-        <v>0.702</v>
+        <v>0.7024</v>
       </c>
       <c r="J63">
         <v>0.2161</v>
       </c>
       <c r="K63">
-        <v>0.38</v>
+        <v>0.3791</v>
       </c>
       <c r="L63">
-        <v>0.298</v>
+        <v>0.2976</v>
       </c>
       <c r="M63">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N63" t="s">
         <v>74</v>
@@ -3409,7 +3409,7 @@
         <v>0.4263</v>
       </c>
       <c r="M64">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N64" t="s">
         <v>74</v>
@@ -3438,22 +3438,22 @@
         <v>0.7355</v>
       </c>
       <c r="H65">
-        <v>0.5542</v>
+        <v>0.5564</v>
       </c>
       <c r="I65">
-        <v>0.6448</v>
+        <v>0.646</v>
       </c>
       <c r="J65">
         <v>0.2645</v>
       </c>
       <c r="K65">
-        <v>0.4458</v>
+        <v>0.4436</v>
       </c>
       <c r="L65">
-        <v>0.3552</v>
+        <v>0.354</v>
       </c>
       <c r="M65">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N65" t="s">
         <v>74</v>
@@ -3497,7 +3497,7 @@
         <v>0.3678</v>
       </c>
       <c r="M66">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N66" t="s">
         <v>74</v>
@@ -3523,25 +3523,25 @@
         <v>54</v>
       </c>
       <c r="G67">
-        <v>0.7765</v>
+        <v>0.7785</v>
       </c>
       <c r="H67">
         <v>0.5936</v>
       </c>
       <c r="I67">
-        <v>0.6850000000000001</v>
+        <v>0.6861</v>
       </c>
       <c r="J67">
-        <v>0.2235</v>
+        <v>0.2215</v>
       </c>
       <c r="K67">
         <v>0.4064</v>
       </c>
       <c r="L67">
-        <v>0.315</v>
+        <v>0.3139</v>
       </c>
       <c r="M67">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N67" t="s">
         <v>74</v>
@@ -3585,7 +3585,7 @@
         <v>0.1861</v>
       </c>
       <c r="M68">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N68" t="s">
         <v>74</v>
@@ -3629,7 +3629,7 @@
         <v>0.3864</v>
       </c>
       <c r="M69">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N69" t="s">
         <v>74</v>
@@ -3673,7 +3673,7 @@
         <v>0.1592</v>
       </c>
       <c r="M70">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N70" t="s">
         <v>74</v>
@@ -3717,7 +3717,7 @@
         <v>0.4982</v>
       </c>
       <c r="M71">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N71" t="s">
         <v>74</v>
@@ -3743,25 +3743,25 @@
         <v>59</v>
       </c>
       <c r="G72">
-        <v>0.7581</v>
+        <v>0.7564</v>
       </c>
       <c r="H72">
-        <v>0.5893</v>
+        <v>0.6036</v>
       </c>
       <c r="I72">
-        <v>0.6737</v>
+        <v>0.68</v>
       </c>
       <c r="J72">
-        <v>0.2419</v>
+        <v>0.2436</v>
       </c>
       <c r="K72">
-        <v>0.4107</v>
+        <v>0.3964</v>
       </c>
       <c r="L72">
-        <v>0.3263</v>
+        <v>0.32</v>
       </c>
       <c r="M72">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N72" t="s">
         <v>74</v>
@@ -3805,7 +3805,7 @@
         <v>0.1961</v>
       </c>
       <c r="M73">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N73" t="s">
         <v>74</v>
@@ -3831,25 +3831,25 @@
         <v>61</v>
       </c>
       <c r="G74">
-        <v>0.7658</v>
+        <v>0.7652</v>
       </c>
       <c r="H74">
-        <v>0.6336000000000001</v>
+        <v>0.6403</v>
       </c>
       <c r="I74">
-        <v>0.6997</v>
+        <v>0.7028</v>
       </c>
       <c r="J74">
-        <v>0.2342</v>
+        <v>0.2348</v>
       </c>
       <c r="K74">
-        <v>0.3664</v>
+        <v>0.3597</v>
       </c>
       <c r="L74">
-        <v>0.3003</v>
+        <v>0.2972</v>
       </c>
       <c r="M74">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N74" t="s">
         <v>74</v>
@@ -3875,25 +3875,25 @@
         <v>62</v>
       </c>
       <c r="G75">
-        <v>0.7715</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="H75">
-        <v>0.6</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="I75">
-        <v>0.6858</v>
+        <v>0.6956</v>
       </c>
       <c r="J75">
-        <v>0.2285</v>
+        <v>0.2132</v>
       </c>
       <c r="K75">
-        <v>0.4</v>
+        <v>0.3957</v>
       </c>
       <c r="L75">
-        <v>0.3142</v>
+        <v>0.3044</v>
       </c>
       <c r="M75">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N75" t="s">
         <v>74</v>
@@ -3937,7 +3937,7 @@
         <v>0.2981</v>
       </c>
       <c r="M76">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N76" t="s">
         <v>74</v>
@@ -3981,7 +3981,7 @@
         <v>0.1646</v>
       </c>
       <c r="M77">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N77" t="s">
         <v>74</v>
@@ -4025,7 +4025,7 @@
         <v>0.5506</v>
       </c>
       <c r="M78">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N78" t="s">
         <v>74</v>
@@ -4051,25 +4051,25 @@
         <v>66</v>
       </c>
       <c r="G79">
-        <v>0.4513</v>
+        <v>0.4528</v>
       </c>
       <c r="H79">
-        <v>0.3436</v>
+        <v>0.3462</v>
       </c>
       <c r="I79">
-        <v>0.3974</v>
+        <v>0.3995</v>
       </c>
       <c r="J79">
-        <v>0.5487</v>
+        <v>0.5472</v>
       </c>
       <c r="K79">
-        <v>0.6564</v>
+        <v>0.6538</v>
       </c>
       <c r="L79">
-        <v>0.6026</v>
+        <v>0.6005</v>
       </c>
       <c r="M79">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N79" t="s">
         <v>74</v>
@@ -4098,22 +4098,22 @@
         <v>0.6981000000000001</v>
       </c>
       <c r="H80">
-        <v>0.5513</v>
+        <v>0.5518</v>
       </c>
       <c r="I80">
-        <v>0.6247</v>
+        <v>0.625</v>
       </c>
       <c r="J80">
         <v>0.3019</v>
       </c>
       <c r="K80">
-        <v>0.4487</v>
+        <v>0.4482</v>
       </c>
       <c r="L80">
-        <v>0.3753</v>
+        <v>0.375</v>
       </c>
       <c r="M80">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N80" t="s">
         <v>74</v>
@@ -4157,7 +4157,7 @@
         <v>0.1689</v>
       </c>
       <c r="M81">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N81" t="s">
         <v>74</v>
@@ -4183,25 +4183,25 @@
         <v>69</v>
       </c>
       <c r="G82">
-        <v>0.881</v>
+        <v>0.8824</v>
       </c>
       <c r="H82">
         <v>0.7954</v>
       </c>
       <c r="I82">
-        <v>0.8381999999999999</v>
+        <v>0.8389</v>
       </c>
       <c r="J82">
-        <v>0.119</v>
+        <v>0.1176</v>
       </c>
       <c r="K82">
         <v>0.2046</v>
       </c>
       <c r="L82">
-        <v>0.1618</v>
+        <v>0.1611</v>
       </c>
       <c r="M82">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N82" t="s">
         <v>74</v>
@@ -4230,22 +4230,22 @@
         <v>0.8836000000000001</v>
       </c>
       <c r="H83">
-        <v>0.7907</v>
+        <v>0.7937</v>
       </c>
       <c r="I83">
-        <v>0.8372000000000001</v>
+        <v>0.8386</v>
       </c>
       <c r="J83">
         <v>0.1164</v>
       </c>
       <c r="K83">
-        <v>0.2093</v>
+        <v>0.2063</v>
       </c>
       <c r="L83">
-        <v>0.1628</v>
+        <v>0.1614</v>
       </c>
       <c r="M83">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N83" t="s">
         <v>74</v>
@@ -4271,25 +4271,25 @@
         <v>71</v>
       </c>
       <c r="G84">
-        <v>0.5511</v>
+        <v>0.5608</v>
       </c>
       <c r="H84">
-        <v>0.4167</v>
+        <v>0.4383</v>
       </c>
       <c r="I84">
-        <v>0.4839</v>
+        <v>0.4996</v>
       </c>
       <c r="J84">
-        <v>0.4489</v>
+        <v>0.4392</v>
       </c>
       <c r="K84">
-        <v>0.5833</v>
+        <v>0.5617</v>
       </c>
       <c r="L84">
-        <v>0.5161</v>
+        <v>0.5004</v>
       </c>
       <c r="M84">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N84" t="s">
         <v>74</v>
@@ -4333,7 +4333,7 @@
         <v>0.4002</v>
       </c>
       <c r="M85">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N85" t="s">
         <v>74</v>
@@ -4359,25 +4359,25 @@
         <v>47</v>
       </c>
       <c r="G86">
-        <v>0.5534</v>
+        <v>0.5496</v>
       </c>
       <c r="H86">
-        <v>0.4103</v>
+        <v>0.3751</v>
       </c>
       <c r="I86">
-        <v>0.4818</v>
+        <v>0.4624</v>
       </c>
       <c r="J86">
-        <v>0.4466</v>
+        <v>0.4504</v>
       </c>
       <c r="K86">
-        <v>0.5897</v>
+        <v>0.6249</v>
       </c>
       <c r="L86">
-        <v>0.5182</v>
+        <v>0.5376</v>
       </c>
       <c r="M86">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N86" t="s">
         <v>74</v>
@@ -4421,7 +4421,7 @@
         <v>0.4952</v>
       </c>
       <c r="M87">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N87" t="s">
         <v>74</v>
@@ -4465,7 +4465,7 @@
         <v>0.8215</v>
       </c>
       <c r="M88">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N88" t="s">
         <v>74</v>
@@ -4494,22 +4494,22 @@
         <v>0.3868</v>
       </c>
       <c r="H89">
-        <v>0.2289</v>
+        <v>0.2278</v>
       </c>
       <c r="I89">
-        <v>0.3078</v>
+        <v>0.3073</v>
       </c>
       <c r="J89">
         <v>0.6132</v>
       </c>
       <c r="K89">
-        <v>0.7711</v>
+        <v>0.7722</v>
       </c>
       <c r="L89">
-        <v>0.6922</v>
+        <v>0.6927</v>
       </c>
       <c r="M89">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N89" t="s">
         <v>74</v>
@@ -4553,7 +4553,7 @@
         <v>0.787</v>
       </c>
       <c r="M90">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N90" t="s">
         <v>74</v>
@@ -4597,7 +4597,7 @@
         <v>0.7528</v>
       </c>
       <c r="M91">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N91" t="s">
         <v>74</v>
@@ -4623,25 +4623,25 @@
         <v>53</v>
       </c>
       <c r="G92">
-        <v>0.3289</v>
+        <v>0.3277</v>
       </c>
       <c r="H92">
         <v>0.1783</v>
       </c>
       <c r="I92">
-        <v>0.2536</v>
+        <v>0.253</v>
       </c>
       <c r="J92">
-        <v>0.6711</v>
+        <v>0.6723</v>
       </c>
       <c r="K92">
         <v>0.8217</v>
       </c>
       <c r="L92">
-        <v>0.7464</v>
+        <v>0.747</v>
       </c>
       <c r="M92">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N92" t="s">
         <v>74</v>
@@ -4685,7 +4685,7 @@
         <v>0.7208</v>
       </c>
       <c r="M93">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N93" t="s">
         <v>74</v>
@@ -4729,7 +4729,7 @@
         <v>0.5089</v>
       </c>
       <c r="M94">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N94" t="s">
         <v>74</v>
@@ -4755,25 +4755,25 @@
         <v>56</v>
       </c>
       <c r="G95">
-        <v>0.2978</v>
+        <v>0.295</v>
       </c>
       <c r="H95">
         <v>0.1658</v>
       </c>
       <c r="I95">
-        <v>0.2318</v>
+        <v>0.2304</v>
       </c>
       <c r="J95">
-        <v>0.7022</v>
+        <v>0.705</v>
       </c>
       <c r="K95">
         <v>0.8342000000000001</v>
       </c>
       <c r="L95">
-        <v>0.7682</v>
+        <v>0.7696</v>
       </c>
       <c r="M95">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N95" t="s">
         <v>74</v>
@@ -4817,7 +4817,7 @@
         <v>0.3737</v>
       </c>
       <c r="M96">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N96" t="s">
         <v>74</v>
@@ -4861,7 +4861,7 @@
         <v>0.8246</v>
       </c>
       <c r="M97">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N97" t="s">
         <v>74</v>
@@ -4887,25 +4887,25 @@
         <v>59</v>
       </c>
       <c r="G98">
-        <v>0.3682</v>
+        <v>0.35</v>
       </c>
       <c r="H98">
-        <v>0.2222</v>
+        <v>0.2302</v>
       </c>
       <c r="I98">
-        <v>0.2952</v>
+        <v>0.2901</v>
       </c>
       <c r="J98">
-        <v>0.6318</v>
+        <v>0.65</v>
       </c>
       <c r="K98">
-        <v>0.7778</v>
+        <v>0.7698</v>
       </c>
       <c r="L98">
-        <v>0.7048</v>
+        <v>0.7099</v>
       </c>
       <c r="M98">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N98" t="s">
         <v>74</v>
@@ -4949,7 +4949,7 @@
         <v>0.521</v>
       </c>
       <c r="M99">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N99" t="s">
         <v>74</v>
@@ -4993,7 +4993,7 @@
         <v>0.6879999999999999</v>
       </c>
       <c r="M100">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N100" t="s">
         <v>74</v>
@@ -5019,25 +5019,25 @@
         <v>62</v>
       </c>
       <c r="G101">
-        <v>0.3638</v>
+        <v>0.3675</v>
       </c>
       <c r="H101">
-        <v>0.2105</v>
+        <v>0.2229</v>
       </c>
       <c r="I101">
-        <v>0.2872</v>
+        <v>0.2952</v>
       </c>
       <c r="J101">
-        <v>0.6362</v>
+        <v>0.6325</v>
       </c>
       <c r="K101">
-        <v>0.7895</v>
+        <v>0.7771</v>
       </c>
       <c r="L101">
-        <v>0.7128</v>
+        <v>0.7048</v>
       </c>
       <c r="M101">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N101" t="s">
         <v>74</v>
@@ -5066,22 +5066,22 @@
         <v>0.373</v>
       </c>
       <c r="H102">
-        <v>0.2292</v>
+        <v>0.2286</v>
       </c>
       <c r="I102">
-        <v>0.3011</v>
+        <v>0.3008</v>
       </c>
       <c r="J102">
         <v>0.627</v>
       </c>
       <c r="K102">
-        <v>0.7708</v>
+        <v>0.7714</v>
       </c>
       <c r="L102">
-        <v>0.6989</v>
+        <v>0.6992</v>
       </c>
       <c r="M102">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N102" t="s">
         <v>74</v>
@@ -5125,7 +5125,7 @@
         <v>0.4225</v>
       </c>
       <c r="M103">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N103" t="s">
         <v>74</v>
@@ -5154,22 +5154,22 @@
         <v>0.2374</v>
       </c>
       <c r="H104">
-        <v>0.1287</v>
+        <v>0.1248</v>
       </c>
       <c r="I104">
-        <v>0.183</v>
+        <v>0.1811</v>
       </c>
       <c r="J104">
         <v>0.7625999999999999</v>
       </c>
       <c r="K104">
-        <v>0.8713</v>
+        <v>0.8752</v>
       </c>
       <c r="L104">
-        <v>0.8169999999999999</v>
+        <v>0.8189</v>
       </c>
       <c r="M104">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N104" t="s">
         <v>74</v>
@@ -5195,25 +5195,25 @@
         <v>66</v>
       </c>
       <c r="G105">
-        <v>0.222</v>
+        <v>0.2275</v>
       </c>
       <c r="H105">
         <v>0.1171</v>
       </c>
       <c r="I105">
-        <v>0.1696</v>
+        <v>0.1723</v>
       </c>
       <c r="J105">
-        <v>0.778</v>
+        <v>0.7725</v>
       </c>
       <c r="K105">
         <v>0.8829</v>
       </c>
       <c r="L105">
-        <v>0.8304</v>
+        <v>0.8277</v>
       </c>
       <c r="M105">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N105" t="s">
         <v>74</v>
@@ -5239,25 +5239,25 @@
         <v>67</v>
       </c>
       <c r="G106">
-        <v>0.3244</v>
+        <v>0.326</v>
       </c>
       <c r="H106">
         <v>0.1641</v>
       </c>
       <c r="I106">
-        <v>0.2442</v>
+        <v>0.245</v>
       </c>
       <c r="J106">
-        <v>0.6756</v>
+        <v>0.674</v>
       </c>
       <c r="K106">
         <v>0.8359</v>
       </c>
       <c r="L106">
-        <v>0.7558</v>
+        <v>0.755</v>
       </c>
       <c r="M106">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N106" t="s">
         <v>74</v>
@@ -5301,7 +5301,7 @@
         <v>0.4468</v>
       </c>
       <c r="M107">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N107" t="s">
         <v>74</v>
@@ -5345,7 +5345,7 @@
         <v>0.4633</v>
       </c>
       <c r="M108">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N108" t="s">
         <v>74</v>
@@ -5389,7 +5389,7 @@
         <v>0.3837</v>
       </c>
       <c r="M109">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N109" t="s">
         <v>74</v>
@@ -5415,25 +5415,25 @@
         <v>71</v>
       </c>
       <c r="G110">
-        <v>0.2458</v>
+        <v>0.2492</v>
       </c>
       <c r="H110">
-        <v>0.1344</v>
+        <v>0.1358</v>
       </c>
       <c r="I110">
-        <v>0.1901</v>
+        <v>0.1925</v>
       </c>
       <c r="J110">
-        <v>0.7542</v>
+        <v>0.7508</v>
       </c>
       <c r="K110">
-        <v>0.8656</v>
+        <v>0.8642</v>
       </c>
       <c r="L110">
-        <v>0.8099</v>
+        <v>0.8075</v>
       </c>
       <c r="M110">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N110" t="s">
         <v>74</v>
@@ -5459,25 +5459,25 @@
         <v>73</v>
       </c>
       <c r="G111">
-        <v>0.3008</v>
+        <v>0.2974</v>
       </c>
       <c r="H111">
-        <v>0.1728</v>
+        <v>0.1716</v>
       </c>
       <c r="I111">
-        <v>0.2368</v>
+        <v>0.2345</v>
       </c>
       <c r="J111">
-        <v>0.6992</v>
+        <v>0.7026</v>
       </c>
       <c r="K111">
-        <v>0.8272</v>
+        <v>0.8284</v>
       </c>
       <c r="L111">
-        <v>0.7632</v>
+        <v>0.7655</v>
       </c>
       <c r="M111">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N111" t="s">
         <v>74</v>
@@ -5503,25 +5503,25 @@
         <v>48</v>
       </c>
       <c r="G112">
-        <v>0.5810999999999999</v>
+        <v>0.6071</v>
       </c>
       <c r="H112">
-        <v>0.453</v>
+        <v>0.4594</v>
       </c>
       <c r="I112">
-        <v>0.517</v>
+        <v>0.5332</v>
       </c>
       <c r="J112">
-        <v>0.4189</v>
+        <v>0.3929</v>
       </c>
       <c r="K112">
-        <v>0.547</v>
+        <v>0.5406</v>
       </c>
       <c r="L112">
-        <v>0.483</v>
+        <v>0.4668</v>
       </c>
       <c r="M112">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N112" t="s">
         <v>74</v>
@@ -5547,25 +5547,25 @@
         <v>49</v>
       </c>
       <c r="G113">
-        <v>0.2558</v>
+        <v>0.2651</v>
       </c>
       <c r="H113">
-        <v>0.1326</v>
+        <v>0.1412</v>
       </c>
       <c r="I113">
-        <v>0.1942</v>
+        <v>0.2032</v>
       </c>
       <c r="J113">
-        <v>0.7442</v>
+        <v>0.7349</v>
       </c>
       <c r="K113">
-        <v>0.8673999999999999</v>
+        <v>0.8588</v>
       </c>
       <c r="L113">
-        <v>0.8058</v>
+        <v>0.7968</v>
       </c>
       <c r="M113">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N113" t="s">
         <v>74</v>
@@ -5591,25 +5591,25 @@
         <v>50</v>
       </c>
       <c r="G114">
-        <v>0.3998</v>
+        <v>0.4196</v>
       </c>
       <c r="H114">
-        <v>0.2459</v>
+        <v>0.2606</v>
       </c>
       <c r="I114">
-        <v>0.3228</v>
+        <v>0.3401</v>
       </c>
       <c r="J114">
-        <v>0.6002</v>
+        <v>0.5804</v>
       </c>
       <c r="K114">
-        <v>0.7541</v>
+        <v>0.7393999999999999</v>
       </c>
       <c r="L114">
-        <v>0.6772</v>
+        <v>0.6599</v>
       </c>
       <c r="M114">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N114" t="s">
         <v>74</v>
@@ -5635,25 +5635,25 @@
         <v>51</v>
       </c>
       <c r="G115">
-        <v>0.3015</v>
+        <v>0.3099</v>
       </c>
       <c r="H115">
-        <v>0.1481</v>
+        <v>0.1552</v>
       </c>
       <c r="I115">
-        <v>0.2248</v>
+        <v>0.2326</v>
       </c>
       <c r="J115">
-        <v>0.6985</v>
+        <v>0.6901</v>
       </c>
       <c r="K115">
-        <v>0.8519</v>
+        <v>0.8448</v>
       </c>
       <c r="L115">
-        <v>0.7752</v>
+        <v>0.7674</v>
       </c>
       <c r="M115">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N115" t="s">
         <v>74</v>
@@ -5679,25 +5679,25 @@
         <v>52</v>
       </c>
       <c r="G116">
-        <v>0.3496</v>
+        <v>0.3631</v>
       </c>
       <c r="H116">
-        <v>0.1811</v>
+        <v>0.1933</v>
       </c>
       <c r="I116">
-        <v>0.2654</v>
+        <v>0.2782</v>
       </c>
       <c r="J116">
-        <v>0.6504</v>
+        <v>0.6369</v>
       </c>
       <c r="K116">
-        <v>0.8189</v>
+        <v>0.8067</v>
       </c>
       <c r="L116">
-        <v>0.7346</v>
+        <v>0.7218</v>
       </c>
       <c r="M116">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N116" t="s">
         <v>74</v>
@@ -5723,25 +5723,25 @@
         <v>53</v>
       </c>
       <c r="G117">
-        <v>0.3411</v>
+        <v>0.3613</v>
       </c>
       <c r="H117">
-        <v>0.1904</v>
+        <v>0.205</v>
       </c>
       <c r="I117">
-        <v>0.2658</v>
+        <v>0.2832</v>
       </c>
       <c r="J117">
-        <v>0.6589</v>
+        <v>0.6387</v>
       </c>
       <c r="K117">
-        <v>0.8096</v>
+        <v>0.795</v>
       </c>
       <c r="L117">
-        <v>0.7342</v>
+        <v>0.7168</v>
       </c>
       <c r="M117">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N117" t="s">
         <v>74</v>
@@ -5767,25 +5767,25 @@
         <v>54</v>
       </c>
       <c r="G118">
-        <v>0.3814</v>
+        <v>0.405</v>
       </c>
       <c r="H118">
-        <v>0.2269</v>
+        <v>0.2494</v>
       </c>
       <c r="I118">
-        <v>0.3042</v>
+        <v>0.3272</v>
       </c>
       <c r="J118">
-        <v>0.6186</v>
+        <v>0.595</v>
       </c>
       <c r="K118">
-        <v>0.7731</v>
+        <v>0.7506</v>
       </c>
       <c r="L118">
-        <v>0.6958</v>
+        <v>0.6728</v>
       </c>
       <c r="M118">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N118" t="s">
         <v>74</v>
@@ -5811,25 +5811,25 @@
         <v>55</v>
       </c>
       <c r="G119">
-        <v>0.5802</v>
+        <v>0.5994</v>
       </c>
       <c r="H119">
-        <v>0.4612</v>
+        <v>0.4766</v>
       </c>
       <c r="I119">
-        <v>0.5207000000000001</v>
+        <v>0.538</v>
       </c>
       <c r="J119">
-        <v>0.4198</v>
+        <v>0.4006</v>
       </c>
       <c r="K119">
-        <v>0.5387999999999999</v>
+        <v>0.5234</v>
       </c>
       <c r="L119">
-        <v>0.4793</v>
+        <v>0.462</v>
       </c>
       <c r="M119">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N119" t="s">
         <v>74</v>
@@ -5855,25 +5855,25 @@
         <v>56</v>
       </c>
       <c r="G120">
-        <v>0.3027</v>
+        <v>0.3135</v>
       </c>
       <c r="H120">
-        <v>0.1826</v>
+        <v>0.1912</v>
       </c>
       <c r="I120">
-        <v>0.2427</v>
+        <v>0.2524</v>
       </c>
       <c r="J120">
-        <v>0.6973</v>
+        <v>0.6865</v>
       </c>
       <c r="K120">
-        <v>0.8174</v>
+        <v>0.8088</v>
       </c>
       <c r="L120">
-        <v>0.7573</v>
+        <v>0.7476</v>
       </c>
       <c r="M120">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N120" t="s">
         <v>74</v>
@@ -5899,25 +5899,25 @@
         <v>57</v>
       </c>
       <c r="G121">
-        <v>0.7336</v>
+        <v>0.7433</v>
       </c>
       <c r="H121">
-        <v>0.5415</v>
+        <v>0.5673</v>
       </c>
       <c r="I121">
-        <v>0.6375999999999999</v>
+        <v>0.6553</v>
       </c>
       <c r="J121">
-        <v>0.2664</v>
+        <v>0.2567</v>
       </c>
       <c r="K121">
-        <v>0.4585</v>
+        <v>0.4327</v>
       </c>
       <c r="L121">
-        <v>0.3624</v>
+        <v>0.3447</v>
       </c>
       <c r="M121">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N121" t="s">
         <v>74</v>
@@ -5943,25 +5943,25 @@
         <v>58</v>
       </c>
       <c r="G122">
-        <v>0.245</v>
+        <v>0.2588</v>
       </c>
       <c r="H122">
-        <v>0.1331</v>
+        <v>0.1431</v>
       </c>
       <c r="I122">
-        <v>0.189</v>
+        <v>0.201</v>
       </c>
       <c r="J122">
-        <v>0.755</v>
+        <v>0.7412</v>
       </c>
       <c r="K122">
-        <v>0.8669</v>
+        <v>0.8569</v>
       </c>
       <c r="L122">
-        <v>0.8110000000000001</v>
+        <v>0.799</v>
       </c>
       <c r="M122">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N122" t="s">
         <v>74</v>
@@ -5987,25 +5987,25 @@
         <v>59</v>
       </c>
       <c r="G123">
-        <v>0.3834</v>
+        <v>0.3922</v>
       </c>
       <c r="H123">
-        <v>0.2179</v>
+        <v>0.2488</v>
       </c>
       <c r="I123">
-        <v>0.3007</v>
+        <v>0.3205</v>
       </c>
       <c r="J123">
-        <v>0.6166</v>
+        <v>0.6078</v>
       </c>
       <c r="K123">
-        <v>0.7821</v>
+        <v>0.7512</v>
       </c>
       <c r="L123">
-        <v>0.6993</v>
+        <v>0.6795</v>
       </c>
       <c r="M123">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N123" t="s">
         <v>74</v>
@@ -6031,25 +6031,25 @@
         <v>60</v>
       </c>
       <c r="G124">
-        <v>0.5574</v>
+        <v>0.6052</v>
       </c>
       <c r="H124">
-        <v>0.4389</v>
+        <v>0.4506</v>
       </c>
       <c r="I124">
-        <v>0.4982</v>
+        <v>0.5279</v>
       </c>
       <c r="J124">
-        <v>0.4426</v>
+        <v>0.3948</v>
       </c>
       <c r="K124">
-        <v>0.5611</v>
+        <v>0.5494</v>
       </c>
       <c r="L124">
-        <v>0.5018</v>
+        <v>0.4721</v>
       </c>
       <c r="M124">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N124" t="s">
         <v>74</v>
@@ -6075,25 +6075,25 @@
         <v>61</v>
       </c>
       <c r="G125">
-        <v>0.4097</v>
+        <v>0.4252</v>
       </c>
       <c r="H125">
-        <v>0.2359</v>
+        <v>0.2562</v>
       </c>
       <c r="I125">
-        <v>0.3228</v>
+        <v>0.3407</v>
       </c>
       <c r="J125">
-        <v>0.5903</v>
+        <v>0.5748</v>
       </c>
       <c r="K125">
-        <v>0.7641</v>
+        <v>0.7438</v>
       </c>
       <c r="L125">
-        <v>0.6772</v>
+        <v>0.6593</v>
       </c>
       <c r="M125">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N125" t="s">
         <v>74</v>
@@ -6119,25 +6119,25 @@
         <v>62</v>
       </c>
       <c r="G126">
-        <v>0.3745</v>
+        <v>0.4035</v>
       </c>
       <c r="H126">
-        <v>0.2181</v>
+        <v>0.2517</v>
       </c>
       <c r="I126">
-        <v>0.2963</v>
+        <v>0.3276</v>
       </c>
       <c r="J126">
-        <v>0.6254999999999999</v>
+        <v>0.5965</v>
       </c>
       <c r="K126">
-        <v>0.7819</v>
+        <v>0.7483</v>
       </c>
       <c r="L126">
-        <v>0.7037</v>
+        <v>0.6724</v>
       </c>
       <c r="M126">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N126" t="s">
         <v>74</v>
@@ -6163,25 +6163,25 @@
         <v>63</v>
       </c>
       <c r="G127">
-        <v>0.3826</v>
+        <v>0.3914</v>
       </c>
       <c r="H127">
-        <v>0.2287</v>
+        <v>0.2635</v>
       </c>
       <c r="I127">
-        <v>0.3056</v>
+        <v>0.3274</v>
       </c>
       <c r="J127">
-        <v>0.6173999999999999</v>
+        <v>0.6086</v>
       </c>
       <c r="K127">
-        <v>0.7713</v>
+        <v>0.7365</v>
       </c>
       <c r="L127">
-        <v>0.6944</v>
+        <v>0.6726</v>
       </c>
       <c r="M127">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N127" t="s">
         <v>74</v>
@@ -6207,25 +6207,25 @@
         <v>64</v>
       </c>
       <c r="G128">
-        <v>0.6705</v>
+        <v>0.7058</v>
       </c>
       <c r="H128">
-        <v>0.5258</v>
+        <v>0.5382</v>
       </c>
       <c r="I128">
-        <v>0.5982</v>
+        <v>0.622</v>
       </c>
       <c r="J128">
-        <v>0.3295</v>
+        <v>0.2942</v>
       </c>
       <c r="K128">
-        <v>0.4742</v>
+        <v>0.4618</v>
       </c>
       <c r="L128">
-        <v>0.4018</v>
+        <v>0.378</v>
       </c>
       <c r="M128">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N128" t="s">
         <v>74</v>
@@ -6251,25 +6251,25 @@
         <v>65</v>
       </c>
       <c r="G129">
-        <v>0.2409</v>
+        <v>0.2527</v>
       </c>
       <c r="H129">
-        <v>0.1275</v>
+        <v>0.1352</v>
       </c>
       <c r="I129">
-        <v>0.1842</v>
+        <v>0.1939</v>
       </c>
       <c r="J129">
-        <v>0.7591</v>
+        <v>0.7473</v>
       </c>
       <c r="K129">
-        <v>0.8725000000000001</v>
+        <v>0.8648</v>
       </c>
       <c r="L129">
-        <v>0.8158</v>
+        <v>0.8061</v>
       </c>
       <c r="M129">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N129" t="s">
         <v>74</v>
@@ -6295,25 +6295,25 @@
         <v>66</v>
       </c>
       <c r="G130">
-        <v>0.2387</v>
+        <v>0.2483</v>
       </c>
       <c r="H130">
-        <v>0.1214</v>
+        <v>0.1246</v>
       </c>
       <c r="I130">
-        <v>0.18</v>
+        <v>0.1864</v>
       </c>
       <c r="J130">
-        <v>0.7613</v>
+        <v>0.7517</v>
       </c>
       <c r="K130">
-        <v>0.8786</v>
+        <v>0.8754</v>
       </c>
       <c r="L130">
-        <v>0.82</v>
+        <v>0.8136</v>
       </c>
       <c r="M130">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N130" t="s">
         <v>74</v>
@@ -6339,25 +6339,25 @@
         <v>67</v>
       </c>
       <c r="G131">
-        <v>0.3488</v>
+        <v>0.3748</v>
       </c>
       <c r="H131">
-        <v>0.1679</v>
+        <v>0.1793</v>
       </c>
       <c r="I131">
-        <v>0.2583</v>
+        <v>0.277</v>
       </c>
       <c r="J131">
-        <v>0.6512</v>
+        <v>0.6252</v>
       </c>
       <c r="K131">
-        <v>0.8321</v>
+        <v>0.8207</v>
       </c>
       <c r="L131">
-        <v>0.7417</v>
+        <v>0.723</v>
       </c>
       <c r="M131">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N131" t="s">
         <v>74</v>
@@ -6383,25 +6383,25 @@
         <v>68</v>
       </c>
       <c r="G132">
-        <v>0.6188</v>
+        <v>0.6438</v>
       </c>
       <c r="H132">
-        <v>0.5512</v>
+        <v>0.5601</v>
       </c>
       <c r="I132">
-        <v>0.585</v>
+        <v>0.602</v>
       </c>
       <c r="J132">
-        <v>0.3812</v>
+        <v>0.3562</v>
       </c>
       <c r="K132">
-        <v>0.4488</v>
+        <v>0.4399</v>
       </c>
       <c r="L132">
-        <v>0.415</v>
+        <v>0.398</v>
       </c>
       <c r="M132">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N132" t="s">
         <v>74</v>
@@ -6427,25 +6427,25 @@
         <v>69</v>
       </c>
       <c r="G133">
-        <v>0.5787</v>
+        <v>0.624</v>
       </c>
       <c r="H133">
-        <v>0.4887</v>
+        <v>0.4925</v>
       </c>
       <c r="I133">
-        <v>0.5337</v>
+        <v>0.5582</v>
       </c>
       <c r="J133">
-        <v>0.4213</v>
+        <v>0.376</v>
       </c>
       <c r="K133">
-        <v>0.5113</v>
+        <v>0.5075</v>
       </c>
       <c r="L133">
-        <v>0.4663</v>
+        <v>0.4418</v>
       </c>
       <c r="M133">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N133" t="s">
         <v>74</v>
@@ -6471,25 +6471,25 @@
         <v>70</v>
       </c>
       <c r="G134">
-        <v>0.7083</v>
+        <v>0.7327</v>
       </c>
       <c r="H134">
-        <v>0.5688</v>
+        <v>0.5871</v>
       </c>
       <c r="I134">
-        <v>0.6385</v>
+        <v>0.6599</v>
       </c>
       <c r="J134">
-        <v>0.2917</v>
+        <v>0.2673</v>
       </c>
       <c r="K134">
-        <v>0.4312</v>
+        <v>0.4129</v>
       </c>
       <c r="L134">
-        <v>0.3615</v>
+        <v>0.3401</v>
       </c>
       <c r="M134">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N134" t="s">
         <v>74</v>
@@ -6515,25 +6515,25 @@
         <v>71</v>
       </c>
       <c r="G135">
-        <v>0.2553</v>
+        <v>0.2753</v>
       </c>
       <c r="H135">
-        <v>0.1471</v>
+        <v>0.1593</v>
       </c>
       <c r="I135">
-        <v>0.2012</v>
+        <v>0.2173</v>
       </c>
       <c r="J135">
-        <v>0.7447</v>
+        <v>0.7247</v>
       </c>
       <c r="K135">
-        <v>0.8529</v>
+        <v>0.8407</v>
       </c>
       <c r="L135">
-        <v>0.7988</v>
+        <v>0.7827</v>
       </c>
       <c r="M135">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N135" t="s">
         <v>74</v>
@@ -6559,25 +6559,25 @@
         <v>73</v>
       </c>
       <c r="G136">
-        <v>0.304</v>
+        <v>0.3233</v>
       </c>
       <c r="H136">
-        <v>0.1831</v>
+        <v>0.1893</v>
       </c>
       <c r="I136">
-        <v>0.2436</v>
+        <v>0.2563</v>
       </c>
       <c r="J136">
-        <v>0.696</v>
+        <v>0.6767</v>
       </c>
       <c r="K136">
-        <v>0.8169</v>
+        <v>0.8107</v>
       </c>
       <c r="L136">
-        <v>0.7564</v>
+        <v>0.7437</v>
       </c>
       <c r="M136">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N136" t="s">
         <v>74</v>
@@ -6621,7 +6621,7 @@
         <v>0.821</v>
       </c>
       <c r="M137">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N137" t="s">
         <v>74</v>
@@ -6647,25 +6647,25 @@
         <v>50</v>
       </c>
       <c r="G138">
-        <v>0.3999</v>
+        <v>0.3971</v>
       </c>
       <c r="H138">
         <v>0.2297</v>
       </c>
       <c r="I138">
-        <v>0.3148</v>
+        <v>0.3134</v>
       </c>
       <c r="J138">
-        <v>0.6001</v>
+        <v>0.6029</v>
       </c>
       <c r="K138">
         <v>0.7703</v>
       </c>
       <c r="L138">
-        <v>0.6852</v>
+        <v>0.6866</v>
       </c>
       <c r="M138">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N138" t="s">
         <v>74</v>
@@ -6709,7 +6709,7 @@
         <v>0.7964</v>
       </c>
       <c r="M139">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N139" t="s">
         <v>74</v>
@@ -6753,7 +6753,7 @@
         <v>0.7523</v>
       </c>
       <c r="M140">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N140" t="s">
         <v>74</v>
@@ -6782,22 +6782,22 @@
         <v>0.3216</v>
       </c>
       <c r="H141">
-        <v>0.1736</v>
+        <v>0.1724</v>
       </c>
       <c r="I141">
-        <v>0.2476</v>
+        <v>0.247</v>
       </c>
       <c r="J141">
         <v>0.6784</v>
       </c>
       <c r="K141">
-        <v>0.8264</v>
+        <v>0.8276</v>
       </c>
       <c r="L141">
-        <v>0.7524</v>
+        <v>0.753</v>
       </c>
       <c r="M141">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N141" t="s">
         <v>74</v>
@@ -6841,7 +6841,7 @@
         <v>0.7248</v>
       </c>
       <c r="M142">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N142" t="s">
         <v>74</v>
@@ -6885,7 +6885,7 @@
         <v>0.4986</v>
       </c>
       <c r="M143">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N143" t="s">
         <v>74</v>
@@ -6929,7 +6929,7 @@
         <v>0.7654</v>
       </c>
       <c r="M144">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N144" t="s">
         <v>74</v>
@@ -6973,7 +6973,7 @@
         <v>0.3798</v>
       </c>
       <c r="M145">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N145" t="s">
         <v>74</v>
@@ -7002,22 +7002,22 @@
         <v>0.2338</v>
       </c>
       <c r="H146">
-        <v>0.1327</v>
+        <v>0.1314</v>
       </c>
       <c r="I146">
-        <v>0.1833</v>
+        <v>0.1826</v>
       </c>
       <c r="J146">
         <v>0.7662</v>
       </c>
       <c r="K146">
-        <v>0.8673</v>
+        <v>0.8686</v>
       </c>
       <c r="L146">
-        <v>0.8167</v>
+        <v>0.8174</v>
       </c>
       <c r="M146">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N146" t="s">
         <v>74</v>
@@ -7043,25 +7043,25 @@
         <v>59</v>
       </c>
       <c r="G147">
-        <v>0.3407</v>
+        <v>0.337</v>
       </c>
       <c r="H147">
-        <v>0.2013</v>
+        <v>0.2039</v>
       </c>
       <c r="I147">
-        <v>0.271</v>
+        <v>0.2705</v>
       </c>
       <c r="J147">
-        <v>0.6593</v>
+        <v>0.663</v>
       </c>
       <c r="K147">
-        <v>0.7987</v>
+        <v>0.7961</v>
       </c>
       <c r="L147">
-        <v>0.729</v>
+        <v>0.7295</v>
       </c>
       <c r="M147">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N147" t="s">
         <v>74</v>
@@ -7105,7 +7105,7 @@
         <v>0.5158</v>
       </c>
       <c r="M148">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N148" t="s">
         <v>74</v>
@@ -7131,25 +7131,25 @@
         <v>61</v>
       </c>
       <c r="G149">
-        <v>0.3704</v>
+        <v>0.3633</v>
       </c>
       <c r="H149">
         <v>0.2124</v>
       </c>
       <c r="I149">
-        <v>0.2914</v>
+        <v>0.2878</v>
       </c>
       <c r="J149">
-        <v>0.6296</v>
+        <v>0.6367</v>
       </c>
       <c r="K149">
         <v>0.7876</v>
       </c>
       <c r="L149">
-        <v>0.7086</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="M149">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N149" t="s">
         <v>74</v>
@@ -7175,25 +7175,25 @@
         <v>62</v>
       </c>
       <c r="G150">
-        <v>0.3674</v>
+        <v>0.3806</v>
       </c>
       <c r="H150">
-        <v>0.2014</v>
+        <v>0.2043</v>
       </c>
       <c r="I150">
-        <v>0.2844</v>
+        <v>0.2924</v>
       </c>
       <c r="J150">
-        <v>0.6326000000000001</v>
+        <v>0.6194</v>
       </c>
       <c r="K150">
-        <v>0.7986</v>
+        <v>0.7957</v>
       </c>
       <c r="L150">
-        <v>0.7156</v>
+        <v>0.7076</v>
       </c>
       <c r="M150">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N150" t="s">
         <v>74</v>
@@ -7219,25 +7219,25 @@
         <v>63</v>
       </c>
       <c r="G151">
-        <v>0.3719</v>
+        <v>0.3729</v>
       </c>
       <c r="H151">
         <v>0.2173</v>
       </c>
       <c r="I151">
-        <v>0.2946</v>
+        <v>0.2951</v>
       </c>
       <c r="J151">
-        <v>0.6281</v>
+        <v>0.6271</v>
       </c>
       <c r="K151">
         <v>0.7827</v>
       </c>
       <c r="L151">
-        <v>0.7054</v>
+        <v>0.7049</v>
       </c>
       <c r="M151">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N151" t="s">
         <v>74</v>
@@ -7281,7 +7281,7 @@
         <v>0.4184</v>
       </c>
       <c r="M152">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N152" t="s">
         <v>74</v>
@@ -7325,7 +7325,7 @@
         <v>0.8272</v>
       </c>
       <c r="M153">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N153" t="s">
         <v>74</v>
@@ -7351,25 +7351,25 @@
         <v>66</v>
       </c>
       <c r="G154">
-        <v>0.2191</v>
+        <v>0.2099</v>
       </c>
       <c r="H154">
-        <v>0.111</v>
+        <v>0.1119</v>
       </c>
       <c r="I154">
-        <v>0.165</v>
+        <v>0.1609</v>
       </c>
       <c r="J154">
-        <v>0.7809</v>
+        <v>0.7901</v>
       </c>
       <c r="K154">
-        <v>0.889</v>
+        <v>0.8881</v>
       </c>
       <c r="L154">
-        <v>0.835</v>
+        <v>0.8391</v>
       </c>
       <c r="M154">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N154" t="s">
         <v>74</v>
@@ -7398,22 +7398,22 @@
         <v>0.3017</v>
       </c>
       <c r="H155">
-        <v>0.1735</v>
+        <v>0.1669</v>
       </c>
       <c r="I155">
-        <v>0.2376</v>
+        <v>0.2343</v>
       </c>
       <c r="J155">
         <v>0.6983</v>
       </c>
       <c r="K155">
-        <v>0.8265</v>
+        <v>0.8331</v>
       </c>
       <c r="L155">
-        <v>0.7624</v>
+        <v>0.7657</v>
       </c>
       <c r="M155">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N155" t="s">
         <v>74</v>
@@ -7457,7 +7457,7 @@
         <v>0.4574</v>
       </c>
       <c r="M156">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N156" t="s">
         <v>74</v>
@@ -7501,7 +7501,7 @@
         <v>0.4752</v>
       </c>
       <c r="M157">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N157" t="s">
         <v>74</v>
@@ -7545,7 +7545,7 @@
         <v>0.3987</v>
       </c>
       <c r="M158">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N158" t="s">
         <v>74</v>
@@ -7571,25 +7571,25 @@
         <v>71</v>
       </c>
       <c r="G159">
-        <v>0.2304</v>
+        <v>0.2477</v>
       </c>
       <c r="H159">
-        <v>0.1271</v>
+        <v>0.1307</v>
       </c>
       <c r="I159">
-        <v>0.1788</v>
+        <v>0.1892</v>
       </c>
       <c r="J159">
-        <v>0.7696</v>
+        <v>0.7523</v>
       </c>
       <c r="K159">
-        <v>0.8729</v>
+        <v>0.8693</v>
       </c>
       <c r="L159">
-        <v>0.8212</v>
+        <v>0.8108</v>
       </c>
       <c r="M159">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N159" t="s">
         <v>74</v>
@@ -7615,25 +7615,25 @@
         <v>73</v>
       </c>
       <c r="G160">
-        <v>0.3042</v>
+        <v>0.3001</v>
       </c>
       <c r="H160">
         <v>0.1671</v>
       </c>
       <c r="I160">
-        <v>0.2357</v>
+        <v>0.2336</v>
       </c>
       <c r="J160">
-        <v>0.6958</v>
+        <v>0.6999</v>
       </c>
       <c r="K160">
         <v>0.8329</v>
       </c>
       <c r="L160">
-        <v>0.7643</v>
+        <v>0.7664</v>
       </c>
       <c r="M160">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N160" t="s">
         <v>74</v>
@@ -7677,7 +7677,7 @@
         <v>0.2924</v>
       </c>
       <c r="M161">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N161" t="s">
         <v>74</v>
@@ -7721,7 +7721,7 @@
         <v>0.4152</v>
       </c>
       <c r="M162">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N162" t="s">
         <v>74</v>
@@ -7750,22 +7750,22 @@
         <v>0.7233000000000001</v>
       </c>
       <c r="H163">
-        <v>0.5465</v>
+        <v>0.5455</v>
       </c>
       <c r="I163">
-        <v>0.6349</v>
+        <v>0.6344</v>
       </c>
       <c r="J163">
         <v>0.2767</v>
       </c>
       <c r="K163">
-        <v>0.4535</v>
+        <v>0.4545</v>
       </c>
       <c r="L163">
-        <v>0.3651</v>
+        <v>0.3656</v>
       </c>
       <c r="M163">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N163" t="s">
         <v>74</v>
@@ -7809,7 +7809,7 @@
         <v>0.3696</v>
       </c>
       <c r="M164">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N164" t="s">
         <v>74</v>
@@ -7853,7 +7853,7 @@
         <v>0.3088</v>
       </c>
       <c r="M165">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N165" t="s">
         <v>74</v>
@@ -7897,7 +7897,7 @@
         <v>0.1854</v>
       </c>
       <c r="M166">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N166" t="s">
         <v>74</v>
@@ -7941,7 +7941,7 @@
         <v>0.3883</v>
       </c>
       <c r="M167">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N167" t="s">
         <v>74</v>
@@ -7985,7 +7985,7 @@
         <v>0.1694</v>
       </c>
       <c r="M168">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N168" t="s">
         <v>74</v>
@@ -8029,7 +8029,7 @@
         <v>0.5002</v>
       </c>
       <c r="M169">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N169" t="s">
         <v>74</v>
@@ -8055,25 +8055,25 @@
         <v>59</v>
       </c>
       <c r="G170">
-        <v>0.7571</v>
+        <v>0.7543</v>
       </c>
       <c r="H170">
-        <v>0.5939</v>
+        <v>0.6152</v>
       </c>
       <c r="I170">
-        <v>0.6755</v>
+        <v>0.6848</v>
       </c>
       <c r="J170">
-        <v>0.2429</v>
+        <v>0.2457</v>
       </c>
       <c r="K170">
-        <v>0.4061</v>
+        <v>0.3848</v>
       </c>
       <c r="L170">
-        <v>0.3245</v>
+        <v>0.3152</v>
       </c>
       <c r="M170">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N170" t="s">
         <v>74</v>
@@ -8117,7 +8117,7 @@
         <v>0.1951</v>
       </c>
       <c r="M171">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N171" t="s">
         <v>74</v>
@@ -8161,7 +8161,7 @@
         <v>0.2948</v>
       </c>
       <c r="M172">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N172" t="s">
         <v>74</v>
@@ -8187,25 +8187,25 @@
         <v>62</v>
       </c>
       <c r="G173">
-        <v>0.7488</v>
+        <v>0.7611</v>
       </c>
       <c r="H173">
-        <v>0.6101</v>
+        <v>0.6012</v>
       </c>
       <c r="I173">
-        <v>0.6794</v>
+        <v>0.6811</v>
       </c>
       <c r="J173">
-        <v>0.2512</v>
+        <v>0.2389</v>
       </c>
       <c r="K173">
-        <v>0.3899</v>
+        <v>0.3988</v>
       </c>
       <c r="L173">
-        <v>0.3206</v>
+        <v>0.3189</v>
       </c>
       <c r="M173">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N173" t="s">
         <v>74</v>
@@ -8249,7 +8249,7 @@
         <v>0.3</v>
       </c>
       <c r="M174">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N174" t="s">
         <v>74</v>
@@ -8293,7 +8293,7 @@
         <v>0.1684</v>
       </c>
       <c r="M175">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N175" t="s">
         <v>74</v>
@@ -8337,7 +8337,7 @@
         <v>0.5407</v>
       </c>
       <c r="M176">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N176" t="s">
         <v>74</v>
@@ -8363,25 +8363,25 @@
         <v>66</v>
       </c>
       <c r="G177">
-        <v>0.483</v>
+        <v>0.4759</v>
       </c>
       <c r="H177">
-        <v>0.3524</v>
+        <v>0.3412</v>
       </c>
       <c r="I177">
-        <v>0.4177</v>
+        <v>0.4085</v>
       </c>
       <c r="J177">
-        <v>0.517</v>
+        <v>0.5241</v>
       </c>
       <c r="K177">
-        <v>0.6476</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="L177">
-        <v>0.5823</v>
+        <v>0.5915</v>
       </c>
       <c r="M177">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N177" t="s">
         <v>74</v>
@@ -8425,7 +8425,7 @@
         <v>0.3664</v>
       </c>
       <c r="M178">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N178" t="s">
         <v>74</v>
@@ -8469,7 +8469,7 @@
         <v>0.1682</v>
       </c>
       <c r="M179">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N179" t="s">
         <v>74</v>
@@ -8513,7 +8513,7 @@
         <v>0.1753</v>
       </c>
       <c r="M180">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N180" t="s">
         <v>74</v>
@@ -8557,7 +8557,7 @@
         <v>0.1561</v>
       </c>
       <c r="M181">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N181" t="s">
         <v>74</v>
@@ -8583,25 +8583,25 @@
         <v>71</v>
       </c>
       <c r="G182">
-        <v>0.5809</v>
+        <v>0.582</v>
       </c>
       <c r="H182">
-        <v>0.4308</v>
+        <v>0.4469</v>
       </c>
       <c r="I182">
-        <v>0.5058</v>
+        <v>0.5144</v>
       </c>
       <c r="J182">
-        <v>0.4191</v>
+        <v>0.418</v>
       </c>
       <c r="K182">
-        <v>0.5692</v>
+        <v>0.5531</v>
       </c>
       <c r="L182">
-        <v>0.4942</v>
+        <v>0.4856</v>
       </c>
       <c r="M182">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N182" t="s">
         <v>74</v>
@@ -8645,7 +8645,7 @@
         <v>0.3816</v>
       </c>
       <c r="M183">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N183" t="s">
         <v>74</v>
@@ -8689,7 +8689,7 @@
         <v>0.6568000000000001</v>
       </c>
       <c r="M184">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N184" t="s">
         <v>74</v>
@@ -8733,7 +8733,7 @@
         <v>0.5693</v>
       </c>
       <c r="M185">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N185" t="s">
         <v>74</v>
@@ -8777,7 +8777,7 @@
         <v>0.5558</v>
       </c>
       <c r="M186">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N186" t="s">
         <v>74</v>
@@ -8821,7 +8821,7 @@
         <v>0.5142</v>
       </c>
       <c r="M187">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N187" t="s">
         <v>74</v>
@@ -8847,25 +8847,25 @@
         <v>55</v>
       </c>
       <c r="G188">
-        <v>0.7564</v>
+        <v>0.7579</v>
       </c>
       <c r="H188">
-        <v>0.6355</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="I188">
-        <v>0.696</v>
+        <v>0.6978</v>
       </c>
       <c r="J188">
-        <v>0.2436</v>
+        <v>0.2421</v>
       </c>
       <c r="K188">
-        <v>0.3645</v>
+        <v>0.3624</v>
       </c>
       <c r="L188">
-        <v>0.304</v>
+        <v>0.3022</v>
       </c>
       <c r="M188">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N188" t="s">
         <v>74</v>
@@ -8909,7 +8909,7 @@
         <v>0.6153999999999999</v>
       </c>
       <c r="M189">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N189" t="s">
         <v>74</v>
@@ -8938,22 +8938,22 @@
         <v>0.8277</v>
       </c>
       <c r="H190">
-        <v>0.7229</v>
+        <v>0.7275</v>
       </c>
       <c r="I190">
-        <v>0.7753</v>
+        <v>0.7776</v>
       </c>
       <c r="J190">
         <v>0.1723</v>
       </c>
       <c r="K190">
-        <v>0.2771</v>
+        <v>0.2725</v>
       </c>
       <c r="L190">
-        <v>0.2247</v>
+        <v>0.2224</v>
       </c>
       <c r="M190">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N190" t="s">
         <v>74</v>
@@ -8997,7 +8997,7 @@
         <v>0.713</v>
       </c>
       <c r="M191">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N191" t="s">
         <v>74</v>
@@ -9023,25 +9023,25 @@
         <v>59</v>
       </c>
       <c r="G192">
-        <v>0.57</v>
+        <v>0.5707</v>
       </c>
       <c r="H192">
-        <v>0.4068</v>
+        <v>0.4019</v>
       </c>
       <c r="I192">
-        <v>0.4884</v>
+        <v>0.4863</v>
       </c>
       <c r="J192">
-        <v>0.43</v>
+        <v>0.4293</v>
       </c>
       <c r="K192">
-        <v>0.5931999999999999</v>
+        <v>0.5981</v>
       </c>
       <c r="L192">
-        <v>0.5116000000000001</v>
+        <v>0.5137</v>
       </c>
       <c r="M192">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N192" t="s">
         <v>74</v>
@@ -9085,7 +9085,7 @@
         <v>0.3038</v>
       </c>
       <c r="M193">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N193" t="s">
         <v>74</v>
@@ -9129,7 +9129,7 @@
         <v>0.5011</v>
       </c>
       <c r="M194">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N194" t="s">
         <v>74</v>
@@ -9155,25 +9155,25 @@
         <v>62</v>
       </c>
       <c r="G195">
-        <v>0.5309</v>
+        <v>0.5478</v>
       </c>
       <c r="H195">
-        <v>0.4138</v>
+        <v>0.4293</v>
       </c>
       <c r="I195">
-        <v>0.4724</v>
+        <v>0.4886</v>
       </c>
       <c r="J195">
-        <v>0.4691</v>
+        <v>0.4522</v>
       </c>
       <c r="K195">
-        <v>0.5862000000000001</v>
+        <v>0.5707</v>
       </c>
       <c r="L195">
-        <v>0.5276</v>
+        <v>0.5114</v>
       </c>
       <c r="M195">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N195" t="s">
         <v>74</v>
@@ -9217,7 +9217,7 @@
         <v>0.518</v>
       </c>
       <c r="M196">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N196" t="s">
         <v>74</v>
@@ -9246,22 +9246,22 @@
         <v>0.804</v>
       </c>
       <c r="H197">
-        <v>0.7</v>
+        <v>0.7028</v>
       </c>
       <c r="I197">
-        <v>0.752</v>
+        <v>0.7534</v>
       </c>
       <c r="J197">
         <v>0.196</v>
       </c>
       <c r="K197">
-        <v>0.3</v>
+        <v>0.2972</v>
       </c>
       <c r="L197">
-        <v>0.248</v>
+        <v>0.2466</v>
       </c>
       <c r="M197">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N197" t="s">
         <v>74</v>
@@ -9290,22 +9290,22 @@
         <v>0.3212</v>
       </c>
       <c r="H198">
-        <v>0.2034</v>
+        <v>0.1985</v>
       </c>
       <c r="I198">
-        <v>0.2623</v>
+        <v>0.2599</v>
       </c>
       <c r="J198">
         <v>0.6788</v>
       </c>
       <c r="K198">
-        <v>0.7966</v>
+        <v>0.8015</v>
       </c>
       <c r="L198">
-        <v>0.7377</v>
+        <v>0.7401</v>
       </c>
       <c r="M198">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N198" t="s">
         <v>74</v>
@@ -9331,25 +9331,25 @@
         <v>66</v>
       </c>
       <c r="G199">
-        <v>0.3017</v>
+        <v>0.3032</v>
       </c>
       <c r="H199">
-        <v>0.1831</v>
+        <v>0.1835</v>
       </c>
       <c r="I199">
-        <v>0.2424</v>
+        <v>0.2434</v>
       </c>
       <c r="J199">
-        <v>0.6983</v>
+        <v>0.6968</v>
       </c>
       <c r="K199">
-        <v>0.8169</v>
+        <v>0.8165</v>
       </c>
       <c r="L199">
-        <v>0.7576000000000001</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="M199">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N199" t="s">
         <v>74</v>
@@ -9375,25 +9375,25 @@
         <v>67</v>
       </c>
       <c r="G200">
-        <v>0.4855</v>
+        <v>0.4786</v>
       </c>
       <c r="H200">
         <v>0.3697</v>
       </c>
       <c r="I200">
-        <v>0.4276</v>
+        <v>0.4242</v>
       </c>
       <c r="J200">
-        <v>0.5145</v>
+        <v>0.5214</v>
       </c>
       <c r="K200">
         <v>0.6303</v>
       </c>
       <c r="L200">
-        <v>0.5724</v>
+        <v>0.5758</v>
       </c>
       <c r="M200">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N200" t="s">
         <v>74</v>
@@ -9422,22 +9422,22 @@
         <v>0.7901</v>
       </c>
       <c r="H201">
-        <v>0.6621</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="I201">
-        <v>0.7261</v>
+        <v>0.7295</v>
       </c>
       <c r="J201">
         <v>0.2099</v>
       </c>
       <c r="K201">
-        <v>0.3379</v>
+        <v>0.3311</v>
       </c>
       <c r="L201">
-        <v>0.2739</v>
+        <v>0.2705</v>
       </c>
       <c r="M201">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N201" t="s">
         <v>74</v>
@@ -9463,25 +9463,25 @@
         <v>69</v>
       </c>
       <c r="G202">
-        <v>0.8008999999999999</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="H202">
         <v>0.6485</v>
       </c>
       <c r="I202">
-        <v>0.7247</v>
+        <v>0.7252</v>
       </c>
       <c r="J202">
-        <v>0.1991</v>
+        <v>0.1981</v>
       </c>
       <c r="K202">
         <v>0.3515</v>
       </c>
       <c r="L202">
-        <v>0.2753</v>
+        <v>0.2748</v>
       </c>
       <c r="M202">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N202" t="s">
         <v>74</v>
@@ -9510,22 +9510,22 @@
         <v>0.8342000000000001</v>
       </c>
       <c r="H203">
-        <v>0.7074</v>
+        <v>0.7094</v>
       </c>
       <c r="I203">
-        <v>0.7708</v>
+        <v>0.7718</v>
       </c>
       <c r="J203">
         <v>0.1658</v>
       </c>
       <c r="K203">
-        <v>0.2926</v>
+        <v>0.2906</v>
       </c>
       <c r="L203">
-        <v>0.2292</v>
+        <v>0.2282</v>
       </c>
       <c r="M203">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N203" t="s">
         <v>74</v>
@@ -9551,25 +9551,25 @@
         <v>71</v>
       </c>
       <c r="G204">
-        <v>0.3705</v>
+        <v>0.3779</v>
       </c>
       <c r="H204">
-        <v>0.231</v>
+        <v>0.2502</v>
       </c>
       <c r="I204">
-        <v>0.3008</v>
+        <v>0.314</v>
       </c>
       <c r="J204">
-        <v>0.6294999999999999</v>
+        <v>0.6221</v>
       </c>
       <c r="K204">
-        <v>0.769</v>
+        <v>0.7498</v>
       </c>
       <c r="L204">
-        <v>0.6992</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="M204">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N204" t="s">
         <v>74</v>
@@ -9613,7 +9613,7 @@
         <v>0.5979</v>
       </c>
       <c r="M205">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N205" t="s">
         <v>74</v>
@@ -9657,7 +9657,7 @@
         <v>0.4228</v>
       </c>
       <c r="M206">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N206" t="s">
         <v>74</v>
@@ -9683,25 +9683,25 @@
         <v>53</v>
       </c>
       <c r="G207">
-        <v>0.6463</v>
+        <v>0.6502</v>
       </c>
       <c r="H207">
         <v>0.5121</v>
       </c>
       <c r="I207">
-        <v>0.5792</v>
+        <v>0.5812</v>
       </c>
       <c r="J207">
-        <v>0.3537</v>
+        <v>0.3498</v>
       </c>
       <c r="K207">
         <v>0.4879</v>
       </c>
       <c r="L207">
-        <v>0.4208</v>
+        <v>0.4188</v>
       </c>
       <c r="M207">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N207" t="s">
         <v>74</v>
@@ -9745,7 +9745,7 @@
         <v>0.3996</v>
       </c>
       <c r="M208">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N208" t="s">
         <v>74</v>
@@ -9789,7 +9789,7 @@
         <v>0.2168</v>
       </c>
       <c r="M209">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N209" t="s">
         <v>74</v>
@@ -9833,7 +9833,7 @@
         <v>0.4697</v>
       </c>
       <c r="M210">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N210" t="s">
         <v>74</v>
@@ -9877,7 +9877,7 @@
         <v>0.1663</v>
       </c>
       <c r="M211">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N211" t="s">
         <v>74</v>
@@ -9921,7 +9921,7 @@
         <v>0.5668</v>
       </c>
       <c r="M212">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N212" t="s">
         <v>74</v>
@@ -9947,25 +9947,25 @@
         <v>59</v>
       </c>
       <c r="G213">
-        <v>0.6685</v>
+        <v>0.6561</v>
       </c>
       <c r="H213">
-        <v>0.5416</v>
+        <v>0.5477</v>
       </c>
       <c r="I213">
-        <v>0.605</v>
+        <v>0.6019</v>
       </c>
       <c r="J213">
-        <v>0.3315</v>
+        <v>0.3439</v>
       </c>
       <c r="K213">
-        <v>0.4584</v>
+        <v>0.4523</v>
       </c>
       <c r="L213">
-        <v>0.395</v>
+        <v>0.3981</v>
       </c>
       <c r="M213">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N213" t="s">
         <v>74</v>
@@ -10009,7 +10009,7 @@
         <v>0.2195</v>
       </c>
       <c r="M214">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N214" t="s">
         <v>74</v>
@@ -10053,7 +10053,7 @@
         <v>0.3682</v>
       </c>
       <c r="M215">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N215" t="s">
         <v>74</v>
@@ -10079,25 +10079,25 @@
         <v>62</v>
       </c>
       <c r="G216">
-        <v>0.7186</v>
+        <v>0.7439</v>
       </c>
       <c r="H216">
-        <v>0.5259</v>
+        <v>0.5333</v>
       </c>
       <c r="I216">
-        <v>0.6222</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="J216">
-        <v>0.2814</v>
+        <v>0.2561</v>
       </c>
       <c r="K216">
-        <v>0.4741</v>
+        <v>0.4667</v>
       </c>
       <c r="L216">
-        <v>0.3778</v>
+        <v>0.3614</v>
       </c>
       <c r="M216">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N216" t="s">
         <v>74</v>
@@ -10141,7 +10141,7 @@
         <v>0.3666</v>
       </c>
       <c r="M217">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N217" t="s">
         <v>74</v>
@@ -10185,7 +10185,7 @@
         <v>0.1798</v>
       </c>
       <c r="M218">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N218" t="s">
         <v>74</v>
@@ -10229,7 +10229,7 @@
         <v>0.6165</v>
       </c>
       <c r="M219">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N219" t="s">
         <v>74</v>
@@ -10255,25 +10255,25 @@
         <v>66</v>
       </c>
       <c r="G220">
-        <v>0.3906</v>
+        <v>0.395</v>
       </c>
       <c r="H220">
-        <v>0.2525</v>
+        <v>0.2559</v>
       </c>
       <c r="I220">
-        <v>0.3216</v>
+        <v>0.3254</v>
       </c>
       <c r="J220">
-        <v>0.6094000000000001</v>
+        <v>0.605</v>
       </c>
       <c r="K220">
-        <v>0.7475000000000001</v>
+        <v>0.7441</v>
       </c>
       <c r="L220">
-        <v>0.6784</v>
+        <v>0.6746</v>
       </c>
       <c r="M220">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N220" t="s">
         <v>74</v>
@@ -10317,7 +10317,7 @@
         <v>0.4296</v>
       </c>
       <c r="M221">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N221" t="s">
         <v>74</v>
@@ -10343,25 +10343,25 @@
         <v>68</v>
       </c>
       <c r="G222">
-        <v>0.858</v>
+        <v>0.859</v>
       </c>
       <c r="H222">
-        <v>0.7307</v>
+        <v>0.7365</v>
       </c>
       <c r="I222">
-        <v>0.7944</v>
+        <v>0.7978</v>
       </c>
       <c r="J222">
-        <v>0.142</v>
+        <v>0.141</v>
       </c>
       <c r="K222">
-        <v>0.2693</v>
+        <v>0.2635</v>
       </c>
       <c r="L222">
-        <v>0.2056</v>
+        <v>0.2022</v>
       </c>
       <c r="M222">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N222" t="s">
         <v>74</v>
@@ -10405,7 +10405,7 @@
         <v>0.1978</v>
       </c>
       <c r="M223">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N223" t="s">
         <v>74</v>
@@ -10431,25 +10431,25 @@
         <v>70</v>
       </c>
       <c r="G224">
-        <v>0.8738</v>
+        <v>0.876</v>
       </c>
       <c r="H224">
         <v>0.7506</v>
       </c>
       <c r="I224">
-        <v>0.8122</v>
+        <v>0.8133</v>
       </c>
       <c r="J224">
-        <v>0.1262</v>
+        <v>0.124</v>
       </c>
       <c r="K224">
         <v>0.2494</v>
       </c>
       <c r="L224">
-        <v>0.1878</v>
+        <v>0.1867</v>
       </c>
       <c r="M224">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N224" t="s">
         <v>74</v>
@@ -10475,25 +10475,25 @@
         <v>71</v>
       </c>
       <c r="G225">
-        <v>0.4755</v>
+        <v>0.4794</v>
       </c>
       <c r="H225">
-        <v>0.3555</v>
+        <v>0.3655</v>
       </c>
       <c r="I225">
-        <v>0.4155</v>
+        <v>0.4224</v>
       </c>
       <c r="J225">
-        <v>0.5245</v>
+        <v>0.5206</v>
       </c>
       <c r="K225">
-        <v>0.6445</v>
+        <v>0.6345</v>
       </c>
       <c r="L225">
-        <v>0.5845</v>
+        <v>0.5776</v>
       </c>
       <c r="M225">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N225" t="s">
         <v>74</v>
@@ -10537,7 +10537,7 @@
         <v>0.4508</v>
       </c>
       <c r="M226">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N226" t="s">
         <v>74</v>
@@ -10581,7 +10581,7 @@
         <v>0.499</v>
       </c>
       <c r="M227">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N227" t="s">
         <v>74</v>
@@ -10625,7 +10625,7 @@
         <v>0.4445</v>
       </c>
       <c r="M228">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N228" t="s">
         <v>74</v>
@@ -10669,7 +10669,7 @@
         <v>0.2478</v>
       </c>
       <c r="M229">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N229" t="s">
         <v>74</v>
@@ -10698,22 +10698,22 @@
         <v>0.5095</v>
       </c>
       <c r="H230">
-        <v>0.3738</v>
+        <v>0.3723</v>
       </c>
       <c r="I230">
-        <v>0.4416</v>
+        <v>0.4409</v>
       </c>
       <c r="J230">
         <v>0.4905</v>
       </c>
       <c r="K230">
-        <v>0.6262</v>
+        <v>0.6277</v>
       </c>
       <c r="L230">
-        <v>0.5584</v>
+        <v>0.5591</v>
       </c>
       <c r="M230">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N230" t="s">
         <v>74</v>
@@ -10757,7 +10757,7 @@
         <v>0.1901</v>
       </c>
       <c r="M231">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N231" t="s">
         <v>74</v>
@@ -10786,22 +10786,22 @@
         <v>0.4163</v>
       </c>
       <c r="H232">
-        <v>0.3045</v>
+        <v>0.2991</v>
       </c>
       <c r="I232">
-        <v>0.3604</v>
+        <v>0.3577</v>
       </c>
       <c r="J232">
         <v>0.5837</v>
       </c>
       <c r="K232">
-        <v>0.6955</v>
+        <v>0.7009</v>
       </c>
       <c r="L232">
-        <v>0.6395999999999999</v>
+        <v>0.6423</v>
       </c>
       <c r="M232">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N232" t="s">
         <v>74</v>
@@ -10827,25 +10827,25 @@
         <v>59</v>
       </c>
       <c r="G233">
-        <v>0.6218</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="H233">
-        <v>0.4649</v>
+        <v>0.4569</v>
       </c>
       <c r="I233">
-        <v>0.5434</v>
+        <v>0.5427</v>
       </c>
       <c r="J233">
-        <v>0.3782</v>
+        <v>0.3715</v>
       </c>
       <c r="K233">
-        <v>0.5351</v>
+        <v>0.5431</v>
       </c>
       <c r="L233">
-        <v>0.4566</v>
+        <v>0.4573</v>
       </c>
       <c r="M233">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N233" t="s">
         <v>74</v>
@@ -10889,7 +10889,7 @@
         <v>0.2524</v>
       </c>
       <c r="M234">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N234" t="s">
         <v>74</v>
@@ -10933,7 +10933,7 @@
         <v>0.4225</v>
       </c>
       <c r="M235">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N235" t="s">
         <v>74</v>
@@ -10959,25 +10959,25 @@
         <v>62</v>
       </c>
       <c r="G236">
-        <v>0.5951</v>
+        <v>0.6057</v>
       </c>
       <c r="H236">
-        <v>0.4939</v>
+        <v>0.5009</v>
       </c>
       <c r="I236">
-        <v>0.5445</v>
+        <v>0.5533</v>
       </c>
       <c r="J236">
-        <v>0.4049</v>
+        <v>0.3943</v>
       </c>
       <c r="K236">
-        <v>0.5061</v>
+        <v>0.4991</v>
       </c>
       <c r="L236">
-        <v>0.4555</v>
+        <v>0.4467</v>
       </c>
       <c r="M236">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N236" t="s">
         <v>74</v>
@@ -11003,25 +11003,25 @@
         <v>63</v>
       </c>
       <c r="G237">
-        <v>0.6508</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="H237">
         <v>0.485</v>
       </c>
       <c r="I237">
-        <v>0.5679</v>
+        <v>0.5703</v>
       </c>
       <c r="J237">
-        <v>0.3492</v>
+        <v>0.3443</v>
       </c>
       <c r="K237">
         <v>0.515</v>
       </c>
       <c r="L237">
-        <v>0.4321</v>
+        <v>0.4297</v>
       </c>
       <c r="M237">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N237" t="s">
         <v>74</v>
@@ -11065,7 +11065,7 @@
         <v>0.2078</v>
       </c>
       <c r="M238">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N238" t="s">
         <v>74</v>
@@ -11109,7 +11109,7 @@
         <v>0.6914</v>
       </c>
       <c r="M239">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N239" t="s">
         <v>74</v>
@@ -11135,25 +11135,25 @@
         <v>66</v>
       </c>
       <c r="G240">
-        <v>0.3581</v>
+        <v>0.3543</v>
       </c>
       <c r="H240">
-        <v>0.2146</v>
+        <v>0.212</v>
       </c>
       <c r="I240">
-        <v>0.2864</v>
+        <v>0.2832</v>
       </c>
       <c r="J240">
-        <v>0.6419</v>
+        <v>0.6457000000000001</v>
       </c>
       <c r="K240">
-        <v>0.7854</v>
+        <v>0.788</v>
       </c>
       <c r="L240">
-        <v>0.7136</v>
+        <v>0.7168</v>
       </c>
       <c r="M240">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N240" t="s">
         <v>74</v>
@@ -11197,7 +11197,7 @@
         <v>0.5188</v>
       </c>
       <c r="M241">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N241" t="s">
         <v>74</v>
@@ -11241,7 +11241,7 @@
         <v>0.232</v>
       </c>
       <c r="M242">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N242" t="s">
         <v>74</v>
@@ -11285,7 +11285,7 @@
         <v>0.2343</v>
       </c>
       <c r="M243">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N243" t="s">
         <v>74</v>
@@ -11329,7 +11329,7 @@
         <v>0.1988</v>
       </c>
       <c r="M244">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N244" t="s">
         <v>74</v>
@@ -11355,25 +11355,25 @@
         <v>71</v>
       </c>
       <c r="G245">
-        <v>0.4165</v>
+        <v>0.4271</v>
       </c>
       <c r="H245">
-        <v>0.2901</v>
+        <v>0.3011</v>
       </c>
       <c r="I245">
-        <v>0.3533</v>
+        <v>0.3641</v>
       </c>
       <c r="J245">
-        <v>0.5835</v>
+        <v>0.5729</v>
       </c>
       <c r="K245">
-        <v>0.7099</v>
+        <v>0.6989</v>
       </c>
       <c r="L245">
-        <v>0.6467000000000001</v>
+        <v>0.6359</v>
       </c>
       <c r="M245">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N245" t="s">
         <v>74</v>
@@ -11417,7 +11417,7 @@
         <v>0.5311</v>
       </c>
       <c r="M246">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N246" t="s">
         <v>74</v>
@@ -11446,22 +11446,22 @@
         <v>0.617</v>
       </c>
       <c r="H247">
-        <v>0.4668</v>
+        <v>0.4648</v>
       </c>
       <c r="I247">
-        <v>0.5419</v>
+        <v>0.5409</v>
       </c>
       <c r="J247">
         <v>0.383</v>
       </c>
       <c r="K247">
-        <v>0.5332</v>
+        <v>0.5352</v>
       </c>
       <c r="L247">
-        <v>0.4581</v>
+        <v>0.4591</v>
       </c>
       <c r="M247">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N247" t="s">
         <v>74</v>
@@ -11490,22 +11490,22 @@
         <v>0.8207</v>
       </c>
       <c r="H248">
-        <v>0.6805</v>
+        <v>0.6852</v>
       </c>
       <c r="I248">
-        <v>0.7506</v>
+        <v>0.753</v>
       </c>
       <c r="J248">
         <v>0.1793</v>
       </c>
       <c r="K248">
-        <v>0.3195</v>
+        <v>0.3148</v>
       </c>
       <c r="L248">
-        <v>0.2494</v>
+        <v>0.247</v>
       </c>
       <c r="M248">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N248" t="s">
         <v>74</v>
@@ -11531,25 +11531,25 @@
         <v>56</v>
       </c>
       <c r="G249">
-        <v>0.537</v>
+        <v>0.5375</v>
       </c>
       <c r="H249">
         <v>0.3651</v>
       </c>
       <c r="I249">
-        <v>0.451</v>
+        <v>0.4513</v>
       </c>
       <c r="J249">
-        <v>0.463</v>
+        <v>0.4625</v>
       </c>
       <c r="K249">
         <v>0.6349</v>
       </c>
       <c r="L249">
-        <v>0.549</v>
+        <v>0.5487</v>
       </c>
       <c r="M249">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N249" t="s">
         <v>74</v>
@@ -11593,7 +11593,7 @@
         <v>0.1962</v>
       </c>
       <c r="M250">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N250" t="s">
         <v>74</v>
@@ -11637,7 +11637,7 @@
         <v>0.6375999999999999</v>
       </c>
       <c r="M251">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N251" t="s">
         <v>74</v>
@@ -11663,25 +11663,25 @@
         <v>59</v>
       </c>
       <c r="G252">
-        <v>0.588</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="H252">
-        <v>0.4874</v>
+        <v>0.4906</v>
       </c>
       <c r="I252">
-        <v>0.5377</v>
+        <v>0.5389</v>
       </c>
       <c r="J252">
-        <v>0.412</v>
+        <v>0.4128</v>
       </c>
       <c r="K252">
-        <v>0.5125999999999999</v>
+        <v>0.5094</v>
       </c>
       <c r="L252">
-        <v>0.4623</v>
+        <v>0.4611</v>
       </c>
       <c r="M252">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N252" t="s">
         <v>74</v>
@@ -11725,7 +11725,7 @@
         <v>0.2546</v>
       </c>
       <c r="M253">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N253" t="s">
         <v>74</v>
@@ -11769,7 +11769,7 @@
         <v>0.4304</v>
       </c>
       <c r="M254">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N254" t="s">
         <v>74</v>
@@ -11795,25 +11795,25 @@
         <v>62</v>
       </c>
       <c r="G255">
-        <v>0.6214</v>
+        <v>0.6227</v>
       </c>
       <c r="H255">
-        <v>0.4759</v>
+        <v>0.4843</v>
       </c>
       <c r="I255">
-        <v>0.5486</v>
+        <v>0.5535</v>
       </c>
       <c r="J255">
-        <v>0.3786</v>
+        <v>0.3773</v>
       </c>
       <c r="K255">
-        <v>0.5241</v>
+        <v>0.5157</v>
       </c>
       <c r="L255">
-        <v>0.4514</v>
+        <v>0.4465</v>
       </c>
       <c r="M255">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N255" t="s">
         <v>74</v>
@@ -11857,7 +11857,7 @@
         <v>0.4356</v>
       </c>
       <c r="M256">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N256" t="s">
         <v>74</v>
@@ -11901,7 +11901,7 @@
         <v>0.2192</v>
       </c>
       <c r="M257">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N257" t="s">
         <v>74</v>
@@ -11927,25 +11927,25 @@
         <v>65</v>
       </c>
       <c r="G258">
-        <v>0.376</v>
+        <v>0.3728</v>
       </c>
       <c r="H258">
-        <v>0.248</v>
+        <v>0.2453</v>
       </c>
       <c r="I258">
-        <v>0.312</v>
+        <v>0.309</v>
       </c>
       <c r="J258">
-        <v>0.624</v>
+        <v>0.6272</v>
       </c>
       <c r="K258">
-        <v>0.752</v>
+        <v>0.7547</v>
       </c>
       <c r="L258">
-        <v>0.6879999999999999</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="M258">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N258" t="s">
         <v>74</v>
@@ -11971,25 +11971,25 @@
         <v>66</v>
       </c>
       <c r="G259">
-        <v>0.3375</v>
+        <v>0.3315</v>
       </c>
       <c r="H259">
-        <v>0.2289</v>
+        <v>0.223</v>
       </c>
       <c r="I259">
-        <v>0.2832</v>
+        <v>0.2772</v>
       </c>
       <c r="J259">
-        <v>0.6625</v>
+        <v>0.6685</v>
       </c>
       <c r="K259">
-        <v>0.7711</v>
+        <v>0.777</v>
       </c>
       <c r="L259">
-        <v>0.7168</v>
+        <v>0.7228</v>
       </c>
       <c r="M259">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N259" t="s">
         <v>74</v>
@@ -12033,7 +12033,7 @@
         <v>0.4943</v>
       </c>
       <c r="M260">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N260" t="s">
         <v>74</v>
@@ -12059,25 +12059,25 @@
         <v>68</v>
       </c>
       <c r="G261">
-        <v>0.8327</v>
+        <v>0.8364</v>
       </c>
       <c r="H261">
         <v>0.6901</v>
       </c>
       <c r="I261">
-        <v>0.7614</v>
+        <v>0.7632</v>
       </c>
       <c r="J261">
-        <v>0.1673</v>
+        <v>0.1636</v>
       </c>
       <c r="K261">
         <v>0.3099</v>
       </c>
       <c r="L261">
-        <v>0.2386</v>
+        <v>0.2368</v>
       </c>
       <c r="M261">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N261" t="s">
         <v>74</v>
@@ -12121,7 +12121,7 @@
         <v>0.2437</v>
       </c>
       <c r="M262">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N262" t="s">
         <v>74</v>
@@ -12165,7 +12165,7 @@
         <v>0.2096</v>
       </c>
       <c r="M263">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N263" t="s">
         <v>74</v>
@@ -12191,25 +12191,25 @@
         <v>71</v>
       </c>
       <c r="G264">
-        <v>0.4272</v>
+        <v>0.4245</v>
       </c>
       <c r="H264">
-        <v>0.2715</v>
+        <v>0.2754</v>
       </c>
       <c r="I264">
-        <v>0.3494</v>
+        <v>0.35</v>
       </c>
       <c r="J264">
-        <v>0.5728</v>
+        <v>0.5755</v>
       </c>
       <c r="K264">
-        <v>0.7285</v>
+        <v>0.7246</v>
       </c>
       <c r="L264">
-        <v>0.6506</v>
+        <v>0.65</v>
       </c>
       <c r="M264">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N264" t="s">
         <v>74</v>
@@ -12253,7 +12253,7 @@
         <v>0.5331</v>
       </c>
       <c r="M265">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N265" t="s">
         <v>74</v>
@@ -12282,22 +12282,22 @@
         <v>0.803</v>
       </c>
       <c r="H266">
-        <v>0.6108</v>
+        <v>0.6098</v>
       </c>
       <c r="I266">
-        <v>0.7069</v>
+        <v>0.7064</v>
       </c>
       <c r="J266">
         <v>0.197</v>
       </c>
       <c r="K266">
-        <v>0.3892</v>
+        <v>0.3902</v>
       </c>
       <c r="L266">
-        <v>0.2931</v>
+        <v>0.2936</v>
       </c>
       <c r="M266">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N266" t="s">
         <v>74</v>
@@ -12326,22 +12326,22 @@
         <v>0.4803</v>
       </c>
       <c r="H267">
-        <v>0.343</v>
+        <v>0.3378</v>
       </c>
       <c r="I267">
-        <v>0.4116</v>
+        <v>0.4091</v>
       </c>
       <c r="J267">
         <v>0.5197000000000001</v>
       </c>
       <c r="K267">
-        <v>0.657</v>
+        <v>0.6622</v>
       </c>
       <c r="L267">
-        <v>0.5884</v>
+        <v>0.5909</v>
       </c>
       <c r="M267">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N267" t="s">
         <v>74</v>
@@ -12385,7 +12385,7 @@
         <v>0.2161</v>
       </c>
       <c r="M268">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N268" t="s">
         <v>74</v>
@@ -12414,22 +12414,22 @@
         <v>0.4136</v>
       </c>
       <c r="H269">
-        <v>0.2138</v>
+        <v>0.2117</v>
       </c>
       <c r="I269">
-        <v>0.3137</v>
+        <v>0.3126</v>
       </c>
       <c r="J269">
         <v>0.5864</v>
       </c>
       <c r="K269">
-        <v>0.7862</v>
+        <v>0.7883</v>
       </c>
       <c r="L269">
-        <v>0.6863</v>
+        <v>0.6874</v>
       </c>
       <c r="M269">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N269" t="s">
         <v>74</v>
@@ -12455,25 +12455,25 @@
         <v>59</v>
       </c>
       <c r="G270">
-        <v>0.5603</v>
+        <v>0.5478</v>
       </c>
       <c r="H270">
-        <v>0.427</v>
+        <v>0.4265</v>
       </c>
       <c r="I270">
-        <v>0.4936</v>
+        <v>0.4872</v>
       </c>
       <c r="J270">
-        <v>0.4397</v>
+        <v>0.4522</v>
       </c>
       <c r="K270">
-        <v>0.573</v>
+        <v>0.5735</v>
       </c>
       <c r="L270">
-        <v>0.5064</v>
+        <v>0.5128</v>
       </c>
       <c r="M270">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N270" t="s">
         <v>74</v>
@@ -12502,22 +12502,22 @@
         <v>0.7631</v>
       </c>
       <c r="H271">
-        <v>0.6273</v>
+        <v>0.6288</v>
       </c>
       <c r="I271">
-        <v>0.6952</v>
+        <v>0.696</v>
       </c>
       <c r="J271">
         <v>0.2369</v>
       </c>
       <c r="K271">
-        <v>0.3727</v>
+        <v>0.3712</v>
       </c>
       <c r="L271">
-        <v>0.3048</v>
+        <v>0.304</v>
       </c>
       <c r="M271">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N271" t="s">
         <v>74</v>
@@ -12546,22 +12546,22 @@
         <v>0.6047</v>
       </c>
       <c r="H272">
-        <v>0.4501</v>
+        <v>0.4525</v>
       </c>
       <c r="I272">
-        <v>0.5274</v>
+        <v>0.5286</v>
       </c>
       <c r="J272">
         <v>0.3953</v>
       </c>
       <c r="K272">
-        <v>0.5499000000000001</v>
+        <v>0.5475</v>
       </c>
       <c r="L272">
-        <v>0.4726</v>
+        <v>0.4714</v>
       </c>
       <c r="M272">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N272" t="s">
         <v>74</v>
@@ -12587,25 +12587,25 @@
         <v>62</v>
       </c>
       <c r="G273">
-        <v>0.5798</v>
+        <v>0.5703</v>
       </c>
       <c r="H273">
-        <v>0.4256</v>
+        <v>0.4316</v>
       </c>
       <c r="I273">
-        <v>0.5027</v>
+        <v>0.501</v>
       </c>
       <c r="J273">
-        <v>0.4202</v>
+        <v>0.4297</v>
       </c>
       <c r="K273">
-        <v>0.5744</v>
+        <v>0.5684</v>
       </c>
       <c r="L273">
-        <v>0.4973</v>
+        <v>0.499</v>
       </c>
       <c r="M273">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N273" t="s">
         <v>74</v>
@@ -12649,7 +12649,7 @@
         <v>0.4762</v>
       </c>
       <c r="M274">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N274" t="s">
         <v>74</v>
@@ -12693,7 +12693,7 @@
         <v>0.2388</v>
       </c>
       <c r="M275">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N275" t="s">
         <v>74</v>
@@ -12722,22 +12722,22 @@
         <v>0.3649</v>
       </c>
       <c r="H276">
-        <v>0.2002</v>
+        <v>0.1972</v>
       </c>
       <c r="I276">
-        <v>0.2825</v>
+        <v>0.281</v>
       </c>
       <c r="J276">
         <v>0.6351</v>
       </c>
       <c r="K276">
-        <v>0.7998</v>
+        <v>0.8028</v>
       </c>
       <c r="L276">
-        <v>0.7175</v>
+        <v>0.719</v>
       </c>
       <c r="M276">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N276" t="s">
         <v>74</v>
@@ -12763,25 +12763,25 @@
         <v>66</v>
       </c>
       <c r="G277">
-        <v>0.315</v>
+        <v>0.3027</v>
       </c>
       <c r="H277">
-        <v>0.1784</v>
+        <v>0.1748</v>
       </c>
       <c r="I277">
-        <v>0.2467</v>
+        <v>0.2388</v>
       </c>
       <c r="J277">
-        <v>0.6850000000000001</v>
+        <v>0.6973</v>
       </c>
       <c r="K277">
-        <v>0.8216</v>
+        <v>0.8252</v>
       </c>
       <c r="L277">
-        <v>0.7533</v>
+        <v>0.7612</v>
       </c>
       <c r="M277">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N277" t="s">
         <v>74</v>
@@ -12810,22 +12810,22 @@
         <v>0.5137</v>
       </c>
       <c r="H278">
-        <v>0.3587</v>
+        <v>0.3544</v>
       </c>
       <c r="I278">
-        <v>0.4362</v>
+        <v>0.4341</v>
       </c>
       <c r="J278">
         <v>0.4863</v>
       </c>
       <c r="K278">
-        <v>0.6413</v>
+        <v>0.6456</v>
       </c>
       <c r="L278">
-        <v>0.5638</v>
+        <v>0.5659</v>
       </c>
       <c r="M278">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N278" t="s">
         <v>74</v>
@@ -12851,25 +12851,25 @@
         <v>68</v>
       </c>
       <c r="G279">
-        <v>0.8058</v>
+        <v>0.8073</v>
       </c>
       <c r="H279">
-        <v>0.658</v>
+        <v>0.6619</v>
       </c>
       <c r="I279">
-        <v>0.7319</v>
+        <v>0.7346</v>
       </c>
       <c r="J279">
-        <v>0.1942</v>
+        <v>0.1927</v>
       </c>
       <c r="K279">
-        <v>0.342</v>
+        <v>0.3381</v>
       </c>
       <c r="L279">
-        <v>0.2681</v>
+        <v>0.2654</v>
       </c>
       <c r="M279">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N279" t="s">
         <v>74</v>
@@ -12913,7 +12913,7 @@
         <v>0.2586</v>
       </c>
       <c r="M280">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N280" t="s">
         <v>74</v>
@@ -12957,7 +12957,7 @@
         <v>0.2214</v>
       </c>
       <c r="M281">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N281" t="s">
         <v>74</v>
@@ -12983,25 +12983,25 @@
         <v>71</v>
       </c>
       <c r="G282">
-        <v>0.3777</v>
+        <v>0.3981</v>
       </c>
       <c r="H282">
-        <v>0.2504</v>
+        <v>0.2474</v>
       </c>
       <c r="I282">
-        <v>0.314</v>
+        <v>0.3228</v>
       </c>
       <c r="J282">
-        <v>0.6223</v>
+        <v>0.6019</v>
       </c>
       <c r="K282">
-        <v>0.7496</v>
+        <v>0.7526</v>
       </c>
       <c r="L282">
-        <v>0.6860000000000001</v>
+        <v>0.6772</v>
       </c>
       <c r="M282">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N282" t="s">
         <v>74</v>
@@ -13045,7 +13045,7 @@
         <v>0.5828</v>
       </c>
       <c r="M283">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N283" t="s">
         <v>74</v>
@@ -13074,22 +13074,22 @@
         <v>0.2845</v>
       </c>
       <c r="H284">
-        <v>0.191</v>
+        <v>0.1855</v>
       </c>
       <c r="I284">
-        <v>0.2378</v>
+        <v>0.235</v>
       </c>
       <c r="J284">
         <v>0.7155</v>
       </c>
       <c r="K284">
-        <v>0.8090000000000001</v>
+        <v>0.8145</v>
       </c>
       <c r="L284">
-        <v>0.7622</v>
+        <v>0.765</v>
       </c>
       <c r="M284">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N284" t="s">
         <v>74</v>
@@ -13133,7 +13133,7 @@
         <v>0.3758</v>
       </c>
       <c r="M285">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N285" t="s">
         <v>74</v>
@@ -13177,7 +13177,7 @@
         <v>0.8169999999999999</v>
       </c>
       <c r="M286">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N286" t="s">
         <v>74</v>
@@ -13203,25 +13203,25 @@
         <v>59</v>
       </c>
       <c r="G287">
-        <v>0.3803</v>
+        <v>0.3613</v>
       </c>
       <c r="H287">
-        <v>0.201</v>
+        <v>0.2117</v>
       </c>
       <c r="I287">
-        <v>0.2906</v>
+        <v>0.2865</v>
       </c>
       <c r="J287">
-        <v>0.6197</v>
+        <v>0.6387</v>
       </c>
       <c r="K287">
-        <v>0.799</v>
+        <v>0.7883</v>
       </c>
       <c r="L287">
-        <v>0.7094</v>
+        <v>0.7135</v>
       </c>
       <c r="M287">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N287" t="s">
         <v>74</v>
@@ -13265,7 +13265,7 @@
         <v>0.5206</v>
       </c>
       <c r="M288">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N288" t="s">
         <v>74</v>
@@ -13309,7 +13309,7 @@
         <v>0.6794</v>
       </c>
       <c r="M289">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N289" t="s">
         <v>74</v>
@@ -13335,25 +13335,25 @@
         <v>62</v>
       </c>
       <c r="G290">
-        <v>0.3558</v>
+        <v>0.3628</v>
       </c>
       <c r="H290">
-        <v>0.219</v>
+        <v>0.2182</v>
       </c>
       <c r="I290">
-        <v>0.2874</v>
+        <v>0.2905</v>
       </c>
       <c r="J290">
-        <v>0.6442</v>
+        <v>0.6372</v>
       </c>
       <c r="K290">
-        <v>0.781</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="L290">
-        <v>0.7126</v>
+        <v>0.7095</v>
       </c>
       <c r="M290">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N290" t="s">
         <v>74</v>
@@ -13397,7 +13397,7 @@
         <v>0.6877</v>
       </c>
       <c r="M291">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N291" t="s">
         <v>74</v>
@@ -13441,7 +13441,7 @@
         <v>0.4199</v>
       </c>
       <c r="M292">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N292" t="s">
         <v>74</v>
@@ -13485,7 +13485,7 @@
         <v>0.8196</v>
       </c>
       <c r="M293">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N293" t="s">
         <v>74</v>
@@ -13511,25 +13511,25 @@
         <v>66</v>
       </c>
       <c r="G294">
-        <v>0.2225</v>
+        <v>0.2217</v>
       </c>
       <c r="H294">
-        <v>0.1221</v>
+        <v>0.12</v>
       </c>
       <c r="I294">
-        <v>0.1723</v>
+        <v>0.1708</v>
       </c>
       <c r="J294">
-        <v>0.7775</v>
+        <v>0.7783</v>
       </c>
       <c r="K294">
-        <v>0.8779</v>
+        <v>0.88</v>
       </c>
       <c r="L294">
-        <v>0.8277</v>
+        <v>0.8292</v>
       </c>
       <c r="M294">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N294" t="s">
         <v>74</v>
@@ -13555,25 +13555,25 @@
         <v>67</v>
       </c>
       <c r="G295">
-        <v>0.3375</v>
+        <v>0.3344</v>
       </c>
       <c r="H295">
         <v>0.1746</v>
       </c>
       <c r="I295">
-        <v>0.256</v>
+        <v>0.2545</v>
       </c>
       <c r="J295">
-        <v>0.6625</v>
+        <v>0.6656</v>
       </c>
       <c r="K295">
         <v>0.8254</v>
       </c>
       <c r="L295">
-        <v>0.744</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="M295">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N295" t="s">
         <v>74</v>
@@ -13617,7 +13617,7 @@
         <v>0.4494</v>
       </c>
       <c r="M296">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N296" t="s">
         <v>74</v>
@@ -13661,7 +13661,7 @@
         <v>0.4708</v>
       </c>
       <c r="M297">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N297" t="s">
         <v>74</v>
@@ -13705,7 +13705,7 @@
         <v>0.3855</v>
       </c>
       <c r="M298">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N298" t="s">
         <v>74</v>
@@ -13731,25 +13731,25 @@
         <v>71</v>
       </c>
       <c r="G299">
-        <v>0.2489</v>
+        <v>0.2497</v>
       </c>
       <c r="H299">
-        <v>0.1546</v>
+        <v>0.1636</v>
       </c>
       <c r="I299">
-        <v>0.2017</v>
+        <v>0.2066</v>
       </c>
       <c r="J299">
-        <v>0.7511</v>
+        <v>0.7503</v>
       </c>
       <c r="K299">
-        <v>0.8454</v>
+        <v>0.8364</v>
       </c>
       <c r="L299">
-        <v>0.7983</v>
+        <v>0.7934</v>
       </c>
       <c r="M299">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N299" t="s">
         <v>74</v>
@@ -13793,7 +13793,7 @@
         <v>0.7628</v>
       </c>
       <c r="M300">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N300" t="s">
         <v>74</v>
@@ -13837,7 +13837,7 @@
         <v>0.1815</v>
       </c>
       <c r="M301">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N301" t="s">
         <v>74</v>
@@ -13881,7 +13881,7 @@
         <v>0.6006</v>
       </c>
       <c r="M302">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N302" t="s">
         <v>74</v>
@@ -13907,25 +13907,25 @@
         <v>59</v>
       </c>
       <c r="G303">
-        <v>0.6639</v>
+        <v>0.6802</v>
       </c>
       <c r="H303">
-        <v>0.4986</v>
+        <v>0.5092</v>
       </c>
       <c r="I303">
-        <v>0.5812</v>
+        <v>0.5947</v>
       </c>
       <c r="J303">
-        <v>0.3361</v>
+        <v>0.3198</v>
       </c>
       <c r="K303">
-        <v>0.5014</v>
+        <v>0.4908</v>
       </c>
       <c r="L303">
-        <v>0.4188</v>
+        <v>0.4053</v>
       </c>
       <c r="M303">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N303" t="s">
         <v>74</v>
@@ -13969,7 +13969,7 @@
         <v>0.2468</v>
       </c>
       <c r="M304">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N304" t="s">
         <v>74</v>
@@ -14013,7 +14013,7 @@
         <v>0.4006</v>
       </c>
       <c r="M305">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N305" t="s">
         <v>74</v>
@@ -14039,25 +14039,25 @@
         <v>62</v>
       </c>
       <c r="G306">
-        <v>0.6709000000000001</v>
+        <v>0.6893</v>
       </c>
       <c r="H306">
-        <v>0.5095</v>
+        <v>0.5272</v>
       </c>
       <c r="I306">
-        <v>0.5901999999999999</v>
+        <v>0.6082</v>
       </c>
       <c r="J306">
-        <v>0.3291</v>
+        <v>0.3107</v>
       </c>
       <c r="K306">
-        <v>0.4905</v>
+        <v>0.4728</v>
       </c>
       <c r="L306">
-        <v>0.4098</v>
+        <v>0.3918</v>
       </c>
       <c r="M306">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N306" t="s">
         <v>74</v>
@@ -14101,7 +14101,7 @@
         <v>0.3948</v>
       </c>
       <c r="M307">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N307" t="s">
         <v>74</v>
@@ -14130,22 +14130,22 @@
         <v>0.8554</v>
       </c>
       <c r="H308">
-        <v>0.7314000000000001</v>
+        <v>0.742</v>
       </c>
       <c r="I308">
-        <v>0.7934</v>
+        <v>0.7987</v>
       </c>
       <c r="J308">
         <v>0.1446</v>
       </c>
       <c r="K308">
-        <v>0.2686</v>
+        <v>0.258</v>
       </c>
       <c r="L308">
-        <v>0.2066</v>
+        <v>0.2013</v>
       </c>
       <c r="M308">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N308" t="s">
         <v>74</v>
@@ -14189,7 +14189,7 @@
         <v>0.6544</v>
       </c>
       <c r="M309">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N309" t="s">
         <v>74</v>
@@ -14215,25 +14215,25 @@
         <v>66</v>
       </c>
       <c r="G310">
-        <v>0.3702</v>
+        <v>0.3692</v>
       </c>
       <c r="H310">
-        <v>0.2239</v>
+        <v>0.2184</v>
       </c>
       <c r="I310">
-        <v>0.297</v>
+        <v>0.2938</v>
       </c>
       <c r="J310">
-        <v>0.6298</v>
+        <v>0.6308</v>
       </c>
       <c r="K310">
-        <v>0.7761</v>
+        <v>0.7816</v>
       </c>
       <c r="L310">
-        <v>0.703</v>
+        <v>0.7062</v>
       </c>
       <c r="M310">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N310" t="s">
         <v>74</v>
@@ -14277,7 +14277,7 @@
         <v>0.4692</v>
       </c>
       <c r="M311">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N311" t="s">
         <v>74</v>
@@ -14321,7 +14321,7 @@
         <v>0.2226</v>
       </c>
       <c r="M312">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N312" t="s">
         <v>74</v>
@@ -14350,22 +14350,22 @@
         <v>0.8532</v>
       </c>
       <c r="H313">
-        <v>0.7201</v>
+        <v>0.7228</v>
       </c>
       <c r="I313">
-        <v>0.7866</v>
+        <v>0.788</v>
       </c>
       <c r="J313">
         <v>0.1468</v>
       </c>
       <c r="K313">
-        <v>0.2799</v>
+        <v>0.2772</v>
       </c>
       <c r="L313">
-        <v>0.2134</v>
+        <v>0.212</v>
       </c>
       <c r="M313">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N313" t="s">
         <v>74</v>
@@ -14409,7 +14409,7 @@
         <v>0.1968</v>
       </c>
       <c r="M314">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N314" t="s">
         <v>74</v>
@@ -14435,25 +14435,25 @@
         <v>71</v>
       </c>
       <c r="G315">
-        <v>0.4795</v>
+        <v>0.4822</v>
       </c>
       <c r="H315">
-        <v>0.3288</v>
+        <v>0.3293</v>
       </c>
       <c r="I315">
-        <v>0.4042</v>
+        <v>0.4058</v>
       </c>
       <c r="J315">
-        <v>0.5205</v>
+        <v>0.5178</v>
       </c>
       <c r="K315">
-        <v>0.6712</v>
+        <v>0.6707</v>
       </c>
       <c r="L315">
-        <v>0.5958</v>
+        <v>0.5942</v>
       </c>
       <c r="M315">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N315" t="s">
         <v>74</v>
@@ -14497,7 +14497,7 @@
         <v>0.5016</v>
       </c>
       <c r="M316">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N316" t="s">
         <v>74</v>
@@ -14541,7 +14541,7 @@
         <v>0.8438</v>
       </c>
       <c r="M317">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N317" t="s">
         <v>74</v>
@@ -14567,25 +14567,25 @@
         <v>59</v>
       </c>
       <c r="G318">
-        <v>0.2775</v>
+        <v>0.2776</v>
       </c>
       <c r="H318">
-        <v>0.1423</v>
+        <v>0.1501</v>
       </c>
       <c r="I318">
-        <v>0.2099</v>
+        <v>0.2138</v>
       </c>
       <c r="J318">
-        <v>0.7225</v>
+        <v>0.7224</v>
       </c>
       <c r="K318">
-        <v>0.8577</v>
+        <v>0.8499</v>
       </c>
       <c r="L318">
-        <v>0.7901</v>
+        <v>0.7862</v>
       </c>
       <c r="M318">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N318" t="s">
         <v>74</v>
@@ -14629,7 +14629,7 @@
         <v>0.6422</v>
       </c>
       <c r="M319">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N319" t="s">
         <v>74</v>
@@ -14673,7 +14673,7 @@
         <v>0.7798</v>
       </c>
       <c r="M320">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N320" t="s">
         <v>74</v>
@@ -14699,25 +14699,25 @@
         <v>62</v>
       </c>
       <c r="G321">
-        <v>0.2612</v>
+        <v>0.2751</v>
       </c>
       <c r="H321">
-        <v>0.1629</v>
+        <v>0.1607</v>
       </c>
       <c r="I321">
-        <v>0.212</v>
+        <v>0.2179</v>
       </c>
       <c r="J321">
-        <v>0.7388</v>
+        <v>0.7249</v>
       </c>
       <c r="K321">
-        <v>0.8371</v>
+        <v>0.8393</v>
       </c>
       <c r="L321">
-        <v>0.788</v>
+        <v>0.7821</v>
       </c>
       <c r="M321">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N321" t="s">
         <v>74</v>
@@ -14761,7 +14761,7 @@
         <v>0.7845</v>
       </c>
       <c r="M322">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N322" t="s">
         <v>74</v>
@@ -14805,7 +14805,7 @@
         <v>0.5343</v>
       </c>
       <c r="M323">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N323" t="s">
         <v>74</v>
@@ -14849,7 +14849,7 @@
         <v>0.8403</v>
       </c>
       <c r="M324">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N324" t="s">
         <v>74</v>
@@ -14893,7 +14893,7 @@
         <v>0.8426</v>
       </c>
       <c r="M325">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N325" t="s">
         <v>74</v>
@@ -14937,7 +14937,7 @@
         <v>0.8092</v>
       </c>
       <c r="M326">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N326" t="s">
         <v>74</v>
@@ -14981,7 +14981,7 @@
         <v>0.58</v>
       </c>
       <c r="M327">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N327" t="s">
         <v>74</v>
@@ -15025,7 +15025,7 @@
         <v>0.5938</v>
       </c>
       <c r="M328">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N328" t="s">
         <v>74</v>
@@ -15069,7 +15069,7 @@
         <v>0.4856</v>
       </c>
       <c r="M329">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N329" t="s">
         <v>74</v>
@@ -15095,25 +15095,25 @@
         <v>71</v>
       </c>
       <c r="G330">
-        <v>0.2156</v>
+        <v>0.2194</v>
       </c>
       <c r="H330">
-        <v>0.1193</v>
+        <v>0.1172</v>
       </c>
       <c r="I330">
-        <v>0.1675</v>
+        <v>0.1683</v>
       </c>
       <c r="J330">
-        <v>0.7844</v>
+        <v>0.7806</v>
       </c>
       <c r="K330">
-        <v>0.8807</v>
+        <v>0.8828</v>
       </c>
       <c r="L330">
-        <v>0.8325</v>
+        <v>0.8317</v>
       </c>
       <c r="M330">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N330" t="s">
         <v>74</v>
@@ -15142,22 +15142,22 @@
         <v>0.2311</v>
       </c>
       <c r="H331">
-        <v>0.1312</v>
+        <v>0.1295</v>
       </c>
       <c r="I331">
-        <v>0.1812</v>
+        <v>0.1803</v>
       </c>
       <c r="J331">
         <v>0.7689</v>
       </c>
       <c r="K331">
-        <v>0.8688</v>
+        <v>0.8705000000000001</v>
       </c>
       <c r="L331">
-        <v>0.8188</v>
+        <v>0.8197</v>
       </c>
       <c r="M331">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N331" t="s">
         <v>74</v>
@@ -15183,25 +15183,25 @@
         <v>59</v>
       </c>
       <c r="G332">
-        <v>0.7773</v>
+        <v>0.7745</v>
       </c>
       <c r="H332">
-        <v>0.5722</v>
+        <v>0.5888</v>
       </c>
       <c r="I332">
-        <v>0.6748</v>
+        <v>0.6816</v>
       </c>
       <c r="J332">
-        <v>0.2227</v>
+        <v>0.2255</v>
       </c>
       <c r="K332">
-        <v>0.4278</v>
+        <v>0.4112</v>
       </c>
       <c r="L332">
-        <v>0.3252</v>
+        <v>0.3184</v>
       </c>
       <c r="M332">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N332" t="s">
         <v>74</v>
@@ -15245,7 +15245,7 @@
         <v>0.203</v>
       </c>
       <c r="M333">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N333" t="s">
         <v>74</v>
@@ -15271,25 +15271,25 @@
         <v>61</v>
       </c>
       <c r="G334">
-        <v>0.7604</v>
+        <v>0.7614</v>
       </c>
       <c r="H334">
         <v>0.6439</v>
       </c>
       <c r="I334">
-        <v>0.7022</v>
+        <v>0.7026</v>
       </c>
       <c r="J334">
-        <v>0.2396</v>
+        <v>0.2386</v>
       </c>
       <c r="K334">
         <v>0.3561</v>
       </c>
       <c r="L334">
-        <v>0.2978</v>
+        <v>0.2974</v>
       </c>
       <c r="M334">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N334" t="s">
         <v>74</v>
@@ -15315,25 +15315,25 @@
         <v>62</v>
       </c>
       <c r="G335">
-        <v>0.7649</v>
+        <v>0.7776</v>
       </c>
       <c r="H335">
-        <v>0.598</v>
+        <v>0.6044</v>
       </c>
       <c r="I335">
-        <v>0.6814</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="J335">
-        <v>0.2351</v>
+        <v>0.2224</v>
       </c>
       <c r="K335">
-        <v>0.402</v>
+        <v>0.3956</v>
       </c>
       <c r="L335">
-        <v>0.3186</v>
+        <v>0.309</v>
       </c>
       <c r="M335">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N335" t="s">
         <v>74</v>
@@ -15377,7 +15377,7 @@
         <v>0.3072</v>
       </c>
       <c r="M336">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N336" t="s">
         <v>74</v>
@@ -15421,7 +15421,7 @@
         <v>0.167</v>
       </c>
       <c r="M337">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N337" t="s">
         <v>74</v>
@@ -15465,7 +15465,7 @@
         <v>0.5554</v>
       </c>
       <c r="M338">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N338" t="s">
         <v>74</v>
@@ -15491,25 +15491,25 @@
         <v>66</v>
       </c>
       <c r="G339">
-        <v>0.4426</v>
+        <v>0.4547</v>
       </c>
       <c r="H339">
-        <v>0.3436</v>
+        <v>0.3242</v>
       </c>
       <c r="I339">
-        <v>0.3931</v>
+        <v>0.3894</v>
       </c>
       <c r="J339">
-        <v>0.5574</v>
+        <v>0.5453</v>
       </c>
       <c r="K339">
-        <v>0.6564</v>
+        <v>0.6758</v>
       </c>
       <c r="L339">
-        <v>0.6069</v>
+        <v>0.6106</v>
       </c>
       <c r="M339">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N339" t="s">
         <v>74</v>
@@ -15535,25 +15535,25 @@
         <v>67</v>
       </c>
       <c r="G340">
-        <v>0.7095</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="H340">
-        <v>0.5447</v>
+        <v>0.5455</v>
       </c>
       <c r="I340">
-        <v>0.6271</v>
+        <v>0.6284</v>
       </c>
       <c r="J340">
-        <v>0.2905</v>
+        <v>0.2888</v>
       </c>
       <c r="K340">
-        <v>0.4553</v>
+        <v>0.4545</v>
       </c>
       <c r="L340">
-        <v>0.3729</v>
+        <v>0.3716</v>
       </c>
       <c r="M340">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N340" t="s">
         <v>74</v>
@@ -15597,7 +15597,7 @@
         <v>0.1763</v>
       </c>
       <c r="M341">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N341" t="s">
         <v>74</v>
@@ -15641,7 +15641,7 @@
         <v>0.1704</v>
       </c>
       <c r="M342">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N342" t="s">
         <v>74</v>
@@ -15685,7 +15685,7 @@
         <v>0.1674</v>
       </c>
       <c r="M343">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N343" t="s">
         <v>74</v>
@@ -15711,25 +15711,25 @@
         <v>71</v>
       </c>
       <c r="G344">
-        <v>0.5693</v>
+        <v>0.5697</v>
       </c>
       <c r="H344">
-        <v>0.391</v>
+        <v>0.405</v>
       </c>
       <c r="I344">
-        <v>0.4802</v>
+        <v>0.4874</v>
       </c>
       <c r="J344">
-        <v>0.4307</v>
+        <v>0.4303</v>
       </c>
       <c r="K344">
-        <v>0.609</v>
+        <v>0.595</v>
       </c>
       <c r="L344">
-        <v>0.5198</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="M344">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N344" t="s">
         <v>74</v>
@@ -15773,7 +15773,7 @@
         <v>0.3962</v>
       </c>
       <c r="M345">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N345" t="s">
         <v>74</v>
@@ -15799,25 +15799,25 @@
         <v>60</v>
       </c>
       <c r="G346">
-        <v>0.7725</v>
+        <v>0.7759</v>
       </c>
       <c r="H346">
-        <v>0.6306</v>
+        <v>0.6281</v>
       </c>
       <c r="I346">
-        <v>0.7016</v>
+        <v>0.702</v>
       </c>
       <c r="J346">
-        <v>0.2275</v>
+        <v>0.2241</v>
       </c>
       <c r="K346">
-        <v>0.3694</v>
+        <v>0.3719</v>
       </c>
       <c r="L346">
-        <v>0.2984</v>
+        <v>0.298</v>
       </c>
       <c r="M346">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N346" t="s">
         <v>74</v>
@@ -15843,25 +15843,25 @@
         <v>61</v>
       </c>
       <c r="G347">
-        <v>0.6014</v>
+        <v>0.6136</v>
       </c>
       <c r="H347">
-        <v>0.4871</v>
+        <v>0.4811</v>
       </c>
       <c r="I347">
-        <v>0.5442</v>
+        <v>0.5474</v>
       </c>
       <c r="J347">
-        <v>0.3986</v>
+        <v>0.3864</v>
       </c>
       <c r="K347">
-        <v>0.5129</v>
+        <v>0.5189</v>
       </c>
       <c r="L347">
-        <v>0.4558</v>
+        <v>0.4526</v>
       </c>
       <c r="M347">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N347" t="s">
         <v>74</v>
@@ -15887,25 +15887,25 @@
         <v>62</v>
       </c>
       <c r="G348">
-        <v>0.5712</v>
+        <v>0.5897</v>
       </c>
       <c r="H348">
-        <v>0.4771</v>
+        <v>0.475</v>
       </c>
       <c r="I348">
-        <v>0.5242</v>
+        <v>0.5324</v>
       </c>
       <c r="J348">
-        <v>0.4288</v>
+        <v>0.4103</v>
       </c>
       <c r="K348">
-        <v>0.5229</v>
+        <v>0.525</v>
       </c>
       <c r="L348">
-        <v>0.4758</v>
+        <v>0.4676</v>
       </c>
       <c r="M348">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N348" t="s">
         <v>74</v>
@@ -15931,25 +15931,25 @@
         <v>63</v>
       </c>
       <c r="G349">
-        <v>0.5911</v>
+        <v>0.5955</v>
       </c>
       <c r="H349">
-        <v>0.4776</v>
+        <v>0.4729</v>
       </c>
       <c r="I349">
-        <v>0.5344</v>
+        <v>0.5342</v>
       </c>
       <c r="J349">
-        <v>0.4089</v>
+        <v>0.4045</v>
       </c>
       <c r="K349">
-        <v>0.5224</v>
+        <v>0.5271</v>
       </c>
       <c r="L349">
-        <v>0.4656</v>
+        <v>0.4658</v>
       </c>
       <c r="M349">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N349" t="s">
         <v>74</v>
@@ -15975,25 +15975,25 @@
         <v>64</v>
       </c>
       <c r="G350">
-        <v>0.8282</v>
+        <v>0.8259</v>
       </c>
       <c r="H350">
-        <v>0.6892</v>
+        <v>0.6952</v>
       </c>
       <c r="I350">
-        <v>0.7587</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="J350">
-        <v>0.1718</v>
+        <v>0.1741</v>
       </c>
       <c r="K350">
-        <v>0.3108</v>
+        <v>0.3048</v>
       </c>
       <c r="L350">
-        <v>0.2413</v>
+        <v>0.2394</v>
       </c>
       <c r="M350">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N350" t="s">
         <v>74</v>
@@ -16019,25 +16019,25 @@
         <v>65</v>
       </c>
       <c r="G351">
-        <v>0.3513</v>
+        <v>0.3342</v>
       </c>
       <c r="H351">
-        <v>0.2159</v>
+        <v>0.222</v>
       </c>
       <c r="I351">
-        <v>0.2836</v>
+        <v>0.2781</v>
       </c>
       <c r="J351">
-        <v>0.6487000000000001</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="K351">
-        <v>0.7841</v>
+        <v>0.778</v>
       </c>
       <c r="L351">
-        <v>0.7164</v>
+        <v>0.7219</v>
       </c>
       <c r="M351">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N351" t="s">
         <v>74</v>
@@ -16063,25 +16063,25 @@
         <v>66</v>
       </c>
       <c r="G352">
-        <v>0.3035</v>
+        <v>0.2924</v>
       </c>
       <c r="H352">
-        <v>0.1886</v>
+        <v>0.1859</v>
       </c>
       <c r="I352">
-        <v>0.246</v>
+        <v>0.2392</v>
       </c>
       <c r="J352">
-        <v>0.6965</v>
+        <v>0.7076</v>
       </c>
       <c r="K352">
-        <v>0.8114</v>
+        <v>0.8141</v>
       </c>
       <c r="L352">
-        <v>0.754</v>
+        <v>0.7608</v>
       </c>
       <c r="M352">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N352" t="s">
         <v>74</v>
@@ -16107,25 +16107,25 @@
         <v>67</v>
       </c>
       <c r="G353">
-        <v>0.5323</v>
+        <v>0.5201</v>
       </c>
       <c r="H353">
-        <v>0.4045</v>
+        <v>0.3766</v>
       </c>
       <c r="I353">
-        <v>0.4684</v>
+        <v>0.4484</v>
       </c>
       <c r="J353">
-        <v>0.4677</v>
+        <v>0.4799</v>
       </c>
       <c r="K353">
-        <v>0.5955</v>
+        <v>0.6234</v>
       </c>
       <c r="L353">
-        <v>0.5316</v>
+        <v>0.5516</v>
       </c>
       <c r="M353">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N353" t="s">
         <v>74</v>
@@ -16151,25 +16151,25 @@
         <v>68</v>
       </c>
       <c r="G354">
-        <v>0.7989000000000001</v>
+        <v>0.7956</v>
       </c>
       <c r="H354">
-        <v>0.6614</v>
+        <v>0.6532</v>
       </c>
       <c r="I354">
-        <v>0.7302</v>
+        <v>0.7244</v>
       </c>
       <c r="J354">
-        <v>0.2011</v>
+        <v>0.2044</v>
       </c>
       <c r="K354">
-        <v>0.3386</v>
+        <v>0.3468</v>
       </c>
       <c r="L354">
-        <v>0.2698</v>
+        <v>0.2756</v>
       </c>
       <c r="M354">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N354" t="s">
         <v>74</v>
@@ -16195,25 +16195,25 @@
         <v>69</v>
       </c>
       <c r="G355">
-        <v>0.8147</v>
+        <v>0.8068</v>
       </c>
       <c r="H355">
-        <v>0.6459</v>
+        <v>0.6585</v>
       </c>
       <c r="I355">
-        <v>0.7302999999999999</v>
+        <v>0.7326</v>
       </c>
       <c r="J355">
-        <v>0.1853</v>
+        <v>0.1932</v>
       </c>
       <c r="K355">
-        <v>0.3541</v>
+        <v>0.3415</v>
       </c>
       <c r="L355">
-        <v>0.2697</v>
+        <v>0.2674</v>
       </c>
       <c r="M355">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N355" t="s">
         <v>74</v>
@@ -16239,25 +16239,25 @@
         <v>70</v>
       </c>
       <c r="G356">
-        <v>0.8213</v>
+        <v>0.8279</v>
       </c>
       <c r="H356">
-        <v>0.711</v>
+        <v>0.7093</v>
       </c>
       <c r="I356">
-        <v>0.7662</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="J356">
-        <v>0.1787</v>
+        <v>0.1721</v>
       </c>
       <c r="K356">
-        <v>0.289</v>
+        <v>0.2907</v>
       </c>
       <c r="L356">
-        <v>0.2338</v>
+        <v>0.2314</v>
       </c>
       <c r="M356">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N356" t="s">
         <v>74</v>
@@ -16283,25 +16283,25 @@
         <v>71</v>
       </c>
       <c r="G357">
-        <v>0.3871</v>
+        <v>0.3961</v>
       </c>
       <c r="H357">
-        <v>0.2475</v>
+        <v>0.2468</v>
       </c>
       <c r="I357">
-        <v>0.3173</v>
+        <v>0.3214</v>
       </c>
       <c r="J357">
-        <v>0.6129</v>
+        <v>0.6039</v>
       </c>
       <c r="K357">
-        <v>0.7524999999999999</v>
+        <v>0.7532</v>
       </c>
       <c r="L357">
-        <v>0.6827</v>
+        <v>0.6786</v>
       </c>
       <c r="M357">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N357" t="s">
         <v>74</v>
@@ -16327,25 +16327,25 @@
         <v>73</v>
       </c>
       <c r="G358">
-        <v>0.5075</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="H358">
-        <v>0.3229</v>
+        <v>0.3242</v>
       </c>
       <c r="I358">
-        <v>0.4152</v>
+        <v>0.4174</v>
       </c>
       <c r="J358">
-        <v>0.4925</v>
+        <v>0.4894</v>
       </c>
       <c r="K358">
-        <v>0.6771</v>
+        <v>0.6758</v>
       </c>
       <c r="L358">
-        <v>0.5848</v>
+        <v>0.5826</v>
       </c>
       <c r="M358">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N358" t="s">
         <v>74</v>
@@ -16374,22 +16374,22 @@
         <v>0.4033</v>
       </c>
       <c r="H359">
-        <v>0.2374</v>
+        <v>0.2348</v>
       </c>
       <c r="I359">
-        <v>0.3204</v>
+        <v>0.319</v>
       </c>
       <c r="J359">
         <v>0.5967</v>
       </c>
       <c r="K359">
-        <v>0.7625999999999999</v>
+        <v>0.7652</v>
       </c>
       <c r="L359">
-        <v>0.6796</v>
+        <v>0.681</v>
       </c>
       <c r="M359">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N359" t="s">
         <v>74</v>
@@ -16415,25 +16415,25 @@
         <v>62</v>
       </c>
       <c r="G360">
-        <v>0.3947</v>
+        <v>0.3851</v>
       </c>
       <c r="H360">
-        <v>0.2232</v>
+        <v>0.2196</v>
       </c>
       <c r="I360">
-        <v>0.309</v>
+        <v>0.3024</v>
       </c>
       <c r="J360">
-        <v>0.6052999999999999</v>
+        <v>0.6149</v>
       </c>
       <c r="K360">
-        <v>0.7768</v>
+        <v>0.7804</v>
       </c>
       <c r="L360">
-        <v>0.6909999999999999</v>
+        <v>0.6976</v>
       </c>
       <c r="M360">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N360" t="s">
         <v>74</v>
@@ -16477,7 +16477,7 @@
         <v>0.6902</v>
       </c>
       <c r="M361">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N361" t="s">
         <v>74</v>
@@ -16521,7 +16521,7 @@
         <v>0.4004</v>
       </c>
       <c r="M362">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N362" t="s">
         <v>74</v>
@@ -16565,7 +16565,7 @@
         <v>0.8013</v>
       </c>
       <c r="M363">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N363" t="s">
         <v>74</v>
@@ -16591,25 +16591,25 @@
         <v>66</v>
       </c>
       <c r="G364">
-        <v>0.228</v>
+        <v>0.2326</v>
       </c>
       <c r="H364">
-        <v>0.1343</v>
+        <v>0.1296</v>
       </c>
       <c r="I364">
-        <v>0.1812</v>
+        <v>0.1811</v>
       </c>
       <c r="J364">
-        <v>0.772</v>
+        <v>0.7674</v>
       </c>
       <c r="K364">
-        <v>0.8657</v>
+        <v>0.8704</v>
       </c>
       <c r="L364">
-        <v>0.8188</v>
+        <v>0.8189</v>
       </c>
       <c r="M364">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N364" t="s">
         <v>74</v>
@@ -16638,22 +16638,22 @@
         <v>0.3287</v>
       </c>
       <c r="H365">
-        <v>0.2004</v>
+        <v>0.1993</v>
       </c>
       <c r="I365">
-        <v>0.2646</v>
+        <v>0.264</v>
       </c>
       <c r="J365">
         <v>0.6713</v>
       </c>
       <c r="K365">
-        <v>0.7996</v>
+        <v>0.8007</v>
       </c>
       <c r="L365">
-        <v>0.7354000000000001</v>
+        <v>0.736</v>
       </c>
       <c r="M365">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N365" t="s">
         <v>74</v>
@@ -16697,7 +16697,7 @@
         <v>0.4296</v>
       </c>
       <c r="M366">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N366" t="s">
         <v>74</v>
@@ -16741,7 +16741,7 @@
         <v>0.4522</v>
       </c>
       <c r="M367">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N367" t="s">
         <v>74</v>
@@ -16785,7 +16785,7 @@
         <v>0.3717</v>
       </c>
       <c r="M368">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N368" t="s">
         <v>74</v>
@@ -16811,25 +16811,25 @@
         <v>71</v>
       </c>
       <c r="G369">
-        <v>0.245</v>
+        <v>0.2469</v>
       </c>
       <c r="H369">
-        <v>0.1644</v>
+        <v>0.1666</v>
       </c>
       <c r="I369">
-        <v>0.2047</v>
+        <v>0.2068</v>
       </c>
       <c r="J369">
-        <v>0.755</v>
+        <v>0.7531</v>
       </c>
       <c r="K369">
-        <v>0.8356</v>
+        <v>0.8334</v>
       </c>
       <c r="L369">
-        <v>0.7953</v>
+        <v>0.7932</v>
       </c>
       <c r="M369">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N369" t="s">
         <v>74</v>
@@ -16873,7 +16873,7 @@
         <v>0.7413</v>
       </c>
       <c r="M370">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N370" t="s">
         <v>74</v>
@@ -16899,25 +16899,25 @@
         <v>62</v>
       </c>
       <c r="G371">
-        <v>0.5272</v>
+        <v>0.5455</v>
       </c>
       <c r="H371">
-        <v>0.4242</v>
+        <v>0.435</v>
       </c>
       <c r="I371">
-        <v>0.4757</v>
+        <v>0.4902</v>
       </c>
       <c r="J371">
-        <v>0.4728</v>
+        <v>0.4545</v>
       </c>
       <c r="K371">
-        <v>0.5758</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="L371">
-        <v>0.5243</v>
+        <v>0.5098</v>
       </c>
       <c r="M371">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N371" t="s">
         <v>74</v>
@@ -16961,7 +16961,7 @@
         <v>0.5148</v>
       </c>
       <c r="M372">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N372" t="s">
         <v>74</v>
@@ -17005,7 +17005,7 @@
         <v>0.2417</v>
       </c>
       <c r="M373">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N373" t="s">
         <v>74</v>
@@ -17034,22 +17034,22 @@
         <v>0.3249</v>
       </c>
       <c r="H374">
-        <v>0.2064</v>
+        <v>0.2043</v>
       </c>
       <c r="I374">
-        <v>0.2656</v>
+        <v>0.2646</v>
       </c>
       <c r="J374">
         <v>0.6751</v>
       </c>
       <c r="K374">
-        <v>0.7936</v>
+        <v>0.7957</v>
       </c>
       <c r="L374">
-        <v>0.7344000000000001</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="M374">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N374" t="s">
         <v>74</v>
@@ -17075,25 +17075,25 @@
         <v>66</v>
       </c>
       <c r="G375">
-        <v>0.2832</v>
+        <v>0.2751</v>
       </c>
       <c r="H375">
-        <v>0.1713</v>
+        <v>0.169</v>
       </c>
       <c r="I375">
-        <v>0.2272</v>
+        <v>0.2221</v>
       </c>
       <c r="J375">
-        <v>0.7168</v>
+        <v>0.7249</v>
       </c>
       <c r="K375">
-        <v>0.8287</v>
+        <v>0.831</v>
       </c>
       <c r="L375">
-        <v>0.7728</v>
+        <v>0.7779</v>
       </c>
       <c r="M375">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N375" t="s">
         <v>74</v>
@@ -17122,22 +17122,22 @@
         <v>0.4736</v>
       </c>
       <c r="H376">
-        <v>0.3881</v>
+        <v>0.3895</v>
       </c>
       <c r="I376">
-        <v>0.4308</v>
+        <v>0.4316</v>
       </c>
       <c r="J376">
         <v>0.5264</v>
       </c>
       <c r="K376">
-        <v>0.6119</v>
+        <v>0.6105</v>
       </c>
       <c r="L376">
-        <v>0.5692</v>
+        <v>0.5684</v>
       </c>
       <c r="M376">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N376" t="s">
         <v>74</v>
@@ -17163,25 +17163,25 @@
         <v>68</v>
       </c>
       <c r="G377">
-        <v>0.7951</v>
+        <v>0.7966</v>
       </c>
       <c r="H377">
-        <v>0.6514</v>
+        <v>0.6515</v>
       </c>
       <c r="I377">
-        <v>0.7232</v>
+        <v>0.724</v>
       </c>
       <c r="J377">
-        <v>0.2049</v>
+        <v>0.2034</v>
       </c>
       <c r="K377">
-        <v>0.3486</v>
+        <v>0.3485</v>
       </c>
       <c r="L377">
-        <v>0.2768</v>
+        <v>0.276</v>
       </c>
       <c r="M377">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N377" t="s">
         <v>74</v>
@@ -17210,22 +17210,22 @@
         <v>0.8074</v>
       </c>
       <c r="H378">
-        <v>0.6278</v>
+        <v>0.6317</v>
       </c>
       <c r="I378">
-        <v>0.7176</v>
+        <v>0.7196</v>
       </c>
       <c r="J378">
         <v>0.1926</v>
       </c>
       <c r="K378">
-        <v>0.3722</v>
+        <v>0.3683</v>
       </c>
       <c r="L378">
-        <v>0.2824</v>
+        <v>0.2804</v>
       </c>
       <c r="M378">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N378" t="s">
         <v>74</v>
@@ -17269,7 +17269,7 @@
         <v>0.227</v>
       </c>
       <c r="M379">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N379" t="s">
         <v>74</v>
@@ -17295,25 +17295,25 @@
         <v>71</v>
       </c>
       <c r="G380">
-        <v>0.3659</v>
+        <v>0.3686</v>
       </c>
       <c r="H380">
-        <v>0.2324</v>
+        <v>0.2347</v>
       </c>
       <c r="I380">
-        <v>0.2992</v>
+        <v>0.3016</v>
       </c>
       <c r="J380">
-        <v>0.6341</v>
+        <v>0.6314</v>
       </c>
       <c r="K380">
-        <v>0.7675999999999999</v>
+        <v>0.7653</v>
       </c>
       <c r="L380">
-        <v>0.7008</v>
+        <v>0.6984</v>
       </c>
       <c r="M380">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N380" t="s">
         <v>74</v>
@@ -17342,22 +17342,22 @@
         <v>0.4737</v>
       </c>
       <c r="H381">
-        <v>0.3226</v>
+        <v>0.3219</v>
       </c>
       <c r="I381">
-        <v>0.3982</v>
+        <v>0.3978</v>
       </c>
       <c r="J381">
         <v>0.5263</v>
       </c>
       <c r="K381">
-        <v>0.6774</v>
+        <v>0.6781</v>
       </c>
       <c r="L381">
-        <v>0.6018</v>
+        <v>0.6022</v>
       </c>
       <c r="M381">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N381" t="s">
         <v>74</v>
@@ -17383,25 +17383,25 @@
         <v>63</v>
       </c>
       <c r="G382">
-        <v>0.5626</v>
+        <v>0.5508</v>
       </c>
       <c r="H382">
-        <v>0.4359</v>
+        <v>0.4189</v>
       </c>
       <c r="I382">
-        <v>0.4992</v>
+        <v>0.4848</v>
       </c>
       <c r="J382">
-        <v>0.4374</v>
+        <v>0.4492</v>
       </c>
       <c r="K382">
-        <v>0.5641</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="L382">
-        <v>0.5008</v>
+        <v>0.5152</v>
       </c>
       <c r="M382">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N382" t="s">
         <v>74</v>
@@ -17427,25 +17427,25 @@
         <v>64</v>
       </c>
       <c r="G383">
-        <v>0.8159999999999999</v>
+        <v>0.8173</v>
       </c>
       <c r="H383">
-        <v>0.7000999999999999</v>
+        <v>0.6996</v>
       </c>
       <c r="I383">
-        <v>0.758</v>
+        <v>0.7585</v>
       </c>
       <c r="J383">
-        <v>0.184</v>
+        <v>0.1827</v>
       </c>
       <c r="K383">
-        <v>0.2999</v>
+        <v>0.3004</v>
       </c>
       <c r="L383">
-        <v>0.242</v>
+        <v>0.2415</v>
       </c>
       <c r="M383">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N383" t="s">
         <v>74</v>
@@ -17471,25 +17471,25 @@
         <v>65</v>
       </c>
       <c r="G384">
-        <v>0.3436</v>
+        <v>0.3394</v>
       </c>
       <c r="H384">
-        <v>0.2055</v>
+        <v>0.1815</v>
       </c>
       <c r="I384">
-        <v>0.2746</v>
+        <v>0.2604</v>
       </c>
       <c r="J384">
-        <v>0.6564</v>
+        <v>0.6606</v>
       </c>
       <c r="K384">
-        <v>0.7945</v>
+        <v>0.8185</v>
       </c>
       <c r="L384">
-        <v>0.7254</v>
+        <v>0.7396</v>
       </c>
       <c r="M384">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N384" t="s">
         <v>74</v>
@@ -17515,25 +17515,25 @@
         <v>66</v>
       </c>
       <c r="G385">
-        <v>0.3115</v>
+        <v>0.2992</v>
       </c>
       <c r="H385">
-        <v>0.1683</v>
+        <v>0.1623</v>
       </c>
       <c r="I385">
-        <v>0.2399</v>
+        <v>0.2308</v>
       </c>
       <c r="J385">
-        <v>0.6885</v>
+        <v>0.7008</v>
       </c>
       <c r="K385">
-        <v>0.8317</v>
+        <v>0.8377</v>
       </c>
       <c r="L385">
-        <v>0.7601</v>
+        <v>0.7692</v>
       </c>
       <c r="M385">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N385" t="s">
         <v>74</v>
@@ -17559,25 +17559,25 @@
         <v>67</v>
       </c>
       <c r="G386">
-        <v>0.5191</v>
+        <v>0.5046</v>
       </c>
       <c r="H386">
-        <v>0.3794</v>
+        <v>0.3667</v>
       </c>
       <c r="I386">
-        <v>0.4492</v>
+        <v>0.4356</v>
       </c>
       <c r="J386">
-        <v>0.4809</v>
+        <v>0.4954</v>
       </c>
       <c r="K386">
-        <v>0.6206</v>
+        <v>0.6333</v>
       </c>
       <c r="L386">
-        <v>0.5508</v>
+        <v>0.5644</v>
       </c>
       <c r="M386">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N386" t="s">
         <v>74</v>
@@ -17603,25 +17603,25 @@
         <v>68</v>
       </c>
       <c r="G387">
-        <v>0.804</v>
+        <v>0.796</v>
       </c>
       <c r="H387">
-        <v>0.6664</v>
+        <v>0.6624</v>
       </c>
       <c r="I387">
-        <v>0.7352</v>
+        <v>0.7292</v>
       </c>
       <c r="J387">
-        <v>0.196</v>
+        <v>0.204</v>
       </c>
       <c r="K387">
-        <v>0.3336</v>
+        <v>0.3376</v>
       </c>
       <c r="L387">
-        <v>0.2648</v>
+        <v>0.2708</v>
       </c>
       <c r="M387">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N387" t="s">
         <v>74</v>
@@ -17647,25 +17647,25 @@
         <v>69</v>
       </c>
       <c r="G388">
-        <v>0.8292</v>
+        <v>0.8173</v>
       </c>
       <c r="H388">
-        <v>0.6483</v>
+        <v>0.6486</v>
       </c>
       <c r="I388">
-        <v>0.7388</v>
+        <v>0.733</v>
       </c>
       <c r="J388">
-        <v>0.1708</v>
+        <v>0.1827</v>
       </c>
       <c r="K388">
-        <v>0.3517</v>
+        <v>0.3514</v>
       </c>
       <c r="L388">
-        <v>0.2612</v>
+        <v>0.267</v>
       </c>
       <c r="M388">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N388" t="s">
         <v>74</v>
@@ -17691,25 +17691,25 @@
         <v>70</v>
       </c>
       <c r="G389">
-        <v>0.8351</v>
+        <v>0.8355</v>
       </c>
       <c r="H389">
-        <v>0.7167</v>
+        <v>0.7157</v>
       </c>
       <c r="I389">
-        <v>0.7759</v>
+        <v>0.7756</v>
       </c>
       <c r="J389">
-        <v>0.1649</v>
+        <v>0.1645</v>
       </c>
       <c r="K389">
-        <v>0.2833</v>
+        <v>0.2843</v>
       </c>
       <c r="L389">
-        <v>0.2241</v>
+        <v>0.2244</v>
       </c>
       <c r="M389">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N389" t="s">
         <v>74</v>
@@ -17735,25 +17735,25 @@
         <v>71</v>
       </c>
       <c r="G390">
-        <v>0.3891</v>
+        <v>0.3977</v>
       </c>
       <c r="H390">
-        <v>0.2265</v>
+        <v>0.2175</v>
       </c>
       <c r="I390">
-        <v>0.3078</v>
+        <v>0.3076</v>
       </c>
       <c r="J390">
-        <v>0.6109</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="K390">
-        <v>0.7735</v>
+        <v>0.7825</v>
       </c>
       <c r="L390">
-        <v>0.6922</v>
+        <v>0.6924</v>
       </c>
       <c r="M390">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N390" t="s">
         <v>74</v>
@@ -17779,25 +17779,25 @@
         <v>73</v>
       </c>
       <c r="G391">
-        <v>0.4816</v>
+        <v>0.4774</v>
       </c>
       <c r="H391">
-        <v>0.343</v>
+        <v>0.329</v>
       </c>
       <c r="I391">
-        <v>0.4123</v>
+        <v>0.4032</v>
       </c>
       <c r="J391">
-        <v>0.5184</v>
+        <v>0.5226</v>
       </c>
       <c r="K391">
-        <v>0.657</v>
+        <v>0.671</v>
       </c>
       <c r="L391">
-        <v>0.5877</v>
+        <v>0.5968</v>
       </c>
       <c r="M391">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N391" t="s">
         <v>74</v>
@@ -17823,25 +17823,25 @@
         <v>64</v>
       </c>
       <c r="G392">
-        <v>0.8058</v>
+        <v>0.8094</v>
       </c>
       <c r="H392">
         <v>0.6926</v>
       </c>
       <c r="I392">
-        <v>0.7492</v>
+        <v>0.751</v>
       </c>
       <c r="J392">
-        <v>0.1942</v>
+        <v>0.1906</v>
       </c>
       <c r="K392">
         <v>0.3074</v>
       </c>
       <c r="L392">
-        <v>0.2508</v>
+        <v>0.249</v>
       </c>
       <c r="M392">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N392" t="s">
         <v>74</v>
@@ -17885,7 +17885,7 @@
         <v>0.7382</v>
       </c>
       <c r="M393">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N393" t="s">
         <v>74</v>
@@ -17911,25 +17911,25 @@
         <v>66</v>
       </c>
       <c r="G394">
-        <v>0.2627</v>
+        <v>0.2563</v>
       </c>
       <c r="H394">
         <v>0.1961</v>
       </c>
       <c r="I394">
-        <v>0.2294</v>
+        <v>0.2262</v>
       </c>
       <c r="J394">
-        <v>0.7373</v>
+        <v>0.7437</v>
       </c>
       <c r="K394">
         <v>0.8038999999999999</v>
       </c>
       <c r="L394">
-        <v>0.7706</v>
+        <v>0.7738</v>
       </c>
       <c r="M394">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N394" t="s">
         <v>74</v>
@@ -17958,22 +17958,22 @@
         <v>0.476</v>
       </c>
       <c r="H395">
-        <v>0.3603</v>
+        <v>0.3574</v>
       </c>
       <c r="I395">
-        <v>0.4182</v>
+        <v>0.4167</v>
       </c>
       <c r="J395">
         <v>0.524</v>
       </c>
       <c r="K395">
-        <v>0.6397</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="L395">
-        <v>0.5818</v>
+        <v>0.5833</v>
       </c>
       <c r="M395">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N395" t="s">
         <v>74</v>
@@ -18017,7 +18017,7 @@
         <v>0.2655</v>
       </c>
       <c r="M396">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N396" t="s">
         <v>74</v>
@@ -18061,7 +18061,7 @@
         <v>0.2924</v>
       </c>
       <c r="M397">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N397" t="s">
         <v>74</v>
@@ -18105,7 +18105,7 @@
         <v>0.2333</v>
       </c>
       <c r="M398">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N398" t="s">
         <v>74</v>
@@ -18131,25 +18131,25 @@
         <v>71</v>
       </c>
       <c r="G399">
-        <v>0.3768</v>
+        <v>0.389</v>
       </c>
       <c r="H399">
-        <v>0.2311</v>
+        <v>0.2285</v>
       </c>
       <c r="I399">
-        <v>0.304</v>
+        <v>0.3088</v>
       </c>
       <c r="J399">
-        <v>0.6232</v>
+        <v>0.611</v>
       </c>
       <c r="K399">
-        <v>0.7689</v>
+        <v>0.7715</v>
       </c>
       <c r="L399">
-        <v>0.696</v>
+        <v>0.6912</v>
       </c>
       <c r="M399">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N399" t="s">
         <v>74</v>
@@ -18193,7 +18193,7 @@
         <v>0.5941</v>
       </c>
       <c r="M400">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N400" t="s">
         <v>74</v>
@@ -18237,7 +18237,7 @@
         <v>0.8355</v>
       </c>
       <c r="M401">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N401" t="s">
         <v>74</v>
@@ -18281,7 +18281,7 @@
         <v>0.834</v>
       </c>
       <c r="M402">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N402" t="s">
         <v>74</v>
@@ -18307,25 +18307,25 @@
         <v>67</v>
       </c>
       <c r="G403">
-        <v>0.2759</v>
+        <v>0.271</v>
       </c>
       <c r="H403">
         <v>0.148</v>
       </c>
       <c r="I403">
-        <v>0.2119</v>
+        <v>0.2095</v>
       </c>
       <c r="J403">
-        <v>0.7241</v>
+        <v>0.729</v>
       </c>
       <c r="K403">
         <v>0.852</v>
       </c>
       <c r="L403">
-        <v>0.7881</v>
+        <v>0.7905</v>
       </c>
       <c r="M403">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N403" t="s">
         <v>74</v>
@@ -18369,7 +18369,7 @@
         <v>0.5225</v>
       </c>
       <c r="M404">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N404" t="s">
         <v>74</v>
@@ -18413,7 +18413,7 @@
         <v>0.553</v>
       </c>
       <c r="M405">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N405" t="s">
         <v>74</v>
@@ -18457,7 +18457,7 @@
         <v>0.4601</v>
       </c>
       <c r="M406">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N406" t="s">
         <v>74</v>
@@ -18483,25 +18483,25 @@
         <v>71</v>
       </c>
       <c r="G407">
-        <v>0.2377</v>
+        <v>0.2361</v>
       </c>
       <c r="H407">
-        <v>0.1236</v>
+        <v>0.1253</v>
       </c>
       <c r="I407">
-        <v>0.1806</v>
+        <v>0.1807</v>
       </c>
       <c r="J407">
-        <v>0.7623</v>
+        <v>0.7639</v>
       </c>
       <c r="K407">
-        <v>0.8764</v>
+        <v>0.8747</v>
       </c>
       <c r="L407">
-        <v>0.8194</v>
+        <v>0.8193</v>
       </c>
       <c r="M407">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N407" t="s">
         <v>74</v>
@@ -18530,22 +18530,22 @@
         <v>0.2239</v>
       </c>
       <c r="H408">
-        <v>0.1495</v>
+        <v>0.145</v>
       </c>
       <c r="I408">
-        <v>0.1867</v>
+        <v>0.1844</v>
       </c>
       <c r="J408">
         <v>0.7761</v>
       </c>
       <c r="K408">
-        <v>0.8505</v>
+        <v>0.855</v>
       </c>
       <c r="L408">
-        <v>0.8133</v>
+        <v>0.8156</v>
       </c>
       <c r="M408">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N408" t="s">
         <v>74</v>
@@ -18571,25 +18571,25 @@
         <v>66</v>
       </c>
       <c r="G409">
-        <v>0.4759</v>
+        <v>0.4574</v>
       </c>
       <c r="H409">
-        <v>0.4121</v>
+        <v>0.4006</v>
       </c>
       <c r="I409">
-        <v>0.444</v>
+        <v>0.429</v>
       </c>
       <c r="J409">
-        <v>0.5241</v>
+        <v>0.5426</v>
       </c>
       <c r="K409">
-        <v>0.5879</v>
+        <v>0.5994</v>
       </c>
       <c r="L409">
-        <v>0.556</v>
+        <v>0.571</v>
       </c>
       <c r="M409">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N409" t="s">
         <v>74</v>
@@ -18615,25 +18615,25 @@
         <v>67</v>
       </c>
       <c r="G410">
-        <v>0.7569</v>
+        <v>0.7582</v>
       </c>
       <c r="H410">
-        <v>0.6078</v>
+        <v>0.6108</v>
       </c>
       <c r="I410">
-        <v>0.6824</v>
+        <v>0.6845</v>
       </c>
       <c r="J410">
-        <v>0.2431</v>
+        <v>0.2418</v>
       </c>
       <c r="K410">
-        <v>0.3922</v>
+        <v>0.3892</v>
       </c>
       <c r="L410">
-        <v>0.3176</v>
+        <v>0.3155</v>
       </c>
       <c r="M410">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N410" t="s">
         <v>74</v>
@@ -18677,7 +18677,7 @@
         <v>0.1812</v>
       </c>
       <c r="M411">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N411" t="s">
         <v>74</v>
@@ -18721,7 +18721,7 @@
         <v>0.1685</v>
       </c>
       <c r="M412">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N412" t="s">
         <v>74</v>
@@ -18747,25 +18747,25 @@
         <v>70</v>
       </c>
       <c r="G413">
-        <v>0.8848</v>
+        <v>0.8859</v>
       </c>
       <c r="H413">
         <v>0.7818000000000001</v>
       </c>
       <c r="I413">
-        <v>0.8333</v>
+        <v>0.8338</v>
       </c>
       <c r="J413">
-        <v>0.1152</v>
+        <v>0.1141</v>
       </c>
       <c r="K413">
         <v>0.2182</v>
       </c>
       <c r="L413">
-        <v>0.1667</v>
+        <v>0.1662</v>
       </c>
       <c r="M413">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N413" t="s">
         <v>74</v>
@@ -18791,25 +18791,25 @@
         <v>71</v>
       </c>
       <c r="G414">
-        <v>0.6175</v>
+        <v>0.6214</v>
       </c>
       <c r="H414">
-        <v>0.4862</v>
+        <v>0.4958</v>
       </c>
       <c r="I414">
-        <v>0.5518999999999999</v>
+        <v>0.5586</v>
       </c>
       <c r="J414">
-        <v>0.3825</v>
+        <v>0.3786</v>
       </c>
       <c r="K414">
-        <v>0.5138</v>
+        <v>0.5042</v>
       </c>
       <c r="L414">
-        <v>0.4481</v>
+        <v>0.4414</v>
       </c>
       <c r="M414">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N414" t="s">
         <v>74</v>
@@ -18853,7 +18853,7 @@
         <v>0.3456</v>
       </c>
       <c r="M415">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N415" t="s">
         <v>74</v>
@@ -18879,25 +18879,25 @@
         <v>67</v>
       </c>
       <c r="G416">
-        <v>0.78</v>
+        <v>0.7798</v>
       </c>
       <c r="H416">
-        <v>0.6652</v>
+        <v>0.6647</v>
       </c>
       <c r="I416">
-        <v>0.7226</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="J416">
-        <v>0.22</v>
+        <v>0.2202</v>
       </c>
       <c r="K416">
-        <v>0.3348</v>
+        <v>0.3353</v>
       </c>
       <c r="L416">
-        <v>0.2774</v>
+        <v>0.2777</v>
       </c>
       <c r="M416">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N416" t="s">
         <v>74</v>
@@ -18941,7 +18941,7 @@
         <v>0.1761</v>
       </c>
       <c r="M417">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N417" t="s">
         <v>74</v>
@@ -18970,22 +18970,22 @@
         <v>0.8724</v>
       </c>
       <c r="H418">
-        <v>0.7796999999999999</v>
+        <v>0.781</v>
       </c>
       <c r="I418">
-        <v>0.826</v>
+        <v>0.8267</v>
       </c>
       <c r="J418">
         <v>0.1276</v>
       </c>
       <c r="K418">
-        <v>0.2203</v>
+        <v>0.219</v>
       </c>
       <c r="L418">
-        <v>0.174</v>
+        <v>0.1733</v>
       </c>
       <c r="M418">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N418" t="s">
         <v>74</v>
@@ -19014,22 +19014,22 @@
         <v>0.8898</v>
       </c>
       <c r="H419">
-        <v>0.7868000000000001</v>
+        <v>0.7916</v>
       </c>
       <c r="I419">
-        <v>0.8383</v>
+        <v>0.8407</v>
       </c>
       <c r="J419">
         <v>0.1102</v>
       </c>
       <c r="K419">
-        <v>0.2132</v>
+        <v>0.2084</v>
       </c>
       <c r="L419">
-        <v>0.1617</v>
+        <v>0.1593</v>
       </c>
       <c r="M419">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N419" t="s">
         <v>74</v>
@@ -19055,25 +19055,25 @@
         <v>71</v>
       </c>
       <c r="G420">
-        <v>0.6826</v>
+        <v>0.6819</v>
       </c>
       <c r="H420">
-        <v>0.5557</v>
+        <v>0.54</v>
       </c>
       <c r="I420">
-        <v>0.6192</v>
+        <v>0.611</v>
       </c>
       <c r="J420">
-        <v>0.3174</v>
+        <v>0.3181</v>
       </c>
       <c r="K420">
-        <v>0.4443</v>
+        <v>0.46</v>
       </c>
       <c r="L420">
-        <v>0.3808</v>
+        <v>0.389</v>
       </c>
       <c r="M420">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N420" t="s">
         <v>74</v>
@@ -19099,25 +19099,25 @@
         <v>73</v>
       </c>
       <c r="G421">
-        <v>0.767</v>
+        <v>0.7802</v>
       </c>
       <c r="H421">
-        <v>0.6183</v>
+        <v>0.6312</v>
       </c>
       <c r="I421">
-        <v>0.6926</v>
+        <v>0.7057</v>
       </c>
       <c r="J421">
-        <v>0.233</v>
+        <v>0.2198</v>
       </c>
       <c r="K421">
-        <v>0.3817</v>
+        <v>0.3688</v>
       </c>
       <c r="L421">
-        <v>0.3074</v>
+        <v>0.2943</v>
       </c>
       <c r="M421">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N421" t="s">
         <v>74</v>
@@ -19161,7 +19161,7 @@
         <v>0.2331</v>
       </c>
       <c r="M422">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N422" t="s">
         <v>74</v>
@@ -19205,7 +19205,7 @@
         <v>0.2368</v>
       </c>
       <c r="M423">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N423" t="s">
         <v>74</v>
@@ -19249,7 +19249,7 @@
         <v>0.2026</v>
       </c>
       <c r="M424">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N424" t="s">
         <v>74</v>
@@ -19275,25 +19275,25 @@
         <v>71</v>
       </c>
       <c r="G425">
-        <v>0.3947</v>
+        <v>0.4016</v>
       </c>
       <c r="H425">
-        <v>0.3324</v>
+        <v>0.3287</v>
       </c>
       <c r="I425">
-        <v>0.3636</v>
+        <v>0.3651</v>
       </c>
       <c r="J425">
-        <v>0.6052999999999999</v>
+        <v>0.5984</v>
       </c>
       <c r="K425">
-        <v>0.6676</v>
+        <v>0.6713</v>
       </c>
       <c r="L425">
-        <v>0.6364</v>
+        <v>0.6349</v>
       </c>
       <c r="M425">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N425" t="s">
         <v>74</v>
@@ -19322,22 +19322,22 @@
         <v>0.5464</v>
       </c>
       <c r="H426">
-        <v>0.4205</v>
+        <v>0.4164</v>
       </c>
       <c r="I426">
-        <v>0.4834</v>
+        <v>0.4814</v>
       </c>
       <c r="J426">
         <v>0.4536</v>
       </c>
       <c r="K426">
-        <v>0.5795</v>
+        <v>0.5836</v>
       </c>
       <c r="L426">
-        <v>0.5165999999999999</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="M426">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N426" t="s">
         <v>74</v>
@@ -19381,7 +19381,7 @@
         <v>0.5329</v>
       </c>
       <c r="M427">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N427" t="s">
         <v>74</v>
@@ -19425,7 +19425,7 @@
         <v>0.425</v>
       </c>
       <c r="M428">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N428" t="s">
         <v>74</v>
@@ -19451,25 +19451,25 @@
         <v>71</v>
       </c>
       <c r="G429">
-        <v>0.2612</v>
+        <v>0.2617</v>
       </c>
       <c r="H429">
-        <v>0.1373</v>
+        <v>0.1423</v>
       </c>
       <c r="I429">
-        <v>0.1992</v>
+        <v>0.202</v>
       </c>
       <c r="J429">
-        <v>0.7388</v>
+        <v>0.7383</v>
       </c>
       <c r="K429">
-        <v>0.8627</v>
+        <v>0.8577</v>
       </c>
       <c r="L429">
-        <v>0.8008</v>
+        <v>0.798</v>
       </c>
       <c r="M429">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N429" t="s">
         <v>74</v>
@@ -19513,7 +19513,7 @@
         <v>0.7814</v>
       </c>
       <c r="M430">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N430" t="s">
         <v>74</v>
@@ -19557,7 +19557,7 @@
         <v>0.4189</v>
       </c>
       <c r="M431">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N431" t="s">
         <v>74</v>
@@ -19583,25 +19583,25 @@
         <v>71</v>
       </c>
       <c r="G432">
-        <v>0.2362</v>
+        <v>0.2419</v>
       </c>
       <c r="H432">
-        <v>0.1268</v>
+        <v>0.1301</v>
       </c>
       <c r="I432">
-        <v>0.1815</v>
+        <v>0.186</v>
       </c>
       <c r="J432">
-        <v>0.7638</v>
+        <v>0.7581</v>
       </c>
       <c r="K432">
-        <v>0.8732</v>
+        <v>0.8699</v>
       </c>
       <c r="L432">
-        <v>0.8185</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="M432">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N432" t="s">
         <v>74</v>
@@ -19627,25 +19627,25 @@
         <v>73</v>
       </c>
       <c r="G433">
-        <v>0.2817</v>
+        <v>0.2758</v>
       </c>
       <c r="H433">
         <v>0.1469</v>
       </c>
       <c r="I433">
-        <v>0.2143</v>
+        <v>0.2114</v>
       </c>
       <c r="J433">
-        <v>0.7183</v>
+        <v>0.7242</v>
       </c>
       <c r="K433">
         <v>0.8531</v>
       </c>
       <c r="L433">
-        <v>0.7857</v>
+        <v>0.7886</v>
       </c>
       <c r="M433">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N433" t="s">
         <v>74</v>
@@ -19671,25 +19671,25 @@
         <v>71</v>
       </c>
       <c r="G434">
-        <v>0.2367</v>
+        <v>0.2293</v>
       </c>
       <c r="H434">
-        <v>0.1316</v>
+        <v>0.1368</v>
       </c>
       <c r="I434">
-        <v>0.1841</v>
+        <v>0.183</v>
       </c>
       <c r="J434">
-        <v>0.7633</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="K434">
-        <v>0.8683999999999999</v>
+        <v>0.8632</v>
       </c>
       <c r="L434">
-        <v>0.8159</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="M434">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N434" t="s">
         <v>74</v>
@@ -19733,7 +19733,7 @@
         <v>0.8053</v>
       </c>
       <c r="M435">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N435" t="s">
         <v>74</v>
@@ -19759,25 +19759,25 @@
         <v>73</v>
       </c>
       <c r="G436">
-        <v>0.6721</v>
+        <v>0.6663</v>
       </c>
       <c r="H436">
-        <v>0.5437</v>
+        <v>0.5423</v>
       </c>
       <c r="I436">
-        <v>0.6079</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="J436">
-        <v>0.3279</v>
+        <v>0.3337</v>
       </c>
       <c r="K436">
-        <v>0.4563</v>
+        <v>0.4577</v>
       </c>
       <c r="L436">
-        <v>0.3921</v>
+        <v>0.3957</v>
       </c>
       <c r="M436">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N436" t="s">
         <v>74</v>
